--- a/Starlink_Usage_Current_by_Kit.xlsx
+++ b/Starlink_Usage_Current_by_Kit.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2593" uniqueCount="1132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2590" uniqueCount="1129">
   <si>
     <t xml:space="preserve">Company</t>
   </si>
@@ -154,6 +154,24 @@
     <t xml:space="preserve">Master Serial List</t>
   </si>
   <si>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 020955122 - KIT4P00073922FPF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4P00073922FPF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">814641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMAR-05900510-Los Angeles CA-020426442-KIT4P00065630DZT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4P00065630DZT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">807635</t>
+  </si>
+  <si>
     <t xml:space="preserve">SMS - 05900510 - Los Angeles CA - 021437232 - KIT4P00084602TKW</t>
   </si>
   <si>
@@ -163,15 +181,6 @@
     <t xml:space="preserve">816225</t>
   </si>
   <si>
-    <t xml:space="preserve">SMAR-05900510-Los Angeles CA-020426442-KIT4P00065630DZT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4P00065630DZT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">807635</t>
-  </si>
-  <si>
     <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 020955102 - KIT4P000739257CR</t>
   </si>
   <si>
@@ -190,13 +199,22 @@
     <t xml:space="preserve">814433</t>
   </si>
   <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 020955122 - KIT4P00073922FPF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4P00073922FPF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">814641</t>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021437292 - KIT4P000832806P4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4P000832806P4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles, CA - 021437242 - KIT4P00083890S2G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4P00083890S2G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816226</t>
   </si>
   <si>
     <t xml:space="preserve">SS - 05900510 - Los Angeles CA  - 020650002 - KIT4M05413770WCC</t>
@@ -208,22 +226,13 @@
     <t xml:space="preserve">812819</t>
   </si>
   <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021437292 - KIT4P000832806P4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4P000832806P4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles, CA - 021437242 - KIT4P00083890S2G</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4P00083890S2G</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816226</t>
+    <t xml:space="preserve">SMRT-05900510-Los Angeles CA-021437282-KIT4P00084593R9F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4P00084593R9F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816227</t>
   </si>
   <si>
     <t xml:space="preserve">SMS - 05900510 - Los Angeles CA - 020955082 - KIT4P000739124KF</t>
@@ -253,15 +262,6 @@
     <t xml:space="preserve">812842</t>
   </si>
   <si>
-    <t xml:space="preserve">SMRT-05900510-Los Angeles CA-021437282-KIT4P00084593R9F</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4P00084593R9F</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816227</t>
-  </si>
-  <si>
     <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 020955052 - KIT4P00073152MPN</t>
   </si>
   <si>
@@ -271,6 +271,15 @@
     <t xml:space="preserve">814494</t>
   </si>
   <si>
+    <t xml:space="preserve">STS - 05900510 - Los Angeles CA - 02048270111112 - KIT4P000655962DJ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4P000655962DJ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">809604</t>
+  </si>
+  <si>
     <t xml:space="preserve">SMS - 05900510 - Los Angeles CA - 020955072 - KIT4P0007258645B</t>
   </si>
   <si>
@@ -280,15 +289,6 @@
     <t xml:space="preserve">814495</t>
   </si>
   <si>
-    <t xml:space="preserve">STS - 05900510 - Los Angeles CA - 02048270111112 - KIT4P000655962DJ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4P000655962DJ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">809604</t>
-  </si>
-  <si>
     <t xml:space="preserve">SS - 05900510 - Los Angeles CA  - 020649242 - KIT4P00065644SB2</t>
   </si>
   <si>
@@ -325,6 +325,15 @@
     <t xml:space="preserve">809614</t>
   </si>
   <si>
+    <t xml:space="preserve">SMA - 05900510 - Los Angeles CA - 020955392 - KIT4M05563527J4C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05563527J4C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">814452</t>
+  </si>
+  <si>
     <t xml:space="preserve">STS - 05900510 - Los Angeles CA - 020482701110 - KIT4M041546939GJ</t>
   </si>
   <si>
@@ -334,15 +343,6 @@
     <t xml:space="preserve">809607</t>
   </si>
   <si>
-    <t xml:space="preserve">SMA - 05900510 - Los Angeles CA - 020955392 - KIT4M05563527J4C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05563527J4C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">814452</t>
-  </si>
-  <si>
     <t xml:space="preserve">SMRT-05900510-Los Angeles CA-020649462-KIT4M05413796V9K</t>
   </si>
   <si>
@@ -388,6 +388,24 @@
     <t xml:space="preserve">814441</t>
   </si>
   <si>
+    <t xml:space="preserve">SMS - 05900510 - Los Angeles CA - 020955322 - KIT4M055635305RS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M055635305RS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">814440</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STS - 05900510 - Los Angeles CA - 0204827018 - KIT4M0415609166K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M0415609166K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">809609</t>
+  </si>
+  <si>
     <t xml:space="preserve">SS - 05900510 - Los Angeles, CA - 020955622 - KIT4M05563549RSR</t>
   </si>
   <si>
@@ -397,6 +415,15 @@
     <t xml:space="preserve">814483</t>
   </si>
   <si>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 020649542 - KIT4M05413810Q4Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05413810Q4Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">812815</t>
+  </si>
+  <si>
     <t xml:space="preserve">SMRT-05900510-Los Angeles, CA-020955372-KIT4M05563537G4G</t>
   </si>
   <si>
@@ -406,31 +433,40 @@
     <t xml:space="preserve">814456</t>
   </si>
   <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 020649542 - KIT4M05413810Q4Z</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05413810Q4Z</t>
-  </si>
-  <si>
-    <t xml:space="preserve">812815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMS - 05900510 - Los Angeles CA - 020955322 - KIT4M055635305RS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M055635305RS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">814440</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STS - 05900510 - Los Angeles CA - 0204827018 - KIT4M0415609166K</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M0415609166K</t>
-  </si>
-  <si>
-    <t xml:space="preserve">809609</t>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 020955682 - KIT4M055635887MK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M055635887MK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">814446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021438032 - KIT4M05799683GCK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05799683GCK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816270</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021437252 - KIT4P00083897XCW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4P00083897XCW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 020649352 - KIT4M05368220FG8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05368220FG8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">810648</t>
   </si>
   <si>
     <t xml:space="preserve">SS - 05900510 - Los Angeles CA  - 020650212 - KIT4M05413779VSD</t>
@@ -442,15 +478,6 @@
     <t xml:space="preserve">810103</t>
   </si>
   <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 020955682 - KIT4M055635887MK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M055635887MK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">814446</t>
-  </si>
-  <si>
     <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021438042 - KIT4M05799686CMX</t>
   </si>
   <si>
@@ -460,6 +487,15 @@
     <t xml:space="preserve">816282</t>
   </si>
   <si>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 020955632 - KIT4M055635329VD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M055635329VD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">814479</t>
+  </si>
+  <si>
     <t xml:space="preserve">SS - 05900510 - Los Angeles CA  - 020650232 - KIT4M054138222CP</t>
   </si>
   <si>
@@ -469,6 +505,15 @@
     <t xml:space="preserve">812811</t>
   </si>
   <si>
+    <t xml:space="preserve">STS - 05900510 - Los Angeles CA - 02048270111110 - KIT4M03867737P9P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M03867737P9P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">809622</t>
+  </si>
+  <si>
     <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 020955552 - KIT4M055635475JB</t>
   </si>
   <si>
@@ -478,31 +523,31 @@
     <t xml:space="preserve">814465</t>
   </si>
   <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 020649352 - KIT4M05368220FG8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05368220FG8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">810648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 020955632 - KIT4M055635329VD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M055635329VD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">814479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STS - 05900510 - Los Angeles CA - 02048270111110 - KIT4M03867737P9P</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M03867737P9P</t>
-  </si>
-  <si>
-    <t xml:space="preserve">809622</t>
+    <t xml:space="preserve">STS - 05900510 - Los Angeles CA - 020482701116 - KIT4M03986275Q4M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M03986275Q4M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">809621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 020955472 - KIT4M055635834N7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M055635834N7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">814462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMS - 05900510 - Los Angeles CA - 020650172 - KIT4M05413811F4Q</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05413811F4Q</t>
+  </si>
+  <si>
+    <t xml:space="preserve">810104</t>
   </si>
   <si>
     <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 020955142 - KIT4M05563518ZJD</t>
@@ -523,15 +568,6 @@
     <t xml:space="preserve">814453</t>
   </si>
   <si>
-    <t xml:space="preserve">STS - 05900510 - Los Angeles CA - 020482701116 - KIT4M03986275Q4M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M03986275Q4M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">809621</t>
-  </si>
-  <si>
     <t xml:space="preserve">SMS - 05900510 - Los Angeles CA - 020649872 - KIT4M054138175VJ</t>
   </si>
   <si>
@@ -541,33 +577,6 @@
     <t xml:space="preserve">812823</t>
   </si>
   <si>
-    <t xml:space="preserve">SMS - 05900510 - Los Angeles CA - 020650172 - KIT4M05413811F4Q</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05413811F4Q</t>
-  </si>
-  <si>
-    <t xml:space="preserve">810104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 020955472 - KIT4M055635834N7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M055635834N7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">814462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021437252 - KIT4P00083897XCW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4P00083897XCW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816223</t>
-  </si>
-  <si>
     <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 020955332 - KIT4M05563590ZFQ</t>
   </si>
   <si>
@@ -577,6 +586,15 @@
     <t xml:space="preserve">814461</t>
   </si>
   <si>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA  - 020649842 - KIT4M025787739XF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M025787739XF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">809864</t>
+  </si>
+  <si>
     <t xml:space="preserve">SMS - 05900510 - Los Angeles CA - 020955092 - KIT4P00073957GV5</t>
   </si>
   <si>
@@ -586,15 +604,6 @@
     <t xml:space="preserve">814642</t>
   </si>
   <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021438032 - KIT4M05799683GCK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05799683GCK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816270</t>
-  </si>
-  <si>
     <t xml:space="preserve">SS - 05900510 - Los Angeles, CA - 020649562 - KIT4M054138125NW</t>
   </si>
   <si>
@@ -622,13 +631,22 @@
     <t xml:space="preserve">812800</t>
   </si>
   <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA  - 020649842 - KIT4M025787739XF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M025787739XF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">809864</t>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA  - 020650252 - KIT4M05413820QXJ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05413820QXJ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">810098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STS - 05900510 - Los Angeles CA - 0204827014 - KIT4M04475149XG5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M04475149XG5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">809657</t>
   </si>
   <si>
     <t xml:space="preserve">STS - 05900510 - Los Angeles CA - 020482702 - KIT4M04604743HSS</t>
@@ -640,6 +658,15 @@
     <t xml:space="preserve">809663</t>
   </si>
   <si>
+    <t xml:space="preserve">STS - 05900510 - Los Angeles CA - 020649342 - KIT4M05413775N9M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05413775N9M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">812818</t>
+  </si>
+  <si>
     <t xml:space="preserve">SMA - 05900510 - Los Angeles CA - 020650012 - KIT4M05413814GPJ</t>
   </si>
   <si>
@@ -649,33 +676,6 @@
     <t xml:space="preserve">812812</t>
   </si>
   <si>
-    <t xml:space="preserve">STS - 05900510 - Los Angeles CA - 020649342 - KIT4M05413775N9M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05413775N9M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">812818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA  - 020650252 - KIT4M05413820QXJ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05413820QXJ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">810098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STS - 05900510 - Los Angeles CA - 0204827014 - KIT4M04475149XG5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M04475149XG5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">809657</t>
-  </si>
-  <si>
     <t xml:space="preserve">STS - 05900510 - Los Angeles CA - 020482704 - KIT4M04604745G8Z</t>
   </si>
   <si>
@@ -685,6 +685,15 @@
     <t xml:space="preserve">809661</t>
   </si>
   <si>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 020955492 - KIT4M05563520SH2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05563520SH2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">814478</t>
+  </si>
+  <si>
     <t xml:space="preserve">SMA - 05900510 - Los Angeles CA - 020649902 - KIT4M05413805MKQ</t>
   </si>
   <si>
@@ -703,6 +712,15 @@
     <t xml:space="preserve">814474</t>
   </si>
   <si>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles, CA - 020649762 - KIT4M0460475549Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M0460475549Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">809859</t>
+  </si>
+  <si>
     <t xml:space="preserve">STS - 05900510 - Los Angeles CA - 02048270111114 - KIT4P00065593VWC</t>
   </si>
   <si>
@@ -712,6 +730,15 @@
     <t xml:space="preserve">809606</t>
   </si>
   <si>
+    <t xml:space="preserve">SMA - 05900510 - Los Angeles CA - 020955182 - KIT4M05563562F45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05563562F45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">814443</t>
+  </si>
+  <si>
     <t xml:space="preserve">SS - 05900510 - Los Angeles, CA - 020649552 - KIT4M05413835RPF </t>
   </si>
   <si>
@@ -721,13 +748,31 @@
     <t xml:space="preserve">812827</t>
   </si>
   <si>
-    <t xml:space="preserve">SMA - 05900510 - Los Angeles CA - 020955182 - KIT4M05563562F45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05563562F45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">814443</t>
+    <t xml:space="preserve">SMRT-05900510-LOS ANGELES CA-020955202-KIT4M05563534GZ7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05563534GZ7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">814467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STS - 05900510 - Los Angeles CA - 0204827011118 - KIT4M03867766NGK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M03867766NGK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">809615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 020650142 - KIT4M05413839D24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05413839D24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">810096</t>
   </si>
   <si>
     <t xml:space="preserve">STS - 05900510 - Los Angeles CA - 020649672 - KIT4M04606113TPB</t>
@@ -739,31 +784,22 @@
     <t xml:space="preserve">809862</t>
   </si>
   <si>
-    <t xml:space="preserve">STS - 05900510 - Los Angeles CA - 0204827011118 - KIT4M03867766NGK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M03867766NGK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">809615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMRT-05900510-LOS ANGELES CA-020955202-KIT4M05563534GZ7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05563534GZ7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">814467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles, CA - 020649762 - KIT4M0460475549Z</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M0460475549Z</t>
-  </si>
-  <si>
-    <t xml:space="preserve">809859</t>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - CW6578840- KIT4M04475128THH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M04475128THH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">809860</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 020955262 - KIT4M05563521ZSX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05563521ZSX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">814476</t>
   </si>
   <si>
     <t xml:space="preserve">STS - 05900510 - Los Angeles, CA - 0204827011112 - KIT4M04158967K28</t>
@@ -775,15 +811,6 @@
     <t xml:space="preserve">809620</t>
   </si>
   <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 020955262 - KIT4M05563521ZSX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05563521ZSX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">814476</t>
-  </si>
-  <si>
     <t xml:space="preserve">STS - 05900510 - Los Angeles CA - 020649812 - KIT4M04604742S6S</t>
   </si>
   <si>
@@ -829,6 +856,24 @@
     <t xml:space="preserve">814447</t>
   </si>
   <si>
+    <t xml:space="preserve">STS - 05900510 - Los Angeles CA - 02048270112 - KIT4M044751638F5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M044751638F5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">809618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMRT-05900510-Los Angeles, CA-020955452-KIT4M05563529K2D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05563529K2D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">814473</t>
+  </si>
+  <si>
     <t xml:space="preserve">SS  - 05900510 - Los Angeles CA - 020649932 - KIT4M054138324MW</t>
   </si>
   <si>
@@ -847,22 +892,13 @@
     <t xml:space="preserve">814484</t>
   </si>
   <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 020955492 - KIT4M05563520SH2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05563520SH2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">814478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 020650142 - KIT4M05413839D24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05413839D24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">810096</t>
+    <t xml:space="preserve">STS - 05900510 - Los Angeles CA - 02048270116 - KIT4M03476116F45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M03476116F45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">809608</t>
   </si>
   <si>
     <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 020955602 - KIT4M05563560225</t>
@@ -883,31 +919,13 @@
     <t xml:space="preserve">812803</t>
   </si>
   <si>
-    <t xml:space="preserve">SMRT-05900510-Los Angeles, CA-020955452-KIT4M05563529K2D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05563529K2D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">814473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STS - 05900510 - Los Angeles CA - 02048270112 - KIT4M044751638F5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M044751638F5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">809618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STS - 05900510 - Los Angeles CA - 02048270116 - KIT4M03476116F45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M03476116F45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">809608</t>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles, CA - 020649782 - KIT4M03986264P49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M03986264P49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">809875</t>
   </si>
   <si>
     <t xml:space="preserve">SMRT-05900510-Los Angeles, CA-020955582-KIT4M05563593DMC</t>
@@ -919,13 +937,40 @@
     <t xml:space="preserve">814442</t>
   </si>
   <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - CW6578840- KIT4M04475128THH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M04475128THH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">809860</t>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 020955272 - KIT4M05563585TXM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05563585TXM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">814475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS - 05900510 -  Los Angeles CA - 020955382 - KIT4M05563509CHJ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05563509CHJ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">814431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMRT-05900510-Los Angeles CA-020650202-KIT4M05413803FDK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05413803FDK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">812850</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles, CA - 020649412 - KIT4M05413769796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05413769796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">812839</t>
   </si>
   <si>
     <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 020955132 - KIT4M055635238J6</t>
@@ -937,33 +982,6 @@
     <t xml:space="preserve">814449</t>
   </si>
   <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles, CA - 020649412 - KIT4M05413769796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05413769796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">812839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMRT-05900510-Los Angeles CA-020650202-KIT4M05413803FDK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05413803FDK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">812850</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS - 05900510 -  Los Angeles CA - 020955382 - KIT4M05563509CHJ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05563509CHJ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">814431</t>
-  </si>
-  <si>
     <t xml:space="preserve">SS - 05900510 - Los Angeles, CA - 020649942 - KIT4M05413786BXC</t>
   </si>
   <si>
@@ -973,6 +991,24 @@
     <t xml:space="preserve">812838</t>
   </si>
   <si>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 020955692 - KIT4M05563579H9F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05563579H9F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">814480</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMRT-05900510-Los Angeles, CA-020955352-KIT4M05563525VC6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05563525VC6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">814458</t>
+  </si>
+  <si>
     <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 020649372 - KIT4M05368221HQ5</t>
   </si>
   <si>
@@ -991,13 +1027,31 @@
     <t xml:space="preserve">814432</t>
   </si>
   <si>
-    <t xml:space="preserve">SMRT-05900510-Los Angeles, CA-020955352-KIT4M05563525VC6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05563525VC6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">814458</t>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 020955292 - KIT4M05563531XSB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05563531XSB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">814469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMS - 05900510 - Los Angeles CA - 020955522 - KIT4M05563504MBB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05563504MBB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">814460</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 020650102 - KIT4M054138257Z7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M054138257Z7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">810106</t>
   </si>
   <si>
     <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 020650112 - KIT4M05413840D9J</t>
@@ -1009,6 +1063,15 @@
     <t xml:space="preserve">810099</t>
   </si>
   <si>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021438092 - KIT4M05799694RW2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05799694RW2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816277</t>
+  </si>
+  <si>
     <t xml:space="preserve">STS - 05900510 - Los Angeles CA - 020649742 - KIT4M04350554X4Z</t>
   </si>
   <si>
@@ -1018,15 +1081,6 @@
     <t xml:space="preserve">809866</t>
   </si>
   <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 020955272 - KIT4M05563585TXM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05563585TXM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">814475</t>
-  </si>
-  <si>
     <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 020955342 - KIT4M05563524MJ4</t>
   </si>
   <si>
@@ -1036,6 +1090,15 @@
     <t xml:space="preserve">814472</t>
   </si>
   <si>
+    <t xml:space="preserve">STS - 05900510 - Los Angeles CA - 020482706 - KIT4M04604744V6K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M04604744V6K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">809659</t>
+  </si>
+  <si>
     <t xml:space="preserve">SMS - 05900510 - Los Angeles CA - 020649362 - KIT4M05368336DBC</t>
   </si>
   <si>
@@ -1054,13 +1117,31 @@
     <t xml:space="preserve">814435</t>
   </si>
   <si>
-    <t xml:space="preserve">STS - 05900510 - Los Angeles CA - 020482706 - KIT4M04604744V6K</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M04604744V6K</t>
-  </si>
-  <si>
-    <t xml:space="preserve">809659</t>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021437392 - KIT4M05872555BJR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05872555BJR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMA - 05900510 - Los Angeles CA - 021437782 - KIT4M058724975J4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M058724975J4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMS - 05900510 - Los Angeles CA - 020955112 - KIT4P00073918HBX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4P00073918HBX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">814645</t>
   </si>
   <si>
     <t xml:space="preserve">SS  - 05900510 - Los Angeles CA - 020650162 - KIT4M05413837SMB</t>
@@ -1072,33 +1153,6 @@
     <t xml:space="preserve">810100</t>
   </si>
   <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021437392 - KIT4M05872555BJR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05872555BJR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 020955692 - KIT4M05563579H9F</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05563579H9F</t>
-  </si>
-  <si>
-    <t xml:space="preserve">814480</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 020955292 - KIT4M05563531XSB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05563531XSB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">814469</t>
-  </si>
-  <si>
     <t xml:space="preserve">SMRT-05900510-Los Angeles CA-020650132-KIT4M05413828PCT</t>
   </si>
   <si>
@@ -1135,33 +1189,6 @@
     <t xml:space="preserve">812795</t>
   </si>
   <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021438092 - KIT4M05799694RW2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05799694RW2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMA - 05900510 - Los Angeles CA - 021437782 - KIT4M058724975J4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M058724975J4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 020650102 - KIT4M054138257Z7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M054138257Z7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">810106</t>
-  </si>
-  <si>
     <t xml:space="preserve">SS  - 05900510 - Los Angeles CA - 020649302 - KIT4M05368226W57</t>
   </si>
   <si>
@@ -1171,6 +1198,15 @@
     <t xml:space="preserve">810833</t>
   </si>
   <si>
+    <t xml:space="preserve">SMA - 05900510 - Los Angeles CA - 020649912 - KIT4M05413836KJC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05413836KJC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">810097</t>
+  </si>
+  <si>
     <t xml:space="preserve">SMS - 05900510 - Los Angeles CA - 020650242 - KIT4M05413804SKS</t>
   </si>
   <si>
@@ -1216,13 +1252,31 @@
     <t xml:space="preserve">809873</t>
   </si>
   <si>
-    <t xml:space="preserve">SMA - 05900510 - Los Angeles CA - 020649912 - KIT4M05413836KJC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05413836KJC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">810097</t>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 6858375 - KIT4M05872512N5W</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05872512N5W</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA  - 020649682 - KIT4M046047384RX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M046047384RX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">809870</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMRT-05900510-Los Angeles CA-020649292-KIT4M05368201SNV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05368201SNV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">810651</t>
   </si>
   <si>
     <t xml:space="preserve">STS - 05900510 - Los Angeles CA - 020482701112 - KIT4M04158973M2C</t>
@@ -1234,40 +1288,31 @@
     <t xml:space="preserve">809610</t>
   </si>
   <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 6858375 - KIT4M05872512N5W</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05872512N5W</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMRT-05900510-Los Angeles CA-020649292-KIT4M05368201SNV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05368201SNV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">810651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles, CA - 020649782 - KIT4M03986264P49</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M03986264P49</t>
-  </si>
-  <si>
-    <t xml:space="preserve">809875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA  - 020649682 - KIT4M046047384RX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M046047384RX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">809870</t>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021438002 - KIT4M05799701SGS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05799701SGS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles, CA - 020649592 - KIT4M05413787HHK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05413787HHK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">812809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 020649712 - KIT4M046047397TM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M046047397TM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">809863</t>
   </si>
   <si>
     <t xml:space="preserve">STS - 05900510 - Los Angeles CA - 020482708 - KIT4M04604736T7C</t>
@@ -1297,22 +1342,31 @@
     <t xml:space="preserve">812784</t>
   </si>
   <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles, CA - 020649592 - KIT4M05413787HHK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05413787HHK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">812809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMS - 05900510 - Los Angeles CA - 020955112 - KIT4P00073918HBX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4P00073918HBX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">814645</t>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA  - 020649222 - KIT4P00065640BFW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4P00065640BFW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">812929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS  - 05900510 - Los Angeles CA - 020649532 - KIT4M05413808FFZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05413808FFZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">812828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 020649632 - KIT4M054138064J9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M054138064J9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">812844</t>
   </si>
   <si>
     <t xml:space="preserve">SS  - 05900510 - Los Angeles CA - 020649442 - KIT4M054137885SM</t>
@@ -1324,6 +1378,15 @@
     <t xml:space="preserve">812846</t>
   </si>
   <si>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 020650042 - KIT4M05413819JV5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05413819JV5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">812796</t>
+  </si>
+  <si>
     <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 020955712 - KIT4M05563586ZTR</t>
   </si>
   <si>
@@ -1333,49 +1396,22 @@
     <t xml:space="preserve">814445</t>
   </si>
   <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 020649712 - KIT4M046047397TM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M046047397TM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">809863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS  - 05900510 - Los Angeles CA - 020649532 - KIT4M05413808FFZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05413808FFZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">812828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 020649632 - KIT4M054138064J9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M054138064J9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">812844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021438002 - KIT4M05799701SGS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05799701SGS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA  - 020649222 - KIT4P00065640BFW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4P00065640BFW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">812929</t>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 020955362 - KIT4M05563528MKX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05563528MKX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">814471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021438222 - KIT4M058725299QP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M058725299QP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816080</t>
   </si>
   <si>
     <t xml:space="preserve">SS - 05900510 - Los Angeles CA  - 020650152 - KIT4M054138189C7</t>
@@ -1396,15 +1432,6 @@
     <t xml:space="preserve">814437</t>
   </si>
   <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021438222 - KIT4M058725299QP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M058725299QP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816080</t>
-  </si>
-  <si>
     <t xml:space="preserve">SS - 05900510 - Los Angeles CA  - 020649582 - KIT4M05413774JZX</t>
   </si>
   <si>
@@ -1414,6 +1441,15 @@
     <t xml:space="preserve">812836</t>
   </si>
   <si>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021438072 - KIT4M057996885ZV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M057996885ZV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816269</t>
+  </si>
+  <si>
     <t xml:space="preserve">SS  - 05900510 - Los Angeles CA - 020649282 - KIT4M05368213974</t>
   </si>
   <si>
@@ -1432,6 +1468,15 @@
     <t xml:space="preserve">814455</t>
   </si>
   <si>
+    <t xml:space="preserve">SMRT-05900510-Los Angeles CA-020650122-KIT4M05413776H84</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05413776H84</t>
+  </si>
+  <si>
+    <t xml:space="preserve">810101</t>
+  </si>
+  <si>
     <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 020955502 - KIT4M05563502GJS</t>
   </si>
   <si>
@@ -1441,6 +1486,15 @@
     <t xml:space="preserve">814470</t>
   </si>
   <si>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021437992 -  KIT4M05799663CPM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05799663CPM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816272</t>
+  </si>
+  <si>
     <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 020955252 - KIT4M05563584FVC</t>
   </si>
   <si>
@@ -1450,40 +1504,13 @@
     <t xml:space="preserve">814439</t>
   </si>
   <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021438072 - KIT4M057996885ZV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M057996885ZV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMRT-05900510-Los Angeles CA-020650122-KIT4M05413776H84</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05413776H84</t>
-  </si>
-  <si>
-    <t xml:space="preserve">810101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 020955362 - KIT4M05563528MKX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05563528MKX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">814471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021437992 -  KIT4M05799663CPM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05799663CPM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816272</t>
+    <t xml:space="preserve">SMA - 05900510 -  Los Angeles CA - 020649512 - KIT4M054138318Q7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M054138318Q7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">812814</t>
   </si>
   <si>
     <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 020649252 - KIT4P00066848VQM</t>
@@ -1504,6 +1531,24 @@
     <t xml:space="preserve">809867</t>
   </si>
   <si>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles, CA - 020955432 - KIT4M05563533M9N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05563533M9N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">814485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMA - 05900510 - Los Angeles CA - 020955482 - KIT4M055635088NK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M055635088NK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">814434</t>
+  </si>
+  <si>
     <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 020955402 - KIT4M05563610HM2</t>
   </si>
   <si>
@@ -1522,15 +1567,6 @@
     <t xml:space="preserve">812804</t>
   </si>
   <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 020650042 - KIT4M05413819JV5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05413819JV5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">812796</t>
-  </si>
-  <si>
     <t xml:space="preserve">STS - 05900510 - Los Angeles CA - 0204827011110 - KIT4M03866627GHD</t>
   </si>
   <si>
@@ -1540,15 +1576,6 @@
     <t xml:space="preserve">809619</t>
   </si>
   <si>
-    <t xml:space="preserve">SMA - 05900510 - Los Angeles CA - 020955482 - KIT4M055635088NK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M055635088NK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">814434</t>
-  </si>
-  <si>
     <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 020650182 - KIT4M05413821GGW</t>
   </si>
   <si>
@@ -1558,22 +1585,22 @@
     <t xml:space="preserve">812830</t>
   </si>
   <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles, CA - 020955432 - KIT4M05563533M9N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05563533M9N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">814485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMA - 05900510 -  Los Angeles CA - 020649512 - KIT4M054138318Q7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M054138318Q7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">812814</t>
+    <t xml:space="preserve">SS - 05900510 -  Los Angeles CA - 021437622 - KIT4M0587258755W</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M0587258755W</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS  - 05900510 - Los Angeles CA - 020650262 - KIT4M054138249M8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M054138249M8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">812794</t>
   </si>
   <si>
     <t xml:space="preserve">SS - 05900510 - Los Angeles, CA - 020649962 - KIT4M05413783PFQ</t>
@@ -1585,13 +1612,31 @@
     <t xml:space="preserve">812845</t>
   </si>
   <si>
-    <t xml:space="preserve">SMS - 05900510 - Los Angeles CA - 020955522 - KIT4M05563504MBB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05563504MBB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">814460</t>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 020649492 - KIT4M054138074NS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M054138074NS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">812816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STS - 05900510 - Los Angeles CA - 0204827010 - KIT4M046047372KJ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M046047372KJ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">809658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STS - 05900510 - Los Angeles CA - 020649832 - KIT4M03866596RZG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M03866596RZG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">809869</t>
   </si>
   <si>
     <t xml:space="preserve">SMA - 05900510 - Los Angeles CA - 020649732 - KIT4M046047467T4</t>
@@ -1603,22 +1648,13 @@
     <t xml:space="preserve">809865</t>
   </si>
   <si>
-    <t xml:space="preserve">STS - 05900510 - Los Angeles CA - 0204827010 - KIT4M046047372KJ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M046047372KJ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">809658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 020649492 - KIT4M054138074NS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M054138074NS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">812816</t>
+    <t xml:space="preserve">SMA - 05900510 - Los Angeles CA - 020649322 - KIT4M053683324KZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M053683324KZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">810832</t>
   </si>
   <si>
     <t xml:space="preserve">STS - 05900510 - Los Angeles CA - 0204827016 - KIT4M041536494G6</t>
@@ -1657,6 +1693,15 @@
     <t xml:space="preserve">809616</t>
   </si>
   <si>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 020649822 - KIT4M04604740BM6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M04604740BM6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">809872</t>
+  </si>
+  <si>
     <t xml:space="preserve">STS - 05900510 - Los Angeles CA - 0204827012 - KIT4M04606110GTV</t>
   </si>
   <si>
@@ -1666,13 +1711,13 @@
     <t xml:space="preserve">809660</t>
   </si>
   <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 020649822 - KIT4M04604740BM6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M04604740BM6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">809872</t>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021437932 - KIT4M05799732NQK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05799732NQK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816275</t>
   </si>
   <si>
     <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021437612 - KIT4M058725265DP</t>
@@ -1684,6 +1729,15 @@
     <t xml:space="preserve">816192</t>
   </si>
   <si>
+    <t xml:space="preserve">SMA - 05900510 - Los Angeles CA - 020955152 - KIT4M05563514P8T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05563514P8T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">814436</t>
+  </si>
+  <si>
     <t xml:space="preserve">SMS - 05900510 - Los Angeles CA - 020649852 - KIT4M05413789Z8C</t>
   </si>
   <si>
@@ -1711,24 +1765,6 @@
     <t xml:space="preserve">816085</t>
   </si>
   <si>
-    <t xml:space="preserve">SMA - 05900510 - Los Angeles CA - 020955152 - KIT4M05563514P8T</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05563514P8T</t>
-  </si>
-  <si>
-    <t xml:space="preserve">814436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021437932 - KIT4M05799732NQK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05799732NQK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816275</t>
-  </si>
-  <si>
     <t xml:space="preserve">SSC - 05900510 - Los Angeles CA - 021437792 - KIT4M05872507528</t>
   </si>
   <si>
@@ -1738,13 +1774,13 @@
     <t xml:space="preserve">816083</t>
   </si>
   <si>
-    <t xml:space="preserve">SS - 05900510 -  Los Angeles CA - 021437622 - KIT4M0587258755W</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M0587258755W</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816187</t>
+    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491800F52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M06491800F52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816406</t>
   </si>
   <si>
     <t xml:space="preserve">SMRT-05900510-Los Angeles CA-021437812-KIT4M058724947VX</t>
@@ -1765,6 +1801,15 @@
     <t xml:space="preserve">816107</t>
   </si>
   <si>
+    <t xml:space="preserve">STS - 05900510 - Los Angeles CA - 02048270110 - KIT4M038677586ZX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M038677586ZX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">809623</t>
+  </si>
+  <si>
     <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 6862083  - KIT4M05799682BXX</t>
   </si>
   <si>
@@ -1783,6 +1828,15 @@
     <t xml:space="preserve">816088</t>
   </si>
   <si>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 6862083  - KIT4M057996395ZF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M057996395ZF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816268</t>
+  </si>
+  <si>
     <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021438172 - KIT4M05872500684</t>
   </si>
   <si>
@@ -1792,15 +1846,6 @@
     <t xml:space="preserve">816081</t>
   </si>
   <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 6862083  - KIT4M057996395ZF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M057996395ZF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816268</t>
-  </si>
-  <si>
     <t xml:space="preserve">SMA - 05900510 - Los Angeles CA - 021437412 - KIT4M05872548P2H</t>
   </si>
   <si>
@@ -1810,6 +1855,33 @@
     <t xml:space="preserve">816066</t>
   </si>
   <si>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021438022 - KIT4M05799705T6B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05799705T6B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021438282 - KIT4M05872508VTN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05872508VTN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS - 05900510 -  Los Angeles CA - 021438232 - KIT4M05872520QJM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05872520QJM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816078</t>
+  </si>
+  <si>
     <t xml:space="preserve">SMA - 05900510 - Los Angeles CA - 021437302 - KIT4M05872571T4K</t>
   </si>
   <si>
@@ -1819,31 +1891,49 @@
     <t xml:space="preserve">816106</t>
   </si>
   <si>
-    <t xml:space="preserve">SS - 05900510 -  Los Angeles CA - 021438232 - KIT4M05872520QJM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05872520QJM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021438282 - KIT4M05872508VTN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05872508VTN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021438022 - KIT4M05799705T6B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05799705T6B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816285</t>
+    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918277QF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M064918277QF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021437732 - KIT4M05872588W8G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05872588W8G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS - 05900510 -  Los Angeles CA - 021438182 - KIT4M05872528P9D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05872528P9D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021438252 - KIT4M05872519KTN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05872519KTN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021437312 - KIT4M05872568PR6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05872568PR6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816094</t>
   </si>
   <si>
     <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021437722 - KIT4M05872498PP4</t>
@@ -1855,40 +1945,58 @@
     <t xml:space="preserve">816104</t>
   </si>
   <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021437312 - KIT4M05872568PR6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05872568PR6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS - 05900510 -  Los Angeles CA - 021438182 - KIT4M05872528P9D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05872528P9D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021437732 - KIT4M05872588W8G</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05872588W8G</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021438252 - KIT4M05872519KTN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05872519KTN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816084</t>
+    <t xml:space="preserve">SMRT-05900510-Los Angeles CA-021437482-KIT4M05872578G7Q</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05872578G7Q</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021437362 - KIT4M05872574NKX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05872574NKX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021437752 - KIT4M05872577TWT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05872577TWT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021437462 - KIT4M05872575BC8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05872575BC8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021437502 - KIT4M058725695CN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M058725695CN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021437952 - KIT4M05872523VVB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05872523VVB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816215</t>
   </si>
   <si>
     <t xml:space="preserve">SMRT-05900510-Los Angeles CA-021437822-KIT4M0587253378R</t>
@@ -1909,13 +2017,85 @@
     <t xml:space="preserve">816079</t>
   </si>
   <si>
-    <t xml:space="preserve">SMRT-05900510-Los Angeles CA-021437482-KIT4M05872578G7Q</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05872578G7Q</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816102</t>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021438112 - KIT4M0579970825J</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M0579970825J</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816290</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491798S8Q</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M06491798S8Q</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491829CD2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M06491829CD2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918197VX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M064918197VX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491786BS9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M06491786BS9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021437802 - KIT4M05872589TM9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05872589TM9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064917914G5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M064917914G5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021437332 - KIT4M05872554RHM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05872554RHM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491799CRP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M06491799CRP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816394</t>
   </si>
   <si>
     <t xml:space="preserve">SMRT-05900510-Los Angeles CA-021437712-KIT4M05872570FCC</t>
@@ -1927,24 +2107,6 @@
     <t xml:space="preserve">816105</t>
   </si>
   <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021438112 - KIT4M0579970825J</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M0579970825J</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816290</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021437332 - KIT4M05872554RHM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05872554RHM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816071</t>
-  </si>
-  <si>
     <t xml:space="preserve">SMRT-05900510-Los Angeles CA-021437882-KIT4M05872527QK6</t>
   </si>
   <si>
@@ -1954,42 +2116,6 @@
     <t xml:space="preserve">816214</t>
   </si>
   <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021437362 - KIT4M05872574NKX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05872574NKX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021437752 - KIT4M05872577TWT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05872577TWT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021437462 - KIT4M05872575BC8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05872575BC8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021437502 - KIT4M058725695CN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M058725695CN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816101</t>
-  </si>
-  <si>
     <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021437692 - KIT4M05872518P78</t>
   </si>
   <si>
@@ -1999,6 +2125,24 @@
     <t xml:space="preserve">816184</t>
   </si>
   <si>
+    <t xml:space="preserve">SSC - 05900510 -  Los Angeles CA - 021437862 - KIT4M05872516CJM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05872516CJM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMRT-05900510-Los Angeles CA-021437352-KIT4M05872545Q8H</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05872545Q8H</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816112</t>
+  </si>
+  <si>
     <t xml:space="preserve">SMS - 05900510 - Los Angeles CA - 021437342 - KIT4M05872557NFB</t>
   </si>
   <si>
@@ -2008,40 +2152,58 @@
     <t xml:space="preserve">816095</t>
   </si>
   <si>
-    <t xml:space="preserve">SMRT-05900510-Los Angeles CA-021437352-KIT4M05872545Q8H</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05872545Q8H</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSC - 05900510 -  Los Angeles CA - 021437862 - KIT4M05872516CJM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05872516CJM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021437802 - KIT4M05872589TM9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05872589TM9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021437952 - KIT4M05872523VVB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05872523VVB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816215</t>
+    <t xml:space="preserve">SS - 05900510 -  Los Angeles CA - 021437682 - KIT4M05872544BXG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05872544BXG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMS - 05900510 - Los Angeles CA - 020649892 - KIT4M05413777DGG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05413777DGG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">812802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021438192 - KIT4M05872511F6P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05872511F6P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816090</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 020955542 - KIT4M05563551N6Q</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05563551N6Q</t>
+  </si>
+  <si>
+    <t xml:space="preserve">814450</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021438082 - KIT4M05799668SS7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05799668SS7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMA - 05900510 - Los Angeles CA - 021437402 - KIT4M05872537SGZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05872537SGZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816073</t>
   </si>
   <si>
     <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021437662 - KIT4M05872534RXS</t>
@@ -2053,15 +2215,6 @@
     <t xml:space="preserve">816216</t>
   </si>
   <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021438082 - KIT4M05799668SS7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05799668SS7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816279</t>
-  </si>
-  <si>
     <t xml:space="preserve">SMS - 05900510 - Los Angeles CA - 021437372 - KIT4M058725505J5</t>
   </si>
   <si>
@@ -2071,33 +2224,6 @@
     <t xml:space="preserve">816117</t>
   </si>
   <si>
-    <t xml:space="preserve">SMA - 05900510 - Los Angeles CA - 021437402 - KIT4M05872537SGZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05872537SGZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021438192 - KIT4M05872511F6P</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05872511F6P</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816090</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS - 05900510 -  Los Angeles CA - 021437682 - KIT4M05872544BXG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05872544BXG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816176</t>
-  </si>
-  <si>
     <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021437572 - KIT4M05872579JPF</t>
   </si>
   <si>
@@ -2116,6 +2242,15 @@
     <t xml:space="preserve">816222</t>
   </si>
   <si>
+    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491808P4F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M06491808P4F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816399</t>
+  </si>
+  <si>
     <t xml:space="preserve">SS - 05900510 - Los Angeles, CA  - 020649572 - KIT4M05413816N8K</t>
   </si>
   <si>
@@ -2125,13 +2260,31 @@
     <t xml:space="preserve">812832</t>
   </si>
   <si>
-    <t xml:space="preserve">SS  - 05900510 - Los Angeles CA - 020650262 - KIT4M054138249M8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M054138249M8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">812794</t>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021438162 - KIT4M05799712SBX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05799712SBX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918239TM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M064918239TM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491796QQN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M06491796QQN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816405</t>
   </si>
   <si>
     <t xml:space="preserve">SMA - 05900510 - Los Angeles CA - 021437382 - KIT4M058725438WP</t>
@@ -2143,13 +2296,58 @@
     <t xml:space="preserve">816115</t>
   </si>
   <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021438162 - KIT4M05799712SBX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05799712SBX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816276</t>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021437742 - KIT4M05872539ZMR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05872539ZMR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021437512 - KIT4M05872559VR9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05872559VR9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMA - 05900510 - Los Angeles CA - 021437322 - KIT4M05872567V72</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05872567V72</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021437472 - KIT4M05872565VJK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05872565VJK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021437912 - KIT4M05872525NP5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05872525NP5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021437522 - KIT4M05872576R4B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05872576R4B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816110</t>
   </si>
   <si>
     <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021437432 - KIT4M0587256692N</t>
@@ -2161,6 +2359,123 @@
     <t xml:space="preserve">816072</t>
   </si>
   <si>
+    <t xml:space="preserve">SMS - 05900510 - Los Angeles CA - 020955422 - KIT4M05563517BVR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05563517BVR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">814438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA  - 020649212 - KIT4P00065633ZXC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4P00065633ZXC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">812922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021437962 - KIT4M05799706Z6R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05799706Z6R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021438292 - KIt4m058725108K2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M058725108K2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMRT-05900510-Los Angeles CA-021437842-KIT4M05872547MK2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05872547MK2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021437542 - KIT4M05872553WFR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05872553WFR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021437442 - KIT4M05872584M6H</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05872584M6H</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA  - 021437562 - KIT4M05872583P58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05872583P58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491809ZR6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M06491809ZR6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491803672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M06491803672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021437552 - KIT4M05872586VCH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05872586VCH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021437672 - KIT4M05872531DSZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05872531DSZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS - 05900510 -  Los Angeles CA - 021437602 - KIT4M05872524CFG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05872524CFG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816205</t>
+  </si>
+  <si>
     <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021437582 - KIT4M05872573K7P</t>
   </si>
   <si>
@@ -2179,166 +2494,148 @@
     <t xml:space="preserve">816118</t>
   </si>
   <si>
-    <t xml:space="preserve">SMRT-05900510-Los Angeles CA-021437842-KIT4M05872547MK2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05872547MK2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021437542 - KIT4M05872553WFR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05872553WFR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021437962 - KIT4M05799706Z6R</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05799706Z6R</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021438292 - KIt4m058725108K2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M058725108K2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMS - 05900510 - Los Angeles CA - 020955422 - KIT4M05563517BVR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05563517BVR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">814438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA  - 020649212 - KIT4P00065633ZXC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4P00065633ZXC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">812922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMA - 05900510 - Los Angeles CA - 021437322 - KIT4M05872567V72</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05872567V72</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021437472 - KIT4M05872565VJK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05872565VJK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS - 05900510 -  Los Angeles CA - 021437602 - KIT4M05872524CFG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05872524CFG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021437912 - KIT4M05872525NP5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05872525NP5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMA - 05900510 - Los Angeles CA - 020649322 - KIT4M053683324KZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M053683324KZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">810832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA  - 021437562 - KIT4M05872583P58</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05872583P58</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021437442 - KIT4M05872584M6H</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05872584M6H</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021437552 - KIT4M05872586VCH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05872586VCH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021437522 - KIT4M05872576R4B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05872576R4B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816110</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021437672 - KIT4M05872531DSZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05872531DSZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021437742 - KIT4M05872539ZMR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05872539ZMR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021437512 - KIT4M05872559VR9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05872559VR9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816114</t>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021438052 - KIT4M05872522W7W</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05872522W7W</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021437652 - KIT4M05872551G9S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05872551G9S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816180</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 020649392 - KIT4M05368206BZP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05368206BZP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">810645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMS - 05900510 - Los Angeles CA - 020649382 - KIT4M05368219KRH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05368219KRH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">810646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMS - 05900510 - Los Angeles CA -021437942 - KIT4M05799709G5Q</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05799709G5Q</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021438142  - KIT4M05799685DG5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05799685DG5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 020650022 - KIT4M05413813HSJ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05413813HSJ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">812797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 020955642 - KIT4M05563573WKC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05563573WKC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">814488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021438152 - KIT4M05799733FPK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05799733FPK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021438062 - KIT4M05799676NNK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05799676NNK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021437702 - KIT4M05872515PJT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05872515PJT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021437982 - KIT4M05799678R5P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05799678R5P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMA - 05900510 - Los Angeles CA - 020649772 - KIT4M04475152RGR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M04475152RGR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">809861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMS - 05900510 - Los Angeles CA - 021437902 - KIT4M05799717WZV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05799717WZV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816280</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMA - 05900510 - Los Angeles CA - 020955042 - KIT4P00072391SZM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4P00072391SZM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">814493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles, CA - 020955312 - KIT4M0556351956H</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M0556351956H</t>
+  </si>
+  <si>
+    <t xml:space="preserve">814477</t>
   </si>
   <si>
     <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021438212 - KIT4M058725047FZ</t>
@@ -2350,31 +2647,67 @@
     <t xml:space="preserve">816289</t>
   </si>
   <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021438152 - KIT4M05799733FPK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05799733FPK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMS - 05900510 - Los Angeles CA - 021437902 - KIT4M05799717WZV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05799717WZV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816280</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021437702 - KIT4M05872515PJT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05872515PJT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816218</t>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021438272 - KIT4M05872517VS2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05872517VS2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMA - 05900510 - Los Angeles CA - 021437492 - KIT4M0587256196K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M0587256196K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064917936NF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M064917936NF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021437972 - KIT4M06490327GMP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M06490327GMP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMS - 05900510 - Los Angeles CA - 021437872 - KIT4M06490319DDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M06490319DDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816220</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMS - 05900510 - Los Angeles CA - 021437892 - KIT4M06490321NJX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M06490321NJX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918068FF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M064918068FF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816400</t>
   </si>
   <si>
     <t xml:space="preserve">SS - 05900510 - Los Angeles, CA - 021437852 - KIT4M0587257292W</t>
@@ -2386,6 +2719,15 @@
     <t xml:space="preserve">816207</t>
   </si>
   <si>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles, CA - 021437772 - KIT4M05872563FWB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05872563FWB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816208</t>
+  </si>
+  <si>
     <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021437762 - KIT4M05872564MCF</t>
   </si>
   <si>
@@ -2395,22 +2737,13 @@
     <t xml:space="preserve">816203</t>
   </si>
   <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles, CA - 021437772 - KIT4M05872563FWB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05872563FWB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021437972 - KIT4M06490327GMP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M06490327GMP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816199</t>
+    <t xml:space="preserve">SMS - 05900510 - Los Angeles CA - 021437452 - KIT4M05872580C6X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05872580C6X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816097</t>
   </si>
   <si>
     <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021437262 - KIT4P0008460369B</t>
@@ -2422,121 +2755,13 @@
     <t xml:space="preserve">816224</t>
   </si>
   <si>
-    <t xml:space="preserve">SMS - 05900510 - Los Angeles CA - 021437452 - KIT4M05872580C6X</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05872580C6X</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMS - 05900510 - Los Angeles CA - 021437872 - KIT4M06490319DDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M06490319DDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816220</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMS - 05900510 - Los Angeles CA - 021437892 - KIT4M06490321NJX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M06490321NJX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021438062 - KIT4M05799676NNK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05799676NNK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021437982 - KIT4M05799678R5P</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05799678R5P</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STS - 05900510 - Los Angeles CA - 02048270110 - KIT4M038677586ZX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M038677586ZX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">809623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMS - 05900510 - Los Angeles CA -021437942 - KIT4M05799709G5Q</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05799709G5Q</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMA - 05900510 - Los Angeles CA - 021437492 - KIT4M0587256196K</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M0587256196K</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021438272 - KIT4M05872517VS2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05872517VS2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021438052 - KIT4M05872522W7W</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05872522W7W</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021437652 - KIT4M05872551G9S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05872551G9S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816180</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 020650022 - KIT4M05413813HSJ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05413813HSJ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">812797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021438142  - KIT4M05799685DG5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05799685DG5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816271</t>
+    <t xml:space="preserve">SMRT-05900510-Los Angeles CA-020649472-KIT4M05413795QHK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05413795QHK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">812801</t>
   </si>
   <si>
     <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021437642 - KIT4M05872590N8X</t>
@@ -2557,6 +2782,24 @@
     <t xml:space="preserve">812807</t>
   </si>
   <si>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021438102 - KIT4M05872513F7N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05872513F7N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STS - 05900510 - Los Angeles CA - 02048270114 - KIT4M04476539RJ5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M04476539RJ5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">809612</t>
+  </si>
+  <si>
     <t xml:space="preserve">SS - 05900510 - Los Angeles, CA - 020649702 - KIT4M04604741P2X</t>
   </si>
   <si>
@@ -2575,22 +2818,154 @@
     <t xml:space="preserve">812927</t>
   </si>
   <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021438102 - KIT4M05872513F7N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05872513F7N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STS - 05900510 - Los Angeles CA - 02048270114 - KIT4M04476539RJ5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M04476539RJ5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">809612</t>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021438202 - KIT4M05872506TTB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05872506TTB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021438012 - KIT4M05799715GJ2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05799715GJ2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMRT-05900510-Los Angeles CA-020650032-KIT4M05413802FVN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05413802FVN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">812813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021437922 - KIT4M05872496MW6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05872496MW6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMS - 05900510 - Los Angeles CA - 020649502 - KIT4M05413801QJB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05413801QJB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">812824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMS - 05900510 - Los Angeles CA - 020955222 - KIT4M05563536BPJ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05563536BPJ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">814466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 020955162 - KIT4M05563554WCW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05563554WCW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">814444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 020650062 - KIT4M05413797HK5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05413797HK5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">812808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles, CA - 020649482 - KIT4M054137938P7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M054137938P7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">812848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS  - 05900510 - Los Angeles CA - 020650222 - KIT4M05413790XCD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05413790XCD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">812822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS - 05900510 -  Los Angeles CA - 020955572 - KIT4M05563606ZRC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05563606ZRC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">814464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles, CA - 020649992 - KIT4M05413809J58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05413809J58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">812805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STS - 05900510 - Los Angeles CA - 020650092 - KIT4M05413830JN7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05413830JN7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">810105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 020955442 - KIT4M05563503XXP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05563503XXP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">814430</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 020955562 - KIT4M05563505WPS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05563505WPS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">814448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STS - 05900510 - Los Angeles CA - 020649982 - KIT4M05413823B5P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05413823B5P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">812837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918322GZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M064918322GZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816414</t>
   </si>
   <si>
     <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 020649802 - KIT4M04604734ZZX</t>
@@ -2602,49 +2977,85 @@
     <t xml:space="preserve">809876</t>
   </si>
   <si>
-    <t xml:space="preserve">SMA - 05900510 - Los Angeles CA - 020649772 - KIT4M04475152RGR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M04475152RGR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">809861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles, CA - 020649482 - KIT4M054137938P7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M054137938P7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">812848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMRT-05900510-Los Angeles CA-020650032-KIT4M05413802FVN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05413802FVN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">812813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles, CA - 020649992 - KIT4M05413809J58</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05413809J58</t>
-  </si>
-  <si>
-    <t xml:space="preserve">812805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMS - 05900510 - Los Angeles CA - 020649502 - KIT4M05413801QJB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05413801QJB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">812824</t>
+    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M0649183125S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M0649183125S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491836Z2D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M06491836Z2D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491835TD6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M06491835TD6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491837DPX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M06491837DPX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491833JGV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M06491833JGV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMRT-05900510-Los Angeles CA-020649522-KIT4M05413834FTH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05413834FTH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">812817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMA - 05900510 - Los Angeles CA - 020426432 - KIT4P00066070HN4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4P00066070HN4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">807636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918346DB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M064918346DB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 020649612 - KIT4M05413827DC4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05413827DC4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">812829</t>
   </si>
   <si>
     <t xml:space="preserve">SMS - 05900510 - Los Angeles CA - 020955512 - KIT4M055635779MM</t>
@@ -2656,262 +3067,13 @@
     <t xml:space="preserve">814487</t>
   </si>
   <si>
-    <t xml:space="preserve">SS - 05900510 -  Los Angeles CA - 020955572 - KIT4M05563606ZRC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05563606ZRC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">814464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918346DB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M064918346DB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491833JGV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M06491833JGV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918322GZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M064918322GZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M0649183125S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M0649183125S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491837DPX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M06491837DPX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491836Z2D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M06491836Z2D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491835TD6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M06491835TD6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMA - 05900510 - Los Angeles CA - 020426432 - KIT4P00066070HN4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4P00066070HN4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">807636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STS - 05900510 - Los Angeles CA - 020649982 - KIT4M05413823B5P</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05413823B5P</t>
-  </si>
-  <si>
-    <t xml:space="preserve">812837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMA - 05900510 - Los Angeles CA - 020955042 - KIT4P00072391SZM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4P00072391SZM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">814493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 020649612 - KIT4M05413827DC4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05413827DC4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">812829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STS - 05900510 - Los Angeles CA - 020650092 - KIT4M05413830JN7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05413830JN7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">810105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 020955442 - KIT4M05563503XXP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05563503XXP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">814430</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMRT-05900510-Los Angeles CA-020649522-KIT4M05413834FTH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05413834FTH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">812817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 020955562 - KIT4M05563505WPS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05563505WPS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">814448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles, CA - 020955312 - KIT4M0556351956H</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M0556351956H</t>
-  </si>
-  <si>
-    <t xml:space="preserve">814477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021437922 - KIT4M05872496MW6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05872496MW6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021438202 - KIT4M05872506TTB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05872506TTB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 021438012 - KIT4M05799715GJ2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05799715GJ2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS  - 05900510 - Los Angeles CA - 020650222 - KIT4M05413790XCD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05413790XCD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">812822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 020955642 - KIT4M05563573WKC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05563573WKC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">814488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMS - 05900510 - Los Angeles CA - 020955222 - KIT4M05563536BPJ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05563536BPJ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">814466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 020955542 - KIT4M05563551N6Q</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05563551N6Q</t>
-  </si>
-  <si>
-    <t xml:space="preserve">814450</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 020955162 - KIT4M05563554WCW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05563554WCW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">814444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 020650062 - KIT4M05413797HK5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05413797HK5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">812808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMRT-05900510-Los Angeles CA-020649472-KIT4M05413795QHK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05413795QHK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">812801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMS - 05900510 - Los Angeles CA - 020649382 - KIT4M05368219KRH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05368219KRH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">810646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 020649392 - KIT4M05368206BZP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05368206BZP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">810645</t>
+    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 020649662 - KIT4M05413772977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05413772977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">812841</t>
   </si>
   <si>
     <t xml:space="preserve">SMS - 05900510 - Los Angeles CA - 020649332 - KIT4M05368340DMZ</t>
@@ -2923,15 +3085,6 @@
     <t xml:space="preserve">810649</t>
   </si>
   <si>
-    <t xml:space="preserve">SMS - 05900510 - Los Angeles CA - 020649892 - KIT4M05413777DGG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05413777DGG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">812802</t>
-  </si>
-  <si>
     <t xml:space="preserve">SS - 05900510 - Los Angeles CA - 020649952 - KIT4M05413782GHW</t>
   </si>
   <si>
@@ -2941,15 +3094,6 @@
     <t xml:space="preserve">812835</t>
   </si>
   <si>
-    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 020649662 - KIT4M05413772977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05413772977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">812841</t>
-  </si>
-  <si>
     <t xml:space="preserve">STS - 05900510 - Los Angeles CA - 020649922 - KIT4M05413780XFH</t>
   </si>
   <si>
@@ -2959,13 +3103,31 @@
     <t xml:space="preserve">812833</t>
   </si>
   <si>
-    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064917914G5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M064917914G5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816392</t>
+    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491805F7Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M06491805F7Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491802BZV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M06491802BZV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816390</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491804TBC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M06491804TBC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816373</t>
   </si>
   <si>
     <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064917925MB</t>
@@ -2977,13 +3139,31 @@
     <t xml:space="preserve">816381</t>
   </si>
   <si>
-    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064917936NF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M064917936NF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816404</t>
+    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491794MTJ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M06491794MTJ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491795MWG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M06491795MWG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491797NCX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M06491797NCX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816408</t>
   </si>
   <si>
     <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491790945</t>
@@ -2995,58 +3175,22 @@
     <t xml:space="preserve">816410</t>
   </si>
   <si>
-    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491795MWG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M06491795MWG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491796QQN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M06491796QQN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491797NCX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M06491797NCX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491798S8Q</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M06491798S8Q</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491799CRP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M06491799CRP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491800F52</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M06491800F52</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816406</t>
+    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491789PJ6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M06491789PJ6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS - 05900510 -  Los Angeles CA - 021437632 - KIT4M05872585HZZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M05872585HZZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816211</t>
   </si>
   <si>
     <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918015Z2</t>
@@ -3058,85 +3202,31 @@
     <t xml:space="preserve">816376</t>
   </si>
   <si>
-    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491794MTJ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M06491794MTJ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS - 05900510 -  Los Angeles CA - 021437632 - KIT4M05872585HZZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M05872585HZZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491786BS9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M06491786BS9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491789PJ6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M06491789PJ6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491805F7Z</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M06491805F7Z</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491804TBC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M06491804TBC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491803672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M06491803672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491802BZV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M06491802BZV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816390</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918068FF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M064918068FF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816400</t>
+    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M0649181062D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M0649181062D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491811JB5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M06491811JB5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491812JDV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M06491812JDV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816409</t>
   </si>
   <si>
     <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491807TRH</t>
@@ -3148,22 +3238,58 @@
     <t xml:space="preserve">816386</t>
   </si>
   <si>
-    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491808P4F</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M06491808P4F</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491809ZR6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M06491809ZR6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816402</t>
+    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491821G25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M06491821G25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491820X58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M06491820X58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491818QD2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M06491818QD2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491817T79</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M06491817T79</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918154FM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M064918154FM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918165MW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M064918165MW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816374</t>
   </si>
   <si>
     <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491814FV7</t>
@@ -3175,60 +3301,6 @@
     <t xml:space="preserve">816370</t>
   </si>
   <si>
-    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918154FM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M064918154FM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918165MW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M064918165MW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491817T79</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M06491817T79</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M0649181062D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M0649181062D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491811JB5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M06491811JB5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491812JDV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M06491812JDV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816409</t>
-  </si>
-  <si>
     <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491813KGS</t>
   </si>
   <si>
@@ -3238,40 +3310,40 @@
     <t xml:space="preserve">816377</t>
   </si>
   <si>
-    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491821G25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M06491821G25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491820X58</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M06491820X58</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918197VX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M064918197VX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491818QD2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M06491818QD2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816378</t>
+    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491828XWF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M06491828XWF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491826SQM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M06491826SQM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491824JCK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M06491824JCK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491825PF9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT4M06491825PF9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816367</t>
   </si>
   <si>
     <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491822SF6</t>
@@ -3283,78 +3355,6 @@
     <t xml:space="preserve">816412</t>
   </si>
   <si>
-    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918239TM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M064918239TM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491824JCK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M06491824JCK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491825PF9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M06491825PF9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491829CD2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M06491829CD2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491828XWF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M06491828XWF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918277QF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M064918277QF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491826SQM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M06491826SQM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816380</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STS - 05900510 - Los Angeles CA - 020649832 - KIT4M03866596RZG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT4M03866596RZG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">809869</t>
-  </si>
-  <si>
     <t xml:space="preserve">SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491830G2J</t>
   </si>
   <si>
@@ -3388,49 +3388,41 @@
     <t xml:space="preserve">Notes</t>
   </si>
   <si>
-    <t xml:space="preserve">Ecode resolved from SmartSource_Starlink_Main_Tracker__1_.xlsx first, then Starlink_Master_Serial_Number.xlsx.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The two sources carry identical eCodes on every kit they share, so the merge introduced no conflicts.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ecode Source names which file supplied each value. Shaded Ecode cells have no code in either source.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Master file lists KIT4P00065641GDF as KIT4P000656451GDF (one extra character); corrected here on the</t>
-  </si>
-  <si>
-    <t xml:space="preserve">strength of its matching eCode 812924. The typo should be fixed at the source.</t>
+    <t xml:space="preserve">One row per kit, deduplicated to each kit's most recent billing period.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ecode resolved from SmartSource_Starlink_Main_Tracker.xlsx first, then Starlink_Master_Serial_Number.xlsx.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The two sources carry identical eCodes on every kit they share. Shaded cells have no code in either.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Master file lists KIT4P00065641GDF as KIT4P000656451GDF (one extra character); corrected here.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plan Amount is set to 50 GB for every kit - all kits pool at 50 GB regardless of what the export lists.</t>
   </si>
   <si>
     <t xml:space="preserve">Model is derived from the kit serial prefix: KIT4M = Mini, KIT4P = G3 HPERF.</t>
   </si>
   <si>
-    <t xml:space="preserve">The total row sums the pooled allowance (kits x 50 GB) and total usage, and counts kits and mapped eCodes.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plan Amount is set to 50 GB for every kit. The source usage export listed 295 kits at 50 GB,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59 at 500 GB, and 13 blank; all were normalized to 50 GB.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">One row per kit, deduplicated to each kit's latest billing period (2026-08-01 to 2026-09-01 for all 367).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">August 2026 is an in-progress period. Usage is what has been recorded to date, not a completed month.</t>
+    <t xml:space="preserve">Ecode Source names which file supplied each code.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Totals are stored in GB and display in TB past 1,000 GB (decimal, 1 TB = 1,000 GB).</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0"/>
     <numFmt numFmtId="166" formatCode="@"/>
     <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="168" formatCode="#,##0.00;\-;\-"/>
+    <numFmt numFmtId="169" formatCode="[&gt;=1000]#,##0.00,&quot; TB&quot;;#,##0.00&quot; GB&quot;"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -3556,7 +3548,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3597,15 +3589,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3613,8 +3601,8 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
@@ -3914,7 +3902,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M382"/>
+  <dimension ref="A1:M379"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13"/>
@@ -4006,7 +3994,7 @@
       </c>
       <c r="L2" s="5"/>
       <c r="M2" s="7" t="n">
-        <v>2256.38</v>
+        <v>2258.31</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4045,7 +4033,7 @@
       </c>
       <c r="L3" s="5"/>
       <c r="M3" s="7" t="n">
-        <v>2064.26</v>
+        <v>2218.24</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4084,7 +4072,7 @@
       </c>
       <c r="L4" s="5"/>
       <c r="M4" s="7" t="n">
-        <v>1581.24</v>
+        <v>1595.08</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4123,7 +4111,7 @@
       </c>
       <c r="L5" s="5"/>
       <c r="M5" s="7" t="n">
-        <v>1062.15</v>
+        <v>1062.48</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4279,7 +4267,7 @@
       </c>
       <c r="L9" s="5"/>
       <c r="M9" s="7" t="n">
-        <v>696.24</v>
+        <v>703.79</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4318,7 +4306,7 @@
       </c>
       <c r="L10" s="5"/>
       <c r="M10" s="7" t="n">
-        <v>603.4</v>
+        <v>660.55</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4357,7 +4345,7 @@
       </c>
       <c r="L11" s="5"/>
       <c r="M11" s="7" t="n">
-        <v>597.23</v>
+        <v>639.94</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4396,7 +4384,7 @@
       </c>
       <c r="L12" s="5"/>
       <c r="M12" s="7" t="n">
-        <v>579.42</v>
+        <v>603.4</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4419,7 +4407,7 @@
         <v>54</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="H13" s="5" t="s">
         <v>18</v>
@@ -4435,7 +4423,7 @@
       </c>
       <c r="L13" s="5"/>
       <c r="M13" s="7" t="n">
-        <v>555.46</v>
+        <v>579.42</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4458,7 +4446,7 @@
         <v>57</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="H14" s="5" t="s">
         <v>18</v>
@@ -4474,7 +4462,7 @@
       </c>
       <c r="L14" s="5"/>
       <c r="M14" s="7" t="n">
-        <v>491.43</v>
+        <v>577.77</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4497,7 +4485,7 @@
         <v>60</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="H15" s="5" t="s">
         <v>18</v>
@@ -4513,7 +4501,7 @@
       </c>
       <c r="L15" s="5"/>
       <c r="M15" s="7" t="n">
-        <v>462.9</v>
+        <v>521.04</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4552,7 +4540,7 @@
       </c>
       <c r="L16" s="5"/>
       <c r="M16" s="7" t="n">
-        <v>429.4</v>
+        <v>508.16</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4575,7 +4563,7 @@
         <v>66</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="H17" s="5" t="s">
         <v>18</v>
@@ -4591,7 +4579,7 @@
       </c>
       <c r="L17" s="5"/>
       <c r="M17" s="7" t="n">
-        <v>420.68</v>
+        <v>462.9</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4630,7 +4618,7 @@
       </c>
       <c r="L18" s="5"/>
       <c r="M18" s="7" t="n">
-        <v>413.08</v>
+        <v>437.85</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4653,7 +4641,7 @@
         <v>72</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="H19" s="5" t="s">
         <v>18</v>
@@ -4669,7 +4657,7 @@
       </c>
       <c r="L19" s="5"/>
       <c r="M19" s="7" t="n">
-        <v>386.13</v>
+        <v>413.08</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4708,7 +4696,7 @@
       </c>
       <c r="L20" s="5"/>
       <c r="M20" s="7" t="n">
-        <v>380.11</v>
+        <v>403.43</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4731,7 +4719,7 @@
         <v>78</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="H21" s="5" t="s">
         <v>18</v>
@@ -4747,7 +4735,7 @@
       </c>
       <c r="L21" s="5"/>
       <c r="M21" s="7" t="n">
-        <v>360.21</v>
+        <v>380.11</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4786,7 +4774,7 @@
       </c>
       <c r="L22" s="5"/>
       <c r="M22" s="7" t="n">
-        <v>342.3</v>
+        <v>353.1</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4812,7 +4800,7 @@
         <v>17</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I23" s="6" t="n">
         <v>46235</v>
@@ -4825,7 +4813,7 @@
       </c>
       <c r="L23" s="5"/>
       <c r="M23" s="7" t="n">
-        <v>335.8</v>
+        <v>337.02</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4851,7 +4839,7 @@
         <v>17</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I24" s="6" t="n">
         <v>46235</v>
@@ -4864,7 +4852,7 @@
       </c>
       <c r="L24" s="5"/>
       <c r="M24" s="7" t="n">
-        <v>325.26</v>
+        <v>335.8</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4981,7 +4969,7 @@
       </c>
       <c r="L27" s="5"/>
       <c r="M27" s="7" t="n">
-        <v>254.32</v>
+        <v>259.89</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5046,7 +5034,7 @@
         <v>38</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I29" s="6" t="n">
         <v>46235</v>
@@ -5059,7 +5047,7 @@
       </c>
       <c r="L29" s="5"/>
       <c r="M29" s="7" t="n">
-        <v>246.3</v>
+        <v>250.03</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5085,7 +5073,7 @@
         <v>38</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I30" s="6" t="n">
         <v>46235</v>
@@ -5098,7 +5086,7 @@
       </c>
       <c r="L30" s="5"/>
       <c r="M30" s="7" t="n">
-        <v>245.67</v>
+        <v>246.3</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5176,7 +5164,7 @@
       </c>
       <c r="L32" s="5"/>
       <c r="M32" s="7" t="n">
-        <v>162.81</v>
+        <v>166.94</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5215,7 +5203,7 @@
       </c>
       <c r="L33" s="5"/>
       <c r="M33" s="7" t="n">
-        <v>143.18</v>
+        <v>160.36</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5293,7 +5281,7 @@
       </c>
       <c r="L35" s="5"/>
       <c r="M35" s="7" t="n">
-        <v>125.74</v>
+        <v>125.83</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5332,7 +5320,7 @@
       </c>
       <c r="L36" s="5"/>
       <c r="M36" s="7" t="n">
-        <v>111.45</v>
+        <v>120.64</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5358,7 +5346,7 @@
         <v>38</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I37" s="6" t="n">
         <v>46235</v>
@@ -5371,7 +5359,7 @@
       </c>
       <c r="L37" s="5"/>
       <c r="M37" s="7" t="n">
-        <v>108.22</v>
+        <v>116.87</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5410,7 +5398,7 @@
       </c>
       <c r="L38" s="5"/>
       <c r="M38" s="7" t="n">
-        <v>107.61</v>
+        <v>113.16</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5449,7 +5437,7 @@
       </c>
       <c r="L39" s="5"/>
       <c r="M39" s="7" t="n">
-        <v>105.55</v>
+        <v>109.69</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5475,7 +5463,7 @@
         <v>38</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I40" s="6" t="n">
         <v>46235</v>
@@ -5488,7 +5476,7 @@
       </c>
       <c r="L40" s="5"/>
       <c r="M40" s="7" t="n">
-        <v>104.21</v>
+        <v>108.22</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5514,7 +5502,7 @@
         <v>38</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I41" s="6" t="n">
         <v>46235</v>
@@ -5527,7 +5515,7 @@
       </c>
       <c r="L41" s="5"/>
       <c r="M41" s="7" t="n">
-        <v>96.01</v>
+        <v>108</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5566,7 +5554,7 @@
       </c>
       <c r="L42" s="5"/>
       <c r="M42" s="7" t="n">
-        <v>95.05</v>
+        <v>104.07</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5589,7 +5577,7 @@
         <v>144</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="H43" s="5" t="s">
         <v>18</v>
@@ -5605,7 +5593,7 @@
       </c>
       <c r="L43" s="5"/>
       <c r="M43" s="7" t="n">
-        <v>93.38</v>
+        <v>101.3</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5631,7 +5619,7 @@
         <v>38</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I44" s="6" t="n">
         <v>46235</v>
@@ -5644,7 +5632,7 @@
       </c>
       <c r="L44" s="5"/>
       <c r="M44" s="7" t="n">
-        <v>92.69</v>
+        <v>99.77</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5670,7 +5658,7 @@
         <v>38</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I45" s="6" t="n">
         <v>46235</v>
@@ -5683,7 +5671,7 @@
       </c>
       <c r="L45" s="5"/>
       <c r="M45" s="7" t="n">
-        <v>88.88</v>
+        <v>96.01</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5709,7 +5697,7 @@
         <v>38</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I46" s="6" t="n">
         <v>46235</v>
@@ -5722,7 +5710,7 @@
       </c>
       <c r="L46" s="5"/>
       <c r="M46" s="7" t="n">
-        <v>88.57</v>
+        <v>94.22</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5761,7 +5749,7 @@
       </c>
       <c r="L47" s="5"/>
       <c r="M47" s="7" t="n">
-        <v>87.97</v>
+        <v>93.1</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5787,7 +5775,7 @@
         <v>38</v>
       </c>
       <c r="H48" s="5" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I48" s="6" t="n">
         <v>46235</v>
@@ -5800,7 +5788,7 @@
       </c>
       <c r="L48" s="5"/>
       <c r="M48" s="7" t="n">
-        <v>86.29</v>
+        <v>92.69</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5826,7 +5814,7 @@
         <v>38</v>
       </c>
       <c r="H49" s="5" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I49" s="6" t="n">
         <v>46235</v>
@@ -5839,7 +5827,7 @@
       </c>
       <c r="L49" s="5"/>
       <c r="M49" s="7" t="n">
-        <v>85.1</v>
+        <v>91.98</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5878,7 +5866,7 @@
       </c>
       <c r="L50" s="5"/>
       <c r="M50" s="7" t="n">
-        <v>84.98</v>
+        <v>89.81</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5917,7 +5905,7 @@
       </c>
       <c r="L51" s="5"/>
       <c r="M51" s="7" t="n">
-        <v>84.38</v>
+        <v>87.13</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5956,7 +5944,7 @@
       </c>
       <c r="L52" s="5"/>
       <c r="M52" s="7" t="n">
-        <v>83.05</v>
+        <v>86.98</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5995,7 +5983,7 @@
       </c>
       <c r="L53" s="5"/>
       <c r="M53" s="7" t="n">
-        <v>82.2</v>
+        <v>86.22</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6034,7 +6022,7 @@
       </c>
       <c r="L54" s="5"/>
       <c r="M54" s="7" t="n">
-        <v>81.22</v>
+        <v>85.18</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6057,7 +6045,7 @@
         <v>180</v>
       </c>
       <c r="G55" s="5" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="H55" s="5" t="s">
         <v>18</v>
@@ -6073,7 +6061,7 @@
       </c>
       <c r="L55" s="5"/>
       <c r="M55" s="7" t="n">
-        <v>75.32</v>
+        <v>84.98</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6112,7 +6100,7 @@
       </c>
       <c r="L56" s="5"/>
       <c r="M56" s="7" t="n">
-        <v>74.5</v>
+        <v>83.95</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6135,7 +6123,7 @@
         <v>186</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="H57" s="5" t="s">
         <v>18</v>
@@ -6151,7 +6139,7 @@
       </c>
       <c r="L57" s="5"/>
       <c r="M57" s="7" t="n">
-        <v>72.83</v>
+        <v>77.59</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6177,7 +6165,7 @@
         <v>38</v>
       </c>
       <c r="H58" s="5" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I58" s="6" t="n">
         <v>46235</v>
@@ -6190,7 +6178,7 @@
       </c>
       <c r="L58" s="5"/>
       <c r="M58" s="7" t="n">
-        <v>67.46</v>
+        <v>77.14</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6213,7 +6201,7 @@
         <v>192</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="H59" s="5" t="s">
         <v>18</v>
@@ -6229,7 +6217,7 @@
       </c>
       <c r="L59" s="5"/>
       <c r="M59" s="7" t="n">
-        <v>67.21</v>
+        <v>72.83</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6268,7 +6256,7 @@
       </c>
       <c r="L60" s="5"/>
       <c r="M60" s="7" t="n">
-        <v>66.06</v>
+        <v>67.84</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6307,7 +6295,7 @@
       </c>
       <c r="L61" s="5"/>
       <c r="M61" s="7" t="n">
-        <v>61.57</v>
+        <v>66.06</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6333,7 +6321,7 @@
         <v>38</v>
       </c>
       <c r="H62" s="5" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I62" s="6" t="n">
         <v>46235</v>
@@ -6346,7 +6334,7 @@
       </c>
       <c r="L62" s="5"/>
       <c r="M62" s="7" t="n">
-        <v>61.24</v>
+        <v>61.57</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6385,7 +6373,7 @@
       </c>
       <c r="L63" s="5"/>
       <c r="M63" s="7" t="n">
-        <v>59.03</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6411,7 +6399,7 @@
         <v>38</v>
       </c>
       <c r="H64" s="5" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I64" s="6" t="n">
         <v>46235</v>
@@ -6424,7 +6412,7 @@
       </c>
       <c r="L64" s="5"/>
       <c r="M64" s="7" t="n">
-        <v>58.94</v>
+        <v>59.43</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6450,7 +6438,7 @@
         <v>38</v>
       </c>
       <c r="H65" s="5" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I65" s="6" t="n">
         <v>46235</v>
@@ -6463,7 +6451,7 @@
       </c>
       <c r="L65" s="5"/>
       <c r="M65" s="7" t="n">
-        <v>58.62</v>
+        <v>59.03</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6489,7 +6477,7 @@
         <v>38</v>
       </c>
       <c r="H66" s="5" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I66" s="6" t="n">
         <v>46235</v>
@@ -6502,7 +6490,7 @@
       </c>
       <c r="L66" s="5"/>
       <c r="M66" s="7" t="n">
-        <v>55.43</v>
+        <v>58.97</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6528,7 +6516,7 @@
         <v>38</v>
       </c>
       <c r="H67" s="5" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I67" s="6" t="n">
         <v>46235</v>
@@ -6541,7 +6529,7 @@
       </c>
       <c r="L67" s="5"/>
       <c r="M67" s="7" t="n">
-        <v>54.34</v>
+        <v>58.94</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6580,7 +6568,7 @@
       </c>
       <c r="L68" s="5"/>
       <c r="M68" s="7" t="n">
-        <v>53.51</v>
+        <v>55.59</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6619,7 +6607,7 @@
       </c>
       <c r="L69" s="5"/>
       <c r="M69" s="7" t="n">
-        <v>52.7</v>
+        <v>55.15</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6658,7 +6646,7 @@
       </c>
       <c r="L70" s="5"/>
       <c r="M70" s="7" t="n">
-        <v>52.27</v>
+        <v>52.7</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6681,10 +6669,10 @@
         <v>228</v>
       </c>
       <c r="G71" s="5" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="H71" s="5" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I71" s="6" t="n">
         <v>46235</v>
@@ -6697,7 +6685,7 @@
       </c>
       <c r="L71" s="5"/>
       <c r="M71" s="7" t="n">
-        <v>49.23</v>
+        <v>52.27</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6723,7 +6711,7 @@
         <v>38</v>
       </c>
       <c r="H72" s="5" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I72" s="6" t="n">
         <v>46235</v>
@@ -6736,7 +6724,7 @@
       </c>
       <c r="L72" s="5"/>
       <c r="M72" s="7" t="n">
-        <v>48.24</v>
+        <v>51.12</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6759,10 +6747,10 @@
         <v>234</v>
       </c>
       <c r="G73" s="5" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="H73" s="5" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I73" s="6" t="n">
         <v>46235</v>
@@ -6775,7 +6763,7 @@
       </c>
       <c r="L73" s="5"/>
       <c r="M73" s="7" t="n">
-        <v>48.01</v>
+        <v>49.23</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6801,7 +6789,7 @@
         <v>38</v>
       </c>
       <c r="H74" s="5" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I74" s="6" t="n">
         <v>46235</v>
@@ -6814,7 +6802,7 @@
       </c>
       <c r="L74" s="5"/>
       <c r="M74" s="7" t="n">
-        <v>46.66</v>
+        <v>48.47</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6840,7 +6828,7 @@
         <v>38</v>
       </c>
       <c r="H75" s="5" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I75" s="6" t="n">
         <v>46235</v>
@@ -6853,7 +6841,7 @@
       </c>
       <c r="L75" s="5"/>
       <c r="M75" s="7" t="n">
-        <v>46.47</v>
+        <v>48.24</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6892,7 +6880,7 @@
       </c>
       <c r="L76" s="5"/>
       <c r="M76" s="7" t="n">
-        <v>46.27</v>
+        <v>47.79</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6931,7 +6919,7 @@
       </c>
       <c r="L77" s="5"/>
       <c r="M77" s="7" t="n">
-        <v>46.2</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6970,7 +6958,7 @@
       </c>
       <c r="L78" s="5"/>
       <c r="M78" s="7" t="n">
-        <v>45.31</v>
+        <v>46.99</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6996,7 +6984,7 @@
         <v>38</v>
       </c>
       <c r="H79" s="5" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I79" s="6" t="n">
         <v>46235</v>
@@ -7009,7 +6997,7 @@
       </c>
       <c r="L79" s="5"/>
       <c r="M79" s="7" t="n">
-        <v>43.66</v>
+        <v>46.74</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7048,7 +7036,7 @@
       </c>
       <c r="L80" s="5"/>
       <c r="M80" s="7" t="n">
-        <v>43.24</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7087,7 +7075,7 @@
       </c>
       <c r="L81" s="5"/>
       <c r="M81" s="7" t="n">
-        <v>42.82</v>
+        <v>46.17</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7126,7 +7114,7 @@
       </c>
       <c r="L82" s="5"/>
       <c r="M82" s="7" t="n">
-        <v>42.59</v>
+        <v>45.31</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7152,7 +7140,7 @@
         <v>38</v>
       </c>
       <c r="H83" s="5" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I83" s="6" t="n">
         <v>46235</v>
@@ -7165,7 +7153,7 @@
       </c>
       <c r="L83" s="5"/>
       <c r="M83" s="7" t="n">
-        <v>42.04</v>
+        <v>43.24</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7204,7 +7192,7 @@
       </c>
       <c r="L84" s="5"/>
       <c r="M84" s="7" t="n">
-        <v>41.87</v>
+        <v>42.82</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7230,7 +7218,7 @@
         <v>38</v>
       </c>
       <c r="H85" s="5" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I85" s="6" t="n">
         <v>46235</v>
@@ -7243,7 +7231,7 @@
       </c>
       <c r="L85" s="5"/>
       <c r="M85" s="7" t="n">
-        <v>39.91</v>
+        <v>42.59</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7282,7 +7270,7 @@
       </c>
       <c r="L86" s="5"/>
       <c r="M86" s="7" t="n">
-        <v>39.87</v>
+        <v>42.04</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7321,7 +7309,7 @@
       </c>
       <c r="L87" s="5"/>
       <c r="M87" s="7" t="n">
-        <v>38.95</v>
+        <v>41.87</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7360,7 +7348,7 @@
       </c>
       <c r="L88" s="5"/>
       <c r="M88" s="7" t="n">
-        <v>38.38</v>
+        <v>40.42</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7399,7 +7387,7 @@
       </c>
       <c r="L89" s="5"/>
       <c r="M89" s="7" t="n">
-        <v>38.09</v>
+        <v>40.41</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7438,7 +7426,7 @@
       </c>
       <c r="L90" s="5"/>
       <c r="M90" s="7" t="n">
-        <v>37.8</v>
+        <v>39.91</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7477,7 +7465,7 @@
       </c>
       <c r="L91" s="5"/>
       <c r="M91" s="7" t="n">
-        <v>37.31</v>
+        <v>39.91</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7516,7 +7504,7 @@
       </c>
       <c r="L92" s="5"/>
       <c r="M92" s="7" t="n">
-        <v>37.2</v>
+        <v>39.05</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7542,7 +7530,7 @@
         <v>38</v>
       </c>
       <c r="H93" s="5" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I93" s="6" t="n">
         <v>46235</v>
@@ -7555,7 +7543,7 @@
       </c>
       <c r="L93" s="5"/>
       <c r="M93" s="7" t="n">
-        <v>34.69</v>
+        <v>38.09</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7594,7 +7582,7 @@
       </c>
       <c r="L94" s="5"/>
       <c r="M94" s="7" t="n">
-        <v>33.82</v>
+        <v>37.8</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7633,7 +7621,7 @@
       </c>
       <c r="L95" s="5"/>
       <c r="M95" s="7" t="n">
-        <v>33.62</v>
+        <v>36.67</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7672,7 +7660,7 @@
       </c>
       <c r="L96" s="5"/>
       <c r="M96" s="7" t="n">
-        <v>32.44</v>
+        <v>35.76</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7711,7 +7699,7 @@
       </c>
       <c r="L97" s="5"/>
       <c r="M97" s="7" t="n">
-        <v>32.34</v>
+        <v>33.89</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7750,7 +7738,7 @@
       </c>
       <c r="L98" s="5"/>
       <c r="M98" s="7" t="n">
-        <v>31.03</v>
+        <v>33.37</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7789,7 +7777,7 @@
       </c>
       <c r="L99" s="5"/>
       <c r="M99" s="7" t="n">
-        <v>30.63</v>
+        <v>32.81</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7828,7 +7816,7 @@
       </c>
       <c r="L100" s="5"/>
       <c r="M100" s="7" t="n">
-        <v>29.83</v>
+        <v>32.57</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7854,7 +7842,7 @@
         <v>38</v>
       </c>
       <c r="H101" s="5" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I101" s="6" t="n">
         <v>46235</v>
@@ -7867,7 +7855,7 @@
       </c>
       <c r="L101" s="5"/>
       <c r="M101" s="7" t="n">
-        <v>29.14</v>
+        <v>32.44</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7906,7 +7894,7 @@
       </c>
       <c r="L102" s="5"/>
       <c r="M102" s="7" t="n">
-        <v>28.13</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7945,7 +7933,7 @@
       </c>
       <c r="L103" s="5"/>
       <c r="M103" s="7" t="n">
-        <v>28.07</v>
+        <v>31.26</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7971,7 +7959,7 @@
         <v>38</v>
       </c>
       <c r="H104" s="5" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I104" s="6" t="n">
         <v>46235</v>
@@ -7984,7 +7972,7 @@
       </c>
       <c r="L104" s="5"/>
       <c r="M104" s="7" t="n">
-        <v>27.1</v>
+        <v>31.12</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8023,7 +8011,7 @@
       </c>
       <c r="L105" s="5"/>
       <c r="M105" s="7" t="n">
-        <v>26.69</v>
+        <v>29.14</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8062,7 +8050,7 @@
       </c>
       <c r="L106" s="5"/>
       <c r="M106" s="7" t="n">
-        <v>26.27</v>
+        <v>28.14</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8101,7 +8089,7 @@
       </c>
       <c r="L107" s="5"/>
       <c r="M107" s="7" t="n">
-        <v>26.26</v>
+        <v>27.7</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8127,7 +8115,7 @@
         <v>38</v>
       </c>
       <c r="H108" s="5" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I108" s="6" t="n">
         <v>46235</v>
@@ -8140,7 +8128,7 @@
       </c>
       <c r="L108" s="5"/>
       <c r="M108" s="7" t="n">
-        <v>25.13</v>
+        <v>27.29</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8166,7 +8154,7 @@
         <v>38</v>
       </c>
       <c r="H109" s="5" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I109" s="6" t="n">
         <v>46235</v>
@@ -8179,7 +8167,7 @@
       </c>
       <c r="L109" s="5"/>
       <c r="M109" s="7" t="n">
-        <v>24.54</v>
+        <v>27.19</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8218,7 +8206,7 @@
       </c>
       <c r="L110" s="5"/>
       <c r="M110" s="7" t="n">
-        <v>24.04</v>
+        <v>27.1</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8244,7 +8232,7 @@
         <v>38</v>
       </c>
       <c r="H111" s="5" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I111" s="6" t="n">
         <v>46235</v>
@@ -8257,7 +8245,7 @@
       </c>
       <c r="L111" s="5"/>
       <c r="M111" s="7" t="n">
-        <v>23.28</v>
+        <v>26.77</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8283,7 +8271,7 @@
         <v>38</v>
       </c>
       <c r="H112" s="5" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I112" s="6" t="n">
         <v>46235</v>
@@ -8296,7 +8284,7 @@
       </c>
       <c r="L112" s="5"/>
       <c r="M112" s="7" t="n">
-        <v>23.08</v>
+        <v>26.69</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8335,7 +8323,7 @@
       </c>
       <c r="L113" s="5"/>
       <c r="M113" s="7" t="n">
-        <v>22.03</v>
+        <v>26.26</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8361,7 +8349,7 @@
         <v>38</v>
       </c>
       <c r="H114" s="5" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I114" s="6" t="n">
         <v>46235</v>
@@ -8374,7 +8362,7 @@
       </c>
       <c r="L114" s="5"/>
       <c r="M114" s="7" t="n">
-        <v>21.55</v>
+        <v>25.81</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8400,7 +8388,7 @@
         <v>38</v>
       </c>
       <c r="H115" s="5" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I115" s="6" t="n">
         <v>46235</v>
@@ -8413,7 +8401,7 @@
       </c>
       <c r="L115" s="5"/>
       <c r="M115" s="7" t="n">
-        <v>21.54</v>
+        <v>25.13</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8452,7 +8440,7 @@
       </c>
       <c r="L116" s="5"/>
       <c r="M116" s="7" t="n">
-        <v>21.3</v>
+        <v>24.54</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8491,7 +8479,7 @@
       </c>
       <c r="L117" s="5"/>
       <c r="M117" s="7" t="n">
-        <v>21.05</v>
+        <v>24.51</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8530,7 +8518,7 @@
       </c>
       <c r="L118" s="5"/>
       <c r="M118" s="7" t="n">
-        <v>20.7</v>
+        <v>23.88</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8553,7 +8541,7 @@
         <v>372</v>
       </c>
       <c r="G119" s="5" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="H119" s="5" t="s">
         <v>18</v>
@@ -8569,7 +8557,7 @@
       </c>
       <c r="L119" s="5"/>
       <c r="M119" s="7" t="n">
-        <v>20.19</v>
+        <v>23.86</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8595,7 +8583,7 @@
         <v>38</v>
       </c>
       <c r="H120" s="5" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I120" s="6" t="n">
         <v>46235</v>
@@ -8608,7 +8596,7 @@
       </c>
       <c r="L120" s="5"/>
       <c r="M120" s="7" t="n">
-        <v>19.89</v>
+        <v>23.32</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8634,7 +8622,7 @@
         <v>38</v>
       </c>
       <c r="H121" s="5" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I121" s="6" t="n">
         <v>46235</v>
@@ -8647,7 +8635,7 @@
       </c>
       <c r="L121" s="5"/>
       <c r="M121" s="7" t="n">
-        <v>19.66</v>
+        <v>21.54</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8673,7 +8661,7 @@
         <v>38</v>
       </c>
       <c r="H122" s="5" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I122" s="6" t="n">
         <v>46235</v>
@@ -8686,7 +8674,7 @@
       </c>
       <c r="L122" s="5"/>
       <c r="M122" s="7" t="n">
-        <v>19.57</v>
+        <v>21.3</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8712,7 +8700,7 @@
         <v>38</v>
       </c>
       <c r="H123" s="5" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I123" s="6" t="n">
         <v>46235</v>
@@ -8725,7 +8713,7 @@
       </c>
       <c r="L123" s="5"/>
       <c r="M123" s="7" t="n">
-        <v>19.21</v>
+        <v>21.16</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8764,7 +8752,7 @@
       </c>
       <c r="L124" s="5"/>
       <c r="M124" s="7" t="n">
-        <v>19.17</v>
+        <v>20.7</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8790,7 +8778,7 @@
         <v>38</v>
       </c>
       <c r="H125" s="5" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I125" s="6" t="n">
         <v>46235</v>
@@ -8803,7 +8791,7 @@
       </c>
       <c r="L125" s="5"/>
       <c r="M125" s="7" t="n">
-        <v>19.15</v>
+        <v>19.62</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8829,7 +8817,7 @@
         <v>38</v>
       </c>
       <c r="H126" s="5" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I126" s="6" t="n">
         <v>46235</v>
@@ -8842,7 +8830,7 @@
       </c>
       <c r="L126" s="5"/>
       <c r="M126" s="7" t="n">
-        <v>18.53</v>
+        <v>19.59</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8881,7 +8869,7 @@
       </c>
       <c r="L127" s="5"/>
       <c r="M127" s="7" t="n">
-        <v>18.44</v>
+        <v>19.21</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8907,7 +8895,7 @@
         <v>38</v>
       </c>
       <c r="H128" s="5" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I128" s="6" t="n">
         <v>46235</v>
@@ -8920,7 +8908,7 @@
       </c>
       <c r="L128" s="5"/>
       <c r="M128" s="7" t="n">
-        <v>17.98</v>
+        <v>19.17</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8946,7 +8934,7 @@
         <v>38</v>
       </c>
       <c r="H129" s="5" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I129" s="6" t="n">
         <v>46235</v>
@@ -8959,7 +8947,7 @@
       </c>
       <c r="L129" s="5"/>
       <c r="M129" s="7" t="n">
-        <v>17.07</v>
+        <v>19.15</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8998,7 +8986,7 @@
       </c>
       <c r="L130" s="5"/>
       <c r="M130" s="7" t="n">
-        <v>16.08</v>
+        <v>18.73</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9037,7 +9025,7 @@
       </c>
       <c r="L131" s="5"/>
       <c r="M131" s="7" t="n">
-        <v>15.65</v>
+        <v>18.44</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9063,7 +9051,7 @@
         <v>38</v>
       </c>
       <c r="H132" s="5" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I132" s="6" t="n">
         <v>46235</v>
@@ -9076,7 +9064,7 @@
       </c>
       <c r="L132" s="5"/>
       <c r="M132" s="7" t="n">
-        <v>15.43</v>
+        <v>18.29</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9115,7 +9103,7 @@
       </c>
       <c r="L133" s="5"/>
       <c r="M133" s="7" t="n">
-        <v>14.63</v>
+        <v>17.64</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9154,7 +9142,7 @@
       </c>
       <c r="L134" s="5"/>
       <c r="M134" s="7" t="n">
-        <v>14.46</v>
+        <v>17.47</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9193,7 +9181,7 @@
       </c>
       <c r="L135" s="5"/>
       <c r="M135" s="7" t="n">
-        <v>14.44</v>
+        <v>17.07</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9232,7 +9220,7 @@
       </c>
       <c r="L136" s="5"/>
       <c r="M136" s="7" t="n">
-        <v>14.37</v>
+        <v>16.22</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9271,7 +9259,7 @@
       </c>
       <c r="L137" s="5"/>
       <c r="M137" s="7" t="n">
-        <v>14.16</v>
+        <v>15.51</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9294,10 +9282,10 @@
         <v>429</v>
       </c>
       <c r="G138" s="5" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="H138" s="5" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I138" s="6" t="n">
         <v>46235</v>
@@ -9310,7 +9298,7 @@
       </c>
       <c r="L138" s="5"/>
       <c r="M138" s="7" t="n">
-        <v>13.23</v>
+        <v>14.59</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9336,7 +9324,7 @@
         <v>38</v>
       </c>
       <c r="H139" s="5" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I139" s="6" t="n">
         <v>46235</v>
@@ -9349,7 +9337,7 @@
       </c>
       <c r="L139" s="5"/>
       <c r="M139" s="7" t="n">
-        <v>13.2</v>
+        <v>14.46</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9375,7 +9363,7 @@
         <v>38</v>
       </c>
       <c r="H140" s="5" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I140" s="6" t="n">
         <v>46235</v>
@@ -9388,7 +9376,7 @@
       </c>
       <c r="L140" s="5"/>
       <c r="M140" s="7" t="n">
-        <v>12.57</v>
+        <v>14.45</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9414,7 +9402,7 @@
         <v>38</v>
       </c>
       <c r="H141" s="5" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I141" s="6" t="n">
         <v>46235</v>
@@ -9427,7 +9415,7 @@
       </c>
       <c r="L141" s="5"/>
       <c r="M141" s="7" t="n">
-        <v>12.33</v>
+        <v>14.37</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9450,7 +9438,7 @@
         <v>441</v>
       </c>
       <c r="G142" s="5" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="H142" s="5" t="s">
         <v>18</v>
@@ -9466,7 +9454,7 @@
       </c>
       <c r="L142" s="5"/>
       <c r="M142" s="7" t="n">
-        <v>11.99</v>
+        <v>14.23</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9505,7 +9493,7 @@
       </c>
       <c r="L143" s="5"/>
       <c r="M143" s="7" t="n">
-        <v>11.96</v>
+        <v>14.13</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9544,7 +9532,7 @@
       </c>
       <c r="L144" s="5"/>
       <c r="M144" s="7" t="n">
-        <v>11.46</v>
+        <v>13.38</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9567,7 +9555,7 @@
         <v>450</v>
       </c>
       <c r="G145" s="5" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="H145" s="5" t="s">
         <v>18</v>
@@ -9583,7 +9571,7 @@
       </c>
       <c r="L145" s="5"/>
       <c r="M145" s="7" t="n">
-        <v>11.24</v>
+        <v>13.24</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9622,7 +9610,7 @@
       </c>
       <c r="L146" s="5"/>
       <c r="M146" s="7" t="n">
-        <v>11.15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9661,7 +9649,7 @@
       </c>
       <c r="L147" s="5"/>
       <c r="M147" s="7" t="n">
-        <v>10.96</v>
+        <v>12.57</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9700,7 +9688,7 @@
       </c>
       <c r="L148" s="5"/>
       <c r="M148" s="7" t="n">
-        <v>10.72</v>
+        <v>12.22</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9739,7 +9727,7 @@
       </c>
       <c r="L149" s="5"/>
       <c r="M149" s="7" t="n">
-        <v>10.42</v>
+        <v>11.92</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9765,7 +9753,7 @@
         <v>38</v>
       </c>
       <c r="H150" s="5" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I150" s="6" t="n">
         <v>46235</v>
@@ -9778,7 +9766,7 @@
       </c>
       <c r="L150" s="5"/>
       <c r="M150" s="7" t="n">
-        <v>9.18</v>
+        <v>11.19</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9817,7 +9805,7 @@
       </c>
       <c r="L151" s="5"/>
       <c r="M151" s="7" t="n">
-        <v>9.14</v>
+        <v>10.96</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9856,7 +9844,7 @@
       </c>
       <c r="L152" s="5"/>
       <c r="M152" s="7" t="n">
-        <v>8.87</v>
+        <v>10.42</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9895,7 +9883,7 @@
       </c>
       <c r="L153" s="5"/>
       <c r="M153" s="7" t="n">
-        <v>8.75</v>
+        <v>9.73</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9921,7 +9909,7 @@
         <v>38</v>
       </c>
       <c r="H154" s="5" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I154" s="6" t="n">
         <v>46235</v>
@@ -9934,7 +9922,7 @@
       </c>
       <c r="L154" s="5"/>
       <c r="M154" s="7" t="n">
-        <v>8.67</v>
+        <v>9.18</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9960,7 +9948,7 @@
         <v>38</v>
       </c>
       <c r="H155" s="5" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I155" s="6" t="n">
         <v>46235</v>
@@ -9973,7 +9961,7 @@
       </c>
       <c r="L155" s="5"/>
       <c r="M155" s="7" t="n">
-        <v>8.29</v>
+        <v>9.14</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9999,7 +9987,7 @@
         <v>38</v>
       </c>
       <c r="H156" s="5" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I156" s="6" t="n">
         <v>46235</v>
@@ -10012,7 +10000,7 @@
       </c>
       <c r="L156" s="5"/>
       <c r="M156" s="7" t="n">
-        <v>8.09</v>
+        <v>9.03</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10051,7 +10039,7 @@
       </c>
       <c r="L157" s="5"/>
       <c r="M157" s="7" t="n">
-        <v>7.71</v>
+        <v>8.87</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10074,7 +10062,7 @@
         <v>489</v>
       </c>
       <c r="G158" s="5" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="H158" s="5" t="s">
         <v>18</v>
@@ -10090,7 +10078,7 @@
       </c>
       <c r="L158" s="5"/>
       <c r="M158" s="7" t="n">
-        <v>7.15</v>
+        <v>8.85</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10116,7 +10104,7 @@
         <v>38</v>
       </c>
       <c r="H159" s="5" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I159" s="6" t="n">
         <v>46235</v>
@@ -10129,7 +10117,7 @@
       </c>
       <c r="L159" s="5"/>
       <c r="M159" s="7" t="n">
-        <v>7.07</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10168,7 +10156,7 @@
       </c>
       <c r="L160" s="5"/>
       <c r="M160" s="7" t="n">
-        <v>6.03</v>
+        <v>7.84</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10191,7 +10179,7 @@
         <v>498</v>
       </c>
       <c r="G161" s="5" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="H161" s="5" t="s">
         <v>18</v>
@@ -10207,7 +10195,7 @@
       </c>
       <c r="L161" s="5"/>
       <c r="M161" s="7" t="n">
-        <v>5.9</v>
+        <v>7.27</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10233,7 +10221,7 @@
         <v>38</v>
       </c>
       <c r="H162" s="5" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I162" s="6" t="n">
         <v>46235</v>
@@ -10246,7 +10234,7 @@
       </c>
       <c r="L162" s="5"/>
       <c r="M162" s="7" t="n">
-        <v>5.87</v>
+        <v>7.08</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10272,7 +10260,7 @@
         <v>38</v>
       </c>
       <c r="H163" s="5" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I163" s="6" t="n">
         <v>46235</v>
@@ -10285,7 +10273,7 @@
       </c>
       <c r="L163" s="5"/>
       <c r="M163" s="7" t="n">
-        <v>5.78</v>
+        <v>6.77</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10324,7 +10312,7 @@
       </c>
       <c r="L164" s="5"/>
       <c r="M164" s="7" t="n">
-        <v>5.54</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10363,7 +10351,7 @@
       </c>
       <c r="L165" s="5"/>
       <c r="M165" s="7" t="n">
-        <v>5.51</v>
+        <v>6.34</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10402,7 +10390,7 @@
       </c>
       <c r="L166" s="5"/>
       <c r="M166" s="7" t="n">
-        <v>5.37</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10428,7 +10416,7 @@
         <v>38</v>
       </c>
       <c r="H167" s="5" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I167" s="6" t="n">
         <v>46235</v>
@@ -10441,7 +10429,7 @@
       </c>
       <c r="L167" s="5"/>
       <c r="M167" s="7" t="n">
-        <v>4.81</v>
+        <v>5.78</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10480,7 +10468,7 @@
       </c>
       <c r="L168" s="5"/>
       <c r="M168" s="7" t="n">
-        <v>4.65</v>
+        <v>5.51</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10519,7 +10507,7 @@
       </c>
       <c r="L169" s="5"/>
       <c r="M169" s="7" t="n">
-        <v>3.74</v>
+        <v>5.41</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10545,7 +10533,7 @@
         <v>38</v>
       </c>
       <c r="H170" s="5" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I170" s="6" t="n">
         <v>46235</v>
@@ -10558,7 +10546,7 @@
       </c>
       <c r="L170" s="5"/>
       <c r="M170" s="7" t="n">
-        <v>3.43</v>
+        <v>4.69</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10584,7 +10572,7 @@
         <v>38</v>
       </c>
       <c r="H171" s="5" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I171" s="6" t="n">
         <v>46235</v>
@@ -10597,7 +10585,7 @@
       </c>
       <c r="L171" s="5"/>
       <c r="M171" s="7" t="n">
-        <v>3.42</v>
+        <v>4.65</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10636,7 +10624,7 @@
       </c>
       <c r="L172" s="5"/>
       <c r="M172" s="7" t="n">
-        <v>3.17</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10675,7 +10663,7 @@
       </c>
       <c r="L173" s="5"/>
       <c r="M173" s="7" t="n">
-        <v>3.02</v>
+        <v>3.74</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10714,7 +10702,7 @@
       </c>
       <c r="L174" s="5"/>
       <c r="M174" s="7" t="n">
-        <v>2.96</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10740,7 +10728,7 @@
         <v>38</v>
       </c>
       <c r="H175" s="5" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I175" s="6" t="n">
         <v>46235</v>
@@ -10753,7 +10741,7 @@
       </c>
       <c r="L175" s="5"/>
       <c r="M175" s="7" t="n">
-        <v>2.95</v>
+        <v>3.43</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10792,7 +10780,7 @@
       </c>
       <c r="L176" s="5"/>
       <c r="M176" s="7" t="n">
-        <v>2.61</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10831,7 +10819,7 @@
       </c>
       <c r="L177" s="5"/>
       <c r="M177" s="7" t="n">
-        <v>2.56</v>
+        <v>3.02</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10870,7 +10858,7 @@
       </c>
       <c r="L178" s="5"/>
       <c r="M178" s="7" t="n">
-        <v>2.17</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10909,7 +10897,7 @@
       </c>
       <c r="L179" s="5"/>
       <c r="M179" s="7" t="n">
-        <v>1.58</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10935,7 +10923,7 @@
         <v>38</v>
       </c>
       <c r="H180" s="5" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I180" s="6" t="n">
         <v>46235</v>
@@ -10948,7 +10936,7 @@
       </c>
       <c r="L180" s="5"/>
       <c r="M180" s="7" t="n">
-        <v>1.09</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10974,7 +10962,7 @@
         <v>38</v>
       </c>
       <c r="H181" s="5" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I181" s="6" t="n">
         <v>46235</v>
@@ -10987,7 +10975,7 @@
       </c>
       <c r="L181" s="5"/>
       <c r="M181" s="7" t="n">
-        <v>1</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11013,7 +11001,7 @@
         <v>38</v>
       </c>
       <c r="H182" s="5" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I182" s="6" t="n">
         <v>46235</v>
@@ -11026,7 +11014,7 @@
       </c>
       <c r="L182" s="5"/>
       <c r="M182" s="7" t="n">
-        <v>0.82</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11065,7 +11053,7 @@
       </c>
       <c r="L183" s="5"/>
       <c r="M183" s="7" t="n">
-        <v>0.46</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11104,7 +11092,7 @@
       </c>
       <c r="L184" s="5"/>
       <c r="M184" s="7" t="n">
-        <v>0.42</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11143,7 +11131,7 @@
       </c>
       <c r="L185" s="5"/>
       <c r="M185" s="7" t="n">
-        <v>0.38</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11182,7 +11170,7 @@
       </c>
       <c r="L186" s="5"/>
       <c r="M186" s="7" t="n">
-        <v>0.26</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11221,7 +11209,7 @@
       </c>
       <c r="L187" s="5"/>
       <c r="M187" s="7" t="n">
-        <v>0.26</v>
+        <v>1</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11260,7 +11248,7 @@
       </c>
       <c r="L188" s="5"/>
       <c r="M188" s="7" t="n">
-        <v>0.23</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11299,7 +11287,7 @@
       </c>
       <c r="L189" s="5"/>
       <c r="M189" s="7" t="n">
-        <v>0.19</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11338,7 +11326,7 @@
       </c>
       <c r="L190" s="5"/>
       <c r="M190" s="7" t="n">
-        <v>0.17</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11377,7 +11365,7 @@
       </c>
       <c r="L191" s="5"/>
       <c r="M191" s="7" t="n">
-        <v>0.14</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11416,7 +11404,7 @@
       </c>
       <c r="L192" s="5"/>
       <c r="M192" s="7" t="n">
-        <v>0.14</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11442,7 +11430,7 @@
         <v>38</v>
       </c>
       <c r="H193" s="5" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I193" s="6" t="n">
         <v>46235</v>
@@ -11455,7 +11443,7 @@
       </c>
       <c r="L193" s="5"/>
       <c r="M193" s="7" t="n">
-        <v>0.13</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11494,7 +11482,7 @@
       </c>
       <c r="L194" s="5"/>
       <c r="M194" s="7" t="n">
-        <v>0.12</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11533,7 +11521,7 @@
       </c>
       <c r="L195" s="5"/>
       <c r="M195" s="7" t="n">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11572,7 +11560,7 @@
       </c>
       <c r="L196" s="5"/>
       <c r="M196" s="7" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11611,7 +11599,7 @@
       </c>
       <c r="L197" s="5"/>
       <c r="M197" s="7" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11650,7 +11638,7 @@
       </c>
       <c r="L198" s="5"/>
       <c r="M198" s="7" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11689,7 +11677,7 @@
       </c>
       <c r="L199" s="5"/>
       <c r="M199" s="7" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11728,7 +11716,7 @@
       </c>
       <c r="L200" s="5"/>
       <c r="M200" s="7" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11767,7 +11755,7 @@
       </c>
       <c r="L201" s="5"/>
       <c r="M201" s="7" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11806,7 +11794,7 @@
       </c>
       <c r="L202" s="5"/>
       <c r="M202" s="7" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11845,7 +11833,7 @@
       </c>
       <c r="L203" s="5"/>
       <c r="M203" s="7" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11884,7 +11872,7 @@
       </c>
       <c r="L204" s="5"/>
       <c r="M204" s="7" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11923,7 +11911,7 @@
       </c>
       <c r="L205" s="5"/>
       <c r="M205" s="7" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11962,7 +11950,7 @@
       </c>
       <c r="L206" s="5"/>
       <c r="M206" s="7" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12001,7 +11989,7 @@
       </c>
       <c r="L207" s="5"/>
       <c r="M207" s="7" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12040,7 +12028,7 @@
       </c>
       <c r="L208" s="5"/>
       <c r="M208" s="7" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12508,7 +12496,7 @@
       </c>
       <c r="L220" s="5"/>
       <c r="M220" s="7" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12547,7 +12535,7 @@
       </c>
       <c r="L221" s="5"/>
       <c r="M221" s="7" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12586,7 +12574,7 @@
       </c>
       <c r="L222" s="5"/>
       <c r="M222" s="7" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12625,7 +12613,7 @@
       </c>
       <c r="L223" s="5"/>
       <c r="M223" s="7" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12664,7 +12652,7 @@
       </c>
       <c r="L224" s="5"/>
       <c r="M224" s="7" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12703,7 +12691,7 @@
       </c>
       <c r="L225" s="5"/>
       <c r="M225" s="7" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12742,7 +12730,7 @@
       </c>
       <c r="L226" s="5"/>
       <c r="M226" s="7" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12765,7 +12753,7 @@
         <v>696</v>
       </c>
       <c r="G227" s="5" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="H227" s="5" t="s">
         <v>18</v>
@@ -12781,7 +12769,7 @@
       </c>
       <c r="L227" s="5"/>
       <c r="M227" s="7" t="n">
-        <v>0.07</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12820,7 +12808,7 @@
       </c>
       <c r="L228" s="5"/>
       <c r="M228" s="7" t="n">
-        <v>0.07</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12859,7 +12847,7 @@
       </c>
       <c r="L229" s="5"/>
       <c r="M229" s="7" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12898,7 +12886,7 @@
       </c>
       <c r="L230" s="5"/>
       <c r="M230" s="7" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12937,7 +12925,7 @@
       </c>
       <c r="L231" s="5"/>
       <c r="M231" s="7" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12976,7 +12964,7 @@
       </c>
       <c r="L232" s="5"/>
       <c r="M232" s="7" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="233" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13015,7 +13003,7 @@
       </c>
       <c r="L233" s="5"/>
       <c r="M233" s="7" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13054,7 +13042,7 @@
       </c>
       <c r="L234" s="5"/>
       <c r="M234" s="7" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13093,7 +13081,7 @@
       </c>
       <c r="L235" s="5"/>
       <c r="M235" s="7" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13132,7 +13120,7 @@
       </c>
       <c r="L236" s="5"/>
       <c r="M236" s="7" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13171,7 +13159,7 @@
       </c>
       <c r="L237" s="5"/>
       <c r="M237" s="7" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13210,7 +13198,7 @@
       </c>
       <c r="L238" s="5"/>
       <c r="M238" s="7" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13249,7 +13237,7 @@
       </c>
       <c r="L239" s="5"/>
       <c r="M239" s="7" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13272,7 +13260,7 @@
         <v>735</v>
       </c>
       <c r="G240" s="5" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="H240" s="5" t="s">
         <v>18</v>
@@ -13288,7 +13276,7 @@
       </c>
       <c r="L240" s="5"/>
       <c r="M240" s="7" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13311,7 +13299,7 @@
         <v>738</v>
       </c>
       <c r="G241" s="5" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="H241" s="5" t="s">
         <v>18</v>
@@ -13327,7 +13315,7 @@
       </c>
       <c r="L241" s="5"/>
       <c r="M241" s="7" t="n">
-        <v>0.05</v>
+        <v>0.07</v>
       </c>
     </row>
     <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13366,7 +13354,7 @@
       </c>
       <c r="L242" s="5"/>
       <c r="M242" s="7" t="n">
-        <v>0.05</v>
+        <v>0.07</v>
       </c>
     </row>
     <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13405,7 +13393,7 @@
       </c>
       <c r="L243" s="5"/>
       <c r="M243" s="7" t="n">
-        <v>0.05</v>
+        <v>0.07</v>
       </c>
     </row>
     <row r="244" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13444,7 +13432,7 @@
       </c>
       <c r="L244" s="5"/>
       <c r="M244" s="7" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13470,7 +13458,7 @@
         <v>38</v>
       </c>
       <c r="H245" s="5" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I245" s="6" t="n">
         <v>46235</v>
@@ -13483,7 +13471,7 @@
       </c>
       <c r="L245" s="5"/>
       <c r="M245" s="7" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13522,7 +13510,7 @@
       </c>
       <c r="L246" s="5"/>
       <c r="M246" s="7" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="247" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13561,7 +13549,7 @@
       </c>
       <c r="L247" s="5"/>
       <c r="M247" s="7" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13795,7 +13783,7 @@
       </c>
       <c r="L253" s="5"/>
       <c r="M253" s="7" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13834,7 +13822,7 @@
       </c>
       <c r="L254" s="5"/>
       <c r="M254" s="7" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="255" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13873,7 +13861,7 @@
       </c>
       <c r="L255" s="5"/>
       <c r="M255" s="7" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13896,7 +13884,7 @@
         <v>783</v>
       </c>
       <c r="G256" s="5" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="H256" s="5" t="s">
         <v>18</v>
@@ -13912,7 +13900,7 @@
       </c>
       <c r="L256" s="5"/>
       <c r="M256" s="7" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="257" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13951,7 +13939,7 @@
       </c>
       <c r="L257" s="5"/>
       <c r="M257" s="7" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="258" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13990,7 +13978,7 @@
       </c>
       <c r="L258" s="5"/>
       <c r="M258" s="7" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="259" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14029,7 +14017,7 @@
       </c>
       <c r="L259" s="5"/>
       <c r="M259" s="7" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="260" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14068,7 +14056,7 @@
       </c>
       <c r="L260" s="5"/>
       <c r="M260" s="7" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="261" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14091,7 +14079,7 @@
         <v>798</v>
       </c>
       <c r="G261" s="5" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="H261" s="5" t="s">
         <v>18</v>
@@ -14107,7 +14095,7 @@
       </c>
       <c r="L261" s="5"/>
       <c r="M261" s="7" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="262" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14146,7 +14134,7 @@
       </c>
       <c r="L262" s="5"/>
       <c r="M262" s="7" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="263" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14185,7 +14173,7 @@
       </c>
       <c r="L263" s="5"/>
       <c r="M263" s="7" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="264" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14224,7 +14212,7 @@
       </c>
       <c r="L264" s="5"/>
       <c r="M264" s="7" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="265" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14263,7 +14251,7 @@
       </c>
       <c r="L265" s="5"/>
       <c r="M265" s="7" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="266" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14302,7 +14290,7 @@
       </c>
       <c r="L266" s="5"/>
       <c r="M266" s="7" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="267" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14328,7 +14316,7 @@
         <v>38</v>
       </c>
       <c r="H267" s="5" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I267" s="6" t="n">
         <v>46235</v>
@@ -14341,7 +14329,7 @@
       </c>
       <c r="L267" s="5"/>
       <c r="M267" s="7" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="268" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14380,7 +14368,7 @@
       </c>
       <c r="L268" s="5"/>
       <c r="M268" s="7" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="269" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14419,7 +14407,7 @@
       </c>
       <c r="L269" s="5"/>
       <c r="M269" s="7" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="270" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14523,7 +14511,7 @@
         <v>38</v>
       </c>
       <c r="H272" s="5" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I272" s="6" t="n">
         <v>46235</v>
@@ -14562,7 +14550,7 @@
         <v>38</v>
       </c>
       <c r="H273" s="5" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I273" s="6" t="n">
         <v>46235</v>
@@ -14653,7 +14641,7 @@
       </c>
       <c r="L275" s="5"/>
       <c r="M275" s="7" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="276" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14692,7 +14680,7 @@
       </c>
       <c r="L276" s="5"/>
       <c r="M276" s="7" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="277" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14718,7 +14706,7 @@
         <v>38</v>
       </c>
       <c r="H277" s="5" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I277" s="6" t="n">
         <v>46235</v>
@@ -14731,7 +14719,7 @@
       </c>
       <c r="L277" s="5"/>
       <c r="M277" s="7" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="278" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14754,7 +14742,7 @@
         <v>849</v>
       </c>
       <c r="G278" s="5" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="H278" s="5" t="s">
         <v>18</v>
@@ -14770,7 +14758,7 @@
       </c>
       <c r="L278" s="5"/>
       <c r="M278" s="7" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="279" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14809,7 +14797,7 @@
       </c>
       <c r="L279" s="5"/>
       <c r="M279" s="7" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="280" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14835,7 +14823,7 @@
         <v>38</v>
       </c>
       <c r="H280" s="5" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I280" s="6" t="n">
         <v>46235</v>
@@ -14848,7 +14836,7 @@
       </c>
       <c r="L280" s="5"/>
       <c r="M280" s="7" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="281" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14874,7 +14862,7 @@
         <v>38</v>
       </c>
       <c r="H281" s="5" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I281" s="6" t="n">
         <v>46235</v>
@@ -14887,7 +14875,7 @@
       </c>
       <c r="L281" s="5"/>
       <c r="M281" s="7" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="282" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14926,7 +14914,7 @@
       </c>
       <c r="L282" s="5"/>
       <c r="M282" s="7" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="283" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14965,7 +14953,7 @@
       </c>
       <c r="L283" s="5"/>
       <c r="M283" s="7" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="284" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14988,7 +14976,7 @@
         <v>867</v>
       </c>
       <c r="G284" s="5" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="H284" s="5" t="s">
         <v>18</v>
@@ -15004,7 +14992,7 @@
       </c>
       <c r="L284" s="5"/>
       <c r="M284" s="7" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="285" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15043,7 +15031,7 @@
       </c>
       <c r="L285" s="5"/>
       <c r="M285" s="7" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="286" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15082,7 +15070,7 @@
       </c>
       <c r="L286" s="5"/>
       <c r="M286" s="7" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="287" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15121,7 +15109,7 @@
       </c>
       <c r="L287" s="5"/>
       <c r="M287" s="7" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="288" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15160,7 +15148,7 @@
       </c>
       <c r="L288" s="5"/>
       <c r="M288" s="7" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="289" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15199,7 +15187,7 @@
       </c>
       <c r="L289" s="5"/>
       <c r="M289" s="7" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="290" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15238,7 +15226,7 @@
       </c>
       <c r="L290" s="5"/>
       <c r="M290" s="7" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="291" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15277,7 +15265,7 @@
       </c>
       <c r="L291" s="5"/>
       <c r="M291" s="7" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="292" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15316,7 +15304,7 @@
       </c>
       <c r="L292" s="5"/>
       <c r="M292" s="7" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="293" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15355,7 +15343,7 @@
       </c>
       <c r="L293" s="5"/>
       <c r="M293" s="7" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="294" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15394,7 +15382,7 @@
       </c>
       <c r="L294" s="5"/>
       <c r="M294" s="7" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="295" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15433,7 +15421,7 @@
       </c>
       <c r="L295" s="5"/>
       <c r="M295" s="7" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="296" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15456,10 +15444,10 @@
         <v>903</v>
       </c>
       <c r="G296" s="5" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="H296" s="5" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I296" s="6" t="n">
         <v>46235</v>
@@ -15472,7 +15460,7 @@
       </c>
       <c r="L296" s="5"/>
       <c r="M296" s="7" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="297" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15511,7 +15499,7 @@
       </c>
       <c r="L297" s="5"/>
       <c r="M297" s="7" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="298" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15550,7 +15538,7 @@
       </c>
       <c r="L298" s="5"/>
       <c r="M298" s="7" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="299" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15589,7 +15577,7 @@
       </c>
       <c r="L299" s="5"/>
       <c r="M299" s="7" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="300" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15615,7 +15603,7 @@
         <v>38</v>
       </c>
       <c r="H300" s="5" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I300" s="6" t="n">
         <v>46235</v>
@@ -15628,7 +15616,7 @@
       </c>
       <c r="L300" s="5"/>
       <c r="M300" s="7" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="301" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15667,7 +15655,7 @@
       </c>
       <c r="L301" s="5"/>
       <c r="M301" s="7" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="302" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15706,7 +15694,7 @@
       </c>
       <c r="L302" s="5"/>
       <c r="M302" s="7" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="303" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15732,7 +15720,7 @@
         <v>38</v>
       </c>
       <c r="H303" s="5" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I303" s="6" t="n">
         <v>46235</v>
@@ -15745,7 +15733,7 @@
       </c>
       <c r="L303" s="5"/>
       <c r="M303" s="7" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="304" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15771,7 +15759,7 @@
         <v>38</v>
       </c>
       <c r="H304" s="5" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I304" s="6" t="n">
         <v>46235</v>
@@ -15784,7 +15772,7 @@
       </c>
       <c r="L304" s="5"/>
       <c r="M304" s="7" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="305" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15807,7 +15795,7 @@
         <v>930</v>
       </c>
       <c r="G305" s="5" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="H305" s="5" t="s">
         <v>18</v>
@@ -15823,7 +15811,7 @@
       </c>
       <c r="L305" s="5"/>
       <c r="M305" s="7" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="306" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16196,7 +16184,7 @@
         <v>38</v>
       </c>
       <c r="H315" s="5" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I315" s="6" t="n">
         <v>46235</v>
@@ -16235,7 +16223,7 @@
         <v>38</v>
       </c>
       <c r="H316" s="5" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I316" s="6" t="n">
         <v>46235</v>
@@ -16274,7 +16262,7 @@
         <v>38</v>
       </c>
       <c r="H317" s="5" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I317" s="6" t="n">
         <v>46235</v>
@@ -16313,7 +16301,7 @@
         <v>38</v>
       </c>
       <c r="H318" s="5" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I318" s="6" t="n">
         <v>46235</v>
@@ -16508,7 +16496,7 @@
         <v>38</v>
       </c>
       <c r="H323" s="5" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I323" s="6" t="n">
         <v>46235</v>
@@ -16778,10 +16766,10 @@
         <v>1004</v>
       </c>
       <c r="G330" s="5" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="H330" s="5" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I330" s="6" t="n">
         <v>46235</v>
@@ -16976,7 +16964,7 @@
         <v>38</v>
       </c>
       <c r="H335" s="5" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I335" s="6" t="n">
         <v>46235</v>
@@ -18146,7 +18134,7 @@
         <v>38</v>
       </c>
       <c r="H365" s="5" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I365" s="6" t="n">
         <v>46235</v>
@@ -18284,88 +18272,73 @@
         <v>1119</v>
       </c>
       <c r="B369" s="9"/>
-      <c r="C369" s="10"/>
-      <c r="D369" s="10"/>
+      <c r="C369" s="9"/>
+      <c r="D369" s="9"/>
       <c r="E369" s="9"/>
-      <c r="F369" s="11" t="str">
+      <c r="F369" s="10" t="str">
         <f aca="false">COUNTA(F2:F368)&amp;" mapped"</f>
         <v>366 mapped</v>
       </c>
-      <c r="G369" s="11"/>
-      <c r="H369" s="11"/>
-      <c r="I369" s="12"/>
-      <c r="J369" s="12"/>
-      <c r="K369" s="11" t="str">
-        <f aca="false">TEXT(COUNTIF(K2:K368,"50 GB")*50,"#,##0")&amp;" GB"</f>
-        <v>18,350 GB</v>
-      </c>
-      <c r="L369" s="13" t="str">
+      <c r="G369" s="9"/>
+      <c r="H369" s="9"/>
+      <c r="I369" s="9"/>
+      <c r="J369" s="9"/>
+      <c r="K369" s="11" t="n">
+        <f aca="false">COUNTIF(K2:K368,"50 GB")*50</f>
+        <v>18350</v>
+      </c>
+      <c r="L369" s="12" t="str">
         <f aca="false">COUNTA(E2:E368)&amp;" kits"</f>
         <v>367 kits</v>
       </c>
-      <c r="M369" s="14" t="n">
+      <c r="M369" s="13" t="n">
         <f aca="false">SUM(M2:M368)</f>
-        <v>24298.74</v>
+        <v>25454.55</v>
       </c>
     </row>
     <row r="371" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A371" s="15" t="s">
+      <c r="A371" s="14" t="s">
         <v>1120</v>
       </c>
     </row>
     <row r="372" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A372" s="16" t="s">
+      <c r="A372" s="15" t="s">
         <v>1121</v>
       </c>
     </row>
     <row r="373" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A373" s="16" t="s">
+      <c r="A373" s="15" t="s">
         <v>1122</v>
       </c>
     </row>
     <row r="374" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A374" s="16" t="s">
+      <c r="A374" s="15" t="s">
         <v>1123</v>
       </c>
     </row>
     <row r="375" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A375" s="16" t="s">
+      <c r="A375" s="15" t="s">
         <v>1124</v>
       </c>
     </row>
     <row r="376" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A376" s="16" t="s">
+      <c r="A376" s="15" t="s">
         <v>1125</v>
       </c>
     </row>
     <row r="377" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A377" s="16" t="s">
+      <c r="A377" s="15" t="s">
         <v>1126</v>
       </c>
     </row>
     <row r="378" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A378" s="16" t="s">
+      <c r="A378" s="15" t="s">
         <v>1127</v>
       </c>
     </row>
     <row r="379" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A379" s="16" t="s">
+      <c r="A379" s="15" t="s">
         <v>1128</v>
-      </c>
-    </row>
-    <row r="380" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A380" s="16" t="s">
-        <v>1129</v>
-      </c>
-    </row>
-    <row r="381" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A381" s="16" t="s">
-        <v>1130</v>
-      </c>
-    </row>
-    <row r="382" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A382" s="16" t="s">
-        <v>1131</v>
       </c>
     </row>
   </sheetData>

--- a/Starlink_Usage_Current_by_Kit.xlsx
+++ b/Starlink_Usage_Current_by_Kit.xlsx
@@ -20113,7 +20113,7 @@
     <row r="379">
       <c r="A379" s="15" t="inlineStr">
         <is>
-          <t>Generated 2026-08-25 08:19 by build_starlink_usage.py</t>
+          <t>Generated 2026-08-25 08:24 by build_starlink_usage.py</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_Current_by_Kit.xlsx
+++ b/Starlink_Usage_Current_by_Kit.xlsx
@@ -20113,7 +20113,7 @@
     <row r="379">
       <c r="A379" s="15" t="inlineStr">
         <is>
-          <t>Generated 2026-08-25 08:24 by build_starlink_usage.py</t>
+          <t>Generated 2026-08-25 08:49 by build_starlink_usage.py</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_Current_by_Kit.xlsx
+++ b/Starlink_Usage_Current_by_Kit.xlsx
@@ -630,7 +630,7 @@
       </c>
       <c r="L2" s="5" t="n"/>
       <c r="M2" s="7" t="n">
-        <v>2258.31</v>
+        <v>2258.5</v>
       </c>
     </row>
     <row r="3">
@@ -683,7 +683,7 @@
       </c>
       <c r="L3" s="5" t="n"/>
       <c r="M3" s="7" t="n">
-        <v>2218.24</v>
+        <v>2255.16</v>
       </c>
     </row>
     <row r="4">
@@ -736,7 +736,7 @@
       </c>
       <c r="L4" s="5" t="n"/>
       <c r="M4" s="7" t="n">
-        <v>1595.08</v>
+        <v>1597.61</v>
       </c>
     </row>
     <row r="5">
@@ -789,7 +789,7 @@
       </c>
       <c r="L5" s="5" t="n"/>
       <c r="M5" s="7" t="n">
-        <v>1062.48</v>
+        <v>1062.8</v>
       </c>
     </row>
     <row r="6">
@@ -959,7 +959,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270111116 - KIT4P00065612DJF</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955122 - KIT4P00073922FPF</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
@@ -970,12 +970,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065612DJF</t>
+          <t>KIT4P00073922FPF</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>809605</t>
+          <t>814641</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="L9" s="5" t="n"/>
       <c r="M9" s="7" t="n">
-        <v>703.79</v>
+        <v>732.97</v>
       </c>
     </row>
     <row r="10">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955122 - KIT4P00073922FPF</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270111116 - KIT4P00065612DJF</t>
         </is>
       </c>
       <c r="C10" s="3" t="n">
@@ -1023,12 +1023,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073922FPF</t>
+          <t>KIT4P00065612DJF</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>814641</t>
+          <t>809605</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="L10" s="5" t="n"/>
       <c r="M10" s="7" t="n">
-        <v>660.55</v>
+        <v>704.34</v>
       </c>
     </row>
     <row r="11">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="L11" s="5" t="n"/>
       <c r="M11" s="7" t="n">
-        <v>639.9400000000001</v>
+        <v>642.0700000000001</v>
       </c>
     </row>
     <row r="12">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955102 - KIT4P000739257CR</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955192 - KIT4M05563510TWC</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
@@ -1182,17 +1182,17 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>KIT4P000739257CR</t>
+          <t>KIT4M05563510TWC</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>814609</t>
+          <t>814433</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="L13" s="5" t="n"/>
       <c r="M13" s="7" t="n">
-        <v>579.42</v>
+        <v>582.5700000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955192 - KIT4M05563510TWC</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955102 - KIT4P000739257CR</t>
         </is>
       </c>
       <c r="C14" s="3" t="n">
@@ -1235,17 +1235,17 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563510TWC</t>
+          <t>KIT4P000739257CR</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>814433</t>
+          <t>814609</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L14" s="5" t="n"/>
       <c r="M14" s="7" t="n">
-        <v>577.77</v>
+        <v>579.86</v>
       </c>
     </row>
     <row r="15">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437292 - KIT4P000832806P4</t>
+          <t>SS - 05900510 - Los Angeles, CA - 021437242 - KIT4P00083890S2G</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>KIT4P000832806P4</t>
+          <t>KIT4P00083890S2G</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>816228</t>
+          <t>816226</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="L15" s="5" t="n"/>
       <c r="M15" s="7" t="n">
-        <v>521.04</v>
+        <v>541.74</v>
       </c>
     </row>
     <row r="16">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 021437242 - KIT4P00083890S2G</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437292 - KIT4P000832806P4</t>
         </is>
       </c>
       <c r="C16" s="3" t="n">
@@ -1341,12 +1341,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00083890S2G</t>
+          <t>KIT4P000832806P4</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>816226</t>
+          <t>816228</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="L16" s="5" t="n"/>
       <c r="M16" s="7" t="n">
-        <v>508.16</v>
+        <v>536.3099999999999</v>
       </c>
     </row>
     <row r="17">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020650002 - KIT4M05413770WCC</t>
+          <t>SMRT-05900510-Los Angeles CA-021437282-KIT4P00084593R9F</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
@@ -1394,17 +1394,17 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413770WCC</t>
+          <t>KIT4P00084593R9F</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>812819</t>
+          <t>816227</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="L17" s="5" t="n"/>
       <c r="M17" s="7" t="n">
-        <v>462.9</v>
+        <v>483.87</v>
       </c>
     </row>
     <row r="18">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437282-KIT4P00084593R9F</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020650002 - KIT4M05413770WCC</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00084593R9F</t>
+          <t>KIT4M05413770WCC</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>816227</t>
+          <t>812819</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="L18" s="5" t="n"/>
       <c r="M18" s="7" t="n">
-        <v>437.85</v>
+        <v>462.9</v>
       </c>
     </row>
     <row r="19">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="L20" s="5" t="n"/>
       <c r="M20" s="7" t="n">
-        <v>403.43</v>
+        <v>408.93</v>
       </c>
     </row>
     <row r="21">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="L22" s="5" t="n"/>
       <c r="M22" s="7" t="n">
-        <v>353.1</v>
+        <v>359.58</v>
       </c>
     </row>
     <row r="23">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="L23" s="5" t="n"/>
       <c r="M23" s="7" t="n">
-        <v>337.02</v>
+        <v>343.05</v>
       </c>
     </row>
     <row r="24">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="L27" s="5" t="n"/>
       <c r="M27" s="7" t="n">
-        <v>259.89</v>
+        <v>260.21</v>
       </c>
     </row>
     <row r="28">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="L29" s="5" t="n"/>
       <c r="M29" s="7" t="n">
-        <v>250.03</v>
+        <v>250.11</v>
       </c>
     </row>
     <row r="30">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="L32" s="5" t="n"/>
       <c r="M32" s="7" t="n">
-        <v>166.94</v>
+        <v>168.79</v>
       </c>
     </row>
     <row r="33">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="L36" s="5" t="n"/>
       <c r="M36" s="7" t="n">
-        <v>120.64</v>
+        <v>122.2</v>
       </c>
     </row>
     <row r="37">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="L37" s="5" t="n"/>
       <c r="M37" s="7" t="n">
-        <v>116.87</v>
+        <v>119.27</v>
       </c>
     </row>
     <row r="38">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649542 - KIT4M05413810Q4Z</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955682 - KIT4M055635887MK</t>
         </is>
       </c>
       <c r="C39" s="3" t="n">
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413810Q4Z</t>
+          <t>KIT4M055635887MK</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>812815</t>
+          <t>814446</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="L39" s="5" t="n"/>
       <c r="M39" s="7" t="n">
-        <v>109.69</v>
+        <v>112.32</v>
       </c>
     </row>
     <row r="40">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles, CA-020955372-KIT4M05563537G4G</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438032 - KIT4M05799683GCK</t>
         </is>
       </c>
       <c r="C40" s="3" t="n">
@@ -2613,12 +2613,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563537G4G</t>
+          <t>KIT4M05799683GCK</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>814456</t>
+          <t>816270</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="L40" s="5" t="n"/>
       <c r="M40" s="7" t="n">
-        <v>108.22</v>
+        <v>112.21</v>
       </c>
     </row>
     <row r="41">
@@ -2655,7 +2655,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955682 - KIT4M055635887MK</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649542 - KIT4M05413810Q4Z</t>
         </is>
       </c>
       <c r="C41" s="3" t="n">
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635887MK</t>
+          <t>KIT4M05413810Q4Z</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>814446</t>
+          <t>812815</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="L41" s="5" t="n"/>
       <c r="M41" s="7" t="n">
-        <v>108</v>
+        <v>109.69</v>
       </c>
     </row>
     <row r="42">
@@ -2708,7 +2708,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438032 - KIT4M05799683GCK</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437252 - KIT4P00083897XCW</t>
         </is>
       </c>
       <c r="C42" s="3" t="n">
@@ -2719,17 +2719,17 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799683GCK</t>
+          <t>KIT4P00083897XCW</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>816270</t>
+          <t>816223</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H42" s="5" t="inlineStr">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="L42" s="5" t="n"/>
       <c r="M42" s="7" t="n">
-        <v>104.07</v>
+        <v>108.58</v>
       </c>
     </row>
     <row r="43">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437252 - KIT4P00083897XCW</t>
+          <t>SMRT-05900510-Los Angeles, CA-020955372-KIT4M05563537G4G</t>
         </is>
       </c>
       <c r="C43" s="3" t="n">
@@ -2772,17 +2772,17 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00083897XCW</t>
+          <t>KIT4M05563537G4G</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>816223</t>
+          <t>814456</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="L43" s="5" t="n"/>
       <c r="M43" s="7" t="n">
-        <v>101.3</v>
+        <v>108.22</v>
       </c>
     </row>
     <row r="44">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="L44" s="5" t="n"/>
       <c r="M44" s="7" t="n">
-        <v>99.77</v>
+        <v>102.52</v>
       </c>
     </row>
     <row r="45">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="L47" s="5" t="n"/>
       <c r="M47" s="7" t="n">
-        <v>93.09999999999999</v>
+        <v>93.20999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="L50" s="5" t="n"/>
       <c r="M50" s="7" t="n">
-        <v>89.81</v>
+        <v>89.98999999999999</v>
       </c>
     </row>
     <row r="51">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="L51" s="5" t="n"/>
       <c r="M51" s="7" t="n">
-        <v>87.13</v>
+        <v>87.18000000000001</v>
       </c>
     </row>
     <row r="52">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955472 - KIT4M055635834N7</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020650172 - KIT4M05413811F4Q</t>
         </is>
       </c>
       <c r="C52" s="3" t="n">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635834N7</t>
+          <t>KIT4M05413811F4Q</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>814462</t>
+          <t>810104</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="L52" s="5" t="n"/>
       <c r="M52" s="7" t="n">
-        <v>86.98</v>
+        <v>87.03</v>
       </c>
     </row>
     <row r="53">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020650172 - KIT4M05413811F4Q</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955472 - KIT4M055635834N7</t>
         </is>
       </c>
       <c r="C53" s="3" t="n">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413811F4Q</t>
+          <t>KIT4M055635834N7</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>810104</t>
+          <t>814462</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="L53" s="5" t="n"/>
       <c r="M53" s="7" t="n">
-        <v>86.22</v>
+        <v>86.98</v>
       </c>
     </row>
     <row r="54">
@@ -3503,7 +3503,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955332 - KIT4M05563590ZFQ</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649842 - KIT4M025787739XF</t>
         </is>
       </c>
       <c r="C57" s="3" t="n">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563590ZFQ</t>
+          <t>KIT4M025787739XF</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>814461</t>
+          <t>809864</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="L57" s="5" t="n"/>
       <c r="M57" s="7" t="n">
-        <v>77.59</v>
+        <v>81.42</v>
       </c>
     </row>
     <row r="58">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649842 - KIT4M025787739XF</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955332 - KIT4M05563590ZFQ</t>
         </is>
       </c>
       <c r="C58" s="3" t="n">
@@ -3567,12 +3567,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>KIT4M025787739XF</t>
+          <t>KIT4M05563590ZFQ</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>809864</t>
+          <t>814461</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="L58" s="5" t="n"/>
       <c r="M58" s="7" t="n">
-        <v>77.14</v>
+        <v>78.06999999999999</v>
       </c>
     </row>
     <row r="59">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="L60" s="5" t="n"/>
       <c r="M60" s="7" t="n">
-        <v>67.84</v>
+        <v>67.91</v>
       </c>
     </row>
     <row r="61">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="L63" s="5" t="n"/>
       <c r="M63" s="7" t="n">
-        <v>61.1</v>
+        <v>61.23</v>
       </c>
     </row>
     <row r="64">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="L64" s="5" t="n"/>
       <c r="M64" s="7" t="n">
-        <v>59.43</v>
+        <v>60.42</v>
       </c>
     </row>
     <row r="65">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482704 - KIT4M04604745G8Z</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955492 - KIT4M05563520SH2</t>
         </is>
       </c>
       <c r="C68" s="3" t="n">
@@ -4097,12 +4097,12 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604745G8Z</t>
+          <t>KIT4M05563520SH2</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>809661</t>
+          <t>814478</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="L68" s="5" t="n"/>
       <c r="M68" s="7" t="n">
-        <v>55.59</v>
+        <v>56.27</v>
       </c>
     </row>
     <row r="69">
@@ -4139,7 +4139,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955492 - KIT4M05563520SH2</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482704 - KIT4M04604745G8Z</t>
         </is>
       </c>
       <c r="C69" s="3" t="n">
@@ -4150,12 +4150,12 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563520SH2</t>
+          <t>KIT4M04604745G8Z</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>814478</t>
+          <t>809661</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="L69" s="5" t="n"/>
       <c r="M69" s="7" t="n">
-        <v>55.15</v>
+        <v>55.75</v>
       </c>
     </row>
     <row r="70">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270111114 - KIT4P00065593VWC</t>
+          <t>SS - 05900510 - Los Angeles CA - CW6578840- KIT4M04475128THH</t>
         </is>
       </c>
       <c r="C73" s="3" t="n">
@@ -4362,17 +4362,17 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065593VWC</t>
+          <t>KIT4M04475128THH</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>809606</t>
+          <t>809860</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H73" s="5" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="L73" s="5" t="n"/>
       <c r="M73" s="7" t="n">
-        <v>49.23</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="74">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955182 - KIT4M05563562F45</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270111114 - KIT4P00065593VWC</t>
         </is>
       </c>
       <c r="C74" s="3" t="n">
@@ -4415,17 +4415,17 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563562F45</t>
+          <t>KIT4P00065593VWC</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>814443</t>
+          <t>809606</t>
         </is>
       </c>
       <c r="G74" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H74" s="5" t="inlineStr">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="L74" s="5" t="n"/>
       <c r="M74" s="7" t="n">
-        <v>48.47</v>
+        <v>49.23</v>
       </c>
     </row>
     <row r="75">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SS - 05900510 - Los Angeles, CA - 020649552 - KIT4M05413835RPF </t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955182 - KIT4M05563562F45</t>
         </is>
       </c>
       <c r="C75" s="3" t="n">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413835RPF</t>
+          <t>KIT4M05563562F45</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>812827</t>
+          <t>814443</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="L75" s="5" t="n"/>
       <c r="M75" s="7" t="n">
-        <v>48.24</v>
+        <v>48.47</v>
       </c>
     </row>
     <row r="76">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-LOS ANGELES CA-020955202-KIT4M05563534GZ7</t>
+          <t xml:space="preserve">SS - 05900510 - Los Angeles, CA - 020649552 - KIT4M05413835RPF </t>
         </is>
       </c>
       <c r="C76" s="3" t="n">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563534GZ7</t>
+          <t>KIT4M05413835RPF</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>814467</t>
+          <t>812827</t>
         </is>
       </c>
       <c r="G76" s="5" t="inlineStr">
@@ -4552,7 +4552,7 @@
       </c>
       <c r="L76" s="5" t="n"/>
       <c r="M76" s="7" t="n">
-        <v>47.79</v>
+        <v>48.25</v>
       </c>
     </row>
     <row r="77">
@@ -4605,7 +4605,7 @@
       </c>
       <c r="L77" s="5" t="n"/>
       <c r="M77" s="7" t="n">
-        <v>47.74</v>
+        <v>47.93</v>
       </c>
     </row>
     <row r="78">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020650142 - KIT4M05413839D24</t>
+          <t>SMRT-05900510-LOS ANGELES CA-020955202-KIT4M05563534GZ7</t>
         </is>
       </c>
       <c r="C78" s="3" t="n">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413839D24</t>
+          <t>KIT4M05563534GZ7</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>810096</t>
+          <t>814467</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="L78" s="5" t="n"/>
       <c r="M78" s="7" t="n">
-        <v>46.99</v>
+        <v>47.79</v>
       </c>
     </row>
     <row r="79">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649672 - KIT4M04606113TPB</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020650142 - KIT4M05413839D24</t>
         </is>
       </c>
       <c r="C79" s="3" t="n">
@@ -4680,12 +4680,12 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04606113TPB</t>
+          <t>KIT4M05413839D24</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>809862</t>
+          <t>810096</t>
         </is>
       </c>
       <c r="G79" s="5" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="L79" s="5" t="n"/>
       <c r="M79" s="7" t="n">
-        <v>46.74</v>
+        <v>47.58</v>
       </c>
     </row>
     <row r="80">
@@ -4722,7 +4722,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - CW6578840- KIT4M04475128THH</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649672 - KIT4M04606113TPB</t>
         </is>
       </c>
       <c r="C80" s="3" t="n">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475128THH</t>
+          <t>KIT4M04606113TPB</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>809860</t>
+          <t>809862</t>
         </is>
       </c>
       <c r="G80" s="5" t="inlineStr">
@@ -4764,7 +4764,7 @@
       </c>
       <c r="L80" s="5" t="n"/>
       <c r="M80" s="7" t="n">
-        <v>46.4</v>
+        <v>46.74</v>
       </c>
     </row>
     <row r="81">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="L81" s="5" t="n"/>
       <c r="M81" s="7" t="n">
-        <v>46.17</v>
+        <v>46.65</v>
       </c>
     </row>
     <row r="82">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270112 - KIT4M044751638F5</t>
+          <t>SMRT-05900510-Los Angeles, CA-020955452-KIT4M05563529K2D</t>
         </is>
       </c>
       <c r="C88" s="3" t="n">
@@ -5157,12 +5157,12 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>KIT4M044751638F5</t>
+          <t>KIT4M05563529K2D</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>809618</t>
+          <t>814473</t>
         </is>
       </c>
       <c r="G88" s="5" t="inlineStr">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="L88" s="5" t="n"/>
       <c r="M88" s="7" t="n">
-        <v>40.42</v>
+        <v>40.8</v>
       </c>
     </row>
     <row r="89">
@@ -5199,7 +5199,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles, CA-020955452-KIT4M05563529K2D</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270112 - KIT4M044751638F5</t>
         </is>
       </c>
       <c r="C89" s="3" t="n">
@@ -5210,12 +5210,12 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563529K2D</t>
+          <t>KIT4M044751638F5</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>814473</t>
+          <t>809618</t>
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr">
@@ -5241,7 +5241,7 @@
       </c>
       <c r="L89" s="5" t="n"/>
       <c r="M89" s="7" t="n">
-        <v>40.41</v>
+        <v>40.77</v>
       </c>
     </row>
     <row r="90">
@@ -5400,7 +5400,7 @@
       </c>
       <c r="L92" s="5" t="n"/>
       <c r="M92" s="7" t="n">
-        <v>39.05</v>
+        <v>39.25</v>
       </c>
     </row>
     <row r="93">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955602 - KIT4M05563560225</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649782 - KIT4M03986264P49</t>
         </is>
       </c>
       <c r="C93" s="3" t="n">
@@ -5422,12 +5422,12 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563560225</t>
+          <t>KIT4M03986264P49</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>814454</t>
+          <t>809875</t>
         </is>
       </c>
       <c r="G93" s="5" t="inlineStr">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="L93" s="5" t="n"/>
       <c r="M93" s="7" t="n">
-        <v>38.09</v>
+        <v>38.99</v>
       </c>
     </row>
     <row r="94">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020650082 - KIT4M05413792H8C</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955602 - KIT4M05563560225</t>
         </is>
       </c>
       <c r="C94" s="3" t="n">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413792H8C</t>
+          <t>KIT4M05563560225</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>812803</t>
+          <t>814454</t>
         </is>
       </c>
       <c r="G94" s="5" t="inlineStr">
@@ -5506,7 +5506,7 @@
       </c>
       <c r="L94" s="5" t="n"/>
       <c r="M94" s="7" t="n">
-        <v>37.8</v>
+        <v>38.09</v>
       </c>
     </row>
     <row r="95">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649782 - KIT4M03986264P49</t>
+          <t>STS - 05900510 - Los Angeles CA - 020650082 - KIT4M05413792H8C</t>
         </is>
       </c>
       <c r="C95" s="3" t="n">
@@ -5528,12 +5528,12 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03986264P49</t>
+          <t>KIT4M05413792H8C</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>809875</t>
+          <t>812803</t>
         </is>
       </c>
       <c r="G95" s="5" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="L95" s="5" t="n"/>
       <c r="M95" s="7" t="n">
-        <v>36.67</v>
+        <v>37.8</v>
       </c>
     </row>
     <row r="96">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="L96" s="5" t="n"/>
       <c r="M96" s="7" t="n">
-        <v>35.76</v>
+        <v>35.77</v>
       </c>
     </row>
     <row r="97">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955272 - KIT4M05563585TXM</t>
+          <t>SS - 05900510 -  Los Angeles CA - 020955382 - KIT4M05563509CHJ</t>
         </is>
       </c>
       <c r="C97" s="3" t="n">
@@ -5634,12 +5634,12 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563585TXM</t>
+          <t>KIT4M05563509CHJ</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>814475</t>
+          <t>814431</t>
         </is>
       </c>
       <c r="G97" s="5" t="inlineStr">
@@ -5665,7 +5665,7 @@
       </c>
       <c r="L97" s="5" t="n"/>
       <c r="M97" s="7" t="n">
-        <v>33.89</v>
+        <v>34.29</v>
       </c>
     </row>
     <row r="98">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 020955382 - KIT4M05563509CHJ</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955272 - KIT4M05563585TXM</t>
         </is>
       </c>
       <c r="C98" s="3" t="n">
@@ -5687,12 +5687,12 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563509CHJ</t>
+          <t>KIT4M05563585TXM</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>814431</t>
+          <t>814475</t>
         </is>
       </c>
       <c r="G98" s="5" t="inlineStr">
@@ -5718,7 +5718,7 @@
       </c>
       <c r="L98" s="5" t="n"/>
       <c r="M98" s="7" t="n">
-        <v>33.37</v>
+        <v>33.89</v>
       </c>
     </row>
     <row r="99">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="L99" s="5" t="n"/>
       <c r="M99" s="7" t="n">
-        <v>32.81</v>
+        <v>33.12</v>
       </c>
     </row>
     <row r="100">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649412 - KIT4M05413769796</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955692 - KIT4M05563579H9F</t>
         </is>
       </c>
       <c r="C100" s="3" t="n">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413769796</t>
+          <t>KIT4M05563579H9F</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>812839</t>
+          <t>814480</t>
         </is>
       </c>
       <c r="G100" s="5" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="L100" s="5" t="n"/>
       <c r="M100" s="7" t="n">
-        <v>32.57</v>
+        <v>32.85</v>
       </c>
     </row>
     <row r="101">
@@ -5835,7 +5835,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955132 - KIT4M055635238J6</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649412 - KIT4M05413769796</t>
         </is>
       </c>
       <c r="C101" s="3" t="n">
@@ -5846,12 +5846,12 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635238J6</t>
+          <t>KIT4M05413769796</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>814449</t>
+          <t>812839</t>
         </is>
       </c>
       <c r="G101" s="5" t="inlineStr">
@@ -5877,7 +5877,7 @@
       </c>
       <c r="L101" s="5" t="n"/>
       <c r="M101" s="7" t="n">
-        <v>32.44</v>
+        <v>32.57</v>
       </c>
     </row>
     <row r="102">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649942 - KIT4M05413786BXC</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955132 - KIT4M055635238J6</t>
         </is>
       </c>
       <c r="C102" s="3" t="n">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413786BXC</t>
+          <t>KIT4M055635238J6</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>812838</t>
+          <t>814449</t>
         </is>
       </c>
       <c r="G102" s="5" t="inlineStr">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="L102" s="5" t="n"/>
       <c r="M102" s="7" t="n">
-        <v>31.59</v>
+        <v>32.44</v>
       </c>
     </row>
     <row r="103">
@@ -5941,7 +5941,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955692 - KIT4M05563579H9F</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649942 - KIT4M05413786BXC</t>
         </is>
       </c>
       <c r="C103" s="3" t="n">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563579H9F</t>
+          <t>KIT4M05413786BXC</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>814480</t>
+          <t>812838</t>
         </is>
       </c>
       <c r="G103" s="5" t="inlineStr">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="L103" s="5" t="n"/>
       <c r="M103" s="7" t="n">
-        <v>31.26</v>
+        <v>31.99</v>
       </c>
     </row>
     <row r="104">
@@ -6036,7 +6036,7 @@
       </c>
       <c r="L104" s="5" t="n"/>
       <c r="M104" s="7" t="n">
-        <v>31.12</v>
+        <v>31.77</v>
       </c>
     </row>
     <row r="105">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649372 - KIT4M05368221HQ5</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955522 - KIT4M05563504MBB</t>
         </is>
       </c>
       <c r="C105" s="3" t="n">
@@ -6058,12 +6058,12 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368221HQ5</t>
+          <t>KIT4M05563504MBB</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>810834</t>
+          <t>814460</t>
         </is>
       </c>
       <c r="G105" s="5" t="inlineStr">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="L105" s="5" t="n"/>
       <c r="M105" s="7" t="n">
-        <v>29.14</v>
+        <v>30.66</v>
       </c>
     </row>
     <row r="106">
@@ -6100,7 +6100,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020955462 - KIT4M05563513GTF</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955292 - KIT4M05563531XSB</t>
         </is>
       </c>
       <c r="C106" s="3" t="n">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563513GTF</t>
+          <t>KIT4M05563531XSB</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>814432</t>
+          <t>814469</t>
         </is>
       </c>
       <c r="G106" s="5" t="inlineStr">
@@ -6142,7 +6142,7 @@
       </c>
       <c r="L106" s="5" t="n"/>
       <c r="M106" s="7" t="n">
-        <v>28.14</v>
+        <v>30.41</v>
       </c>
     </row>
     <row r="107">
@@ -6153,7 +6153,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955292 - KIT4M05563531XSB</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649372 - KIT4M05368221HQ5</t>
         </is>
       </c>
       <c r="C107" s="3" t="n">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563531XSB</t>
+          <t>KIT4M05368221HQ5</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>814469</t>
+          <t>810834</t>
         </is>
       </c>
       <c r="G107" s="5" t="inlineStr">
@@ -6195,7 +6195,7 @@
       </c>
       <c r="L107" s="5" t="n"/>
       <c r="M107" s="7" t="n">
-        <v>27.7</v>
+        <v>29.14</v>
       </c>
     </row>
     <row r="108">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955522 - KIT4M05563504MBB</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020955462 - KIT4M05563513GTF</t>
         </is>
       </c>
       <c r="C108" s="3" t="n">
@@ -6217,12 +6217,12 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563504MBB</t>
+          <t>KIT4M05563513GTF</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>814460</t>
+          <t>814432</t>
         </is>
       </c>
       <c r="G108" s="5" t="inlineStr">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="L108" s="5" t="n"/>
       <c r="M108" s="7" t="n">
-        <v>27.29</v>
+        <v>28.14</v>
       </c>
     </row>
     <row r="109">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="L109" s="5" t="n"/>
       <c r="M109" s="7" t="n">
-        <v>27.19</v>
+        <v>27.66</v>
       </c>
     </row>
     <row r="110">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="L111" s="5" t="n"/>
       <c r="M111" s="7" t="n">
-        <v>26.77</v>
+        <v>26.81</v>
       </c>
     </row>
     <row r="112">
@@ -6471,7 +6471,7 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955342 - KIT4M05563524MJ4</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437392 - KIT4M05872555BJR</t>
         </is>
       </c>
       <c r="C113" s="3" t="n">
@@ -6482,12 +6482,12 @@
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563524MJ4</t>
+          <t>KIT4M05872555BJR</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>814472</t>
+          <t>816074</t>
         </is>
       </c>
       <c r="G113" s="5" t="inlineStr">
@@ -6513,7 +6513,7 @@
       </c>
       <c r="L113" s="5" t="n"/>
       <c r="M113" s="7" t="n">
-        <v>26.26</v>
+        <v>26.44</v>
       </c>
     </row>
     <row r="114">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482706 - KIT4M04604744V6K</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955342 - KIT4M05563524MJ4</t>
         </is>
       </c>
       <c r="C114" s="3" t="n">
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604744V6K</t>
+          <t>KIT4M05563524MJ4</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>809659</t>
+          <t>814472</t>
         </is>
       </c>
       <c r="G114" s="5" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="L114" s="5" t="n"/>
       <c r="M114" s="7" t="n">
-        <v>25.81</v>
+        <v>26.26</v>
       </c>
     </row>
     <row r="115">
@@ -6577,7 +6577,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649362 - KIT4M05368336DBC</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482706 - KIT4M04604744V6K</t>
         </is>
       </c>
       <c r="C115" s="3" t="n">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368336DBC</t>
+          <t>KIT4M04604744V6K</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>810831</t>
+          <t>809659</t>
         </is>
       </c>
       <c r="G115" s="5" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="L115" s="5" t="n"/>
       <c r="M115" s="7" t="n">
-        <v>25.13</v>
+        <v>26.16</v>
       </c>
     </row>
     <row r="116">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955212 - KIT4M05563512GBQ</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649362 - KIT4M05368336DBC</t>
         </is>
       </c>
       <c r="C116" s="3" t="n">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563512GBQ</t>
+          <t>KIT4M05368336DBC</t>
         </is>
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>814435</t>
+          <t>810831</t>
         </is>
       </c>
       <c r="G116" s="5" t="inlineStr">
@@ -6672,7 +6672,7 @@
       </c>
       <c r="L116" s="5" t="n"/>
       <c r="M116" s="7" t="n">
-        <v>24.54</v>
+        <v>25.13</v>
       </c>
     </row>
     <row r="117">
@@ -6683,7 +6683,7 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437392 - KIT4M05872555BJR</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955212 - KIT4M05563512GBQ</t>
         </is>
       </c>
       <c r="C117" s="3" t="n">
@@ -6694,12 +6694,12 @@
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872555BJR</t>
+          <t>KIT4M05563512GBQ</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>816074</t>
+          <t>814435</t>
         </is>
       </c>
       <c r="G117" s="5" t="inlineStr">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="L117" s="5" t="n"/>
       <c r="M117" s="7" t="n">
-        <v>24.51</v>
+        <v>24.54</v>
       </c>
     </row>
     <row r="118">
@@ -6736,7 +6736,7 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437782 - KIT4M058724975J4</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955112 - KIT4P00073918HBX</t>
         </is>
       </c>
       <c r="C118" s="3" t="n">
@@ -6747,17 +6747,17 @@
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058724975J4</t>
+          <t>KIT4P00073918HBX</t>
         </is>
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>816075</t>
+          <t>814645</t>
         </is>
       </c>
       <c r="G118" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H118" s="5" t="inlineStr">
@@ -6778,7 +6778,7 @@
       </c>
       <c r="L118" s="5" t="n"/>
       <c r="M118" s="7" t="n">
-        <v>23.88</v>
+        <v>23.89</v>
       </c>
     </row>
     <row r="119">
@@ -6789,7 +6789,7 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955112 - KIT4P00073918HBX</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437782 - KIT4M058724975J4</t>
         </is>
       </c>
       <c r="C119" s="3" t="n">
@@ -6800,17 +6800,17 @@
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073918HBX</t>
+          <t>KIT4M058724975J4</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>814645</t>
+          <t>816075</t>
         </is>
       </c>
       <c r="G119" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H119" s="5" t="inlineStr">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="L119" s="5" t="n"/>
       <c r="M119" s="7" t="n">
-        <v>23.86</v>
+        <v>23.88</v>
       </c>
     </row>
     <row r="120">
@@ -7107,7 +7107,7 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649302 - KIT4M05368226W57</t>
+          <t>SS - 05900510 - Los Angeles CA - 6858375 - KIT4M05872512N5W</t>
         </is>
       </c>
       <c r="C125" s="3" t="n">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368226W57</t>
+          <t>KIT4M05872512N5W</t>
         </is>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>810833</t>
+          <t>816077</t>
         </is>
       </c>
       <c r="G125" s="5" t="inlineStr">
@@ -7149,7 +7149,7 @@
       </c>
       <c r="L125" s="5" t="n"/>
       <c r="M125" s="7" t="n">
-        <v>19.62</v>
+        <v>19.87</v>
       </c>
     </row>
     <row r="126">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="L126" s="5" t="n"/>
       <c r="M126" s="7" t="n">
-        <v>19.59</v>
+        <v>19.67</v>
       </c>
     </row>
     <row r="127">
@@ -7213,7 +7213,7 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020650242 - KIT4M05413804SKS</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649302 - KIT4M05368226W57</t>
         </is>
       </c>
       <c r="C127" s="3" t="n">
@@ -7224,12 +7224,12 @@
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413804SKS</t>
+          <t>KIT4M05368226W57</t>
         </is>
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>810102</t>
+          <t>810833</t>
         </is>
       </c>
       <c r="G127" s="5" t="inlineStr">
@@ -7255,7 +7255,7 @@
       </c>
       <c r="L127" s="5" t="n"/>
       <c r="M127" s="7" t="n">
-        <v>19.21</v>
+        <v>19.62</v>
       </c>
     </row>
     <row r="128">
@@ -7266,7 +7266,7 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955282 - KIT4M055635227ZR</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020650242 - KIT4M05413804SKS</t>
         </is>
       </c>
       <c r="C128" s="3" t="n">
@@ -7277,12 +7277,12 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635227ZR</t>
+          <t>KIT4M05413804SKS</t>
         </is>
       </c>
       <c r="F128" s="4" t="inlineStr">
         <is>
-          <t>814482</t>
+          <t>810102</t>
         </is>
       </c>
       <c r="G128" s="5" t="inlineStr">
@@ -7308,7 +7308,7 @@
       </c>
       <c r="L128" s="5" t="n"/>
       <c r="M128" s="7" t="n">
-        <v>19.17</v>
+        <v>19.21</v>
       </c>
     </row>
     <row r="129">
@@ -7319,7 +7319,7 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955532 - KIT4M05563548P9Q</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955282 - KIT4M055635227ZR</t>
         </is>
       </c>
       <c r="C129" s="3" t="n">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563548P9Q</t>
+          <t>KIT4M055635227ZR</t>
         </is>
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>814468</t>
+          <t>814482</t>
         </is>
       </c>
       <c r="G129" s="5" t="inlineStr">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="L129" s="5" t="n"/>
       <c r="M129" s="7" t="n">
-        <v>19.15</v>
+        <v>19.17</v>
       </c>
     </row>
     <row r="130">
@@ -7372,7 +7372,7 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955302 - KIT4M055635158PC</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955532 - KIT4M05563548P9Q</t>
         </is>
       </c>
       <c r="C130" s="3" t="n">
@@ -7383,12 +7383,12 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635158PC</t>
+          <t>KIT4M05563548P9Q</t>
         </is>
       </c>
       <c r="F130" s="4" t="inlineStr">
         <is>
-          <t>814457</t>
+          <t>814468</t>
         </is>
       </c>
       <c r="G130" s="5" t="inlineStr">
@@ -7414,7 +7414,7 @@
       </c>
       <c r="L130" s="5" t="n"/>
       <c r="M130" s="7" t="n">
-        <v>18.73</v>
+        <v>19.15</v>
       </c>
     </row>
     <row r="131">
@@ -7425,7 +7425,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA  - 020649722 - KIT4M04604747TPT</t>
+          <t>SS - 05900510 - Los Angeles CA - 020650042 - KIT4M05413819JV5</t>
         </is>
       </c>
       <c r="C131" s="3" t="n">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604747TPT</t>
+          <t>KIT4M05413819JV5</t>
         </is>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>809873</t>
+          <t>812796</t>
         </is>
       </c>
       <c r="G131" s="5" t="inlineStr">
@@ -7467,7 +7467,7 @@
       </c>
       <c r="L131" s="5" t="n"/>
       <c r="M131" s="7" t="n">
-        <v>18.44</v>
+        <v>18.82</v>
       </c>
     </row>
     <row r="132">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 6858375 - KIT4M05872512N5W</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955302 - KIT4M055635158PC</t>
         </is>
       </c>
       <c r="C132" s="3" t="n">
@@ -7489,12 +7489,12 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872512N5W</t>
+          <t>KIT4M055635158PC</t>
         </is>
       </c>
       <c r="F132" s="4" t="inlineStr">
         <is>
-          <t>816077</t>
+          <t>814457</t>
         </is>
       </c>
       <c r="G132" s="5" t="inlineStr">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="L132" s="5" t="n"/>
       <c r="M132" s="7" t="n">
-        <v>18.29</v>
+        <v>18.73</v>
       </c>
     </row>
     <row r="133">
@@ -7573,7 +7573,7 @@
       </c>
       <c r="L133" s="5" t="n"/>
       <c r="M133" s="7" t="n">
-        <v>17.64</v>
+        <v>18.51</v>
       </c>
     </row>
     <row r="134">
@@ -7584,7 +7584,7 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020649292-KIT4M05368201SNV</t>
+          <t>SS - 05900510 - Los Angeles, CA  - 020649722 - KIT4M04604747TPT</t>
         </is>
       </c>
       <c r="C134" s="3" t="n">
@@ -7595,12 +7595,12 @@
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368201SNV</t>
+          <t>KIT4M04604747TPT</t>
         </is>
       </c>
       <c r="F134" s="4" t="inlineStr">
         <is>
-          <t>810651</t>
+          <t>809873</t>
         </is>
       </c>
       <c r="G134" s="5" t="inlineStr">
@@ -7626,7 +7626,7 @@
       </c>
       <c r="L134" s="5" t="n"/>
       <c r="M134" s="7" t="n">
-        <v>17.47</v>
+        <v>18.44</v>
       </c>
     </row>
     <row r="135">
@@ -7637,7 +7637,7 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482701112 - KIT4M04158973M2C</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649712 - KIT4M046047397TM</t>
         </is>
       </c>
       <c r="C135" s="3" t="n">
@@ -7648,12 +7648,12 @@
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158973M2C</t>
+          <t>KIT4M046047397TM</t>
         </is>
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>809610</t>
+          <t>809863</t>
         </is>
       </c>
       <c r="G135" s="5" t="inlineStr">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="L135" s="5" t="n"/>
       <c r="M135" s="7" t="n">
-        <v>17.07</v>
+        <v>18.11</v>
       </c>
     </row>
     <row r="136">
@@ -7690,7 +7690,7 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438002 - KIT4M05799701SGS</t>
+          <t>SMRT-05900510-Los Angeles CA-020649292-KIT4M05368201SNV</t>
         </is>
       </c>
       <c r="C136" s="3" t="n">
@@ -7701,12 +7701,12 @@
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799701SGS</t>
+          <t>KIT4M05368201SNV</t>
         </is>
       </c>
       <c r="F136" s="4" t="inlineStr">
         <is>
-          <t>816284</t>
+          <t>810651</t>
         </is>
       </c>
       <c r="G136" s="5" t="inlineStr">
@@ -7732,7 +7732,7 @@
       </c>
       <c r="L136" s="5" t="n"/>
       <c r="M136" s="7" t="n">
-        <v>16.22</v>
+        <v>17.47</v>
       </c>
     </row>
     <row r="137">
@@ -7743,7 +7743,7 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649592 - KIT4M05413787HHK</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482701112 - KIT4M04158973M2C</t>
         </is>
       </c>
       <c r="C137" s="3" t="n">
@@ -7754,12 +7754,12 @@
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413787HHK</t>
+          <t>KIT4M04158973M2C</t>
         </is>
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>812809</t>
+          <t>809610</t>
         </is>
       </c>
       <c r="G137" s="5" t="inlineStr">
@@ -7785,7 +7785,7 @@
       </c>
       <c r="L137" s="5" t="n"/>
       <c r="M137" s="7" t="n">
-        <v>15.51</v>
+        <v>17.07</v>
       </c>
     </row>
     <row r="138">
@@ -7796,7 +7796,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649712 - KIT4M046047397TM</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438002 - KIT4M05799701SGS</t>
         </is>
       </c>
       <c r="C138" s="3" t="n">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047397TM</t>
+          <t>KIT4M05799701SGS</t>
         </is>
       </c>
       <c r="F138" s="4" t="inlineStr">
         <is>
-          <t>809863</t>
+          <t>816284</t>
         </is>
       </c>
       <c r="G138" s="5" t="inlineStr">
@@ -7838,7 +7838,7 @@
       </c>
       <c r="L138" s="5" t="n"/>
       <c r="M138" s="7" t="n">
-        <v>14.59</v>
+        <v>16.3</v>
       </c>
     </row>
     <row r="139">
@@ -7849,7 +7849,7 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482708 - KIT4M04604736T7C</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649592 - KIT4M05413787HHK</t>
         </is>
       </c>
       <c r="C139" s="3" t="n">
@@ -7860,12 +7860,12 @@
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604736T7C</t>
+          <t>KIT4M05413787HHK</t>
         </is>
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>809662</t>
+          <t>812809</t>
         </is>
       </c>
       <c r="G139" s="5" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="L139" s="5" t="n"/>
       <c r="M139" s="7" t="n">
-        <v>14.46</v>
+        <v>15.51</v>
       </c>
     </row>
     <row r="140">
@@ -7902,7 +7902,7 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020649862 - KIT4M04475159PMD</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649532 - KIT4M05413808FFZ</t>
         </is>
       </c>
       <c r="C140" s="3" t="n">
@@ -7913,12 +7913,12 @@
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475159PMD</t>
+          <t>KIT4M05413808FFZ</t>
         </is>
       </c>
       <c r="F140" s="4" t="inlineStr">
         <is>
-          <t>809868</t>
+          <t>812828</t>
         </is>
       </c>
       <c r="G140" s="5" t="inlineStr">
@@ -7944,7 +7944,7 @@
       </c>
       <c r="L140" s="5" t="n"/>
       <c r="M140" s="7" t="n">
-        <v>14.45</v>
+        <v>15.16</v>
       </c>
     </row>
     <row r="141">
@@ -7955,7 +7955,7 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - CW6642812 - KIT4M054138292ZP</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649222 - KIT4P00065640BFW</t>
         </is>
       </c>
       <c r="C141" s="3" t="n">
@@ -7966,17 +7966,17 @@
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138292ZP</t>
+          <t>KIT4P00065640BFW</t>
         </is>
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>812784</t>
+          <t>812929</t>
         </is>
       </c>
       <c r="G141" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H141" s="5" t="inlineStr">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="L141" s="5" t="n"/>
       <c r="M141" s="7" t="n">
-        <v>14.37</v>
+        <v>15.08</v>
       </c>
     </row>
     <row r="142">
@@ -8008,7 +8008,7 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649222 - KIT4P00065640BFW</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482708 - KIT4M04604736T7C</t>
         </is>
       </c>
       <c r="C142" s="3" t="n">
@@ -8019,17 +8019,17 @@
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065640BFW</t>
+          <t>KIT4M04604736T7C</t>
         </is>
       </c>
       <c r="F142" s="4" t="inlineStr">
         <is>
-          <t>812929</t>
+          <t>809662</t>
         </is>
       </c>
       <c r="G142" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H142" s="5" t="inlineStr">
@@ -8050,7 +8050,7 @@
       </c>
       <c r="L142" s="5" t="n"/>
       <c r="M142" s="7" t="n">
-        <v>14.23</v>
+        <v>14.46</v>
       </c>
     </row>
     <row r="143">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649532 - KIT4M05413808FFZ</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020649862 - KIT4M04475159PMD</t>
         </is>
       </c>
       <c r="C143" s="3" t="n">
@@ -8072,12 +8072,12 @@
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413808FFZ</t>
+          <t>KIT4M04475159PMD</t>
         </is>
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>812828</t>
+          <t>809868</t>
         </is>
       </c>
       <c r="G143" s="5" t="inlineStr">
@@ -8103,7 +8103,7 @@
       </c>
       <c r="L143" s="5" t="n"/>
       <c r="M143" s="7" t="n">
-        <v>14.13</v>
+        <v>14.45</v>
       </c>
     </row>
     <row r="144">
@@ -8114,7 +8114,7 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649632 - KIT4M054138064J9</t>
+          <t>SMA - 05900510 - Los Angeles CA - CW6642812 - KIT4M054138292ZP</t>
         </is>
       </c>
       <c r="C144" s="3" t="n">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138064J9</t>
+          <t>KIT4M054138292ZP</t>
         </is>
       </c>
       <c r="F144" s="4" t="inlineStr">
         <is>
-          <t>812844</t>
+          <t>812784</t>
         </is>
       </c>
       <c r="G144" s="5" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="L144" s="5" t="n"/>
       <c r="M144" s="7" t="n">
-        <v>13.38</v>
+        <v>14.37</v>
       </c>
     </row>
     <row r="145">
@@ -8167,7 +8167,7 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649442 - KIT4M054137885SM</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649632 - KIT4M054138064J9</t>
         </is>
       </c>
       <c r="C145" s="3" t="n">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137885SM</t>
+          <t>KIT4M054138064J9</t>
         </is>
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>812846</t>
+          <t>812844</t>
         </is>
       </c>
       <c r="G145" s="5" t="inlineStr">
@@ -8209,7 +8209,7 @@
       </c>
       <c r="L145" s="5" t="n"/>
       <c r="M145" s="7" t="n">
-        <v>13.24</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="146">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020650042 - KIT4M05413819JV5</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649442 - KIT4M054137885SM</t>
         </is>
       </c>
       <c r="C146" s="3" t="n">
@@ -8231,12 +8231,12 @@
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413819JV5</t>
+          <t>KIT4M054137885SM</t>
         </is>
       </c>
       <c r="F146" s="4" t="inlineStr">
         <is>
-          <t>812796</t>
+          <t>812846</t>
         </is>
       </c>
       <c r="G146" s="5" t="inlineStr">
@@ -8262,7 +8262,7 @@
       </c>
       <c r="L146" s="5" t="n"/>
       <c r="M146" s="7" t="n">
-        <v>13</v>
+        <v>13.24</v>
       </c>
     </row>
     <row r="147">
@@ -8421,7 +8421,7 @@
       </c>
       <c r="L149" s="5" t="n"/>
       <c r="M149" s="7" t="n">
-        <v>11.92</v>
+        <v>11.93</v>
       </c>
     </row>
     <row r="150">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649282 - KIT4M05368213974</t>
+          <t>SMA - 05900510 -  Los Angeles CA - 020649512 - KIT4M054138318Q7</t>
         </is>
       </c>
       <c r="C154" s="3" t="n">
@@ -8655,12 +8655,12 @@
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368213974</t>
+          <t>KIT4M054138318Q7</t>
         </is>
       </c>
       <c r="F154" s="4" t="inlineStr">
         <is>
-          <t>810647</t>
+          <t>812814</t>
         </is>
       </c>
       <c r="G154" s="5" t="inlineStr">
@@ -8686,7 +8686,7 @@
       </c>
       <c r="L154" s="5" t="n"/>
       <c r="M154" s="7" t="n">
-        <v>9.18</v>
+        <v>9.279999999999999</v>
       </c>
     </row>
     <row r="155">
@@ -8697,7 +8697,7 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955612 - KIT4M0556355588P</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649282 - KIT4M05368213974</t>
         </is>
       </c>
       <c r="C155" s="3" t="n">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0556355588P</t>
+          <t>KIT4M05368213974</t>
         </is>
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>814455</t>
+          <t>810647</t>
         </is>
       </c>
       <c r="G155" s="5" t="inlineStr">
@@ -8739,7 +8739,7 @@
       </c>
       <c r="L155" s="5" t="n"/>
       <c r="M155" s="7" t="n">
-        <v>9.140000000000001</v>
+        <v>9.18</v>
       </c>
     </row>
     <row r="156">
@@ -8750,7 +8750,7 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020650122-KIT4M05413776H84</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955612 - KIT4M0556355588P</t>
         </is>
       </c>
       <c r="C156" s="3" t="n">
@@ -8761,12 +8761,12 @@
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413776H84</t>
+          <t>KIT4M0556355588P</t>
         </is>
       </c>
       <c r="F156" s="4" t="inlineStr">
         <is>
-          <t>810101</t>
+          <t>814455</t>
         </is>
       </c>
       <c r="G156" s="5" t="inlineStr">
@@ -8792,7 +8792,7 @@
       </c>
       <c r="L156" s="5" t="n"/>
       <c r="M156" s="7" t="n">
-        <v>9.029999999999999</v>
+        <v>9.140000000000001</v>
       </c>
     </row>
     <row r="157">
@@ -8803,7 +8803,7 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955502 - KIT4M05563502GJS</t>
+          <t>SMRT-05900510-Los Angeles CA-020650122-KIT4M05413776H84</t>
         </is>
       </c>
       <c r="C157" s="3" t="n">
@@ -8814,12 +8814,12 @@
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563502GJS</t>
+          <t>KIT4M05413776H84</t>
         </is>
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>814470</t>
+          <t>810101</t>
         </is>
       </c>
       <c r="G157" s="5" t="inlineStr">
@@ -8845,7 +8845,7 @@
       </c>
       <c r="L157" s="5" t="n"/>
       <c r="M157" s="7" t="n">
-        <v>8.869999999999999</v>
+        <v>9.029999999999999</v>
       </c>
     </row>
     <row r="158">
@@ -8898,7 +8898,7 @@
       </c>
       <c r="L158" s="5" t="n"/>
       <c r="M158" s="7" t="n">
-        <v>8.85</v>
+        <v>8.93</v>
       </c>
     </row>
     <row r="159">
@@ -8909,7 +8909,7 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955252 - KIT4M05563584FVC</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955502 - KIT4M05563502GJS</t>
         </is>
       </c>
       <c r="C159" s="3" t="n">
@@ -8920,12 +8920,12 @@
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563584FVC</t>
+          <t>KIT4M05563502GJS</t>
         </is>
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>814439</t>
+          <t>814470</t>
         </is>
       </c>
       <c r="G159" s="5" t="inlineStr">
@@ -8951,7 +8951,7 @@
       </c>
       <c r="L159" s="5" t="n"/>
       <c r="M159" s="7" t="n">
-        <v>8.75</v>
+        <v>8.869999999999999</v>
       </c>
     </row>
     <row r="160">
@@ -8962,7 +8962,7 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 -  Los Angeles CA - 020649512 - KIT4M054138318Q7</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955252 - KIT4M05563584FVC</t>
         </is>
       </c>
       <c r="C160" s="3" t="n">
@@ -8973,12 +8973,12 @@
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138318Q7</t>
+          <t>KIT4M05563584FVC</t>
         </is>
       </c>
       <c r="F160" s="4" t="inlineStr">
         <is>
-          <t>812814</t>
+          <t>814439</t>
         </is>
       </c>
       <c r="G160" s="5" t="inlineStr">
@@ -9004,7 +9004,7 @@
       </c>
       <c r="L160" s="5" t="n"/>
       <c r="M160" s="7" t="n">
-        <v>7.84</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="161">
@@ -9216,7 +9216,7 @@
       </c>
       <c r="L164" s="5" t="n"/>
       <c r="M164" s="7" t="n">
-        <v>6.4</v>
+        <v>6.52</v>
       </c>
     </row>
     <row r="165">
@@ -9269,7 +9269,7 @@
       </c>
       <c r="L165" s="5" t="n"/>
       <c r="M165" s="7" t="n">
-        <v>6.34</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="166">
@@ -9280,7 +9280,7 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649642 - KIT4M05413826Z6Z</t>
+          <t>SS - 05900510 -  Los Angeles CA - 021437622 - KIT4M0587258755W</t>
         </is>
       </c>
       <c r="C166" s="3" t="n">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413826Z6Z</t>
+          <t>KIT4M0587258755W</t>
         </is>
       </c>
       <c r="F166" s="4" t="inlineStr">
         <is>
-          <t>812804</t>
+          <t>816187</t>
         </is>
       </c>
       <c r="G166" s="5" t="inlineStr">
@@ -9322,7 +9322,7 @@
       </c>
       <c r="L166" s="5" t="n"/>
       <c r="M166" s="7" t="n">
-        <v>5.9</v>
+        <v>6.06</v>
       </c>
     </row>
     <row r="167">
@@ -9333,7 +9333,7 @@
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827011110 - KIT4M03866627GHD</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649642 - KIT4M05413826Z6Z</t>
         </is>
       </c>
       <c r="C167" s="3" t="n">
@@ -9344,12 +9344,12 @@
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03866627GHD</t>
+          <t>KIT4M05413826Z6Z</t>
         </is>
       </c>
       <c r="F167" s="4" t="inlineStr">
         <is>
-          <t>809619</t>
+          <t>812804</t>
         </is>
       </c>
       <c r="G167" s="5" t="inlineStr">
@@ -9375,7 +9375,7 @@
       </c>
       <c r="L167" s="5" t="n"/>
       <c r="M167" s="7" t="n">
-        <v>5.78</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="168">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020650182 - KIT4M05413821GGW</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827011110 - KIT4M03866627GHD</t>
         </is>
       </c>
       <c r="C168" s="3" t="n">
@@ -9397,12 +9397,12 @@
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413821GGW</t>
+          <t>KIT4M03866627GHD</t>
         </is>
       </c>
       <c r="F168" s="4" t="inlineStr">
         <is>
-          <t>812830</t>
+          <t>809619</t>
         </is>
       </c>
       <c r="G168" s="5" t="inlineStr">
@@ -9428,7 +9428,7 @@
       </c>
       <c r="L168" s="5" t="n"/>
       <c r="M168" s="7" t="n">
-        <v>5.51</v>
+        <v>5.78</v>
       </c>
     </row>
     <row r="169">
@@ -9439,7 +9439,7 @@
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 021437622 - KIT4M0587258755W</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020650182 - KIT4M05413821GGW</t>
         </is>
       </c>
       <c r="C169" s="3" t="n">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0587258755W</t>
+          <t>KIT4M05413821GGW</t>
         </is>
       </c>
       <c r="F169" s="4" t="inlineStr">
         <is>
-          <t>816187</t>
+          <t>812830</t>
         </is>
       </c>
       <c r="G169" s="5" t="inlineStr">
@@ -9481,7 +9481,7 @@
       </c>
       <c r="L169" s="5" t="n"/>
       <c r="M169" s="7" t="n">
-        <v>5.41</v>
+        <v>5.51</v>
       </c>
     </row>
     <row r="170">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="L170" s="5" t="n"/>
       <c r="M170" s="7" t="n">
-        <v>4.69</v>
+        <v>4.74</v>
       </c>
     </row>
     <row r="171">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649492 - KIT4M054138074NS</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827010 - KIT4M046047372KJ</t>
         </is>
       </c>
       <c r="C172" s="3" t="n">
@@ -9609,12 +9609,12 @@
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138074NS</t>
+          <t>KIT4M046047372KJ</t>
         </is>
       </c>
       <c r="F172" s="4" t="inlineStr">
         <is>
-          <t>812816</t>
+          <t>809658</t>
         </is>
       </c>
       <c r="G172" s="5" t="inlineStr">
@@ -9640,7 +9640,7 @@
       </c>
       <c r="L172" s="5" t="n"/>
       <c r="M172" s="7" t="n">
-        <v>3.8</v>
+        <v>4.36</v>
       </c>
     </row>
     <row r="173">
@@ -9651,7 +9651,7 @@
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827010 - KIT4M046047372KJ</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649492 - KIT4M054138074NS</t>
         </is>
       </c>
       <c r="C173" s="3" t="n">
@@ -9662,12 +9662,12 @@
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047372KJ</t>
+          <t>KIT4M054138074NS</t>
         </is>
       </c>
       <c r="F173" s="4" t="inlineStr">
         <is>
-          <t>809658</t>
+          <t>812816</t>
         </is>
       </c>
       <c r="G173" s="5" t="inlineStr">
@@ -9693,7 +9693,7 @@
       </c>
       <c r="L173" s="5" t="n"/>
       <c r="M173" s="7" t="n">
-        <v>3.74</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="174">
@@ -9746,7 +9746,7 @@
       </c>
       <c r="L174" s="5" t="n"/>
       <c r="M174" s="7" t="n">
-        <v>3.7</v>
+        <v>3.78</v>
       </c>
     </row>
     <row r="175">
@@ -9757,7 +9757,7 @@
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649732 - KIT4M046047467T4</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827016 - KIT4M041536494G6</t>
         </is>
       </c>
       <c r="C175" s="3" t="n">
@@ -9768,12 +9768,12 @@
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047467T4</t>
+          <t>KIT4M041536494G6</t>
         </is>
       </c>
       <c r="F175" s="4" t="inlineStr">
         <is>
-          <t>809865</t>
+          <t>809617</t>
         </is>
       </c>
       <c r="G175" s="5" t="inlineStr">
@@ -9799,7 +9799,7 @@
       </c>
       <c r="L175" s="5" t="n"/>
       <c r="M175" s="7" t="n">
-        <v>3.43</v>
+        <v>3.52</v>
       </c>
     </row>
     <row r="176">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="L176" s="5" t="n"/>
       <c r="M176" s="7" t="n">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
     </row>
     <row r="177">
@@ -9863,7 +9863,7 @@
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827016 - KIT4M041536494G6</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649732 - KIT4M046047467T4</t>
         </is>
       </c>
       <c r="C177" s="3" t="n">
@@ -9874,12 +9874,12 @@
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>KIT4M041536494G6</t>
+          <t>KIT4M046047467T4</t>
         </is>
       </c>
       <c r="F177" s="4" t="inlineStr">
         <is>
-          <t>809617</t>
+          <t>809865</t>
         </is>
       </c>
       <c r="G177" s="5" t="inlineStr">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="L177" s="5" t="n"/>
       <c r="M177" s="7" t="n">
-        <v>3.02</v>
+        <v>3.43</v>
       </c>
     </row>
     <row r="178">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="L180" s="5" t="n"/>
       <c r="M180" s="7" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="181">
@@ -10117,7 +10117,7 @@
       </c>
       <c r="L181" s="5" t="n"/>
       <c r="M181" s="7" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="182">
@@ -10329,7 +10329,7 @@
       </c>
       <c r="L185" s="5" t="n"/>
       <c r="M185" s="7" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="186">
@@ -10658,7 +10658,7 @@
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437592 - KIT4M05872582TC7</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270110 - KIT4M038677586ZX</t>
         </is>
       </c>
       <c r="C192" s="3" t="n">
@@ -10669,12 +10669,12 @@
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872582TC7</t>
+          <t>KIT4M038677586ZX</t>
         </is>
       </c>
       <c r="F192" s="4" t="inlineStr">
         <is>
-          <t>816107</t>
+          <t>809623</t>
         </is>
       </c>
       <c r="G192" s="5" t="inlineStr">
@@ -10711,7 +10711,7 @@
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270110 - KIT4M038677586ZX</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437592 - KIT4M05872582TC7</t>
         </is>
       </c>
       <c r="C193" s="3" t="n">
@@ -10722,12 +10722,12 @@
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>KIT4M038677586ZX</t>
+          <t>KIT4M05872582TC7</t>
         </is>
       </c>
       <c r="F193" s="4" t="inlineStr">
         <is>
-          <t>809623</t>
+          <t>816107</t>
         </is>
       </c>
       <c r="G193" s="5" t="inlineStr">
@@ -10753,7 +10753,7 @@
       </c>
       <c r="L193" s="5" t="n"/>
       <c r="M193" s="7" t="n">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="194">
@@ -10870,7 +10870,7 @@
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438172 - KIT4M05872500684</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438152 - KIT4M05799733FPK</t>
         </is>
       </c>
       <c r="C196" s="3" t="n">
@@ -10881,12 +10881,12 @@
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872500684</t>
+          <t>KIT4M05799733FPK</t>
         </is>
       </c>
       <c r="F196" s="4" t="inlineStr">
         <is>
-          <t>816081</t>
+          <t>816286</t>
         </is>
       </c>
       <c r="G196" s="5" t="inlineStr">
@@ -10912,7 +10912,7 @@
       </c>
       <c r="L196" s="5" t="n"/>
       <c r="M196" s="7" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="197">
@@ -10923,7 +10923,7 @@
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 6862083  - KIT4M057996395ZF</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438172 - KIT4M05872500684</t>
         </is>
       </c>
       <c r="C197" s="3" t="n">
@@ -10934,12 +10934,12 @@
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>KIT4M057996395ZF</t>
+          <t>KIT4M05872500684</t>
         </is>
       </c>
       <c r="F197" s="4" t="inlineStr">
         <is>
-          <t>816268</t>
+          <t>816081</t>
         </is>
       </c>
       <c r="G197" s="5" t="inlineStr">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437412 - KIT4M05872548P2H</t>
+          <t>SS - 05900510 - Los Angeles CA - 6862083  - KIT4M057996395ZF</t>
         </is>
       </c>
       <c r="C198" s="3" t="n">
@@ -10987,12 +10987,12 @@
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872548P2H</t>
+          <t>KIT4M057996395ZF</t>
         </is>
       </c>
       <c r="F198" s="4" t="inlineStr">
         <is>
-          <t>816066</t>
+          <t>816268</t>
         </is>
       </c>
       <c r="G198" s="5" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="L198" s="5" t="n"/>
       <c r="M198" s="7" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="199">
@@ -11029,7 +11029,7 @@
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438282 - KIT4M05872508VTN</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437412 - KIT4M05872548P2H</t>
         </is>
       </c>
       <c r="C199" s="3" t="n">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872508VTN</t>
+          <t>KIT4M05872548P2H</t>
         </is>
       </c>
       <c r="F199" s="4" t="inlineStr">
         <is>
-          <t>816076</t>
+          <t>816066</t>
         </is>
       </c>
       <c r="G199" s="5" t="inlineStr">
@@ -11071,7 +11071,7 @@
       </c>
       <c r="L199" s="5" t="n"/>
       <c r="M199" s="7" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="200">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438022 - KIT4M05799705T6B</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438282 - KIT4M05872508VTN</t>
         </is>
       </c>
       <c r="C200" s="3" t="n">
@@ -11093,12 +11093,12 @@
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799705T6B</t>
+          <t>KIT4M05872508VTN</t>
         </is>
       </c>
       <c r="F200" s="4" t="inlineStr">
         <is>
-          <t>816285</t>
+          <t>816076</t>
         </is>
       </c>
       <c r="G200" s="5" t="inlineStr">
@@ -11241,7 +11241,7 @@
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918277QF</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438022 - KIT4M05799705T6B</t>
         </is>
       </c>
       <c r="C203" s="3" t="n">
@@ -11252,12 +11252,12 @@
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918277QF</t>
+          <t>KIT4M05799705T6B</t>
         </is>
       </c>
       <c r="F203" s="4" t="inlineStr">
         <is>
-          <t>816403</t>
+          <t>816285</t>
         </is>
       </c>
       <c r="G203" s="5" t="inlineStr">
@@ -11283,7 +11283,7 @@
       </c>
       <c r="L203" s="5" t="n"/>
       <c r="M203" s="7" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="204">
@@ -11294,7 +11294,7 @@
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437312 - KIT4M05872568PR6</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918277QF</t>
         </is>
       </c>
       <c r="C204" s="3" t="n">
@@ -11305,12 +11305,12 @@
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872568PR6</t>
+          <t>KIT4M064918277QF</t>
         </is>
       </c>
       <c r="F204" s="4" t="inlineStr">
         <is>
-          <t>816094</t>
+          <t>816403</t>
         </is>
       </c>
       <c r="G204" s="5" t="inlineStr">
@@ -11336,7 +11336,7 @@
       </c>
       <c r="L204" s="5" t="n"/>
       <c r="M204" s="7" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="205">
@@ -11347,7 +11347,7 @@
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 021438182 - KIT4M05872528P9D</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437722 - KIT4M05872498PP4</t>
         </is>
       </c>
       <c r="C205" s="3" t="n">
@@ -11358,12 +11358,12 @@
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872528P9D</t>
+          <t>KIT4M05872498PP4</t>
         </is>
       </c>
       <c r="F205" s="4" t="inlineStr">
         <is>
-          <t>816089</t>
+          <t>816104</t>
         </is>
       </c>
       <c r="G205" s="5" t="inlineStr">
@@ -11506,7 +11506,7 @@
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437722 - KIT4M05872498PP4</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437312 - KIT4M05872568PR6</t>
         </is>
       </c>
       <c r="C208" s="3" t="n">
@@ -11517,12 +11517,12 @@
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872498PP4</t>
+          <t>KIT4M05872568PR6</t>
         </is>
       </c>
       <c r="F208" s="4" t="inlineStr">
         <is>
-          <t>816104</t>
+          <t>816094</t>
         </is>
       </c>
       <c r="G208" s="5" t="inlineStr">
@@ -11559,7 +11559,7 @@
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437882-KIT4M05872527QK6</t>
+          <t>SS - 05900510 -  Los Angeles CA - 021438182 - KIT4M05872528P9D</t>
         </is>
       </c>
       <c r="C209" s="3" t="n">
@@ -11570,12 +11570,12 @@
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872527QK6</t>
+          <t>KIT4M05872528P9D</t>
         </is>
       </c>
       <c r="F209" s="4" t="inlineStr">
         <is>
-          <t>816214</t>
+          <t>816089</t>
         </is>
       </c>
       <c r="G209" s="5" t="inlineStr">
@@ -11601,7 +11601,7 @@
       </c>
       <c r="L209" s="5" t="n"/>
       <c r="M209" s="7" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="210">
@@ -11983,7 +11983,7 @@
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437692 - KIT4M05872518P78</t>
+          <t>SMRT-05900510-Los Angeles CA-021437882-KIT4M05872527QK6</t>
         </is>
       </c>
       <c r="C217" s="3" t="n">
@@ -11994,12 +11994,12 @@
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872518P78</t>
+          <t>KIT4M05872527QK6</t>
         </is>
       </c>
       <c r="F217" s="4" t="inlineStr">
         <is>
-          <t>816184</t>
+          <t>816214</t>
         </is>
       </c>
       <c r="G217" s="5" t="inlineStr">
@@ -12407,7 +12407,7 @@
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438112 - KIT4M0579970825J</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437692 - KIT4M05872518P78</t>
         </is>
       </c>
       <c r="C225" s="3" t="n">
@@ -12418,12 +12418,12 @@
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0579970825J</t>
+          <t>KIT4M05872518P78</t>
         </is>
       </c>
       <c r="F225" s="4" t="inlineStr">
         <is>
-          <t>816290</t>
+          <t>816184</t>
         </is>
       </c>
       <c r="G225" s="5" t="inlineStr">
@@ -12460,7 +12460,7 @@
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>SSC - 05900510 -  Los Angeles CA - 021437862 - KIT4M05872516CJM</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438112 - KIT4M0579970825J</t>
         </is>
       </c>
       <c r="C226" s="3" t="n">
@@ -12471,12 +12471,12 @@
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872516CJM</t>
+          <t>KIT4M0579970825J</t>
         </is>
       </c>
       <c r="F226" s="4" t="inlineStr">
         <is>
-          <t>816087</t>
+          <t>816290</t>
         </is>
       </c>
       <c r="G226" s="5" t="inlineStr">
@@ -12513,7 +12513,7 @@
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437332 - KIT4M05872554RHM</t>
+          <t>SSC - 05900510 -  Los Angeles CA - 021437862 - KIT4M05872516CJM</t>
         </is>
       </c>
       <c r="C227" s="3" t="n">
@@ -12524,12 +12524,12 @@
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872554RHM</t>
+          <t>KIT4M05872516CJM</t>
         </is>
       </c>
       <c r="F227" s="4" t="inlineStr">
         <is>
-          <t>816071</t>
+          <t>816087</t>
         </is>
       </c>
       <c r="G227" s="5" t="inlineStr">
@@ -12725,7 +12725,7 @@
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437342 - KIT4M05872557NFB</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437332 - KIT4M05872554RHM</t>
         </is>
       </c>
       <c r="C231" s="3" t="n">
@@ -12736,12 +12736,12 @@
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872557NFB</t>
+          <t>KIT4M05872554RHM</t>
         </is>
       </c>
       <c r="F231" s="4" t="inlineStr">
         <is>
-          <t>816095</t>
+          <t>816071</t>
         </is>
       </c>
       <c r="G231" s="5" t="inlineStr">
@@ -12778,7 +12778,7 @@
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437662 - KIT4M05872534RXS</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437342 - KIT4M05872557NFB</t>
         </is>
       </c>
       <c r="C232" s="3" t="n">
@@ -12789,12 +12789,12 @@
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872534RXS</t>
+          <t>KIT4M05872557NFB</t>
         </is>
       </c>
       <c r="F232" s="4" t="inlineStr">
         <is>
-          <t>816216</t>
+          <t>816095</t>
         </is>
       </c>
       <c r="G232" s="5" t="inlineStr">
@@ -12820,7 +12820,7 @@
       </c>
       <c r="L232" s="5" t="n"/>
       <c r="M232" s="7" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="233">
@@ -12937,7 +12937,7 @@
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438192 - KIT4M05872511F6P</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437662 - KIT4M05872534RXS</t>
         </is>
       </c>
       <c r="C235" s="3" t="n">
@@ -12948,12 +12948,12 @@
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872511F6P</t>
+          <t>KIT4M05872534RXS</t>
         </is>
       </c>
       <c r="F235" s="4" t="inlineStr">
         <is>
-          <t>816090</t>
+          <t>816216</t>
         </is>
       </c>
       <c r="G235" s="5" t="inlineStr">
@@ -12990,7 +12990,7 @@
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438082 - KIT4M05799668SS7</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438192 - KIT4M05872511F6P</t>
         </is>
       </c>
       <c r="C236" s="3" t="n">
@@ -13001,12 +13001,12 @@
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799668SS7</t>
+          <t>KIT4M05872511F6P</t>
         </is>
       </c>
       <c r="F236" s="4" t="inlineStr">
         <is>
-          <t>816279</t>
+          <t>816090</t>
         </is>
       </c>
       <c r="G236" s="5" t="inlineStr">
@@ -13096,7 +13096,7 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437372 - KIT4M058725505J5</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438082 - KIT4M05799668SS7</t>
         </is>
       </c>
       <c r="C238" s="3" t="n">
@@ -13107,12 +13107,12 @@
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725505J5</t>
+          <t>KIT4M05799668SS7</t>
         </is>
       </c>
       <c r="F238" s="4" t="inlineStr">
         <is>
-          <t>816117</t>
+          <t>816279</t>
         </is>
       </c>
       <c r="G238" s="5" t="inlineStr">
@@ -13255,7 +13255,7 @@
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437272 - KIT4P0008459589D</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437372 - KIT4M058725505J5</t>
         </is>
       </c>
       <c r="C241" s="3" t="n">
@@ -13266,17 +13266,17 @@
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0008459589D</t>
+          <t>KIT4M058725505J5</t>
         </is>
       </c>
       <c r="F241" s="4" t="inlineStr">
         <is>
-          <t>816222</t>
+          <t>816117</t>
         </is>
       </c>
       <c r="G241" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H241" s="5" t="inlineStr">
@@ -13297,7 +13297,7 @@
       </c>
       <c r="L241" s="5" t="n"/>
       <c r="M241" s="7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="242">
@@ -13308,7 +13308,7 @@
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491808P4F</t>
+          <t>SS - 05900510 - Los Angeles, CA  - 020649572 - KIT4M05413816N8K</t>
         </is>
       </c>
       <c r="C242" s="3" t="n">
@@ -13319,12 +13319,12 @@
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491808P4F</t>
+          <t>KIT4M05413816N8K</t>
         </is>
       </c>
       <c r="F242" s="4" t="inlineStr">
         <is>
-          <t>816399</t>
+          <t>812832</t>
         </is>
       </c>
       <c r="G242" s="5" t="inlineStr">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA  - 020649572 - KIT4M05413816N8K</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437272 - KIT4P0008459589D</t>
         </is>
       </c>
       <c r="C243" s="3" t="n">
@@ -13372,17 +13372,17 @@
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413816N8K</t>
+          <t>KIT4P0008459589D</t>
         </is>
       </c>
       <c r="F243" s="4" t="inlineStr">
         <is>
-          <t>812832</t>
+          <t>816222</t>
         </is>
       </c>
       <c r="G243" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H243" s="5" t="inlineStr">
@@ -13414,7 +13414,7 @@
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438162 - KIT4M05799712SBX</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491808P4F</t>
         </is>
       </c>
       <c r="C244" s="3" t="n">
@@ -13425,12 +13425,12 @@
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799712SBX</t>
+          <t>KIT4M06491808P4F</t>
         </is>
       </c>
       <c r="F244" s="4" t="inlineStr">
         <is>
-          <t>816276</t>
+          <t>816399</t>
         </is>
       </c>
       <c r="G244" s="5" t="inlineStr">
@@ -13456,7 +13456,7 @@
       </c>
       <c r="L244" s="5" t="n"/>
       <c r="M244" s="7" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="245">
@@ -13467,7 +13467,7 @@
       </c>
       <c r="B245" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491796QQN</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438162 - KIT4M05799712SBX</t>
         </is>
       </c>
       <c r="C245" s="3" t="n">
@@ -13478,12 +13478,12 @@
       </c>
       <c r="E245" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491796QQN</t>
+          <t>KIT4M05799712SBX</t>
         </is>
       </c>
       <c r="F245" s="4" t="inlineStr">
         <is>
-          <t>816405</t>
+          <t>816276</t>
         </is>
       </c>
       <c r="G245" s="5" t="inlineStr">
@@ -13573,7 +13573,7 @@
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918239TM</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491796QQN</t>
         </is>
       </c>
       <c r="C247" s="3" t="n">
@@ -13584,12 +13584,12 @@
       </c>
       <c r="E247" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918239TM</t>
+          <t>KIT4M06491796QQN</t>
         </is>
       </c>
       <c r="F247" s="4" t="inlineStr">
         <is>
-          <t>816398</t>
+          <t>816405</t>
         </is>
       </c>
       <c r="G247" s="5" t="inlineStr">
@@ -13626,7 +13626,7 @@
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955422 - KIT4M05563517BVR</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918239TM</t>
         </is>
       </c>
       <c r="C248" s="3" t="n">
@@ -13637,12 +13637,12 @@
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563517BVR</t>
+          <t>KIT4M064918239TM</t>
         </is>
       </c>
       <c r="F248" s="4" t="inlineStr">
         <is>
-          <t>814438</t>
+          <t>816398</t>
         </is>
       </c>
       <c r="G248" s="5" t="inlineStr">
@@ -13668,7 +13668,7 @@
       </c>
       <c r="L248" s="5" t="n"/>
       <c r="M248" s="7" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="249">
@@ -14686,7 +14686,7 @@
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438292 - KIt4m058725108K2</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955422 - KIT4M05563517BVR</t>
         </is>
       </c>
       <c r="C268" s="3" t="n">
@@ -14697,12 +14697,12 @@
       </c>
       <c r="E268" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725108K2</t>
+          <t>KIT4M05563517BVR</t>
         </is>
       </c>
       <c r="F268" s="4" t="inlineStr">
         <is>
-          <t>816287</t>
+          <t>814438</t>
         </is>
       </c>
       <c r="G268" s="5" t="inlineStr">
@@ -14792,7 +14792,7 @@
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438272 - KIT4M05872517VS2</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438292 - KIt4m058725108K2</t>
         </is>
       </c>
       <c r="C270" s="3" t="n">
@@ -14803,12 +14803,12 @@
       </c>
       <c r="E270" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872517VS2</t>
+          <t>KIT4M058725108K2</t>
         </is>
       </c>
       <c r="F270" s="4" t="inlineStr">
         <is>
-          <t>816288</t>
+          <t>816287</t>
         </is>
       </c>
       <c r="G270" s="5" t="inlineStr">
@@ -14834,7 +14834,7 @@
       </c>
       <c r="L270" s="5" t="n"/>
       <c r="M270" s="7" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="271">
@@ -14845,7 +14845,7 @@
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020650022 - KIT4M05413813HSJ</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438212 - KIT4M058725047FZ</t>
         </is>
       </c>
       <c r="C271" s="3" t="n">
@@ -14856,12 +14856,12 @@
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413813HSJ</t>
+          <t>KIT4M058725047FZ</t>
         </is>
       </c>
       <c r="F271" s="4" t="inlineStr">
         <is>
-          <t>812797</t>
+          <t>816289</t>
         </is>
       </c>
       <c r="G271" s="5" t="inlineStr">
@@ -14898,7 +14898,7 @@
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438152 - KIT4M05799733FPK</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437902 - KIT4M05799717WZV</t>
         </is>
       </c>
       <c r="C272" s="3" t="n">
@@ -14909,12 +14909,12 @@
       </c>
       <c r="E272" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799733FPK</t>
+          <t>KIT4M05799717WZV</t>
         </is>
       </c>
       <c r="F272" s="4" t="inlineStr">
         <is>
-          <t>816286</t>
+          <t>816280</t>
         </is>
       </c>
       <c r="G272" s="5" t="inlineStr">
@@ -14951,7 +14951,7 @@
       </c>
       <c r="B273" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649382 - KIT4M05368219KRH</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649392 - KIT4M05368206BZP</t>
         </is>
       </c>
       <c r="C273" s="3" t="n">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E273" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368219KRH</t>
+          <t>KIT4M05368206BZP</t>
         </is>
       </c>
       <c r="F273" s="4" t="inlineStr">
         <is>
-          <t>810646</t>
+          <t>810645</t>
         </is>
       </c>
       <c r="G273" s="5" t="inlineStr">
@@ -15004,7 +15004,7 @@
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649392 - KIT4M05368206BZP</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918322GZ</t>
         </is>
       </c>
       <c r="C274" s="3" t="n">
@@ -15015,12 +15015,12 @@
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368206BZP</t>
+          <t>KIT4M064918322GZ</t>
         </is>
       </c>
       <c r="F274" s="4" t="inlineStr">
         <is>
-          <t>810645</t>
+          <t>816414</t>
         </is>
       </c>
       <c r="G274" s="5" t="inlineStr">
@@ -15057,7 +15057,7 @@
       </c>
       <c r="B275" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437262 - KIT4P0008460369B</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491811JB5</t>
         </is>
       </c>
       <c r="C275" s="3" t="n">
@@ -15068,17 +15068,17 @@
       </c>
       <c r="E275" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0008460369B</t>
+          <t>KIT4M06491811JB5</t>
         </is>
       </c>
       <c r="F275" s="4" t="inlineStr">
         <is>
-          <t>816224</t>
+          <t>816411</t>
         </is>
       </c>
       <c r="G275" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H275" s="5" t="inlineStr">
@@ -15110,7 +15110,7 @@
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437892 - KIT4M06490321NJX</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491822SF6</t>
         </is>
       </c>
       <c r="C276" s="3" t="n">
@@ -15121,12 +15121,12 @@
       </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06490321NJX</t>
+          <t>KIT4M06491822SF6</t>
         </is>
       </c>
       <c r="F276" s="4" t="inlineStr">
         <is>
-          <t>816219</t>
+          <t>816412</t>
         </is>
       </c>
       <c r="G276" s="5" t="inlineStr">
@@ -15163,7 +15163,7 @@
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437452 - KIT4M05872580C6X</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491812JDV</t>
         </is>
       </c>
       <c r="C277" s="3" t="n">
@@ -15174,12 +15174,12 @@
       </c>
       <c r="E277" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872580C6X</t>
+          <t>KIT4M06491812JDV</t>
         </is>
       </c>
       <c r="F277" s="4" t="inlineStr">
         <is>
-          <t>816097</t>
+          <t>816409</t>
         </is>
       </c>
       <c r="G277" s="5" t="inlineStr">
@@ -15216,7 +15216,7 @@
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437972 - KIT4M06490327GMP</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491824JCK</t>
         </is>
       </c>
       <c r="C278" s="3" t="n">
@@ -15227,12 +15227,12 @@
       </c>
       <c r="E278" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06490327GMP</t>
+          <t>KIT4M06491824JCK</t>
         </is>
       </c>
       <c r="F278" s="4" t="inlineStr">
         <is>
-          <t>816199</t>
+          <t>816413</t>
         </is>
       </c>
       <c r="G278" s="5" t="inlineStr">
@@ -15269,7 +15269,7 @@
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064917936NF</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649382 - KIT4M05368219KRH</t>
         </is>
       </c>
       <c r="C279" s="3" t="n">
@@ -15280,12 +15280,12 @@
       </c>
       <c r="E279" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064917936NF</t>
+          <t>KIT4M05368219KRH</t>
         </is>
       </c>
       <c r="F279" s="4" t="inlineStr">
         <is>
-          <t>816404</t>
+          <t>810646</t>
         </is>
       </c>
       <c r="G279" s="5" t="inlineStr">
@@ -15322,7 +15322,7 @@
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918068FF</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437262 - KIT4P0008460369B</t>
         </is>
       </c>
       <c r="C280" s="3" t="n">
@@ -15333,17 +15333,17 @@
       </c>
       <c r="E280" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918068FF</t>
+          <t>KIT4P0008460369B</t>
         </is>
       </c>
       <c r="F280" s="4" t="inlineStr">
         <is>
-          <t>816400</t>
+          <t>816224</t>
         </is>
       </c>
       <c r="G280" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H280" s="5" t="inlineStr">
@@ -15481,7 +15481,7 @@
       </c>
       <c r="B283" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955642 - KIT4M05563573WKC</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437892 - KIT4M06490321NJX</t>
         </is>
       </c>
       <c r="C283" s="3" t="n">
@@ -15492,12 +15492,12 @@
       </c>
       <c r="E283" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563573WKC</t>
+          <t>KIT4M06490321NJX</t>
         </is>
       </c>
       <c r="F283" s="4" t="inlineStr">
         <is>
-          <t>814488</t>
+          <t>816219</t>
         </is>
       </c>
       <c r="G283" s="5" t="inlineStr">
@@ -15534,7 +15534,7 @@
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437762 - KIT4M05872564MCF</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491789PJ6</t>
         </is>
       </c>
       <c r="C284" s="3" t="n">
@@ -15545,12 +15545,12 @@
       </c>
       <c r="E284" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872564MCF</t>
+          <t>KIT4M06491789PJ6</t>
         </is>
       </c>
       <c r="F284" s="4" t="inlineStr">
         <is>
-          <t>816203</t>
+          <t>816407</t>
         </is>
       </c>
       <c r="G284" s="5" t="inlineStr">
@@ -15587,7 +15587,7 @@
       </c>
       <c r="B285" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 021437772 - KIT4M05872563FWB</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437452 - KIT4M05872580C6X</t>
         </is>
       </c>
       <c r="C285" s="3" t="n">
@@ -15598,12 +15598,12 @@
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872563FWB</t>
+          <t>KIT4M05872580C6X</t>
         </is>
       </c>
       <c r="F285" s="4" t="inlineStr">
         <is>
-          <t>816208</t>
+          <t>816097</t>
         </is>
       </c>
       <c r="G285" s="5" t="inlineStr">
@@ -15640,7 +15640,7 @@
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438052 - KIT4M05872522W7W</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437972 - KIT4M06490327GMP</t>
         </is>
       </c>
       <c r="C286" s="3" t="n">
@@ -15651,12 +15651,12 @@
       </c>
       <c r="E286" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872522W7W</t>
+          <t>KIT4M06490327GMP</t>
         </is>
       </c>
       <c r="F286" s="4" t="inlineStr">
         <is>
-          <t>816217</t>
+          <t>816199</t>
         </is>
       </c>
       <c r="G286" s="5" t="inlineStr">
@@ -15693,7 +15693,7 @@
       </c>
       <c r="B287" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437492 - KIT4M0587256196K</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918068FF</t>
         </is>
       </c>
       <c r="C287" s="3" t="n">
@@ -15704,12 +15704,12 @@
       </c>
       <c r="E287" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0587256196K</t>
+          <t>KIT4M064918068FF</t>
         </is>
       </c>
       <c r="F287" s="4" t="inlineStr">
         <is>
-          <t>816098</t>
+          <t>816400</t>
         </is>
       </c>
       <c r="G287" s="5" t="inlineStr">
@@ -15746,7 +15746,7 @@
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437652 - KIT4M05872551G9S</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491797NCX</t>
         </is>
       </c>
       <c r="C288" s="3" t="n">
@@ -15757,12 +15757,12 @@
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872551G9S</t>
+          <t>KIT4M06491797NCX</t>
         </is>
       </c>
       <c r="F288" s="4" t="inlineStr">
         <is>
-          <t>816180</t>
+          <t>816408</t>
         </is>
       </c>
       <c r="G288" s="5" t="inlineStr">
@@ -15799,7 +15799,7 @@
       </c>
       <c r="B289" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437982 - KIT4M05799678R5P</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020955312 - KIT4M0556351956H</t>
         </is>
       </c>
       <c r="C289" s="3" t="n">
@@ -15810,12 +15810,12 @@
       </c>
       <c r="E289" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799678R5P</t>
+          <t>KIT4M0556351956H</t>
         </is>
       </c>
       <c r="F289" s="4" t="inlineStr">
         <is>
-          <t>816281</t>
+          <t>814477</t>
         </is>
       </c>
       <c r="G289" s="5" t="inlineStr">
@@ -15852,7 +15852,7 @@
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438062 - KIT4M05799676NNK</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438142  - KIT4M05799685DG5</t>
         </is>
       </c>
       <c r="C290" s="3" t="n">
@@ -15863,12 +15863,12 @@
       </c>
       <c r="E290" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799676NNK</t>
+          <t>KIT4M05799685DG5</t>
         </is>
       </c>
       <c r="F290" s="4" t="inlineStr">
         <is>
-          <t>816283</t>
+          <t>816271</t>
         </is>
       </c>
       <c r="G290" s="5" t="inlineStr">
@@ -15905,7 +15905,7 @@
       </c>
       <c r="B291" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438142  - KIT4M05799685DG5</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437982 - KIT4M05799678R5P</t>
         </is>
       </c>
       <c r="C291" s="3" t="n">
@@ -15916,12 +15916,12 @@
       </c>
       <c r="E291" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799685DG5</t>
+          <t>KIT4M05799678R5P</t>
         </is>
       </c>
       <c r="F291" s="4" t="inlineStr">
         <is>
-          <t>816271</t>
+          <t>816281</t>
         </is>
       </c>
       <c r="G291" s="5" t="inlineStr">
@@ -16011,7 +16011,7 @@
       </c>
       <c r="B293" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437902 - KIT4M05799717WZV</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438062 - KIT4M05799676NNK</t>
         </is>
       </c>
       <c r="C293" s="3" t="n">
@@ -16022,12 +16022,12 @@
       </c>
       <c r="E293" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799717WZV</t>
+          <t>KIT4M05799676NNK</t>
         </is>
       </c>
       <c r="F293" s="4" t="inlineStr">
         <is>
-          <t>816280</t>
+          <t>816283</t>
         </is>
       </c>
       <c r="G293" s="5" t="inlineStr">
@@ -16064,7 +16064,7 @@
       </c>
       <c r="B294" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438212 - KIT4M058725047FZ</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020650022 - KIT4M05413813HSJ</t>
         </is>
       </c>
       <c r="C294" s="3" t="n">
@@ -16075,12 +16075,12 @@
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725047FZ</t>
+          <t>KIT4M05413813HSJ</t>
         </is>
       </c>
       <c r="F294" s="4" t="inlineStr">
         <is>
-          <t>816289</t>
+          <t>812797</t>
         </is>
       </c>
       <c r="G294" s="5" t="inlineStr">
@@ -16170,7 +16170,7 @@
       </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649772 - KIT4M04475152RGR</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438272 - KIT4M05872517VS2</t>
         </is>
       </c>
       <c r="C296" s="3" t="n">
@@ -16181,12 +16181,12 @@
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475152RGR</t>
+          <t>KIT4M05872517VS2</t>
         </is>
       </c>
       <c r="F296" s="4" t="inlineStr">
         <is>
-          <t>809861</t>
+          <t>816288</t>
         </is>
       </c>
       <c r="G296" s="5" t="inlineStr">
@@ -16223,7 +16223,7 @@
       </c>
       <c r="B297" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020955312 - KIT4M0556351956H</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955642 - KIT4M05563573WKC</t>
         </is>
       </c>
       <c r="C297" s="3" t="n">
@@ -16234,12 +16234,12 @@
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0556351956H</t>
+          <t>KIT4M05563573WKC</t>
         </is>
       </c>
       <c r="F297" s="4" t="inlineStr">
         <is>
-          <t>814477</t>
+          <t>814488</t>
         </is>
       </c>
       <c r="G297" s="5" t="inlineStr">
@@ -16276,7 +16276,7 @@
       </c>
       <c r="B298" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955042 - KIT4P00072391SZM</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649772 - KIT4M04475152RGR</t>
         </is>
       </c>
       <c r="C298" s="3" t="n">
@@ -16287,17 +16287,17 @@
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00072391SZM</t>
+          <t>KIT4M04475152RGR</t>
         </is>
       </c>
       <c r="F298" s="4" t="inlineStr">
         <is>
-          <t>814493</t>
+          <t>809861</t>
         </is>
       </c>
       <c r="G298" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H298" s="5" t="inlineStr">
@@ -16329,7 +16329,7 @@
       </c>
       <c r="B299" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020649472-KIT4M05413795QHK</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955042 - KIT4P00072391SZM</t>
         </is>
       </c>
       <c r="C299" s="3" t="n">
@@ -16340,17 +16340,17 @@
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413795QHK</t>
+          <t>KIT4P00072391SZM</t>
         </is>
       </c>
       <c r="F299" s="4" t="inlineStr">
         <is>
-          <t>812801</t>
+          <t>814493</t>
         </is>
       </c>
       <c r="G299" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H299" s="5" t="inlineStr">
@@ -16371,7 +16371,7 @@
       </c>
       <c r="L299" s="5" t="n"/>
       <c r="M299" s="7" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="300">
@@ -16382,7 +16382,7 @@
       </c>
       <c r="B300" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 -  Los Angeles CA - 020649602 - KIT4M05413773R6G</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437762 - KIT4M05872564MCF</t>
         </is>
       </c>
       <c r="C300" s="3" t="n">
@@ -16393,12 +16393,12 @@
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413773R6G</t>
+          <t>KIT4M05872564MCF</t>
         </is>
       </c>
       <c r="F300" s="4" t="inlineStr">
         <is>
-          <t>812807</t>
+          <t>816203</t>
         </is>
       </c>
       <c r="G300" s="5" t="inlineStr">
@@ -16424,7 +16424,7 @@
       </c>
       <c r="L300" s="5" t="n"/>
       <c r="M300" s="7" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="301">
@@ -16435,7 +16435,7 @@
       </c>
       <c r="B301" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437642 - KIT4M05872590N8X</t>
+          <t>SS - 05900510 - Los Angeles, CA - 021437772 - KIT4M05872563FWB</t>
         </is>
       </c>
       <c r="C301" s="3" t="n">
@@ -16446,12 +16446,12 @@
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872590N8X</t>
+          <t>KIT4M05872563FWB</t>
         </is>
       </c>
       <c r="F301" s="4" t="inlineStr">
         <is>
-          <t>816204</t>
+          <t>816208</t>
         </is>
       </c>
       <c r="G301" s="5" t="inlineStr">
@@ -16477,7 +16477,7 @@
       </c>
       <c r="L301" s="5" t="n"/>
       <c r="M301" s="7" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="302">
@@ -16488,7 +16488,7 @@
       </c>
       <c r="B302" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649232 - KIT4P0006563862J</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438052 - KIT4M05872522W7W</t>
         </is>
       </c>
       <c r="C302" s="3" t="n">
@@ -16499,17 +16499,17 @@
       </c>
       <c r="E302" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0006563862J</t>
+          <t>KIT4M05872522W7W</t>
         </is>
       </c>
       <c r="F302" s="4" t="inlineStr">
         <is>
-          <t>812927</t>
+          <t>816217</t>
         </is>
       </c>
       <c r="G302" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H302" s="5" t="inlineStr">
@@ -16530,7 +16530,7 @@
       </c>
       <c r="L302" s="5" t="n"/>
       <c r="M302" s="7" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="303">
@@ -16541,7 +16541,7 @@
       </c>
       <c r="B303" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438102 - KIT4M05872513F7N</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437492 - KIT4M0587256196K</t>
         </is>
       </c>
       <c r="C303" s="3" t="n">
@@ -16552,12 +16552,12 @@
       </c>
       <c r="E303" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872513F7N</t>
+          <t>KIT4M0587256196K</t>
         </is>
       </c>
       <c r="F303" s="4" t="inlineStr">
         <is>
-          <t>816161</t>
+          <t>816098</t>
         </is>
       </c>
       <c r="G303" s="5" t="inlineStr">
@@ -16583,7 +16583,7 @@
       </c>
       <c r="L303" s="5" t="n"/>
       <c r="M303" s="7" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="304">
@@ -16594,7 +16594,7 @@
       </c>
       <c r="B304" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270114 - KIT4M04476539RJ5</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437652 - KIT4M05872551G9S</t>
         </is>
       </c>
       <c r="C304" s="3" t="n">
@@ -16605,12 +16605,12 @@
       </c>
       <c r="E304" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04476539RJ5</t>
+          <t>KIT4M05872551G9S</t>
         </is>
       </c>
       <c r="F304" s="4" t="inlineStr">
         <is>
-          <t>809612</t>
+          <t>816180</t>
         </is>
       </c>
       <c r="G304" s="5" t="inlineStr">
@@ -16636,7 +16636,7 @@
       </c>
       <c r="L304" s="5" t="n"/>
       <c r="M304" s="7" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="305">
@@ -16647,7 +16647,7 @@
       </c>
       <c r="B305" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649702 - KIT4M04604741P2X</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064917936NF</t>
         </is>
       </c>
       <c r="C305" s="3" t="n">
@@ -16658,12 +16658,12 @@
       </c>
       <c r="E305" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604741P2X</t>
+          <t>KIT4M064917936NF</t>
         </is>
       </c>
       <c r="F305" s="4" t="inlineStr">
         <is>
-          <t>809871</t>
+          <t>816404</t>
         </is>
       </c>
       <c r="G305" s="5" t="inlineStr">
@@ -16689,7 +16689,7 @@
       </c>
       <c r="L305" s="5" t="n"/>
       <c r="M305" s="7" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="306">
@@ -16700,7 +16700,7 @@
       </c>
       <c r="B306" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649992 - KIT4M05413809J58</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491790945</t>
         </is>
       </c>
       <c r="C306" s="3" t="n">
@@ -16711,12 +16711,12 @@
       </c>
       <c r="E306" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413809J58</t>
+          <t>KIT4M06491790945</t>
         </is>
       </c>
       <c r="F306" s="4" t="inlineStr">
         <is>
-          <t>812805</t>
+          <t>816410</t>
         </is>
       </c>
       <c r="G306" s="5" t="inlineStr">
@@ -16742,7 +16742,7 @@
       </c>
       <c r="L306" s="5" t="n"/>
       <c r="M306" s="7" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="307">
@@ -16753,7 +16753,7 @@
       </c>
       <c r="B307" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438202 - KIT4M05872506TTB</t>
+          <t>SMRT-05900510-Los Angeles CA-020649472-KIT4M05413795QHK</t>
         </is>
       </c>
       <c r="C307" s="3" t="n">
@@ -16764,12 +16764,12 @@
       </c>
       <c r="E307" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872506TTB</t>
+          <t>KIT4M05413795QHK</t>
         </is>
       </c>
       <c r="F307" s="4" t="inlineStr">
         <is>
-          <t>816082</t>
+          <t>812801</t>
         </is>
       </c>
       <c r="G307" s="5" t="inlineStr">
@@ -16795,7 +16795,7 @@
       </c>
       <c r="L307" s="5" t="n"/>
       <c r="M307" s="7" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="308">
@@ -16806,7 +16806,7 @@
       </c>
       <c r="B308" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437922 - KIT4M05872496MW6</t>
+          <t>SMA - 05900510 -  Los Angeles CA - 020649602 - KIT4M05413773R6G</t>
         </is>
       </c>
       <c r="C308" s="3" t="n">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E308" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872496MW6</t>
+          <t>KIT4M05413773R6G</t>
         </is>
       </c>
       <c r="F308" s="4" t="inlineStr">
         <is>
-          <t>816206</t>
+          <t>812807</t>
         </is>
       </c>
       <c r="G308" s="5" t="inlineStr">
@@ -16848,7 +16848,7 @@
       </c>
       <c r="L308" s="5" t="n"/>
       <c r="M308" s="7" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="309">
@@ -16859,7 +16859,7 @@
       </c>
       <c r="B309" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955562 - KIT4M05563505WPS</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437642 - KIT4M05872590N8X</t>
         </is>
       </c>
       <c r="C309" s="3" t="n">
@@ -16870,12 +16870,12 @@
       </c>
       <c r="E309" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563505WPS</t>
+          <t>KIT4M05872590N8X</t>
         </is>
       </c>
       <c r="F309" s="4" t="inlineStr">
         <is>
-          <t>814448</t>
+          <t>816204</t>
         </is>
       </c>
       <c r="G309" s="5" t="inlineStr">
@@ -16901,7 +16901,7 @@
       </c>
       <c r="L309" s="5" t="n"/>
       <c r="M309" s="7" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="310">
@@ -16912,7 +16912,7 @@
       </c>
       <c r="B310" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649982 - KIT4M05413823B5P</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649702 - KIT4M04604741P2X</t>
         </is>
       </c>
       <c r="C310" s="3" t="n">
@@ -16923,12 +16923,12 @@
       </c>
       <c r="E310" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413823B5P</t>
+          <t>KIT4M04604741P2X</t>
         </is>
       </c>
       <c r="F310" s="4" t="inlineStr">
         <is>
-          <t>812837</t>
+          <t>809871</t>
         </is>
       </c>
       <c r="G310" s="5" t="inlineStr">
@@ -16954,7 +16954,7 @@
       </c>
       <c r="L310" s="5" t="n"/>
       <c r="M310" s="7" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="311">
@@ -16965,7 +16965,7 @@
       </c>
       <c r="B311" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020649522-KIT4M05413834FTH</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649232 - KIT4P0006563862J</t>
         </is>
       </c>
       <c r="C311" s="3" t="n">
@@ -16976,17 +16976,17 @@
       </c>
       <c r="E311" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413834FTH</t>
+          <t>KIT4P0006563862J</t>
         </is>
       </c>
       <c r="F311" s="4" t="inlineStr">
         <is>
-          <t>812817</t>
+          <t>812927</t>
         </is>
       </c>
       <c r="G311" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H311" s="5" t="inlineStr">
@@ -17007,7 +17007,7 @@
       </c>
       <c r="L311" s="5" t="n"/>
       <c r="M311" s="7" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="312">
@@ -17018,7 +17018,7 @@
       </c>
       <c r="B312" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020650092 - KIT4M05413830JN7</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270114 - KIT4M04476539RJ5</t>
         </is>
       </c>
       <c r="C312" s="3" t="n">
@@ -17029,12 +17029,12 @@
       </c>
       <c r="E312" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413830JN7</t>
+          <t>KIT4M04476539RJ5</t>
         </is>
       </c>
       <c r="F312" s="4" t="inlineStr">
         <is>
-          <t>810105</t>
+          <t>809612</t>
         </is>
       </c>
       <c r="G312" s="5" t="inlineStr">
@@ -17060,7 +17060,7 @@
       </c>
       <c r="L312" s="5" t="n"/>
       <c r="M312" s="7" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="313">
@@ -17071,7 +17071,7 @@
       </c>
       <c r="B313" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955442 - KIT4M05563503XXP</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438102 - KIT4M05872513F7N</t>
         </is>
       </c>
       <c r="C313" s="3" t="n">
@@ -17082,12 +17082,12 @@
       </c>
       <c r="E313" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563503XXP</t>
+          <t>KIT4M05872513F7N</t>
         </is>
       </c>
       <c r="F313" s="4" t="inlineStr">
         <is>
-          <t>814430</t>
+          <t>816161</t>
         </is>
       </c>
       <c r="G313" s="5" t="inlineStr">
@@ -17113,7 +17113,7 @@
       </c>
       <c r="L313" s="5" t="n"/>
       <c r="M313" s="7" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="314">
@@ -17169,7 +17169,7 @@
       </c>
       <c r="B315" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955162 - KIT4M05563554WCW</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955442 - KIT4M05563503XXP</t>
         </is>
       </c>
       <c r="C315" s="3" t="n">
@@ -17180,12 +17180,12 @@
       </c>
       <c r="E315" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563554WCW</t>
+          <t>KIT4M05563503XXP</t>
         </is>
       </c>
       <c r="F315" s="4" t="inlineStr">
         <is>
-          <t>814444</t>
+          <t>814430</t>
         </is>
       </c>
       <c r="G315" s="5" t="inlineStr">
@@ -17381,7 +17381,7 @@
       </c>
       <c r="B319" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649612 - KIT4M05413827DC4</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955162 - KIT4M05563554WCW</t>
         </is>
       </c>
       <c r="C319" s="3" t="n">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E319" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413827DC4</t>
+          <t>KIT4M05563554WCW</t>
         </is>
       </c>
       <c r="F319" s="4" t="inlineStr">
         <is>
-          <t>812829</t>
+          <t>814444</t>
         </is>
       </c>
       <c r="G319" s="5" t="inlineStr">
@@ -17434,7 +17434,7 @@
       </c>
       <c r="B320" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649502 - KIT4M05413801QJB</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649612 - KIT4M05413827DC4</t>
         </is>
       </c>
       <c r="C320" s="3" t="n">
@@ -17445,12 +17445,12 @@
       </c>
       <c r="E320" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413801QJB</t>
+          <t>KIT4M05413827DC4</t>
         </is>
       </c>
       <c r="F320" s="4" t="inlineStr">
         <is>
-          <t>812824</t>
+          <t>812829</t>
         </is>
       </c>
       <c r="G320" s="5" t="inlineStr">
@@ -17487,7 +17487,7 @@
       </c>
       <c r="B321" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491789PJ6</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438202 - KIT4M05872506TTB</t>
         </is>
       </c>
       <c r="C321" s="3" t="n">
@@ -17498,12 +17498,12 @@
       </c>
       <c r="E321" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491789PJ6</t>
+          <t>KIT4M05872506TTB</t>
         </is>
       </c>
       <c r="F321" s="4" t="inlineStr">
         <is>
-          <t>816407</t>
+          <t>816082</t>
         </is>
       </c>
       <c r="G321" s="5" t="inlineStr">
@@ -17540,7 +17540,7 @@
       </c>
       <c r="B322" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 021437632 - KIT4M05872585HZZ</t>
+          <t>SMRT-05900510-Los Angeles CA-020649522-KIT4M05413834FTH</t>
         </is>
       </c>
       <c r="C322" s="3" t="n">
@@ -17551,12 +17551,12 @@
       </c>
       <c r="E322" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872585HZZ</t>
+          <t>KIT4M05413834FTH</t>
         </is>
       </c>
       <c r="F322" s="4" t="inlineStr">
         <is>
-          <t>816211</t>
+          <t>812817</t>
         </is>
       </c>
       <c r="G322" s="5" t="inlineStr">
@@ -17593,7 +17593,7 @@
       </c>
       <c r="B323" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020650032-KIT4M05413802FVN</t>
+          <t>STS - 05900510 - Los Angeles CA - 020650092 - KIT4M05413830JN7</t>
         </is>
       </c>
       <c r="C323" s="3" t="n">
@@ -17604,12 +17604,12 @@
       </c>
       <c r="E323" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413802FVN</t>
+          <t>KIT4M05413830JN7</t>
         </is>
       </c>
       <c r="F323" s="4" t="inlineStr">
         <is>
-          <t>812813</t>
+          <t>810105</t>
         </is>
       </c>
       <c r="G323" s="5" t="inlineStr">
@@ -17646,7 +17646,7 @@
       </c>
       <c r="B324" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020650222 - KIT4M05413790XCD</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437922 - KIT4M05872496MW6</t>
         </is>
       </c>
       <c r="C324" s="3" t="n">
@@ -17657,12 +17657,12 @@
       </c>
       <c r="E324" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413790XCD</t>
+          <t>KIT4M05872496MW6</t>
         </is>
       </c>
       <c r="F324" s="4" t="inlineStr">
         <is>
-          <t>812822</t>
+          <t>816206</t>
         </is>
       </c>
       <c r="G324" s="5" t="inlineStr">
@@ -17699,7 +17699,7 @@
       </c>
       <c r="B325" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020650062 - KIT4M05413797HK5</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649992 - KIT4M05413809J58</t>
         </is>
       </c>
       <c r="C325" s="3" t="n">
@@ -17710,12 +17710,12 @@
       </c>
       <c r="E325" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413797HK5</t>
+          <t>KIT4M05413809J58</t>
         </is>
       </c>
       <c r="F325" s="4" t="inlineStr">
         <is>
-          <t>812808</t>
+          <t>812805</t>
         </is>
       </c>
       <c r="G325" s="5" t="inlineStr">
@@ -17752,7 +17752,7 @@
       </c>
       <c r="B326" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649482 - KIT4M054137938P7</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955562 - KIT4M05563505WPS</t>
         </is>
       </c>
       <c r="C326" s="3" t="n">
@@ -17763,12 +17763,12 @@
       </c>
       <c r="E326" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137938P7</t>
+          <t>KIT4M05563505WPS</t>
         </is>
       </c>
       <c r="F326" s="4" t="inlineStr">
         <is>
-          <t>812848</t>
+          <t>814448</t>
         </is>
       </c>
       <c r="G326" s="5" t="inlineStr">
@@ -17805,7 +17805,7 @@
       </c>
       <c r="B327" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918015Z2</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649982 - KIT4M05413823B5P</t>
         </is>
       </c>
       <c r="C327" s="3" t="n">
@@ -17816,12 +17816,12 @@
       </c>
       <c r="E327" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918015Z2</t>
+          <t>KIT4M05413823B5P</t>
         </is>
       </c>
       <c r="F327" s="4" t="inlineStr">
         <is>
-          <t>816376</t>
+          <t>812837</t>
         </is>
       </c>
       <c r="G327" s="5" t="inlineStr">
@@ -17858,7 +17858,7 @@
       </c>
       <c r="B328" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491807TRH</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649502 - KIT4M05413801QJB</t>
         </is>
       </c>
       <c r="C328" s="3" t="n">
@@ -17869,12 +17869,12 @@
       </c>
       <c r="E328" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491807TRH</t>
+          <t>KIT4M05413801QJB</t>
         </is>
       </c>
       <c r="F328" s="4" t="inlineStr">
         <is>
-          <t>816386</t>
+          <t>812824</t>
         </is>
       </c>
       <c r="G328" s="5" t="inlineStr">
@@ -17911,7 +17911,7 @@
       </c>
       <c r="B329" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491805F7Z</t>
+          <t>SS - 05900510 -  Los Angeles CA - 021437632 - KIT4M05872585HZZ</t>
         </is>
       </c>
       <c r="C329" s="3" t="n">
@@ -17922,12 +17922,12 @@
       </c>
       <c r="E329" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491805F7Z</t>
+          <t>KIT4M05872585HZZ</t>
         </is>
       </c>
       <c r="F329" s="4" t="inlineStr">
         <is>
-          <t>816382</t>
+          <t>816211</t>
         </is>
       </c>
       <c r="G329" s="5" t="inlineStr">
@@ -17964,7 +17964,7 @@
       </c>
       <c r="B330" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491804TBC</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649482 - KIT4M054137938P7</t>
         </is>
       </c>
       <c r="C330" s="3" t="n">
@@ -17975,12 +17975,12 @@
       </c>
       <c r="E330" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491804TBC</t>
+          <t>KIT4M054137938P7</t>
         </is>
       </c>
       <c r="F330" s="4" t="inlineStr">
         <is>
-          <t>816373</t>
+          <t>812848</t>
         </is>
       </c>
       <c r="G330" s="5" t="inlineStr">
@@ -18017,7 +18017,7 @@
       </c>
       <c r="B331" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491797NCX</t>
+          <t>SMRT-05900510-Los Angeles CA-020650032-KIT4M05413802FVN</t>
         </is>
       </c>
       <c r="C331" s="3" t="n">
@@ -18028,12 +18028,12 @@
       </c>
       <c r="E331" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491797NCX</t>
+          <t>KIT4M05413802FVN</t>
         </is>
       </c>
       <c r="F331" s="4" t="inlineStr">
         <is>
-          <t>816408</t>
+          <t>812813</t>
         </is>
       </c>
       <c r="G331" s="5" t="inlineStr">
@@ -18070,7 +18070,7 @@
       </c>
       <c r="B332" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064917925MB</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020650222 - KIT4M05413790XCD</t>
         </is>
       </c>
       <c r="C332" s="3" t="n">
@@ -18081,12 +18081,12 @@
       </c>
       <c r="E332" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064917925MB</t>
+          <t>KIT4M05413790XCD</t>
         </is>
       </c>
       <c r="F332" s="4" t="inlineStr">
         <is>
-          <t>816381</t>
+          <t>812822</t>
         </is>
       </c>
       <c r="G332" s="5" t="inlineStr">
@@ -18123,7 +18123,7 @@
       </c>
       <c r="B333" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491802BZV</t>
+          <t>SS - 05900510 - Los Angeles CA - 020650062 - KIT4M05413797HK5</t>
         </is>
       </c>
       <c r="C333" s="3" t="n">
@@ -18134,12 +18134,12 @@
       </c>
       <c r="E333" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491802BZV</t>
+          <t>KIT4M05413797HK5</t>
         </is>
       </c>
       <c r="F333" s="4" t="inlineStr">
         <is>
-          <t>816390</t>
+          <t>812808</t>
         </is>
       </c>
       <c r="G333" s="5" t="inlineStr">
@@ -18176,7 +18176,7 @@
       </c>
       <c r="B334" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491795MWG</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491804TBC</t>
         </is>
       </c>
       <c r="C334" s="3" t="n">
@@ -18187,12 +18187,12 @@
       </c>
       <c r="E334" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491795MWG</t>
+          <t>KIT4M06491804TBC</t>
         </is>
       </c>
       <c r="F334" s="4" t="inlineStr">
         <is>
-          <t>816383</t>
+          <t>816373</t>
         </is>
       </c>
       <c r="G334" s="5" t="inlineStr">
@@ -18229,7 +18229,7 @@
       </c>
       <c r="B335" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491794MTJ</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491805F7Z</t>
         </is>
       </c>
       <c r="C335" s="3" t="n">
@@ -18240,12 +18240,12 @@
       </c>
       <c r="E335" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491794MTJ</t>
+          <t>KIT4M06491805F7Z</t>
         </is>
       </c>
       <c r="F335" s="4" t="inlineStr">
         <is>
-          <t>816375</t>
+          <t>816382</t>
         </is>
       </c>
       <c r="G335" s="5" t="inlineStr">
@@ -18282,7 +18282,7 @@
       </c>
       <c r="B336" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491790945</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491794MTJ</t>
         </is>
       </c>
       <c r="C336" s="3" t="n">
@@ -18293,12 +18293,12 @@
       </c>
       <c r="E336" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491790945</t>
+          <t>KIT4M06491794MTJ</t>
         </is>
       </c>
       <c r="F336" s="4" t="inlineStr">
         <is>
-          <t>816410</t>
+          <t>816375</t>
         </is>
       </c>
       <c r="G336" s="5" t="inlineStr">
@@ -18335,7 +18335,7 @@
       </c>
       <c r="B337" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491822SF6</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491821G25</t>
         </is>
       </c>
       <c r="C337" s="3" t="n">
@@ -18346,12 +18346,12 @@
       </c>
       <c r="E337" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491822SF6</t>
+          <t>KIT4M06491821G25</t>
         </is>
       </c>
       <c r="F337" s="4" t="inlineStr">
         <is>
-          <t>816412</t>
+          <t>816379</t>
         </is>
       </c>
       <c r="G337" s="5" t="inlineStr">
@@ -18388,7 +18388,7 @@
       </c>
       <c r="B338" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491821G25</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491820X58</t>
         </is>
       </c>
       <c r="C338" s="3" t="n">
@@ -18399,12 +18399,12 @@
       </c>
       <c r="E338" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491821G25</t>
+          <t>KIT4M06491820X58</t>
         </is>
       </c>
       <c r="F338" s="4" t="inlineStr">
         <is>
-          <t>816379</t>
+          <t>816385</t>
         </is>
       </c>
       <c r="G338" s="5" t="inlineStr">
@@ -18441,7 +18441,7 @@
       </c>
       <c r="B339" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491820X58</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491817T79</t>
         </is>
       </c>
       <c r="C339" s="3" t="n">
@@ -18452,12 +18452,12 @@
       </c>
       <c r="E339" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491820X58</t>
+          <t>KIT4M06491817T79</t>
         </is>
       </c>
       <c r="F339" s="4" t="inlineStr">
         <is>
-          <t>816385</t>
+          <t>816415</t>
         </is>
       </c>
       <c r="G339" s="5" t="inlineStr">
@@ -18600,7 +18600,7 @@
       </c>
       <c r="B342" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491817T79</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918154FM</t>
         </is>
       </c>
       <c r="C342" s="3" t="n">
@@ -18611,12 +18611,12 @@
       </c>
       <c r="E342" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491817T79</t>
+          <t>KIT4M064918154FM</t>
         </is>
       </c>
       <c r="F342" s="4" t="inlineStr">
         <is>
-          <t>816415</t>
+          <t>816368</t>
         </is>
       </c>
       <c r="G342" s="5" t="inlineStr">
@@ -18653,7 +18653,7 @@
       </c>
       <c r="B343" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918154FM</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491813KGS</t>
         </is>
       </c>
       <c r="C343" s="3" t="n">
@@ -18664,12 +18664,12 @@
       </c>
       <c r="E343" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918154FM</t>
+          <t>KIT4M06491813KGS</t>
         </is>
       </c>
       <c r="F343" s="4" t="inlineStr">
         <is>
-          <t>816368</t>
+          <t>816377</t>
         </is>
       </c>
       <c r="G343" s="5" t="inlineStr">
@@ -18759,7 +18759,7 @@
       </c>
       <c r="B345" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M0649181062D</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491807TRH</t>
         </is>
       </c>
       <c r="C345" s="3" t="n">
@@ -18770,12 +18770,12 @@
       </c>
       <c r="E345" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0649181062D</t>
+          <t>KIT4M06491807TRH</t>
         </is>
       </c>
       <c r="F345" s="4" t="inlineStr">
         <is>
-          <t>816388</t>
+          <t>816386</t>
         </is>
       </c>
       <c r="G345" s="5" t="inlineStr">
@@ -18812,7 +18812,7 @@
       </c>
       <c r="B346" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491813KGS</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M0649181062D</t>
         </is>
       </c>
       <c r="C346" s="3" t="n">
@@ -18823,12 +18823,12 @@
       </c>
       <c r="E346" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491813KGS</t>
+          <t>KIT4M0649181062D</t>
         </is>
       </c>
       <c r="F346" s="4" t="inlineStr">
         <is>
-          <t>816377</t>
+          <t>816388</t>
         </is>
       </c>
       <c r="G346" s="5" t="inlineStr">
@@ -18865,7 +18865,7 @@
       </c>
       <c r="B347" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491812JDV</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064917925MB</t>
         </is>
       </c>
       <c r="C347" s="3" t="n">
@@ -18876,12 +18876,12 @@
       </c>
       <c r="E347" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491812JDV</t>
+          <t>KIT4M064917925MB</t>
         </is>
       </c>
       <c r="F347" s="4" t="inlineStr">
         <is>
-          <t>816409</t>
+          <t>816381</t>
         </is>
       </c>
       <c r="G347" s="5" t="inlineStr">
@@ -18918,7 +18918,7 @@
       </c>
       <c r="B348" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491811JB5</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491795MWG</t>
         </is>
       </c>
       <c r="C348" s="3" t="n">
@@ -18929,12 +18929,12 @@
       </c>
       <c r="E348" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491811JB5</t>
+          <t>KIT4M06491795MWG</t>
         </is>
       </c>
       <c r="F348" s="4" t="inlineStr">
         <is>
-          <t>816411</t>
+          <t>816383</t>
         </is>
       </c>
       <c r="G348" s="5" t="inlineStr">
@@ -18971,7 +18971,7 @@
       </c>
       <c r="B349" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491830G2J</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491802BZV</t>
         </is>
       </c>
       <c r="C349" s="3" t="n">
@@ -18982,12 +18982,12 @@
       </c>
       <c r="E349" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491830G2J</t>
+          <t>KIT4M06491802BZV</t>
         </is>
       </c>
       <c r="F349" s="4" t="inlineStr">
         <is>
-          <t>816372</t>
+          <t>816390</t>
         </is>
       </c>
       <c r="G349" s="5" t="inlineStr">
@@ -19024,7 +19024,7 @@
       </c>
       <c r="B350" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491828XWF</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918015Z2</t>
         </is>
       </c>
       <c r="C350" s="3" t="n">
@@ -19035,12 +19035,12 @@
       </c>
       <c r="E350" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491828XWF</t>
+          <t>KIT4M064918015Z2</t>
         </is>
       </c>
       <c r="F350" s="4" t="inlineStr">
         <is>
-          <t>816387</t>
+          <t>816376</t>
         </is>
       </c>
       <c r="G350" s="5" t="inlineStr">
@@ -19077,7 +19077,7 @@
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491826SQM</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491830G2J</t>
         </is>
       </c>
       <c r="C351" s="3" t="n">
@@ -19088,12 +19088,12 @@
       </c>
       <c r="E351" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491826SQM</t>
+          <t>KIT4M06491830G2J</t>
         </is>
       </c>
       <c r="F351" s="4" t="inlineStr">
         <is>
-          <t>816380</t>
+          <t>816372</t>
         </is>
       </c>
       <c r="G351" s="5" t="inlineStr">
@@ -19130,7 +19130,7 @@
       </c>
       <c r="B352" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491824JCK</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491828XWF</t>
         </is>
       </c>
       <c r="C352" s="3" t="n">
@@ -19141,12 +19141,12 @@
       </c>
       <c r="E352" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491824JCK</t>
+          <t>KIT4M06491828XWF</t>
         </is>
       </c>
       <c r="F352" s="4" t="inlineStr">
         <is>
-          <t>816413</t>
+          <t>816387</t>
         </is>
       </c>
       <c r="G352" s="5" t="inlineStr">
@@ -19289,7 +19289,7 @@
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918322GZ</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M0649183125S</t>
         </is>
       </c>
       <c r="C355" s="3" t="n">
@@ -19300,12 +19300,12 @@
       </c>
       <c r="E355" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918322GZ</t>
+          <t>KIT4M0649183125S</t>
         </is>
       </c>
       <c r="F355" s="4" t="inlineStr">
         <is>
-          <t>816414</t>
+          <t>816371</t>
         </is>
       </c>
       <c r="G355" s="5" t="inlineStr">
@@ -19395,7 +19395,7 @@
       </c>
       <c r="B357" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M0649183125S</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491826SQM</t>
         </is>
       </c>
       <c r="C357" s="3" t="n">
@@ -19406,12 +19406,12 @@
       </c>
       <c r="E357" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0649183125S</t>
+          <t>KIT4M06491826SQM</t>
         </is>
       </c>
       <c r="F357" s="4" t="inlineStr">
         <is>
-          <t>816371</t>
+          <t>816380</t>
         </is>
       </c>
       <c r="G357" s="5" t="inlineStr">
@@ -20113,7 +20113,7 @@
     <row r="379">
       <c r="A379" s="15" t="inlineStr">
         <is>
-          <t>Generated 2026-08-25 08:49 by build_starlink_usage.py</t>
+          <t>Generated 2026-08-25 13:57 by build_starlink_usage.py</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_Current_by_Kit.xlsx
+++ b/Starlink_Usage_Current_by_Kit.xlsx
@@ -20113,7 +20113,7 @@
     <row r="379">
       <c r="A379" s="15" t="inlineStr">
         <is>
-          <t>Generated 2026-08-25 13:57 by build_starlink_usage.py</t>
+          <t>Generated 2026-08-25 15:45 by build_starlink_usage.py</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_Current_by_Kit.xlsx
+++ b/Starlink_Usage_Current_by_Kit.xlsx
@@ -20113,7 +20113,7 @@
     <row r="379">
       <c r="A379" s="15" t="inlineStr">
         <is>
-          <t>Generated 2026-08-25 15:45 by build_starlink_usage.py</t>
+          <t>Generated 2026-08-25 15:50 by build_starlink_usage.py</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_Current_by_Kit.xlsx
+++ b/Starlink_Usage_Current_by_Kit.xlsx
@@ -20113,7 +20113,7 @@
     <row r="379">
       <c r="A379" s="15" t="inlineStr">
         <is>
-          <t>Generated 2026-08-25 15:50 by build_starlink_usage.py</t>
+          <t>Generated 2026-08-25 17:06 by build_starlink_usage.py</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_Current_by_Kit.xlsx
+++ b/Starlink_Usage_Current_by_Kit.xlsx
@@ -20113,7 +20113,7 @@
     <row r="379">
       <c r="A379" s="15" t="inlineStr">
         <is>
-          <t>Generated 2026-08-26 20:03 by build_starlink_usage.py</t>
+          <t>Generated 2026-08-26 20:04 by build_starlink_usage.py</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_Current_by_Kit.xlsx
+++ b/Starlink_Usage_Current_by_Kit.xlsx
@@ -630,7 +630,7 @@
       </c>
       <c r="L2" s="5" t="n"/>
       <c r="M2" s="7" t="n">
-        <v>2414.85</v>
+        <v>2458.61</v>
       </c>
     </row>
     <row r="3">
@@ -683,7 +683,7 @@
       </c>
       <c r="L3" s="5" t="n"/>
       <c r="M3" s="7" t="n">
-        <v>2260.15</v>
+        <v>2261.65</v>
       </c>
     </row>
     <row r="4">
@@ -736,7 +736,7 @@
       </c>
       <c r="L4" s="5" t="n"/>
       <c r="M4" s="7" t="n">
-        <v>1620.36</v>
+        <v>1627.8</v>
       </c>
     </row>
     <row r="5">
@@ -789,7 +789,7 @@
       </c>
       <c r="L5" s="5" t="n"/>
       <c r="M5" s="7" t="n">
-        <v>1141.92</v>
+        <v>1288.24</v>
       </c>
     </row>
     <row r="6">
@@ -842,7 +842,7 @@
       </c>
       <c r="L6" s="5" t="n"/>
       <c r="M6" s="7" t="n">
-        <v>1068.61</v>
+        <v>1070.88</v>
       </c>
     </row>
     <row r="7">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270111116 - KIT4P00065612DJF</t>
+          <t>SS - 05900510 - Los Angeles, CA - 021437242 - KIT4P00083890S2G</t>
         </is>
       </c>
       <c r="C10" s="3" t="n">
@@ -1023,12 +1023,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065612DJF</t>
+          <t>KIT4P00083890S2G</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>809605</t>
+          <t>816226</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="L10" s="5" t="n"/>
       <c r="M10" s="7" t="n">
-        <v>709.23</v>
+        <v>757.27</v>
       </c>
     </row>
     <row r="11">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 021437242 - KIT4P00083890S2G</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270111116 - KIT4P00065612DJF</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00083890S2G</t>
+          <t>KIT4P00065612DJF</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>816226</t>
+          <t>809605</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="L11" s="5" t="n"/>
       <c r="M11" s="7" t="n">
-        <v>696.55</v>
+        <v>710.41</v>
       </c>
     </row>
     <row r="12">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>SMAR-05900510-Los Angeles CA-020426442-KIT4P00065630DZT</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437292 - KIT4P000832806P4</t>
         </is>
       </c>
       <c r="C12" s="3" t="n">
@@ -1129,12 +1129,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065630DZT</t>
+          <t>KIT4P000832806P4</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>807635</t>
+          <t>816228</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="L12" s="5" t="n"/>
       <c r="M12" s="7" t="n">
-        <v>679.27</v>
+        <v>700.64</v>
       </c>
     </row>
     <row r="13">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437282-KIT4P00084593R9F</t>
+          <t>SMAR-05900510-Los Angeles CA-020426442-KIT4P00065630DZT</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00084593R9F</t>
+          <t>KIT4P00065630DZT</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>816227</t>
+          <t>807635</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="L13" s="5" t="n"/>
       <c r="M13" s="7" t="n">
-        <v>653.6799999999999</v>
+        <v>691.6</v>
       </c>
     </row>
     <row r="14">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437292 - KIT4P000832806P4</t>
+          <t>SMRT-05900510-Los Angeles CA-021437282-KIT4P00084593R9F</t>
         </is>
       </c>
       <c r="C14" s="3" t="n">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>KIT4P000832806P4</t>
+          <t>KIT4P00084593R9F</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>816228</t>
+          <t>816227</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L14" s="5" t="n"/>
       <c r="M14" s="7" t="n">
-        <v>647.64</v>
+        <v>681.27</v>
       </c>
     </row>
     <row r="15">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="L15" s="5" t="n"/>
       <c r="M15" s="7" t="n">
-        <v>623.27</v>
+        <v>628.38</v>
       </c>
     </row>
     <row r="16">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="L16" s="5" t="n"/>
       <c r="M16" s="7" t="n">
-        <v>612.08</v>
+        <v>619.1</v>
       </c>
     </row>
     <row r="17">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="L19" s="5" t="n"/>
       <c r="M19" s="7" t="n">
-        <v>448.16</v>
+        <v>458.79</v>
       </c>
     </row>
     <row r="20">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955082 - KIT4P000739124KF</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955052 - KIT4P00073152MPN</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
@@ -1553,12 +1553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>KIT4P000739124KF</t>
+          <t>KIT4P00073152MPN</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>814640</t>
+          <t>814494</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="L20" s="5" t="n"/>
       <c r="M20" s="7" t="n">
-        <v>413.14</v>
+        <v>414.64</v>
       </c>
     </row>
     <row r="21">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955052 - KIT4P00073152MPN</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955082 - KIT4P000739124KF</t>
         </is>
       </c>
       <c r="C21" s="3" t="n">
@@ -1606,12 +1606,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073152MPN</t>
+          <t>KIT4P000739124KF</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>814494</t>
+          <t>814640</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="L21" s="5" t="n"/>
       <c r="M21" s="7" t="n">
-        <v>406.9</v>
+        <v>413.14</v>
       </c>
     </row>
     <row r="22">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="L27" s="5" t="n"/>
       <c r="M27" s="7" t="n">
-        <v>268.68</v>
+        <v>269.41</v>
       </c>
     </row>
     <row r="28">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="L28" s="5" t="n"/>
       <c r="M28" s="7" t="n">
-        <v>251.58</v>
+        <v>252.15</v>
       </c>
     </row>
     <row r="29">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="L32" s="5" t="n"/>
       <c r="M32" s="7" t="n">
-        <v>203.19</v>
+        <v>209.54</v>
       </c>
     </row>
     <row r="33">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438032 - KIT4M05799683GCK</t>
+          <t>SMRT-05900510-LOS ANGELES CA-020955062-KIT4P00073915XX6</t>
         </is>
       </c>
       <c r="C33" s="3" t="n">
@@ -2242,17 +2242,17 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799683GCK</t>
+          <t>KIT4P00073915XX6</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>816270</t>
+          <t>814643</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="L33" s="5" t="n"/>
       <c r="M33" s="7" t="n">
-        <v>167.72</v>
+        <v>180.11</v>
       </c>
     </row>
     <row r="34">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-LOS ANGELES CA-020955062-KIT4P00073915XX6</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438032 - KIT4M05799683GCK</t>
         </is>
       </c>
       <c r="C34" s="3" t="n">
@@ -2295,17 +2295,17 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073915XX6</t>
+          <t>KIT4M05799683GCK</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>814643</t>
+          <t>816270</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H34" s="5" t="inlineStr">
@@ -2326,7 +2326,7 @@
       </c>
       <c r="L34" s="5" t="n"/>
       <c r="M34" s="7" t="n">
-        <v>160.36</v>
+        <v>171.73</v>
       </c>
     </row>
     <row r="35">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="L35" s="5" t="n"/>
       <c r="M35" s="7" t="n">
-        <v>142.78</v>
+        <v>147.51</v>
       </c>
     </row>
     <row r="36">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="L36" s="5" t="n"/>
       <c r="M36" s="7" t="n">
-        <v>132.67</v>
+        <v>136.23</v>
       </c>
     </row>
     <row r="37">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="L41" s="5" t="n"/>
       <c r="M41" s="7" t="n">
-        <v>117.4</v>
+        <v>120.19</v>
       </c>
     </row>
     <row r="42">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="L43" s="5" t="n"/>
       <c r="M43" s="7" t="n">
-        <v>110.4</v>
+        <v>111.17</v>
       </c>
     </row>
     <row r="44">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles, CA-020955372-KIT4M05563537G4G</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955632 - KIT4M055635329VD</t>
         </is>
       </c>
       <c r="C45" s="3" t="n">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563537G4G</t>
+          <t>KIT4M055635329VD</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>814456</t>
+          <t>814479</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="L45" s="5" t="n"/>
       <c r="M45" s="7" t="n">
-        <v>108.22</v>
+        <v>108.78</v>
       </c>
     </row>
     <row r="46">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955632 - KIT4M055635329VD</t>
+          <t>SMRT-05900510-Los Angeles, CA-020955372-KIT4M05563537G4G</t>
         </is>
       </c>
       <c r="C46" s="3" t="n">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635329VD</t>
+          <t>KIT4M05563537G4G</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>814479</t>
+          <t>814456</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="L46" s="5" t="n"/>
       <c r="M46" s="7" t="n">
-        <v>103.48</v>
+        <v>108.22</v>
       </c>
     </row>
     <row r="47">
@@ -2973,7 +2973,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020650212 - KIT4M05413779VSD</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020650172 - KIT4M05413811F4Q</t>
         </is>
       </c>
       <c r="C47" s="3" t="n">
@@ -2984,12 +2984,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413779VSD</t>
+          <t>KIT4M05413811F4Q</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>810103</t>
+          <t>810104</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="L47" s="5" t="n"/>
       <c r="M47" s="7" t="n">
-        <v>96.01000000000001</v>
+        <v>98.8</v>
       </c>
     </row>
     <row r="48">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020650172 - KIT4M05413811F4Q</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020650212 - KIT4M05413779VSD</t>
         </is>
       </c>
       <c r="C48" s="3" t="n">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413811F4Q</t>
+          <t>KIT4M05413779VSD</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>810104</t>
+          <t>810103</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="L48" s="5" t="n"/>
       <c r="M48" s="7" t="n">
-        <v>95.27</v>
+        <v>96.01000000000001</v>
       </c>
     </row>
     <row r="49">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438042 - KIT4M05799686CMX</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270111110 - KIT4M03867737P9P</t>
         </is>
       </c>
       <c r="C49" s="3" t="n">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799686CMX</t>
+          <t>KIT4M03867737P9P</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>816282</t>
+          <t>809622</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="L49" s="5" t="n"/>
       <c r="M49" s="7" t="n">
-        <v>94.89</v>
+        <v>95.45999999999999</v>
       </c>
     </row>
     <row r="50">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270111110 - KIT4M03867737P9P</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482701116 - KIT4M03986275Q4M</t>
         </is>
       </c>
       <c r="C50" s="3" t="n">
@@ -3143,12 +3143,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03867737P9P</t>
+          <t>KIT4M03986275Q4M</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>809622</t>
+          <t>809621</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="L50" s="5" t="n"/>
       <c r="M50" s="7" t="n">
-        <v>94.73</v>
+        <v>95.09999999999999</v>
       </c>
     </row>
     <row r="51">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020650232 - KIT4M054138222CP</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438042 - KIT4M05799686CMX</t>
         </is>
       </c>
       <c r="C51" s="3" t="n">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138222CP</t>
+          <t>KIT4M05799686CMX</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>812811</t>
+          <t>816282</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="L51" s="5" t="n"/>
       <c r="M51" s="7" t="n">
-        <v>92.69</v>
+        <v>94.89</v>
       </c>
     </row>
     <row r="52">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="L52" s="5" t="n"/>
       <c r="M52" s="7" t="n">
-        <v>91.14</v>
+        <v>92.86</v>
       </c>
     </row>
     <row r="53">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482701116 - KIT4M03986275Q4M</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020650232 - KIT4M054138222CP</t>
         </is>
       </c>
       <c r="C53" s="3" t="n">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03986275Q4M</t>
+          <t>KIT4M054138222CP</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>809621</t>
+          <t>812811</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="L53" s="5" t="n"/>
       <c r="M53" s="7" t="n">
-        <v>89.54000000000001</v>
+        <v>92.69</v>
       </c>
     </row>
     <row r="54">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955472 - KIT4M055635834N7</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955522 - KIT4M05563504MBB</t>
         </is>
       </c>
       <c r="C54" s="3" t="n">
@@ -3355,12 +3355,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635834N7</t>
+          <t>KIT4M05563504MBB</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>814462</t>
+          <t>814460</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="L54" s="5" t="n"/>
       <c r="M54" s="7" t="n">
-        <v>86.98</v>
+        <v>92.17</v>
       </c>
     </row>
     <row r="55">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955142 - KIT4M05563518ZJD</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955472 - KIT4M055635834N7</t>
         </is>
       </c>
       <c r="C55" s="3" t="n">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563518ZJD</t>
+          <t>KIT4M055635834N7</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>814451</t>
+          <t>814462</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="L55" s="5" t="n"/>
       <c r="M55" s="7" t="n">
-        <v>85.18000000000001</v>
+        <v>86.98</v>
       </c>
     </row>
     <row r="56">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="L56" s="5" t="n"/>
       <c r="M56" s="7" t="n">
-        <v>84.98</v>
+        <v>86.22</v>
       </c>
     </row>
     <row r="57">
@@ -3503,7 +3503,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649872 - KIT4M054138175VJ</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955142 - KIT4M05563518ZJD</t>
         </is>
       </c>
       <c r="C57" s="3" t="n">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138175VJ</t>
+          <t>KIT4M05563518ZJD</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>812823</t>
+          <t>814451</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="L57" s="5" t="n"/>
       <c r="M57" s="7" t="n">
-        <v>83.95</v>
+        <v>85.18000000000001</v>
       </c>
     </row>
     <row r="58">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955332 - KIT4M05563590ZFQ</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649872 - KIT4M054138175VJ</t>
         </is>
       </c>
       <c r="C58" s="3" t="n">
@@ -3567,12 +3567,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563590ZFQ</t>
+          <t>KIT4M054138175VJ</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>814461</t>
+          <t>812823</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="L58" s="5" t="n"/>
       <c r="M58" s="7" t="n">
-        <v>79.5</v>
+        <v>83.95</v>
       </c>
     </row>
     <row r="59">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955522 - KIT4M05563504MBB</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955332 - KIT4M05563590ZFQ</t>
         </is>
       </c>
       <c r="C59" s="3" t="n">
@@ -3620,12 +3620,12 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563504MBB</t>
+          <t>KIT4M05563590ZFQ</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>814460</t>
+          <t>814461</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
@@ -3651,7 +3651,7 @@
       </c>
       <c r="L59" s="5" t="n"/>
       <c r="M59" s="7" t="n">
-        <v>78.59999999999999</v>
+        <v>79.77</v>
       </c>
     </row>
     <row r="60">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="L60" s="5" t="n"/>
       <c r="M60" s="7" t="n">
-        <v>74.77</v>
+        <v>75.34999999999999</v>
       </c>
     </row>
     <row r="61">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955092 - KIT4P00073957GV5</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955492 - KIT4M05563520SH2</t>
         </is>
       </c>
       <c r="C61" s="3" t="n">
@@ -3726,17 +3726,17 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073957GV5</t>
+          <t>KIT4M05563520SH2</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>814642</t>
+          <t>814478</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
@@ -3757,7 +3757,7 @@
       </c>
       <c r="L61" s="5" t="n"/>
       <c r="M61" s="7" t="n">
-        <v>72.83</v>
+        <v>74.48</v>
       </c>
     </row>
     <row r="62">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020649312-KIT4M05413771PVH</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649782 - KIT4M03986264P49</t>
         </is>
       </c>
       <c r="C62" s="3" t="n">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413771PVH</t>
+          <t>KIT4M03986264P49</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>812800</t>
+          <t>809875</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="L62" s="5" t="n"/>
       <c r="M62" s="7" t="n">
-        <v>70.48</v>
+        <v>73.95999999999999</v>
       </c>
     </row>
     <row r="63">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955492 - KIT4M05563520SH2</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955092 - KIT4P00073957GV5</t>
         </is>
       </c>
       <c r="C63" s="3" t="n">
@@ -3832,17 +3832,17 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563520SH2</t>
+          <t>KIT4P00073957GV5</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>814478</t>
+          <t>814642</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H63" s="5" t="inlineStr">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="L63" s="5" t="n"/>
       <c r="M63" s="7" t="n">
-        <v>70.16</v>
+        <v>72.83</v>
       </c>
     </row>
     <row r="64">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827014 - KIT4M04475149XG5</t>
+          <t>SS - 05900510 - Los Angeles CA - CW6578840- KIT4M04475128THH</t>
         </is>
       </c>
       <c r="C64" s="3" t="n">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475149XG5</t>
+          <t>KIT4M04475128THH</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>809657</t>
+          <t>809860</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="L64" s="5" t="n"/>
       <c r="M64" s="7" t="n">
-        <v>69.09999999999999</v>
+        <v>72.73</v>
       </c>
     </row>
     <row r="65">
@@ -3927,7 +3927,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649782 - KIT4M03986264P49</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827014 - KIT4M04475149XG5</t>
         </is>
       </c>
       <c r="C65" s="3" t="n">
@@ -3938,12 +3938,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03986264P49</t>
+          <t>KIT4M04475149XG5</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>809875</t>
+          <t>809657</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="L65" s="5" t="n"/>
       <c r="M65" s="7" t="n">
-        <v>68.89</v>
+        <v>72.03</v>
       </c>
     </row>
     <row r="66">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - CW6578840- KIT4M04475128THH</t>
+          <t>SMRT-05900510-Los Angeles CA-020649312-KIT4M05413771PVH</t>
         </is>
       </c>
       <c r="C66" s="3" t="n">
@@ -3991,12 +3991,12 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475128THH</t>
+          <t>KIT4M05413771PVH</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>809860</t>
+          <t>812800</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="L66" s="5" t="n"/>
       <c r="M66" s="7" t="n">
-        <v>67.53</v>
+        <v>71.08</v>
       </c>
     </row>
     <row r="67">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="L67" s="5" t="n"/>
       <c r="M67" s="7" t="n">
-        <v>67.45</v>
+        <v>68.39</v>
       </c>
     </row>
     <row r="68">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="L68" s="5" t="n"/>
       <c r="M68" s="7" t="n">
-        <v>66.81999999999999</v>
+        <v>67.2</v>
       </c>
     </row>
     <row r="69">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="L70" s="5" t="n"/>
       <c r="M70" s="7" t="n">
-        <v>59.92</v>
+        <v>60.81</v>
       </c>
     </row>
     <row r="71">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482702 - KIT4M04604743HSS</t>
+          <t>SS - 05900510 - Los Angeles CA - 020650102 - KIT4M054138257Z7</t>
         </is>
       </c>
       <c r="C71" s="3" t="n">
@@ -4256,12 +4256,12 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604743HSS</t>
+          <t>KIT4M054138257Z7</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>809663</t>
+          <t>810106</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
@@ -4287,7 +4287,7 @@
       </c>
       <c r="L71" s="5" t="n"/>
       <c r="M71" s="7" t="n">
-        <v>59.03</v>
+        <v>60.32</v>
       </c>
     </row>
     <row r="72">
@@ -4298,7 +4298,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482704 - KIT4M04604745G8Z</t>
+          <t xml:space="preserve">SS - 05900510 - Los Angeles, CA - 020649552 - KIT4M05413835RPF </t>
         </is>
       </c>
       <c r="C72" s="3" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604745G8Z</t>
+          <t>KIT4M05413835RPF</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>809661</t>
+          <t>812827</t>
         </is>
       </c>
       <c r="G72" s="5" t="inlineStr">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="L72" s="5" t="n"/>
       <c r="M72" s="7" t="n">
-        <v>57.1</v>
+        <v>60.24</v>
       </c>
     </row>
     <row r="73">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649902 - KIT4M05413805MKQ</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482702 - KIT4M04604743HSS</t>
         </is>
       </c>
       <c r="C73" s="3" t="n">
@@ -4362,12 +4362,12 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413805MKQ</t>
+          <t>KIT4M04604743HSS</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>812849</t>
+          <t>809663</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="L73" s="5" t="n"/>
       <c r="M73" s="7" t="n">
-        <v>55.17</v>
+        <v>59.03</v>
       </c>
     </row>
     <row r="74">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SS - 05900510 - Los Angeles, CA - 020649552 - KIT4M05413835RPF </t>
+          <t>STS - 05900510 - Los Angeles CA - 020482704 - KIT4M04604745G8Z</t>
         </is>
       </c>
       <c r="C74" s="3" t="n">
@@ -4415,12 +4415,12 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413835RPF</t>
+          <t>KIT4M04604745G8Z</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>812827</t>
+          <t>809661</t>
         </is>
       </c>
       <c r="G74" s="5" t="inlineStr">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="L74" s="5" t="n"/>
       <c r="M74" s="7" t="n">
-        <v>54.85</v>
+        <v>57.14</v>
       </c>
     </row>
     <row r="75">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649762 - KIT4M0460475549Z</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649902 - KIT4M05413805MKQ</t>
         </is>
       </c>
       <c r="C75" s="3" t="n">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0460475549Z</t>
+          <t>KIT4M05413805MKQ</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>809859</t>
+          <t>812849</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="L75" s="5" t="n"/>
       <c r="M75" s="7" t="n">
-        <v>53.03</v>
+        <v>55.96</v>
       </c>
     </row>
     <row r="76">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955412 - KIT4M05563598Z74</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955112 - KIT4P00073918HBX</t>
         </is>
       </c>
       <c r="C76" s="3" t="n">
@@ -4521,17 +4521,17 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563598Z74</t>
+          <t>KIT4P00073918HBX</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>814474</t>
+          <t>814645</t>
         </is>
       </c>
       <c r="G76" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H76" s="5" t="inlineStr">
@@ -4552,7 +4552,7 @@
       </c>
       <c r="L76" s="5" t="n"/>
       <c r="M76" s="7" t="n">
-        <v>52.27</v>
+        <v>54.59</v>
       </c>
     </row>
     <row r="77">
@@ -4563,7 +4563,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827011118 - KIT4M03867766NGK</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649762 - KIT4M0460475549Z</t>
         </is>
       </c>
       <c r="C77" s="3" t="n">
@@ -4574,12 +4574,12 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03867766NGK</t>
+          <t>KIT4M0460475549Z</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>809615</t>
+          <t>809859</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr">
@@ -4605,7 +4605,7 @@
       </c>
       <c r="L77" s="5" t="n"/>
       <c r="M77" s="7" t="n">
-        <v>50.34</v>
+        <v>53.03</v>
       </c>
     </row>
     <row r="78">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020650142 - KIT4M05413839D24</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955412 - KIT4M05563598Z74</t>
         </is>
       </c>
       <c r="C78" s="3" t="n">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413839D24</t>
+          <t>KIT4M05563598Z74</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>810096</t>
+          <t>814474</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="L78" s="5" t="n"/>
       <c r="M78" s="7" t="n">
-        <v>50.33</v>
+        <v>52.27</v>
       </c>
     </row>
     <row r="79">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270111114 - KIT4P00065593VWC</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827011118 - KIT4M03867766NGK</t>
         </is>
       </c>
       <c r="C79" s="3" t="n">
@@ -4680,17 +4680,17 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065593VWC</t>
+          <t>KIT4M03867766NGK</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>809606</t>
+          <t>809615</t>
         </is>
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H79" s="5" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="L79" s="5" t="n"/>
       <c r="M79" s="7" t="n">
-        <v>49.23</v>
+        <v>50.49</v>
       </c>
     </row>
     <row r="80">
@@ -4722,7 +4722,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955182 - KIT4M05563562F45</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020650142 - KIT4M05413839D24</t>
         </is>
       </c>
       <c r="C80" s="3" t="n">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563562F45</t>
+          <t>KIT4M05413839D24</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>814443</t>
+          <t>810096</t>
         </is>
       </c>
       <c r="G80" s="5" t="inlineStr">
@@ -4764,7 +4764,7 @@
       </c>
       <c r="L80" s="5" t="n"/>
       <c r="M80" s="7" t="n">
-        <v>48.47</v>
+        <v>50.33</v>
       </c>
     </row>
     <row r="81">
@@ -4775,7 +4775,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-LOS ANGELES CA-020955202-KIT4M05563534GZ7</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649932 - KIT4M054138324MW</t>
         </is>
       </c>
       <c r="C81" s="3" t="n">
@@ -4786,12 +4786,12 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563534GZ7</t>
+          <t>KIT4M054138324MW</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>814467</t>
+          <t>812834</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="L81" s="5" t="n"/>
       <c r="M81" s="7" t="n">
-        <v>48.39</v>
+        <v>49.76</v>
       </c>
     </row>
     <row r="82">
@@ -4828,7 +4828,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649932 - KIT4M054138324MW</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955292 - KIT4M05563531XSB</t>
         </is>
       </c>
       <c r="C82" s="3" t="n">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138324MW</t>
+          <t>KIT4M05563531XSB</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>812834</t>
+          <t>814469</t>
         </is>
       </c>
       <c r="G82" s="5" t="inlineStr">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="L82" s="5" t="n"/>
       <c r="M82" s="7" t="n">
-        <v>48.36</v>
+        <v>49.48</v>
       </c>
     </row>
     <row r="83">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955262 - KIT4M05563521ZSX</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270111114 - KIT4P00065593VWC</t>
         </is>
       </c>
       <c r="C83" s="3" t="n">
@@ -4892,17 +4892,17 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563521ZSX</t>
+          <t>KIT4P00065593VWC</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>814476</t>
+          <t>809606</t>
         </is>
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H83" s="5" t="inlineStr">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="L83" s="5" t="n"/>
       <c r="M83" s="7" t="n">
-        <v>48.34</v>
+        <v>49.23</v>
       </c>
     </row>
     <row r="84">
@@ -4934,7 +4934,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955112 - KIT4P00073918HBX</t>
+          <t>SMRT-05900510-LOS ANGELES CA-020955202-KIT4M05563534GZ7</t>
         </is>
       </c>
       <c r="C84" s="3" t="n">
@@ -4945,17 +4945,17 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073918HBX</t>
+          <t>KIT4M05563534GZ7</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>814645</t>
+          <t>814467</t>
         </is>
       </c>
       <c r="G84" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H84" s="5" t="inlineStr">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="L84" s="5" t="n"/>
       <c r="M84" s="7" t="n">
-        <v>47.58</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="85">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649672 - KIT4M04606113TPB</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955182 - KIT4M05563562F45</t>
         </is>
       </c>
       <c r="C85" s="3" t="n">
@@ -4998,12 +4998,12 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04606113TPB</t>
+          <t>KIT4M05563562F45</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>809862</t>
+          <t>814443</t>
         </is>
       </c>
       <c r="G85" s="5" t="inlineStr">
@@ -5029,7 +5029,7 @@
       </c>
       <c r="L85" s="5" t="n"/>
       <c r="M85" s="7" t="n">
-        <v>46.74</v>
+        <v>48.47</v>
       </c>
     </row>
     <row r="86">
@@ -5040,7 +5040,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955292 - KIT4M05563531XSB</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955262 - KIT4M05563521ZSX</t>
         </is>
       </c>
       <c r="C86" s="3" t="n">
@@ -5051,12 +5051,12 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563531XSB</t>
+          <t>KIT4M05563521ZSX</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>814469</t>
+          <t>814476</t>
         </is>
       </c>
       <c r="G86" s="5" t="inlineStr">
@@ -5082,7 +5082,7 @@
       </c>
       <c r="L86" s="5" t="n"/>
       <c r="M86" s="7" t="n">
-        <v>46.72</v>
+        <v>48.34</v>
       </c>
     </row>
     <row r="87">
@@ -5093,7 +5093,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles, CA - 0204827011112 - KIT4M04158967K28</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649672 - KIT4M04606113TPB</t>
         </is>
       </c>
       <c r="C87" s="3" t="n">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158967K28</t>
+          <t>KIT4M04606113TPB</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>809620</t>
+          <t>809862</t>
         </is>
       </c>
       <c r="G87" s="5" t="inlineStr">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="L87" s="5" t="n"/>
       <c r="M87" s="7" t="n">
-        <v>45.69</v>
+        <v>46.74</v>
       </c>
     </row>
     <row r="88">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="L88" s="5" t="n"/>
       <c r="M88" s="7" t="n">
-        <v>43.91</v>
+        <v>45.98</v>
       </c>
     </row>
     <row r="89">
@@ -5199,7 +5199,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649812 - KIT4M04604742S6S</t>
+          <t>STS - 05900510 - Los Angeles, CA - 0204827011112 - KIT4M04158967K28</t>
         </is>
       </c>
       <c r="C89" s="3" t="n">
@@ -5210,12 +5210,12 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604742S6S</t>
+          <t>KIT4M04158967K28</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>809874</t>
+          <t>809620</t>
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr">
@@ -5241,7 +5241,7 @@
       </c>
       <c r="L89" s="5" t="n"/>
       <c r="M89" s="7" t="n">
-        <v>43.24</v>
+        <v>45.91</v>
       </c>
     </row>
     <row r="90">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="L90" s="5" t="n"/>
       <c r="M90" s="7" t="n">
-        <v>42.93</v>
+        <v>43.64</v>
       </c>
     </row>
     <row r="91">
@@ -5305,7 +5305,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649432 - KIT4M05413778RBR</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955692 - KIT4M05563603CP4</t>
         </is>
       </c>
       <c r="C91" s="3" t="n">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413778RBR</t>
+          <t>KIT4M05563603CP4</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>812843</t>
+          <t>814447</t>
         </is>
       </c>
       <c r="G91" s="5" t="inlineStr">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="L91" s="5" t="n"/>
       <c r="M91" s="7" t="n">
-        <v>42.82</v>
+        <v>43.57</v>
       </c>
     </row>
     <row r="92">
@@ -5358,7 +5358,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020650192 - KIT4M054138007JF</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649812 - KIT4M04604742S6S</t>
         </is>
       </c>
       <c r="C92" s="3" t="n">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138007JF</t>
+          <t>KIT4M04604742S6S</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>810095</t>
+          <t>809874</t>
         </is>
       </c>
       <c r="G92" s="5" t="inlineStr">
@@ -5400,7 +5400,7 @@
       </c>
       <c r="L92" s="5" t="n"/>
       <c r="M92" s="7" t="n">
-        <v>42.59</v>
+        <v>43.24</v>
       </c>
     </row>
     <row r="93">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955692 - KIT4M05563603CP4</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649432 - KIT4M05413778RBR</t>
         </is>
       </c>
       <c r="C93" s="3" t="n">
@@ -5422,12 +5422,12 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563603CP4</t>
+          <t>KIT4M05413778RBR</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>814447</t>
+          <t>812843</t>
         </is>
       </c>
       <c r="G93" s="5" t="inlineStr">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="L93" s="5" t="n"/>
       <c r="M93" s="7" t="n">
-        <v>42.26</v>
+        <v>42.82</v>
       </c>
     </row>
     <row r="94">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020650052 - KIT4M05413781K6C</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020650192 - KIT4M054138007JF</t>
         </is>
       </c>
       <c r="C94" s="3" t="n">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413781K6C</t>
+          <t>KIT4M054138007JF</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>812798</t>
+          <t>810095</t>
         </is>
       </c>
       <c r="G94" s="5" t="inlineStr">
@@ -5506,7 +5506,7 @@
       </c>
       <c r="L94" s="5" t="n"/>
       <c r="M94" s="7" t="n">
-        <v>42.04</v>
+        <v>42.59</v>
       </c>
     </row>
     <row r="95">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020955652 - KIT4M0556358988Z</t>
+          <t>SMRT-05900510-Los Angeles, CA-020955582-KIT4M05563593DMC</t>
         </is>
       </c>
       <c r="C95" s="3" t="n">
@@ -5528,12 +5528,12 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0556358988Z</t>
+          <t>KIT4M05563593DMC</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>814484</t>
+          <t>814442</t>
         </is>
       </c>
       <c r="G95" s="5" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="L95" s="5" t="n"/>
       <c r="M95" s="7" t="n">
-        <v>39.91</v>
+        <v>42.18</v>
       </c>
     </row>
     <row r="96">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270116 - KIT4M03476116F45</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020650052 - KIT4M05413781K6C</t>
         </is>
       </c>
       <c r="C96" s="3" t="n">
@@ -5581,12 +5581,12 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03476116F45</t>
+          <t>KIT4M05413781K6C</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>809608</t>
+          <t>812798</t>
         </is>
       </c>
       <c r="G96" s="5" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="L96" s="5" t="n"/>
       <c r="M96" s="7" t="n">
-        <v>39.46</v>
+        <v>42.04</v>
       </c>
     </row>
     <row r="97">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles, CA-020955582-KIT4M05563593DMC</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955132 - KIT4M055635238J6</t>
         </is>
       </c>
       <c r="C97" s="3" t="n">
@@ -5634,12 +5634,12 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563593DMC</t>
+          <t>KIT4M055635238J6</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>814442</t>
+          <t>814449</t>
         </is>
       </c>
       <c r="G97" s="5" t="inlineStr">
@@ -5665,7 +5665,7 @@
       </c>
       <c r="L97" s="5" t="n"/>
       <c r="M97" s="7" t="n">
-        <v>39.02</v>
+        <v>39.94</v>
       </c>
     </row>
     <row r="98">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955132 - KIT4M055635238J6</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020955652 - KIT4M0556358988Z</t>
         </is>
       </c>
       <c r="C98" s="3" t="n">
@@ -5687,12 +5687,12 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635238J6</t>
+          <t>KIT4M0556358988Z</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>814449</t>
+          <t>814484</t>
         </is>
       </c>
       <c r="G98" s="5" t="inlineStr">
@@ -5718,7 +5718,7 @@
       </c>
       <c r="L98" s="5" t="n"/>
       <c r="M98" s="7" t="n">
-        <v>38.27</v>
+        <v>39.91</v>
       </c>
     </row>
     <row r="99">
@@ -5729,7 +5729,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955602 - KIT4M05563560225</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270116 - KIT4M03476116F45</t>
         </is>
       </c>
       <c r="C99" s="3" t="n">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563560225</t>
+          <t>KIT4M03476116F45</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>814454</t>
+          <t>809608</t>
         </is>
       </c>
       <c r="G99" s="5" t="inlineStr">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="L99" s="5" t="n"/>
       <c r="M99" s="7" t="n">
-        <v>38.09</v>
+        <v>39.71</v>
       </c>
     </row>
     <row r="100">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020650102 - KIT4M054138257Z7</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955692 - KIT4M05563579H9F</t>
         </is>
       </c>
       <c r="C100" s="3" t="n">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138257Z7</t>
+          <t>KIT4M05563579H9F</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>810106</t>
+          <t>814480</t>
         </is>
       </c>
       <c r="G100" s="5" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="L100" s="5" t="n"/>
       <c r="M100" s="7" t="n">
-        <v>38.05</v>
+        <v>39.19</v>
       </c>
     </row>
     <row r="101">
@@ -5835,7 +5835,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020650082 - KIT4M05413792H8C</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649712 - KIT4M046047397TM</t>
         </is>
       </c>
       <c r="C101" s="3" t="n">
@@ -5846,12 +5846,12 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413792H8C</t>
+          <t>KIT4M046047397TM</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>812803</t>
+          <t>809863</t>
         </is>
       </c>
       <c r="G101" s="5" t="inlineStr">
@@ -5877,7 +5877,7 @@
       </c>
       <c r="L101" s="5" t="n"/>
       <c r="M101" s="7" t="n">
-        <v>37.8</v>
+        <v>38.83</v>
       </c>
     </row>
     <row r="102">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020650202-KIT4M05413803FDK</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438092 - KIT4M05799694RW2</t>
         </is>
       </c>
       <c r="C102" s="3" t="n">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413803FDK</t>
+          <t>KIT4M05799694RW2</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>812850</t>
+          <t>816277</t>
         </is>
       </c>
       <c r="G102" s="5" t="inlineStr">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="L102" s="5" t="n"/>
       <c r="M102" s="7" t="n">
-        <v>37.4</v>
+        <v>38.4</v>
       </c>
     </row>
     <row r="103">
@@ -5941,7 +5941,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955692 - KIT4M05563579H9F</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955602 - KIT4M05563560225</t>
         </is>
       </c>
       <c r="C103" s="3" t="n">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563579H9F</t>
+          <t>KIT4M05563560225</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>814480</t>
+          <t>814454</t>
         </is>
       </c>
       <c r="G103" s="5" t="inlineStr">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="L103" s="5" t="n"/>
       <c r="M103" s="7" t="n">
-        <v>36.91</v>
+        <v>38.09</v>
       </c>
     </row>
     <row r="104">
@@ -5994,7 +5994,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955272 - KIT4M05563585TXM</t>
+          <t>SMRT-05900510-Los Angeles CA-020650202-KIT4M05413803FDK</t>
         </is>
       </c>
       <c r="C104" s="3" t="n">
@@ -6005,12 +6005,12 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563585TXM</t>
+          <t>KIT4M05413803FDK</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>814475</t>
+          <t>812850</t>
         </is>
       </c>
       <c r="G104" s="5" t="inlineStr">
@@ -6036,7 +6036,7 @@
       </c>
       <c r="L104" s="5" t="n"/>
       <c r="M104" s="7" t="n">
-        <v>36.9</v>
+        <v>38.07</v>
       </c>
     </row>
     <row r="105">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 020955382 - KIT4M05563509CHJ</t>
+          <t>SMRT-05900510-Los Angeles, CA-020955352-KIT4M05563525VC6</t>
         </is>
       </c>
       <c r="C105" s="3" t="n">
@@ -6058,12 +6058,12 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563509CHJ</t>
+          <t>KIT4M05563525VC6</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>814431</t>
+          <t>814458</t>
         </is>
       </c>
       <c r="G105" s="5" t="inlineStr">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="L105" s="5" t="n"/>
       <c r="M105" s="7" t="n">
-        <v>36.43</v>
+        <v>37.97</v>
       </c>
     </row>
     <row r="106">
@@ -6100,7 +6100,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649712 - KIT4M046047397TM</t>
+          <t>STS - 05900510 - Los Angeles CA - 020650082 - KIT4M05413792H8C</t>
         </is>
       </c>
       <c r="C106" s="3" t="n">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047397TM</t>
+          <t>KIT4M05413792H8C</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>809863</t>
+          <t>812803</t>
         </is>
       </c>
       <c r="G106" s="5" t="inlineStr">
@@ -6142,7 +6142,7 @@
       </c>
       <c r="L106" s="5" t="n"/>
       <c r="M106" s="7" t="n">
-        <v>36.43</v>
+        <v>37.81</v>
       </c>
     </row>
     <row r="107">
@@ -6153,7 +6153,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles, CA-020955352-KIT4M05563525VC6</t>
+          <t>SS - 05900510 -  Los Angeles CA - 020955382 - KIT4M05563509CHJ</t>
         </is>
       </c>
       <c r="C107" s="3" t="n">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563525VC6</t>
+          <t>KIT4M05563509CHJ</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>814458</t>
+          <t>814431</t>
         </is>
       </c>
       <c r="G107" s="5" t="inlineStr">
@@ -6195,7 +6195,7 @@
       </c>
       <c r="L107" s="5" t="n"/>
       <c r="M107" s="7" t="n">
-        <v>36.2</v>
+        <v>37.62</v>
       </c>
     </row>
     <row r="108">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="L108" s="5" t="n"/>
       <c r="M108" s="7" t="n">
-        <v>36.01</v>
+        <v>37.56</v>
       </c>
     </row>
     <row r="109">
@@ -6259,7 +6259,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020650042 - KIT4M05413819JV5</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955272 - KIT4M05563585TXM</t>
         </is>
       </c>
       <c r="C109" s="3" t="n">
@@ -6270,12 +6270,12 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413819JV5</t>
+          <t>KIT4M05563585TXM</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>812796</t>
+          <t>814475</t>
         </is>
       </c>
       <c r="G109" s="5" t="inlineStr">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="L109" s="5" t="n"/>
       <c r="M109" s="7" t="n">
-        <v>34.55</v>
+        <v>36.9</v>
       </c>
     </row>
     <row r="110">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438092 - KIT4M05799694RW2</t>
+          <t>SS - 05900510 - Los Angeles CA - 020650042 - KIT4M05413819JV5</t>
         </is>
       </c>
       <c r="C110" s="3" t="n">
@@ -6323,12 +6323,12 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799694RW2</t>
+          <t>KIT4M05413819JV5</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>816277</t>
+          <t>812796</t>
         </is>
       </c>
       <c r="G110" s="5" t="inlineStr">
@@ -6354,7 +6354,7 @@
       </c>
       <c r="L110" s="5" t="n"/>
       <c r="M110" s="7" t="n">
-        <v>34.37</v>
+        <v>34.55</v>
       </c>
     </row>
     <row r="111">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="L111" s="5" t="n"/>
       <c r="M111" s="7" t="n">
-        <v>34.37</v>
+        <v>34.4</v>
       </c>
     </row>
     <row r="112">
@@ -6418,7 +6418,7 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649412 - KIT4M05413769796</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955702 - KIT4M05563571G8W</t>
         </is>
       </c>
       <c r="C112" s="3" t="n">
@@ -6429,12 +6429,12 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413769796</t>
+          <t>KIT4M05563571G8W</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>812839</t>
+          <t>814481</t>
         </is>
       </c>
       <c r="G112" s="5" t="inlineStr">
@@ -6460,7 +6460,7 @@
       </c>
       <c r="L112" s="5" t="n"/>
       <c r="M112" s="7" t="n">
-        <v>32.57</v>
+        <v>32.79</v>
       </c>
     </row>
     <row r="113">
@@ -6471,7 +6471,7 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482706 - KIT4M04604744V6K</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649412 - KIT4M05413769796</t>
         </is>
       </c>
       <c r="C113" s="3" t="n">
@@ -6482,12 +6482,12 @@
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604744V6K</t>
+          <t>KIT4M05413769796</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>809659</t>
+          <t>812839</t>
         </is>
       </c>
       <c r="G113" s="5" t="inlineStr">
@@ -6513,7 +6513,7 @@
       </c>
       <c r="L113" s="5" t="n"/>
       <c r="M113" s="7" t="n">
-        <v>30.85</v>
+        <v>32.57</v>
       </c>
     </row>
     <row r="114">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649372 - KIT4M05368221HQ5</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482706 - KIT4M04604744V6K</t>
         </is>
       </c>
       <c r="C114" s="3" t="n">
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368221HQ5</t>
+          <t>KIT4M04604744V6K</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>810834</t>
+          <t>809659</t>
         </is>
       </c>
       <c r="G114" s="5" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="L114" s="5" t="n"/>
       <c r="M114" s="7" t="n">
-        <v>29.14</v>
+        <v>31.35</v>
       </c>
     </row>
     <row r="115">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="L115" s="5" t="n"/>
       <c r="M115" s="7" t="n">
-        <v>28.91</v>
+        <v>30.04</v>
       </c>
     </row>
     <row r="116">
@@ -6672,7 +6672,7 @@
       </c>
       <c r="L116" s="5" t="n"/>
       <c r="M116" s="7" t="n">
-        <v>27.77</v>
+        <v>29.29</v>
       </c>
     </row>
     <row r="117">
@@ -6683,7 +6683,7 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649742 - KIT4M04350554X4Z</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649372 - KIT4M05368221HQ5</t>
         </is>
       </c>
       <c r="C117" s="3" t="n">
@@ -6694,12 +6694,12 @@
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04350554X4Z</t>
+          <t>KIT4M05368221HQ5</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>809866</t>
+          <t>810834</t>
         </is>
       </c>
       <c r="G117" s="5" t="inlineStr">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="L117" s="5" t="n"/>
       <c r="M117" s="7" t="n">
-        <v>26.69</v>
+        <v>29.14</v>
       </c>
     </row>
     <row r="118">
@@ -6736,7 +6736,7 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955342 - KIT4M05563524MJ4</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827016 - KIT4M041536494G6</t>
         </is>
       </c>
       <c r="C118" s="3" t="n">
@@ -6747,12 +6747,12 @@
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563524MJ4</t>
+          <t>KIT4M041536494G6</t>
         </is>
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>814472</t>
+          <t>809617</t>
         </is>
       </c>
       <c r="G118" s="5" t="inlineStr">
@@ -6778,7 +6778,7 @@
       </c>
       <c r="L118" s="5" t="n"/>
       <c r="M118" s="7" t="n">
-        <v>26.26</v>
+        <v>27.69</v>
       </c>
     </row>
     <row r="119">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="L119" s="5" t="n"/>
       <c r="M119" s="7" t="n">
-        <v>25.25</v>
+        <v>27.31</v>
       </c>
     </row>
     <row r="120">
@@ -6842,7 +6842,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649362 - KIT4M05368336DBC</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649742 - KIT4M04350554X4Z</t>
         </is>
       </c>
       <c r="C120" s="3" t="n">
@@ -6853,12 +6853,12 @@
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368336DBC</t>
+          <t>KIT4M04350554X4Z</t>
         </is>
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t>810831</t>
+          <t>809866</t>
         </is>
       </c>
       <c r="G120" s="5" t="inlineStr">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="L120" s="5" t="n"/>
       <c r="M120" s="7" t="n">
-        <v>25.13</v>
+        <v>27.16</v>
       </c>
     </row>
     <row r="121">
@@ -6895,7 +6895,7 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955212 - KIT4M05563512GBQ</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955342 - KIT4M05563524MJ4</t>
         </is>
       </c>
       <c r="C121" s="3" t="n">
@@ -6906,12 +6906,12 @@
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563512GBQ</t>
+          <t>KIT4M05563524MJ4</t>
         </is>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>814435</t>
+          <t>814472</t>
         </is>
       </c>
       <c r="G121" s="5" t="inlineStr">
@@ -6937,7 +6937,7 @@
       </c>
       <c r="L121" s="5" t="n"/>
       <c r="M121" s="7" t="n">
-        <v>24.55</v>
+        <v>26.26</v>
       </c>
     </row>
     <row r="122">
@@ -6948,7 +6948,7 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955702 - KIT4M05563571G8W</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649362 - KIT4M05368336DBC</t>
         </is>
       </c>
       <c r="C122" s="3" t="n">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563571G8W</t>
+          <t>KIT4M05368336DBC</t>
         </is>
       </c>
       <c r="F122" s="4" t="inlineStr">
         <is>
-          <t>814481</t>
+          <t>810831</t>
         </is>
       </c>
       <c r="G122" s="5" t="inlineStr">
@@ -6990,7 +6990,7 @@
       </c>
       <c r="L122" s="5" t="n"/>
       <c r="M122" s="7" t="n">
-        <v>24.52</v>
+        <v>25.13</v>
       </c>
     </row>
     <row r="123">
@@ -7001,7 +7001,7 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437782 - KIT4M058724975J4</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649532 - KIT4M05413808FFZ</t>
         </is>
       </c>
       <c r="C123" s="3" t="n">
@@ -7012,12 +7012,12 @@
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058724975J4</t>
+          <t>KIT4M05413808FFZ</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>816075</t>
+          <t>812828</t>
         </is>
       </c>
       <c r="G123" s="5" t="inlineStr">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="L123" s="5" t="n"/>
       <c r="M123" s="7" t="n">
-        <v>23.88</v>
+        <v>25.11</v>
       </c>
     </row>
     <row r="124">
@@ -7054,7 +7054,7 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827016 - KIT4M041536494G6</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955212 - KIT4M05563512GBQ</t>
         </is>
       </c>
       <c r="C124" s="3" t="n">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>KIT4M041536494G6</t>
+          <t>KIT4M05563512GBQ</t>
         </is>
       </c>
       <c r="F124" s="4" t="inlineStr">
         <is>
-          <t>809617</t>
+          <t>814435</t>
         </is>
       </c>
       <c r="G124" s="5" t="inlineStr">
@@ -7096,7 +7096,7 @@
       </c>
       <c r="L124" s="5" t="n"/>
       <c r="M124" s="7" t="n">
-        <v>23.69</v>
+        <v>24.55</v>
       </c>
     </row>
     <row r="125">
@@ -7107,7 +7107,7 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020650162 - KIT4M05413837SMB</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437782 - KIT4M058724975J4</t>
         </is>
       </c>
       <c r="C125" s="3" t="n">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413837SMB</t>
+          <t>KIT4M058724975J4</t>
         </is>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>810100</t>
+          <t>816075</t>
         </is>
       </c>
       <c r="G125" s="5" t="inlineStr">
@@ -7149,7 +7149,7 @@
       </c>
       <c r="L125" s="5" t="n"/>
       <c r="M125" s="7" t="n">
-        <v>23.32</v>
+        <v>23.92</v>
       </c>
     </row>
     <row r="126">
@@ -7160,7 +7160,7 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649532 - KIT4M05413808FFZ</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438152 - KIT4M05799733FPK</t>
         </is>
       </c>
       <c r="C126" s="3" t="n">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413808FFZ</t>
+          <t>KIT4M05799733FPK</t>
         </is>
       </c>
       <c r="F126" s="4" t="inlineStr">
         <is>
-          <t>812828</t>
+          <t>816286</t>
         </is>
       </c>
       <c r="G126" s="5" t="inlineStr">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="L126" s="5" t="n"/>
       <c r="M126" s="7" t="n">
-        <v>23.03</v>
+        <v>23.9</v>
       </c>
     </row>
     <row r="127">
@@ -7213,7 +7213,7 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020649292-KIT4M05368201SNV</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020650162 - KIT4M05413837SMB</t>
         </is>
       </c>
       <c r="C127" s="3" t="n">
@@ -7224,12 +7224,12 @@
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368201SNV</t>
+          <t>KIT4M05413837SMB</t>
         </is>
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>810651</t>
+          <t>810100</t>
         </is>
       </c>
       <c r="G127" s="5" t="inlineStr">
@@ -7255,7 +7255,7 @@
       </c>
       <c r="L127" s="5" t="n"/>
       <c r="M127" s="7" t="n">
-        <v>22.19</v>
+        <v>23.32</v>
       </c>
     </row>
     <row r="128">
@@ -7308,7 +7308,7 @@
       </c>
       <c r="L128" s="5" t="n"/>
       <c r="M128" s="7" t="n">
-        <v>21.64</v>
+        <v>22.76</v>
       </c>
     </row>
     <row r="129">
@@ -7319,7 +7319,7 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020650132-KIT4M05413828PCT</t>
+          <t>SMRT-05900510-Los Angeles CA-020649292-KIT4M05368201SNV</t>
         </is>
       </c>
       <c r="C129" s="3" t="n">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413828PCT</t>
+          <t>KIT4M05368201SNV</t>
         </is>
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>812799</t>
+          <t>810651</t>
         </is>
       </c>
       <c r="G129" s="5" t="inlineStr">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="L129" s="5" t="n"/>
       <c r="M129" s="7" t="n">
-        <v>21.54</v>
+        <v>22.42</v>
       </c>
     </row>
     <row r="130">
@@ -7372,7 +7372,7 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-LOS ANGELES CA-020955172-KIT4M05563526WNC</t>
+          <t>SMRT-05900510-Los Angeles CA-020650132-KIT4M05413828PCT</t>
         </is>
       </c>
       <c r="C130" s="3" t="n">
@@ -7383,12 +7383,12 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563526WNC</t>
+          <t>KIT4M05413828PCT</t>
         </is>
       </c>
       <c r="F130" s="4" t="inlineStr">
         <is>
-          <t>814463</t>
+          <t>812799</t>
         </is>
       </c>
       <c r="G130" s="5" t="inlineStr">
@@ -7414,7 +7414,7 @@
       </c>
       <c r="L130" s="5" t="n"/>
       <c r="M130" s="7" t="n">
-        <v>21.16</v>
+        <v>21.54</v>
       </c>
     </row>
     <row r="131">
@@ -7425,7 +7425,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020650072-KIT4M054137987GJ</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438002 - KIT4M05799701SGS</t>
         </is>
       </c>
       <c r="C131" s="3" t="n">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137987GJ</t>
+          <t>KIT4M05799701SGS</t>
         </is>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>812795</t>
+          <t>816284</t>
         </is>
       </c>
       <c r="G131" s="5" t="inlineStr">
@@ -7467,7 +7467,7 @@
       </c>
       <c r="L131" s="5" t="n"/>
       <c r="M131" s="7" t="n">
-        <v>20.74</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="132">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438152 - KIT4M05799733FPK</t>
+          <t>SMRT-05900510-LOS ANGELES CA-020955172-KIT4M05563526WNC</t>
         </is>
       </c>
       <c r="C132" s="3" t="n">
@@ -7489,12 +7489,12 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799733FPK</t>
+          <t>KIT4M05563526WNC</t>
         </is>
       </c>
       <c r="F132" s="4" t="inlineStr">
         <is>
-          <t>816286</t>
+          <t>814463</t>
         </is>
       </c>
       <c r="G132" s="5" t="inlineStr">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="L132" s="5" t="n"/>
       <c r="M132" s="7" t="n">
-        <v>20.43</v>
+        <v>21.16</v>
       </c>
     </row>
     <row r="133">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649222 - KIT4P00065640BFW</t>
+          <t>SMRT-05900510-Los Angeles CA-020650072-KIT4M054137987GJ</t>
         </is>
       </c>
       <c r="C133" s="3" t="n">
@@ -7542,17 +7542,17 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065640BFW</t>
+          <t>KIT4M054137987GJ</t>
         </is>
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>812929</t>
+          <t>812795</t>
         </is>
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
@@ -7573,7 +7573,7 @@
       </c>
       <c r="L133" s="5" t="n"/>
       <c r="M133" s="7" t="n">
-        <v>19.87</v>
+        <v>20.74</v>
       </c>
     </row>
     <row r="134">
@@ -7584,7 +7584,7 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649912 - KIT4M05413836KJC</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482701112 - KIT4M04158973M2C</t>
         </is>
       </c>
       <c r="C134" s="3" t="n">
@@ -7595,12 +7595,12 @@
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413836KJC</t>
+          <t>KIT4M04158973M2C</t>
         </is>
       </c>
       <c r="F134" s="4" t="inlineStr">
         <is>
-          <t>810097</t>
+          <t>809610</t>
         </is>
       </c>
       <c r="G134" s="5" t="inlineStr">
@@ -7626,7 +7626,7 @@
       </c>
       <c r="L134" s="5" t="n"/>
       <c r="M134" s="7" t="n">
-        <v>19.73</v>
+        <v>20.16</v>
       </c>
     </row>
     <row r="135">
@@ -7637,7 +7637,7 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020650242 - KIT4M05413804SKS</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649222 - KIT4P00065640BFW</t>
         </is>
       </c>
       <c r="C135" s="3" t="n">
@@ -7648,17 +7648,17 @@
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413804SKS</t>
+          <t>KIT4P00065640BFW</t>
         </is>
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>810102</t>
+          <t>812929</t>
         </is>
       </c>
       <c r="G135" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H135" s="5" t="inlineStr">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="L135" s="5" t="n"/>
       <c r="M135" s="7" t="n">
-        <v>19.67</v>
+        <v>19.87</v>
       </c>
     </row>
     <row r="136">
@@ -7690,7 +7690,7 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438002 - KIT4M05799701SGS</t>
+          <t>SS - 05900510 -  Los Angeles CA - 021437622 - KIT4M0587258755W</t>
         </is>
       </c>
       <c r="C136" s="3" t="n">
@@ -7701,12 +7701,12 @@
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799701SGS</t>
+          <t>KIT4M0587258755W</t>
         </is>
       </c>
       <c r="F136" s="4" t="inlineStr">
         <is>
-          <t>816284</t>
+          <t>816187</t>
         </is>
       </c>
       <c r="G136" s="5" t="inlineStr">
@@ -7732,7 +7732,7 @@
       </c>
       <c r="L136" s="5" t="n"/>
       <c r="M136" s="7" t="n">
-        <v>19.66</v>
+        <v>19.82</v>
       </c>
     </row>
     <row r="137">
@@ -7743,7 +7743,7 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649302 - KIT4M05368226W57</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649912 - KIT4M05413836KJC</t>
         </is>
       </c>
       <c r="C137" s="3" t="n">
@@ -7754,12 +7754,12 @@
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368226W57</t>
+          <t>KIT4M05413836KJC</t>
         </is>
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>810833</t>
+          <t>810097</t>
         </is>
       </c>
       <c r="G137" s="5" t="inlineStr">
@@ -7785,7 +7785,7 @@
       </c>
       <c r="L137" s="5" t="n"/>
       <c r="M137" s="7" t="n">
-        <v>19.62</v>
+        <v>19.73</v>
       </c>
     </row>
     <row r="138">
@@ -7796,7 +7796,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482701112 - KIT4M04158973M2C</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020650242 - KIT4M05413804SKS</t>
         </is>
       </c>
       <c r="C138" s="3" t="n">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158973M2C</t>
+          <t>KIT4M05413804SKS</t>
         </is>
       </c>
       <c r="F138" s="4" t="inlineStr">
         <is>
-          <t>809610</t>
+          <t>810102</t>
         </is>
       </c>
       <c r="G138" s="5" t="inlineStr">
@@ -7838,7 +7838,7 @@
       </c>
       <c r="L138" s="5" t="n"/>
       <c r="M138" s="7" t="n">
-        <v>19.41</v>
+        <v>19.68</v>
       </c>
     </row>
     <row r="139">
@@ -7849,7 +7849,7 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955282 - KIT4M055635227ZR</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649302 - KIT4M05368226W57</t>
         </is>
       </c>
       <c r="C139" s="3" t="n">
@@ -7860,12 +7860,12 @@
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635227ZR</t>
+          <t>KIT4M05368226W57</t>
         </is>
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>814482</t>
+          <t>810833</t>
         </is>
       </c>
       <c r="G139" s="5" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="L139" s="5" t="n"/>
       <c r="M139" s="7" t="n">
-        <v>19.17</v>
+        <v>19.62</v>
       </c>
     </row>
     <row r="140">
@@ -7902,7 +7902,7 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955532 - KIT4M05563548P9Q</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955282 - KIT4M055635227ZR</t>
         </is>
       </c>
       <c r="C140" s="3" t="n">
@@ -7913,12 +7913,12 @@
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563548P9Q</t>
+          <t>KIT4M055635227ZR</t>
         </is>
       </c>
       <c r="F140" s="4" t="inlineStr">
         <is>
-          <t>814468</t>
+          <t>814482</t>
         </is>
       </c>
       <c r="G140" s="5" t="inlineStr">
@@ -7944,7 +7944,7 @@
       </c>
       <c r="L140" s="5" t="n"/>
       <c r="M140" s="7" t="n">
-        <v>19.15</v>
+        <v>19.17</v>
       </c>
     </row>
     <row r="141">
@@ -7955,7 +7955,7 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955302 - KIT4M055635158PC</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955532 - KIT4M05563548P9Q</t>
         </is>
       </c>
       <c r="C141" s="3" t="n">
@@ -7966,12 +7966,12 @@
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635158PC</t>
+          <t>KIT4M05563548P9Q</t>
         </is>
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>814457</t>
+          <t>814468</t>
         </is>
       </c>
       <c r="G141" s="5" t="inlineStr">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="L141" s="5" t="n"/>
       <c r="M141" s="7" t="n">
-        <v>18.73</v>
+        <v>19.15</v>
       </c>
     </row>
     <row r="142">
@@ -8008,7 +8008,7 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA  - 020649722 - KIT4M04604747TPT</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955302 - KIT4M055635158PC</t>
         </is>
       </c>
       <c r="C142" s="3" t="n">
@@ -8019,12 +8019,12 @@
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604747TPT</t>
+          <t>KIT4M055635158PC</t>
         </is>
       </c>
       <c r="F142" s="4" t="inlineStr">
         <is>
-          <t>809873</t>
+          <t>814457</t>
         </is>
       </c>
       <c r="G142" s="5" t="inlineStr">
@@ -8050,7 +8050,7 @@
       </c>
       <c r="L142" s="5" t="n"/>
       <c r="M142" s="7" t="n">
-        <v>18.44</v>
+        <v>18.73</v>
       </c>
     </row>
     <row r="143">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649632 - KIT4M054138064J9</t>
+          <t>SS - 05900510 - Los Angeles, CA  - 020649722 - KIT4M04604747TPT</t>
         </is>
       </c>
       <c r="C143" s="3" t="n">
@@ -8072,12 +8072,12 @@
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138064J9</t>
+          <t>KIT4M04604747TPT</t>
         </is>
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>812844</t>
+          <t>809873</t>
         </is>
       </c>
       <c r="G143" s="5" t="inlineStr">
@@ -8103,7 +8103,7 @@
       </c>
       <c r="L143" s="5" t="n"/>
       <c r="M143" s="7" t="n">
-        <v>16.19</v>
+        <v>18.44</v>
       </c>
     </row>
     <row r="144">
@@ -8114,7 +8114,7 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649592 - KIT4M05413787HHK</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649212 - KIT4P00065633ZXC</t>
         </is>
       </c>
       <c r="C144" s="3" t="n">
@@ -8125,17 +8125,17 @@
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413787HHK</t>
+          <t>KIT4P00065633ZXC</t>
         </is>
       </c>
       <c r="F144" s="4" t="inlineStr">
         <is>
-          <t>812809</t>
+          <t>812922</t>
         </is>
       </c>
       <c r="G144" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H144" s="5" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="L144" s="5" t="n"/>
       <c r="M144" s="7" t="n">
-        <v>15.65</v>
+        <v>18.09</v>
       </c>
     </row>
     <row r="145">
@@ -8167,7 +8167,7 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 021437622 - KIT4M0587258755W</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649632 - KIT4M054138064J9</t>
         </is>
       </c>
       <c r="C145" s="3" t="n">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0587258755W</t>
+          <t>KIT4M054138064J9</t>
         </is>
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>816187</t>
+          <t>812844</t>
         </is>
       </c>
       <c r="G145" s="5" t="inlineStr">
@@ -8209,7 +8209,7 @@
       </c>
       <c r="L145" s="5" t="n"/>
       <c r="M145" s="7" t="n">
-        <v>15.61</v>
+        <v>17.18</v>
       </c>
     </row>
     <row r="146">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482708 - KIT4M04604736T7C</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649592 - KIT4M05413787HHK</t>
         </is>
       </c>
       <c r="C146" s="3" t="n">
@@ -8231,12 +8231,12 @@
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604736T7C</t>
+          <t>KIT4M05413787HHK</t>
         </is>
       </c>
       <c r="F146" s="4" t="inlineStr">
         <is>
-          <t>809662</t>
+          <t>812809</t>
         </is>
       </c>
       <c r="G146" s="5" t="inlineStr">
@@ -8262,7 +8262,7 @@
       </c>
       <c r="L146" s="5" t="n"/>
       <c r="M146" s="7" t="n">
-        <v>15.25</v>
+        <v>15.65</v>
       </c>
     </row>
     <row r="147">
@@ -8273,7 +8273,7 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955712 - KIT4M05563586ZTR</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482708 - KIT4M04604736T7C</t>
         </is>
       </c>
       <c r="C147" s="3" t="n">
@@ -8284,12 +8284,12 @@
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563586ZTR</t>
+          <t>KIT4M04604736T7C</t>
         </is>
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>814445</t>
+          <t>809662</t>
         </is>
       </c>
       <c r="G147" s="5" t="inlineStr">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="L147" s="5" t="n"/>
       <c r="M147" s="7" t="n">
-        <v>14.65</v>
+        <v>15.55</v>
       </c>
     </row>
     <row r="148">
@@ -8326,7 +8326,7 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020649862 - KIT4M04475159PMD</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649452 - KIT4M05413785QCG</t>
         </is>
       </c>
       <c r="C148" s="3" t="n">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475159PMD</t>
+          <t>KIT4M05413785QCG</t>
         </is>
       </c>
       <c r="F148" s="4" t="inlineStr">
         <is>
-          <t>809868</t>
+          <t>812806</t>
         </is>
       </c>
       <c r="G148" s="5" t="inlineStr">
@@ -8368,7 +8368,7 @@
       </c>
       <c r="L148" s="5" t="n"/>
       <c r="M148" s="7" t="n">
-        <v>14.45</v>
+        <v>15.38</v>
       </c>
     </row>
     <row r="149">
@@ -8379,7 +8379,7 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - CW6642812 - KIT4M054138292ZP</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955712 - KIT4M05563586ZTR</t>
         </is>
       </c>
       <c r="C149" s="3" t="n">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138292ZP</t>
+          <t>KIT4M05563586ZTR</t>
         </is>
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>812784</t>
+          <t>814445</t>
         </is>
       </c>
       <c r="G149" s="5" t="inlineStr">
@@ -8421,7 +8421,7 @@
       </c>
       <c r="L149" s="5" t="n"/>
       <c r="M149" s="7" t="n">
-        <v>14.37</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="150">
@@ -8432,7 +8432,7 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649442 - KIT4M054137885SM</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438222 - KIT4M058725299QP</t>
         </is>
       </c>
       <c r="C150" s="3" t="n">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137885SM</t>
+          <t>KIT4M058725299QP</t>
         </is>
       </c>
       <c r="F150" s="4" t="inlineStr">
         <is>
-          <t>812846</t>
+          <t>816080</t>
         </is>
       </c>
       <c r="G150" s="5" t="inlineStr">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="L150" s="5" t="n"/>
       <c r="M150" s="7" t="n">
-        <v>13.24</v>
+        <v>14.51</v>
       </c>
     </row>
     <row r="151">
@@ -8485,7 +8485,7 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438222 - KIT4M058725299QP</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020649862 - KIT4M04475159PMD</t>
         </is>
       </c>
       <c r="C151" s="3" t="n">
@@ -8496,12 +8496,12 @@
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725299QP</t>
+          <t>KIT4M04475159PMD</t>
         </is>
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>816080</t>
+          <t>809868</t>
         </is>
       </c>
       <c r="G151" s="5" t="inlineStr">
@@ -8527,7 +8527,7 @@
       </c>
       <c r="L151" s="5" t="n"/>
       <c r="M151" s="7" t="n">
-        <v>13.21</v>
+        <v>14.45</v>
       </c>
     </row>
     <row r="152">
@@ -8538,7 +8538,7 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955362 - KIT4M05563528MKX</t>
+          <t>SMA - 05900510 - Los Angeles CA - CW6642812 - KIT4M054138292ZP</t>
         </is>
       </c>
       <c r="C152" s="3" t="n">
@@ -8549,12 +8549,12 @@
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563528MKX</t>
+          <t>KIT4M054138292ZP</t>
         </is>
       </c>
       <c r="F152" s="4" t="inlineStr">
         <is>
-          <t>814471</t>
+          <t>812784</t>
         </is>
       </c>
       <c r="G152" s="5" t="inlineStr">
@@ -8580,7 +8580,7 @@
       </c>
       <c r="L152" s="5" t="n"/>
       <c r="M152" s="7" t="n">
-        <v>12.64</v>
+        <v>14.37</v>
       </c>
     </row>
     <row r="153">
@@ -8591,7 +8591,7 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 -  Los Angeles CA - 020649512 - KIT4M054138318Q7</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437992 -  KIT4M05799663CPM</t>
         </is>
       </c>
       <c r="C153" s="3" t="n">
@@ -8602,12 +8602,12 @@
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138318Q7</t>
+          <t>KIT4M05799663CPM</t>
         </is>
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>812814</t>
+          <t>816272</t>
         </is>
       </c>
       <c r="G153" s="5" t="inlineStr">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="L153" s="5" t="n"/>
       <c r="M153" s="7" t="n">
-        <v>12.45</v>
+        <v>14.19</v>
       </c>
     </row>
     <row r="154">
@@ -8686,7 +8686,7 @@
       </c>
       <c r="L154" s="5" t="n"/>
       <c r="M154" s="7" t="n">
-        <v>12.19</v>
+        <v>13.64</v>
       </c>
     </row>
     <row r="155">
@@ -8697,7 +8697,7 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020650152 - KIT4M054138189C7</t>
+          <t>SMA - 05900510 -  Los Angeles CA - 020649512 - KIT4M054138318Q7</t>
         </is>
       </c>
       <c r="C155" s="3" t="n">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138189C7</t>
+          <t>KIT4M054138318Q7</t>
         </is>
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>812831</t>
+          <t>812814</t>
         </is>
       </c>
       <c r="G155" s="5" t="inlineStr">
@@ -8739,7 +8739,7 @@
       </c>
       <c r="L155" s="5" t="n"/>
       <c r="M155" s="7" t="n">
-        <v>11.19</v>
+        <v>13.51</v>
       </c>
     </row>
     <row r="156">
@@ -8750,7 +8750,7 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 020955242 - KIT4M05563511FF4</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649442 - KIT4M054137885SM</t>
         </is>
       </c>
       <c r="C156" s="3" t="n">
@@ -8761,12 +8761,12 @@
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563511FF4</t>
+          <t>KIT4M054137885SM</t>
         </is>
       </c>
       <c r="F156" s="4" t="inlineStr">
         <is>
-          <t>814437</t>
+          <t>812846</t>
         </is>
       </c>
       <c r="G156" s="5" t="inlineStr">
@@ -8792,7 +8792,7 @@
       </c>
       <c r="L156" s="5" t="n"/>
       <c r="M156" s="7" t="n">
-        <v>10.96</v>
+        <v>13.24</v>
       </c>
     </row>
     <row r="157">
@@ -8803,7 +8803,7 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955482 - KIT4M055635088NK</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955362 - KIT4M05563528MKX</t>
         </is>
       </c>
       <c r="C157" s="3" t="n">
@@ -8814,12 +8814,12 @@
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635088NK</t>
+          <t>KIT4M05563528MKX</t>
         </is>
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>814434</t>
+          <t>814471</t>
         </is>
       </c>
       <c r="G157" s="5" t="inlineStr">
@@ -8845,7 +8845,7 @@
       </c>
       <c r="L157" s="5" t="n"/>
       <c r="M157" s="7" t="n">
-        <v>10.9</v>
+        <v>12.81</v>
       </c>
     </row>
     <row r="158">
@@ -8856,7 +8856,7 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437992 -  KIT4M05799663CPM</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649832 - KIT4M03866596RZG</t>
         </is>
       </c>
       <c r="C158" s="3" t="n">
@@ -8867,12 +8867,12 @@
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799663CPM</t>
+          <t>KIT4M03866596RZG</t>
         </is>
       </c>
       <c r="F158" s="4" t="inlineStr">
         <is>
-          <t>816272</t>
+          <t>809869</t>
         </is>
       </c>
       <c r="G158" s="5" t="inlineStr">
@@ -8898,7 +8898,7 @@
       </c>
       <c r="L158" s="5" t="n"/>
       <c r="M158" s="7" t="n">
-        <v>10.82</v>
+        <v>12.21</v>
       </c>
     </row>
     <row r="159">
@@ -8909,7 +8909,7 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649582 - KIT4M05413774JZX</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955402 - KIT4M05563610HM2</t>
         </is>
       </c>
       <c r="C159" s="3" t="n">
@@ -8920,12 +8920,12 @@
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413774JZX</t>
+          <t>KIT4M05563610HM2</t>
         </is>
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>812836</t>
+          <t>814486</t>
         </is>
       </c>
       <c r="G159" s="5" t="inlineStr">
@@ -8951,7 +8951,7 @@
       </c>
       <c r="L159" s="5" t="n"/>
       <c r="M159" s="7" t="n">
-        <v>10.42</v>
+        <v>11.39</v>
       </c>
     </row>
     <row r="160">
@@ -8962,7 +8962,7 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649452 - KIT4M05413785QCG</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955482 - KIT4M055635088NK</t>
         </is>
       </c>
       <c r="C160" s="3" t="n">
@@ -8973,12 +8973,12 @@
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413785QCG</t>
+          <t>KIT4M055635088NK</t>
         </is>
       </c>
       <c r="F160" s="4" t="inlineStr">
         <is>
-          <t>812806</t>
+          <t>814434</t>
         </is>
       </c>
       <c r="G160" s="5" t="inlineStr">
@@ -9004,7 +9004,7 @@
       </c>
       <c r="L160" s="5" t="n"/>
       <c r="M160" s="7" t="n">
-        <v>10.23</v>
+        <v>11.33</v>
       </c>
     </row>
     <row r="161">
@@ -9015,7 +9015,7 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955402 - KIT4M05563610HM2</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438242 - KIT4M058725094XP</t>
         </is>
       </c>
       <c r="C161" s="3" t="n">
@@ -9026,12 +9026,12 @@
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563610HM2</t>
+          <t>KIT4M058725094XP</t>
         </is>
       </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
-          <t>814486</t>
+          <t>816085</t>
         </is>
       </c>
       <c r="G161" s="5" t="inlineStr">
@@ -9057,7 +9057,7 @@
       </c>
       <c r="L161" s="5" t="n"/>
       <c r="M161" s="7" t="n">
-        <v>9.75</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="162">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649832 - KIT4M03866596RZG</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020650152 - KIT4M054138189C7</t>
         </is>
       </c>
       <c r="C162" s="3" t="n">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03866596RZG</t>
+          <t>KIT4M054138189C7</t>
         </is>
       </c>
       <c r="F162" s="4" t="inlineStr">
         <is>
-          <t>809869</t>
+          <t>812831</t>
         </is>
       </c>
       <c r="G162" s="5" t="inlineStr">
@@ -9110,7 +9110,7 @@
       </c>
       <c r="L162" s="5" t="n"/>
       <c r="M162" s="7" t="n">
-        <v>9.68</v>
+        <v>11.19</v>
       </c>
     </row>
     <row r="163">
@@ -9121,7 +9121,7 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649322 - KIT4M053683324KZ</t>
+          <t>SS - 05900510 -  Los Angeles CA - 020955242 - KIT4M05563511FF4</t>
         </is>
       </c>
       <c r="C163" s="3" t="n">
@@ -9132,12 +9132,12 @@
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>KIT4M053683324KZ</t>
+          <t>KIT4M05563511FF4</t>
         </is>
       </c>
       <c r="F163" s="4" t="inlineStr">
         <is>
-          <t>810832</t>
+          <t>814437</t>
         </is>
       </c>
       <c r="G163" s="5" t="inlineStr">
@@ -9163,7 +9163,7 @@
       </c>
       <c r="L163" s="5" t="n"/>
       <c r="M163" s="7" t="n">
-        <v>9.460000000000001</v>
+        <v>10.96</v>
       </c>
     </row>
     <row r="164">
@@ -9174,7 +9174,7 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020650122-KIT4M05413776H84</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649582 - KIT4M05413774JZX</t>
         </is>
       </c>
       <c r="C164" s="3" t="n">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413776H84</t>
+          <t>KIT4M05413774JZX</t>
         </is>
       </c>
       <c r="F164" s="4" t="inlineStr">
         <is>
-          <t>810101</t>
+          <t>812836</t>
         </is>
       </c>
       <c r="G164" s="5" t="inlineStr">
@@ -9216,7 +9216,7 @@
       </c>
       <c r="L164" s="5" t="n"/>
       <c r="M164" s="7" t="n">
-        <v>9.41</v>
+        <v>10.42</v>
       </c>
     </row>
     <row r="165">
@@ -9227,7 +9227,7 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649282 - KIT4M05368213974</t>
+          <t>SMRT-05900510-Los Angeles CA-020650122-KIT4M05413776H84</t>
         </is>
       </c>
       <c r="C165" s="3" t="n">
@@ -9238,12 +9238,12 @@
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368213974</t>
+          <t>KIT4M05413776H84</t>
         </is>
       </c>
       <c r="F165" s="4" t="inlineStr">
         <is>
-          <t>810647</t>
+          <t>810101</t>
         </is>
       </c>
       <c r="G165" s="5" t="inlineStr">
@@ -9269,7 +9269,7 @@
       </c>
       <c r="L165" s="5" t="n"/>
       <c r="M165" s="7" t="n">
-        <v>9.18</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="166">
@@ -9280,7 +9280,7 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955612 - KIT4M0556355588P</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955152 - KIT4M05563514P8T</t>
         </is>
       </c>
       <c r="C166" s="3" t="n">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0556355588P</t>
+          <t>KIT4M05563514P8T</t>
         </is>
       </c>
       <c r="F166" s="4" t="inlineStr">
         <is>
-          <t>814455</t>
+          <t>814436</t>
         </is>
       </c>
       <c r="G166" s="5" t="inlineStr">
@@ -9322,7 +9322,7 @@
       </c>
       <c r="L166" s="5" t="n"/>
       <c r="M166" s="7" t="n">
-        <v>9.140000000000001</v>
+        <v>9.73</v>
       </c>
     </row>
     <row r="167">
@@ -9333,7 +9333,7 @@
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020955432 - KIT4M05563533M9N</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649322 - KIT4M053683324KZ</t>
         </is>
       </c>
       <c r="C167" s="3" t="n">
@@ -9344,12 +9344,12 @@
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563533M9N</t>
+          <t>KIT4M053683324KZ</t>
         </is>
       </c>
       <c r="F167" s="4" t="inlineStr">
         <is>
-          <t>814485</t>
+          <t>810832</t>
         </is>
       </c>
       <c r="G167" s="5" t="inlineStr">
@@ -9375,7 +9375,7 @@
       </c>
       <c r="L167" s="5" t="n"/>
       <c r="M167" s="7" t="n">
-        <v>9.01</v>
+        <v>9.710000000000001</v>
       </c>
     </row>
     <row r="168">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955502 - KIT4M05563502GJS</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020955432 - KIT4M05563533M9N</t>
         </is>
       </c>
       <c r="C168" s="3" t="n">
@@ -9397,12 +9397,12 @@
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563502GJS</t>
+          <t>KIT4M05563533M9N</t>
         </is>
       </c>
       <c r="F168" s="4" t="inlineStr">
         <is>
-          <t>814470</t>
+          <t>814485</t>
         </is>
       </c>
       <c r="G168" s="5" t="inlineStr">
@@ -9428,7 +9428,7 @@
       </c>
       <c r="L168" s="5" t="n"/>
       <c r="M168" s="7" t="n">
-        <v>8.869999999999999</v>
+        <v>9.470000000000001</v>
       </c>
     </row>
     <row r="169">
@@ -9439,7 +9439,7 @@
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955252 - KIT4M05563584FVC</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649282 - KIT4M05368213974</t>
         </is>
       </c>
       <c r="C169" s="3" t="n">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563584FVC</t>
+          <t>KIT4M05368213974</t>
         </is>
       </c>
       <c r="F169" s="4" t="inlineStr">
         <is>
-          <t>814439</t>
+          <t>810647</t>
         </is>
       </c>
       <c r="G169" s="5" t="inlineStr">
@@ -9481,7 +9481,7 @@
       </c>
       <c r="L169" s="5" t="n"/>
       <c r="M169" s="7" t="n">
-        <v>8.75</v>
+        <v>9.18</v>
       </c>
     </row>
     <row r="170">
@@ -9492,7 +9492,7 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438242 - KIT4M058725094XP</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955612 - KIT4M0556355588P</t>
         </is>
       </c>
       <c r="C170" s="3" t="n">
@@ -9503,12 +9503,12 @@
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725094XP</t>
+          <t>KIT4M0556355588P</t>
         </is>
       </c>
       <c r="F170" s="4" t="inlineStr">
         <is>
-          <t>816085</t>
+          <t>814455</t>
         </is>
       </c>
       <c r="G170" s="5" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="L170" s="5" t="n"/>
       <c r="M170" s="7" t="n">
-        <v>7.88</v>
+        <v>9.140000000000001</v>
       </c>
     </row>
     <row r="171">
@@ -9545,7 +9545,7 @@
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020649252 - KIT4P00066848VQM</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955502 - KIT4M05563502GJS</t>
         </is>
       </c>
       <c r="C171" s="3" t="n">
@@ -9556,17 +9556,17 @@
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00066848VQM</t>
+          <t>KIT4M05563502GJS</t>
         </is>
       </c>
       <c r="F171" s="4" t="inlineStr">
         <is>
-          <t>812923</t>
+          <t>814470</t>
         </is>
       </c>
       <c r="G171" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H171" s="5" t="inlineStr">
@@ -9587,7 +9587,7 @@
       </c>
       <c r="L171" s="5" t="n"/>
       <c r="M171" s="7" t="n">
-        <v>7.27</v>
+        <v>8.869999999999999</v>
       </c>
     </row>
     <row r="172">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827010 - KIT4M046047372KJ</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955252 - KIT4M05563584FVC</t>
         </is>
       </c>
       <c r="C172" s="3" t="n">
@@ -9609,12 +9609,12 @@
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047372KJ</t>
+          <t>KIT4M05563584FVC</t>
         </is>
       </c>
       <c r="F172" s="4" t="inlineStr">
         <is>
-          <t>809658</t>
+          <t>814439</t>
         </is>
       </c>
       <c r="G172" s="5" t="inlineStr">
@@ -9640,7 +9640,7 @@
       </c>
       <c r="L172" s="5" t="n"/>
       <c r="M172" s="7" t="n">
-        <v>7.23</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="173">
@@ -9651,7 +9651,7 @@
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649792 - KIT4M04475151HTP</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020650262 - KIT4M054138249M8</t>
         </is>
       </c>
       <c r="C173" s="3" t="n">
@@ -9662,12 +9662,12 @@
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475151HTP</t>
+          <t>KIT4M054138249M8</t>
         </is>
       </c>
       <c r="F173" s="4" t="inlineStr">
         <is>
-          <t>809867</t>
+          <t>812794</t>
         </is>
       </c>
       <c r="G173" s="5" t="inlineStr">
@@ -9693,7 +9693,7 @@
       </c>
       <c r="L173" s="5" t="n"/>
       <c r="M173" s="7" t="n">
-        <v>7.08</v>
+        <v>8.26</v>
       </c>
     </row>
     <row r="174">
@@ -9704,7 +9704,7 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649212 - KIT4P00065633ZXC</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020649252 - KIT4P00066848VQM</t>
         </is>
       </c>
       <c r="C174" s="3" t="n">
@@ -9715,12 +9715,12 @@
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065633ZXC</t>
+          <t>KIT4P00066848VQM</t>
         </is>
       </c>
       <c r="F174" s="4" t="inlineStr">
         <is>
-          <t>812922</t>
+          <t>812923</t>
         </is>
       </c>
       <c r="G174" s="5" t="inlineStr">
@@ -9746,7 +9746,7 @@
       </c>
       <c r="L174" s="5" t="n"/>
       <c r="M174" s="7" t="n">
-        <v>7.04</v>
+        <v>7.27</v>
       </c>
     </row>
     <row r="175">
@@ -9757,7 +9757,7 @@
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020650262 - KIT4M054138249M8</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649822 - KIT4M04604740BM6</t>
         </is>
       </c>
       <c r="C175" s="3" t="n">
@@ -9768,12 +9768,12 @@
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138249M8</t>
+          <t>KIT4M04604740BM6</t>
         </is>
       </c>
       <c r="F175" s="4" t="inlineStr">
         <is>
-          <t>812794</t>
+          <t>809872</t>
         </is>
       </c>
       <c r="G175" s="5" t="inlineStr">
@@ -9799,7 +9799,7 @@
       </c>
       <c r="L175" s="5" t="n"/>
       <c r="M175" s="7" t="n">
-        <v>6.98</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="176">
@@ -9810,7 +9810,7 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649822 - KIT4M04604740BM6</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827010 - KIT4M046047372KJ</t>
         </is>
       </c>
       <c r="C176" s="3" t="n">
@@ -9821,12 +9821,12 @@
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604740BM6</t>
+          <t>KIT4M046047372KJ</t>
         </is>
       </c>
       <c r="F176" s="4" t="inlineStr">
         <is>
-          <t>809872</t>
+          <t>809658</t>
         </is>
       </c>
       <c r="G176" s="5" t="inlineStr">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="L176" s="5" t="n"/>
       <c r="M176" s="7" t="n">
-        <v>6.45</v>
+        <v>7.23</v>
       </c>
     </row>
     <row r="177">
@@ -9863,7 +9863,7 @@
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles, CA - 0204827011114 - KIT4M03986267RWH</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649792 - KIT4M04475151HTP</t>
         </is>
       </c>
       <c r="C177" s="3" t="n">
@@ -9874,12 +9874,12 @@
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03986267RWH</t>
+          <t>KIT4M04475151HTP</t>
         </is>
       </c>
       <c r="F177" s="4" t="inlineStr">
         <is>
-          <t>809616</t>
+          <t>809867</t>
         </is>
       </c>
       <c r="G177" s="5" t="inlineStr">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="L177" s="5" t="n"/>
       <c r="M177" s="7" t="n">
-        <v>6.01</v>
+        <v>7.08</v>
       </c>
     </row>
     <row r="178">
@@ -9916,7 +9916,7 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649642 - KIT4M05413826Z6Z</t>
+          <t>STS - 05900510 - Los Angeles, CA - 0204827011114 - KIT4M03986267RWH</t>
         </is>
       </c>
       <c r="C178" s="3" t="n">
@@ -9927,12 +9927,12 @@
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413826Z6Z</t>
+          <t>KIT4M03986267RWH</t>
         </is>
       </c>
       <c r="F178" s="4" t="inlineStr">
         <is>
-          <t>812804</t>
+          <t>809616</t>
         </is>
       </c>
       <c r="G178" s="5" t="inlineStr">
@@ -9958,7 +9958,7 @@
       </c>
       <c r="L178" s="5" t="n"/>
       <c r="M178" s="7" t="n">
-        <v>5.9</v>
+        <v>6.07</v>
       </c>
     </row>
     <row r="179">
@@ -9969,7 +9969,7 @@
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827011110 - KIT4M03866627GHD</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649642 - KIT4M05413826Z6Z</t>
         </is>
       </c>
       <c r="C179" s="3" t="n">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03866627GHD</t>
+          <t>KIT4M05413826Z6Z</t>
         </is>
       </c>
       <c r="F179" s="4" t="inlineStr">
         <is>
-          <t>809619</t>
+          <t>812804</t>
         </is>
       </c>
       <c r="G179" s="5" t="inlineStr">
@@ -10011,7 +10011,7 @@
       </c>
       <c r="L179" s="5" t="n"/>
       <c r="M179" s="7" t="n">
-        <v>5.78</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="180">
@@ -10022,7 +10022,7 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020650182 - KIT4M05413821GGW</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827011110 - KIT4M03866627GHD</t>
         </is>
       </c>
       <c r="C180" s="3" t="n">
@@ -10033,12 +10033,12 @@
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413821GGW</t>
+          <t>KIT4M03866627GHD</t>
         </is>
       </c>
       <c r="F180" s="4" t="inlineStr">
         <is>
-          <t>812830</t>
+          <t>809619</t>
         </is>
       </c>
       <c r="G180" s="5" t="inlineStr">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="L180" s="5" t="n"/>
       <c r="M180" s="7" t="n">
-        <v>5.51</v>
+        <v>5.78</v>
       </c>
     </row>
     <row r="181">
@@ -10075,7 +10075,7 @@
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955152 - KIT4M05563514P8T</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020650182 - KIT4M05413821GGW</t>
         </is>
       </c>
       <c r="C181" s="3" t="n">
@@ -10086,12 +10086,12 @@
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563514P8T</t>
+          <t>KIT4M05413821GGW</t>
         </is>
       </c>
       <c r="F181" s="4" t="inlineStr">
         <is>
-          <t>814436</t>
+          <t>812830</t>
         </is>
       </c>
       <c r="G181" s="5" t="inlineStr">
@@ -10117,7 +10117,7 @@
       </c>
       <c r="L181" s="5" t="n"/>
       <c r="M181" s="7" t="n">
-        <v>4.85</v>
+        <v>5.51</v>
       </c>
     </row>
     <row r="182">
@@ -10393,7 +10393,7 @@
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437932 - KIT4M05799732NQK</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270114 - KIT4M04476539RJ5</t>
         </is>
       </c>
       <c r="C187" s="3" t="n">
@@ -10404,12 +10404,12 @@
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799732NQK</t>
+          <t>KIT4M04476539RJ5</t>
         </is>
       </c>
       <c r="F187" s="4" t="inlineStr">
         <is>
-          <t>816275</t>
+          <t>809612</t>
         </is>
       </c>
       <c r="G187" s="5" t="inlineStr">
@@ -10435,7 +10435,7 @@
       </c>
       <c r="L187" s="5" t="n"/>
       <c r="M187" s="7" t="n">
-        <v>2.48</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="188">
@@ -10446,7 +10446,7 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270110 - KIT4M038677586ZX</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437932 - KIT4M05799732NQK</t>
         </is>
       </c>
       <c r="C188" s="3" t="n">
@@ -10457,12 +10457,12 @@
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>KIT4M038677586ZX</t>
+          <t>KIT4M05799732NQK</t>
         </is>
       </c>
       <c r="F188" s="4" t="inlineStr">
         <is>
-          <t>809623</t>
+          <t>816275</t>
         </is>
       </c>
       <c r="G188" s="5" t="inlineStr">
@@ -10488,7 +10488,7 @@
       </c>
       <c r="L188" s="5" t="n"/>
       <c r="M188" s="7" t="n">
-        <v>1.59</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="189">
@@ -10499,7 +10499,7 @@
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437612 - KIT4M058725265DP</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270110 - KIT4M038677586ZX</t>
         </is>
       </c>
       <c r="C189" s="3" t="n">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725265DP</t>
+          <t>KIT4M038677586ZX</t>
         </is>
       </c>
       <c r="F189" s="4" t="inlineStr">
         <is>
-          <t>816192</t>
+          <t>809623</t>
         </is>
       </c>
       <c r="G189" s="5" t="inlineStr">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="L189" s="5" t="n"/>
       <c r="M189" s="7" t="n">
-        <v>1.58</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="190">
@@ -10552,7 +10552,7 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270114 - KIT4M04476539RJ5</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437612 - KIT4M058725265DP</t>
         </is>
       </c>
       <c r="C190" s="3" t="n">
@@ -10563,12 +10563,12 @@
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04476539RJ5</t>
+          <t>KIT4M058725265DP</t>
         </is>
       </c>
       <c r="F190" s="4" t="inlineStr">
         <is>
-          <t>809612</t>
+          <t>816192</t>
         </is>
       </c>
       <c r="G190" s="5" t="inlineStr">
@@ -10594,7 +10594,7 @@
       </c>
       <c r="L190" s="5" t="n"/>
       <c r="M190" s="7" t="n">
-        <v>1.43</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="191">
@@ -20113,7 +20113,7 @@
     <row r="379">
       <c r="A379" s="15" t="inlineStr">
         <is>
-          <t>Generated 2026-08-26 20:04 by build_starlink_usage.py</t>
+          <t>Generated 2026-08-27 07:09 by build_starlink_usage.py</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_Current_by_Kit.xlsx
+++ b/Starlink_Usage_Current_by_Kit.xlsx
@@ -20113,7 +20113,7 @@
     <row r="379">
       <c r="A379" s="15" t="inlineStr">
         <is>
-          <t>Generated 2026-08-27 07:09 by build_starlink_usage.py</t>
+          <t>Generated 2026-08-27 07:26 by build_starlink_usage.py</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_Current_by_Kit.xlsx
+++ b/Starlink_Usage_Current_by_Kit.xlsx
@@ -630,7 +630,7 @@
       </c>
       <c r="L2" s="5" t="n"/>
       <c r="M2" s="7" t="n">
-        <v>2458.61</v>
+        <v>2460.32</v>
       </c>
     </row>
     <row r="3">
@@ -683,7 +683,7 @@
       </c>
       <c r="L3" s="5" t="n"/>
       <c r="M3" s="7" t="n">
-        <v>2261.65</v>
+        <v>2261.72</v>
       </c>
     </row>
     <row r="4">
@@ -736,7 +736,7 @@
       </c>
       <c r="L4" s="5" t="n"/>
       <c r="M4" s="7" t="n">
-        <v>1627.8</v>
+        <v>1627.96</v>
       </c>
     </row>
     <row r="5">
@@ -789,7 +789,7 @@
       </c>
       <c r="L5" s="5" t="n"/>
       <c r="M5" s="7" t="n">
-        <v>1288.24</v>
+        <v>1290.21</v>
       </c>
     </row>
     <row r="6">
@@ -842,7 +842,7 @@
       </c>
       <c r="L6" s="5" t="n"/>
       <c r="M6" s="7" t="n">
-        <v>1070.88</v>
+        <v>1070.89</v>
       </c>
     </row>
     <row r="7">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="L10" s="5" t="n"/>
       <c r="M10" s="7" t="n">
-        <v>757.27</v>
+        <v>769.48</v>
       </c>
     </row>
     <row r="11">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="L12" s="5" t="n"/>
       <c r="M12" s="7" t="n">
-        <v>700.64</v>
+        <v>701.09</v>
       </c>
     </row>
     <row r="13">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="L13" s="5" t="n"/>
       <c r="M13" s="7" t="n">
-        <v>691.6</v>
+        <v>691.67</v>
       </c>
     </row>
     <row r="14">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L14" s="5" t="n"/>
       <c r="M14" s="7" t="n">
-        <v>681.27</v>
+        <v>687.1799999999999</v>
       </c>
     </row>
     <row r="15">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="L15" s="5" t="n"/>
       <c r="M15" s="7" t="n">
-        <v>628.38</v>
+        <v>628.88</v>
       </c>
     </row>
     <row r="16">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="L16" s="5" t="n"/>
       <c r="M16" s="7" t="n">
-        <v>619.1</v>
+        <v>619.17</v>
       </c>
     </row>
     <row r="17">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="L20" s="5" t="n"/>
       <c r="M20" s="7" t="n">
-        <v>414.64</v>
+        <v>414.68</v>
       </c>
     </row>
     <row r="21">
@@ -2326,7 +2326,7 @@
       </c>
       <c r="L34" s="5" t="n"/>
       <c r="M34" s="7" t="n">
-        <v>171.73</v>
+        <v>172.41</v>
       </c>
     </row>
     <row r="35">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="L35" s="5" t="n"/>
       <c r="M35" s="7" t="n">
-        <v>147.51</v>
+        <v>147.6</v>
       </c>
     </row>
     <row r="36">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="L36" s="5" t="n"/>
       <c r="M36" s="7" t="n">
-        <v>136.23</v>
+        <v>136.33</v>
       </c>
     </row>
     <row r="37">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="L41" s="5" t="n"/>
       <c r="M41" s="7" t="n">
-        <v>120.19</v>
+        <v>120.24</v>
       </c>
     </row>
     <row r="42">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="L43" s="5" t="n"/>
       <c r="M43" s="7" t="n">
-        <v>111.17</v>
+        <v>111.2</v>
       </c>
     </row>
     <row r="44">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="L47" s="5" t="n"/>
       <c r="M47" s="7" t="n">
-        <v>98.8</v>
+        <v>98.88</v>
       </c>
     </row>
     <row r="48">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="L54" s="5" t="n"/>
       <c r="M54" s="7" t="n">
-        <v>92.17</v>
+        <v>92.39</v>
       </c>
     </row>
     <row r="55">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955472 - KIT4M055635834N7</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955662 - KIT4M05563574ZBN</t>
         </is>
       </c>
       <c r="C55" s="3" t="n">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635834N7</t>
+          <t>KIT4M05563574ZBN</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>814462</t>
+          <t>814453</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="L55" s="5" t="n"/>
       <c r="M55" s="7" t="n">
-        <v>86.98</v>
+        <v>87.36</v>
       </c>
     </row>
     <row r="56">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955662 - KIT4M05563574ZBN</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955472 - KIT4M055635834N7</t>
         </is>
       </c>
       <c r="C56" s="3" t="n">
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563574ZBN</t>
+          <t>KIT4M055635834N7</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>814453</t>
+          <t>814462</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="L56" s="5" t="n"/>
       <c r="M56" s="7" t="n">
-        <v>86.22</v>
+        <v>86.98</v>
       </c>
     </row>
     <row r="57">
@@ -3651,7 +3651,7 @@
       </c>
       <c r="L59" s="5" t="n"/>
       <c r="M59" s="7" t="n">
-        <v>79.77</v>
+        <v>79.81999999999999</v>
       </c>
     </row>
     <row r="60">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="L62" s="5" t="n"/>
       <c r="M62" s="7" t="n">
-        <v>73.95999999999999</v>
+        <v>74.02</v>
       </c>
     </row>
     <row r="63">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955092 - KIT4P00073957GV5</t>
+          <t>SS - 05900510 - Los Angeles CA - CW6578840- KIT4M04475128THH</t>
         </is>
       </c>
       <c r="C63" s="3" t="n">
@@ -3832,17 +3832,17 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073957GV5</t>
+          <t>KIT4M04475128THH</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>814642</t>
+          <t>809860</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H63" s="5" t="inlineStr">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="L63" s="5" t="n"/>
       <c r="M63" s="7" t="n">
-        <v>72.83</v>
+        <v>72.91</v>
       </c>
     </row>
     <row r="64">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - CW6578840- KIT4M04475128THH</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955092 - KIT4P00073957GV5</t>
         </is>
       </c>
       <c r="C64" s="3" t="n">
@@ -3885,17 +3885,17 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475128THH</t>
+          <t>KIT4P00073957GV5</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>809860</t>
+          <t>814642</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H64" s="5" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="L64" s="5" t="n"/>
       <c r="M64" s="7" t="n">
-        <v>72.73</v>
+        <v>72.83</v>
       </c>
     </row>
     <row r="65">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="L65" s="5" t="n"/>
       <c r="M65" s="7" t="n">
-        <v>72.03</v>
+        <v>72.19</v>
       </c>
     </row>
     <row r="66">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="L67" s="5" t="n"/>
       <c r="M67" s="7" t="n">
-        <v>68.39</v>
+        <v>68.40000000000001</v>
       </c>
     </row>
     <row r="68">
@@ -4287,7 +4287,7 @@
       </c>
       <c r="L71" s="5" t="n"/>
       <c r="M71" s="7" t="n">
-        <v>60.32</v>
+        <v>60.39</v>
       </c>
     </row>
     <row r="72">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="L82" s="5" t="n"/>
       <c r="M82" s="7" t="n">
-        <v>49.48</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="83">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="L95" s="5" t="n"/>
       <c r="M95" s="7" t="n">
-        <v>42.18</v>
+        <v>42.3</v>
       </c>
     </row>
     <row r="96">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955692 - KIT4M05563579H9F</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437392 - KIT4M05872555BJR</t>
         </is>
       </c>
       <c r="C100" s="3" t="n">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563579H9F</t>
+          <t>KIT4M05872555BJR</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>814480</t>
+          <t>816074</t>
         </is>
       </c>
       <c r="G100" s="5" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="L100" s="5" t="n"/>
       <c r="M100" s="7" t="n">
-        <v>39.19</v>
+        <v>39.3</v>
       </c>
     </row>
     <row r="101">
@@ -5835,7 +5835,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649712 - KIT4M046047397TM</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955692 - KIT4M05563579H9F</t>
         </is>
       </c>
       <c r="C101" s="3" t="n">
@@ -5846,12 +5846,12 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047397TM</t>
+          <t>KIT4M05563579H9F</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>809863</t>
+          <t>814480</t>
         </is>
       </c>
       <c r="G101" s="5" t="inlineStr">
@@ -5877,7 +5877,7 @@
       </c>
       <c r="L101" s="5" t="n"/>
       <c r="M101" s="7" t="n">
-        <v>38.83</v>
+        <v>39.19</v>
       </c>
     </row>
     <row r="102">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438092 - KIT4M05799694RW2</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649712 - KIT4M046047397TM</t>
         </is>
       </c>
       <c r="C102" s="3" t="n">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799694RW2</t>
+          <t>KIT4M046047397TM</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>816277</t>
+          <t>809863</t>
         </is>
       </c>
       <c r="G102" s="5" t="inlineStr">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="L102" s="5" t="n"/>
       <c r="M102" s="7" t="n">
-        <v>38.4</v>
+        <v>38.83</v>
       </c>
     </row>
     <row r="103">
@@ -5941,7 +5941,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955602 - KIT4M05563560225</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438092 - KIT4M05799694RW2</t>
         </is>
       </c>
       <c r="C103" s="3" t="n">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563560225</t>
+          <t>KIT4M05799694RW2</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>814454</t>
+          <t>816277</t>
         </is>
       </c>
       <c r="G103" s="5" t="inlineStr">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="L103" s="5" t="n"/>
       <c r="M103" s="7" t="n">
-        <v>38.09</v>
+        <v>38.4</v>
       </c>
     </row>
     <row r="104">
@@ -5994,7 +5994,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020650202-KIT4M05413803FDK</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955602 - KIT4M05563560225</t>
         </is>
       </c>
       <c r="C104" s="3" t="n">
@@ -6005,12 +6005,12 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413803FDK</t>
+          <t>KIT4M05563560225</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>812850</t>
+          <t>814454</t>
         </is>
       </c>
       <c r="G104" s="5" t="inlineStr">
@@ -6036,7 +6036,7 @@
       </c>
       <c r="L104" s="5" t="n"/>
       <c r="M104" s="7" t="n">
-        <v>38.07</v>
+        <v>38.09</v>
       </c>
     </row>
     <row r="105">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles, CA-020955352-KIT4M05563525VC6</t>
+          <t>SMRT-05900510-Los Angeles CA-020650202-KIT4M05413803FDK</t>
         </is>
       </c>
       <c r="C105" s="3" t="n">
@@ -6058,12 +6058,12 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563525VC6</t>
+          <t>KIT4M05413803FDK</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>814458</t>
+          <t>812850</t>
         </is>
       </c>
       <c r="G105" s="5" t="inlineStr">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="L105" s="5" t="n"/>
       <c r="M105" s="7" t="n">
-        <v>37.97</v>
+        <v>38.07</v>
       </c>
     </row>
     <row r="106">
@@ -6100,7 +6100,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020650082 - KIT4M05413792H8C</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955702 - KIT4M05563571G8W</t>
         </is>
       </c>
       <c r="C106" s="3" t="n">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413792H8C</t>
+          <t>KIT4M05563571G8W</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>812803</t>
+          <t>814481</t>
         </is>
       </c>
       <c r="G106" s="5" t="inlineStr">
@@ -6142,7 +6142,7 @@
       </c>
       <c r="L106" s="5" t="n"/>
       <c r="M106" s="7" t="n">
-        <v>37.81</v>
+        <v>38.03</v>
       </c>
     </row>
     <row r="107">
@@ -6153,7 +6153,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 020955382 - KIT4M05563509CHJ</t>
+          <t>SMRT-05900510-Los Angeles, CA-020955352-KIT4M05563525VC6</t>
         </is>
       </c>
       <c r="C107" s="3" t="n">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563509CHJ</t>
+          <t>KIT4M05563525VC6</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>814431</t>
+          <t>814458</t>
         </is>
       </c>
       <c r="G107" s="5" t="inlineStr">
@@ -6195,7 +6195,7 @@
       </c>
       <c r="L107" s="5" t="n"/>
       <c r="M107" s="7" t="n">
-        <v>37.62</v>
+        <v>38.01</v>
       </c>
     </row>
     <row r="108">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437392 - KIT4M05872555BJR</t>
+          <t>STS - 05900510 - Los Angeles CA - 020650082 - KIT4M05413792H8C</t>
         </is>
       </c>
       <c r="C108" s="3" t="n">
@@ -6217,12 +6217,12 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872555BJR</t>
+          <t>KIT4M05413792H8C</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>816074</t>
+          <t>812803</t>
         </is>
       </c>
       <c r="G108" s="5" t="inlineStr">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="L108" s="5" t="n"/>
       <c r="M108" s="7" t="n">
-        <v>37.56</v>
+        <v>37.81</v>
       </c>
     </row>
     <row r="109">
@@ -6259,7 +6259,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955272 - KIT4M05563585TXM</t>
+          <t>SS - 05900510 -  Los Angeles CA - 020955382 - KIT4M05563509CHJ</t>
         </is>
       </c>
       <c r="C109" s="3" t="n">
@@ -6270,12 +6270,12 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563585TXM</t>
+          <t>KIT4M05563509CHJ</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>814475</t>
+          <t>814431</t>
         </is>
       </c>
       <c r="G109" s="5" t="inlineStr">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="L109" s="5" t="n"/>
       <c r="M109" s="7" t="n">
-        <v>36.9</v>
+        <v>37.62</v>
       </c>
     </row>
     <row r="110">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020650042 - KIT4M05413819JV5</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955272 - KIT4M05563585TXM</t>
         </is>
       </c>
       <c r="C110" s="3" t="n">
@@ -6323,12 +6323,12 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413819JV5</t>
+          <t>KIT4M05563585TXM</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>812796</t>
+          <t>814475</t>
         </is>
       </c>
       <c r="G110" s="5" t="inlineStr">
@@ -6354,7 +6354,7 @@
       </c>
       <c r="L110" s="5" t="n"/>
       <c r="M110" s="7" t="n">
-        <v>34.55</v>
+        <v>36.9</v>
       </c>
     </row>
     <row r="111">
@@ -6365,7 +6365,7 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649942 - KIT4M05413786BXC</t>
+          <t>SS - 05900510 - Los Angeles CA - 020650042 - KIT4M05413819JV5</t>
         </is>
       </c>
       <c r="C111" s="3" t="n">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413786BXC</t>
+          <t>KIT4M05413819JV5</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>812838</t>
+          <t>812796</t>
         </is>
       </c>
       <c r="G111" s="5" t="inlineStr">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="L111" s="5" t="n"/>
       <c r="M111" s="7" t="n">
-        <v>34.4</v>
+        <v>34.55</v>
       </c>
     </row>
     <row r="112">
@@ -6418,7 +6418,7 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955702 - KIT4M05563571G8W</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649942 - KIT4M05413786BXC</t>
         </is>
       </c>
       <c r="C112" s="3" t="n">
@@ -6429,12 +6429,12 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563571G8W</t>
+          <t>KIT4M05413786BXC</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>814481</t>
+          <t>812838</t>
         </is>
       </c>
       <c r="G112" s="5" t="inlineStr">
@@ -6460,7 +6460,7 @@
       </c>
       <c r="L112" s="5" t="n"/>
       <c r="M112" s="7" t="n">
-        <v>32.79</v>
+        <v>34.4</v>
       </c>
     </row>
     <row r="113">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="L119" s="5" t="n"/>
       <c r="M119" s="7" t="n">
-        <v>27.31</v>
+        <v>27.36</v>
       </c>
     </row>
     <row r="120">
@@ -6948,7 +6948,7 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649362 - KIT4M05368336DBC</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649532 - KIT4M05413808FFZ</t>
         </is>
       </c>
       <c r="C122" s="3" t="n">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368336DBC</t>
+          <t>KIT4M05413808FFZ</t>
         </is>
       </c>
       <c r="F122" s="4" t="inlineStr">
         <is>
-          <t>810831</t>
+          <t>812828</t>
         </is>
       </c>
       <c r="G122" s="5" t="inlineStr">
@@ -6990,7 +6990,7 @@
       </c>
       <c r="L122" s="5" t="n"/>
       <c r="M122" s="7" t="n">
-        <v>25.13</v>
+        <v>25.36</v>
       </c>
     </row>
     <row r="123">
@@ -7001,7 +7001,7 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649532 - KIT4M05413808FFZ</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649362 - KIT4M05368336DBC</t>
         </is>
       </c>
       <c r="C123" s="3" t="n">
@@ -7012,12 +7012,12 @@
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413808FFZ</t>
+          <t>KIT4M05368336DBC</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>812828</t>
+          <t>810831</t>
         </is>
       </c>
       <c r="G123" s="5" t="inlineStr">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="L123" s="5" t="n"/>
       <c r="M123" s="7" t="n">
-        <v>25.11</v>
+        <v>25.13</v>
       </c>
     </row>
     <row r="124">
@@ -7637,7 +7637,7 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649222 - KIT4P00065640BFW</t>
+          <t>SS - 05900510 -  Los Angeles CA - 021437622 - KIT4M0587258755W</t>
         </is>
       </c>
       <c r="C135" s="3" t="n">
@@ -7648,17 +7648,17 @@
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065640BFW</t>
+          <t>KIT4M0587258755W</t>
         </is>
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>812929</t>
+          <t>816187</t>
         </is>
       </c>
       <c r="G135" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H135" s="5" t="inlineStr">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="L135" s="5" t="n"/>
       <c r="M135" s="7" t="n">
-        <v>19.87</v>
+        <v>19.91</v>
       </c>
     </row>
     <row r="136">
@@ -7690,7 +7690,7 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 021437622 - KIT4M0587258755W</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649222 - KIT4P00065640BFW</t>
         </is>
       </c>
       <c r="C136" s="3" t="n">
@@ -7701,17 +7701,17 @@
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0587258755W</t>
+          <t>KIT4P00065640BFW</t>
         </is>
       </c>
       <c r="F136" s="4" t="inlineStr">
         <is>
-          <t>816187</t>
+          <t>812929</t>
         </is>
       </c>
       <c r="G136" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H136" s="5" t="inlineStr">
@@ -7732,7 +7732,7 @@
       </c>
       <c r="L136" s="5" t="n"/>
       <c r="M136" s="7" t="n">
-        <v>19.82</v>
+        <v>19.87</v>
       </c>
     </row>
     <row r="137">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="L144" s="5" t="n"/>
       <c r="M144" s="7" t="n">
-        <v>18.09</v>
+        <v>18.13</v>
       </c>
     </row>
     <row r="145">
@@ -8368,7 +8368,7 @@
       </c>
       <c r="L148" s="5" t="n"/>
       <c r="M148" s="7" t="n">
-        <v>15.38</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="149">
@@ -8739,7 +8739,7 @@
       </c>
       <c r="L155" s="5" t="n"/>
       <c r="M155" s="7" t="n">
-        <v>13.51</v>
+        <v>13.53</v>
       </c>
     </row>
     <row r="156">
@@ -9057,7 +9057,7 @@
       </c>
       <c r="L161" s="5" t="n"/>
       <c r="M161" s="7" t="n">
-        <v>11.2</v>
+        <v>11.25</v>
       </c>
     </row>
     <row r="162">
@@ -20113,7 +20113,7 @@
     <row r="379">
       <c r="A379" s="15" t="inlineStr">
         <is>
-          <t>Generated 2026-08-27 07:26 by build_starlink_usage.py</t>
+          <t>Generated 2026-08-27 08:19 by build_starlink_usage.py</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_Current_by_Kit.xlsx
+++ b/Starlink_Usage_Current_by_Kit.xlsx
@@ -630,7 +630,7 @@
       </c>
       <c r="L2" s="5" t="n"/>
       <c r="M2" s="7" t="n">
-        <v>2460.32</v>
+        <v>2485.21</v>
       </c>
     </row>
     <row r="3">
@@ -683,7 +683,7 @@
       </c>
       <c r="L3" s="5" t="n"/>
       <c r="M3" s="7" t="n">
-        <v>2261.72</v>
+        <v>2262.8</v>
       </c>
     </row>
     <row r="4">
@@ -736,7 +736,7 @@
       </c>
       <c r="L4" s="5" t="n"/>
       <c r="M4" s="7" t="n">
-        <v>1627.96</v>
+        <v>1632.8</v>
       </c>
     </row>
     <row r="5">
@@ -789,7 +789,7 @@
       </c>
       <c r="L5" s="5" t="n"/>
       <c r="M5" s="7" t="n">
-        <v>1290.21</v>
+        <v>1365.59</v>
       </c>
     </row>
     <row r="6">
@@ -842,7 +842,7 @@
       </c>
       <c r="L6" s="5" t="n"/>
       <c r="M6" s="7" t="n">
-        <v>1070.89</v>
+        <v>1072.32</v>
       </c>
     </row>
     <row r="7">
@@ -906,7 +906,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649202 - KIT4P00066901JZZ</t>
+          <t>SS - 05900510 - Los Angeles, CA - 021437242 - KIT4P00083890S2G</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
@@ -917,12 +917,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00066901JZZ</t>
+          <t>KIT4P00083890S2G</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>812926</t>
+          <t>816226</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="L8" s="5" t="n"/>
       <c r="M8" s="7" t="n">
-        <v>781.74</v>
+        <v>800</v>
       </c>
     </row>
     <row r="9">
@@ -959,7 +959,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles, CA - 020955232 - KIT4M05563538RZV</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649202 - KIT4P00066901JZZ</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
@@ -970,17 +970,17 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563538RZV</t>
+          <t>KIT4P00066901JZZ</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>814459</t>
+          <t>812926</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="L9" s="5" t="n"/>
       <c r="M9" s="7" t="n">
-        <v>772.1900000000001</v>
+        <v>781.74</v>
       </c>
     </row>
     <row r="10">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 021437242 - KIT4P00083890S2G</t>
+          <t>SS - 05900510 -  Los Angeles, CA - 020955232 - KIT4M05563538RZV</t>
         </is>
       </c>
       <c r="C10" s="3" t="n">
@@ -1023,17 +1023,17 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00083890S2G</t>
+          <t>KIT4M05563538RZV</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>816226</t>
+          <t>814459</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="L10" s="5" t="n"/>
       <c r="M10" s="7" t="n">
-        <v>769.48</v>
+        <v>772.1900000000001</v>
       </c>
     </row>
     <row r="11">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270111116 - KIT4P00065612DJF</t>
+          <t>SMRT-05900510-Los Angeles CA-021437282-KIT4P00084593R9F</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065612DJF</t>
+          <t>KIT4P00084593R9F</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>809605</t>
+          <t>816227</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="L11" s="5" t="n"/>
       <c r="M11" s="7" t="n">
-        <v>710.41</v>
+        <v>727.3</v>
       </c>
     </row>
     <row r="12">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="L12" s="5" t="n"/>
       <c r="M12" s="7" t="n">
-        <v>701.09</v>
+        <v>722.6900000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>SMAR-05900510-Los Angeles CA-020426442-KIT4P00065630DZT</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270111116 - KIT4P00065612DJF</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065630DZT</t>
+          <t>KIT4P00065612DJF</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>807635</t>
+          <t>809605</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="L13" s="5" t="n"/>
       <c r="M13" s="7" t="n">
-        <v>691.67</v>
+        <v>711.0700000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437282-KIT4P00084593R9F</t>
+          <t>SMAR-05900510-Los Angeles CA-020426442-KIT4P00065630DZT</t>
         </is>
       </c>
       <c r="C14" s="3" t="n">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00084593R9F</t>
+          <t>KIT4P00065630DZT</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>816227</t>
+          <t>807635</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L14" s="5" t="n"/>
       <c r="M14" s="7" t="n">
-        <v>687.1799999999999</v>
+        <v>693.37</v>
       </c>
     </row>
     <row r="15">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="L15" s="5" t="n"/>
       <c r="M15" s="7" t="n">
-        <v>628.88</v>
+        <v>631.21</v>
       </c>
     </row>
     <row r="16">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="L16" s="5" t="n"/>
       <c r="M16" s="7" t="n">
-        <v>619.17</v>
+        <v>622.72</v>
       </c>
     </row>
     <row r="17">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020650002 - KIT4M05413770WCC</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020649622 - KIT4M05413794SSC</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413770WCC</t>
+          <t>KIT4M05413794SSC</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>812819</t>
+          <t>812847</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="L18" s="5" t="n"/>
       <c r="M18" s="7" t="n">
-        <v>462.9</v>
+        <v>467.59</v>
       </c>
     </row>
     <row r="19">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020649622 - KIT4M05413794SSC</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020650002 - KIT4M05413770WCC</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413794SSC</t>
+          <t>KIT4M05413770WCC</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>812847</t>
+          <t>812819</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="L19" s="5" t="n"/>
       <c r="M19" s="7" t="n">
-        <v>458.79</v>
+        <v>462.9</v>
       </c>
     </row>
     <row r="20">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="L20" s="5" t="n"/>
       <c r="M20" s="7" t="n">
-        <v>414.68</v>
+        <v>429.22</v>
       </c>
     </row>
     <row r="21">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="L27" s="5" t="n"/>
       <c r="M27" s="7" t="n">
-        <v>269.41</v>
+        <v>269.63</v>
       </c>
     </row>
     <row r="28">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="L32" s="5" t="n"/>
       <c r="M32" s="7" t="n">
-        <v>209.54</v>
+        <v>209.99</v>
       </c>
     </row>
     <row r="33">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="L33" s="5" t="n"/>
       <c r="M33" s="7" t="n">
-        <v>180.11</v>
+        <v>184.99</v>
       </c>
     </row>
     <row r="34">
@@ -2326,7 +2326,7 @@
       </c>
       <c r="L34" s="5" t="n"/>
       <c r="M34" s="7" t="n">
-        <v>172.41</v>
+        <v>176.35</v>
       </c>
     </row>
     <row r="35">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="L35" s="5" t="n"/>
       <c r="M35" s="7" t="n">
-        <v>147.6</v>
+        <v>149.04</v>
       </c>
     </row>
     <row r="36">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="L36" s="5" t="n"/>
       <c r="M36" s="7" t="n">
-        <v>136.33</v>
+        <v>141.58</v>
       </c>
     </row>
     <row r="37">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955682 - KIT4M055635887MK</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649352 - KIT4M05368220FG8</t>
         </is>
       </c>
       <c r="C39" s="3" t="n">
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635887MK</t>
+          <t>KIT4M05368220FG8</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>814446</t>
+          <t>810648</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="L39" s="5" t="n"/>
       <c r="M39" s="7" t="n">
-        <v>121.78</v>
+        <v>122.56</v>
       </c>
     </row>
     <row r="40">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437252 - KIT4P00083897XCW</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955682 - KIT4M055635887MK</t>
         </is>
       </c>
       <c r="C40" s="3" t="n">
@@ -2613,17 +2613,17 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00083897XCW</t>
+          <t>KIT4M055635887MK</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>816223</t>
+          <t>814446</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H40" s="5" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="L40" s="5" t="n"/>
       <c r="M40" s="7" t="n">
-        <v>120.72</v>
+        <v>121.78</v>
       </c>
     </row>
     <row r="41">
@@ -2655,7 +2655,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649352 - KIT4M05368220FG8</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437252 - KIT4P00083897XCW</t>
         </is>
       </c>
       <c r="C41" s="3" t="n">
@@ -2666,17 +2666,17 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368220FG8</t>
+          <t>KIT4P00083897XCW</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>810648</t>
+          <t>816223</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="L41" s="5" t="n"/>
       <c r="M41" s="7" t="n">
-        <v>120.24</v>
+        <v>120.72</v>
       </c>
     </row>
     <row r="42">
@@ -2708,7 +2708,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020955622 - KIT4M05563549RSR</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649842 - KIT4M025787739XF</t>
         </is>
       </c>
       <c r="C42" s="3" t="n">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563549RSR</t>
+          <t>KIT4M025787739XF</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>814483</t>
+          <t>809864</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="L42" s="5" t="n"/>
       <c r="M42" s="7" t="n">
-        <v>113.16</v>
+        <v>113.53</v>
       </c>
     </row>
     <row r="43">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649842 - KIT4M025787739XF</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020955622 - KIT4M05563549RSR</t>
         </is>
       </c>
       <c r="C43" s="3" t="n">
@@ -2772,12 +2772,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>KIT4M025787739XF</t>
+          <t>KIT4M05563549RSR</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>809864</t>
+          <t>814483</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="L43" s="5" t="n"/>
       <c r="M43" s="7" t="n">
-        <v>111.2</v>
+        <v>113.16</v>
       </c>
     </row>
     <row r="44">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="L45" s="5" t="n"/>
       <c r="M45" s="7" t="n">
-        <v>108.78</v>
+        <v>109.26</v>
       </c>
     </row>
     <row r="46">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="L47" s="5" t="n"/>
       <c r="M47" s="7" t="n">
-        <v>98.88</v>
+        <v>99.02</v>
       </c>
     </row>
     <row r="48">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020650212 - KIT4M05413779VSD</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482701116 - KIT4M03986275Q4M</t>
         </is>
       </c>
       <c r="C48" s="3" t="n">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413779VSD</t>
+          <t>KIT4M03986275Q4M</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>810103</t>
+          <t>809621</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="L48" s="5" t="n"/>
       <c r="M48" s="7" t="n">
-        <v>96.01000000000001</v>
+        <v>96.95</v>
       </c>
     </row>
     <row r="49">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270111110 - KIT4M03867737P9P</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955522 - KIT4M05563504MBB</t>
         </is>
       </c>
       <c r="C49" s="3" t="n">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03867737P9P</t>
+          <t>KIT4M05563504MBB</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>809622</t>
+          <t>814460</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="L49" s="5" t="n"/>
       <c r="M49" s="7" t="n">
-        <v>95.45999999999999</v>
+        <v>96.91</v>
       </c>
     </row>
     <row r="50">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482701116 - KIT4M03986275Q4M</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270111110 - KIT4M03867737P9P</t>
         </is>
       </c>
       <c r="C50" s="3" t="n">
@@ -3143,12 +3143,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03986275Q4M</t>
+          <t>KIT4M03867737P9P</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>809621</t>
+          <t>809622</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="L50" s="5" t="n"/>
       <c r="M50" s="7" t="n">
-        <v>95.09999999999999</v>
+        <v>96.65000000000001</v>
       </c>
     </row>
     <row r="51">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438042 - KIT4M05799686CMX</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020650212 - KIT4M05413779VSD</t>
         </is>
       </c>
       <c r="C51" s="3" t="n">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799686CMX</t>
+          <t>KIT4M05413779VSD</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>816282</t>
+          <t>810103</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="L51" s="5" t="n"/>
       <c r="M51" s="7" t="n">
-        <v>94.89</v>
+        <v>96.01000000000001</v>
       </c>
     </row>
     <row r="52">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955552 - KIT4M055635475JB</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438042 - KIT4M05799686CMX</t>
         </is>
       </c>
       <c r="C52" s="3" t="n">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635475JB</t>
+          <t>KIT4M05799686CMX</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>814465</t>
+          <t>816282</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="L52" s="5" t="n"/>
       <c r="M52" s="7" t="n">
-        <v>92.86</v>
+        <v>94.89</v>
       </c>
     </row>
     <row r="53">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020650232 - KIT4M054138222CP</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955552 - KIT4M055635475JB</t>
         </is>
       </c>
       <c r="C53" s="3" t="n">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138222CP</t>
+          <t>KIT4M055635475JB</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>812811</t>
+          <t>814465</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="L53" s="5" t="n"/>
       <c r="M53" s="7" t="n">
-        <v>92.69</v>
+        <v>93.37</v>
       </c>
     </row>
     <row r="54">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955522 - KIT4M05563504MBB</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020650232 - KIT4M054138222CP</t>
         </is>
       </c>
       <c r="C54" s="3" t="n">
@@ -3355,12 +3355,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563504MBB</t>
+          <t>KIT4M054138222CP</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>814460</t>
+          <t>812811</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="L54" s="5" t="n"/>
       <c r="M54" s="7" t="n">
-        <v>92.39</v>
+        <v>93.11</v>
       </c>
     </row>
     <row r="55">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="L55" s="5" t="n"/>
       <c r="M55" s="7" t="n">
-        <v>87.36</v>
+        <v>88.51000000000001</v>
       </c>
     </row>
     <row r="56">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="L56" s="5" t="n"/>
       <c r="M56" s="7" t="n">
-        <v>86.98</v>
+        <v>88.3</v>
       </c>
     </row>
     <row r="57">
@@ -3651,7 +3651,7 @@
       </c>
       <c r="L59" s="5" t="n"/>
       <c r="M59" s="7" t="n">
-        <v>79.81999999999999</v>
+        <v>79.88</v>
       </c>
     </row>
     <row r="60">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649562 - KIT4M054138125NW</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649782 - KIT4M03986264P49</t>
         </is>
       </c>
       <c r="C60" s="3" t="n">
@@ -3673,12 +3673,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138125NW</t>
+          <t>KIT4M03986264P49</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>812826</t>
+          <t>809875</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="L60" s="5" t="n"/>
       <c r="M60" s="7" t="n">
-        <v>75.34999999999999</v>
+        <v>76.11</v>
       </c>
     </row>
     <row r="61">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955492 - KIT4M05563520SH2</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649562 - KIT4M054138125NW</t>
         </is>
       </c>
       <c r="C61" s="3" t="n">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563520SH2</t>
+          <t>KIT4M054138125NW</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>814478</t>
+          <t>812826</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
@@ -3757,7 +3757,7 @@
       </c>
       <c r="L61" s="5" t="n"/>
       <c r="M61" s="7" t="n">
-        <v>74.48</v>
+        <v>75.64</v>
       </c>
     </row>
     <row r="62">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649782 - KIT4M03986264P49</t>
+          <t>SS - 05900510 - Los Angeles CA - CW6578840- KIT4M04475128THH</t>
         </is>
       </c>
       <c r="C62" s="3" t="n">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03986264P49</t>
+          <t>KIT4M04475128THH</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>809875</t>
+          <t>809860</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="L62" s="5" t="n"/>
       <c r="M62" s="7" t="n">
-        <v>74.02</v>
+        <v>75.58</v>
       </c>
     </row>
     <row r="63">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - CW6578840- KIT4M04475128THH</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955492 - KIT4M05563520SH2</t>
         </is>
       </c>
       <c r="C63" s="3" t="n">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475128THH</t>
+          <t>KIT4M05563520SH2</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>809860</t>
+          <t>814478</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="L63" s="5" t="n"/>
       <c r="M63" s="7" t="n">
-        <v>72.91</v>
+        <v>74.56999999999999</v>
       </c>
     </row>
     <row r="64">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955092 - KIT4P00073957GV5</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827014 - KIT4M04475149XG5</t>
         </is>
       </c>
       <c r="C64" s="3" t="n">
@@ -3885,17 +3885,17 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073957GV5</t>
+          <t>KIT4M04475149XG5</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>814642</t>
+          <t>809657</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H64" s="5" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="L64" s="5" t="n"/>
       <c r="M64" s="7" t="n">
-        <v>72.83</v>
+        <v>73.42</v>
       </c>
     </row>
     <row r="65">
@@ -3927,7 +3927,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827014 - KIT4M04475149XG5</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955092 - KIT4P00073957GV5</t>
         </is>
       </c>
       <c r="C65" s="3" t="n">
@@ -3938,17 +3938,17 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475149XG5</t>
+          <t>KIT4P00073957GV5</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>809657</t>
+          <t>814642</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H65" s="5" t="inlineStr">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="L65" s="5" t="n"/>
       <c r="M65" s="7" t="n">
-        <v>72.19</v>
+        <v>72.83</v>
       </c>
     </row>
     <row r="66">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="L66" s="5" t="n"/>
       <c r="M66" s="7" t="n">
-        <v>71.08</v>
+        <v>71.22</v>
       </c>
     </row>
     <row r="67">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="L67" s="5" t="n"/>
       <c r="M67" s="7" t="n">
-        <v>68.40000000000001</v>
+        <v>69.13</v>
       </c>
     </row>
     <row r="68">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="L68" s="5" t="n"/>
       <c r="M68" s="7" t="n">
-        <v>67.2</v>
+        <v>67.27</v>
       </c>
     </row>
     <row r="69">
@@ -4192,7 +4192,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649342 - KIT4M05413775N9M</t>
+          <t>SS - 05900510 - Los Angeles CA - 020650102 - KIT4M054138257Z7</t>
         </is>
       </c>
       <c r="C70" s="3" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413775N9M</t>
+          <t>KIT4M054138257Z7</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>812818</t>
+          <t>810106</t>
         </is>
       </c>
       <c r="G70" s="5" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="L70" s="5" t="n"/>
       <c r="M70" s="7" t="n">
-        <v>60.81</v>
+        <v>61.28</v>
       </c>
     </row>
     <row r="71">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020650102 - KIT4M054138257Z7</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649342 - KIT4M05413775N9M</t>
         </is>
       </c>
       <c r="C71" s="3" t="n">
@@ -4256,12 +4256,12 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138257Z7</t>
+          <t>KIT4M05413775N9M</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>810106</t>
+          <t>812818</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
@@ -4287,7 +4287,7 @@
       </c>
       <c r="L71" s="5" t="n"/>
       <c r="M71" s="7" t="n">
-        <v>60.39</v>
+        <v>60.81</v>
       </c>
     </row>
     <row r="72">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="L72" s="5" t="n"/>
       <c r="M72" s="7" t="n">
-        <v>60.24</v>
+        <v>60.78</v>
       </c>
     </row>
     <row r="73">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482702 - KIT4M04604743HSS</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955112 - KIT4P00073918HBX</t>
         </is>
       </c>
       <c r="C73" s="3" t="n">
@@ -4362,17 +4362,17 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604743HSS</t>
+          <t>KIT4P00073918HBX</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>809663</t>
+          <t>814645</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H73" s="5" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="L73" s="5" t="n"/>
       <c r="M73" s="7" t="n">
-        <v>59.03</v>
+        <v>59.84</v>
       </c>
     </row>
     <row r="74">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482704 - KIT4M04604745G8Z</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482702 - KIT4M04604743HSS</t>
         </is>
       </c>
       <c r="C74" s="3" t="n">
@@ -4415,12 +4415,12 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604745G8Z</t>
+          <t>KIT4M04604743HSS</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>809661</t>
+          <t>809663</t>
         </is>
       </c>
       <c r="G74" s="5" t="inlineStr">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="L74" s="5" t="n"/>
       <c r="M74" s="7" t="n">
-        <v>57.14</v>
+        <v>59.03</v>
       </c>
     </row>
     <row r="75">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649902 - KIT4M05413805MKQ</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482704 - KIT4M04604745G8Z</t>
         </is>
       </c>
       <c r="C75" s="3" t="n">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413805MKQ</t>
+          <t>KIT4M04604745G8Z</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>812849</t>
+          <t>809661</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="L75" s="5" t="n"/>
       <c r="M75" s="7" t="n">
-        <v>55.96</v>
+        <v>57.14</v>
       </c>
     </row>
     <row r="76">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955112 - KIT4P00073918HBX</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649902 - KIT4M05413805MKQ</t>
         </is>
       </c>
       <c r="C76" s="3" t="n">
@@ -4521,17 +4521,17 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073918HBX</t>
+          <t>KIT4M05413805MKQ</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>814645</t>
+          <t>812849</t>
         </is>
       </c>
       <c r="G76" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H76" s="5" t="inlineStr">
@@ -4552,7 +4552,7 @@
       </c>
       <c r="L76" s="5" t="n"/>
       <c r="M76" s="7" t="n">
-        <v>54.59</v>
+        <v>56.64</v>
       </c>
     </row>
     <row r="77">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="L78" s="5" t="n"/>
       <c r="M78" s="7" t="n">
-        <v>52.27</v>
+        <v>52.28</v>
       </c>
     </row>
     <row r="79">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827011118 - KIT4M03867766NGK</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955132 - KIT4M055635238J6</t>
         </is>
       </c>
       <c r="C79" s="3" t="n">
@@ -4680,12 +4680,12 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03867766NGK</t>
+          <t>KIT4M055635238J6</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>809615</t>
+          <t>814449</t>
         </is>
       </c>
       <c r="G79" s="5" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="L79" s="5" t="n"/>
       <c r="M79" s="7" t="n">
-        <v>50.49</v>
+        <v>51.56</v>
       </c>
     </row>
     <row r="80">
@@ -4722,7 +4722,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020650142 - KIT4M05413839D24</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827011118 - KIT4M03867766NGK</t>
         </is>
       </c>
       <c r="C80" s="3" t="n">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413839D24</t>
+          <t>KIT4M03867766NGK</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>810096</t>
+          <t>809615</t>
         </is>
       </c>
       <c r="G80" s="5" t="inlineStr">
@@ -4764,7 +4764,7 @@
       </c>
       <c r="L80" s="5" t="n"/>
       <c r="M80" s="7" t="n">
-        <v>50.33</v>
+        <v>50.95</v>
       </c>
     </row>
     <row r="81">
@@ -4775,7 +4775,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649932 - KIT4M054138324MW</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955292 - KIT4M05563531XSB</t>
         </is>
       </c>
       <c r="C81" s="3" t="n">
@@ -4786,12 +4786,12 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138324MW</t>
+          <t>KIT4M05563531XSB</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>812834</t>
+          <t>814469</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="L81" s="5" t="n"/>
       <c r="M81" s="7" t="n">
-        <v>49.76</v>
+        <v>50.76</v>
       </c>
     </row>
     <row r="82">
@@ -4828,7 +4828,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955292 - KIT4M05563531XSB</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020650142 - KIT4M05413839D24</t>
         </is>
       </c>
       <c r="C82" s="3" t="n">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563531XSB</t>
+          <t>KIT4M05413839D24</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>814469</t>
+          <t>810096</t>
         </is>
       </c>
       <c r="G82" s="5" t="inlineStr">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="L82" s="5" t="n"/>
       <c r="M82" s="7" t="n">
-        <v>49.6</v>
+        <v>50.33</v>
       </c>
     </row>
     <row r="83">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270111114 - KIT4P00065593VWC</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649932 - KIT4M054138324MW</t>
         </is>
       </c>
       <c r="C83" s="3" t="n">
@@ -4892,17 +4892,17 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065593VWC</t>
+          <t>KIT4M054138324MW</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>809606</t>
+          <t>812834</t>
         </is>
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H83" s="5" t="inlineStr">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="L83" s="5" t="n"/>
       <c r="M83" s="7" t="n">
-        <v>49.23</v>
+        <v>49.76</v>
       </c>
     </row>
     <row r="84">
@@ -4934,7 +4934,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-LOS ANGELES CA-020955202-KIT4M05563534GZ7</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270111114 - KIT4P00065593VWC</t>
         </is>
       </c>
       <c r="C84" s="3" t="n">
@@ -4945,17 +4945,17 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563534GZ7</t>
+          <t>KIT4P00065593VWC</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>814467</t>
+          <t>809606</t>
         </is>
       </c>
       <c r="G84" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H84" s="5" t="inlineStr">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="L84" s="5" t="n"/>
       <c r="M84" s="7" t="n">
-        <v>48.5</v>
+        <v>49.23</v>
       </c>
     </row>
     <row r="85">
@@ -5029,7 +5029,7 @@
       </c>
       <c r="L85" s="5" t="n"/>
       <c r="M85" s="7" t="n">
-        <v>48.47</v>
+        <v>48.74</v>
       </c>
     </row>
     <row r="86">
@@ -5040,7 +5040,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955262 - KIT4M05563521ZSX</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649712 - KIT4M046047397TM</t>
         </is>
       </c>
       <c r="C86" s="3" t="n">
@@ -5051,12 +5051,12 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563521ZSX</t>
+          <t>KIT4M046047397TM</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>814476</t>
+          <t>809863</t>
         </is>
       </c>
       <c r="G86" s="5" t="inlineStr">
@@ -5082,7 +5082,7 @@
       </c>
       <c r="L86" s="5" t="n"/>
       <c r="M86" s="7" t="n">
-        <v>48.34</v>
+        <v>48.64</v>
       </c>
     </row>
     <row r="87">
@@ -5093,7 +5093,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649672 - KIT4M04606113TPB</t>
+          <t>SMRT-05900510-LOS ANGELES CA-020955202-KIT4M05563534GZ7</t>
         </is>
       </c>
       <c r="C87" s="3" t="n">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04606113TPB</t>
+          <t>KIT4M05563534GZ7</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>809862</t>
+          <t>814467</t>
         </is>
       </c>
       <c r="G87" s="5" t="inlineStr">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="L87" s="5" t="n"/>
       <c r="M87" s="7" t="n">
-        <v>46.74</v>
+        <v>48.53</v>
       </c>
     </row>
     <row r="88">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270112 - KIT4M044751638F5</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955262 - KIT4M05563521ZSX</t>
         </is>
       </c>
       <c r="C88" s="3" t="n">
@@ -5157,12 +5157,12 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>KIT4M044751638F5</t>
+          <t>KIT4M05563521ZSX</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>809618</t>
+          <t>814476</t>
         </is>
       </c>
       <c r="G88" s="5" t="inlineStr">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="L88" s="5" t="n"/>
       <c r="M88" s="7" t="n">
-        <v>45.98</v>
+        <v>48.34</v>
       </c>
     </row>
     <row r="89">
@@ -5199,7 +5199,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles, CA - 0204827011112 - KIT4M04158967K28</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649672 - KIT4M04606113TPB</t>
         </is>
       </c>
       <c r="C89" s="3" t="n">
@@ -5210,12 +5210,12 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158967K28</t>
+          <t>KIT4M04606113TPB</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>809620</t>
+          <t>809862</t>
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr">
@@ -5241,7 +5241,7 @@
       </c>
       <c r="L89" s="5" t="n"/>
       <c r="M89" s="7" t="n">
-        <v>45.91</v>
+        <v>46.74</v>
       </c>
     </row>
     <row r="90">
@@ -5252,7 +5252,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles, CA-020955452-KIT4M05563529K2D</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955692 - KIT4M05563603CP4</t>
         </is>
       </c>
       <c r="C90" s="3" t="n">
@@ -5263,12 +5263,12 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563529K2D</t>
+          <t>KIT4M05563603CP4</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>814473</t>
+          <t>814447</t>
         </is>
       </c>
       <c r="G90" s="5" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="L90" s="5" t="n"/>
       <c r="M90" s="7" t="n">
-        <v>43.64</v>
+        <v>46.53</v>
       </c>
     </row>
     <row r="91">
@@ -5305,7 +5305,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955692 - KIT4M05563603CP4</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270112 - KIT4M044751638F5</t>
         </is>
       </c>
       <c r="C91" s="3" t="n">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563603CP4</t>
+          <t>KIT4M044751638F5</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>814447</t>
+          <t>809618</t>
         </is>
       </c>
       <c r="G91" s="5" t="inlineStr">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="L91" s="5" t="n"/>
       <c r="M91" s="7" t="n">
-        <v>43.57</v>
+        <v>45.98</v>
       </c>
     </row>
     <row r="92">
@@ -5358,7 +5358,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649812 - KIT4M04604742S6S</t>
+          <t>STS - 05900510 - Los Angeles, CA - 0204827011112 - KIT4M04158967K28</t>
         </is>
       </c>
       <c r="C92" s="3" t="n">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604742S6S</t>
+          <t>KIT4M04158967K28</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>809874</t>
+          <t>809620</t>
         </is>
       </c>
       <c r="G92" s="5" t="inlineStr">
@@ -5400,7 +5400,7 @@
       </c>
       <c r="L92" s="5" t="n"/>
       <c r="M92" s="7" t="n">
-        <v>43.24</v>
+        <v>45.91</v>
       </c>
     </row>
     <row r="93">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649432 - KIT4M05413778RBR</t>
+          <t>SMRT-05900510-Los Angeles, CA-020955452-KIT4M05563529K2D</t>
         </is>
       </c>
       <c r="C93" s="3" t="n">
@@ -5422,12 +5422,12 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413778RBR</t>
+          <t>KIT4M05563529K2D</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>812843</t>
+          <t>814473</t>
         </is>
       </c>
       <c r="G93" s="5" t="inlineStr">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="L93" s="5" t="n"/>
       <c r="M93" s="7" t="n">
-        <v>42.82</v>
+        <v>45.09</v>
       </c>
     </row>
     <row r="94">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020650192 - KIT4M054138007JF</t>
+          <t>SMRT-05900510-Los Angeles, CA-020955582-KIT4M05563593DMC</t>
         </is>
       </c>
       <c r="C94" s="3" t="n">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138007JF</t>
+          <t>KIT4M05563593DMC</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>810095</t>
+          <t>814442</t>
         </is>
       </c>
       <c r="G94" s="5" t="inlineStr">
@@ -5506,7 +5506,7 @@
       </c>
       <c r="L94" s="5" t="n"/>
       <c r="M94" s="7" t="n">
-        <v>42.59</v>
+        <v>44.75</v>
       </c>
     </row>
     <row r="95">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles, CA-020955582-KIT4M05563593DMC</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649812 - KIT4M04604742S6S</t>
         </is>
       </c>
       <c r="C95" s="3" t="n">
@@ -5528,12 +5528,12 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563593DMC</t>
+          <t>KIT4M04604742S6S</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>814442</t>
+          <t>809874</t>
         </is>
       </c>
       <c r="G95" s="5" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="L95" s="5" t="n"/>
       <c r="M95" s="7" t="n">
-        <v>42.3</v>
+        <v>43.24</v>
       </c>
     </row>
     <row r="96">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020650052 - KIT4M05413781K6C</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649432 - KIT4M05413778RBR</t>
         </is>
       </c>
       <c r="C96" s="3" t="n">
@@ -5581,12 +5581,12 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413781K6C</t>
+          <t>KIT4M05413778RBR</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>812798</t>
+          <t>812843</t>
         </is>
       </c>
       <c r="G96" s="5" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="L96" s="5" t="n"/>
       <c r="M96" s="7" t="n">
-        <v>42.04</v>
+        <v>42.82</v>
       </c>
     </row>
     <row r="97">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955132 - KIT4M055635238J6</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020650192 - KIT4M054138007JF</t>
         </is>
       </c>
       <c r="C97" s="3" t="n">
@@ -5634,12 +5634,12 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635238J6</t>
+          <t>KIT4M054138007JF</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>814449</t>
+          <t>810095</t>
         </is>
       </c>
       <c r="G97" s="5" t="inlineStr">
@@ -5665,7 +5665,7 @@
       </c>
       <c r="L97" s="5" t="n"/>
       <c r="M97" s="7" t="n">
-        <v>39.94</v>
+        <v>42.59</v>
       </c>
     </row>
     <row r="98">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020955652 - KIT4M0556358988Z</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020650052 - KIT4M05413781K6C</t>
         </is>
       </c>
       <c r="C98" s="3" t="n">
@@ -5687,12 +5687,12 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0556358988Z</t>
+          <t>KIT4M05413781K6C</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>814484</t>
+          <t>812798</t>
         </is>
       </c>
       <c r="G98" s="5" t="inlineStr">
@@ -5718,7 +5718,7 @@
       </c>
       <c r="L98" s="5" t="n"/>
       <c r="M98" s="7" t="n">
-        <v>39.91</v>
+        <v>42.04</v>
       </c>
     </row>
     <row r="99">
@@ -5729,7 +5729,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270116 - KIT4M03476116F45</t>
+          <t>SMRT-05900510-Los Angeles, CA-020955352-KIT4M05563525VC6</t>
         </is>
       </c>
       <c r="C99" s="3" t="n">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03476116F45</t>
+          <t>KIT4M05563525VC6</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>809608</t>
+          <t>814458</t>
         </is>
       </c>
       <c r="G99" s="5" t="inlineStr">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="L99" s="5" t="n"/>
       <c r="M99" s="7" t="n">
-        <v>39.71</v>
+        <v>41.28</v>
       </c>
     </row>
     <row r="100">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="L100" s="5" t="n"/>
       <c r="M100" s="7" t="n">
-        <v>39.3</v>
+        <v>41.21</v>
       </c>
     </row>
     <row r="101">
@@ -5835,7 +5835,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955692 - KIT4M05563579H9F</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438092 - KIT4M05799694RW2</t>
         </is>
       </c>
       <c r="C101" s="3" t="n">
@@ -5846,12 +5846,12 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563579H9F</t>
+          <t>KIT4M05799694RW2</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>814480</t>
+          <t>816277</t>
         </is>
       </c>
       <c r="G101" s="5" t="inlineStr">
@@ -5877,7 +5877,7 @@
       </c>
       <c r="L101" s="5" t="n"/>
       <c r="M101" s="7" t="n">
-        <v>39.19</v>
+        <v>40.13</v>
       </c>
     </row>
     <row r="102">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649712 - KIT4M046047397TM</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020955652 - KIT4M0556358988Z</t>
         </is>
       </c>
       <c r="C102" s="3" t="n">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047397TM</t>
+          <t>KIT4M0556358988Z</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>809863</t>
+          <t>814484</t>
         </is>
       </c>
       <c r="G102" s="5" t="inlineStr">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="L102" s="5" t="n"/>
       <c r="M102" s="7" t="n">
-        <v>38.83</v>
+        <v>39.91</v>
       </c>
     </row>
     <row r="103">
@@ -5941,7 +5941,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438092 - KIT4M05799694RW2</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955702 - KIT4M05563571G8W</t>
         </is>
       </c>
       <c r="C103" s="3" t="n">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799694RW2</t>
+          <t>KIT4M05563571G8W</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>816277</t>
+          <t>814481</t>
         </is>
       </c>
       <c r="G103" s="5" t="inlineStr">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="L103" s="5" t="n"/>
       <c r="M103" s="7" t="n">
-        <v>38.4</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="104">
@@ -5994,7 +5994,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955602 - KIT4M05563560225</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270116 - KIT4M03476116F45</t>
         </is>
       </c>
       <c r="C104" s="3" t="n">
@@ -6005,12 +6005,12 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563560225</t>
+          <t>KIT4M03476116F45</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>814454</t>
+          <t>809608</t>
         </is>
       </c>
       <c r="G104" s="5" t="inlineStr">
@@ -6036,7 +6036,7 @@
       </c>
       <c r="L104" s="5" t="n"/>
       <c r="M104" s="7" t="n">
-        <v>38.09</v>
+        <v>39.71</v>
       </c>
     </row>
     <row r="105">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020650202-KIT4M05413803FDK</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955692 - KIT4M05563579H9F</t>
         </is>
       </c>
       <c r="C105" s="3" t="n">
@@ -6058,12 +6058,12 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413803FDK</t>
+          <t>KIT4M05563579H9F</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>812850</t>
+          <t>814480</t>
         </is>
       </c>
       <c r="G105" s="5" t="inlineStr">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="L105" s="5" t="n"/>
       <c r="M105" s="7" t="n">
-        <v>38.07</v>
+        <v>39.23</v>
       </c>
     </row>
     <row r="106">
@@ -6100,7 +6100,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955702 - KIT4M05563571G8W</t>
+          <t>SMRT-05900510-Los Angeles CA-020650202-KIT4M05413803FDK</t>
         </is>
       </c>
       <c r="C106" s="3" t="n">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563571G8W</t>
+          <t>KIT4M05413803FDK</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>814481</t>
+          <t>812850</t>
         </is>
       </c>
       <c r="G106" s="5" t="inlineStr">
@@ -6142,7 +6142,7 @@
       </c>
       <c r="L106" s="5" t="n"/>
       <c r="M106" s="7" t="n">
-        <v>38.03</v>
+        <v>38.55</v>
       </c>
     </row>
     <row r="107">
@@ -6153,7 +6153,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles, CA-020955352-KIT4M05563525VC6</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955602 - KIT4M05563560225</t>
         </is>
       </c>
       <c r="C107" s="3" t="n">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563525VC6</t>
+          <t>KIT4M05563560225</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>814458</t>
+          <t>814454</t>
         </is>
       </c>
       <c r="G107" s="5" t="inlineStr">
@@ -6195,7 +6195,7 @@
       </c>
       <c r="L107" s="5" t="n"/>
       <c r="M107" s="7" t="n">
-        <v>38.01</v>
+        <v>38.09</v>
       </c>
     </row>
     <row r="108">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020650082 - KIT4M05413792H8C</t>
+          <t>SS - 05900510 -  Los Angeles CA - 020955382 - KIT4M05563509CHJ</t>
         </is>
       </c>
       <c r="C108" s="3" t="n">
@@ -6217,12 +6217,12 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413792H8C</t>
+          <t>KIT4M05563509CHJ</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>812803</t>
+          <t>814431</t>
         </is>
       </c>
       <c r="G108" s="5" t="inlineStr">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="L108" s="5" t="n"/>
       <c r="M108" s="7" t="n">
-        <v>37.81</v>
+        <v>37.99</v>
       </c>
     </row>
     <row r="109">
@@ -6259,7 +6259,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 020955382 - KIT4M05563509CHJ</t>
+          <t>STS - 05900510 - Los Angeles CA - 020650082 - KIT4M05413792H8C</t>
         </is>
       </c>
       <c r="C109" s="3" t="n">
@@ -6270,12 +6270,12 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563509CHJ</t>
+          <t>KIT4M05413792H8C</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>814431</t>
+          <t>812803</t>
         </is>
       </c>
       <c r="G109" s="5" t="inlineStr">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="L109" s="5" t="n"/>
       <c r="M109" s="7" t="n">
-        <v>37.62</v>
+        <v>37.81</v>
       </c>
     </row>
     <row r="110">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="L111" s="5" t="n"/>
       <c r="M111" s="7" t="n">
-        <v>34.55</v>
+        <v>35.26</v>
       </c>
     </row>
     <row r="112">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482706 - KIT4M04604744V6K</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020955462 - KIT4M05563513GTF</t>
         </is>
       </c>
       <c r="C114" s="3" t="n">
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604744V6K</t>
+          <t>KIT4M05563513GTF</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>809659</t>
+          <t>814432</t>
         </is>
       </c>
       <c r="G114" s="5" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="L114" s="5" t="n"/>
       <c r="M114" s="7" t="n">
-        <v>31.35</v>
+        <v>31.71</v>
       </c>
     </row>
     <row r="115">
@@ -6577,7 +6577,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020955462 - KIT4M05563513GTF</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482706 - KIT4M04604744V6K</t>
         </is>
       </c>
       <c r="C115" s="3" t="n">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563513GTF</t>
+          <t>KIT4M04604744V6K</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>814432</t>
+          <t>809659</t>
         </is>
       </c>
       <c r="G115" s="5" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="L115" s="5" t="n"/>
       <c r="M115" s="7" t="n">
-        <v>30.04</v>
+        <v>31.38</v>
       </c>
     </row>
     <row r="116">
@@ -6672,7 +6672,7 @@
       </c>
       <c r="L116" s="5" t="n"/>
       <c r="M116" s="7" t="n">
-        <v>29.29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="117">
@@ -6736,7 +6736,7 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827016 - KIT4M041536494G6</t>
+          <t>SS - 05900510 - Los Angeles CA - 6858375 - KIT4M05872512N5W</t>
         </is>
       </c>
       <c r="C118" s="3" t="n">
@@ -6747,12 +6747,12 @@
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>KIT4M041536494G6</t>
+          <t>KIT4M05872512N5W</t>
         </is>
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>809617</t>
+          <t>816077</t>
         </is>
       </c>
       <c r="G118" s="5" t="inlineStr">
@@ -6778,7 +6778,7 @@
       </c>
       <c r="L118" s="5" t="n"/>
       <c r="M118" s="7" t="n">
-        <v>27.69</v>
+        <v>28.95</v>
       </c>
     </row>
     <row r="119">
@@ -6789,7 +6789,7 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 6858375 - KIT4M05872512N5W</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827016 - KIT4M041536494G6</t>
         </is>
       </c>
       <c r="C119" s="3" t="n">
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872512N5W</t>
+          <t>KIT4M041536494G6</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>816077</t>
+          <t>809617</t>
         </is>
       </c>
       <c r="G119" s="5" t="inlineStr">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="L119" s="5" t="n"/>
       <c r="M119" s="7" t="n">
-        <v>27.36</v>
+        <v>28.61</v>
       </c>
     </row>
     <row r="120">
@@ -6895,7 +6895,7 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955342 - KIT4M05563524MJ4</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649532 - KIT4M05413808FFZ</t>
         </is>
       </c>
       <c r="C121" s="3" t="n">
@@ -6906,12 +6906,12 @@
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563524MJ4</t>
+          <t>KIT4M05413808FFZ</t>
         </is>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>814472</t>
+          <t>812828</t>
         </is>
       </c>
       <c r="G121" s="5" t="inlineStr">
@@ -6937,7 +6937,7 @@
       </c>
       <c r="L121" s="5" t="n"/>
       <c r="M121" s="7" t="n">
-        <v>26.26</v>
+        <v>26.76</v>
       </c>
     </row>
     <row r="122">
@@ -6948,7 +6948,7 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649532 - KIT4M05413808FFZ</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955342 - KIT4M05563524MJ4</t>
         </is>
       </c>
       <c r="C122" s="3" t="n">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413808FFZ</t>
+          <t>KIT4M05563524MJ4</t>
         </is>
       </c>
       <c r="F122" s="4" t="inlineStr">
         <is>
-          <t>812828</t>
+          <t>814472</t>
         </is>
       </c>
       <c r="G122" s="5" t="inlineStr">
@@ -6990,7 +6990,7 @@
       </c>
       <c r="L122" s="5" t="n"/>
       <c r="M122" s="7" t="n">
-        <v>25.36</v>
+        <v>26.26</v>
       </c>
     </row>
     <row r="123">
@@ -7001,7 +7001,7 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649362 - KIT4M05368336DBC</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649212 - KIT4P00065633ZXC</t>
         </is>
       </c>
       <c r="C123" s="3" t="n">
@@ -7012,17 +7012,17 @@
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368336DBC</t>
+          <t>KIT4P00065633ZXC</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>810831</t>
+          <t>812922</t>
         </is>
       </c>
       <c r="G123" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H123" s="5" t="inlineStr">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="L123" s="5" t="n"/>
       <c r="M123" s="7" t="n">
-        <v>25.13</v>
+        <v>25.67</v>
       </c>
     </row>
     <row r="124">
@@ -7054,7 +7054,7 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955212 - KIT4M05563512GBQ</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649362 - KIT4M05368336DBC</t>
         </is>
       </c>
       <c r="C124" s="3" t="n">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563512GBQ</t>
+          <t>KIT4M05368336DBC</t>
         </is>
       </c>
       <c r="F124" s="4" t="inlineStr">
         <is>
-          <t>814435</t>
+          <t>810831</t>
         </is>
       </c>
       <c r="G124" s="5" t="inlineStr">
@@ -7096,7 +7096,7 @@
       </c>
       <c r="L124" s="5" t="n"/>
       <c r="M124" s="7" t="n">
-        <v>24.55</v>
+        <v>25.13</v>
       </c>
     </row>
     <row r="125">
@@ -7107,7 +7107,7 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437782 - KIT4M058724975J4</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955212 - KIT4M05563512GBQ</t>
         </is>
       </c>
       <c r="C125" s="3" t="n">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058724975J4</t>
+          <t>KIT4M05563512GBQ</t>
         </is>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>816075</t>
+          <t>814435</t>
         </is>
       </c>
       <c r="G125" s="5" t="inlineStr">
@@ -7149,7 +7149,7 @@
       </c>
       <c r="L125" s="5" t="n"/>
       <c r="M125" s="7" t="n">
-        <v>23.92</v>
+        <v>24.55</v>
       </c>
     </row>
     <row r="126">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="L126" s="5" t="n"/>
       <c r="M126" s="7" t="n">
-        <v>23.9</v>
+        <v>24.22</v>
       </c>
     </row>
     <row r="127">
@@ -7213,7 +7213,7 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020650162 - KIT4M05413837SMB</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437782 - KIT4M058724975J4</t>
         </is>
       </c>
       <c r="C127" s="3" t="n">
@@ -7224,12 +7224,12 @@
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413837SMB</t>
+          <t>KIT4M058724975J4</t>
         </is>
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>810100</t>
+          <t>816075</t>
         </is>
       </c>
       <c r="G127" s="5" t="inlineStr">
@@ -7255,7 +7255,7 @@
       </c>
       <c r="L127" s="5" t="n"/>
       <c r="M127" s="7" t="n">
-        <v>23.32</v>
+        <v>23.93</v>
       </c>
     </row>
     <row r="128">
@@ -7308,7 +7308,7 @@
       </c>
       <c r="L128" s="5" t="n"/>
       <c r="M128" s="7" t="n">
-        <v>22.76</v>
+        <v>23.82</v>
       </c>
     </row>
     <row r="129">
@@ -7319,7 +7319,7 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020649292-KIT4M05368201SNV</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020650162 - KIT4M05413837SMB</t>
         </is>
       </c>
       <c r="C129" s="3" t="n">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368201SNV</t>
+          <t>KIT4M05413837SMB</t>
         </is>
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>810651</t>
+          <t>810100</t>
         </is>
       </c>
       <c r="G129" s="5" t="inlineStr">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="L129" s="5" t="n"/>
       <c r="M129" s="7" t="n">
-        <v>22.42</v>
+        <v>23.32</v>
       </c>
     </row>
     <row r="130">
@@ -7372,7 +7372,7 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020650132-KIT4M05413828PCT</t>
+          <t>SMRT-05900510-Los Angeles CA-020649292-KIT4M05368201SNV</t>
         </is>
       </c>
       <c r="C130" s="3" t="n">
@@ -7383,12 +7383,12 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413828PCT</t>
+          <t>KIT4M05368201SNV</t>
         </is>
       </c>
       <c r="F130" s="4" t="inlineStr">
         <is>
-          <t>812799</t>
+          <t>810651</t>
         </is>
       </c>
       <c r="G130" s="5" t="inlineStr">
@@ -7414,7 +7414,7 @@
       </c>
       <c r="L130" s="5" t="n"/>
       <c r="M130" s="7" t="n">
-        <v>21.54</v>
+        <v>22.78</v>
       </c>
     </row>
     <row r="131">
@@ -7467,7 +7467,7 @@
       </c>
       <c r="L131" s="5" t="n"/>
       <c r="M131" s="7" t="n">
-        <v>21.2</v>
+        <v>22.13</v>
       </c>
     </row>
     <row r="132">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-LOS ANGELES CA-020955172-KIT4M05563526WNC</t>
+          <t>SMRT-05900510-Los Angeles CA-020650132-KIT4M05413828PCT</t>
         </is>
       </c>
       <c r="C132" s="3" t="n">
@@ -7489,12 +7489,12 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563526WNC</t>
+          <t>KIT4M05413828PCT</t>
         </is>
       </c>
       <c r="F132" s="4" t="inlineStr">
         <is>
-          <t>814463</t>
+          <t>812799</t>
         </is>
       </c>
       <c r="G132" s="5" t="inlineStr">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="L132" s="5" t="n"/>
       <c r="M132" s="7" t="n">
-        <v>21.16</v>
+        <v>21.54</v>
       </c>
     </row>
     <row r="133">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020650072-KIT4M054137987GJ</t>
+          <t>SMRT-05900510-LOS ANGELES CA-020955172-KIT4M05563526WNC</t>
         </is>
       </c>
       <c r="C133" s="3" t="n">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137987GJ</t>
+          <t>KIT4M05563526WNC</t>
         </is>
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>812795</t>
+          <t>814463</t>
         </is>
       </c>
       <c r="G133" s="5" t="inlineStr">
@@ -7573,7 +7573,7 @@
       </c>
       <c r="L133" s="5" t="n"/>
       <c r="M133" s="7" t="n">
-        <v>20.74</v>
+        <v>21.16</v>
       </c>
     </row>
     <row r="134">
@@ -7584,7 +7584,7 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482701112 - KIT4M04158973M2C</t>
+          <t>SS - 05900510 -  Los Angeles CA - 021437622 - KIT4M0587258755W</t>
         </is>
       </c>
       <c r="C134" s="3" t="n">
@@ -7595,12 +7595,12 @@
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158973M2C</t>
+          <t>KIT4M0587258755W</t>
         </is>
       </c>
       <c r="F134" s="4" t="inlineStr">
         <is>
-          <t>809610</t>
+          <t>816187</t>
         </is>
       </c>
       <c r="G134" s="5" t="inlineStr">
@@ -7626,7 +7626,7 @@
       </c>
       <c r="L134" s="5" t="n"/>
       <c r="M134" s="7" t="n">
-        <v>20.16</v>
+        <v>21.03</v>
       </c>
     </row>
     <row r="135">
@@ -7637,7 +7637,7 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 021437622 - KIT4M0587258755W</t>
+          <t>SMRT-05900510-Los Angeles CA-020650072-KIT4M054137987GJ</t>
         </is>
       </c>
       <c r="C135" s="3" t="n">
@@ -7648,12 +7648,12 @@
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0587258755W</t>
+          <t>KIT4M054137987GJ</t>
         </is>
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>816187</t>
+          <t>812795</t>
         </is>
       </c>
       <c r="G135" s="5" t="inlineStr">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="L135" s="5" t="n"/>
       <c r="M135" s="7" t="n">
-        <v>19.91</v>
+        <v>20.74</v>
       </c>
     </row>
     <row r="136">
@@ -7690,7 +7690,7 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649222 - KIT4P00065640BFW</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482701112 - KIT4M04158973M2C</t>
         </is>
       </c>
       <c r="C136" s="3" t="n">
@@ -7701,17 +7701,17 @@
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065640BFW</t>
+          <t>KIT4M04158973M2C</t>
         </is>
       </c>
       <c r="F136" s="4" t="inlineStr">
         <is>
-          <t>812929</t>
+          <t>809610</t>
         </is>
       </c>
       <c r="G136" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H136" s="5" t="inlineStr">
@@ -7732,7 +7732,7 @@
       </c>
       <c r="L136" s="5" t="n"/>
       <c r="M136" s="7" t="n">
-        <v>19.87</v>
+        <v>20.45</v>
       </c>
     </row>
     <row r="137">
@@ -7743,7 +7743,7 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649912 - KIT4M05413836KJC</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649222 - KIT4P00065640BFW</t>
         </is>
       </c>
       <c r="C137" s="3" t="n">
@@ -7754,17 +7754,17 @@
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413836KJC</t>
+          <t>KIT4P00065640BFW</t>
         </is>
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>810097</t>
+          <t>812929</t>
         </is>
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr">
@@ -7785,7 +7785,7 @@
       </c>
       <c r="L137" s="5" t="n"/>
       <c r="M137" s="7" t="n">
-        <v>19.73</v>
+        <v>19.87</v>
       </c>
     </row>
     <row r="138">
@@ -7796,7 +7796,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020650242 - KIT4M05413804SKS</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649912 - KIT4M05413836KJC</t>
         </is>
       </c>
       <c r="C138" s="3" t="n">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413804SKS</t>
+          <t>KIT4M05413836KJC</t>
         </is>
       </c>
       <c r="F138" s="4" t="inlineStr">
         <is>
-          <t>810102</t>
+          <t>810097</t>
         </is>
       </c>
       <c r="G138" s="5" t="inlineStr">
@@ -7838,7 +7838,7 @@
       </c>
       <c r="L138" s="5" t="n"/>
       <c r="M138" s="7" t="n">
-        <v>19.68</v>
+        <v>19.73</v>
       </c>
     </row>
     <row r="139">
@@ -7849,7 +7849,7 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649302 - KIT4M05368226W57</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020650242 - KIT4M05413804SKS</t>
         </is>
       </c>
       <c r="C139" s="3" t="n">
@@ -7860,12 +7860,12 @@
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368226W57</t>
+          <t>KIT4M05413804SKS</t>
         </is>
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>810833</t>
+          <t>810102</t>
         </is>
       </c>
       <c r="G139" s="5" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="L139" s="5" t="n"/>
       <c r="M139" s="7" t="n">
-        <v>19.62</v>
+        <v>19.68</v>
       </c>
     </row>
     <row r="140">
@@ -7902,7 +7902,7 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955282 - KIT4M055635227ZR</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649302 - KIT4M05368226W57</t>
         </is>
       </c>
       <c r="C140" s="3" t="n">
@@ -7913,12 +7913,12 @@
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635227ZR</t>
+          <t>KIT4M05368226W57</t>
         </is>
       </c>
       <c r="F140" s="4" t="inlineStr">
         <is>
-          <t>814482</t>
+          <t>810833</t>
         </is>
       </c>
       <c r="G140" s="5" t="inlineStr">
@@ -7944,7 +7944,7 @@
       </c>
       <c r="L140" s="5" t="n"/>
       <c r="M140" s="7" t="n">
-        <v>19.17</v>
+        <v>19.62</v>
       </c>
     </row>
     <row r="141">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="L141" s="5" t="n"/>
       <c r="M141" s="7" t="n">
-        <v>19.15</v>
+        <v>19.27</v>
       </c>
     </row>
     <row r="142">
@@ -8008,7 +8008,7 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955302 - KIT4M055635158PC</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955282 - KIT4M055635227ZR</t>
         </is>
       </c>
       <c r="C142" s="3" t="n">
@@ -8019,12 +8019,12 @@
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635158PC</t>
+          <t>KIT4M055635227ZR</t>
         </is>
       </c>
       <c r="F142" s="4" t="inlineStr">
         <is>
-          <t>814457</t>
+          <t>814482</t>
         </is>
       </c>
       <c r="G142" s="5" t="inlineStr">
@@ -8050,7 +8050,7 @@
       </c>
       <c r="L142" s="5" t="n"/>
       <c r="M142" s="7" t="n">
-        <v>18.73</v>
+        <v>19.17</v>
       </c>
     </row>
     <row r="143">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA  - 020649722 - KIT4M04604747TPT</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955302 - KIT4M055635158PC</t>
         </is>
       </c>
       <c r="C143" s="3" t="n">
@@ -8072,12 +8072,12 @@
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604747TPT</t>
+          <t>KIT4M055635158PC</t>
         </is>
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>809873</t>
+          <t>814457</t>
         </is>
       </c>
       <c r="G143" s="5" t="inlineStr">
@@ -8103,7 +8103,7 @@
       </c>
       <c r="L143" s="5" t="n"/>
       <c r="M143" s="7" t="n">
-        <v>18.44</v>
+        <v>18.74</v>
       </c>
     </row>
     <row r="144">
@@ -8114,7 +8114,7 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649212 - KIT4P00065633ZXC</t>
+          <t>SS - 05900510 - Los Angeles, CA  - 020649722 - KIT4M04604747TPT</t>
         </is>
       </c>
       <c r="C144" s="3" t="n">
@@ -8125,17 +8125,17 @@
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065633ZXC</t>
+          <t>KIT4M04604747TPT</t>
         </is>
       </c>
       <c r="F144" s="4" t="inlineStr">
         <is>
-          <t>812922</t>
+          <t>809873</t>
         </is>
       </c>
       <c r="G144" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H144" s="5" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="L144" s="5" t="n"/>
       <c r="M144" s="7" t="n">
-        <v>18.13</v>
+        <v>18.44</v>
       </c>
     </row>
     <row r="145">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649592 - KIT4M05413787HHK</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649452 - KIT4M05413785QCG</t>
         </is>
       </c>
       <c r="C146" s="3" t="n">
@@ -8231,12 +8231,12 @@
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413787HHK</t>
+          <t>KIT4M05413785QCG</t>
         </is>
       </c>
       <c r="F146" s="4" t="inlineStr">
         <is>
-          <t>812809</t>
+          <t>812806</t>
         </is>
       </c>
       <c r="G146" s="5" t="inlineStr">
@@ -8262,7 +8262,7 @@
       </c>
       <c r="L146" s="5" t="n"/>
       <c r="M146" s="7" t="n">
-        <v>15.65</v>
+        <v>16.64</v>
       </c>
     </row>
     <row r="147">
@@ -8273,7 +8273,7 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482708 - KIT4M04604736T7C</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649592 - KIT4M05413787HHK</t>
         </is>
       </c>
       <c r="C147" s="3" t="n">
@@ -8284,12 +8284,12 @@
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604736T7C</t>
+          <t>KIT4M05413787HHK</t>
         </is>
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>809662</t>
+          <t>812809</t>
         </is>
       </c>
       <c r="G147" s="5" t="inlineStr">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="L147" s="5" t="n"/>
       <c r="M147" s="7" t="n">
-        <v>15.55</v>
+        <v>15.65</v>
       </c>
     </row>
     <row r="148">
@@ -8326,7 +8326,7 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649452 - KIT4M05413785QCG</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482708 - KIT4M04604736T7C</t>
         </is>
       </c>
       <c r="C148" s="3" t="n">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413785QCG</t>
+          <t>KIT4M04604736T7C</t>
         </is>
       </c>
       <c r="F148" s="4" t="inlineStr">
         <is>
-          <t>812806</t>
+          <t>809662</t>
         </is>
       </c>
       <c r="G148" s="5" t="inlineStr">
@@ -8368,7 +8368,7 @@
       </c>
       <c r="L148" s="5" t="n"/>
       <c r="M148" s="7" t="n">
-        <v>15.4</v>
+        <v>15.55</v>
       </c>
     </row>
     <row r="149">
@@ -8379,7 +8379,7 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955712 - KIT4M05563586ZTR</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649832 - KIT4M03866596RZG</t>
         </is>
       </c>
       <c r="C149" s="3" t="n">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563586ZTR</t>
+          <t>KIT4M03866596RZG</t>
         </is>
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>814445</t>
+          <t>809869</t>
         </is>
       </c>
       <c r="G149" s="5" t="inlineStr">
@@ -8421,7 +8421,7 @@
       </c>
       <c r="L149" s="5" t="n"/>
       <c r="M149" s="7" t="n">
-        <v>15.1</v>
+        <v>15.46</v>
       </c>
     </row>
     <row r="150">
@@ -8432,7 +8432,7 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438222 - KIT4M058725299QP</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955712 - KIT4M05563586ZTR</t>
         </is>
       </c>
       <c r="C150" s="3" t="n">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725299QP</t>
+          <t>KIT4M05563586ZTR</t>
         </is>
       </c>
       <c r="F150" s="4" t="inlineStr">
         <is>
-          <t>816080</t>
+          <t>814445</t>
         </is>
       </c>
       <c r="G150" s="5" t="inlineStr">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="L150" s="5" t="n"/>
       <c r="M150" s="7" t="n">
-        <v>14.51</v>
+        <v>15.39</v>
       </c>
     </row>
     <row r="151">
@@ -8485,7 +8485,7 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020649862 - KIT4M04475159PMD</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437992 -  KIT4M05799663CPM</t>
         </is>
       </c>
       <c r="C151" s="3" t="n">
@@ -8496,12 +8496,12 @@
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475159PMD</t>
+          <t>KIT4M05799663CPM</t>
         </is>
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>809868</t>
+          <t>816272</t>
         </is>
       </c>
       <c r="G151" s="5" t="inlineStr">
@@ -8527,7 +8527,7 @@
       </c>
       <c r="L151" s="5" t="n"/>
       <c r="M151" s="7" t="n">
-        <v>14.45</v>
+        <v>14.71</v>
       </c>
     </row>
     <row r="152">
@@ -8538,7 +8538,7 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - CW6642812 - KIT4M054138292ZP</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438222 - KIT4M058725299QP</t>
         </is>
       </c>
       <c r="C152" s="3" t="n">
@@ -8549,12 +8549,12 @@
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138292ZP</t>
+          <t>KIT4M058725299QP</t>
         </is>
       </c>
       <c r="F152" s="4" t="inlineStr">
         <is>
-          <t>812784</t>
+          <t>816080</t>
         </is>
       </c>
       <c r="G152" s="5" t="inlineStr">
@@ -8580,7 +8580,7 @@
       </c>
       <c r="L152" s="5" t="n"/>
       <c r="M152" s="7" t="n">
-        <v>14.37</v>
+        <v>14.7</v>
       </c>
     </row>
     <row r="153">
@@ -8591,7 +8591,7 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437992 -  KIT4M05799663CPM</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020649862 - KIT4M04475159PMD</t>
         </is>
       </c>
       <c r="C153" s="3" t="n">
@@ -8602,12 +8602,12 @@
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799663CPM</t>
+          <t>KIT4M04475159PMD</t>
         </is>
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>816272</t>
+          <t>809868</t>
         </is>
       </c>
       <c r="G153" s="5" t="inlineStr">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="L153" s="5" t="n"/>
       <c r="M153" s="7" t="n">
-        <v>14.19</v>
+        <v>14.45</v>
       </c>
     </row>
     <row r="154">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438072 - KIT4M057996885ZV</t>
+          <t>SMA - 05900510 - Los Angeles CA - CW6642812 - KIT4M054138292ZP</t>
         </is>
       </c>
       <c r="C154" s="3" t="n">
@@ -8655,12 +8655,12 @@
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>KIT4M057996885ZV</t>
+          <t>KIT4M054138292ZP</t>
         </is>
       </c>
       <c r="F154" s="4" t="inlineStr">
         <is>
-          <t>816269</t>
+          <t>812784</t>
         </is>
       </c>
       <c r="G154" s="5" t="inlineStr">
@@ -8686,7 +8686,7 @@
       </c>
       <c r="L154" s="5" t="n"/>
       <c r="M154" s="7" t="n">
-        <v>13.64</v>
+        <v>14.37</v>
       </c>
     </row>
     <row r="155">
@@ -8739,7 +8739,7 @@
       </c>
       <c r="L155" s="5" t="n"/>
       <c r="M155" s="7" t="n">
-        <v>13.53</v>
+        <v>14.26</v>
       </c>
     </row>
     <row r="156">
@@ -8750,7 +8750,7 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649442 - KIT4M054137885SM</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438072 - KIT4M057996885ZV</t>
         </is>
       </c>
       <c r="C156" s="3" t="n">
@@ -8761,12 +8761,12 @@
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137885SM</t>
+          <t>KIT4M057996885ZV</t>
         </is>
       </c>
       <c r="F156" s="4" t="inlineStr">
         <is>
-          <t>812846</t>
+          <t>816269</t>
         </is>
       </c>
       <c r="G156" s="5" t="inlineStr">
@@ -8792,7 +8792,7 @@
       </c>
       <c r="L156" s="5" t="n"/>
       <c r="M156" s="7" t="n">
-        <v>13.24</v>
+        <v>13.64</v>
       </c>
     </row>
     <row r="157">
@@ -8803,7 +8803,7 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955362 - KIT4M05563528MKX</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649442 - KIT4M054137885SM</t>
         </is>
       </c>
       <c r="C157" s="3" t="n">
@@ -8814,12 +8814,12 @@
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563528MKX</t>
+          <t>KIT4M054137885SM</t>
         </is>
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>814471</t>
+          <t>812846</t>
         </is>
       </c>
       <c r="G157" s="5" t="inlineStr">
@@ -8845,7 +8845,7 @@
       </c>
       <c r="L157" s="5" t="n"/>
       <c r="M157" s="7" t="n">
-        <v>12.81</v>
+        <v>13.24</v>
       </c>
     </row>
     <row r="158">
@@ -8856,7 +8856,7 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649832 - KIT4M03866596RZG</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955362 - KIT4M05563528MKX</t>
         </is>
       </c>
       <c r="C158" s="3" t="n">
@@ -8867,12 +8867,12 @@
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03866596RZG</t>
+          <t>KIT4M05563528MKX</t>
         </is>
       </c>
       <c r="F158" s="4" t="inlineStr">
         <is>
-          <t>809869</t>
+          <t>814471</t>
         </is>
       </c>
       <c r="G158" s="5" t="inlineStr">
@@ -8898,7 +8898,7 @@
       </c>
       <c r="L158" s="5" t="n"/>
       <c r="M158" s="7" t="n">
-        <v>12.21</v>
+        <v>12.86</v>
       </c>
     </row>
     <row r="159">
@@ -8909,7 +8909,7 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955402 - KIT4M05563610HM2</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438242 - KIT4M058725094XP</t>
         </is>
       </c>
       <c r="C159" s="3" t="n">
@@ -8920,12 +8920,12 @@
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563610HM2</t>
+          <t>KIT4M058725094XP</t>
         </is>
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>814486</t>
+          <t>816085</t>
         </is>
       </c>
       <c r="G159" s="5" t="inlineStr">
@@ -8951,7 +8951,7 @@
       </c>
       <c r="L159" s="5" t="n"/>
       <c r="M159" s="7" t="n">
-        <v>11.39</v>
+        <v>12.73</v>
       </c>
     </row>
     <row r="160">
@@ -8962,7 +8962,7 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955482 - KIT4M055635088NK</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955402 - KIT4M05563610HM2</t>
         </is>
       </c>
       <c r="C160" s="3" t="n">
@@ -8973,12 +8973,12 @@
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635088NK</t>
+          <t>KIT4M05563610HM2</t>
         </is>
       </c>
       <c r="F160" s="4" t="inlineStr">
         <is>
-          <t>814434</t>
+          <t>814486</t>
         </is>
       </c>
       <c r="G160" s="5" t="inlineStr">
@@ -9004,7 +9004,7 @@
       </c>
       <c r="L160" s="5" t="n"/>
       <c r="M160" s="7" t="n">
-        <v>11.33</v>
+        <v>11.62</v>
       </c>
     </row>
     <row r="161">
@@ -9015,7 +9015,7 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438242 - KIT4M058725094XP</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955482 - KIT4M055635088NK</t>
         </is>
       </c>
       <c r="C161" s="3" t="n">
@@ -9026,12 +9026,12 @@
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725094XP</t>
+          <t>KIT4M055635088NK</t>
         </is>
       </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
-          <t>816085</t>
+          <t>814434</t>
         </is>
       </c>
       <c r="G161" s="5" t="inlineStr">
@@ -9057,7 +9057,7 @@
       </c>
       <c r="L161" s="5" t="n"/>
       <c r="M161" s="7" t="n">
-        <v>11.25</v>
+        <v>11.39</v>
       </c>
     </row>
     <row r="162">
@@ -9216,7 +9216,7 @@
       </c>
       <c r="L164" s="5" t="n"/>
       <c r="M164" s="7" t="n">
-        <v>10.42</v>
+        <v>10.46</v>
       </c>
     </row>
     <row r="165">
@@ -9269,7 +9269,7 @@
       </c>
       <c r="L165" s="5" t="n"/>
       <c r="M165" s="7" t="n">
-        <v>10.1</v>
+        <v>10.11</v>
       </c>
     </row>
     <row r="166">
@@ -9280,7 +9280,7 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955152 - KIT4M05563514P8T</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020955432 - KIT4M05563533M9N</t>
         </is>
       </c>
       <c r="C166" s="3" t="n">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563514P8T</t>
+          <t>KIT4M05563533M9N</t>
         </is>
       </c>
       <c r="F166" s="4" t="inlineStr">
         <is>
-          <t>814436</t>
+          <t>814485</t>
         </is>
       </c>
       <c r="G166" s="5" t="inlineStr">
@@ -9322,7 +9322,7 @@
       </c>
       <c r="L166" s="5" t="n"/>
       <c r="M166" s="7" t="n">
-        <v>9.73</v>
+        <v>9.81</v>
       </c>
     </row>
     <row r="167">
@@ -9333,7 +9333,7 @@
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649322 - KIT4M053683324KZ</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955152 - KIT4M05563514P8T</t>
         </is>
       </c>
       <c r="C167" s="3" t="n">
@@ -9344,12 +9344,12 @@
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>KIT4M053683324KZ</t>
+          <t>KIT4M05563514P8T</t>
         </is>
       </c>
       <c r="F167" s="4" t="inlineStr">
         <is>
-          <t>810832</t>
+          <t>814436</t>
         </is>
       </c>
       <c r="G167" s="5" t="inlineStr">
@@ -9375,7 +9375,7 @@
       </c>
       <c r="L167" s="5" t="n"/>
       <c r="M167" s="7" t="n">
-        <v>9.710000000000001</v>
+        <v>9.81</v>
       </c>
     </row>
     <row r="168">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020955432 - KIT4M05563533M9N</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649322 - KIT4M053683324KZ</t>
         </is>
       </c>
       <c r="C168" s="3" t="n">
@@ -9397,12 +9397,12 @@
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563533M9N</t>
+          <t>KIT4M053683324KZ</t>
         </is>
       </c>
       <c r="F168" s="4" t="inlineStr">
         <is>
-          <t>814485</t>
+          <t>810832</t>
         </is>
       </c>
       <c r="G168" s="5" t="inlineStr">
@@ -9428,7 +9428,7 @@
       </c>
       <c r="L168" s="5" t="n"/>
       <c r="M168" s="7" t="n">
-        <v>9.470000000000001</v>
+        <v>9.710000000000001</v>
       </c>
     </row>
     <row r="169">
@@ -9693,7 +9693,7 @@
       </c>
       <c r="L173" s="5" t="n"/>
       <c r="M173" s="7" t="n">
-        <v>8.26</v>
+        <v>8.52</v>
       </c>
     </row>
     <row r="174">
@@ -9958,7 +9958,7 @@
       </c>
       <c r="L178" s="5" t="n"/>
       <c r="M178" s="7" t="n">
-        <v>6.07</v>
+        <v>6.09</v>
       </c>
     </row>
     <row r="179">
@@ -10340,7 +10340,7 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827012 - KIT4M04606110GTV</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270114 - KIT4M04476539RJ5</t>
         </is>
       </c>
       <c r="C186" s="3" t="n">
@@ -10351,12 +10351,12 @@
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04606110GTV</t>
+          <t>KIT4M04476539RJ5</t>
         </is>
       </c>
       <c r="F186" s="4" t="inlineStr">
         <is>
-          <t>809660</t>
+          <t>809612</t>
         </is>
       </c>
       <c r="G186" s="5" t="inlineStr">
@@ -10382,7 +10382,7 @@
       </c>
       <c r="L186" s="5" t="n"/>
       <c r="M186" s="7" t="n">
-        <v>2.61</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="187">
@@ -10393,7 +10393,7 @@
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270114 - KIT4M04476539RJ5</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827012 - KIT4M04606110GTV</t>
         </is>
       </c>
       <c r="C187" s="3" t="n">
@@ -10404,12 +10404,12 @@
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04476539RJ5</t>
+          <t>KIT4M04606110GTV</t>
         </is>
       </c>
       <c r="F187" s="4" t="inlineStr">
         <is>
-          <t>809612</t>
+          <t>809660</t>
         </is>
       </c>
       <c r="G187" s="5" t="inlineStr">
@@ -10435,7 +10435,7 @@
       </c>
       <c r="L187" s="5" t="n"/>
       <c r="M187" s="7" t="n">
-        <v>2.53</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="188">
@@ -10700,7 +10700,7 @@
       </c>
       <c r="L192" s="5" t="n"/>
       <c r="M192" s="7" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="193">
@@ -10764,7 +10764,7 @@
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438282 - KIT4M05872508VTN</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437582 - KIT4M05872573K7P</t>
         </is>
       </c>
       <c r="C194" s="3" t="n">
@@ -10775,12 +10775,12 @@
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872508VTN</t>
+          <t>KIT4M05872573K7P</t>
         </is>
       </c>
       <c r="F194" s="4" t="inlineStr">
         <is>
-          <t>816076</t>
+          <t>816067</t>
         </is>
       </c>
       <c r="G194" s="5" t="inlineStr">
@@ -10806,7 +10806,7 @@
       </c>
       <c r="L194" s="5" t="n"/>
       <c r="M194" s="7" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="195">
@@ -10817,7 +10817,7 @@
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491804TBC</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438282 - KIT4M05872508VTN</t>
         </is>
       </c>
       <c r="C195" s="3" t="n">
@@ -10828,12 +10828,12 @@
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491804TBC</t>
+          <t>KIT4M05872508VTN</t>
         </is>
       </c>
       <c r="F195" s="4" t="inlineStr">
         <is>
-          <t>816373</t>
+          <t>816076</t>
         </is>
       </c>
       <c r="G195" s="5" t="inlineStr">
@@ -10859,7 +10859,7 @@
       </c>
       <c r="L195" s="5" t="n"/>
       <c r="M195" s="7" t="n">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="196">
@@ -10870,7 +10870,7 @@
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>SSC - 05900510 - Los Angeles CA - 021437792 - KIT4M05872507528</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491804TBC</t>
         </is>
       </c>
       <c r="C196" s="3" t="n">
@@ -10881,12 +10881,12 @@
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872507528</t>
+          <t>KIT4M06491804TBC</t>
         </is>
       </c>
       <c r="F196" s="4" t="inlineStr">
         <is>
-          <t>816083</t>
+          <t>816373</t>
         </is>
       </c>
       <c r="G196" s="5" t="inlineStr">
@@ -10912,7 +10912,7 @@
       </c>
       <c r="L196" s="5" t="n"/>
       <c r="M196" s="7" t="n">
-        <v>0.38</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="197">
@@ -10923,7 +10923,7 @@
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491800F52</t>
+          <t>SSC - 05900510 - Los Angeles CA - 021437792 - KIT4M05872507528</t>
         </is>
       </c>
       <c r="C197" s="3" t="n">
@@ -10934,12 +10934,12 @@
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491800F52</t>
+          <t>KIT4M05872507528</t>
         </is>
       </c>
       <c r="F197" s="4" t="inlineStr">
         <is>
-          <t>816406</t>
+          <t>816083</t>
         </is>
       </c>
       <c r="G197" s="5" t="inlineStr">
@@ -10965,7 +10965,7 @@
       </c>
       <c r="L197" s="5" t="n"/>
       <c r="M197" s="7" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="198">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437812-KIT4M058724947VX</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491800F52</t>
         </is>
       </c>
       <c r="C198" s="3" t="n">
@@ -10987,12 +10987,12 @@
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058724947VX</t>
+          <t>KIT4M06491800F52</t>
         </is>
       </c>
       <c r="F198" s="4" t="inlineStr">
         <is>
-          <t>816086</t>
+          <t>816406</t>
         </is>
       </c>
       <c r="G198" s="5" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="L198" s="5" t="n"/>
       <c r="M198" s="7" t="n">
-        <v>0.26</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="199">
@@ -11029,7 +11029,7 @@
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437592 - KIT4M05872582TC7</t>
+          <t>SMRT-05900510-Los Angeles CA-021437812-KIT4M058724947VX</t>
         </is>
       </c>
       <c r="C199" s="3" t="n">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872582TC7</t>
+          <t>KIT4M058724947VX</t>
         </is>
       </c>
       <c r="F199" s="4" t="inlineStr">
         <is>
-          <t>816107</t>
+          <t>816086</t>
         </is>
       </c>
       <c r="G199" s="5" t="inlineStr">
@@ -11071,7 +11071,7 @@
       </c>
       <c r="L199" s="5" t="n"/>
       <c r="M199" s="7" t="n">
-        <v>0.23</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="200">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020649522-KIT4M05413834FTH</t>
+          <t>SS - 05900510 - Los Angeles CA - 020650062 - KIT4M05413797HK5</t>
         </is>
       </c>
       <c r="C200" s="3" t="n">
@@ -11093,12 +11093,12 @@
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413834FTH</t>
+          <t>KIT4M05413797HK5</t>
         </is>
       </c>
       <c r="F200" s="4" t="inlineStr">
         <is>
-          <t>812817</t>
+          <t>812808</t>
         </is>
       </c>
       <c r="G200" s="5" t="inlineStr">
@@ -11124,7 +11124,7 @@
       </c>
       <c r="L200" s="5" t="n"/>
       <c r="M200" s="7" t="n">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="201">
@@ -11135,7 +11135,7 @@
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 6862083  - KIT4M05799682BXX</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437592 - KIT4M05872582TC7</t>
         </is>
       </c>
       <c r="C201" s="3" t="n">
@@ -11146,12 +11146,12 @@
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799682BXX</t>
+          <t>KIT4M05872582TC7</t>
         </is>
       </c>
       <c r="F201" s="4" t="inlineStr">
         <is>
-          <t>816278</t>
+          <t>816107</t>
         </is>
       </c>
       <c r="G201" s="5" t="inlineStr">
@@ -11177,7 +11177,7 @@
       </c>
       <c r="L201" s="5" t="n"/>
       <c r="M201" s="7" t="n">
-        <v>0.19</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="202">
@@ -11188,7 +11188,7 @@
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437832 - KIT4M05872486FXZ</t>
+          <t>SMRT-05900510-Los Angeles CA-020649522-KIT4M05413834FTH</t>
         </is>
       </c>
       <c r="C202" s="3" t="n">
@@ -11199,12 +11199,12 @@
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872486FXZ</t>
+          <t>KIT4M05413834FTH</t>
         </is>
       </c>
       <c r="F202" s="4" t="inlineStr">
         <is>
-          <t>816088</t>
+          <t>812817</t>
         </is>
       </c>
       <c r="G202" s="5" t="inlineStr">
@@ -11230,7 +11230,7 @@
       </c>
       <c r="L202" s="5" t="n"/>
       <c r="M202" s="7" t="n">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="203">
@@ -11241,7 +11241,7 @@
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955422 - KIT4M05563517BVR</t>
+          <t>SS - 05900510 - Los Angeles CA - 6862083  - KIT4M05799682BXX</t>
         </is>
       </c>
       <c r="C203" s="3" t="n">
@@ -11252,12 +11252,12 @@
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563517BVR</t>
+          <t>KIT4M05799682BXX</t>
         </is>
       </c>
       <c r="F203" s="4" t="inlineStr">
         <is>
-          <t>814438</t>
+          <t>816278</t>
         </is>
       </c>
       <c r="G203" s="5" t="inlineStr">
@@ -11283,7 +11283,7 @@
       </c>
       <c r="L203" s="5" t="n"/>
       <c r="M203" s="7" t="n">
-        <v>0.16</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="204">
@@ -11294,7 +11294,7 @@
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491790945</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437832 - KIT4M05872486FXZ</t>
         </is>
       </c>
       <c r="C204" s="3" t="n">
@@ -11305,12 +11305,12 @@
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491790945</t>
+          <t>KIT4M05872486FXZ</t>
         </is>
       </c>
       <c r="F204" s="4" t="inlineStr">
         <is>
-          <t>816410</t>
+          <t>816088</t>
         </is>
       </c>
       <c r="G204" s="5" t="inlineStr">
@@ -11336,7 +11336,7 @@
       </c>
       <c r="L204" s="5" t="n"/>
       <c r="M204" s="7" t="n">
-        <v>0.14</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="205">
@@ -11347,7 +11347,7 @@
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491836Z2D</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955422 - KIT4M05563517BVR</t>
         </is>
       </c>
       <c r="C205" s="3" t="n">
@@ -11358,12 +11358,12 @@
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491836Z2D</t>
+          <t>KIT4M05563517BVR</t>
         </is>
       </c>
       <c r="F205" s="4" t="inlineStr">
         <is>
-          <t>816366</t>
+          <t>814438</t>
         </is>
       </c>
       <c r="G205" s="5" t="inlineStr">
@@ -11389,7 +11389,7 @@
       </c>
       <c r="L205" s="5" t="n"/>
       <c r="M205" s="7" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="206">
@@ -11400,7 +11400,7 @@
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438172 - KIT4M05872500684</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491790945</t>
         </is>
       </c>
       <c r="C206" s="3" t="n">
@@ -11411,12 +11411,12 @@
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872500684</t>
+          <t>KIT4M06491790945</t>
         </is>
       </c>
       <c r="F206" s="4" t="inlineStr">
         <is>
-          <t>816081</t>
+          <t>816410</t>
         </is>
       </c>
       <c r="G206" s="5" t="inlineStr">
@@ -11453,7 +11453,7 @@
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 6862083  - KIT4M057996395ZF</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491836Z2D</t>
         </is>
       </c>
       <c r="C207" s="3" t="n">
@@ -11464,12 +11464,12 @@
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>KIT4M057996395ZF</t>
+          <t>KIT4M06491836Z2D</t>
         </is>
       </c>
       <c r="F207" s="4" t="inlineStr">
         <is>
-          <t>816268</t>
+          <t>816366</t>
         </is>
       </c>
       <c r="G207" s="5" t="inlineStr">
@@ -11506,7 +11506,7 @@
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437412 - KIT4M05872548P2H</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438172 - KIT4M05872500684</t>
         </is>
       </c>
       <c r="C208" s="3" t="n">
@@ -11517,12 +11517,12 @@
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872548P2H</t>
+          <t>KIT4M05872500684</t>
         </is>
       </c>
       <c r="F208" s="4" t="inlineStr">
         <is>
-          <t>816066</t>
+          <t>816081</t>
         </is>
       </c>
       <c r="G208" s="5" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="L208" s="5" t="n"/>
       <c r="M208" s="7" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="209">
@@ -11559,7 +11559,7 @@
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491814FV7</t>
+          <t>SS - 05900510 - Los Angeles CA - 6862083  - KIT4M057996395ZF</t>
         </is>
       </c>
       <c r="C209" s="3" t="n">
@@ -11570,12 +11570,12 @@
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491814FV7</t>
+          <t>KIT4M057996395ZF</t>
         </is>
       </c>
       <c r="F209" s="4" t="inlineStr">
         <is>
-          <t>816370</t>
+          <t>816268</t>
         </is>
       </c>
       <c r="G209" s="5" t="inlineStr">
@@ -11601,7 +11601,7 @@
       </c>
       <c r="L209" s="5" t="n"/>
       <c r="M209" s="7" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="210">
@@ -11612,7 +11612,7 @@
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437302 - KIT4M05872571T4K</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437412 - KIT4M05872548P2H</t>
         </is>
       </c>
       <c r="C210" s="3" t="n">
@@ -11623,12 +11623,12 @@
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872571T4K</t>
+          <t>KIT4M05872548P2H</t>
         </is>
       </c>
       <c r="F210" s="4" t="inlineStr">
         <is>
-          <t>816106</t>
+          <t>816066</t>
         </is>
       </c>
       <c r="G210" s="5" t="inlineStr">
@@ -11654,7 +11654,7 @@
       </c>
       <c r="L210" s="5" t="n"/>
       <c r="M210" s="7" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="211">
@@ -11771,7 +11771,7 @@
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918277QF</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491814FV7</t>
         </is>
       </c>
       <c r="C213" s="3" t="n">
@@ -11782,12 +11782,12 @@
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918277QF</t>
+          <t>KIT4M06491814FV7</t>
         </is>
       </c>
       <c r="F213" s="4" t="inlineStr">
         <is>
-          <t>816403</t>
+          <t>816370</t>
         </is>
       </c>
       <c r="G213" s="5" t="inlineStr">
@@ -11813,7 +11813,7 @@
       </c>
       <c r="L213" s="5" t="n"/>
       <c r="M213" s="7" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="214">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437722 - KIT4M05872498PP4</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437302 - KIT4M05872571T4K</t>
         </is>
       </c>
       <c r="C214" s="3" t="n">
@@ -11835,12 +11835,12 @@
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872498PP4</t>
+          <t>KIT4M05872571T4K</t>
         </is>
       </c>
       <c r="F214" s="4" t="inlineStr">
         <is>
-          <t>816104</t>
+          <t>816106</t>
         </is>
       </c>
       <c r="G214" s="5" t="inlineStr">
@@ -11866,7 +11866,7 @@
       </c>
       <c r="L214" s="5" t="n"/>
       <c r="M214" s="7" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="215">
@@ -11877,7 +11877,7 @@
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437732 - KIT4M05872588W8G</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918277QF</t>
         </is>
       </c>
       <c r="C215" s="3" t="n">
@@ -11888,12 +11888,12 @@
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872588W8G</t>
+          <t>KIT4M064918277QF</t>
         </is>
       </c>
       <c r="F215" s="4" t="inlineStr">
         <is>
-          <t>816100</t>
+          <t>816403</t>
         </is>
       </c>
       <c r="G215" s="5" t="inlineStr">
@@ -11919,7 +11919,7 @@
       </c>
       <c r="L215" s="5" t="n"/>
       <c r="M215" s="7" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="216">
@@ -11930,7 +11930,7 @@
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437312 - KIT4M05872568PR6</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437722 - KIT4M05872498PP4</t>
         </is>
       </c>
       <c r="C216" s="3" t="n">
@@ -11941,12 +11941,12 @@
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872568PR6</t>
+          <t>KIT4M05872498PP4</t>
         </is>
       </c>
       <c r="F216" s="4" t="inlineStr">
         <is>
-          <t>816094</t>
+          <t>816104</t>
         </is>
       </c>
       <c r="G216" s="5" t="inlineStr">
@@ -12036,7 +12036,7 @@
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438252 - KIT4M05872519KTN</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437312 - KIT4M05872568PR6</t>
         </is>
       </c>
       <c r="C218" s="3" t="n">
@@ -12047,12 +12047,12 @@
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872519KTN</t>
+          <t>KIT4M05872568PR6</t>
         </is>
       </c>
       <c r="F218" s="4" t="inlineStr">
         <is>
-          <t>816084</t>
+          <t>816094</t>
         </is>
       </c>
       <c r="G218" s="5" t="inlineStr">
@@ -12089,7 +12089,7 @@
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491821G25</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437732 - KIT4M05872588W8G</t>
         </is>
       </c>
       <c r="C219" s="3" t="n">
@@ -12100,12 +12100,12 @@
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491821G25</t>
+          <t>KIT4M05872588W8G</t>
         </is>
       </c>
       <c r="F219" s="4" t="inlineStr">
         <is>
-          <t>816379</t>
+          <t>816100</t>
         </is>
       </c>
       <c r="G219" s="5" t="inlineStr">
@@ -12142,7 +12142,7 @@
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438112 - KIT4M0579970825J</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438252 - KIT4M05872519KTN</t>
         </is>
       </c>
       <c r="C220" s="3" t="n">
@@ -12153,12 +12153,12 @@
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0579970825J</t>
+          <t>KIT4M05872519KTN</t>
         </is>
       </c>
       <c r="F220" s="4" t="inlineStr">
         <is>
-          <t>816290</t>
+          <t>816084</t>
         </is>
       </c>
       <c r="G220" s="5" t="inlineStr">
@@ -12184,7 +12184,7 @@
       </c>
       <c r="L220" s="5" t="n"/>
       <c r="M220" s="7" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="221">
@@ -12195,7 +12195,7 @@
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491817T79</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491821G25</t>
         </is>
       </c>
       <c r="C221" s="3" t="n">
@@ -12206,12 +12206,12 @@
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491817T79</t>
+          <t>KIT4M06491821G25</t>
         </is>
       </c>
       <c r="F221" s="4" t="inlineStr">
         <is>
-          <t>816415</t>
+          <t>816379</t>
         </is>
       </c>
       <c r="G221" s="5" t="inlineStr">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="L221" s="5" t="n"/>
       <c r="M221" s="7" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="222">
@@ -12248,7 +12248,7 @@
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437752 - KIT4M05872577TWT</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918154FM</t>
         </is>
       </c>
       <c r="C222" s="3" t="n">
@@ -12259,12 +12259,12 @@
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872577TWT</t>
+          <t>KIT4M064918154FM</t>
         </is>
       </c>
       <c r="F222" s="4" t="inlineStr">
         <is>
-          <t>816212</t>
+          <t>816368</t>
         </is>
       </c>
       <c r="G222" s="5" t="inlineStr">
@@ -12301,7 +12301,7 @@
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438262 - KIT4M05872530RPF</t>
+          <t>SSC - 05900510 -  Los Angeles CA - 021437862 - KIT4M05872516CJM</t>
         </is>
       </c>
       <c r="C223" s="3" t="n">
@@ -12312,12 +12312,12 @@
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872530RPF</t>
+          <t>KIT4M05872516CJM</t>
         </is>
       </c>
       <c r="F223" s="4" t="inlineStr">
         <is>
-          <t>816079</t>
+          <t>816087</t>
         </is>
       </c>
       <c r="G223" s="5" t="inlineStr">
@@ -12354,7 +12354,7 @@
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491799CRP</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438112 - KIT4M0579970825J</t>
         </is>
       </c>
       <c r="C224" s="3" t="n">
@@ -12365,12 +12365,12 @@
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491799CRP</t>
+          <t>KIT4M0579970825J</t>
         </is>
       </c>
       <c r="F224" s="4" t="inlineStr">
         <is>
-          <t>816394</t>
+          <t>816290</t>
         </is>
       </c>
       <c r="G224" s="5" t="inlineStr">
@@ -12407,7 +12407,7 @@
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437952 - KIT4M05872523VVB</t>
+          <t>SMRT-05900510-Los Angeles CA-021437822-KIT4M0587253378R</t>
         </is>
       </c>
       <c r="C225" s="3" t="n">
@@ -12418,12 +12418,12 @@
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872523VVB</t>
+          <t>KIT4M0587253378R</t>
         </is>
       </c>
       <c r="F225" s="4" t="inlineStr">
         <is>
-          <t>816215</t>
+          <t>816210</t>
         </is>
       </c>
       <c r="G225" s="5" t="inlineStr">
@@ -12566,7 +12566,7 @@
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437332 - KIT4M05872554RHM</t>
+          <t>SMRT-05900510-Los Angeles CA-021437712-KIT4M05872570FCC</t>
         </is>
       </c>
       <c r="C228" s="3" t="n">
@@ -12577,12 +12577,12 @@
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872554RHM</t>
+          <t>KIT4M05872570FCC</t>
         </is>
       </c>
       <c r="F228" s="4" t="inlineStr">
         <is>
-          <t>816071</t>
+          <t>816105</t>
         </is>
       </c>
       <c r="G228" s="5" t="inlineStr">
@@ -12619,7 +12619,7 @@
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>SSC - 05900510 -  Los Angeles CA - 021437862 - KIT4M05872516CJM</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437952 - KIT4M05872523VVB</t>
         </is>
       </c>
       <c r="C229" s="3" t="n">
@@ -12630,12 +12630,12 @@
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872516CJM</t>
+          <t>KIT4M05872523VVB</t>
         </is>
       </c>
       <c r="F229" s="4" t="inlineStr">
         <is>
-          <t>816087</t>
+          <t>816215</t>
         </is>
       </c>
       <c r="G229" s="5" t="inlineStr">
@@ -12672,7 +12672,7 @@
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437822-KIT4M0587253378R</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437332 - KIT4M05872554RHM</t>
         </is>
       </c>
       <c r="C230" s="3" t="n">
@@ -12683,12 +12683,12 @@
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0587253378R</t>
+          <t>KIT4M05872554RHM</t>
         </is>
       </c>
       <c r="F230" s="4" t="inlineStr">
         <is>
-          <t>816210</t>
+          <t>816071</t>
         </is>
       </c>
       <c r="G230" s="5" t="inlineStr">
@@ -12725,7 +12725,7 @@
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437462 - KIT4M05872575BC8</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491798S8Q</t>
         </is>
       </c>
       <c r="C231" s="3" t="n">
@@ -12736,12 +12736,12 @@
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872575BC8</t>
+          <t>KIT4M06491798S8Q</t>
         </is>
       </c>
       <c r="F231" s="4" t="inlineStr">
         <is>
-          <t>816103</t>
+          <t>816395</t>
         </is>
       </c>
       <c r="G231" s="5" t="inlineStr">
@@ -12778,7 +12778,7 @@
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437712-KIT4M05872570FCC</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437462 - KIT4M05872575BC8</t>
         </is>
       </c>
       <c r="C232" s="3" t="n">
@@ -12789,12 +12789,12 @@
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872570FCC</t>
+          <t>KIT4M05872575BC8</t>
         </is>
       </c>
       <c r="F232" s="4" t="inlineStr">
         <is>
-          <t>816105</t>
+          <t>816103</t>
         </is>
       </c>
       <c r="G232" s="5" t="inlineStr">
@@ -12831,7 +12831,7 @@
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064917925MB</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437802 - KIT4M05872589TM9</t>
         </is>
       </c>
       <c r="C233" s="3" t="n">
@@ -12842,12 +12842,12 @@
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064917925MB</t>
+          <t>KIT4M05872589TM9</t>
         </is>
       </c>
       <c r="F233" s="4" t="inlineStr">
         <is>
-          <t>816381</t>
+          <t>816195</t>
         </is>
       </c>
       <c r="G233" s="5" t="inlineStr">
@@ -13043,7 +13043,7 @@
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437802 - KIT4M05872589TM9</t>
+          <t>SMRT-05900510-Los Angeles CA-021437482-KIT4M05872578G7Q</t>
         </is>
       </c>
       <c r="C237" s="3" t="n">
@@ -13054,12 +13054,12 @@
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872589TM9</t>
+          <t>KIT4M05872578G7Q</t>
         </is>
       </c>
       <c r="F237" s="4" t="inlineStr">
         <is>
-          <t>816195</t>
+          <t>816102</t>
         </is>
       </c>
       <c r="G237" s="5" t="inlineStr">
@@ -13096,7 +13096,7 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437482-KIT4M05872578G7Q</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437752 - KIT4M05872577TWT</t>
         </is>
       </c>
       <c r="C238" s="3" t="n">
@@ -13107,12 +13107,12 @@
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872578G7Q</t>
+          <t>KIT4M05872577TWT</t>
         </is>
       </c>
       <c r="F238" s="4" t="inlineStr">
         <is>
-          <t>816102</t>
+          <t>816212</t>
         </is>
       </c>
       <c r="G238" s="5" t="inlineStr">
@@ -13255,7 +13255,7 @@
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491818QD2</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491820X58</t>
         </is>
       </c>
       <c r="C241" s="3" t="n">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491818QD2</t>
+          <t>KIT4M06491820X58</t>
         </is>
       </c>
       <c r="F241" s="4" t="inlineStr">
         <is>
-          <t>816378</t>
+          <t>816385</t>
         </is>
       </c>
       <c r="G241" s="5" t="inlineStr">
@@ -13308,7 +13308,7 @@
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491829CD2</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491826SQM</t>
         </is>
       </c>
       <c r="C242" s="3" t="n">
@@ -13319,12 +13319,12 @@
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491829CD2</t>
+          <t>KIT4M06491826SQM</t>
         </is>
       </c>
       <c r="F242" s="4" t="inlineStr">
         <is>
-          <t>816393</t>
+          <t>816380</t>
         </is>
       </c>
       <c r="G242" s="5" t="inlineStr">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491830G2J</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491829CD2</t>
         </is>
       </c>
       <c r="C243" s="3" t="n">
@@ -13372,12 +13372,12 @@
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491830G2J</t>
+          <t>KIT4M06491829CD2</t>
         </is>
       </c>
       <c r="F243" s="4" t="inlineStr">
         <is>
-          <t>816372</t>
+          <t>816393</t>
         </is>
       </c>
       <c r="G243" s="5" t="inlineStr">
@@ -13414,7 +13414,7 @@
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M0649183125S</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491830G2J</t>
         </is>
       </c>
       <c r="C244" s="3" t="n">
@@ -13425,12 +13425,12 @@
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0649183125S</t>
+          <t>KIT4M06491830G2J</t>
         </is>
       </c>
       <c r="F244" s="4" t="inlineStr">
         <is>
-          <t>816371</t>
+          <t>816372</t>
         </is>
       </c>
       <c r="G244" s="5" t="inlineStr">
@@ -13520,7 +13520,7 @@
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491826SQM</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918197VX</t>
         </is>
       </c>
       <c r="C246" s="3" t="n">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491826SQM</t>
+          <t>KIT4M064918197VX</t>
         </is>
       </c>
       <c r="F246" s="4" t="inlineStr">
         <is>
-          <t>816380</t>
+          <t>816397</t>
         </is>
       </c>
       <c r="G246" s="5" t="inlineStr">
@@ -13573,7 +13573,7 @@
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918197VX</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491818QD2</t>
         </is>
       </c>
       <c r="C247" s="3" t="n">
@@ -13584,12 +13584,12 @@
       </c>
       <c r="E247" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918197VX</t>
+          <t>KIT4M06491818QD2</t>
         </is>
       </c>
       <c r="F247" s="4" t="inlineStr">
         <is>
-          <t>816397</t>
+          <t>816378</t>
         </is>
       </c>
       <c r="G247" s="5" t="inlineStr">
@@ -13626,7 +13626,7 @@
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918154FM</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918165MW</t>
         </is>
       </c>
       <c r="C248" s="3" t="n">
@@ -13637,12 +13637,12 @@
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918154FM</t>
+          <t>KIT4M064918165MW</t>
         </is>
       </c>
       <c r="F248" s="4" t="inlineStr">
         <is>
-          <t>816368</t>
+          <t>816374</t>
         </is>
       </c>
       <c r="G248" s="5" t="inlineStr">
@@ -13679,7 +13679,7 @@
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491798S8Q</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491799CRP</t>
         </is>
       </c>
       <c r="C249" s="3" t="n">
@@ -13690,12 +13690,12 @@
       </c>
       <c r="E249" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491798S8Q</t>
+          <t>KIT4M06491799CRP</t>
         </is>
       </c>
       <c r="F249" s="4" t="inlineStr">
         <is>
-          <t>816395</t>
+          <t>816394</t>
         </is>
       </c>
       <c r="G249" s="5" t="inlineStr">
@@ -13732,7 +13732,7 @@
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491820X58</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M0649183125S</t>
         </is>
       </c>
       <c r="C250" s="3" t="n">
@@ -13743,12 +13743,12 @@
       </c>
       <c r="E250" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491820X58</t>
+          <t>KIT4M0649183125S</t>
         </is>
       </c>
       <c r="F250" s="4" t="inlineStr">
         <is>
-          <t>816385</t>
+          <t>816371</t>
         </is>
       </c>
       <c r="G250" s="5" t="inlineStr">
@@ -13785,7 +13785,7 @@
       </c>
       <c r="B251" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918165MW</t>
+          <t>SMRT-05900510-Los Angeles CA-021437882-KIT4M05872527QK6</t>
         </is>
       </c>
       <c r="C251" s="3" t="n">
@@ -13796,12 +13796,12 @@
       </c>
       <c r="E251" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918165MW</t>
+          <t>KIT4M05872527QK6</t>
         </is>
       </c>
       <c r="F251" s="4" t="inlineStr">
         <is>
-          <t>816374</t>
+          <t>816214</t>
         </is>
       </c>
       <c r="G251" s="5" t="inlineStr">
@@ -13838,7 +13838,7 @@
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437692 - KIT4M05872518P78</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491817T79</t>
         </is>
       </c>
       <c r="C252" s="3" t="n">
@@ -13849,12 +13849,12 @@
       </c>
       <c r="E252" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872518P78</t>
+          <t>KIT4M06491817T79</t>
         </is>
       </c>
       <c r="F252" s="4" t="inlineStr">
         <is>
-          <t>816184</t>
+          <t>816415</t>
         </is>
       </c>
       <c r="G252" s="5" t="inlineStr">
@@ -13891,7 +13891,7 @@
       </c>
       <c r="B253" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437882-KIT4M05872527QK6</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064917925MB</t>
         </is>
       </c>
       <c r="C253" s="3" t="n">
@@ -13902,12 +13902,12 @@
       </c>
       <c r="E253" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872527QK6</t>
+          <t>KIT4M064917925MB</t>
         </is>
       </c>
       <c r="F253" s="4" t="inlineStr">
         <is>
-          <t>816214</t>
+          <t>816381</t>
         </is>
       </c>
       <c r="G253" s="5" t="inlineStr">
@@ -13944,7 +13944,7 @@
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649892 - KIT4M05413777DGG</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438262 - KIT4M05872530RPF</t>
         </is>
       </c>
       <c r="C254" s="3" t="n">
@@ -13955,12 +13955,12 @@
       </c>
       <c r="E254" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413777DGG</t>
+          <t>KIT4M05872530RPF</t>
         </is>
       </c>
       <c r="F254" s="4" t="inlineStr">
         <is>
-          <t>812802</t>
+          <t>816079</t>
         </is>
       </c>
       <c r="G254" s="5" t="inlineStr">
@@ -13986,7 +13986,7 @@
       </c>
       <c r="L254" s="5" t="n"/>
       <c r="M254" s="7" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="255">
@@ -13997,7 +13997,7 @@
       </c>
       <c r="B255" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491833JGV</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437692 - KIT4M05872518P78</t>
         </is>
       </c>
       <c r="C255" s="3" t="n">
@@ -14008,12 +14008,12 @@
       </c>
       <c r="E255" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491833JGV</t>
+          <t>KIT4M05872518P78</t>
         </is>
       </c>
       <c r="F255" s="4" t="inlineStr">
         <is>
-          <t>816384</t>
+          <t>816184</t>
         </is>
       </c>
       <c r="G255" s="5" t="inlineStr">
@@ -14039,7 +14039,7 @@
       </c>
       <c r="L255" s="5" t="n"/>
       <c r="M255" s="7" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="256">
@@ -14050,7 +14050,7 @@
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918015Z2</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491795MWG</t>
         </is>
       </c>
       <c r="C256" s="3" t="n">
@@ -14061,12 +14061,12 @@
       </c>
       <c r="E256" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918015Z2</t>
+          <t>KIT4M06491795MWG</t>
         </is>
       </c>
       <c r="F256" s="4" t="inlineStr">
         <is>
-          <t>816376</t>
+          <t>816383</t>
         </is>
       </c>
       <c r="G256" s="5" t="inlineStr">
@@ -14103,7 +14103,7 @@
       </c>
       <c r="B257" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437402 - KIT4M05872537SGZ</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437372 - KIT4M058725505J5</t>
         </is>
       </c>
       <c r="C257" s="3" t="n">
@@ -14114,12 +14114,12 @@
       </c>
       <c r="E257" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872537SGZ</t>
+          <t>KIT4M058725505J5</t>
         </is>
       </c>
       <c r="F257" s="4" t="inlineStr">
         <is>
-          <t>816073</t>
+          <t>816117</t>
         </is>
       </c>
       <c r="G257" s="5" t="inlineStr">
@@ -14156,7 +14156,7 @@
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437662 - KIT4M05872534RXS</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437402 - KIT4M05872537SGZ</t>
         </is>
       </c>
       <c r="C258" s="3" t="n">
@@ -14167,12 +14167,12 @@
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872534RXS</t>
+          <t>KIT4M05872537SGZ</t>
         </is>
       </c>
       <c r="F258" s="4" t="inlineStr">
         <is>
-          <t>816216</t>
+          <t>816073</t>
         </is>
       </c>
       <c r="G258" s="5" t="inlineStr">
@@ -14209,7 +14209,7 @@
       </c>
       <c r="B259" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491813KGS</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437572 - KIT4M05872579JPF</t>
         </is>
       </c>
       <c r="C259" s="3" t="n">
@@ -14220,12 +14220,12 @@
       </c>
       <c r="E259" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491813KGS</t>
+          <t>KIT4M05872579JPF</t>
         </is>
       </c>
       <c r="F259" s="4" t="inlineStr">
         <is>
-          <t>816377</t>
+          <t>816111</t>
         </is>
       </c>
       <c r="G259" s="5" t="inlineStr">
@@ -14262,7 +14262,7 @@
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437572 - KIT4M05872579JPF</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437662 - KIT4M05872534RXS</t>
         </is>
       </c>
       <c r="C260" s="3" t="n">
@@ -14273,12 +14273,12 @@
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872579JPF</t>
+          <t>KIT4M05872534RXS</t>
         </is>
       </c>
       <c r="F260" s="4" t="inlineStr">
         <is>
-          <t>816111</t>
+          <t>816216</t>
         </is>
       </c>
       <c r="G260" s="5" t="inlineStr">
@@ -14315,7 +14315,7 @@
       </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437372 - KIT4M058725505J5</t>
+          <t>SS - 05900510 -  Los Angeles CA - 021437682 - KIT4M05872544BXG</t>
         </is>
       </c>
       <c r="C261" s="3" t="n">
@@ -14326,12 +14326,12 @@
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725505J5</t>
+          <t>KIT4M05872544BXG</t>
         </is>
       </c>
       <c r="F261" s="4" t="inlineStr">
         <is>
-          <t>816117</t>
+          <t>816176</t>
         </is>
       </c>
       <c r="G261" s="5" t="inlineStr">
@@ -14368,7 +14368,7 @@
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 021437682 - KIT4M05872544BXG</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491833JGV</t>
         </is>
       </c>
       <c r="C262" s="3" t="n">
@@ -14379,12 +14379,12 @@
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872544BXG</t>
+          <t>KIT4M06491833JGV</t>
         </is>
       </c>
       <c r="F262" s="4" t="inlineStr">
         <is>
-          <t>816176</t>
+          <t>816384</t>
         </is>
       </c>
       <c r="G262" s="5" t="inlineStr">
@@ -14474,7 +14474,7 @@
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491795MWG</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918015Z2</t>
         </is>
       </c>
       <c r="C264" s="3" t="n">
@@ -14485,12 +14485,12 @@
       </c>
       <c r="E264" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491795MWG</t>
+          <t>KIT4M064918015Z2</t>
         </is>
       </c>
       <c r="F264" s="4" t="inlineStr">
         <is>
-          <t>816383</t>
+          <t>816376</t>
         </is>
       </c>
       <c r="G264" s="5" t="inlineStr">
@@ -14580,7 +14580,7 @@
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438192 - KIT4M05872511F6P</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955542 - KIT4M05563551N6Q</t>
         </is>
       </c>
       <c r="C266" s="3" t="n">
@@ -14591,12 +14591,12 @@
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872511F6P</t>
+          <t>KIT4M05563551N6Q</t>
         </is>
       </c>
       <c r="F266" s="4" t="inlineStr">
         <is>
-          <t>816090</t>
+          <t>814450</t>
         </is>
       </c>
       <c r="G266" s="5" t="inlineStr">
@@ -14633,7 +14633,7 @@
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955542 - KIT4M05563551N6Q</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438192 - KIT4M05872511F6P</t>
         </is>
       </c>
       <c r="C267" s="3" t="n">
@@ -14644,12 +14644,12 @@
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563551N6Q</t>
+          <t>KIT4M05872511F6P</t>
         </is>
       </c>
       <c r="F267" s="4" t="inlineStr">
         <is>
-          <t>814450</t>
+          <t>816090</t>
         </is>
       </c>
       <c r="G267" s="5" t="inlineStr">
@@ -14686,7 +14686,7 @@
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA  - 020649572 - KIT4M05413816N8K</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491813KGS</t>
         </is>
       </c>
       <c r="C268" s="3" t="n">
@@ -14697,12 +14697,12 @@
       </c>
       <c r="E268" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413816N8K</t>
+          <t>KIT4M06491813KGS</t>
         </is>
       </c>
       <c r="F268" s="4" t="inlineStr">
         <is>
-          <t>812832</t>
+          <t>816377</t>
         </is>
       </c>
       <c r="G268" s="5" t="inlineStr">
@@ -14728,7 +14728,7 @@
       </c>
       <c r="L268" s="5" t="n"/>
       <c r="M268" s="7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="269">
@@ -14739,7 +14739,7 @@
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491797NCX</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649892 - KIT4M05413777DGG</t>
         </is>
       </c>
       <c r="C269" s="3" t="n">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E269" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491797NCX</t>
+          <t>KIT4M05413777DGG</t>
         </is>
       </c>
       <c r="F269" s="4" t="inlineStr">
         <is>
-          <t>816408</t>
+          <t>812802</t>
         </is>
       </c>
       <c r="G269" s="5" t="inlineStr">
@@ -14781,7 +14781,7 @@
       </c>
       <c r="L269" s="5" t="n"/>
       <c r="M269" s="7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="270">
@@ -14845,7 +14845,7 @@
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491808P4F</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491797NCX</t>
         </is>
       </c>
       <c r="C271" s="3" t="n">
@@ -14856,12 +14856,12 @@
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491808P4F</t>
+          <t>KIT4M06491797NCX</t>
         </is>
       </c>
       <c r="F271" s="4" t="inlineStr">
         <is>
-          <t>816399</t>
+          <t>816408</t>
         </is>
       </c>
       <c r="G271" s="5" t="inlineStr">
@@ -14898,7 +14898,7 @@
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438162 - KIT4M05799712SBX</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491808P4F</t>
         </is>
       </c>
       <c r="C272" s="3" t="n">
@@ -14909,12 +14909,12 @@
       </c>
       <c r="E272" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799712SBX</t>
+          <t>KIT4M06491808P4F</t>
         </is>
       </c>
       <c r="F272" s="4" t="inlineStr">
         <is>
-          <t>816276</t>
+          <t>816399</t>
         </is>
       </c>
       <c r="G272" s="5" t="inlineStr">
@@ -14940,7 +14940,7 @@
       </c>
       <c r="L272" s="5" t="n"/>
       <c r="M272" s="7" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="273">
@@ -14951,7 +14951,7 @@
       </c>
       <c r="B273" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491822SF6</t>
+          <t>SS - 05900510 - Los Angeles, CA  - 020649572 - KIT4M05413816N8K</t>
         </is>
       </c>
       <c r="C273" s="3" t="n">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E273" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491822SF6</t>
+          <t>KIT4M05413816N8K</t>
         </is>
       </c>
       <c r="F273" s="4" t="inlineStr">
         <is>
-          <t>816412</t>
+          <t>812832</t>
         </is>
       </c>
       <c r="G273" s="5" t="inlineStr">
@@ -14993,7 +14993,7 @@
       </c>
       <c r="L273" s="5" t="n"/>
       <c r="M273" s="7" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="274">
@@ -15004,7 +15004,7 @@
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918239TM</t>
+          <t>SMA - 05900510 -  Los Angeles CA - 020649602 - KIT4M05413773R6G</t>
         </is>
       </c>
       <c r="C274" s="3" t="n">
@@ -15015,12 +15015,12 @@
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918239TM</t>
+          <t>KIT4M05413773R6G</t>
         </is>
       </c>
       <c r="F274" s="4" t="inlineStr">
         <is>
-          <t>816398</t>
+          <t>812807</t>
         </is>
       </c>
       <c r="G274" s="5" t="inlineStr">
@@ -15046,7 +15046,7 @@
       </c>
       <c r="L274" s="5" t="n"/>
       <c r="M274" s="7" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="275">
@@ -15110,7 +15110,7 @@
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437382 - KIT4M058725438WP</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918239TM</t>
         </is>
       </c>
       <c r="C276" s="3" t="n">
@@ -15121,12 +15121,12 @@
       </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725438WP</t>
+          <t>KIT4M064918239TM</t>
         </is>
       </c>
       <c r="F276" s="4" t="inlineStr">
         <is>
-          <t>816115</t>
+          <t>816398</t>
         </is>
       </c>
       <c r="G276" s="5" t="inlineStr">
@@ -15163,7 +15163,7 @@
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649702 - KIT4M04604741P2X</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491822SF6</t>
         </is>
       </c>
       <c r="C277" s="3" t="n">
@@ -15174,12 +15174,12 @@
       </c>
       <c r="E277" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604741P2X</t>
+          <t>KIT4M06491822SF6</t>
         </is>
       </c>
       <c r="F277" s="4" t="inlineStr">
         <is>
-          <t>809871</t>
+          <t>816412</t>
         </is>
       </c>
       <c r="G277" s="5" t="inlineStr">
@@ -15205,7 +15205,7 @@
       </c>
       <c r="L277" s="5" t="n"/>
       <c r="M277" s="7" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="278">
@@ -15216,7 +15216,7 @@
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491837DPX</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437382 - KIT4M058725438WP</t>
         </is>
       </c>
       <c r="C278" s="3" t="n">
@@ -15227,12 +15227,12 @@
       </c>
       <c r="E278" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491837DPX</t>
+          <t>KIT4M058725438WP</t>
         </is>
       </c>
       <c r="F278" s="4" t="inlineStr">
         <is>
-          <t>816389</t>
+          <t>816115</t>
         </is>
       </c>
       <c r="G278" s="5" t="inlineStr">
@@ -15258,7 +15258,7 @@
       </c>
       <c r="L278" s="5" t="n"/>
       <c r="M278" s="7" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="279">
@@ -15269,7 +15269,7 @@
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491811JB5</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438162 - KIT4M05799712SBX</t>
         </is>
       </c>
       <c r="C279" s="3" t="n">
@@ -15280,12 +15280,12 @@
       </c>
       <c r="E279" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491811JB5</t>
+          <t>KIT4M05799712SBX</t>
         </is>
       </c>
       <c r="F279" s="4" t="inlineStr">
         <is>
-          <t>816411</t>
+          <t>816276</t>
         </is>
       </c>
       <c r="G279" s="5" t="inlineStr">
@@ -15311,7 +15311,7 @@
       </c>
       <c r="L279" s="5" t="n"/>
       <c r="M279" s="7" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="280">
@@ -15322,7 +15322,7 @@
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491803672</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M0649181062D</t>
         </is>
       </c>
       <c r="C280" s="3" t="n">
@@ -15333,12 +15333,12 @@
       </c>
       <c r="E280" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491803672</t>
+          <t>KIT4M0649181062D</t>
         </is>
       </c>
       <c r="F280" s="4" t="inlineStr">
         <is>
-          <t>816391</t>
+          <t>816388</t>
         </is>
       </c>
       <c r="G280" s="5" t="inlineStr">
@@ -15375,7 +15375,7 @@
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918322GZ</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491805F7Z</t>
         </is>
       </c>
       <c r="C281" s="3" t="n">
@@ -15386,12 +15386,12 @@
       </c>
       <c r="E281" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918322GZ</t>
+          <t>KIT4M06491805F7Z</t>
         </is>
       </c>
       <c r="F281" s="4" t="inlineStr">
         <is>
-          <t>816414</t>
+          <t>816382</t>
         </is>
       </c>
       <c r="G281" s="5" t="inlineStr">
@@ -15428,7 +15428,7 @@
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491828XWF</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491794MTJ</t>
         </is>
       </c>
       <c r="C282" s="3" t="n">
@@ -15439,12 +15439,12 @@
       </c>
       <c r="E282" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491828XWF</t>
+          <t>KIT4M06491794MTJ</t>
         </is>
       </c>
       <c r="F282" s="4" t="inlineStr">
         <is>
-          <t>816387</t>
+          <t>816375</t>
         </is>
       </c>
       <c r="G282" s="5" t="inlineStr">
@@ -15587,7 +15587,7 @@
       </c>
       <c r="B285" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M0649181062D</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491809ZR6</t>
         </is>
       </c>
       <c r="C285" s="3" t="n">
@@ -15598,12 +15598,12 @@
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0649181062D</t>
+          <t>KIT4M06491809ZR6</t>
         </is>
       </c>
       <c r="F285" s="4" t="inlineStr">
         <is>
-          <t>816388</t>
+          <t>816402</t>
         </is>
       </c>
       <c r="G285" s="5" t="inlineStr">
@@ -15693,7 +15693,7 @@
       </c>
       <c r="B287" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437322 - KIT4M05872567V72</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491802BZV</t>
         </is>
       </c>
       <c r="C287" s="3" t="n">
@@ -15704,12 +15704,12 @@
       </c>
       <c r="E287" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872567V72</t>
+          <t>KIT4M06491802BZV</t>
         </is>
       </c>
       <c r="F287" s="4" t="inlineStr">
         <is>
-          <t>816099</t>
+          <t>816390</t>
         </is>
       </c>
       <c r="G287" s="5" t="inlineStr">
@@ -15746,7 +15746,7 @@
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 021437562 - KIT4M05872583P58</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491803672</t>
         </is>
       </c>
       <c r="C288" s="3" t="n">
@@ -15757,12 +15757,12 @@
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872583P58</t>
+          <t>KIT4M06491803672</t>
         </is>
       </c>
       <c r="F288" s="4" t="inlineStr">
         <is>
-          <t>816069</t>
+          <t>816391</t>
         </is>
       </c>
       <c r="G288" s="5" t="inlineStr">
@@ -15852,7 +15852,7 @@
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437532 - KIT4M05872556RC9</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437742 - KIT4M05872539ZMR</t>
         </is>
       </c>
       <c r="C290" s="3" t="n">
@@ -15863,12 +15863,12 @@
       </c>
       <c r="E290" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872556RC9</t>
+          <t>KIT4M05872539ZMR</t>
         </is>
       </c>
       <c r="F290" s="4" t="inlineStr">
         <is>
-          <t>816118</t>
+          <t>816108</t>
         </is>
       </c>
       <c r="G290" s="5" t="inlineStr">
@@ -15905,7 +15905,7 @@
       </c>
       <c r="B291" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437542 - KIT4M05872553WFR</t>
+          <t>SMRT-05900510-Los Angeles CA-021437842-KIT4M05872547MK2</t>
         </is>
       </c>
       <c r="C291" s="3" t="n">
@@ -15916,12 +15916,12 @@
       </c>
       <c r="E291" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872553WFR</t>
+          <t>KIT4M05872547MK2</t>
         </is>
       </c>
       <c r="F291" s="4" t="inlineStr">
         <is>
-          <t>816116</t>
+          <t>816209</t>
         </is>
       </c>
       <c r="G291" s="5" t="inlineStr">
@@ -15958,7 +15958,7 @@
       </c>
       <c r="B292" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437742 - KIT4M05872539ZMR</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437542 - KIT4M05872553WFR</t>
         </is>
       </c>
       <c r="C292" s="3" t="n">
@@ -15969,12 +15969,12 @@
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872539ZMR</t>
+          <t>KIT4M05872553WFR</t>
         </is>
       </c>
       <c r="F292" s="4" t="inlineStr">
         <is>
-          <t>816108</t>
+          <t>816116</t>
         </is>
       </c>
       <c r="G292" s="5" t="inlineStr">
@@ -16011,7 +16011,7 @@
       </c>
       <c r="B293" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437912 - KIT4M05872525NP5</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437512 - KIT4M05872559VR9</t>
         </is>
       </c>
       <c r="C293" s="3" t="n">
@@ -16022,12 +16022,12 @@
       </c>
       <c r="E293" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872525NP5</t>
+          <t>KIT4M05872559VR9</t>
         </is>
       </c>
       <c r="F293" s="4" t="inlineStr">
         <is>
-          <t>816213</t>
+          <t>816114</t>
         </is>
       </c>
       <c r="G293" s="5" t="inlineStr">
@@ -16064,7 +16064,7 @@
       </c>
       <c r="B294" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 021437602 - KIT4M05872524CFG</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438292 - KIt4m058725108K2</t>
         </is>
       </c>
       <c r="C294" s="3" t="n">
@@ -16075,12 +16075,12 @@
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872524CFG</t>
+          <t>KIT4M058725108K2</t>
         </is>
       </c>
       <c r="F294" s="4" t="inlineStr">
         <is>
-          <t>816205</t>
+          <t>816287</t>
         </is>
       </c>
       <c r="G294" s="5" t="inlineStr">
@@ -16117,7 +16117,7 @@
       </c>
       <c r="B295" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437842-KIT4M05872547MK2</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437962 - KIT4M05799706Z6R</t>
         </is>
       </c>
       <c r="C295" s="3" t="n">
@@ -16128,12 +16128,12 @@
       </c>
       <c r="E295" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872547MK2</t>
+          <t>KIT4M05799706Z6R</t>
         </is>
       </c>
       <c r="F295" s="4" t="inlineStr">
         <is>
-          <t>816209</t>
+          <t>816273</t>
         </is>
       </c>
       <c r="G295" s="5" t="inlineStr">
@@ -16170,7 +16170,7 @@
       </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437672 - KIT4M05872531DSZ</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491811JB5</t>
         </is>
       </c>
       <c r="C296" s="3" t="n">
@@ -16181,12 +16181,12 @@
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872531DSZ</t>
+          <t>KIT4M06491811JB5</t>
         </is>
       </c>
       <c r="F296" s="4" t="inlineStr">
         <is>
-          <t>816171</t>
+          <t>816411</t>
         </is>
       </c>
       <c r="G296" s="5" t="inlineStr">
@@ -16223,7 +16223,7 @@
       </c>
       <c r="B297" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437962 - KIT4M05799706Z6R</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649702 - KIT4M04604741P2X</t>
         </is>
       </c>
       <c r="C297" s="3" t="n">
@@ -16234,12 +16234,12 @@
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799706Z6R</t>
+          <t>KIT4M04604741P2X</t>
         </is>
       </c>
       <c r="F297" s="4" t="inlineStr">
         <is>
-          <t>816273</t>
+          <t>809871</t>
         </is>
       </c>
       <c r="G297" s="5" t="inlineStr">
@@ -16276,7 +16276,7 @@
       </c>
       <c r="B298" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438292 - KIt4m058725108K2</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491837DPX</t>
         </is>
       </c>
       <c r="C298" s="3" t="n">
@@ -16287,12 +16287,12 @@
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725108K2</t>
+          <t>KIT4M06491837DPX</t>
         </is>
       </c>
       <c r="F298" s="4" t="inlineStr">
         <is>
-          <t>816287</t>
+          <t>816389</t>
         </is>
       </c>
       <c r="G298" s="5" t="inlineStr">
@@ -16329,7 +16329,7 @@
       </c>
       <c r="B299" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437552 - KIT4M05872586VCH</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918322GZ</t>
         </is>
       </c>
       <c r="C299" s="3" t="n">
@@ -16340,12 +16340,12 @@
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872586VCH</t>
+          <t>KIT4M064918322GZ</t>
         </is>
       </c>
       <c r="F299" s="4" t="inlineStr">
         <is>
-          <t>816068</t>
+          <t>816414</t>
         </is>
       </c>
       <c r="G299" s="5" t="inlineStr">
@@ -16382,7 +16382,7 @@
       </c>
       <c r="B300" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437472 - KIT4M05872565VJK</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491828XWF</t>
         </is>
       </c>
       <c r="C300" s="3" t="n">
@@ -16393,12 +16393,12 @@
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872565VJK</t>
+          <t>KIT4M06491828XWF</t>
         </is>
       </c>
       <c r="F300" s="4" t="inlineStr">
         <is>
-          <t>816109</t>
+          <t>816387</t>
         </is>
       </c>
       <c r="G300" s="5" t="inlineStr">
@@ -16435,7 +16435,7 @@
       </c>
       <c r="B301" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491794MTJ</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437522 - KIT4M05872576R4B</t>
         </is>
       </c>
       <c r="C301" s="3" t="n">
@@ -16446,12 +16446,12 @@
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491794MTJ</t>
+          <t>KIT4M05872576R4B</t>
         </is>
       </c>
       <c r="F301" s="4" t="inlineStr">
         <is>
-          <t>816375</t>
+          <t>816110</t>
         </is>
       </c>
       <c r="G301" s="5" t="inlineStr">
@@ -16488,7 +16488,7 @@
       </c>
       <c r="B302" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491805F7Z</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649992 - KIT4M05413809J58</t>
         </is>
       </c>
       <c r="C302" s="3" t="n">
@@ -16499,12 +16499,12 @@
       </c>
       <c r="E302" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491805F7Z</t>
+          <t>KIT4M05413809J58</t>
         </is>
       </c>
       <c r="F302" s="4" t="inlineStr">
         <is>
-          <t>816382</t>
+          <t>812805</t>
         </is>
       </c>
       <c r="G302" s="5" t="inlineStr">
@@ -16594,7 +16594,7 @@
       </c>
       <c r="B304" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437522 - KIT4M05872576R4B</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437552 - KIT4M05872586VCH</t>
         </is>
       </c>
       <c r="C304" s="3" t="n">
@@ -16605,12 +16605,12 @@
       </c>
       <c r="E304" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872576R4B</t>
+          <t>KIT4M05872586VCH</t>
         </is>
       </c>
       <c r="F304" s="4" t="inlineStr">
         <is>
-          <t>816110</t>
+          <t>816068</t>
         </is>
       </c>
       <c r="G304" s="5" t="inlineStr">
@@ -16647,7 +16647,7 @@
       </c>
       <c r="B305" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437512 - KIT4M05872559VR9</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437532 - KIT4M05872556RC9</t>
         </is>
       </c>
       <c r="C305" s="3" t="n">
@@ -16658,12 +16658,12 @@
       </c>
       <c r="E305" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872559VR9</t>
+          <t>KIT4M05872556RC9</t>
         </is>
       </c>
       <c r="F305" s="4" t="inlineStr">
         <is>
-          <t>816114</t>
+          <t>816118</t>
         </is>
       </c>
       <c r="G305" s="5" t="inlineStr">
@@ -16700,7 +16700,7 @@
       </c>
       <c r="B306" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437582 - KIT4M05872573K7P</t>
+          <t>SS - 05900510 - Los Angeles CA  - 021437562 - KIT4M05872583P58</t>
         </is>
       </c>
       <c r="C306" s="3" t="n">
@@ -16711,12 +16711,12 @@
       </c>
       <c r="E306" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872573K7P</t>
+          <t>KIT4M05872583P58</t>
         </is>
       </c>
       <c r="F306" s="4" t="inlineStr">
         <is>
-          <t>816067</t>
+          <t>816069</t>
         </is>
       </c>
       <c r="G306" s="5" t="inlineStr">
@@ -16753,7 +16753,7 @@
       </c>
       <c r="B307" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491802BZV</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437322 - KIT4M05872567V72</t>
         </is>
       </c>
       <c r="C307" s="3" t="n">
@@ -16764,12 +16764,12 @@
       </c>
       <c r="E307" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491802BZV</t>
+          <t>KIT4M05872567V72</t>
         </is>
       </c>
       <c r="F307" s="4" t="inlineStr">
         <is>
-          <t>816390</t>
+          <t>816099</t>
         </is>
       </c>
       <c r="G307" s="5" t="inlineStr">
@@ -16806,7 +16806,7 @@
       </c>
       <c r="B308" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491809ZR6</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437472 - KIT4M05872565VJK</t>
         </is>
       </c>
       <c r="C308" s="3" t="n">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E308" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491809ZR6</t>
+          <t>KIT4M05872565VJK</t>
         </is>
       </c>
       <c r="F308" s="4" t="inlineStr">
         <is>
-          <t>816402</t>
+          <t>816109</t>
         </is>
       </c>
       <c r="G308" s="5" t="inlineStr">
@@ -16859,7 +16859,7 @@
       </c>
       <c r="B309" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437452 - KIT4M05872580C6X</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437912 - KIT4M05872525NP5</t>
         </is>
       </c>
       <c r="C309" s="3" t="n">
@@ -16870,12 +16870,12 @@
       </c>
       <c r="E309" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872580C6X</t>
+          <t>KIT4M05872525NP5</t>
         </is>
       </c>
       <c r="F309" s="4" t="inlineStr">
         <is>
-          <t>816097</t>
+          <t>816213</t>
         </is>
       </c>
       <c r="G309" s="5" t="inlineStr">
@@ -16901,7 +16901,7 @@
       </c>
       <c r="L309" s="5" t="n"/>
       <c r="M309" s="7" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="310">
@@ -16912,7 +16912,7 @@
       </c>
       <c r="B310" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437892 - KIT4M06490321NJX</t>
+          <t>SS - 05900510 -  Los Angeles CA - 021437602 - KIT4M05872524CFG</t>
         </is>
       </c>
       <c r="C310" s="3" t="n">
@@ -16923,12 +16923,12 @@
       </c>
       <c r="E310" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06490321NJX</t>
+          <t>KIT4M05872524CFG</t>
         </is>
       </c>
       <c r="F310" s="4" t="inlineStr">
         <is>
-          <t>816219</t>
+          <t>816205</t>
         </is>
       </c>
       <c r="G310" s="5" t="inlineStr">
@@ -16954,7 +16954,7 @@
       </c>
       <c r="L310" s="5" t="n"/>
       <c r="M310" s="7" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="311">
@@ -16965,7 +16965,7 @@
       </c>
       <c r="B311" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437762 - KIT4M05872564MCF</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437672 - KIT4M05872531DSZ</t>
         </is>
       </c>
       <c r="C311" s="3" t="n">
@@ -16976,12 +16976,12 @@
       </c>
       <c r="E311" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872564MCF</t>
+          <t>KIT4M05872531DSZ</t>
         </is>
       </c>
       <c r="F311" s="4" t="inlineStr">
         <is>
-          <t>816203</t>
+          <t>816171</t>
         </is>
       </c>
       <c r="G311" s="5" t="inlineStr">
@@ -17007,7 +17007,7 @@
       </c>
       <c r="L311" s="5" t="n"/>
       <c r="M311" s="7" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="312">
@@ -17018,7 +17018,7 @@
       </c>
       <c r="B312" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437872 - KIT4M06490319DDN</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437452 - KIT4M05872580C6X</t>
         </is>
       </c>
       <c r="C312" s="3" t="n">
@@ -17029,12 +17029,12 @@
       </c>
       <c r="E312" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06490319DDN</t>
+          <t>KIT4M05872580C6X</t>
         </is>
       </c>
       <c r="F312" s="4" t="inlineStr">
         <is>
-          <t>816220</t>
+          <t>816097</t>
         </is>
       </c>
       <c r="G312" s="5" t="inlineStr">
@@ -17071,7 +17071,7 @@
       </c>
       <c r="B313" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 021437772 - KIT4M05872563FWB</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649382 - KIT4M05368219KRH</t>
         </is>
       </c>
       <c r="C313" s="3" t="n">
@@ -17082,12 +17082,12 @@
       </c>
       <c r="E313" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872563FWB</t>
+          <t>KIT4M05368219KRH</t>
         </is>
       </c>
       <c r="F313" s="4" t="inlineStr">
         <is>
-          <t>816208</t>
+          <t>810646</t>
         </is>
       </c>
       <c r="G313" s="5" t="inlineStr">
@@ -17124,7 +17124,7 @@
       </c>
       <c r="B314" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438052 - KIT4M05872522W7W</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437262 - KIT4P0008460369B</t>
         </is>
       </c>
       <c r="C314" s="3" t="n">
@@ -17135,17 +17135,17 @@
       </c>
       <c r="E314" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872522W7W</t>
+          <t>KIT4P0008460369B</t>
         </is>
       </c>
       <c r="F314" s="4" t="inlineStr">
         <is>
-          <t>816217</t>
+          <t>816224</t>
         </is>
       </c>
       <c r="G314" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H314" s="5" t="inlineStr">
@@ -17177,7 +17177,7 @@
       </c>
       <c r="B315" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064917936NF</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649982 - KIT4M05413823B5P</t>
         </is>
       </c>
       <c r="C315" s="3" t="n">
@@ -17188,12 +17188,12 @@
       </c>
       <c r="E315" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064917936NF</t>
+          <t>KIT4M05413823B5P</t>
         </is>
       </c>
       <c r="F315" s="4" t="inlineStr">
         <is>
-          <t>816404</t>
+          <t>812837</t>
         </is>
       </c>
       <c r="G315" s="5" t="inlineStr">
@@ -17230,7 +17230,7 @@
       </c>
       <c r="B316" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437972 - KIT4M06490327GMP</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438052 - KIT4M05872522W7W</t>
         </is>
       </c>
       <c r="C316" s="3" t="n">
@@ -17241,12 +17241,12 @@
       </c>
       <c r="E316" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06490327GMP</t>
+          <t>KIT4M05872522W7W</t>
         </is>
       </c>
       <c r="F316" s="4" t="inlineStr">
         <is>
-          <t>816199</t>
+          <t>816217</t>
         </is>
       </c>
       <c r="G316" s="5" t="inlineStr">
@@ -17283,7 +17283,7 @@
       </c>
       <c r="B317" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437652 - KIT4M05872551G9S</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437902 - KIT4M05799717WZV</t>
         </is>
       </c>
       <c r="C317" s="3" t="n">
@@ -17294,12 +17294,12 @@
       </c>
       <c r="E317" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872551G9S</t>
+          <t>KIT4M05799717WZV</t>
         </is>
       </c>
       <c r="F317" s="4" t="inlineStr">
         <is>
-          <t>816180</t>
+          <t>816280</t>
         </is>
       </c>
       <c r="G317" s="5" t="inlineStr">
@@ -17389,7 +17389,7 @@
       </c>
       <c r="B319" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437702 - KIT4M05872515PJT</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438212 - KIT4M058725047FZ</t>
         </is>
       </c>
       <c r="C319" s="3" t="n">
@@ -17400,12 +17400,12 @@
       </c>
       <c r="E319" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872515PJT</t>
+          <t>KIT4M058725047FZ</t>
         </is>
       </c>
       <c r="F319" s="4" t="inlineStr">
         <is>
-          <t>816218</t>
+          <t>816289</t>
         </is>
       </c>
       <c r="G319" s="5" t="inlineStr">
@@ -17442,7 +17442,7 @@
       </c>
       <c r="B320" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438212 - KIT4M058725047FZ</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437702 - KIT4M05872515PJT</t>
         </is>
       </c>
       <c r="C320" s="3" t="n">
@@ -17453,12 +17453,12 @@
       </c>
       <c r="E320" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725047FZ</t>
+          <t>KIT4M05872515PJT</t>
         </is>
       </c>
       <c r="F320" s="4" t="inlineStr">
         <is>
-          <t>816289</t>
+          <t>816218</t>
         </is>
       </c>
       <c r="G320" s="5" t="inlineStr">
@@ -17495,7 +17495,7 @@
       </c>
       <c r="B321" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955042 - KIT4P00072391SZM</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649772 - KIT4M04475152RGR</t>
         </is>
       </c>
       <c r="C321" s="3" t="n">
@@ -17506,17 +17506,17 @@
       </c>
       <c r="E321" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00072391SZM</t>
+          <t>KIT4M04475152RGR</t>
         </is>
       </c>
       <c r="F321" s="4" t="inlineStr">
         <is>
-          <t>814493</t>
+          <t>809861</t>
         </is>
       </c>
       <c r="G321" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H321" s="5" t="inlineStr">
@@ -17548,7 +17548,7 @@
       </c>
       <c r="B322" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438142  - KIT4M05799685DG5</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438062 - KIT4M05799676NNK</t>
         </is>
       </c>
       <c r="C322" s="3" t="n">
@@ -17559,12 +17559,12 @@
       </c>
       <c r="E322" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799685DG5</t>
+          <t>KIT4M05799676NNK</t>
         </is>
       </c>
       <c r="F322" s="4" t="inlineStr">
         <is>
-          <t>816271</t>
+          <t>816283</t>
         </is>
       </c>
       <c r="G322" s="5" t="inlineStr">
@@ -17601,7 +17601,7 @@
       </c>
       <c r="B323" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438062 - KIT4M05799676NNK</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438142  - KIT4M05799685DG5</t>
         </is>
       </c>
       <c r="C323" s="3" t="n">
@@ -17612,12 +17612,12 @@
       </c>
       <c r="E323" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799676NNK</t>
+          <t>KIT4M05799685DG5</t>
         </is>
       </c>
       <c r="F323" s="4" t="inlineStr">
         <is>
-          <t>816283</t>
+          <t>816271</t>
         </is>
       </c>
       <c r="G323" s="5" t="inlineStr">
@@ -17654,7 +17654,7 @@
       </c>
       <c r="B324" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955642 - KIT4M05563573WKC</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437982 - KIT4M05799678R5P</t>
         </is>
       </c>
       <c r="C324" s="3" t="n">
@@ -17665,12 +17665,12 @@
       </c>
       <c r="E324" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563573WKC</t>
+          <t>KIT4M05799678R5P</t>
         </is>
       </c>
       <c r="F324" s="4" t="inlineStr">
         <is>
-          <t>814488</t>
+          <t>816281</t>
         </is>
       </c>
       <c r="G324" s="5" t="inlineStr">
@@ -17707,7 +17707,7 @@
       </c>
       <c r="B325" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437902 - KIT4M05799717WZV</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955042 - KIT4P00072391SZM</t>
         </is>
       </c>
       <c r="C325" s="3" t="n">
@@ -17718,17 +17718,17 @@
       </c>
       <c r="E325" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799717WZV</t>
+          <t>KIT4P00072391SZM</t>
         </is>
       </c>
       <c r="F325" s="4" t="inlineStr">
         <is>
-          <t>816280</t>
+          <t>814493</t>
         </is>
       </c>
       <c r="G325" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H325" s="5" t="inlineStr">
@@ -17760,7 +17760,7 @@
       </c>
       <c r="B326" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437982 - KIT4M05799678R5P</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437872 - KIT4M06490319DDN</t>
         </is>
       </c>
       <c r="C326" s="3" t="n">
@@ -17771,12 +17771,12 @@
       </c>
       <c r="E326" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799678R5P</t>
+          <t>KIT4M06490319DDN</t>
         </is>
       </c>
       <c r="F326" s="4" t="inlineStr">
         <is>
-          <t>816281</t>
+          <t>816220</t>
         </is>
       </c>
       <c r="G326" s="5" t="inlineStr">
@@ -17813,7 +17813,7 @@
       </c>
       <c r="B327" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA -021437942 - KIT4M05799709G5Q</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437892 - KIT4M06490321NJX</t>
         </is>
       </c>
       <c r="C327" s="3" t="n">
@@ -17824,12 +17824,12 @@
       </c>
       <c r="E327" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799709G5Q</t>
+          <t>KIT4M06490321NJX</t>
         </is>
       </c>
       <c r="F327" s="4" t="inlineStr">
         <is>
-          <t>816274</t>
+          <t>816219</t>
         </is>
       </c>
       <c r="G327" s="5" t="inlineStr">
@@ -17866,7 +17866,7 @@
       </c>
       <c r="B328" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649772 - KIT4M04475152RGR</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437972 - KIT4M06490327GMP</t>
         </is>
       </c>
       <c r="C328" s="3" t="n">
@@ -17877,12 +17877,12 @@
       </c>
       <c r="E328" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475152RGR</t>
+          <t>KIT4M06490327GMP</t>
         </is>
       </c>
       <c r="F328" s="4" t="inlineStr">
         <is>
-          <t>809861</t>
+          <t>816199</t>
         </is>
       </c>
       <c r="G328" s="5" t="inlineStr">
@@ -17919,7 +17919,7 @@
       </c>
       <c r="B329" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437262 - KIT4P0008460369B</t>
+          <t>SS - 05900510 - Los Angeles, CA - 021437772 - KIT4M05872563FWB</t>
         </is>
       </c>
       <c r="C329" s="3" t="n">
@@ -17930,17 +17930,17 @@
       </c>
       <c r="E329" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0008460369B</t>
+          <t>KIT4M05872563FWB</t>
         </is>
       </c>
       <c r="F329" s="4" t="inlineStr">
         <is>
-          <t>816224</t>
+          <t>816208</t>
         </is>
       </c>
       <c r="G329" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H329" s="5" t="inlineStr">
@@ -17972,7 +17972,7 @@
       </c>
       <c r="B330" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649382 - KIT4M05368219KRH</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438272 - KIT4M05872517VS2</t>
         </is>
       </c>
       <c r="C330" s="3" t="n">
@@ -17983,12 +17983,12 @@
       </c>
       <c r="E330" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368219KRH</t>
+          <t>KIT4M05872517VS2</t>
         </is>
       </c>
       <c r="F330" s="4" t="inlineStr">
         <is>
-          <t>810646</t>
+          <t>816288</t>
         </is>
       </c>
       <c r="G330" s="5" t="inlineStr">
@@ -18025,7 +18025,7 @@
       </c>
       <c r="B331" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649392 - KIT4M05368206BZP</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955642 - KIT4M05563573WKC</t>
         </is>
       </c>
       <c r="C331" s="3" t="n">
@@ -18036,12 +18036,12 @@
       </c>
       <c r="E331" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368206BZP</t>
+          <t>KIT4M05563573WKC</t>
         </is>
       </c>
       <c r="F331" s="4" t="inlineStr">
         <is>
-          <t>810645</t>
+          <t>814488</t>
         </is>
       </c>
       <c r="G331" s="5" t="inlineStr">
@@ -18078,7 +18078,7 @@
       </c>
       <c r="B332" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918068FF</t>
+          <t>SMS - 05900510 - Los Angeles CA -021437942 - KIT4M05799709G5Q</t>
         </is>
       </c>
       <c r="C332" s="3" t="n">
@@ -18089,12 +18089,12 @@
       </c>
       <c r="E332" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918068FF</t>
+          <t>KIT4M05799709G5Q</t>
         </is>
       </c>
       <c r="F332" s="4" t="inlineStr">
         <is>
-          <t>816400</t>
+          <t>816274</t>
         </is>
       </c>
       <c r="G332" s="5" t="inlineStr">
@@ -18131,7 +18131,7 @@
       </c>
       <c r="B333" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437492 - KIT4M0587256196K</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437652 - KIT4M05872551G9S</t>
         </is>
       </c>
       <c r="C333" s="3" t="n">
@@ -18142,12 +18142,12 @@
       </c>
       <c r="E333" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0587256196K</t>
+          <t>KIT4M05872551G9S</t>
         </is>
       </c>
       <c r="F333" s="4" t="inlineStr">
         <is>
-          <t>816098</t>
+          <t>816180</t>
         </is>
       </c>
       <c r="G333" s="5" t="inlineStr">
@@ -18184,7 +18184,7 @@
       </c>
       <c r="B334" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 021437852 - KIT4M0587257292W</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437492 - KIT4M0587256196K</t>
         </is>
       </c>
       <c r="C334" s="3" t="n">
@@ -18195,12 +18195,12 @@
       </c>
       <c r="E334" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0587257292W</t>
+          <t>KIT4M0587256196K</t>
         </is>
       </c>
       <c r="F334" s="4" t="inlineStr">
         <is>
-          <t>816207</t>
+          <t>816098</t>
         </is>
       </c>
       <c r="G334" s="5" t="inlineStr">
@@ -18237,7 +18237,7 @@
       </c>
       <c r="B335" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438272 - KIT4M05872517VS2</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437762 - KIT4M05872564MCF</t>
         </is>
       </c>
       <c r="C335" s="3" t="n">
@@ -18248,12 +18248,12 @@
       </c>
       <c r="E335" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872517VS2</t>
+          <t>KIT4M05872564MCF</t>
         </is>
       </c>
       <c r="F335" s="4" t="inlineStr">
         <is>
-          <t>816288</t>
+          <t>816203</t>
         </is>
       </c>
       <c r="G335" s="5" t="inlineStr">
@@ -18290,7 +18290,7 @@
       </c>
       <c r="B336" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020649472-KIT4M05413795QHK</t>
+          <t>SS - 05900510 - Los Angeles, CA - 021437852 - KIT4M0587257292W</t>
         </is>
       </c>
       <c r="C336" s="3" t="n">
@@ -18301,12 +18301,12 @@
       </c>
       <c r="E336" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413795QHK</t>
+          <t>KIT4M0587257292W</t>
         </is>
       </c>
       <c r="F336" s="4" t="inlineStr">
         <is>
-          <t>812801</t>
+          <t>816207</t>
         </is>
       </c>
       <c r="G336" s="5" t="inlineStr">
@@ -18332,7 +18332,7 @@
       </c>
       <c r="L336" s="5" t="n"/>
       <c r="M336" s="7" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="337">
@@ -18343,7 +18343,7 @@
       </c>
       <c r="B337" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437642 - KIT4M05872590N8X</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064917936NF</t>
         </is>
       </c>
       <c r="C337" s="3" t="n">
@@ -18354,12 +18354,12 @@
       </c>
       <c r="E337" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872590N8X</t>
+          <t>KIT4M064917936NF</t>
         </is>
       </c>
       <c r="F337" s="4" t="inlineStr">
         <is>
-          <t>816204</t>
+          <t>816404</t>
         </is>
       </c>
       <c r="G337" s="5" t="inlineStr">
@@ -18385,7 +18385,7 @@
       </c>
       <c r="L337" s="5" t="n"/>
       <c r="M337" s="7" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="338">
@@ -18396,7 +18396,7 @@
       </c>
       <c r="B338" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 -  Los Angeles CA - 020649602 - KIT4M05413773R6G</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918068FF</t>
         </is>
       </c>
       <c r="C338" s="3" t="n">
@@ -18407,12 +18407,12 @@
       </c>
       <c r="E338" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413773R6G</t>
+          <t>KIT4M064918068FF</t>
         </is>
       </c>
       <c r="F338" s="4" t="inlineStr">
         <is>
-          <t>812807</t>
+          <t>816400</t>
         </is>
       </c>
       <c r="G338" s="5" t="inlineStr">
@@ -18438,7 +18438,7 @@
       </c>
       <c r="L338" s="5" t="n"/>
       <c r="M338" s="7" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="339">
@@ -18449,7 +18449,7 @@
       </c>
       <c r="B339" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438102 - KIT4M05872513F7N</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020650222 - KIT4M05413790XCD</t>
         </is>
       </c>
       <c r="C339" s="3" t="n">
@@ -18460,12 +18460,12 @@
       </c>
       <c r="E339" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872513F7N</t>
+          <t>KIT4M05413790XCD</t>
         </is>
       </c>
       <c r="F339" s="4" t="inlineStr">
         <is>
-          <t>816161</t>
+          <t>812822</t>
         </is>
       </c>
       <c r="G339" s="5" t="inlineStr">
@@ -18491,7 +18491,7 @@
       </c>
       <c r="L339" s="5" t="n"/>
       <c r="M339" s="7" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="340">
@@ -18502,7 +18502,7 @@
       </c>
       <c r="B340" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649232 - KIT4P0006563862J</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649392 - KIT4M05368206BZP</t>
         </is>
       </c>
       <c r="C340" s="3" t="n">
@@ -18513,17 +18513,17 @@
       </c>
       <c r="E340" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0006563862J</t>
+          <t>KIT4M05368206BZP</t>
         </is>
       </c>
       <c r="F340" s="4" t="inlineStr">
         <is>
-          <t>812927</t>
+          <t>810645</t>
         </is>
       </c>
       <c r="G340" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H340" s="5" t="inlineStr">
@@ -18544,7 +18544,7 @@
       </c>
       <c r="L340" s="5" t="n"/>
       <c r="M340" s="7" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="341">
@@ -18555,7 +18555,7 @@
       </c>
       <c r="B341" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649612 - KIT4M05413827DC4</t>
+          <t>SMRT-05900510-Los Angeles CA-020649472-KIT4M05413795QHK</t>
         </is>
       </c>
       <c r="C341" s="3" t="n">
@@ -18566,12 +18566,12 @@
       </c>
       <c r="E341" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413827DC4</t>
+          <t>KIT4M05413795QHK</t>
         </is>
       </c>
       <c r="F341" s="4" t="inlineStr">
         <is>
-          <t>812829</t>
+          <t>812801</t>
         </is>
       </c>
       <c r="G341" s="5" t="inlineStr">
@@ -18597,7 +18597,7 @@
       </c>
       <c r="L341" s="5" t="n"/>
       <c r="M341" s="7" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="342">
@@ -18608,7 +18608,7 @@
       </c>
       <c r="B342" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020650092 - KIT4M05413830JN7</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437642 - KIT4M05872590N8X</t>
         </is>
       </c>
       <c r="C342" s="3" t="n">
@@ -18619,12 +18619,12 @@
       </c>
       <c r="E342" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413830JN7</t>
+          <t>KIT4M05872590N8X</t>
         </is>
       </c>
       <c r="F342" s="4" t="inlineStr">
         <is>
-          <t>810105</t>
+          <t>816204</t>
         </is>
       </c>
       <c r="G342" s="5" t="inlineStr">
@@ -18650,7 +18650,7 @@
       </c>
       <c r="L342" s="5" t="n"/>
       <c r="M342" s="7" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="343">
@@ -18661,7 +18661,7 @@
       </c>
       <c r="B343" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438202 - KIT4M05872506TTB</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649232 - KIT4P0006563862J</t>
         </is>
       </c>
       <c r="C343" s="3" t="n">
@@ -18672,17 +18672,17 @@
       </c>
       <c r="E343" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872506TTB</t>
+          <t>KIT4P0006563862J</t>
         </is>
       </c>
       <c r="F343" s="4" t="inlineStr">
         <is>
-          <t>816082</t>
+          <t>812927</t>
         </is>
       </c>
       <c r="G343" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H343" s="5" t="inlineStr">
@@ -18703,7 +18703,7 @@
       </c>
       <c r="L343" s="5" t="n"/>
       <c r="M343" s="7" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="344">
@@ -18714,7 +18714,7 @@
       </c>
       <c r="B344" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649982 - KIT4M05413823B5P</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438102 - KIT4M05872513F7N</t>
         </is>
       </c>
       <c r="C344" s="3" t="n">
@@ -18725,12 +18725,12 @@
       </c>
       <c r="E344" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413823B5P</t>
+          <t>KIT4M05872513F7N</t>
         </is>
       </c>
       <c r="F344" s="4" t="inlineStr">
         <is>
-          <t>812837</t>
+          <t>816161</t>
         </is>
       </c>
       <c r="G344" s="5" t="inlineStr">
@@ -18756,7 +18756,7 @@
       </c>
       <c r="L344" s="5" t="n"/>
       <c r="M344" s="7" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="345">
@@ -18767,7 +18767,7 @@
       </c>
       <c r="B345" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 020955572 - KIT4M05563606ZRC</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438012 - KIT4M05799715GJ2</t>
         </is>
       </c>
       <c r="C345" s="3" t="n">
@@ -18778,24 +18778,16 @@
       </c>
       <c r="E345" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563606ZRC</t>
-        </is>
-      </c>
-      <c r="F345" s="4" t="inlineStr">
-        <is>
-          <t>814464</t>
-        </is>
-      </c>
+          <t>KIT4M05799715GJ2</t>
+        </is>
+      </c>
+      <c r="F345" s="8" t="n"/>
       <c r="G345" s="5" t="inlineStr">
         <is>
           <t>Mini</t>
         </is>
       </c>
-      <c r="H345" s="5" t="inlineStr">
-        <is>
-          <t>Master Serial List</t>
-        </is>
-      </c>
+      <c r="H345" s="5" t="n"/>
       <c r="I345" s="6" t="n">
         <v>46235</v>
       </c>
@@ -18820,7 +18812,7 @@
       </c>
       <c r="B346" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438012 - KIT4M05799715GJ2</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955442 - KIT4M05563503XXP</t>
         </is>
       </c>
       <c r="C346" s="3" t="n">
@@ -18831,16 +18823,24 @@
       </c>
       <c r="E346" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799715GJ2</t>
-        </is>
-      </c>
-      <c r="F346" s="8" t="n"/>
+          <t>KIT4M05563503XXP</t>
+        </is>
+      </c>
+      <c r="F346" s="4" t="inlineStr">
+        <is>
+          <t>814430</t>
+        </is>
+      </c>
       <c r="G346" s="5" t="inlineStr">
         <is>
           <t>Mini</t>
         </is>
       </c>
-      <c r="H346" s="5" t="n"/>
+      <c r="H346" s="5" t="inlineStr">
+        <is>
+          <t>Master Serial List</t>
+        </is>
+      </c>
       <c r="I346" s="6" t="n">
         <v>46235</v>
       </c>
@@ -18865,7 +18865,7 @@
       </c>
       <c r="B347" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955222 - KIT4M05563536BPJ</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438202 - KIT4M05872506TTB</t>
         </is>
       </c>
       <c r="C347" s="3" t="n">
@@ -18876,12 +18876,12 @@
       </c>
       <c r="E347" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563536BPJ</t>
+          <t>KIT4M05872506TTB</t>
         </is>
       </c>
       <c r="F347" s="4" t="inlineStr">
         <is>
-          <t>814466</t>
+          <t>816082</t>
         </is>
       </c>
       <c r="G347" s="5" t="inlineStr">
@@ -18918,7 +18918,7 @@
       </c>
       <c r="B348" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955162 - KIT4M05563554WCW</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437922 - KIT4M05872496MW6</t>
         </is>
       </c>
       <c r="C348" s="3" t="n">
@@ -18929,12 +18929,12 @@
       </c>
       <c r="E348" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563554WCW</t>
+          <t>KIT4M05872496MW6</t>
         </is>
       </c>
       <c r="F348" s="4" t="inlineStr">
         <is>
-          <t>814444</t>
+          <t>816206</t>
         </is>
       </c>
       <c r="G348" s="5" t="inlineStr">
@@ -18971,7 +18971,7 @@
       </c>
       <c r="B349" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955442 - KIT4M05563503XXP</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955512 - KIT4M055635779MM</t>
         </is>
       </c>
       <c r="C349" s="3" t="n">
@@ -18982,12 +18982,12 @@
       </c>
       <c r="E349" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563503XXP</t>
+          <t>KIT4M055635779MM</t>
         </is>
       </c>
       <c r="F349" s="4" t="inlineStr">
         <is>
-          <t>814430</t>
+          <t>814487</t>
         </is>
       </c>
       <c r="G349" s="5" t="inlineStr">
@@ -19024,7 +19024,7 @@
       </c>
       <c r="B350" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955512 - KIT4M055635779MM</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955162 - KIT4M05563554WCW</t>
         </is>
       </c>
       <c r="C350" s="3" t="n">
@@ -19035,12 +19035,12 @@
       </c>
       <c r="E350" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635779MM</t>
+          <t>KIT4M05563554WCW</t>
         </is>
       </c>
       <c r="F350" s="4" t="inlineStr">
         <is>
-          <t>814487</t>
+          <t>814444</t>
         </is>
       </c>
       <c r="G350" s="5" t="inlineStr">
@@ -19077,7 +19077,7 @@
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437922 - KIT4M05872496MW6</t>
+          <t>SS - 05900510 -  Los Angeles CA - 020955572 - KIT4M05563606ZRC</t>
         </is>
       </c>
       <c r="C351" s="3" t="n">
@@ -19088,12 +19088,12 @@
       </c>
       <c r="E351" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872496MW6</t>
+          <t>KIT4M05563606ZRC</t>
         </is>
       </c>
       <c r="F351" s="4" t="inlineStr">
         <is>
-          <t>816206</t>
+          <t>814464</t>
         </is>
       </c>
       <c r="G351" s="5" t="inlineStr">
@@ -19130,7 +19130,7 @@
       </c>
       <c r="B352" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955562 - KIT4M05563505WPS</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955222 - KIT4M05563536BPJ</t>
         </is>
       </c>
       <c r="C352" s="3" t="n">
@@ -19141,12 +19141,12 @@
       </c>
       <c r="E352" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563505WPS</t>
+          <t>KIT4M05563536BPJ</t>
         </is>
       </c>
       <c r="F352" s="4" t="inlineStr">
         <is>
-          <t>814448</t>
+          <t>814466</t>
         </is>
       </c>
       <c r="G352" s="5" t="inlineStr">
@@ -19183,7 +19183,7 @@
       </c>
       <c r="B353" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 021437632 - KIT4M05872585HZZ</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955562 - KIT4M05563505WPS</t>
         </is>
       </c>
       <c r="C353" s="3" t="n">
@@ -19194,12 +19194,12 @@
       </c>
       <c r="E353" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872585HZZ</t>
+          <t>KIT4M05563505WPS</t>
         </is>
       </c>
       <c r="F353" s="4" t="inlineStr">
         <is>
-          <t>816211</t>
+          <t>814448</t>
         </is>
       </c>
       <c r="G353" s="5" t="inlineStr">
@@ -19236,7 +19236,7 @@
       </c>
       <c r="B354" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649992 - KIT4M05413809J58</t>
+          <t>SS - 05900510 -  Los Angeles CA - 021437632 - KIT4M05872585HZZ</t>
         </is>
       </c>
       <c r="C354" s="3" t="n">
@@ -19247,12 +19247,12 @@
       </c>
       <c r="E354" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413809J58</t>
+          <t>KIT4M05872585HZZ</t>
         </is>
       </c>
       <c r="F354" s="4" t="inlineStr">
         <is>
-          <t>812805</t>
+          <t>816211</t>
         </is>
       </c>
       <c r="G354" s="5" t="inlineStr">
@@ -19289,7 +19289,7 @@
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649922 - KIT4M05413780XFH</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649612 - KIT4M05413827DC4</t>
         </is>
       </c>
       <c r="C355" s="3" t="n">
@@ -19300,12 +19300,12 @@
       </c>
       <c r="E355" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413780XFH</t>
+          <t>KIT4M05413827DC4</t>
         </is>
       </c>
       <c r="F355" s="4" t="inlineStr">
         <is>
-          <t>812833</t>
+          <t>812829</t>
         </is>
       </c>
       <c r="G355" s="5" t="inlineStr">
@@ -19342,7 +19342,7 @@
       </c>
       <c r="B356" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020650032-KIT4M05413802FVN</t>
+          <t>STS - 05900510 - Los Angeles CA - 020650092 - KIT4M05413830JN7</t>
         </is>
       </c>
       <c r="C356" s="3" t="n">
@@ -19353,12 +19353,12 @@
       </c>
       <c r="E356" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413802FVN</t>
+          <t>KIT4M05413830JN7</t>
         </is>
       </c>
       <c r="F356" s="4" t="inlineStr">
         <is>
-          <t>812813</t>
+          <t>810105</t>
         </is>
       </c>
       <c r="G356" s="5" t="inlineStr">
@@ -19395,7 +19395,7 @@
       </c>
       <c r="B357" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649482 - KIT4M054137938P7</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649922 - KIT4M05413780XFH</t>
         </is>
       </c>
       <c r="C357" s="3" t="n">
@@ -19406,12 +19406,12 @@
       </c>
       <c r="E357" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137938P7</t>
+          <t>KIT4M05413780XFH</t>
         </is>
       </c>
       <c r="F357" s="4" t="inlineStr">
         <is>
-          <t>812848</t>
+          <t>812833</t>
         </is>
       </c>
       <c r="G357" s="5" t="inlineStr">
@@ -19448,7 +19448,7 @@
       </c>
       <c r="B358" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020650222 - KIT4M05413790XCD</t>
+          <t>SMRT-05900510-Los Angeles CA-020650032-KIT4M05413802FVN</t>
         </is>
       </c>
       <c r="C358" s="3" t="n">
@@ -19459,12 +19459,12 @@
       </c>
       <c r="E358" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413790XCD</t>
+          <t>KIT4M05413802FVN</t>
         </is>
       </c>
       <c r="F358" s="4" t="inlineStr">
         <is>
-          <t>812822</t>
+          <t>812813</t>
         </is>
       </c>
       <c r="G358" s="5" t="inlineStr">
@@ -19501,7 +19501,7 @@
       </c>
       <c r="B359" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020650062 - KIT4M05413797HK5</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649482 - KIT4M054137938P7</t>
         </is>
       </c>
       <c r="C359" s="3" t="n">
@@ -19512,12 +19512,12 @@
       </c>
       <c r="E359" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413797HK5</t>
+          <t>KIT4M054137938P7</t>
         </is>
       </c>
       <c r="F359" s="4" t="inlineStr">
         <is>
-          <t>812808</t>
+          <t>812848</t>
         </is>
       </c>
       <c r="G359" s="5" t="inlineStr">
@@ -20113,7 +20113,7 @@
     <row r="379">
       <c r="A379" s="15" t="inlineStr">
         <is>
-          <t>Generated 2026-08-27 08:19 by build_starlink_usage.py</t>
+          <t>Generated 2026-08-27 14:27 by build_starlink_usage.py</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_Current_by_Kit.xlsx
+++ b/Starlink_Usage_Current_by_Kit.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Current Month by Kit" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Current Month by Kit'!$A$1:$M$368</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Current Month by Kit'!$A$1:$M$370</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M379"/>
+  <dimension ref="A1:M381"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -630,7 +630,7 @@
       </c>
       <c r="L2" s="5" t="n"/>
       <c r="M2" s="7" t="n">
-        <v>2485.21</v>
+        <v>2491.33</v>
       </c>
     </row>
     <row r="3">
@@ -683,7 +683,7 @@
       </c>
       <c r="L3" s="5" t="n"/>
       <c r="M3" s="7" t="n">
-        <v>2262.8</v>
+        <v>2262.88</v>
       </c>
     </row>
     <row r="4">
@@ -736,7 +736,7 @@
       </c>
       <c r="L4" s="5" t="n"/>
       <c r="M4" s="7" t="n">
-        <v>1632.8</v>
+        <v>1634.8</v>
       </c>
     </row>
     <row r="5">
@@ -789,7 +789,7 @@
       </c>
       <c r="L5" s="5" t="n"/>
       <c r="M5" s="7" t="n">
-        <v>1365.59</v>
+        <v>1380.47</v>
       </c>
     </row>
     <row r="6">
@@ -842,7 +842,7 @@
       </c>
       <c r="L6" s="5" t="n"/>
       <c r="M6" s="7" t="n">
-        <v>1072.32</v>
+        <v>1082.84</v>
       </c>
     </row>
     <row r="7">
@@ -948,7 +948,7 @@
       </c>
       <c r="L8" s="5" t="n"/>
       <c r="M8" s="7" t="n">
-        <v>800</v>
+        <v>817.62</v>
       </c>
     </row>
     <row r="9">
@@ -959,7 +959,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649202 - KIT4P00066901JZZ</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437292 - KIT4P000832806P4</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
@@ -970,12 +970,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00066901JZZ</t>
+          <t>KIT4P000832806P4</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>812926</t>
+          <t>816228</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="L9" s="5" t="n"/>
       <c r="M9" s="7" t="n">
-        <v>781.74</v>
+        <v>798.09</v>
       </c>
     </row>
     <row r="10">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles, CA - 020955232 - KIT4M05563538RZV</t>
+          <t>SMRT-05900510-Los Angeles CA-021437282-KIT4P00084593R9F</t>
         </is>
       </c>
       <c r="C10" s="3" t="n">
@@ -1023,17 +1023,17 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563538RZV</t>
+          <t>KIT4P00084593R9F</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>814459</t>
+          <t>816227</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="L10" s="5" t="n"/>
       <c r="M10" s="7" t="n">
-        <v>772.1900000000001</v>
+        <v>795.22</v>
       </c>
     </row>
     <row r="11">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437282-KIT4P00084593R9F</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649202 - KIT4P00066901JZZ</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00084593R9F</t>
+          <t>KIT4P00066901JZZ</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>816227</t>
+          <t>812926</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="L11" s="5" t="n"/>
       <c r="M11" s="7" t="n">
-        <v>727.3</v>
+        <v>781.74</v>
       </c>
     </row>
     <row r="12">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437292 - KIT4P000832806P4</t>
+          <t>SS - 05900510 -  Los Angeles, CA - 020955232 - KIT4M05563538RZV</t>
         </is>
       </c>
       <c r="C12" s="3" t="n">
@@ -1129,17 +1129,17 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>KIT4P000832806P4</t>
+          <t>KIT4M05563538RZV</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>816228</t>
+          <t>814459</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="L12" s="5" t="n"/>
       <c r="M12" s="7" t="n">
-        <v>722.6900000000001</v>
+        <v>772.1900000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="L13" s="5" t="n"/>
       <c r="M13" s="7" t="n">
-        <v>711.0700000000001</v>
+        <v>716.11</v>
       </c>
     </row>
     <row r="14">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L14" s="5" t="n"/>
       <c r="M14" s="7" t="n">
-        <v>693.37</v>
+        <v>708.66</v>
       </c>
     </row>
     <row r="15">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="L15" s="5" t="n"/>
       <c r="M15" s="7" t="n">
-        <v>631.21</v>
+        <v>650.1799999999999</v>
       </c>
     </row>
     <row r="16">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="L16" s="5" t="n"/>
       <c r="M16" s="7" t="n">
-        <v>622.72</v>
+        <v>643.77</v>
       </c>
     </row>
     <row r="17">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="L18" s="5" t="n"/>
       <c r="M18" s="7" t="n">
-        <v>467.59</v>
+        <v>476.04</v>
       </c>
     </row>
     <row r="19">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020650002 - KIT4M05413770WCC</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955052 - KIT4P00073152MPN</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
@@ -1500,17 +1500,17 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413770WCC</t>
+          <t>KIT4P00073152MPN</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>812819</t>
+          <t>814494</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="L19" s="5" t="n"/>
       <c r="M19" s="7" t="n">
-        <v>462.9</v>
+        <v>463.21</v>
       </c>
     </row>
     <row r="20">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955052 - KIT4P00073152MPN</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020650002 - KIT4M05413770WCC</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
@@ -1553,17 +1553,17 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073152MPN</t>
+          <t>KIT4M05413770WCC</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>814494</t>
+          <t>812819</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="L20" s="5" t="n"/>
       <c r="M20" s="7" t="n">
-        <v>429.22</v>
+        <v>462.9</v>
       </c>
     </row>
     <row r="21">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="L27" s="5" t="n"/>
       <c r="M27" s="7" t="n">
-        <v>269.63</v>
+        <v>271.13</v>
       </c>
     </row>
     <row r="28">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="L28" s="5" t="n"/>
       <c r="M28" s="7" t="n">
-        <v>252.15</v>
+        <v>253.57</v>
       </c>
     </row>
     <row r="29">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020649462-KIT4M05413796V9K</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437422 - KIT4M05872536JFD</t>
         </is>
       </c>
       <c r="C31" s="3" t="n">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413796V9K</t>
+          <t>KIT4M05872536JFD</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>812820</t>
+          <t>816070</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="L31" s="5" t="n"/>
       <c r="M31" s="7" t="n">
-        <v>220.94</v>
+        <v>222.58</v>
       </c>
     </row>
     <row r="32">
@@ -2178,7 +2178,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437422 - KIT4M05872536JFD</t>
+          <t>SMRT-05900510-Los Angeles CA-020649462-KIT4M05413796V9K</t>
         </is>
       </c>
       <c r="C32" s="3" t="n">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872536JFD</t>
+          <t>KIT4M05413796V9K</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>816070</t>
+          <t>812820</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="L32" s="5" t="n"/>
       <c r="M32" s="7" t="n">
-        <v>209.99</v>
+        <v>220.94</v>
       </c>
     </row>
     <row r="33">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="L33" s="5" t="n"/>
       <c r="M33" s="7" t="n">
-        <v>184.99</v>
+        <v>214.46</v>
       </c>
     </row>
     <row r="34">
@@ -2326,7 +2326,7 @@
       </c>
       <c r="L34" s="5" t="n"/>
       <c r="M34" s="7" t="n">
-        <v>176.35</v>
+        <v>205.17</v>
       </c>
     </row>
     <row r="35">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="L35" s="5" t="n"/>
       <c r="M35" s="7" t="n">
-        <v>149.04</v>
+        <v>157.27</v>
       </c>
     </row>
     <row r="36">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="L36" s="5" t="n"/>
       <c r="M36" s="7" t="n">
-        <v>141.58</v>
+        <v>150.01</v>
       </c>
     </row>
     <row r="37">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 -  Los Angeles CA - 020649422 - KIT4M05368200MVF</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649352 - KIT4M05368220FG8</t>
         </is>
       </c>
       <c r="C37" s="3" t="n">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368200MVF</t>
+          <t>KIT4M05368220FG8</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>810650</t>
+          <t>810648</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="L37" s="5" t="n"/>
       <c r="M37" s="7" t="n">
-        <v>126.59</v>
+        <v>128.41</v>
       </c>
     </row>
     <row r="38">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955672 - KIT4M055635979XD</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955682 - KIT4M055635887MK</t>
         </is>
       </c>
       <c r="C38" s="3" t="n">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635979XD</t>
+          <t>KIT4M055635887MK</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>814441</t>
+          <t>814446</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="L38" s="5" t="n"/>
       <c r="M38" s="7" t="n">
-        <v>125.83</v>
+        <v>126.61</v>
       </c>
     </row>
     <row r="39">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649352 - KIT4M05368220FG8</t>
+          <t>SMA - 05900510 -  Los Angeles CA - 020649422 - KIT4M05368200MVF</t>
         </is>
       </c>
       <c r="C39" s="3" t="n">
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368220FG8</t>
+          <t>KIT4M05368200MVF</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>810648</t>
+          <t>810650</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="L39" s="5" t="n"/>
       <c r="M39" s="7" t="n">
-        <v>122.56</v>
+        <v>126.59</v>
       </c>
     </row>
     <row r="40">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955682 - KIT4M055635887MK</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955672 - KIT4M055635979XD</t>
         </is>
       </c>
       <c r="C40" s="3" t="n">
@@ -2613,12 +2613,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635887MK</t>
+          <t>KIT4M055635979XD</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>814446</t>
+          <t>814441</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="L40" s="5" t="n"/>
       <c r="M40" s="7" t="n">
-        <v>121.78</v>
+        <v>126.18</v>
       </c>
     </row>
     <row r="41">
@@ -2655,7 +2655,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437252 - KIT4P00083897XCW</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955522 - KIT4M05563504MBB</t>
         </is>
       </c>
       <c r="C41" s="3" t="n">
@@ -2666,17 +2666,17 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00083897XCW</t>
+          <t>KIT4M05563504MBB</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>816223</t>
+          <t>814460</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="L41" s="5" t="n"/>
       <c r="M41" s="7" t="n">
-        <v>120.72</v>
+        <v>121.77</v>
       </c>
     </row>
     <row r="42">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="L42" s="5" t="n"/>
       <c r="M42" s="7" t="n">
-        <v>113.53</v>
+        <v>121.62</v>
       </c>
     </row>
     <row r="43">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020955622 - KIT4M05563549RSR</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437252 - KIT4P00083897XCW</t>
         </is>
       </c>
       <c r="C43" s="3" t="n">
@@ -2772,17 +2772,17 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563549RSR</t>
+          <t>KIT4P00083897XCW</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>814483</t>
+          <t>816223</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="L43" s="5" t="n"/>
       <c r="M43" s="7" t="n">
-        <v>113.16</v>
+        <v>120.74</v>
       </c>
     </row>
     <row r="44">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649542 - KIT4M05413810Q4Z</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482701116 - KIT4M03986275Q4M</t>
         </is>
       </c>
       <c r="C44" s="3" t="n">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413810Q4Z</t>
+          <t>KIT4M03986275Q4M</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>812815</t>
+          <t>809621</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="L44" s="5" t="n"/>
       <c r="M44" s="7" t="n">
-        <v>109.69</v>
+        <v>119.88</v>
       </c>
     </row>
     <row r="45">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955632 - KIT4M055635329VD</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020955622 - KIT4M05563549RSR</t>
         </is>
       </c>
       <c r="C45" s="3" t="n">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635329VD</t>
+          <t>KIT4M05563549RSR</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>814479</t>
+          <t>814483</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="L45" s="5" t="n"/>
       <c r="M45" s="7" t="n">
-        <v>109.26</v>
+        <v>113.16</v>
       </c>
     </row>
     <row r="46">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles, CA-020955372-KIT4M05563537G4G</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955632 - KIT4M055635329VD</t>
         </is>
       </c>
       <c r="C46" s="3" t="n">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563537G4G</t>
+          <t>KIT4M055635329VD</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>814456</t>
+          <t>814479</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="L46" s="5" t="n"/>
       <c r="M46" s="7" t="n">
-        <v>108.22</v>
+        <v>111.47</v>
       </c>
     </row>
     <row r="47">
@@ -2973,7 +2973,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020650172 - KIT4M05413811F4Q</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649542 - KIT4M05413810Q4Z</t>
         </is>
       </c>
       <c r="C47" s="3" t="n">
@@ -2984,12 +2984,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413811F4Q</t>
+          <t>KIT4M05413810Q4Z</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>810104</t>
+          <t>812815</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="L47" s="5" t="n"/>
       <c r="M47" s="7" t="n">
-        <v>99.02</v>
+        <v>109.69</v>
       </c>
     </row>
     <row r="48">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482701116 - KIT4M03986275Q4M</t>
+          <t>SMRT-05900510-Los Angeles, CA-020955372-KIT4M05563537G4G</t>
         </is>
       </c>
       <c r="C48" s="3" t="n">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03986275Q4M</t>
+          <t>KIT4M05563537G4G</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>809621</t>
+          <t>814456</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="L48" s="5" t="n"/>
       <c r="M48" s="7" t="n">
-        <v>96.95</v>
+        <v>108.22</v>
       </c>
     </row>
     <row r="49">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955522 - KIT4M05563504MBB</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020650172 - KIT4M05413811F4Q</t>
         </is>
       </c>
       <c r="C49" s="3" t="n">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563504MBB</t>
+          <t>KIT4M05413811F4Q</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>814460</t>
+          <t>810104</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="L49" s="5" t="n"/>
       <c r="M49" s="7" t="n">
-        <v>96.91</v>
+        <v>99.37</v>
       </c>
     </row>
     <row r="50">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="L50" s="5" t="n"/>
       <c r="M50" s="7" t="n">
-        <v>96.65000000000001</v>
+        <v>99.18000000000001</v>
       </c>
     </row>
     <row r="51">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020650212 - KIT4M05413779VSD</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827014 - KIT4M04475149XG5</t>
         </is>
       </c>
       <c r="C51" s="3" t="n">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413779VSD</t>
+          <t>KIT4M04475149XG5</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>810103</t>
+          <t>809657</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="L51" s="5" t="n"/>
       <c r="M51" s="7" t="n">
-        <v>96.01000000000001</v>
+        <v>98.89</v>
       </c>
     </row>
     <row r="52">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438042 - KIT4M05799686CMX</t>
+          <t>SS - 05900510 - Los Angeles CA - CW6578840- KIT4M04475128THH</t>
         </is>
       </c>
       <c r="C52" s="3" t="n">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799686CMX</t>
+          <t>KIT4M04475128THH</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>816282</t>
+          <t>809860</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="L52" s="5" t="n"/>
       <c r="M52" s="7" t="n">
-        <v>94.89</v>
+        <v>97.45999999999999</v>
       </c>
     </row>
     <row r="53">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955552 - KIT4M055635475JB</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020650212 - KIT4M05413779VSD</t>
         </is>
       </c>
       <c r="C53" s="3" t="n">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635475JB</t>
+          <t>KIT4M05413779VSD</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>814465</t>
+          <t>810103</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="L53" s="5" t="n"/>
       <c r="M53" s="7" t="n">
-        <v>93.37</v>
+        <v>96.01000000000001</v>
       </c>
     </row>
     <row r="54">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020650232 - KIT4M054138222CP</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438042 - KIT4M05799686CMX</t>
         </is>
       </c>
       <c r="C54" s="3" t="n">
@@ -3355,12 +3355,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138222CP</t>
+          <t>KIT4M05799686CMX</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>812811</t>
+          <t>816282</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="L54" s="5" t="n"/>
       <c r="M54" s="7" t="n">
-        <v>93.11</v>
+        <v>94.92</v>
       </c>
     </row>
     <row r="55">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955662 - KIT4M05563574ZBN</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955552 - KIT4M055635475JB</t>
         </is>
       </c>
       <c r="C55" s="3" t="n">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563574ZBN</t>
+          <t>KIT4M055635475JB</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>814453</t>
+          <t>814465</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="L55" s="5" t="n"/>
       <c r="M55" s="7" t="n">
-        <v>88.51000000000001</v>
+        <v>93.91</v>
       </c>
     </row>
     <row r="56">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955472 - KIT4M055635834N7</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020650232 - KIT4M054138222CP</t>
         </is>
       </c>
       <c r="C56" s="3" t="n">
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635834N7</t>
+          <t>KIT4M054138222CP</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>814462</t>
+          <t>812811</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="L56" s="5" t="n"/>
       <c r="M56" s="7" t="n">
-        <v>88.3</v>
+        <v>93.27</v>
       </c>
     </row>
     <row r="57">
@@ -3503,7 +3503,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955142 - KIT4M05563518ZJD</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955662 - KIT4M05563574ZBN</t>
         </is>
       </c>
       <c r="C57" s="3" t="n">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563518ZJD</t>
+          <t>KIT4M05563574ZBN</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>814451</t>
+          <t>814453</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="L57" s="5" t="n"/>
       <c r="M57" s="7" t="n">
-        <v>85.18000000000001</v>
+        <v>91.48999999999999</v>
       </c>
     </row>
     <row r="58">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649872 - KIT4M054138175VJ</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955472 - KIT4M055635834N7</t>
         </is>
       </c>
       <c r="C58" s="3" t="n">
@@ -3567,12 +3567,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138175VJ</t>
+          <t>KIT4M055635834N7</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>812823</t>
+          <t>814462</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="L58" s="5" t="n"/>
       <c r="M58" s="7" t="n">
-        <v>83.95</v>
+        <v>89.20999999999999</v>
       </c>
     </row>
     <row r="59">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955332 - KIT4M05563590ZFQ</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955182 - KIT4M05563562F45</t>
         </is>
       </c>
       <c r="C59" s="3" t="n">
@@ -3620,12 +3620,12 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563590ZFQ</t>
+          <t>KIT4M05563562F45</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>814461</t>
+          <t>814443</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
@@ -3651,7 +3651,7 @@
       </c>
       <c r="L59" s="5" t="n"/>
       <c r="M59" s="7" t="n">
-        <v>79.88</v>
+        <v>89.04000000000001</v>
       </c>
     </row>
     <row r="60">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649782 - KIT4M03986264P49</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955142 - KIT4M05563518ZJD</t>
         </is>
       </c>
       <c r="C60" s="3" t="n">
@@ -3673,12 +3673,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03986264P49</t>
+          <t>KIT4M05563518ZJD</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>809875</t>
+          <t>814451</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="L60" s="5" t="n"/>
       <c r="M60" s="7" t="n">
-        <v>76.11</v>
+        <v>85.18000000000001</v>
       </c>
     </row>
     <row r="61">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649562 - KIT4M054138125NW</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649872 - KIT4M054138175VJ</t>
         </is>
       </c>
       <c r="C61" s="3" t="n">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138125NW</t>
+          <t>KIT4M054138175VJ</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>812826</t>
+          <t>812823</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
@@ -3757,7 +3757,7 @@
       </c>
       <c r="L61" s="5" t="n"/>
       <c r="M61" s="7" t="n">
-        <v>75.64</v>
+        <v>83.95</v>
       </c>
     </row>
     <row r="62">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - CW6578840- KIT4M04475128THH</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649782 - KIT4M03986264P49</t>
         </is>
       </c>
       <c r="C62" s="3" t="n">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475128THH</t>
+          <t>KIT4M03986264P49</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>809860</t>
+          <t>809875</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="L62" s="5" t="n"/>
       <c r="M62" s="7" t="n">
-        <v>75.58</v>
+        <v>81.95</v>
       </c>
     </row>
     <row r="63">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955492 - KIT4M05563520SH2</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955332 - KIT4M05563590ZFQ</t>
         </is>
       </c>
       <c r="C63" s="3" t="n">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563520SH2</t>
+          <t>KIT4M05563590ZFQ</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>814478</t>
+          <t>814461</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="L63" s="5" t="n"/>
       <c r="M63" s="7" t="n">
-        <v>74.56999999999999</v>
+        <v>81.76000000000001</v>
       </c>
     </row>
     <row r="64">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827014 - KIT4M04475149XG5</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649562 - KIT4M054138125NW</t>
         </is>
       </c>
       <c r="C64" s="3" t="n">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475149XG5</t>
+          <t>KIT4M054138125NW</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>809657</t>
+          <t>812826</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="L64" s="5" t="n"/>
       <c r="M64" s="7" t="n">
-        <v>73.42</v>
+        <v>75.87</v>
       </c>
     </row>
     <row r="65">
@@ -3927,7 +3927,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955092 - KIT4P00073957GV5</t>
+          <t>SMRT-05900510-Los Angeles CA-020649312-KIT4M05413771PVH</t>
         </is>
       </c>
       <c r="C65" s="3" t="n">
@@ -3938,17 +3938,17 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073957GV5</t>
+          <t>KIT4M05413771PVH</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>814642</t>
+          <t>812800</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H65" s="5" t="inlineStr">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="L65" s="5" t="n"/>
       <c r="M65" s="7" t="n">
-        <v>72.83</v>
+        <v>74.87</v>
       </c>
     </row>
     <row r="66">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020649312-KIT4M05413771PVH</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955492 - KIT4M05563520SH2</t>
         </is>
       </c>
       <c r="C66" s="3" t="n">
@@ -3991,12 +3991,12 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413771PVH</t>
+          <t>KIT4M05563520SH2</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>812800</t>
+          <t>814478</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="L66" s="5" t="n"/>
       <c r="M66" s="7" t="n">
-        <v>71.22</v>
+        <v>74.56999999999999</v>
       </c>
     </row>
     <row r="67">
@@ -4033,7 +4033,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649272 - KIT4M05413784W4K</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955092 - KIT4P00073957GV5</t>
         </is>
       </c>
       <c r="C67" s="3" t="n">
@@ -4044,17 +4044,17 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413784W4K</t>
+          <t>KIT4P00073957GV5</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>812821</t>
+          <t>814642</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H67" s="5" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="L67" s="5" t="n"/>
       <c r="M67" s="7" t="n">
-        <v>69.13</v>
+        <v>72.83</v>
       </c>
     </row>
     <row r="68">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020650012 - KIT4M05413814GPJ</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955112 - KIT4P00073918HBX</t>
         </is>
       </c>
       <c r="C68" s="3" t="n">
@@ -4097,17 +4097,17 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413814GPJ</t>
+          <t>KIT4P00073918HBX</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>812812</t>
+          <t>814645</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H68" s="5" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="L68" s="5" t="n"/>
       <c r="M68" s="7" t="n">
-        <v>67.27</v>
+        <v>69.8</v>
       </c>
     </row>
     <row r="69">
@@ -4139,7 +4139,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020650252 - KIT4M05413820QXJ</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020650012 - KIT4M05413814GPJ</t>
         </is>
       </c>
       <c r="C69" s="3" t="n">
@@ -4150,12 +4150,12 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413820QXJ</t>
+          <t>KIT4M05413814GPJ</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>810098</t>
+          <t>812812</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="L69" s="5" t="n"/>
       <c r="M69" s="7" t="n">
-        <v>61.68</v>
+        <v>69.54000000000001</v>
       </c>
     </row>
     <row r="70">
@@ -4192,7 +4192,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020650102 - KIT4M054138257Z7</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649272 - KIT4M05413784W4K</t>
         </is>
       </c>
       <c r="C70" s="3" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138257Z7</t>
+          <t>KIT4M05413784W4K</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>810106</t>
+          <t>812821</t>
         </is>
       </c>
       <c r="G70" s="5" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="L70" s="5" t="n"/>
       <c r="M70" s="7" t="n">
-        <v>61.28</v>
+        <v>69.13</v>
       </c>
     </row>
     <row r="71">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649342 - KIT4M05413775N9M</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649712 - KIT4M046047397TM</t>
         </is>
       </c>
       <c r="C71" s="3" t="n">
@@ -4256,12 +4256,12 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413775N9M</t>
+          <t>KIT4M046047397TM</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>812818</t>
+          <t>809863</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
@@ -4287,7 +4287,7 @@
       </c>
       <c r="L71" s="5" t="n"/>
       <c r="M71" s="7" t="n">
-        <v>60.81</v>
+        <v>66.16</v>
       </c>
     </row>
     <row r="72">
@@ -4298,7 +4298,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SS - 05900510 - Los Angeles, CA - 020649552 - KIT4M05413835RPF </t>
+          <t>SS - 05900510 - Los Angeles CA - 020650102 - KIT4M054138257Z7</t>
         </is>
       </c>
       <c r="C72" s="3" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413835RPF</t>
+          <t>KIT4M054138257Z7</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>812827</t>
+          <t>810106</t>
         </is>
       </c>
       <c r="G72" s="5" t="inlineStr">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="L72" s="5" t="n"/>
       <c r="M72" s="7" t="n">
-        <v>60.78</v>
+        <v>65.58</v>
       </c>
     </row>
     <row r="73">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955112 - KIT4P00073918HBX</t>
+          <t xml:space="preserve">SS - 05900510 - Los Angeles, CA - 020649552 - KIT4M05413835RPF </t>
         </is>
       </c>
       <c r="C73" s="3" t="n">
@@ -4362,17 +4362,17 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073918HBX</t>
+          <t>KIT4M05413835RPF</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>814645</t>
+          <t>812827</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H73" s="5" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="L73" s="5" t="n"/>
       <c r="M73" s="7" t="n">
-        <v>59.84</v>
+        <v>64.22</v>
       </c>
     </row>
     <row r="74">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482702 - KIT4M04604743HSS</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955132 - KIT4M055635238J6</t>
         </is>
       </c>
       <c r="C74" s="3" t="n">
@@ -4415,12 +4415,12 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604743HSS</t>
+          <t>KIT4M055635238J6</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>809663</t>
+          <t>814449</t>
         </is>
       </c>
       <c r="G74" s="5" t="inlineStr">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="L74" s="5" t="n"/>
       <c r="M74" s="7" t="n">
-        <v>59.03</v>
+        <v>61.97</v>
       </c>
     </row>
     <row r="75">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482704 - KIT4M04604745G8Z</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020650252 - KIT4M05413820QXJ</t>
         </is>
       </c>
       <c r="C75" s="3" t="n">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604745G8Z</t>
+          <t>KIT4M05413820QXJ</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>809661</t>
+          <t>810098</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="L75" s="5" t="n"/>
       <c r="M75" s="7" t="n">
-        <v>57.14</v>
+        <v>61.69</v>
       </c>
     </row>
     <row r="76">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649902 - KIT4M05413805MKQ</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649342 - KIT4M05413775N9M</t>
         </is>
       </c>
       <c r="C76" s="3" t="n">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413805MKQ</t>
+          <t>KIT4M05413775N9M</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>812849</t>
+          <t>812818</t>
         </is>
       </c>
       <c r="G76" s="5" t="inlineStr">
@@ -4552,7 +4552,7 @@
       </c>
       <c r="L76" s="5" t="n"/>
       <c r="M76" s="7" t="n">
-        <v>56.64</v>
+        <v>61.35</v>
       </c>
     </row>
     <row r="77">
@@ -4563,7 +4563,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649762 - KIT4M0460475549Z</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438092 - KIT4M05799694RW2</t>
         </is>
       </c>
       <c r="C77" s="3" t="n">
@@ -4574,12 +4574,12 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0460475549Z</t>
+          <t>KIT4M05799694RW2</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>809859</t>
+          <t>816277</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr">
@@ -4605,7 +4605,7 @@
       </c>
       <c r="L77" s="5" t="n"/>
       <c r="M77" s="7" t="n">
-        <v>53.03</v>
+        <v>61.15</v>
       </c>
     </row>
     <row r="78">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955412 - KIT4M05563598Z74</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482702 - KIT4M04604743HSS</t>
         </is>
       </c>
       <c r="C78" s="3" t="n">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563598Z74</t>
+          <t>KIT4M04604743HSS</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>814474</t>
+          <t>809663</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="L78" s="5" t="n"/>
       <c r="M78" s="7" t="n">
-        <v>52.28</v>
+        <v>59.03</v>
       </c>
     </row>
     <row r="79">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955132 - KIT4M055635238J6</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649902 - KIT4M05413805MKQ</t>
         </is>
       </c>
       <c r="C79" s="3" t="n">
@@ -4680,12 +4680,12 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635238J6</t>
+          <t>KIT4M05413805MKQ</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>814449</t>
+          <t>812849</t>
         </is>
       </c>
       <c r="G79" s="5" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="L79" s="5" t="n"/>
       <c r="M79" s="7" t="n">
-        <v>51.56</v>
+        <v>58.35</v>
       </c>
     </row>
     <row r="80">
@@ -4722,7 +4722,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827011118 - KIT4M03867766NGK</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649932 - KIT4M054138324MW</t>
         </is>
       </c>
       <c r="C80" s="3" t="n">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03867766NGK</t>
+          <t>KIT4M054138324MW</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>809615</t>
+          <t>812834</t>
         </is>
       </c>
       <c r="G80" s="5" t="inlineStr">
@@ -4764,7 +4764,7 @@
       </c>
       <c r="L80" s="5" t="n"/>
       <c r="M80" s="7" t="n">
-        <v>50.95</v>
+        <v>57.51</v>
       </c>
     </row>
     <row r="81">
@@ -4775,7 +4775,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955292 - KIT4M05563531XSB</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482704 - KIT4M04604745G8Z</t>
         </is>
       </c>
       <c r="C81" s="3" t="n">
@@ -4786,12 +4786,12 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563531XSB</t>
+          <t>KIT4M04604745G8Z</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>814469</t>
+          <t>809661</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="L81" s="5" t="n"/>
       <c r="M81" s="7" t="n">
-        <v>50.76</v>
+        <v>57.14</v>
       </c>
     </row>
     <row r="82">
@@ -4828,7 +4828,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020650142 - KIT4M05413839D24</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955292 - KIT4M05563531XSB</t>
         </is>
       </c>
       <c r="C82" s="3" t="n">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413839D24</t>
+          <t>KIT4M05563531XSB</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>810096</t>
+          <t>814469</t>
         </is>
       </c>
       <c r="G82" s="5" t="inlineStr">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="L82" s="5" t="n"/>
       <c r="M82" s="7" t="n">
-        <v>50.33</v>
+        <v>56.35</v>
       </c>
     </row>
     <row r="83">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649932 - KIT4M054138324MW</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955262 - KIT4M05563521ZSX</t>
         </is>
       </c>
       <c r="C83" s="3" t="n">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138324MW</t>
+          <t>KIT4M05563521ZSX</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>812834</t>
+          <t>814476</t>
         </is>
       </c>
       <c r="G83" s="5" t="inlineStr">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="L83" s="5" t="n"/>
       <c r="M83" s="7" t="n">
-        <v>49.76</v>
+        <v>53.82</v>
       </c>
     </row>
     <row r="84">
@@ -4934,7 +4934,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270111114 - KIT4P00065593VWC</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955412 - KIT4M05563598Z74</t>
         </is>
       </c>
       <c r="C84" s="3" t="n">
@@ -4945,17 +4945,17 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065593VWC</t>
+          <t>KIT4M05563598Z74</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>809606</t>
+          <t>814474</t>
         </is>
       </c>
       <c r="G84" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H84" s="5" t="inlineStr">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="L84" s="5" t="n"/>
       <c r="M84" s="7" t="n">
-        <v>49.23</v>
+        <v>53.22</v>
       </c>
     </row>
     <row r="85">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955182 - KIT4M05563562F45</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649762 - KIT4M0460475549Z</t>
         </is>
       </c>
       <c r="C85" s="3" t="n">
@@ -4998,12 +4998,12 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563562F45</t>
+          <t>KIT4M0460475549Z</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>814443</t>
+          <t>809859</t>
         </is>
       </c>
       <c r="G85" s="5" t="inlineStr">
@@ -5029,7 +5029,7 @@
       </c>
       <c r="L85" s="5" t="n"/>
       <c r="M85" s="7" t="n">
-        <v>48.74</v>
+        <v>53.03</v>
       </c>
     </row>
     <row r="86">
@@ -5040,7 +5040,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649712 - KIT4M046047397TM</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827011118 - KIT4M03867766NGK</t>
         </is>
       </c>
       <c r="C86" s="3" t="n">
@@ -5051,12 +5051,12 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047397TM</t>
+          <t>KIT4M03867766NGK</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>809863</t>
+          <t>809615</t>
         </is>
       </c>
       <c r="G86" s="5" t="inlineStr">
@@ -5082,7 +5082,7 @@
       </c>
       <c r="L86" s="5" t="n"/>
       <c r="M86" s="7" t="n">
-        <v>48.64</v>
+        <v>52.85</v>
       </c>
     </row>
     <row r="87">
@@ -5093,7 +5093,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-LOS ANGELES CA-020955202-KIT4M05563534GZ7</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020650142 - KIT4M05413839D24</t>
         </is>
       </c>
       <c r="C87" s="3" t="n">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563534GZ7</t>
+          <t>KIT4M05413839D24</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>814467</t>
+          <t>810096</t>
         </is>
       </c>
       <c r="G87" s="5" t="inlineStr">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="L87" s="5" t="n"/>
       <c r="M87" s="7" t="n">
-        <v>48.53</v>
+        <v>50.33</v>
       </c>
     </row>
     <row r="88">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955262 - KIT4M05563521ZSX</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270111114 - KIT4P00065593VWC</t>
         </is>
       </c>
       <c r="C88" s="3" t="n">
@@ -5157,17 +5157,17 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563521ZSX</t>
+          <t>KIT4P00065593VWC</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>814476</t>
+          <t>809606</t>
         </is>
       </c>
       <c r="G88" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H88" s="5" t="inlineStr">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="L88" s="5" t="n"/>
       <c r="M88" s="7" t="n">
-        <v>48.34</v>
+        <v>49.23</v>
       </c>
     </row>
     <row r="89">
@@ -5199,7 +5199,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649672 - KIT4M04606113TPB</t>
+          <t>SMRT-05900510-LOS ANGELES CA-020955202-KIT4M05563534GZ7</t>
         </is>
       </c>
       <c r="C89" s="3" t="n">
@@ -5210,12 +5210,12 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04606113TPB</t>
+          <t>KIT4M05563534GZ7</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>809862</t>
+          <t>814467</t>
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr">
@@ -5241,7 +5241,7 @@
       </c>
       <c r="L89" s="5" t="n"/>
       <c r="M89" s="7" t="n">
-        <v>46.74</v>
+        <v>49.16</v>
       </c>
     </row>
     <row r="90">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="L90" s="5" t="n"/>
       <c r="M90" s="7" t="n">
-        <v>46.53</v>
+        <v>48.93</v>
       </c>
     </row>
     <row r="91">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="L91" s="5" t="n"/>
       <c r="M91" s="7" t="n">
-        <v>45.98</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="92">
@@ -5400,7 +5400,7 @@
       </c>
       <c r="L92" s="5" t="n"/>
       <c r="M92" s="7" t="n">
-        <v>45.91</v>
+        <v>47.81</v>
       </c>
     </row>
     <row r="93">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles, CA-020955452-KIT4M05563529K2D</t>
+          <t>SMRT-05900510-Los Angeles, CA-020955582-KIT4M05563593DMC</t>
         </is>
       </c>
       <c r="C93" s="3" t="n">
@@ -5422,12 +5422,12 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563529K2D</t>
+          <t>KIT4M05563593DMC</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>814473</t>
+          <t>814442</t>
         </is>
       </c>
       <c r="G93" s="5" t="inlineStr">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="L93" s="5" t="n"/>
       <c r="M93" s="7" t="n">
-        <v>45.09</v>
+        <v>47.67</v>
       </c>
     </row>
     <row r="94">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles, CA-020955582-KIT4M05563593DMC</t>
+          <t>SMRT-05900510-Los Angeles, CA-020955352-KIT4M05563525VC6</t>
         </is>
       </c>
       <c r="C94" s="3" t="n">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563593DMC</t>
+          <t>KIT4M05563525VC6</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>814442</t>
+          <t>814458</t>
         </is>
       </c>
       <c r="G94" s="5" t="inlineStr">
@@ -5506,7 +5506,7 @@
       </c>
       <c r="L94" s="5" t="n"/>
       <c r="M94" s="7" t="n">
-        <v>44.75</v>
+        <v>47.21</v>
       </c>
     </row>
     <row r="95">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649812 - KIT4M04604742S6S</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649672 - KIT4M04606113TPB</t>
         </is>
       </c>
       <c r="C95" s="3" t="n">
@@ -5528,12 +5528,12 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604742S6S</t>
+          <t>KIT4M04606113TPB</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>809874</t>
+          <t>809862</t>
         </is>
       </c>
       <c r="G95" s="5" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="L95" s="5" t="n"/>
       <c r="M95" s="7" t="n">
-        <v>43.24</v>
+        <v>46.74</v>
       </c>
     </row>
     <row r="96">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649432 - KIT4M05413778RBR</t>
+          <t>SMRT-05900510-Los Angeles, CA-020955452-KIT4M05563529K2D</t>
         </is>
       </c>
       <c r="C96" s="3" t="n">
@@ -5581,12 +5581,12 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413778RBR</t>
+          <t>KIT4M05563529K2D</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>812843</t>
+          <t>814473</t>
         </is>
       </c>
       <c r="G96" s="5" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="L96" s="5" t="n"/>
       <c r="M96" s="7" t="n">
-        <v>42.82</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="97">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020650192 - KIT4M054138007JF</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437392 - KIT4M05872555BJR</t>
         </is>
       </c>
       <c r="C97" s="3" t="n">
@@ -5634,12 +5634,12 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138007JF</t>
+          <t>KIT4M05872555BJR</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>810095</t>
+          <t>816074</t>
         </is>
       </c>
       <c r="G97" s="5" t="inlineStr">
@@ -5665,7 +5665,7 @@
       </c>
       <c r="L97" s="5" t="n"/>
       <c r="M97" s="7" t="n">
-        <v>42.59</v>
+        <v>45.06</v>
       </c>
     </row>
     <row r="98">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020650052 - KIT4M05413781K6C</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649372 - KIT4M05368221HQ5</t>
         </is>
       </c>
       <c r="C98" s="3" t="n">
@@ -5687,12 +5687,12 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413781K6C</t>
+          <t>KIT4M05368221HQ5</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>812798</t>
+          <t>810834</t>
         </is>
       </c>
       <c r="G98" s="5" t="inlineStr">
@@ -5718,7 +5718,7 @@
       </c>
       <c r="L98" s="5" t="n"/>
       <c r="M98" s="7" t="n">
-        <v>42.04</v>
+        <v>44.83</v>
       </c>
     </row>
     <row r="99">
@@ -5729,7 +5729,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles, CA-020955352-KIT4M05563525VC6</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649812 - KIT4M04604742S6S</t>
         </is>
       </c>
       <c r="C99" s="3" t="n">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563525VC6</t>
+          <t>KIT4M04604742S6S</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>814458</t>
+          <t>809874</t>
         </is>
       </c>
       <c r="G99" s="5" t="inlineStr">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="L99" s="5" t="n"/>
       <c r="M99" s="7" t="n">
-        <v>41.28</v>
+        <v>43.24</v>
       </c>
     </row>
     <row r="100">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437392 - KIT4M05872555BJR</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955692 - KIT4M05563579H9F</t>
         </is>
       </c>
       <c r="C100" s="3" t="n">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872555BJR</t>
+          <t>KIT4M05563579H9F</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>816074</t>
+          <t>814480</t>
         </is>
       </c>
       <c r="G100" s="5" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="L100" s="5" t="n"/>
       <c r="M100" s="7" t="n">
-        <v>41.21</v>
+        <v>43.15</v>
       </c>
     </row>
     <row r="101">
@@ -5835,7 +5835,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438092 - KIT4M05799694RW2</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649432 - KIT4M05413778RBR</t>
         </is>
       </c>
       <c r="C101" s="3" t="n">
@@ -5846,12 +5846,12 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799694RW2</t>
+          <t>KIT4M05413778RBR</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>816277</t>
+          <t>812843</t>
         </is>
       </c>
       <c r="G101" s="5" t="inlineStr">
@@ -5877,7 +5877,7 @@
       </c>
       <c r="L101" s="5" t="n"/>
       <c r="M101" s="7" t="n">
-        <v>40.13</v>
+        <v>42.82</v>
       </c>
     </row>
     <row r="102">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020955652 - KIT4M0556358988Z</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020650192 - KIT4M054138007JF</t>
         </is>
       </c>
       <c r="C102" s="3" t="n">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0556358988Z</t>
+          <t>KIT4M054138007JF</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>814484</t>
+          <t>810095</t>
         </is>
       </c>
       <c r="G102" s="5" t="inlineStr">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="L102" s="5" t="n"/>
       <c r="M102" s="7" t="n">
-        <v>39.91</v>
+        <v>42.59</v>
       </c>
     </row>
     <row r="103">
@@ -5941,7 +5941,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955702 - KIT4M05563571G8W</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020650052 - KIT4M05413781K6C</t>
         </is>
       </c>
       <c r="C103" s="3" t="n">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563571G8W</t>
+          <t>KIT4M05413781K6C</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>814481</t>
+          <t>812798</t>
         </is>
       </c>
       <c r="G103" s="5" t="inlineStr">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="L103" s="5" t="n"/>
       <c r="M103" s="7" t="n">
-        <v>39.83</v>
+        <v>42.04</v>
       </c>
     </row>
     <row r="104">
@@ -5994,7 +5994,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270116 - KIT4M03476116F45</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955702 - KIT4M05563571G8W</t>
         </is>
       </c>
       <c r="C104" s="3" t="n">
@@ -6005,12 +6005,12 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03476116F45</t>
+          <t>KIT4M05563571G8W</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>809608</t>
+          <t>814481</t>
         </is>
       </c>
       <c r="G104" s="5" t="inlineStr">
@@ -6036,7 +6036,7 @@
       </c>
       <c r="L104" s="5" t="n"/>
       <c r="M104" s="7" t="n">
-        <v>39.71</v>
+        <v>41.94</v>
       </c>
     </row>
     <row r="105">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955692 - KIT4M05563579H9F</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270116 - KIT4M03476116F45</t>
         </is>
       </c>
       <c r="C105" s="3" t="n">
@@ -6058,12 +6058,12 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563579H9F</t>
+          <t>KIT4M03476116F45</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>814480</t>
+          <t>809608</t>
         </is>
       </c>
       <c r="G105" s="5" t="inlineStr">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="L105" s="5" t="n"/>
       <c r="M105" s="7" t="n">
-        <v>39.23</v>
+        <v>40.11</v>
       </c>
     </row>
     <row r="106">
@@ -6100,7 +6100,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020650202-KIT4M05413803FDK</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020955652 - KIT4M0556358988Z</t>
         </is>
       </c>
       <c r="C106" s="3" t="n">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413803FDK</t>
+          <t>KIT4M0556358988Z</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>812850</t>
+          <t>814484</t>
         </is>
       </c>
       <c r="G106" s="5" t="inlineStr">
@@ -6142,7 +6142,7 @@
       </c>
       <c r="L106" s="5" t="n"/>
       <c r="M106" s="7" t="n">
-        <v>38.55</v>
+        <v>40.07</v>
       </c>
     </row>
     <row r="107">
@@ -6153,7 +6153,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955602 - KIT4M05563560225</t>
+          <t>SMRT-05900510-Los Angeles CA-020650202-KIT4M05413803FDK</t>
         </is>
       </c>
       <c r="C107" s="3" t="n">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563560225</t>
+          <t>KIT4M05413803FDK</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>814454</t>
+          <t>812850</t>
         </is>
       </c>
       <c r="G107" s="5" t="inlineStr">
@@ -6195,7 +6195,7 @@
       </c>
       <c r="L107" s="5" t="n"/>
       <c r="M107" s="7" t="n">
-        <v>38.09</v>
+        <v>39.74</v>
       </c>
     </row>
     <row r="108">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="L108" s="5" t="n"/>
       <c r="M108" s="7" t="n">
-        <v>37.99</v>
+        <v>38.57</v>
       </c>
     </row>
     <row r="109">
@@ -6259,7 +6259,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020650082 - KIT4M05413792H8C</t>
+          <t>SS - 05900510 - Los Angeles CA - 020650042 - KIT4M05413819JV5</t>
         </is>
       </c>
       <c r="C109" s="3" t="n">
@@ -6270,12 +6270,12 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413792H8C</t>
+          <t>KIT4M05413819JV5</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>812803</t>
+          <t>812796</t>
         </is>
       </c>
       <c r="G109" s="5" t="inlineStr">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="L109" s="5" t="n"/>
       <c r="M109" s="7" t="n">
-        <v>37.81</v>
+        <v>38.18</v>
       </c>
     </row>
     <row r="110">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955272 - KIT4M05563585TXM</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955602 - KIT4M05563560225</t>
         </is>
       </c>
       <c r="C110" s="3" t="n">
@@ -6323,12 +6323,12 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563585TXM</t>
+          <t>KIT4M05563560225</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>814475</t>
+          <t>814454</t>
         </is>
       </c>
       <c r="G110" s="5" t="inlineStr">
@@ -6354,7 +6354,7 @@
       </c>
       <c r="L110" s="5" t="n"/>
       <c r="M110" s="7" t="n">
-        <v>36.9</v>
+        <v>38.09</v>
       </c>
     </row>
     <row r="111">
@@ -6365,7 +6365,7 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020650042 - KIT4M05413819JV5</t>
+          <t>STS - 05900510 - Los Angeles CA - 020650082 - KIT4M05413792H8C</t>
         </is>
       </c>
       <c r="C111" s="3" t="n">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413819JV5</t>
+          <t>KIT4M05413792H8C</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>812796</t>
+          <t>812803</t>
         </is>
       </c>
       <c r="G111" s="5" t="inlineStr">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="L111" s="5" t="n"/>
       <c r="M111" s="7" t="n">
-        <v>35.26</v>
+        <v>37.81</v>
       </c>
     </row>
     <row r="112">
@@ -6418,7 +6418,7 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649942 - KIT4M05413786BXC</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955272 - KIT4M05563585TXM</t>
         </is>
       </c>
       <c r="C112" s="3" t="n">
@@ -6429,12 +6429,12 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413786BXC</t>
+          <t>KIT4M05563585TXM</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>812838</t>
+          <t>814475</t>
         </is>
       </c>
       <c r="G112" s="5" t="inlineStr">
@@ -6460,7 +6460,7 @@
       </c>
       <c r="L112" s="5" t="n"/>
       <c r="M112" s="7" t="n">
-        <v>34.4</v>
+        <v>36.91</v>
       </c>
     </row>
     <row r="113">
@@ -6471,7 +6471,7 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649412 - KIT4M05413769796</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827016 - KIT4M041536494G6</t>
         </is>
       </c>
       <c r="C113" s="3" t="n">
@@ -6482,12 +6482,12 @@
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413769796</t>
+          <t>KIT4M041536494G6</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>812839</t>
+          <t>809617</t>
         </is>
       </c>
       <c r="G113" s="5" t="inlineStr">
@@ -6513,7 +6513,7 @@
       </c>
       <c r="L113" s="5" t="n"/>
       <c r="M113" s="7" t="n">
-        <v>32.57</v>
+        <v>35.85</v>
       </c>
     </row>
     <row r="114">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020955462 - KIT4M05563513GTF</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649942 - KIT4M05413786BXC</t>
         </is>
       </c>
       <c r="C114" s="3" t="n">
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563513GTF</t>
+          <t>KIT4M05413786BXC</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>814432</t>
+          <t>812838</t>
         </is>
       </c>
       <c r="G114" s="5" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="L114" s="5" t="n"/>
       <c r="M114" s="7" t="n">
-        <v>31.71</v>
+        <v>34.4</v>
       </c>
     </row>
     <row r="115">
@@ -6577,7 +6577,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482706 - KIT4M04604744V6K</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020955462 - KIT4M05563513GTF</t>
         </is>
       </c>
       <c r="C115" s="3" t="n">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604744V6K</t>
+          <t>KIT4M05563513GTF</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>809659</t>
+          <t>814432</t>
         </is>
       </c>
       <c r="G115" s="5" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="L115" s="5" t="n"/>
       <c r="M115" s="7" t="n">
-        <v>31.38</v>
+        <v>34.21</v>
       </c>
     </row>
     <row r="116">
@@ -6672,7 +6672,7 @@
       </c>
       <c r="L116" s="5" t="n"/>
       <c r="M116" s="7" t="n">
-        <v>30</v>
+        <v>33.91</v>
       </c>
     </row>
     <row r="117">
@@ -6683,7 +6683,7 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649372 - KIT4M05368221HQ5</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649412 - KIT4M05413769796</t>
         </is>
       </c>
       <c r="C117" s="3" t="n">
@@ -6694,12 +6694,12 @@
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368221HQ5</t>
+          <t>KIT4M05413769796</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>810834</t>
+          <t>812839</t>
         </is>
       </c>
       <c r="G117" s="5" t="inlineStr">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="L117" s="5" t="n"/>
       <c r="M117" s="7" t="n">
-        <v>29.14</v>
+        <v>32.57</v>
       </c>
     </row>
     <row r="118">
@@ -6736,7 +6736,7 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 6858375 - KIT4M05872512N5W</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482706 - KIT4M04604744V6K</t>
         </is>
       </c>
       <c r="C118" s="3" t="n">
@@ -6747,12 +6747,12 @@
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872512N5W</t>
+          <t>KIT4M04604744V6K</t>
         </is>
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>816077</t>
+          <t>809659</t>
         </is>
       </c>
       <c r="G118" s="5" t="inlineStr">
@@ -6778,7 +6778,7 @@
       </c>
       <c r="L118" s="5" t="n"/>
       <c r="M118" s="7" t="n">
-        <v>28.95</v>
+        <v>31.38</v>
       </c>
     </row>
     <row r="119">
@@ -6789,7 +6789,7 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827016 - KIT4M041536494G6</t>
+          <t>SS - 05900510 - Los Angeles CA - 6858375 - KIT4M05872512N5W</t>
         </is>
       </c>
       <c r="C119" s="3" t="n">
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>KIT4M041536494G6</t>
+          <t>KIT4M05872512N5W</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>809617</t>
+          <t>816077</t>
         </is>
       </c>
       <c r="G119" s="5" t="inlineStr">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="L119" s="5" t="n"/>
       <c r="M119" s="7" t="n">
-        <v>28.61</v>
+        <v>29.42</v>
       </c>
     </row>
     <row r="120">
@@ -6842,7 +6842,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649742 - KIT4M04350554X4Z</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649682 - KIT4M046047384RX</t>
         </is>
       </c>
       <c r="C120" s="3" t="n">
@@ -6853,12 +6853,12 @@
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04350554X4Z</t>
+          <t>KIT4M046047384RX</t>
         </is>
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t>809866</t>
+          <t>809870</t>
         </is>
       </c>
       <c r="G120" s="5" t="inlineStr">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="L120" s="5" t="n"/>
       <c r="M120" s="7" t="n">
-        <v>27.16</v>
+        <v>28.64</v>
       </c>
     </row>
     <row r="121">
@@ -6895,7 +6895,7 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649532 - KIT4M05413808FFZ</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438152 - KIT4M05799733FPK</t>
         </is>
       </c>
       <c r="C121" s="3" t="n">
@@ -6906,12 +6906,12 @@
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413808FFZ</t>
+          <t>KIT4M05799733FPK</t>
         </is>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>812828</t>
+          <t>816286</t>
         </is>
       </c>
       <c r="G121" s="5" t="inlineStr">
@@ -6937,7 +6937,7 @@
       </c>
       <c r="L121" s="5" t="n"/>
       <c r="M121" s="7" t="n">
-        <v>26.76</v>
+        <v>28.34</v>
       </c>
     </row>
     <row r="122">
@@ -6948,7 +6948,7 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955342 - KIT4M05563524MJ4</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649212 - KIT4P00065633ZXC</t>
         </is>
       </c>
       <c r="C122" s="3" t="n">
@@ -6959,17 +6959,17 @@
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563524MJ4</t>
+          <t>KIT4P00065633ZXC</t>
         </is>
       </c>
       <c r="F122" s="4" t="inlineStr">
         <is>
-          <t>814472</t>
+          <t>812922</t>
         </is>
       </c>
       <c r="G122" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H122" s="5" t="inlineStr">
@@ -6990,7 +6990,7 @@
       </c>
       <c r="L122" s="5" t="n"/>
       <c r="M122" s="7" t="n">
-        <v>26.26</v>
+        <v>27.32</v>
       </c>
     </row>
     <row r="123">
@@ -7001,7 +7001,7 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649212 - KIT4P00065633ZXC</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649742 - KIT4M04350554X4Z</t>
         </is>
       </c>
       <c r="C123" s="3" t="n">
@@ -7012,17 +7012,17 @@
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065633ZXC</t>
+          <t>KIT4M04350554X4Z</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>812922</t>
+          <t>809866</t>
         </is>
       </c>
       <c r="G123" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H123" s="5" t="inlineStr">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="L123" s="5" t="n"/>
       <c r="M123" s="7" t="n">
-        <v>25.67</v>
+        <v>27.16</v>
       </c>
     </row>
     <row r="124">
@@ -7054,7 +7054,7 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649362 - KIT4M05368336DBC</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649532 - KIT4M05413808FFZ</t>
         </is>
       </c>
       <c r="C124" s="3" t="n">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368336DBC</t>
+          <t>KIT4M05413808FFZ</t>
         </is>
       </c>
       <c r="F124" s="4" t="inlineStr">
         <is>
-          <t>810831</t>
+          <t>812828</t>
         </is>
       </c>
       <c r="G124" s="5" t="inlineStr">
@@ -7096,7 +7096,7 @@
       </c>
       <c r="L124" s="5" t="n"/>
       <c r="M124" s="7" t="n">
-        <v>25.13</v>
+        <v>27.14</v>
       </c>
     </row>
     <row r="125">
@@ -7107,7 +7107,7 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955212 - KIT4M05563512GBQ</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955342 - KIT4M05563524MJ4</t>
         </is>
       </c>
       <c r="C125" s="3" t="n">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563512GBQ</t>
+          <t>KIT4M05563524MJ4</t>
         </is>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>814435</t>
+          <t>814472</t>
         </is>
       </c>
       <c r="G125" s="5" t="inlineStr">
@@ -7149,7 +7149,7 @@
       </c>
       <c r="L125" s="5" t="n"/>
       <c r="M125" s="7" t="n">
-        <v>24.55</v>
+        <v>26.26</v>
       </c>
     </row>
     <row r="126">
@@ -7160,7 +7160,7 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438152 - KIT4M05799733FPK</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437782 - KIT4M058724975J4</t>
         </is>
       </c>
       <c r="C126" s="3" t="n">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799733FPK</t>
+          <t>KIT4M058724975J4</t>
         </is>
       </c>
       <c r="F126" s="4" t="inlineStr">
         <is>
-          <t>816286</t>
+          <t>816075</t>
         </is>
       </c>
       <c r="G126" s="5" t="inlineStr">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="L126" s="5" t="n"/>
       <c r="M126" s="7" t="n">
-        <v>24.22</v>
+        <v>26.05</v>
       </c>
     </row>
     <row r="127">
@@ -7213,7 +7213,7 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437782 - KIT4M058724975J4</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649362 - KIT4M05368336DBC</t>
         </is>
       </c>
       <c r="C127" s="3" t="n">
@@ -7224,12 +7224,12 @@
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058724975J4</t>
+          <t>KIT4M05368336DBC</t>
         </is>
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>816075</t>
+          <t>810831</t>
         </is>
       </c>
       <c r="G127" s="5" t="inlineStr">
@@ -7255,7 +7255,7 @@
       </c>
       <c r="L127" s="5" t="n"/>
       <c r="M127" s="7" t="n">
-        <v>23.93</v>
+        <v>25.14</v>
       </c>
     </row>
     <row r="128">
@@ -7266,7 +7266,7 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649682 - KIT4M046047384RX</t>
+          <t>SS - 05900510 -  Los Angeles CA - 021437622 - KIT4M0587258755W</t>
         </is>
       </c>
       <c r="C128" s="3" t="n">
@@ -7277,12 +7277,12 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047384RX</t>
+          <t>KIT4M0587258755W</t>
         </is>
       </c>
       <c r="F128" s="4" t="inlineStr">
         <is>
-          <t>809870</t>
+          <t>816187</t>
         </is>
       </c>
       <c r="G128" s="5" t="inlineStr">
@@ -7308,7 +7308,7 @@
       </c>
       <c r="L128" s="5" t="n"/>
       <c r="M128" s="7" t="n">
-        <v>23.82</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="129">
@@ -7319,7 +7319,7 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020650162 - KIT4M05413837SMB</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955212 - KIT4M05563512GBQ</t>
         </is>
       </c>
       <c r="C129" s="3" t="n">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413837SMB</t>
+          <t>KIT4M05563512GBQ</t>
         </is>
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>810100</t>
+          <t>814435</t>
         </is>
       </c>
       <c r="G129" s="5" t="inlineStr">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="L129" s="5" t="n"/>
       <c r="M129" s="7" t="n">
-        <v>23.32</v>
+        <v>24.55</v>
       </c>
     </row>
     <row r="130">
@@ -7372,7 +7372,7 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020649292-KIT4M05368201SNV</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649822 - KIT4M04604740BM6</t>
         </is>
       </c>
       <c r="C130" s="3" t="n">
@@ -7383,12 +7383,12 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368201SNV</t>
+          <t>KIT4M04604740BM6</t>
         </is>
       </c>
       <c r="F130" s="4" t="inlineStr">
         <is>
-          <t>810651</t>
+          <t>809872</t>
         </is>
       </c>
       <c r="G130" s="5" t="inlineStr">
@@ -7414,7 +7414,7 @@
       </c>
       <c r="L130" s="5" t="n"/>
       <c r="M130" s="7" t="n">
-        <v>22.78</v>
+        <v>23.9</v>
       </c>
     </row>
     <row r="131">
@@ -7425,7 +7425,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438002 - KIT4M05799701SGS</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649832 - KIT4M03866596RZG</t>
         </is>
       </c>
       <c r="C131" s="3" t="n">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799701SGS</t>
+          <t>KIT4M03866596RZG</t>
         </is>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>816284</t>
+          <t>809869</t>
         </is>
       </c>
       <c r="G131" s="5" t="inlineStr">
@@ -7467,7 +7467,7 @@
       </c>
       <c r="L131" s="5" t="n"/>
       <c r="M131" s="7" t="n">
-        <v>22.13</v>
+        <v>23.59</v>
       </c>
     </row>
     <row r="132">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020650132-KIT4M05413828PCT</t>
+          <t>SMRT-05900510-Los Angeles CA-020649292-KIT4M05368201SNV</t>
         </is>
       </c>
       <c r="C132" s="3" t="n">
@@ -7489,12 +7489,12 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413828PCT</t>
+          <t>KIT4M05368201SNV</t>
         </is>
       </c>
       <c r="F132" s="4" t="inlineStr">
         <is>
-          <t>812799</t>
+          <t>810651</t>
         </is>
       </c>
       <c r="G132" s="5" t="inlineStr">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="L132" s="5" t="n"/>
       <c r="M132" s="7" t="n">
-        <v>21.54</v>
+        <v>23.32</v>
       </c>
     </row>
     <row r="133">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-LOS ANGELES CA-020955172-KIT4M05563526WNC</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020650162 - KIT4M05413837SMB</t>
         </is>
       </c>
       <c r="C133" s="3" t="n">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563526WNC</t>
+          <t>KIT4M05413837SMB</t>
         </is>
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>814463</t>
+          <t>810100</t>
         </is>
       </c>
       <c r="G133" s="5" t="inlineStr">
@@ -7573,7 +7573,7 @@
       </c>
       <c r="L133" s="5" t="n"/>
       <c r="M133" s="7" t="n">
-        <v>21.16</v>
+        <v>23.32</v>
       </c>
     </row>
     <row r="134">
@@ -7584,7 +7584,7 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 021437622 - KIT4M0587258755W</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438002 - KIT4M05799701SGS</t>
         </is>
       </c>
       <c r="C134" s="3" t="n">
@@ -7595,12 +7595,12 @@
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0587258755W</t>
+          <t>KIT4M05799701SGS</t>
         </is>
       </c>
       <c r="F134" s="4" t="inlineStr">
         <is>
-          <t>816187</t>
+          <t>816284</t>
         </is>
       </c>
       <c r="G134" s="5" t="inlineStr">
@@ -7626,7 +7626,7 @@
       </c>
       <c r="L134" s="5" t="n"/>
       <c r="M134" s="7" t="n">
-        <v>21.03</v>
+        <v>22.82</v>
       </c>
     </row>
     <row r="135">
@@ -7637,7 +7637,7 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020650072-KIT4M054137987GJ</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020650242 - KIT4M05413804SKS</t>
         </is>
       </c>
       <c r="C135" s="3" t="n">
@@ -7648,12 +7648,12 @@
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137987GJ</t>
+          <t>KIT4M05413804SKS</t>
         </is>
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>812795</t>
+          <t>810102</t>
         </is>
       </c>
       <c r="G135" s="5" t="inlineStr">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="L135" s="5" t="n"/>
       <c r="M135" s="7" t="n">
-        <v>20.74</v>
+        <v>21.64</v>
       </c>
     </row>
     <row r="136">
@@ -7690,7 +7690,7 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482701112 - KIT4M04158973M2C</t>
+          <t>SMRT-05900510-Los Angeles CA-020650132-KIT4M05413828PCT</t>
         </is>
       </c>
       <c r="C136" s="3" t="n">
@@ -7701,12 +7701,12 @@
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158973M2C</t>
+          <t>KIT4M05413828PCT</t>
         </is>
       </c>
       <c r="F136" s="4" t="inlineStr">
         <is>
-          <t>809610</t>
+          <t>812799</t>
         </is>
       </c>
       <c r="G136" s="5" t="inlineStr">
@@ -7732,7 +7732,7 @@
       </c>
       <c r="L136" s="5" t="n"/>
       <c r="M136" s="7" t="n">
-        <v>20.45</v>
+        <v>21.54</v>
       </c>
     </row>
     <row r="137">
@@ -7743,7 +7743,7 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649222 - KIT4P00065640BFW</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482701112 - KIT4M04158973M2C</t>
         </is>
       </c>
       <c r="C137" s="3" t="n">
@@ -7754,17 +7754,17 @@
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065640BFW</t>
+          <t>KIT4M04158973M2C</t>
         </is>
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>812929</t>
+          <t>809610</t>
         </is>
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr">
@@ -7785,7 +7785,7 @@
       </c>
       <c r="L137" s="5" t="n"/>
       <c r="M137" s="7" t="n">
-        <v>19.87</v>
+        <v>21.32</v>
       </c>
     </row>
     <row r="138">
@@ -7796,7 +7796,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649912 - KIT4M05413836KJC</t>
+          <t>SMRT-05900510-LOS ANGELES CA-020955172-KIT4M05563526WNC</t>
         </is>
       </c>
       <c r="C138" s="3" t="n">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413836KJC</t>
+          <t>KIT4M05563526WNC</t>
         </is>
       </c>
       <c r="F138" s="4" t="inlineStr">
         <is>
-          <t>810097</t>
+          <t>814463</t>
         </is>
       </c>
       <c r="G138" s="5" t="inlineStr">
@@ -7838,7 +7838,7 @@
       </c>
       <c r="L138" s="5" t="n"/>
       <c r="M138" s="7" t="n">
-        <v>19.73</v>
+        <v>21.16</v>
       </c>
     </row>
     <row r="139">
@@ -7849,7 +7849,7 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020650242 - KIT4M05413804SKS</t>
+          <t>SMRT-05900510-Los Angeles CA-020650072-KIT4M054137987GJ</t>
         </is>
       </c>
       <c r="C139" s="3" t="n">
@@ -7860,12 +7860,12 @@
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413804SKS</t>
+          <t>KIT4M054137987GJ</t>
         </is>
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>810102</t>
+          <t>812795</t>
         </is>
       </c>
       <c r="G139" s="5" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="L139" s="5" t="n"/>
       <c r="M139" s="7" t="n">
-        <v>19.68</v>
+        <v>20.74</v>
       </c>
     </row>
     <row r="140">
@@ -7902,7 +7902,7 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649302 - KIT4M05368226W57</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955712 - KIT4M05563586ZTR</t>
         </is>
       </c>
       <c r="C140" s="3" t="n">
@@ -7913,12 +7913,12 @@
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368226W57</t>
+          <t>KIT4M05563586ZTR</t>
         </is>
       </c>
       <c r="F140" s="4" t="inlineStr">
         <is>
-          <t>810833</t>
+          <t>814445</t>
         </is>
       </c>
       <c r="G140" s="5" t="inlineStr">
@@ -7944,7 +7944,7 @@
       </c>
       <c r="L140" s="5" t="n"/>
       <c r="M140" s="7" t="n">
-        <v>19.62</v>
+        <v>20.15</v>
       </c>
     </row>
     <row r="141">
@@ -7955,7 +7955,7 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955532 - KIT4M05563548P9Q</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649222 - KIT4P00065640BFW</t>
         </is>
       </c>
       <c r="C141" s="3" t="n">
@@ -7966,17 +7966,17 @@
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563548P9Q</t>
+          <t>KIT4P00065640BFW</t>
         </is>
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>814468</t>
+          <t>812929</t>
         </is>
       </c>
       <c r="G141" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H141" s="5" t="inlineStr">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="L141" s="5" t="n"/>
       <c r="M141" s="7" t="n">
-        <v>19.27</v>
+        <v>19.87</v>
       </c>
     </row>
     <row r="142">
@@ -8008,7 +8008,7 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955282 - KIT4M055635227ZR</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955532 - KIT4M05563548P9Q</t>
         </is>
       </c>
       <c r="C142" s="3" t="n">
@@ -8019,12 +8019,12 @@
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635227ZR</t>
+          <t>KIT4M05563548P9Q</t>
         </is>
       </c>
       <c r="F142" s="4" t="inlineStr">
         <is>
-          <t>814482</t>
+          <t>814468</t>
         </is>
       </c>
       <c r="G142" s="5" t="inlineStr">
@@ -8050,7 +8050,7 @@
       </c>
       <c r="L142" s="5" t="n"/>
       <c r="M142" s="7" t="n">
-        <v>19.17</v>
+        <v>19.77</v>
       </c>
     </row>
     <row r="143">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955302 - KIT4M055635158PC</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649912 - KIT4M05413836KJC</t>
         </is>
       </c>
       <c r="C143" s="3" t="n">
@@ -8072,12 +8072,12 @@
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635158PC</t>
+          <t>KIT4M05413836KJC</t>
         </is>
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>814457</t>
+          <t>810097</t>
         </is>
       </c>
       <c r="G143" s="5" t="inlineStr">
@@ -8103,7 +8103,7 @@
       </c>
       <c r="L143" s="5" t="n"/>
       <c r="M143" s="7" t="n">
-        <v>18.74</v>
+        <v>19.73</v>
       </c>
     </row>
     <row r="144">
@@ -8114,7 +8114,7 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA  - 020649722 - KIT4M04604747TPT</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649302 - KIT4M05368226W57</t>
         </is>
       </c>
       <c r="C144" s="3" t="n">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604747TPT</t>
+          <t>KIT4M05368226W57</t>
         </is>
       </c>
       <c r="F144" s="4" t="inlineStr">
         <is>
-          <t>809873</t>
+          <t>810833</t>
         </is>
       </c>
       <c r="G144" s="5" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="L144" s="5" t="n"/>
       <c r="M144" s="7" t="n">
-        <v>18.44</v>
+        <v>19.62</v>
       </c>
     </row>
     <row r="145">
@@ -8167,7 +8167,7 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649632 - KIT4M054138064J9</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437992 -  KIT4M05799663CPM</t>
         </is>
       </c>
       <c r="C145" s="3" t="n">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138064J9</t>
+          <t>KIT4M05799663CPM</t>
         </is>
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>812844</t>
+          <t>816272</t>
         </is>
       </c>
       <c r="G145" s="5" t="inlineStr">
@@ -8209,7 +8209,7 @@
       </c>
       <c r="L145" s="5" t="n"/>
       <c r="M145" s="7" t="n">
-        <v>17.18</v>
+        <v>19.53</v>
       </c>
     </row>
     <row r="146">
@@ -8262,7 +8262,7 @@
       </c>
       <c r="L146" s="5" t="n"/>
       <c r="M146" s="7" t="n">
-        <v>16.64</v>
+        <v>19.27</v>
       </c>
     </row>
     <row r="147">
@@ -8273,7 +8273,7 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649592 - KIT4M05413787HHK</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955282 - KIT4M055635227ZR</t>
         </is>
       </c>
       <c r="C147" s="3" t="n">
@@ -8284,12 +8284,12 @@
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413787HHK</t>
+          <t>KIT4M055635227ZR</t>
         </is>
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>812809</t>
+          <t>814482</t>
         </is>
       </c>
       <c r="G147" s="5" t="inlineStr">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="L147" s="5" t="n"/>
       <c r="M147" s="7" t="n">
-        <v>15.65</v>
+        <v>19.17</v>
       </c>
     </row>
     <row r="148">
@@ -8326,7 +8326,7 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482708 - KIT4M04604736T7C</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955302 - KIT4M055635158PC</t>
         </is>
       </c>
       <c r="C148" s="3" t="n">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604736T7C</t>
+          <t>KIT4M055635158PC</t>
         </is>
       </c>
       <c r="F148" s="4" t="inlineStr">
         <is>
-          <t>809662</t>
+          <t>814457</t>
         </is>
       </c>
       <c r="G148" s="5" t="inlineStr">
@@ -8368,7 +8368,7 @@
       </c>
       <c r="L148" s="5" t="n"/>
       <c r="M148" s="7" t="n">
-        <v>15.55</v>
+        <v>18.76</v>
       </c>
     </row>
     <row r="149">
@@ -8379,7 +8379,7 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649832 - KIT4M03866596RZG</t>
+          <t>SS - 05900510 - Los Angeles, CA  - 020649722 - KIT4M04604747TPT</t>
         </is>
       </c>
       <c r="C149" s="3" t="n">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03866596RZG</t>
+          <t>KIT4M04604747TPT</t>
         </is>
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>809869</t>
+          <t>809873</t>
         </is>
       </c>
       <c r="G149" s="5" t="inlineStr">
@@ -8421,7 +8421,7 @@
       </c>
       <c r="L149" s="5" t="n"/>
       <c r="M149" s="7" t="n">
-        <v>15.46</v>
+        <v>18.44</v>
       </c>
     </row>
     <row r="150">
@@ -8432,7 +8432,7 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955712 - KIT4M05563586ZTR</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649632 - KIT4M054138064J9</t>
         </is>
       </c>
       <c r="C150" s="3" t="n">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563586ZTR</t>
+          <t>KIT4M054138064J9</t>
         </is>
       </c>
       <c r="F150" s="4" t="inlineStr">
         <is>
-          <t>814445</t>
+          <t>812844</t>
         </is>
       </c>
       <c r="G150" s="5" t="inlineStr">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="L150" s="5" t="n"/>
       <c r="M150" s="7" t="n">
-        <v>15.39</v>
+        <v>17.18</v>
       </c>
     </row>
     <row r="151">
@@ -8485,7 +8485,7 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437992 -  KIT4M05799663CPM</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649592 - KIT4M05413787HHK</t>
         </is>
       </c>
       <c r="C151" s="3" t="n">
@@ -8496,12 +8496,12 @@
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799663CPM</t>
+          <t>KIT4M05413787HHK</t>
         </is>
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>816272</t>
+          <t>812809</t>
         </is>
       </c>
       <c r="G151" s="5" t="inlineStr">
@@ -8527,7 +8527,7 @@
       </c>
       <c r="L151" s="5" t="n"/>
       <c r="M151" s="7" t="n">
-        <v>14.71</v>
+        <v>15.65</v>
       </c>
     </row>
     <row r="152">
@@ -8538,7 +8538,7 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438222 - KIT4M058725299QP</t>
+          <t>SMA - 05900510 -  Los Angeles CA - 020649512 - KIT4M054138318Q7</t>
         </is>
       </c>
       <c r="C152" s="3" t="n">
@@ -8549,12 +8549,12 @@
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725299QP</t>
+          <t>KIT4M054138318Q7</t>
         </is>
       </c>
       <c r="F152" s="4" t="inlineStr">
         <is>
-          <t>816080</t>
+          <t>812814</t>
         </is>
       </c>
       <c r="G152" s="5" t="inlineStr">
@@ -8580,7 +8580,7 @@
       </c>
       <c r="L152" s="5" t="n"/>
       <c r="M152" s="7" t="n">
-        <v>14.7</v>
+        <v>15.63</v>
       </c>
     </row>
     <row r="153">
@@ -8591,7 +8591,7 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020649862 - KIT4M04475159PMD</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482708 - KIT4M04604736T7C</t>
         </is>
       </c>
       <c r="C153" s="3" t="n">
@@ -8602,12 +8602,12 @@
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475159PMD</t>
+          <t>KIT4M04604736T7C</t>
         </is>
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>809868</t>
+          <t>809662</t>
         </is>
       </c>
       <c r="G153" s="5" t="inlineStr">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="L153" s="5" t="n"/>
       <c r="M153" s="7" t="n">
-        <v>14.45</v>
+        <v>15.63</v>
       </c>
     </row>
     <row r="154">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - CW6642812 - KIT4M054138292ZP</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438072 - KIT4M057996885ZV</t>
         </is>
       </c>
       <c r="C154" s="3" t="n">
@@ -8655,12 +8655,12 @@
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138292ZP</t>
+          <t>KIT4M057996885ZV</t>
         </is>
       </c>
       <c r="F154" s="4" t="inlineStr">
         <is>
-          <t>812784</t>
+          <t>816269</t>
         </is>
       </c>
       <c r="G154" s="5" t="inlineStr">
@@ -8686,7 +8686,7 @@
       </c>
       <c r="L154" s="5" t="n"/>
       <c r="M154" s="7" t="n">
-        <v>14.37</v>
+        <v>15.2</v>
       </c>
     </row>
     <row r="155">
@@ -8697,7 +8697,7 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 -  Los Angeles CA - 020649512 - KIT4M054138318Q7</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438222 - KIT4M058725299QP</t>
         </is>
       </c>
       <c r="C155" s="3" t="n">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138318Q7</t>
+          <t>KIT4M058725299QP</t>
         </is>
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>812814</t>
+          <t>816080</t>
         </is>
       </c>
       <c r="G155" s="5" t="inlineStr">
@@ -8739,7 +8739,7 @@
       </c>
       <c r="L155" s="5" t="n"/>
       <c r="M155" s="7" t="n">
-        <v>14.26</v>
+        <v>14.88</v>
       </c>
     </row>
     <row r="156">
@@ -8750,7 +8750,7 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438072 - KIT4M057996885ZV</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955362 - KIT4M05563528MKX</t>
         </is>
       </c>
       <c r="C156" s="3" t="n">
@@ -8761,12 +8761,12 @@
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>KIT4M057996885ZV</t>
+          <t>KIT4M05563528MKX</t>
         </is>
       </c>
       <c r="F156" s="4" t="inlineStr">
         <is>
-          <t>816269</t>
+          <t>814471</t>
         </is>
       </c>
       <c r="G156" s="5" t="inlineStr">
@@ -8792,7 +8792,7 @@
       </c>
       <c r="L156" s="5" t="n"/>
       <c r="M156" s="7" t="n">
-        <v>13.64</v>
+        <v>14.51</v>
       </c>
     </row>
     <row r="157">
@@ -8803,7 +8803,7 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649442 - KIT4M054137885SM</t>
+          <t>SMA - 05900510 - Los Angeles CA - CW6642812 - KIT4M054138292ZP</t>
         </is>
       </c>
       <c r="C157" s="3" t="n">
@@ -8814,12 +8814,12 @@
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137885SM</t>
+          <t>KIT4M054138292ZP</t>
         </is>
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>812846</t>
+          <t>812784</t>
         </is>
       </c>
       <c r="G157" s="5" t="inlineStr">
@@ -8845,7 +8845,7 @@
       </c>
       <c r="L157" s="5" t="n"/>
       <c r="M157" s="7" t="n">
-        <v>13.24</v>
+        <v>14.46</v>
       </c>
     </row>
     <row r="158">
@@ -8856,7 +8856,7 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955362 - KIT4M05563528MKX</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020649862 - KIT4M04475159PMD</t>
         </is>
       </c>
       <c r="C158" s="3" t="n">
@@ -8867,12 +8867,12 @@
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563528MKX</t>
+          <t>KIT4M04475159PMD</t>
         </is>
       </c>
       <c r="F158" s="4" t="inlineStr">
         <is>
-          <t>814471</t>
+          <t>809868</t>
         </is>
       </c>
       <c r="G158" s="5" t="inlineStr">
@@ -8898,7 +8898,7 @@
       </c>
       <c r="L158" s="5" t="n"/>
       <c r="M158" s="7" t="n">
-        <v>12.86</v>
+        <v>14.45</v>
       </c>
     </row>
     <row r="159">
@@ -8951,7 +8951,7 @@
       </c>
       <c r="L159" s="5" t="n"/>
       <c r="M159" s="7" t="n">
-        <v>12.73</v>
+        <v>14.01</v>
       </c>
     </row>
     <row r="160">
@@ -8962,7 +8962,7 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955402 - KIT4M05563610HM2</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955482 - KIT4M055635088NK</t>
         </is>
       </c>
       <c r="C160" s="3" t="n">
@@ -8973,12 +8973,12 @@
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563610HM2</t>
+          <t>KIT4M055635088NK</t>
         </is>
       </c>
       <c r="F160" s="4" t="inlineStr">
         <is>
-          <t>814486</t>
+          <t>814434</t>
         </is>
       </c>
       <c r="G160" s="5" t="inlineStr">
@@ -9004,7 +9004,7 @@
       </c>
       <c r="L160" s="5" t="n"/>
       <c r="M160" s="7" t="n">
-        <v>11.62</v>
+        <v>13.92</v>
       </c>
     </row>
     <row r="161">
@@ -9015,7 +9015,7 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955482 - KIT4M055635088NK</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649322 - KIT4M053683324KZ</t>
         </is>
       </c>
       <c r="C161" s="3" t="n">
@@ -9026,12 +9026,12 @@
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635088NK</t>
+          <t>KIT4M053683324KZ</t>
         </is>
       </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
-          <t>814434</t>
+          <t>810832</t>
         </is>
       </c>
       <c r="G161" s="5" t="inlineStr">
@@ -9057,7 +9057,7 @@
       </c>
       <c r="L161" s="5" t="n"/>
       <c r="M161" s="7" t="n">
-        <v>11.39</v>
+        <v>13.85</v>
       </c>
     </row>
     <row r="162">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020650152 - KIT4M054138189C7</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649442 - KIT4M054137885SM</t>
         </is>
       </c>
       <c r="C162" s="3" t="n">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138189C7</t>
+          <t>KIT4M054137885SM</t>
         </is>
       </c>
       <c r="F162" s="4" t="inlineStr">
         <is>
-          <t>812831</t>
+          <t>812846</t>
         </is>
       </c>
       <c r="G162" s="5" t="inlineStr">
@@ -9110,7 +9110,7 @@
       </c>
       <c r="L162" s="5" t="n"/>
       <c r="M162" s="7" t="n">
-        <v>11.19</v>
+        <v>13.24</v>
       </c>
     </row>
     <row r="163">
@@ -9121,7 +9121,7 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 020955242 - KIT4M05563511FF4</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955402 - KIT4M05563610HM2</t>
         </is>
       </c>
       <c r="C163" s="3" t="n">
@@ -9132,12 +9132,12 @@
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563511FF4</t>
+          <t>KIT4M05563610HM2</t>
         </is>
       </c>
       <c r="F163" s="4" t="inlineStr">
         <is>
-          <t>814437</t>
+          <t>814486</t>
         </is>
       </c>
       <c r="G163" s="5" t="inlineStr">
@@ -9163,7 +9163,7 @@
       </c>
       <c r="L163" s="5" t="n"/>
       <c r="M163" s="7" t="n">
-        <v>10.96</v>
+        <v>12.25</v>
       </c>
     </row>
     <row r="164">
@@ -9174,7 +9174,7 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649582 - KIT4M05413774JZX</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955152 - KIT4M05563514P8T</t>
         </is>
       </c>
       <c r="C164" s="3" t="n">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413774JZX</t>
+          <t>KIT4M05563514P8T</t>
         </is>
       </c>
       <c r="F164" s="4" t="inlineStr">
         <is>
-          <t>812836</t>
+          <t>814436</t>
         </is>
       </c>
       <c r="G164" s="5" t="inlineStr">
@@ -9216,7 +9216,7 @@
       </c>
       <c r="L164" s="5" t="n"/>
       <c r="M164" s="7" t="n">
-        <v>10.46</v>
+        <v>12.14</v>
       </c>
     </row>
     <row r="165">
@@ -9227,7 +9227,7 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020650122-KIT4M05413776H84</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020650152 - KIT4M054138189C7</t>
         </is>
       </c>
       <c r="C165" s="3" t="n">
@@ -9238,12 +9238,12 @@
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413776H84</t>
+          <t>KIT4M054138189C7</t>
         </is>
       </c>
       <c r="F165" s="4" t="inlineStr">
         <is>
-          <t>810101</t>
+          <t>812831</t>
         </is>
       </c>
       <c r="G165" s="5" t="inlineStr">
@@ -9269,7 +9269,7 @@
       </c>
       <c r="L165" s="5" t="n"/>
       <c r="M165" s="7" t="n">
-        <v>10.11</v>
+        <v>11.19</v>
       </c>
     </row>
     <row r="166">
@@ -9280,7 +9280,7 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020955432 - KIT4M05563533M9N</t>
+          <t>SS - 05900510 -  Los Angeles CA - 020955242 - KIT4M05563511FF4</t>
         </is>
       </c>
       <c r="C166" s="3" t="n">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563533M9N</t>
+          <t>KIT4M05563511FF4</t>
         </is>
       </c>
       <c r="F166" s="4" t="inlineStr">
         <is>
-          <t>814485</t>
+          <t>814437</t>
         </is>
       </c>
       <c r="G166" s="5" t="inlineStr">
@@ -9322,7 +9322,7 @@
       </c>
       <c r="L166" s="5" t="n"/>
       <c r="M166" s="7" t="n">
-        <v>9.81</v>
+        <v>10.96</v>
       </c>
     </row>
     <row r="167">
@@ -9333,7 +9333,7 @@
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955152 - KIT4M05563514P8T</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020650262 - KIT4M054138249M8</t>
         </is>
       </c>
       <c r="C167" s="3" t="n">
@@ -9344,12 +9344,12 @@
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563514P8T</t>
+          <t>KIT4M054138249M8</t>
         </is>
       </c>
       <c r="F167" s="4" t="inlineStr">
         <is>
-          <t>814436</t>
+          <t>812794</t>
         </is>
       </c>
       <c r="G167" s="5" t="inlineStr">
@@ -9375,7 +9375,7 @@
       </c>
       <c r="L167" s="5" t="n"/>
       <c r="M167" s="7" t="n">
-        <v>9.81</v>
+        <v>10.72</v>
       </c>
     </row>
     <row r="168">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649322 - KIT4M053683324KZ</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955252 - KIT4M05563584FVC</t>
         </is>
       </c>
       <c r="C168" s="3" t="n">
@@ -9397,12 +9397,12 @@
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>KIT4M053683324KZ</t>
+          <t>KIT4M05563584FVC</t>
         </is>
       </c>
       <c r="F168" s="4" t="inlineStr">
         <is>
-          <t>810832</t>
+          <t>814439</t>
         </is>
       </c>
       <c r="G168" s="5" t="inlineStr">
@@ -9428,7 +9428,7 @@
       </c>
       <c r="L168" s="5" t="n"/>
       <c r="M168" s="7" t="n">
-        <v>9.710000000000001</v>
+        <v>10.63</v>
       </c>
     </row>
     <row r="169">
@@ -9439,7 +9439,7 @@
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649282 - KIT4M05368213974</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649582 - KIT4M05413774JZX</t>
         </is>
       </c>
       <c r="C169" s="3" t="n">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368213974</t>
+          <t>KIT4M05413774JZX</t>
         </is>
       </c>
       <c r="F169" s="4" t="inlineStr">
         <is>
-          <t>810647</t>
+          <t>812836</t>
         </is>
       </c>
       <c r="G169" s="5" t="inlineStr">
@@ -9481,7 +9481,7 @@
       </c>
       <c r="L169" s="5" t="n"/>
       <c r="M169" s="7" t="n">
-        <v>9.18</v>
+        <v>10.46</v>
       </c>
     </row>
     <row r="170">
@@ -9492,7 +9492,7 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955612 - KIT4M0556355588P</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020955432 - KIT4M05563533M9N</t>
         </is>
       </c>
       <c r="C170" s="3" t="n">
@@ -9503,12 +9503,12 @@
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0556355588P</t>
+          <t>KIT4M05563533M9N</t>
         </is>
       </c>
       <c r="F170" s="4" t="inlineStr">
         <is>
-          <t>814455</t>
+          <t>814485</t>
         </is>
       </c>
       <c r="G170" s="5" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="L170" s="5" t="n"/>
       <c r="M170" s="7" t="n">
-        <v>9.140000000000001</v>
+        <v>10.32</v>
       </c>
     </row>
     <row r="171">
@@ -9545,7 +9545,7 @@
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955502 - KIT4M05563502GJS</t>
+          <t>SMRT-05900510-Los Angeles CA-020650122-KIT4M05413776H84</t>
         </is>
       </c>
       <c r="C171" s="3" t="n">
@@ -9556,12 +9556,12 @@
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563502GJS</t>
+          <t>KIT4M05413776H84</t>
         </is>
       </c>
       <c r="F171" s="4" t="inlineStr">
         <is>
-          <t>814470</t>
+          <t>810101</t>
         </is>
       </c>
       <c r="G171" s="5" t="inlineStr">
@@ -9587,7 +9587,7 @@
       </c>
       <c r="L171" s="5" t="n"/>
       <c r="M171" s="7" t="n">
-        <v>8.869999999999999</v>
+        <v>10.27</v>
       </c>
     </row>
     <row r="172">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955252 - KIT4M05563584FVC</t>
+          <t>SS - 05900510 -  Los Angeles CA - 021438232 - KIT4M05872520QJM</t>
         </is>
       </c>
       <c r="C172" s="3" t="n">
@@ -9609,12 +9609,12 @@
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563584FVC</t>
+          <t>KIT4M05872520QJM</t>
         </is>
       </c>
       <c r="F172" s="4" t="inlineStr">
         <is>
-          <t>814439</t>
+          <t>816078</t>
         </is>
       </c>
       <c r="G172" s="5" t="inlineStr">
@@ -9640,7 +9640,7 @@
       </c>
       <c r="L172" s="5" t="n"/>
       <c r="M172" s="7" t="n">
-        <v>8.75</v>
+        <v>9.82</v>
       </c>
     </row>
     <row r="173">
@@ -9651,7 +9651,7 @@
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020650262 - KIT4M054138249M8</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649282 - KIT4M05368213974</t>
         </is>
       </c>
       <c r="C173" s="3" t="n">
@@ -9662,12 +9662,12 @@
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138249M8</t>
+          <t>KIT4M05368213974</t>
         </is>
       </c>
       <c r="F173" s="4" t="inlineStr">
         <is>
-          <t>812794</t>
+          <t>810647</t>
         </is>
       </c>
       <c r="G173" s="5" t="inlineStr">
@@ -9693,7 +9693,7 @@
       </c>
       <c r="L173" s="5" t="n"/>
       <c r="M173" s="7" t="n">
-        <v>8.52</v>
+        <v>9.18</v>
       </c>
     </row>
     <row r="174">
@@ -9704,7 +9704,7 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020649252 - KIT4P00066848VQM</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955612 - KIT4M0556355588P</t>
         </is>
       </c>
       <c r="C174" s="3" t="n">
@@ -9715,17 +9715,17 @@
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00066848VQM</t>
+          <t>KIT4M0556355588P</t>
         </is>
       </c>
       <c r="F174" s="4" t="inlineStr">
         <is>
-          <t>812923</t>
+          <t>814455</t>
         </is>
       </c>
       <c r="G174" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H174" s="5" t="inlineStr">
@@ -9746,7 +9746,7 @@
       </c>
       <c r="L174" s="5" t="n"/>
       <c r="M174" s="7" t="n">
-        <v>7.27</v>
+        <v>9.140000000000001</v>
       </c>
     </row>
     <row r="175">
@@ -9757,7 +9757,7 @@
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649822 - KIT4M04604740BM6</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955502 - KIT4M05563502GJS</t>
         </is>
       </c>
       <c r="C175" s="3" t="n">
@@ -9768,12 +9768,12 @@
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604740BM6</t>
+          <t>KIT4M05563502GJS</t>
         </is>
       </c>
       <c r="F175" s="4" t="inlineStr">
         <is>
-          <t>809872</t>
+          <t>814470</t>
         </is>
       </c>
       <c r="G175" s="5" t="inlineStr">
@@ -9799,7 +9799,7 @@
       </c>
       <c r="L175" s="5" t="n"/>
       <c r="M175" s="7" t="n">
-        <v>7.25</v>
+        <v>8.869999999999999</v>
       </c>
     </row>
     <row r="176">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="L176" s="5" t="n"/>
       <c r="M176" s="7" t="n">
-        <v>7.23</v>
+        <v>8.130000000000001</v>
       </c>
     </row>
     <row r="177">
@@ -9863,7 +9863,7 @@
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649792 - KIT4M04475151HTP</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020649252 - KIT4P00066848VQM</t>
         </is>
       </c>
       <c r="C177" s="3" t="n">
@@ -9874,17 +9874,17 @@
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475151HTP</t>
+          <t>KIT4P00066848VQM</t>
         </is>
       </c>
       <c r="F177" s="4" t="inlineStr">
         <is>
-          <t>809867</t>
+          <t>812923</t>
         </is>
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H177" s="5" t="inlineStr">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="L177" s="5" t="n"/>
       <c r="M177" s="7" t="n">
-        <v>7.08</v>
+        <v>7.27</v>
       </c>
     </row>
     <row r="178">
@@ -9916,7 +9916,7 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles, CA - 0204827011114 - KIT4M03986267RWH</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649792 - KIT4M04475151HTP</t>
         </is>
       </c>
       <c r="C178" s="3" t="n">
@@ -9927,12 +9927,12 @@
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03986267RWH</t>
+          <t>KIT4M04475151HTP</t>
         </is>
       </c>
       <c r="F178" s="4" t="inlineStr">
         <is>
-          <t>809616</t>
+          <t>809867</t>
         </is>
       </c>
       <c r="G178" s="5" t="inlineStr">
@@ -9958,7 +9958,7 @@
       </c>
       <c r="L178" s="5" t="n"/>
       <c r="M178" s="7" t="n">
-        <v>6.09</v>
+        <v>7.08</v>
       </c>
     </row>
     <row r="179">
@@ -9969,7 +9969,7 @@
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649642 - KIT4M05413826Z6Z</t>
+          <t>STS - 05900510 - Los Angeles, CA - 0204827011114 - KIT4M03986267RWH</t>
         </is>
       </c>
       <c r="C179" s="3" t="n">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413826Z6Z</t>
+          <t>KIT4M03986267RWH</t>
         </is>
       </c>
       <c r="F179" s="4" t="inlineStr">
         <is>
-          <t>812804</t>
+          <t>809616</t>
         </is>
       </c>
       <c r="G179" s="5" t="inlineStr">
@@ -10011,7 +10011,7 @@
       </c>
       <c r="L179" s="5" t="n"/>
       <c r="M179" s="7" t="n">
-        <v>5.9</v>
+        <v>6.36</v>
       </c>
     </row>
     <row r="180">
@@ -10022,7 +10022,7 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827011110 - KIT4M03866627GHD</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649642 - KIT4M05413826Z6Z</t>
         </is>
       </c>
       <c r="C180" s="3" t="n">
@@ -10033,12 +10033,12 @@
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03866627GHD</t>
+          <t>KIT4M05413826Z6Z</t>
         </is>
       </c>
       <c r="F180" s="4" t="inlineStr">
         <is>
-          <t>809619</t>
+          <t>812804</t>
         </is>
       </c>
       <c r="G180" s="5" t="inlineStr">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="L180" s="5" t="n"/>
       <c r="M180" s="7" t="n">
-        <v>5.78</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="181">
@@ -10075,7 +10075,7 @@
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020650182 - KIT4M05413821GGW</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827011110 - KIT4M03866627GHD</t>
         </is>
       </c>
       <c r="C181" s="3" t="n">
@@ -10086,12 +10086,12 @@
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413821GGW</t>
+          <t>KIT4M03866627GHD</t>
         </is>
       </c>
       <c r="F181" s="4" t="inlineStr">
         <is>
-          <t>812830</t>
+          <t>809619</t>
         </is>
       </c>
       <c r="G181" s="5" t="inlineStr">
@@ -10117,7 +10117,7 @@
       </c>
       <c r="L181" s="5" t="n"/>
       <c r="M181" s="7" t="n">
-        <v>5.51</v>
+        <v>5.78</v>
       </c>
     </row>
     <row r="182">
@@ -10128,7 +10128,7 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649962 - KIT4M05413783PFQ</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270110 - KIT4M038677586ZX</t>
         </is>
       </c>
       <c r="C182" s="3" t="n">
@@ -10139,12 +10139,12 @@
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413783PFQ</t>
+          <t>KIT4M038677586ZX</t>
         </is>
       </c>
       <c r="F182" s="4" t="inlineStr">
         <is>
-          <t>812845</t>
+          <t>809623</t>
         </is>
       </c>
       <c r="G182" s="5" t="inlineStr">
@@ -10170,7 +10170,7 @@
       </c>
       <c r="L182" s="5" t="n"/>
       <c r="M182" s="7" t="n">
-        <v>4.65</v>
+        <v>5.55</v>
       </c>
     </row>
     <row r="183">
@@ -10181,7 +10181,7 @@
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649492 - KIT4M054138074NS</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020650182 - KIT4M05413821GGW</t>
         </is>
       </c>
       <c r="C183" s="3" t="n">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138074NS</t>
+          <t>KIT4M05413821GGW</t>
         </is>
       </c>
       <c r="F183" s="4" t="inlineStr">
         <is>
-          <t>812816</t>
+          <t>812830</t>
         </is>
       </c>
       <c r="G183" s="5" t="inlineStr">
@@ -10223,7 +10223,7 @@
       </c>
       <c r="L183" s="5" t="n"/>
       <c r="M183" s="7" t="n">
-        <v>3.8</v>
+        <v>5.51</v>
       </c>
     </row>
     <row r="184">
@@ -10234,7 +10234,7 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649732 - KIT4M046047467T4</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649962 - KIT4M05413783PFQ</t>
         </is>
       </c>
       <c r="C184" s="3" t="n">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047467T4</t>
+          <t>KIT4M05413783PFQ</t>
         </is>
       </c>
       <c r="F184" s="4" t="inlineStr">
         <is>
-          <t>809865</t>
+          <t>812845</t>
         </is>
       </c>
       <c r="G184" s="5" t="inlineStr">
@@ -10276,7 +10276,7 @@
       </c>
       <c r="L184" s="5" t="n"/>
       <c r="M184" s="7" t="n">
-        <v>3.43</v>
+        <v>4.65</v>
       </c>
     </row>
     <row r="185">
@@ -10287,7 +10287,7 @@
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649752 - KIT4M03867749CW5</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270114 - KIT4M04476539RJ5</t>
         </is>
       </c>
       <c r="C185" s="3" t="n">
@@ -10298,12 +10298,12 @@
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03867749CW5</t>
+          <t>KIT4M04476539RJ5</t>
         </is>
       </c>
       <c r="F185" s="4" t="inlineStr">
         <is>
-          <t>809877</t>
+          <t>809612</t>
         </is>
       </c>
       <c r="G185" s="5" t="inlineStr">
@@ -10329,7 +10329,7 @@
       </c>
       <c r="L185" s="5" t="n"/>
       <c r="M185" s="7" t="n">
-        <v>2.96</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="186">
@@ -10340,7 +10340,7 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270114 - KIT4M04476539RJ5</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437582 - KIT4M05872573K7P</t>
         </is>
       </c>
       <c r="C186" s="3" t="n">
@@ -10351,12 +10351,12 @@
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04476539RJ5</t>
+          <t>KIT4M05872573K7P</t>
         </is>
       </c>
       <c r="F186" s="4" t="inlineStr">
         <is>
-          <t>809612</t>
+          <t>816067</t>
         </is>
       </c>
       <c r="G186" s="5" t="inlineStr">
@@ -10382,7 +10382,7 @@
       </c>
       <c r="L186" s="5" t="n"/>
       <c r="M186" s="7" t="n">
-        <v>2.66</v>
+        <v>4.28</v>
       </c>
     </row>
     <row r="187">
@@ -10393,7 +10393,7 @@
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827012 - KIT4M04606110GTV</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649492 - KIT4M054138074NS</t>
         </is>
       </c>
       <c r="C187" s="3" t="n">
@@ -10404,12 +10404,12 @@
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04606110GTV</t>
+          <t>KIT4M054138074NS</t>
         </is>
       </c>
       <c r="F187" s="4" t="inlineStr">
         <is>
-          <t>809660</t>
+          <t>812816</t>
         </is>
       </c>
       <c r="G187" s="5" t="inlineStr">
@@ -10435,7 +10435,7 @@
       </c>
       <c r="L187" s="5" t="n"/>
       <c r="M187" s="7" t="n">
-        <v>2.61</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="188">
@@ -10446,7 +10446,7 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437932 - KIT4M05799732NQK</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649732 - KIT4M046047467T4</t>
         </is>
       </c>
       <c r="C188" s="3" t="n">
@@ -10457,12 +10457,12 @@
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799732NQK</t>
+          <t>KIT4M046047467T4</t>
         </is>
       </c>
       <c r="F188" s="4" t="inlineStr">
         <is>
-          <t>816275</t>
+          <t>809865</t>
         </is>
       </c>
       <c r="G188" s="5" t="inlineStr">
@@ -10488,7 +10488,7 @@
       </c>
       <c r="L188" s="5" t="n"/>
       <c r="M188" s="7" t="n">
-        <v>2.48</v>
+        <v>3.43</v>
       </c>
     </row>
     <row r="189">
@@ -10499,7 +10499,7 @@
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270110 - KIT4M038677586ZX</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437902 - KIT4M05799717WZV</t>
         </is>
       </c>
       <c r="C189" s="3" t="n">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>KIT4M038677586ZX</t>
+          <t>KIT4M05799717WZV</t>
         </is>
       </c>
       <c r="F189" s="4" t="inlineStr">
         <is>
-          <t>809623</t>
+          <t>816280</t>
         </is>
       </c>
       <c r="G189" s="5" t="inlineStr">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="L189" s="5" t="n"/>
       <c r="M189" s="7" t="n">
-        <v>2.1</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="190">
@@ -10552,7 +10552,7 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437612 - KIT4M058725265DP</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649752 - KIT4M03867749CW5</t>
         </is>
       </c>
       <c r="C190" s="3" t="n">
@@ -10563,12 +10563,12 @@
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725265DP</t>
+          <t>KIT4M03867749CW5</t>
         </is>
       </c>
       <c r="F190" s="4" t="inlineStr">
         <is>
-          <t>816192</t>
+          <t>809877</t>
         </is>
       </c>
       <c r="G190" s="5" t="inlineStr">
@@ -10594,7 +10594,7 @@
       </c>
       <c r="L190" s="5" t="n"/>
       <c r="M190" s="7" t="n">
-        <v>1.58</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="191">
@@ -10605,7 +10605,7 @@
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020650022 - KIT4M05413813HSJ</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827012 - KIT4M04606110GTV</t>
         </is>
       </c>
       <c r="C191" s="3" t="n">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413813HSJ</t>
+          <t>KIT4M04606110GTV</t>
         </is>
       </c>
       <c r="F191" s="4" t="inlineStr">
         <is>
-          <t>812797</t>
+          <t>809660</t>
         </is>
       </c>
       <c r="G191" s="5" t="inlineStr">
@@ -10647,7 +10647,7 @@
       </c>
       <c r="L191" s="5" t="n"/>
       <c r="M191" s="7" t="n">
-        <v>1.2</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="192">
@@ -10658,7 +10658,7 @@
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649852 - KIT4M05413789Z8C</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437932 - KIT4M05799732NQK</t>
         </is>
       </c>
       <c r="C192" s="3" t="n">
@@ -10669,12 +10669,12 @@
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413789Z8C</t>
+          <t>KIT4M05799732NQK</t>
         </is>
       </c>
       <c r="F192" s="4" t="inlineStr">
         <is>
-          <t>812840</t>
+          <t>816275</t>
         </is>
       </c>
       <c r="G192" s="5" t="inlineStr">
@@ -10700,7 +10700,7 @@
       </c>
       <c r="L192" s="5" t="n"/>
       <c r="M192" s="7" t="n">
-        <v>1.13</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="193">
@@ -10711,7 +10711,7 @@
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020649652 - KIT4M0541381584X</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437612 - KIT4M058725265DP</t>
         </is>
       </c>
       <c r="C193" s="3" t="n">
@@ -10722,12 +10722,12 @@
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0541381584X</t>
+          <t>KIT4M058725265DP</t>
         </is>
       </c>
       <c r="F193" s="4" t="inlineStr">
         <is>
-          <t>812810</t>
+          <t>816192</t>
         </is>
       </c>
       <c r="G193" s="5" t="inlineStr">
@@ -10753,7 +10753,7 @@
       </c>
       <c r="L193" s="5" t="n"/>
       <c r="M193" s="7" t="n">
-        <v>1</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="194">
@@ -10764,7 +10764,7 @@
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437582 - KIT4M05872573K7P</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020650022 - KIT4M05413813HSJ</t>
         </is>
       </c>
       <c r="C194" s="3" t="n">
@@ -10775,12 +10775,12 @@
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872573K7P</t>
+          <t>KIT4M05413813HSJ</t>
         </is>
       </c>
       <c r="F194" s="4" t="inlineStr">
         <is>
-          <t>816067</t>
+          <t>812797</t>
         </is>
       </c>
       <c r="G194" s="5" t="inlineStr">
@@ -10806,7 +10806,7 @@
       </c>
       <c r="L194" s="5" t="n"/>
       <c r="M194" s="7" t="n">
-        <v>0.67</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="195">
@@ -10817,7 +10817,7 @@
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438282 - KIT4M05872508VTN</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649852 - KIT4M05413789Z8C</t>
         </is>
       </c>
       <c r="C195" s="3" t="n">
@@ -10828,12 +10828,12 @@
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872508VTN</t>
+          <t>KIT4M05413789Z8C</t>
         </is>
       </c>
       <c r="F195" s="4" t="inlineStr">
         <is>
-          <t>816076</t>
+          <t>812840</t>
         </is>
       </c>
       <c r="G195" s="5" t="inlineStr">
@@ -10859,7 +10859,7 @@
       </c>
       <c r="L195" s="5" t="n"/>
       <c r="M195" s="7" t="n">
-        <v>0.65</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="196">
@@ -10870,7 +10870,7 @@
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491804TBC</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020649652 - KIT4M0541381584X</t>
         </is>
       </c>
       <c r="C196" s="3" t="n">
@@ -10881,12 +10881,12 @@
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491804TBC</t>
+          <t>KIT4M0541381584X</t>
         </is>
       </c>
       <c r="F196" s="4" t="inlineStr">
         <is>
-          <t>816373</t>
+          <t>812810</t>
         </is>
       </c>
       <c r="G196" s="5" t="inlineStr">
@@ -10912,7 +10912,7 @@
       </c>
       <c r="L196" s="5" t="n"/>
       <c r="M196" s="7" t="n">
-        <v>0.6</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="197">
@@ -10923,7 +10923,7 @@
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>SSC - 05900510 - Los Angeles CA - 021437792 - KIT4M05872507528</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438282 - KIT4M05872508VTN</t>
         </is>
       </c>
       <c r="C197" s="3" t="n">
@@ -10934,12 +10934,12 @@
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872507528</t>
+          <t>KIT4M05872508VTN</t>
         </is>
       </c>
       <c r="F197" s="4" t="inlineStr">
         <is>
-          <t>816083</t>
+          <t>816076</t>
         </is>
       </c>
       <c r="G197" s="5" t="inlineStr">
@@ -10965,7 +10965,7 @@
       </c>
       <c r="L197" s="5" t="n"/>
       <c r="M197" s="7" t="n">
-        <v>0.38</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="198">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491800F52</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491804TBC</t>
         </is>
       </c>
       <c r="C198" s="3" t="n">
@@ -10987,12 +10987,12 @@
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491800F52</t>
+          <t>KIT4M06491804TBC</t>
         </is>
       </c>
       <c r="F198" s="4" t="inlineStr">
         <is>
-          <t>816406</t>
+          <t>816373</t>
         </is>
       </c>
       <c r="G198" s="5" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="L198" s="5" t="n"/>
       <c r="M198" s="7" t="n">
-        <v>0.35</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="199">
@@ -11029,7 +11029,7 @@
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437812-KIT4M058724947VX</t>
+          <t>SSC - 05900510 - Los Angeles CA - 021437792 - KIT4M05872507528</t>
         </is>
       </c>
       <c r="C199" s="3" t="n">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058724947VX</t>
+          <t>KIT4M05872507528</t>
         </is>
       </c>
       <c r="F199" s="4" t="inlineStr">
         <is>
-          <t>816086</t>
+          <t>816083</t>
         </is>
       </c>
       <c r="G199" s="5" t="inlineStr">
@@ -11071,7 +11071,7 @@
       </c>
       <c r="L199" s="5" t="n"/>
       <c r="M199" s="7" t="n">
-        <v>0.26</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="200">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020650062 - KIT4M05413797HK5</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491800F52</t>
         </is>
       </c>
       <c r="C200" s="3" t="n">
@@ -11093,12 +11093,12 @@
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413797HK5</t>
+          <t>KIT4M06491800F52</t>
         </is>
       </c>
       <c r="F200" s="4" t="inlineStr">
         <is>
-          <t>812808</t>
+          <t>816406</t>
         </is>
       </c>
       <c r="G200" s="5" t="inlineStr">
@@ -11124,7 +11124,7 @@
       </c>
       <c r="L200" s="5" t="n"/>
       <c r="M200" s="7" t="n">
-        <v>0.24</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="201">
@@ -11135,7 +11135,7 @@
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437592 - KIT4M05872582TC7</t>
+          <t>SMRT-05900510-Los Angeles CA-021437812-KIT4M058724947VX</t>
         </is>
       </c>
       <c r="C201" s="3" t="n">
@@ -11146,12 +11146,12 @@
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872582TC7</t>
+          <t>KIT4M058724947VX</t>
         </is>
       </c>
       <c r="F201" s="4" t="inlineStr">
         <is>
-          <t>816107</t>
+          <t>816086</t>
         </is>
       </c>
       <c r="G201" s="5" t="inlineStr">
@@ -11177,7 +11177,7 @@
       </c>
       <c r="L201" s="5" t="n"/>
       <c r="M201" s="7" t="n">
-        <v>0.23</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="202">
@@ -11188,7 +11188,7 @@
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020649522-KIT4M05413834FTH</t>
+          <t>SS - 05900510 - Los Angeles CA - 020650062 - KIT4M05413797HK5</t>
         </is>
       </c>
       <c r="C202" s="3" t="n">
@@ -11199,12 +11199,12 @@
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413834FTH</t>
+          <t>KIT4M05413797HK5</t>
         </is>
       </c>
       <c r="F202" s="4" t="inlineStr">
         <is>
-          <t>812817</t>
+          <t>812808</t>
         </is>
       </c>
       <c r="G202" s="5" t="inlineStr">
@@ -11230,7 +11230,7 @@
       </c>
       <c r="L202" s="5" t="n"/>
       <c r="M202" s="7" t="n">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="203">
@@ -11241,7 +11241,7 @@
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 6862083  - KIT4M05799682BXX</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437592 - KIT4M05872582TC7</t>
         </is>
       </c>
       <c r="C203" s="3" t="n">
@@ -11252,12 +11252,12 @@
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799682BXX</t>
+          <t>KIT4M05872582TC7</t>
         </is>
       </c>
       <c r="F203" s="4" t="inlineStr">
         <is>
-          <t>816278</t>
+          <t>816107</t>
         </is>
       </c>
       <c r="G203" s="5" t="inlineStr">
@@ -11283,7 +11283,7 @@
       </c>
       <c r="L203" s="5" t="n"/>
       <c r="M203" s="7" t="n">
-        <v>0.19</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="204">
@@ -11294,7 +11294,7 @@
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437832 - KIT4M05872486FXZ</t>
+          <t>SMRT-05900510-Los Angeles CA-020649522-KIT4M05413834FTH</t>
         </is>
       </c>
       <c r="C204" s="3" t="n">
@@ -11305,12 +11305,12 @@
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872486FXZ</t>
+          <t>KIT4M05413834FTH</t>
         </is>
       </c>
       <c r="F204" s="4" t="inlineStr">
         <is>
-          <t>816088</t>
+          <t>812817</t>
         </is>
       </c>
       <c r="G204" s="5" t="inlineStr">
@@ -11336,7 +11336,7 @@
       </c>
       <c r="L204" s="5" t="n"/>
       <c r="M204" s="7" t="n">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="205">
@@ -11347,7 +11347,7 @@
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955422 - KIT4M05563517BVR</t>
+          <t>SS - 05900510 - Los Angeles CA - 6862083  - KIT4M05799682BXX</t>
         </is>
       </c>
       <c r="C205" s="3" t="n">
@@ -11358,12 +11358,12 @@
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563517BVR</t>
+          <t>KIT4M05799682BXX</t>
         </is>
       </c>
       <c r="F205" s="4" t="inlineStr">
         <is>
-          <t>814438</t>
+          <t>816278</t>
         </is>
       </c>
       <c r="G205" s="5" t="inlineStr">
@@ -11389,7 +11389,7 @@
       </c>
       <c r="L205" s="5" t="n"/>
       <c r="M205" s="7" t="n">
-        <v>0.16</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="206">
@@ -11400,7 +11400,7 @@
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491790945</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437832 - KIT4M05872486FXZ</t>
         </is>
       </c>
       <c r="C206" s="3" t="n">
@@ -11411,12 +11411,12 @@
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491790945</t>
+          <t>KIT4M05872486FXZ</t>
         </is>
       </c>
       <c r="F206" s="4" t="inlineStr">
         <is>
-          <t>816410</t>
+          <t>816088</t>
         </is>
       </c>
       <c r="G206" s="5" t="inlineStr">
@@ -11442,7 +11442,7 @@
       </c>
       <c r="L206" s="5" t="n"/>
       <c r="M206" s="7" t="n">
-        <v>0.14</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="207">
@@ -11453,7 +11453,7 @@
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491836Z2D</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955422 - KIT4M05563517BVR</t>
         </is>
       </c>
       <c r="C207" s="3" t="n">
@@ -11464,12 +11464,12 @@
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491836Z2D</t>
+          <t>KIT4M05563517BVR</t>
         </is>
       </c>
       <c r="F207" s="4" t="inlineStr">
         <is>
-          <t>816366</t>
+          <t>814438</t>
         </is>
       </c>
       <c r="G207" s="5" t="inlineStr">
@@ -11495,7 +11495,7 @@
       </c>
       <c r="L207" s="5" t="n"/>
       <c r="M207" s="7" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="208">
@@ -11506,7 +11506,7 @@
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438172 - KIT4M05872500684</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491790945</t>
         </is>
       </c>
       <c r="C208" s="3" t="n">
@@ -11517,12 +11517,12 @@
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872500684</t>
+          <t>KIT4M06491790945</t>
         </is>
       </c>
       <c r="F208" s="4" t="inlineStr">
         <is>
-          <t>816081</t>
+          <t>816410</t>
         </is>
       </c>
       <c r="G208" s="5" t="inlineStr">
@@ -11612,7 +11612,7 @@
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437412 - KIT4M05872548P2H</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438172 - KIT4M05872500684</t>
         </is>
       </c>
       <c r="C210" s="3" t="n">
@@ -11623,12 +11623,12 @@
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872548P2H</t>
+          <t>KIT4M05872500684</t>
         </is>
       </c>
       <c r="F210" s="4" t="inlineStr">
         <is>
-          <t>816066</t>
+          <t>816081</t>
         </is>
       </c>
       <c r="G210" s="5" t="inlineStr">
@@ -11654,7 +11654,7 @@
       </c>
       <c r="L210" s="5" t="n"/>
       <c r="M210" s="7" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="211">
@@ -11665,7 +11665,7 @@
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 021438232 - KIT4M05872520QJM</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491836Z2D</t>
         </is>
       </c>
       <c r="C211" s="3" t="n">
@@ -11676,12 +11676,12 @@
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872520QJM</t>
+          <t>KIT4M06491836Z2D</t>
         </is>
       </c>
       <c r="F211" s="4" t="inlineStr">
         <is>
-          <t>816078</t>
+          <t>816366</t>
         </is>
       </c>
       <c r="G211" s="5" t="inlineStr">
@@ -11707,7 +11707,7 @@
       </c>
       <c r="L211" s="5" t="n"/>
       <c r="M211" s="7" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="212">
@@ -11718,7 +11718,7 @@
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438022 - KIT4M05799705T6B</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437412 - KIT4M05872548P2H</t>
         </is>
       </c>
       <c r="C212" s="3" t="n">
@@ -11729,12 +11729,12 @@
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799705T6B</t>
+          <t>KIT4M05872548P2H</t>
         </is>
       </c>
       <c r="F212" s="4" t="inlineStr">
         <is>
-          <t>816285</t>
+          <t>816066</t>
         </is>
       </c>
       <c r="G212" s="5" t="inlineStr">
@@ -11760,7 +11760,7 @@
       </c>
       <c r="L212" s="5" t="n"/>
       <c r="M212" s="7" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="213">
@@ -11877,7 +11877,7 @@
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918277QF</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438022 - KIT4M05799705T6B</t>
         </is>
       </c>
       <c r="C215" s="3" t="n">
@@ -11888,12 +11888,12 @@
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918277QF</t>
+          <t>KIT4M05799705T6B</t>
         </is>
       </c>
       <c r="F215" s="4" t="inlineStr">
         <is>
-          <t>816403</t>
+          <t>816285</t>
         </is>
       </c>
       <c r="G215" s="5" t="inlineStr">
@@ -11919,7 +11919,7 @@
       </c>
       <c r="L215" s="5" t="n"/>
       <c r="M215" s="7" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="216">
@@ -11930,7 +11930,7 @@
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437722 - KIT4M05872498PP4</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918277QF</t>
         </is>
       </c>
       <c r="C216" s="3" t="n">
@@ -11941,12 +11941,12 @@
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872498PP4</t>
+          <t>KIT4M064918277QF</t>
         </is>
       </c>
       <c r="F216" s="4" t="inlineStr">
         <is>
-          <t>816104</t>
+          <t>816403</t>
         </is>
       </c>
       <c r="G216" s="5" t="inlineStr">
@@ -11972,7 +11972,7 @@
       </c>
       <c r="L216" s="5" t="n"/>
       <c r="M216" s="7" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="217">
@@ -11983,7 +11983,7 @@
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 021438182 - KIT4M05872528P9D</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437732 - KIT4M05872588W8G</t>
         </is>
       </c>
       <c r="C217" s="3" t="n">
@@ -11994,12 +11994,12 @@
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872528P9D</t>
+          <t>KIT4M05872588W8G</t>
         </is>
       </c>
       <c r="F217" s="4" t="inlineStr">
         <is>
-          <t>816089</t>
+          <t>816100</t>
         </is>
       </c>
       <c r="G217" s="5" t="inlineStr">
@@ -12089,7 +12089,7 @@
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437732 - KIT4M05872588W8G</t>
+          <t>SS - 05900510 -  Los Angeles CA - 021438182 - KIT4M05872528P9D</t>
         </is>
       </c>
       <c r="C219" s="3" t="n">
@@ -12100,12 +12100,12 @@
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872588W8G</t>
+          <t>KIT4M05872528P9D</t>
         </is>
       </c>
       <c r="F219" s="4" t="inlineStr">
         <is>
-          <t>816100</t>
+          <t>816089</t>
         </is>
       </c>
       <c r="G219" s="5" t="inlineStr">
@@ -12142,7 +12142,7 @@
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438252 - KIT4M05872519KTN</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491821G25</t>
         </is>
       </c>
       <c r="C220" s="3" t="n">
@@ -12153,12 +12153,12 @@
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872519KTN</t>
+          <t>KIT4M06491821G25</t>
         </is>
       </c>
       <c r="F220" s="4" t="inlineStr">
         <is>
-          <t>816084</t>
+          <t>816379</t>
         </is>
       </c>
       <c r="G220" s="5" t="inlineStr">
@@ -12195,7 +12195,7 @@
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491821G25</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437722 - KIT4M05872498PP4</t>
         </is>
       </c>
       <c r="C221" s="3" t="n">
@@ -12206,12 +12206,12 @@
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491821G25</t>
+          <t>KIT4M05872498PP4</t>
         </is>
       </c>
       <c r="F221" s="4" t="inlineStr">
         <is>
-          <t>816379</t>
+          <t>816104</t>
         </is>
       </c>
       <c r="G221" s="5" t="inlineStr">
@@ -12248,7 +12248,7 @@
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918154FM</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438252 - KIT4M05872519KTN</t>
         </is>
       </c>
       <c r="C222" s="3" t="n">
@@ -12259,12 +12259,12 @@
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918154FM</t>
+          <t>KIT4M05872519KTN</t>
         </is>
       </c>
       <c r="F222" s="4" t="inlineStr">
         <is>
-          <t>816368</t>
+          <t>816084</t>
         </is>
       </c>
       <c r="G222" s="5" t="inlineStr">
@@ -12290,7 +12290,7 @@
       </c>
       <c r="L222" s="5" t="n"/>
       <c r="M222" s="7" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="223">
@@ -12301,7 +12301,7 @@
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>SSC - 05900510 -  Los Angeles CA - 021437862 - KIT4M05872516CJM</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437502 - KIT4M058725695CN</t>
         </is>
       </c>
       <c r="C223" s="3" t="n">
@@ -12312,12 +12312,12 @@
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872516CJM</t>
+          <t>KIT4M058725695CN</t>
         </is>
       </c>
       <c r="F223" s="4" t="inlineStr">
         <is>
-          <t>816087</t>
+          <t>816101</t>
         </is>
       </c>
       <c r="G223" s="5" t="inlineStr">
@@ -12354,7 +12354,7 @@
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438112 - KIT4M0579970825J</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437332 - KIT4M05872554RHM</t>
         </is>
       </c>
       <c r="C224" s="3" t="n">
@@ -12365,12 +12365,12 @@
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0579970825J</t>
+          <t>KIT4M05872554RHM</t>
         </is>
       </c>
       <c r="F224" s="4" t="inlineStr">
         <is>
-          <t>816290</t>
+          <t>816071</t>
         </is>
       </c>
       <c r="G224" s="5" t="inlineStr">
@@ -12460,7 +12460,7 @@
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437352-KIT4M05872545Q8H</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437342 - KIT4M05872557NFB</t>
         </is>
       </c>
       <c r="C226" s="3" t="n">
@@ -12471,12 +12471,12 @@
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872545Q8H</t>
+          <t>KIT4M05872557NFB</t>
         </is>
       </c>
       <c r="F226" s="4" t="inlineStr">
         <is>
-          <t>816112</t>
+          <t>816095</t>
         </is>
       </c>
       <c r="G226" s="5" t="inlineStr">
@@ -12513,7 +12513,7 @@
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437342 - KIT4M05872557NFB</t>
+          <t>SSC - 05900510 -  Los Angeles CA - 021437862 - KIT4M05872516CJM</t>
         </is>
       </c>
       <c r="C227" s="3" t="n">
@@ -12524,12 +12524,12 @@
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872557NFB</t>
+          <t>KIT4M05872516CJM</t>
         </is>
       </c>
       <c r="F227" s="4" t="inlineStr">
         <is>
-          <t>816095</t>
+          <t>816087</t>
         </is>
       </c>
       <c r="G227" s="5" t="inlineStr">
@@ -12566,7 +12566,7 @@
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437712-KIT4M05872570FCC</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437692 - KIT4M05872518P78</t>
         </is>
       </c>
       <c r="C228" s="3" t="n">
@@ -12577,12 +12577,12 @@
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872570FCC</t>
+          <t>KIT4M05872518P78</t>
         </is>
       </c>
       <c r="F228" s="4" t="inlineStr">
         <is>
-          <t>816105</t>
+          <t>816184</t>
         </is>
       </c>
       <c r="G228" s="5" t="inlineStr">
@@ -12672,7 +12672,7 @@
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437332 - KIT4M05872554RHM</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438112 - KIT4M0579970825J</t>
         </is>
       </c>
       <c r="C230" s="3" t="n">
@@ -12683,12 +12683,12 @@
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872554RHM</t>
+          <t>KIT4M0579970825J</t>
         </is>
       </c>
       <c r="F230" s="4" t="inlineStr">
         <is>
-          <t>816071</t>
+          <t>816290</t>
         </is>
       </c>
       <c r="G230" s="5" t="inlineStr">
@@ -12725,7 +12725,7 @@
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491798S8Q</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491829CD2</t>
         </is>
       </c>
       <c r="C231" s="3" t="n">
@@ -12736,12 +12736,12 @@
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491798S8Q</t>
+          <t>KIT4M06491829CD2</t>
         </is>
       </c>
       <c r="F231" s="4" t="inlineStr">
         <is>
-          <t>816395</t>
+          <t>816393</t>
         </is>
       </c>
       <c r="G231" s="5" t="inlineStr">
@@ -12778,7 +12778,7 @@
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437462 - KIT4M05872575BC8</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M0649183125S</t>
         </is>
       </c>
       <c r="C232" s="3" t="n">
@@ -12789,12 +12789,12 @@
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872575BC8</t>
+          <t>KIT4M0649183125S</t>
         </is>
       </c>
       <c r="F232" s="4" t="inlineStr">
         <is>
-          <t>816103</t>
+          <t>816371</t>
         </is>
       </c>
       <c r="G232" s="5" t="inlineStr">
@@ -12831,7 +12831,7 @@
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437802 - KIT4M05872589TM9</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491825PF9</t>
         </is>
       </c>
       <c r="C233" s="3" t="n">
@@ -12842,12 +12842,12 @@
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872589TM9</t>
+          <t>KIT4M06491825PF9</t>
         </is>
       </c>
       <c r="F233" s="4" t="inlineStr">
         <is>
-          <t>816195</t>
+          <t>816367</t>
         </is>
       </c>
       <c r="G233" s="5" t="inlineStr">
@@ -12884,7 +12884,7 @@
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064917914G5</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491799CRP</t>
         </is>
       </c>
       <c r="C234" s="3" t="n">
@@ -12895,12 +12895,12 @@
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064917914G5</t>
+          <t>KIT4M06491799CRP</t>
         </is>
       </c>
       <c r="F234" s="4" t="inlineStr">
         <is>
-          <t>816392</t>
+          <t>816394</t>
         </is>
       </c>
       <c r="G234" s="5" t="inlineStr">
@@ -12937,7 +12937,7 @@
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491789PJ6</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918165MW</t>
         </is>
       </c>
       <c r="C235" s="3" t="n">
@@ -12948,12 +12948,12 @@
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491789PJ6</t>
+          <t>KIT4M064918165MW</t>
         </is>
       </c>
       <c r="F235" s="4" t="inlineStr">
         <is>
-          <t>816407</t>
+          <t>816374</t>
         </is>
       </c>
       <c r="G235" s="5" t="inlineStr">
@@ -12990,7 +12990,7 @@
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491786BS9</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491817T79</t>
         </is>
       </c>
       <c r="C236" s="3" t="n">
@@ -13001,12 +13001,12 @@
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491786BS9</t>
+          <t>KIT4M06491817T79</t>
         </is>
       </c>
       <c r="F236" s="4" t="inlineStr">
         <is>
-          <t>816396</t>
+          <t>816415</t>
         </is>
       </c>
       <c r="G236" s="5" t="inlineStr">
@@ -13043,7 +13043,7 @@
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437482-KIT4M05872578G7Q</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918154FM</t>
         </is>
       </c>
       <c r="C237" s="3" t="n">
@@ -13054,12 +13054,12 @@
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872578G7Q</t>
+          <t>KIT4M064918154FM</t>
         </is>
       </c>
       <c r="F237" s="4" t="inlineStr">
         <is>
-          <t>816102</t>
+          <t>816368</t>
         </is>
       </c>
       <c r="G237" s="5" t="inlineStr">
@@ -13096,7 +13096,7 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437752 - KIT4M05872577TWT</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491818QD2</t>
         </is>
       </c>
       <c r="C238" s="3" t="n">
@@ -13107,12 +13107,12 @@
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872577TWT</t>
+          <t>KIT4M06491818QD2</t>
         </is>
       </c>
       <c r="F238" s="4" t="inlineStr">
         <is>
-          <t>816212</t>
+          <t>816378</t>
         </is>
       </c>
       <c r="G238" s="5" t="inlineStr">
@@ -13149,7 +13149,7 @@
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437362 - KIT4M05872574NKX</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491820X58</t>
         </is>
       </c>
       <c r="C239" s="3" t="n">
@@ -13160,12 +13160,12 @@
       </c>
       <c r="E239" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872574NKX</t>
+          <t>KIT4M06491820X58</t>
         </is>
       </c>
       <c r="F239" s="4" t="inlineStr">
         <is>
-          <t>816113</t>
+          <t>816385</t>
         </is>
       </c>
       <c r="G239" s="5" t="inlineStr">
@@ -13202,7 +13202,7 @@
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437502 - KIT4M058725695CN</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918197VX</t>
         </is>
       </c>
       <c r="C240" s="3" t="n">
@@ -13213,12 +13213,12 @@
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725695CN</t>
+          <t>KIT4M064918197VX</t>
         </is>
       </c>
       <c r="F240" s="4" t="inlineStr">
         <is>
-          <t>816101</t>
+          <t>816397</t>
         </is>
       </c>
       <c r="G240" s="5" t="inlineStr">
@@ -13255,7 +13255,7 @@
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491820X58</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437462 - KIT4M05872575BC8</t>
         </is>
       </c>
       <c r="C241" s="3" t="n">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491820X58</t>
+          <t>KIT4M05872575BC8</t>
         </is>
       </c>
       <c r="F241" s="4" t="inlineStr">
         <is>
-          <t>816385</t>
+          <t>816103</t>
         </is>
       </c>
       <c r="G241" s="5" t="inlineStr">
@@ -13308,7 +13308,7 @@
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491826SQM</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437752 - KIT4M05872577TWT</t>
         </is>
       </c>
       <c r="C242" s="3" t="n">
@@ -13319,12 +13319,12 @@
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491826SQM</t>
+          <t>KIT4M05872577TWT</t>
         </is>
       </c>
       <c r="F242" s="4" t="inlineStr">
         <is>
-          <t>816380</t>
+          <t>816212</t>
         </is>
       </c>
       <c r="G242" s="5" t="inlineStr">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491829CD2</t>
+          <t>SMRT-05900510-Los Angeles CA-021437882-KIT4M05872527QK6</t>
         </is>
       </c>
       <c r="C243" s="3" t="n">
@@ -13372,12 +13372,12 @@
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491829CD2</t>
+          <t>KIT4M05872527QK6</t>
         </is>
       </c>
       <c r="F243" s="4" t="inlineStr">
         <is>
-          <t>816393</t>
+          <t>816214</t>
         </is>
       </c>
       <c r="G243" s="5" t="inlineStr">
@@ -13414,7 +13414,7 @@
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491830G2J</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437362 - KIT4M05872574NKX</t>
         </is>
       </c>
       <c r="C244" s="3" t="n">
@@ -13425,12 +13425,12 @@
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491830G2J</t>
+          <t>KIT4M05872574NKX</t>
         </is>
       </c>
       <c r="F244" s="4" t="inlineStr">
         <is>
-          <t>816372</t>
+          <t>816113</t>
         </is>
       </c>
       <c r="G244" s="5" t="inlineStr">
@@ -13467,7 +13467,7 @@
       </c>
       <c r="B245" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491825PF9</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491786BS9</t>
         </is>
       </c>
       <c r="C245" s="3" t="n">
@@ -13478,12 +13478,12 @@
       </c>
       <c r="E245" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491825PF9</t>
+          <t>KIT4M06491786BS9</t>
         </is>
       </c>
       <c r="F245" s="4" t="inlineStr">
         <is>
-          <t>816367</t>
+          <t>816396</t>
         </is>
       </c>
       <c r="G245" s="5" t="inlineStr">
@@ -13520,7 +13520,7 @@
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918197VX</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437802 - KIT4M05872589TM9</t>
         </is>
       </c>
       <c r="C246" s="3" t="n">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918197VX</t>
+          <t>KIT4M05872589TM9</t>
         </is>
       </c>
       <c r="F246" s="4" t="inlineStr">
         <is>
-          <t>816397</t>
+          <t>816195</t>
         </is>
       </c>
       <c r="G246" s="5" t="inlineStr">
@@ -13573,7 +13573,7 @@
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491818QD2</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064917925MB</t>
         </is>
       </c>
       <c r="C247" s="3" t="n">
@@ -13584,12 +13584,12 @@
       </c>
       <c r="E247" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491818QD2</t>
+          <t>KIT4M064917925MB</t>
         </is>
       </c>
       <c r="F247" s="4" t="inlineStr">
         <is>
-          <t>816378</t>
+          <t>816381</t>
         </is>
       </c>
       <c r="G247" s="5" t="inlineStr">
@@ -13626,7 +13626,7 @@
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918165MW</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491798S8Q</t>
         </is>
       </c>
       <c r="C248" s="3" t="n">
@@ -13637,12 +13637,12 @@
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918165MW</t>
+          <t>KIT4M06491798S8Q</t>
         </is>
       </c>
       <c r="F248" s="4" t="inlineStr">
         <is>
-          <t>816374</t>
+          <t>816395</t>
         </is>
       </c>
       <c r="G248" s="5" t="inlineStr">
@@ -13679,7 +13679,7 @@
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491799CRP</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064917914G5</t>
         </is>
       </c>
       <c r="C249" s="3" t="n">
@@ -13690,12 +13690,12 @@
       </c>
       <c r="E249" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491799CRP</t>
+          <t>KIT4M064917914G5</t>
         </is>
       </c>
       <c r="F249" s="4" t="inlineStr">
         <is>
-          <t>816394</t>
+          <t>816392</t>
         </is>
       </c>
       <c r="G249" s="5" t="inlineStr">
@@ -13732,7 +13732,7 @@
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M0649183125S</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491789PJ6</t>
         </is>
       </c>
       <c r="C250" s="3" t="n">
@@ -13743,12 +13743,12 @@
       </c>
       <c r="E250" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0649183125S</t>
+          <t>KIT4M06491789PJ6</t>
         </is>
       </c>
       <c r="F250" s="4" t="inlineStr">
         <is>
-          <t>816371</t>
+          <t>816407</t>
         </is>
       </c>
       <c r="G250" s="5" t="inlineStr">
@@ -13785,7 +13785,7 @@
       </c>
       <c r="B251" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437882-KIT4M05872527QK6</t>
+          <t>SMRT-05900510-Los Angeles CA-021437482-KIT4M05872578G7Q</t>
         </is>
       </c>
       <c r="C251" s="3" t="n">
@@ -13796,12 +13796,12 @@
       </c>
       <c r="E251" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872527QK6</t>
+          <t>KIT4M05872578G7Q</t>
         </is>
       </c>
       <c r="F251" s="4" t="inlineStr">
         <is>
-          <t>816214</t>
+          <t>816102</t>
         </is>
       </c>
       <c r="G251" s="5" t="inlineStr">
@@ -13838,7 +13838,7 @@
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491817T79</t>
+          <t>SMRT-05900510-Los Angeles CA-021437712-KIT4M05872570FCC</t>
         </is>
       </c>
       <c r="C252" s="3" t="n">
@@ -13849,12 +13849,12 @@
       </c>
       <c r="E252" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491817T79</t>
+          <t>KIT4M05872570FCC</t>
         </is>
       </c>
       <c r="F252" s="4" t="inlineStr">
         <is>
-          <t>816415</t>
+          <t>816105</t>
         </is>
       </c>
       <c r="G252" s="5" t="inlineStr">
@@ -13891,7 +13891,7 @@
       </c>
       <c r="B253" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064917925MB</t>
+          <t>SMRT-05900510-Los Angeles CA-021437352-KIT4M05872545Q8H</t>
         </is>
       </c>
       <c r="C253" s="3" t="n">
@@ -13902,12 +13902,12 @@
       </c>
       <c r="E253" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064917925MB</t>
+          <t>KIT4M05872545Q8H</t>
         </is>
       </c>
       <c r="F253" s="4" t="inlineStr">
         <is>
-          <t>816381</t>
+          <t>816112</t>
         </is>
       </c>
       <c r="G253" s="5" t="inlineStr">
@@ -13997,7 +13997,7 @@
       </c>
       <c r="B255" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437692 - KIT4M05872518P78</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491830G2J</t>
         </is>
       </c>
       <c r="C255" s="3" t="n">
@@ -14008,12 +14008,12 @@
       </c>
       <c r="E255" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872518P78</t>
+          <t>KIT4M06491830G2J</t>
         </is>
       </c>
       <c r="F255" s="4" t="inlineStr">
         <is>
-          <t>816184</t>
+          <t>816372</t>
         </is>
       </c>
       <c r="G255" s="5" t="inlineStr">
@@ -14050,7 +14050,7 @@
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491795MWG</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491826SQM</t>
         </is>
       </c>
       <c r="C256" s="3" t="n">
@@ -14061,12 +14061,12 @@
       </c>
       <c r="E256" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491795MWG</t>
+          <t>KIT4M06491826SQM</t>
         </is>
       </c>
       <c r="F256" s="4" t="inlineStr">
         <is>
-          <t>816383</t>
+          <t>816380</t>
         </is>
       </c>
       <c r="G256" s="5" t="inlineStr">
@@ -14092,7 +14092,7 @@
       </c>
       <c r="L256" s="5" t="n"/>
       <c r="M256" s="7" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="257">
@@ -14103,7 +14103,7 @@
       </c>
       <c r="B257" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437372 - KIT4M058725505J5</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438192 - KIT4M05872511F6P</t>
         </is>
       </c>
       <c r="C257" s="3" t="n">
@@ -14114,12 +14114,12 @@
       </c>
       <c r="E257" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725505J5</t>
+          <t>KIT4M05872511F6P</t>
         </is>
       </c>
       <c r="F257" s="4" t="inlineStr">
         <is>
-          <t>816117</t>
+          <t>816090</t>
         </is>
       </c>
       <c r="G257" s="5" t="inlineStr">
@@ -14156,7 +14156,7 @@
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437402 - KIT4M05872537SGZ</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955542 - KIT4M05563551N6Q</t>
         </is>
       </c>
       <c r="C258" s="3" t="n">
@@ -14167,12 +14167,12 @@
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872537SGZ</t>
+          <t>KIT4M05563551N6Q</t>
         </is>
       </c>
       <c r="F258" s="4" t="inlineStr">
         <is>
-          <t>816073</t>
+          <t>814450</t>
         </is>
       </c>
       <c r="G258" s="5" t="inlineStr">
@@ -14209,7 +14209,7 @@
       </c>
       <c r="B259" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437572 - KIT4M05872579JPF</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918346DB</t>
         </is>
       </c>
       <c r="C259" s="3" t="n">
@@ -14220,12 +14220,12 @@
       </c>
       <c r="E259" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872579JPF</t>
+          <t>KIT4M064918346DB</t>
         </is>
       </c>
       <c r="F259" s="4" t="inlineStr">
         <is>
-          <t>816111</t>
+          <t>816369</t>
         </is>
       </c>
       <c r="G259" s="5" t="inlineStr">
@@ -14262,7 +14262,7 @@
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437662 - KIT4M05872534RXS</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491833JGV</t>
         </is>
       </c>
       <c r="C260" s="3" t="n">
@@ -14273,12 +14273,12 @@
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872534RXS</t>
+          <t>KIT4M06491833JGV</t>
         </is>
       </c>
       <c r="F260" s="4" t="inlineStr">
         <is>
-          <t>816216</t>
+          <t>816384</t>
         </is>
       </c>
       <c r="G260" s="5" t="inlineStr">
@@ -14315,7 +14315,7 @@
       </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 021437682 - KIT4M05872544BXG</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649892 - KIT4M05413777DGG</t>
         </is>
       </c>
       <c r="C261" s="3" t="n">
@@ -14326,12 +14326,12 @@
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872544BXG</t>
+          <t>KIT4M05413777DGG</t>
         </is>
       </c>
       <c r="F261" s="4" t="inlineStr">
         <is>
-          <t>816176</t>
+          <t>812802</t>
         </is>
       </c>
       <c r="G261" s="5" t="inlineStr">
@@ -14368,7 +14368,7 @@
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491833JGV</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918015Z2</t>
         </is>
       </c>
       <c r="C262" s="3" t="n">
@@ -14379,12 +14379,12 @@
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491833JGV</t>
+          <t>KIT4M064918015Z2</t>
         </is>
       </c>
       <c r="F262" s="4" t="inlineStr">
         <is>
-          <t>816384</t>
+          <t>816376</t>
         </is>
       </c>
       <c r="G262" s="5" t="inlineStr">
@@ -14421,7 +14421,7 @@
       </c>
       <c r="B263" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918346DB</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491813KGS</t>
         </is>
       </c>
       <c r="C263" s="3" t="n">
@@ -14432,12 +14432,12 @@
       </c>
       <c r="E263" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918346DB</t>
+          <t>KIT4M06491813KGS</t>
         </is>
       </c>
       <c r="F263" s="4" t="inlineStr">
         <is>
-          <t>816369</t>
+          <t>816377</t>
         </is>
       </c>
       <c r="G263" s="5" t="inlineStr">
@@ -14474,7 +14474,7 @@
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918015Z2</t>
+          <t>SS - 05900510 -  Los Angeles CA - 021437682 - KIT4M05872544BXG</t>
         </is>
       </c>
       <c r="C264" s="3" t="n">
@@ -14485,12 +14485,12 @@
       </c>
       <c r="E264" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918015Z2</t>
+          <t>KIT4M05872544BXG</t>
         </is>
       </c>
       <c r="F264" s="4" t="inlineStr">
         <is>
-          <t>816376</t>
+          <t>816176</t>
         </is>
       </c>
       <c r="G264" s="5" t="inlineStr">
@@ -14527,7 +14527,7 @@
       </c>
       <c r="B265" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438082 - KIT4M05799668SS7</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437662 - KIT4M05872534RXS</t>
         </is>
       </c>
       <c r="C265" s="3" t="n">
@@ -14538,12 +14538,12 @@
       </c>
       <c r="E265" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799668SS7</t>
+          <t>KIT4M05872534RXS</t>
         </is>
       </c>
       <c r="F265" s="4" t="inlineStr">
         <is>
-          <t>816279</t>
+          <t>816216</t>
         </is>
       </c>
       <c r="G265" s="5" t="inlineStr">
@@ -14580,7 +14580,7 @@
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955542 - KIT4M05563551N6Q</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437402 - KIT4M05872537SGZ</t>
         </is>
       </c>
       <c r="C266" s="3" t="n">
@@ -14591,12 +14591,12 @@
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563551N6Q</t>
+          <t>KIT4M05872537SGZ</t>
         </is>
       </c>
       <c r="F266" s="4" t="inlineStr">
         <is>
-          <t>814450</t>
+          <t>816073</t>
         </is>
       </c>
       <c r="G266" s="5" t="inlineStr">
@@ -14633,7 +14633,7 @@
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438192 - KIT4M05872511F6P</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437372 - KIT4M058725505J5</t>
         </is>
       </c>
       <c r="C267" s="3" t="n">
@@ -14644,12 +14644,12 @@
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872511F6P</t>
+          <t>KIT4M058725505J5</t>
         </is>
       </c>
       <c r="F267" s="4" t="inlineStr">
         <is>
-          <t>816090</t>
+          <t>816117</t>
         </is>
       </c>
       <c r="G267" s="5" t="inlineStr">
@@ -14686,7 +14686,7 @@
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491813KGS</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438082 - KIT4M05799668SS7</t>
         </is>
       </c>
       <c r="C268" s="3" t="n">
@@ -14697,12 +14697,12 @@
       </c>
       <c r="E268" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491813KGS</t>
+          <t>KIT4M05799668SS7</t>
         </is>
       </c>
       <c r="F268" s="4" t="inlineStr">
         <is>
-          <t>816377</t>
+          <t>816279</t>
         </is>
       </c>
       <c r="G268" s="5" t="inlineStr">
@@ -14739,7 +14739,7 @@
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649892 - KIT4M05413777DGG</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491795MWG</t>
         </is>
       </c>
       <c r="C269" s="3" t="n">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E269" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413777DGG</t>
+          <t>KIT4M06491795MWG</t>
         </is>
       </c>
       <c r="F269" s="4" t="inlineStr">
         <is>
-          <t>812802</t>
+          <t>816383</t>
         </is>
       </c>
       <c r="G269" s="5" t="inlineStr">
@@ -14792,7 +14792,7 @@
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437272 - KIT4P0008459589D</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437572 - KIT4M05872579JPF</t>
         </is>
       </c>
       <c r="C270" s="3" t="n">
@@ -14803,17 +14803,17 @@
       </c>
       <c r="E270" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0008459589D</t>
+          <t>KIT4M05872579JPF</t>
         </is>
       </c>
       <c r="F270" s="4" t="inlineStr">
         <is>
-          <t>816222</t>
+          <t>816111</t>
         </is>
       </c>
       <c r="G270" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H270" s="5" t="inlineStr">
@@ -14834,7 +14834,7 @@
       </c>
       <c r="L270" s="5" t="n"/>
       <c r="M270" s="7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="271">
@@ -14845,7 +14845,7 @@
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491797NCX</t>
+          <t>SS - 05900510 - Los Angeles, CA  - 020649572 - KIT4M05413816N8K</t>
         </is>
       </c>
       <c r="C271" s="3" t="n">
@@ -14856,12 +14856,12 @@
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491797NCX</t>
+          <t>KIT4M05413816N8K</t>
         </is>
       </c>
       <c r="F271" s="4" t="inlineStr">
         <is>
-          <t>816408</t>
+          <t>812832</t>
         </is>
       </c>
       <c r="G271" s="5" t="inlineStr">
@@ -14898,7 +14898,7 @@
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491808P4F</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491797NCX</t>
         </is>
       </c>
       <c r="C272" s="3" t="n">
@@ -14909,12 +14909,12 @@
       </c>
       <c r="E272" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491808P4F</t>
+          <t>KIT4M06491797NCX</t>
         </is>
       </c>
       <c r="F272" s="4" t="inlineStr">
         <is>
-          <t>816399</t>
+          <t>816408</t>
         </is>
       </c>
       <c r="G272" s="5" t="inlineStr">
@@ -14951,7 +14951,7 @@
       </c>
       <c r="B273" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA  - 020649572 - KIT4M05413816N8K</t>
+          <t>SMA - 05900510 -  Los Angeles CA - 020649602 - KIT4M05413773R6G</t>
         </is>
       </c>
       <c r="C273" s="3" t="n">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E273" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413816N8K</t>
+          <t>KIT4M05413773R6G</t>
         </is>
       </c>
       <c r="F273" s="4" t="inlineStr">
         <is>
-          <t>812832</t>
+          <t>812807</t>
         </is>
       </c>
       <c r="G273" s="5" t="inlineStr">
@@ -15004,7 +15004,7 @@
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 -  Los Angeles CA - 020649602 - KIT4M05413773R6G</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491808P4F</t>
         </is>
       </c>
       <c r="C274" s="3" t="n">
@@ -15015,12 +15015,12 @@
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413773R6G</t>
+          <t>KIT4M06491808P4F</t>
         </is>
       </c>
       <c r="F274" s="4" t="inlineStr">
         <is>
-          <t>812807</t>
+          <t>816399</t>
         </is>
       </c>
       <c r="G274" s="5" t="inlineStr">
@@ -15057,7 +15057,7 @@
       </c>
       <c r="B275" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491796QQN</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437272 - KIT4P0008459589D</t>
         </is>
       </c>
       <c r="C275" s="3" t="n">
@@ -15068,17 +15068,17 @@
       </c>
       <c r="E275" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491796QQN</t>
+          <t>KIT4P0008459589D</t>
         </is>
       </c>
       <c r="F275" s="4" t="inlineStr">
         <is>
-          <t>816405</t>
+          <t>816222</t>
         </is>
       </c>
       <c r="G275" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H275" s="5" t="inlineStr">
@@ -15099,7 +15099,7 @@
       </c>
       <c r="L275" s="5" t="n"/>
       <c r="M275" s="7" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="276">
@@ -15110,7 +15110,7 @@
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918239TM</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491796QQN</t>
         </is>
       </c>
       <c r="C276" s="3" t="n">
@@ -15121,12 +15121,12 @@
       </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918239TM</t>
+          <t>KIT4M06491796QQN</t>
         </is>
       </c>
       <c r="F276" s="4" t="inlineStr">
         <is>
-          <t>816398</t>
+          <t>816405</t>
         </is>
       </c>
       <c r="G276" s="5" t="inlineStr">
@@ -15163,7 +15163,7 @@
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491822SF6</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918239TM</t>
         </is>
       </c>
       <c r="C277" s="3" t="n">
@@ -15174,12 +15174,12 @@
       </c>
       <c r="E277" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491822SF6</t>
+          <t>KIT4M064918239TM</t>
         </is>
       </c>
       <c r="F277" s="4" t="inlineStr">
         <is>
-          <t>816412</t>
+          <t>816398</t>
         </is>
       </c>
       <c r="G277" s="5" t="inlineStr">
@@ -15216,7 +15216,7 @@
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437382 - KIT4M058725438WP</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491822SF6</t>
         </is>
       </c>
       <c r="C278" s="3" t="n">
@@ -15227,12 +15227,12 @@
       </c>
       <c r="E278" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725438WP</t>
+          <t>KIT4M06491822SF6</t>
         </is>
       </c>
       <c r="F278" s="4" t="inlineStr">
         <is>
-          <t>816115</t>
+          <t>816412</t>
         </is>
       </c>
       <c r="G278" s="5" t="inlineStr">
@@ -15322,7 +15322,7 @@
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M0649181062D</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437382 - KIT4M058725438WP</t>
         </is>
       </c>
       <c r="C280" s="3" t="n">
@@ -15333,12 +15333,12 @@
       </c>
       <c r="E280" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0649181062D</t>
+          <t>KIT4M058725438WP</t>
         </is>
       </c>
       <c r="F280" s="4" t="inlineStr">
         <is>
-          <t>816388</t>
+          <t>816115</t>
         </is>
       </c>
       <c r="G280" s="5" t="inlineStr">
@@ -15364,7 +15364,7 @@
       </c>
       <c r="L280" s="5" t="n"/>
       <c r="M280" s="7" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="281">
@@ -15375,7 +15375,7 @@
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491805F7Z</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437962 - KIT4M05799706Z6R</t>
         </is>
       </c>
       <c r="C281" s="3" t="n">
@@ -15386,12 +15386,12 @@
       </c>
       <c r="E281" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491805F7Z</t>
+          <t>KIT4M05799706Z6R</t>
         </is>
       </c>
       <c r="F281" s="4" t="inlineStr">
         <is>
-          <t>816382</t>
+          <t>816273</t>
         </is>
       </c>
       <c r="G281" s="5" t="inlineStr">
@@ -15428,7 +15428,7 @@
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491794MTJ</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649982 - KIT4M05413823B5P</t>
         </is>
       </c>
       <c r="C282" s="3" t="n">
@@ -15439,12 +15439,12 @@
       </c>
       <c r="E282" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491794MTJ</t>
+          <t>KIT4M05413823B5P</t>
         </is>
       </c>
       <c r="F282" s="4" t="inlineStr">
         <is>
-          <t>816375</t>
+          <t>812837</t>
         </is>
       </c>
       <c r="G282" s="5" t="inlineStr">
@@ -15534,7 +15534,7 @@
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491812JDV</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649992 - KIT4M05413809J58</t>
         </is>
       </c>
       <c r="C284" s="3" t="n">
@@ -15545,12 +15545,12 @@
       </c>
       <c r="E284" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491812JDV</t>
+          <t>KIT4M05413809J58</t>
         </is>
       </c>
       <c r="F284" s="4" t="inlineStr">
         <is>
-          <t>816409</t>
+          <t>812805</t>
         </is>
       </c>
       <c r="G284" s="5" t="inlineStr">
@@ -15587,7 +15587,7 @@
       </c>
       <c r="B285" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491809ZR6</t>
+          <t>SS - 05900510 -  Los Angeles CA - 021437602 - KIT4M05872524CFG</t>
         </is>
       </c>
       <c r="C285" s="3" t="n">
@@ -15598,12 +15598,12 @@
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491809ZR6</t>
+          <t>KIT4M05872524CFG</t>
         </is>
       </c>
       <c r="F285" s="4" t="inlineStr">
         <is>
-          <t>816402</t>
+          <t>816205</t>
         </is>
       </c>
       <c r="G285" s="5" t="inlineStr">
@@ -15640,7 +15640,7 @@
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491807TRH</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438292 - KIt4m058725108K2</t>
         </is>
       </c>
       <c r="C286" s="3" t="n">
@@ -15651,12 +15651,12 @@
       </c>
       <c r="E286" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491807TRH</t>
+          <t>KIT4M058725108K2</t>
         </is>
       </c>
       <c r="F286" s="4" t="inlineStr">
         <is>
-          <t>816386</t>
+          <t>816287</t>
         </is>
       </c>
       <c r="G286" s="5" t="inlineStr">
@@ -15693,7 +15693,7 @@
       </c>
       <c r="B287" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491802BZV</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M0649181062D</t>
         </is>
       </c>
       <c r="C287" s="3" t="n">
@@ -15704,12 +15704,12 @@
       </c>
       <c r="E287" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491802BZV</t>
+          <t>KIT4M0649181062D</t>
         </is>
       </c>
       <c r="F287" s="4" t="inlineStr">
         <is>
-          <t>816390</t>
+          <t>816388</t>
         </is>
       </c>
       <c r="G287" s="5" t="inlineStr">
@@ -15746,7 +15746,7 @@
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491803672</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491805F7Z</t>
         </is>
       </c>
       <c r="C288" s="3" t="n">
@@ -15757,12 +15757,12 @@
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491803672</t>
+          <t>KIT4M06491805F7Z</t>
         </is>
       </c>
       <c r="F288" s="4" t="inlineStr">
         <is>
-          <t>816391</t>
+          <t>816382</t>
         </is>
       </c>
       <c r="G288" s="5" t="inlineStr">
@@ -15799,7 +15799,7 @@
       </c>
       <c r="B289" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437432 - KIT4M0587256692N</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491803672</t>
         </is>
       </c>
       <c r="C289" s="3" t="n">
@@ -15810,12 +15810,12 @@
       </c>
       <c r="E289" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0587256692N</t>
+          <t>KIT4M06491803672</t>
         </is>
       </c>
       <c r="F289" s="4" t="inlineStr">
         <is>
-          <t>816072</t>
+          <t>816391</t>
         </is>
       </c>
       <c r="G289" s="5" t="inlineStr">
@@ -15852,7 +15852,7 @@
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437742 - KIT4M05872539ZMR</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649702 - KIT4M04604741P2X</t>
         </is>
       </c>
       <c r="C290" s="3" t="n">
@@ -15863,12 +15863,12 @@
       </c>
       <c r="E290" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872539ZMR</t>
+          <t>KIT4M04604741P2X</t>
         </is>
       </c>
       <c r="F290" s="4" t="inlineStr">
         <is>
-          <t>816108</t>
+          <t>809871</t>
         </is>
       </c>
       <c r="G290" s="5" t="inlineStr">
@@ -15905,7 +15905,7 @@
       </c>
       <c r="B291" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437842-KIT4M05872547MK2</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437472 - KIT4M05872565VJK</t>
         </is>
       </c>
       <c r="C291" s="3" t="n">
@@ -15916,12 +15916,12 @@
       </c>
       <c r="E291" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872547MK2</t>
+          <t>KIT4M05872565VJK</t>
         </is>
       </c>
       <c r="F291" s="4" t="inlineStr">
         <is>
-          <t>816209</t>
+          <t>816109</t>
         </is>
       </c>
       <c r="G291" s="5" t="inlineStr">
@@ -15958,7 +15958,7 @@
       </c>
       <c r="B292" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437542 - KIT4M05872553WFR</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437322 - KIT4M05872567V72</t>
         </is>
       </c>
       <c r="C292" s="3" t="n">
@@ -15969,12 +15969,12 @@
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872553WFR</t>
+          <t>KIT4M05872567V72</t>
         </is>
       </c>
       <c r="F292" s="4" t="inlineStr">
         <is>
-          <t>816116</t>
+          <t>816099</t>
         </is>
       </c>
       <c r="G292" s="5" t="inlineStr">
@@ -16011,7 +16011,7 @@
       </c>
       <c r="B293" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437512 - KIT4M05872559VR9</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437912 - KIT4M05872525NP5</t>
         </is>
       </c>
       <c r="C293" s="3" t="n">
@@ -16022,12 +16022,12 @@
       </c>
       <c r="E293" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872559VR9</t>
+          <t>KIT4M05872525NP5</t>
         </is>
       </c>
       <c r="F293" s="4" t="inlineStr">
         <is>
-          <t>816114</t>
+          <t>816213</t>
         </is>
       </c>
       <c r="G293" s="5" t="inlineStr">
@@ -16064,7 +16064,7 @@
       </c>
       <c r="B294" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438292 - KIt4m058725108K2</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437672 - KIT4M05872531DSZ</t>
         </is>
       </c>
       <c r="C294" s="3" t="n">
@@ -16075,12 +16075,12 @@
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725108K2</t>
+          <t>KIT4M05872531DSZ</t>
         </is>
       </c>
       <c r="F294" s="4" t="inlineStr">
         <is>
-          <t>816287</t>
+          <t>816171</t>
         </is>
       </c>
       <c r="G294" s="5" t="inlineStr">
@@ -16117,7 +16117,7 @@
       </c>
       <c r="B295" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437962 - KIT4M05799706Z6R</t>
+          <t>SMRT-05900510-Los Angeles CA-021437842-KIT4M05872547MK2</t>
         </is>
       </c>
       <c r="C295" s="3" t="n">
@@ -16128,12 +16128,12 @@
       </c>
       <c r="E295" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799706Z6R</t>
+          <t>KIT4M05872547MK2</t>
         </is>
       </c>
       <c r="F295" s="4" t="inlineStr">
         <is>
-          <t>816273</t>
+          <t>816209</t>
         </is>
       </c>
       <c r="G295" s="5" t="inlineStr">
@@ -16170,7 +16170,7 @@
       </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491811JB5</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437742 - KIT4M05872539ZMR</t>
         </is>
       </c>
       <c r="C296" s="3" t="n">
@@ -16181,12 +16181,12 @@
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491811JB5</t>
+          <t>KIT4M05872539ZMR</t>
         </is>
       </c>
       <c r="F296" s="4" t="inlineStr">
         <is>
-          <t>816411</t>
+          <t>816108</t>
         </is>
       </c>
       <c r="G296" s="5" t="inlineStr">
@@ -16223,7 +16223,7 @@
       </c>
       <c r="B297" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649702 - KIT4M04604741P2X</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437512 - KIT4M05872559VR9</t>
         </is>
       </c>
       <c r="C297" s="3" t="n">
@@ -16234,12 +16234,12 @@
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604741P2X</t>
+          <t>KIT4M05872559VR9</t>
         </is>
       </c>
       <c r="F297" s="4" t="inlineStr">
         <is>
-          <t>809871</t>
+          <t>816114</t>
         </is>
       </c>
       <c r="G297" s="5" t="inlineStr">
@@ -16276,7 +16276,7 @@
       </c>
       <c r="B298" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491837DPX</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437542 - KIT4M05872553WFR</t>
         </is>
       </c>
       <c r="C298" s="3" t="n">
@@ -16287,12 +16287,12 @@
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491837DPX</t>
+          <t>KIT4M05872553WFR</t>
         </is>
       </c>
       <c r="F298" s="4" t="inlineStr">
         <is>
-          <t>816389</t>
+          <t>816116</t>
         </is>
       </c>
       <c r="G298" s="5" t="inlineStr">
@@ -16329,7 +16329,7 @@
       </c>
       <c r="B299" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918322GZ</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491794MTJ</t>
         </is>
       </c>
       <c r="C299" s="3" t="n">
@@ -16340,12 +16340,12 @@
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918322GZ</t>
+          <t>KIT4M06491794MTJ</t>
         </is>
       </c>
       <c r="F299" s="4" t="inlineStr">
         <is>
-          <t>816414</t>
+          <t>816375</t>
         </is>
       </c>
       <c r="G299" s="5" t="inlineStr">
@@ -16382,7 +16382,7 @@
       </c>
       <c r="B300" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491828XWF</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437432 - KIT4M0587256692N</t>
         </is>
       </c>
       <c r="C300" s="3" t="n">
@@ -16393,12 +16393,12 @@
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491828XWF</t>
+          <t>KIT4M0587256692N</t>
         </is>
       </c>
       <c r="F300" s="4" t="inlineStr">
         <is>
-          <t>816387</t>
+          <t>816072</t>
         </is>
       </c>
       <c r="G300" s="5" t="inlineStr">
@@ -16435,7 +16435,7 @@
       </c>
       <c r="B301" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437522 - KIT4M05872576R4B</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437532 - KIT4M05872556RC9</t>
         </is>
       </c>
       <c r="C301" s="3" t="n">
@@ -16446,12 +16446,12 @@
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872576R4B</t>
+          <t>KIT4M05872556RC9</t>
         </is>
       </c>
       <c r="F301" s="4" t="inlineStr">
         <is>
-          <t>816110</t>
+          <t>816118</t>
         </is>
       </c>
       <c r="G301" s="5" t="inlineStr">
@@ -16488,7 +16488,7 @@
       </c>
       <c r="B302" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649992 - KIT4M05413809J58</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491802BZV</t>
         </is>
       </c>
       <c r="C302" s="3" t="n">
@@ -16499,12 +16499,12 @@
       </c>
       <c r="E302" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413809J58</t>
+          <t>KIT4M06491802BZV</t>
         </is>
       </c>
       <c r="F302" s="4" t="inlineStr">
         <is>
-          <t>812805</t>
+          <t>816390</t>
         </is>
       </c>
       <c r="G302" s="5" t="inlineStr">
@@ -16594,7 +16594,7 @@
       </c>
       <c r="B304" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437552 - KIT4M05872586VCH</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437522 - KIT4M05872576R4B</t>
         </is>
       </c>
       <c r="C304" s="3" t="n">
@@ -16605,12 +16605,12 @@
       </c>
       <c r="E304" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872586VCH</t>
+          <t>KIT4M05872576R4B</t>
         </is>
       </c>
       <c r="F304" s="4" t="inlineStr">
         <is>
-          <t>816068</t>
+          <t>816110</t>
         </is>
       </c>
       <c r="G304" s="5" t="inlineStr">
@@ -16647,7 +16647,7 @@
       </c>
       <c r="B305" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437532 - KIT4M05872556RC9</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437552 - KIT4M05872586VCH</t>
         </is>
       </c>
       <c r="C305" s="3" t="n">
@@ -16658,12 +16658,12 @@
       </c>
       <c r="E305" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872556RC9</t>
+          <t>KIT4M05872586VCH</t>
         </is>
       </c>
       <c r="F305" s="4" t="inlineStr">
         <is>
-          <t>816118</t>
+          <t>816068</t>
         </is>
       </c>
       <c r="G305" s="5" t="inlineStr">
@@ -16753,7 +16753,7 @@
       </c>
       <c r="B307" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437322 - KIT4M05872567V72</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491812JDV</t>
         </is>
       </c>
       <c r="C307" s="3" t="n">
@@ -16764,12 +16764,12 @@
       </c>
       <c r="E307" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872567V72</t>
+          <t>KIT4M06491812JDV</t>
         </is>
       </c>
       <c r="F307" s="4" t="inlineStr">
         <is>
-          <t>816099</t>
+          <t>816409</t>
         </is>
       </c>
       <c r="G307" s="5" t="inlineStr">
@@ -16806,7 +16806,7 @@
       </c>
       <c r="B308" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437472 - KIT4M05872565VJK</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491828XWF</t>
         </is>
       </c>
       <c r="C308" s="3" t="n">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E308" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872565VJK</t>
+          <t>KIT4M06491828XWF</t>
         </is>
       </c>
       <c r="F308" s="4" t="inlineStr">
         <is>
-          <t>816109</t>
+          <t>816387</t>
         </is>
       </c>
       <c r="G308" s="5" t="inlineStr">
@@ -16859,7 +16859,7 @@
       </c>
       <c r="B309" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437912 - KIT4M05872525NP5</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491837DPX</t>
         </is>
       </c>
       <c r="C309" s="3" t="n">
@@ -16870,12 +16870,12 @@
       </c>
       <c r="E309" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872525NP5</t>
+          <t>KIT4M06491837DPX</t>
         </is>
       </c>
       <c r="F309" s="4" t="inlineStr">
         <is>
-          <t>816213</t>
+          <t>816389</t>
         </is>
       </c>
       <c r="G309" s="5" t="inlineStr">
@@ -16912,7 +16912,7 @@
       </c>
       <c r="B310" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 021437602 - KIT4M05872524CFG</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918322GZ</t>
         </is>
       </c>
       <c r="C310" s="3" t="n">
@@ -16923,12 +16923,12 @@
       </c>
       <c r="E310" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872524CFG</t>
+          <t>KIT4M064918322GZ</t>
         </is>
       </c>
       <c r="F310" s="4" t="inlineStr">
         <is>
-          <t>816205</t>
+          <t>816414</t>
         </is>
       </c>
       <c r="G310" s="5" t="inlineStr">
@@ -16965,7 +16965,7 @@
       </c>
       <c r="B311" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437672 - KIT4M05872531DSZ</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491811JB5</t>
         </is>
       </c>
       <c r="C311" s="3" t="n">
@@ -16976,12 +16976,12 @@
       </c>
       <c r="E311" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872531DSZ</t>
+          <t>KIT4M06491811JB5</t>
         </is>
       </c>
       <c r="F311" s="4" t="inlineStr">
         <is>
-          <t>816171</t>
+          <t>816411</t>
         </is>
       </c>
       <c r="G311" s="5" t="inlineStr">
@@ -17018,7 +17018,7 @@
       </c>
       <c r="B312" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437452 - KIT4M05872580C6X</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491809ZR6</t>
         </is>
       </c>
       <c r="C312" s="3" t="n">
@@ -17029,12 +17029,12 @@
       </c>
       <c r="E312" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872580C6X</t>
+          <t>KIT4M06491809ZR6</t>
         </is>
       </c>
       <c r="F312" s="4" t="inlineStr">
         <is>
-          <t>816097</t>
+          <t>816402</t>
         </is>
       </c>
       <c r="G312" s="5" t="inlineStr">
@@ -17060,7 +17060,7 @@
       </c>
       <c r="L312" s="5" t="n"/>
       <c r="M312" s="7" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="313">
@@ -17071,7 +17071,7 @@
       </c>
       <c r="B313" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649382 - KIT4M05368219KRH</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491807TRH</t>
         </is>
       </c>
       <c r="C313" s="3" t="n">
@@ -17082,12 +17082,12 @@
       </c>
       <c r="E313" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368219KRH</t>
+          <t>KIT4M06491807TRH</t>
         </is>
       </c>
       <c r="F313" s="4" t="inlineStr">
         <is>
-          <t>810646</t>
+          <t>816386</t>
         </is>
       </c>
       <c r="G313" s="5" t="inlineStr">
@@ -17113,7 +17113,7 @@
       </c>
       <c r="L313" s="5" t="n"/>
       <c r="M313" s="7" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="314">
@@ -17124,7 +17124,7 @@
       </c>
       <c r="B314" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437262 - KIT4P0008460369B</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020955312 - KIT4M0556351956H</t>
         </is>
       </c>
       <c r="C314" s="3" t="n">
@@ -17135,17 +17135,17 @@
       </c>
       <c r="E314" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0008460369B</t>
+          <t>KIT4M0556351956H</t>
         </is>
       </c>
       <c r="F314" s="4" t="inlineStr">
         <is>
-          <t>816224</t>
+          <t>814477</t>
         </is>
       </c>
       <c r="G314" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H314" s="5" t="inlineStr">
@@ -17177,7 +17177,7 @@
       </c>
       <c r="B315" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649982 - KIT4M05413823B5P</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437492 - KIT4M0587256196K</t>
         </is>
       </c>
       <c r="C315" s="3" t="n">
@@ -17188,12 +17188,12 @@
       </c>
       <c r="E315" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413823B5P</t>
+          <t>KIT4M0587256196K</t>
         </is>
       </c>
       <c r="F315" s="4" t="inlineStr">
         <is>
-          <t>812837</t>
+          <t>816098</t>
         </is>
       </c>
       <c r="G315" s="5" t="inlineStr">
@@ -17230,7 +17230,7 @@
       </c>
       <c r="B316" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438052 - KIT4M05872522W7W</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437652 - KIT4M05872551G9S</t>
         </is>
       </c>
       <c r="C316" s="3" t="n">
@@ -17241,12 +17241,12 @@
       </c>
       <c r="E316" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872522W7W</t>
+          <t>KIT4M05872551G9S</t>
         </is>
       </c>
       <c r="F316" s="4" t="inlineStr">
         <is>
-          <t>816217</t>
+          <t>816180</t>
         </is>
       </c>
       <c r="G316" s="5" t="inlineStr">
@@ -17283,7 +17283,7 @@
       </c>
       <c r="B317" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437902 - KIT4M05799717WZV</t>
+          <t>SS - 05900510 - Los Angeles, CA - 021437772 - KIT4M05872563FWB</t>
         </is>
       </c>
       <c r="C317" s="3" t="n">
@@ -17294,12 +17294,12 @@
       </c>
       <c r="E317" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799717WZV</t>
+          <t>KIT4M05872563FWB</t>
         </is>
       </c>
       <c r="F317" s="4" t="inlineStr">
         <is>
-          <t>816280</t>
+          <t>816208</t>
         </is>
       </c>
       <c r="G317" s="5" t="inlineStr">
@@ -17336,7 +17336,7 @@
       </c>
       <c r="B318" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020955312 - KIT4M0556351956H</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437762 - KIT4M05872564MCF</t>
         </is>
       </c>
       <c r="C318" s="3" t="n">
@@ -17347,12 +17347,12 @@
       </c>
       <c r="E318" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0556351956H</t>
+          <t>KIT4M05872564MCF</t>
         </is>
       </c>
       <c r="F318" s="4" t="inlineStr">
         <is>
-          <t>814477</t>
+          <t>816203</t>
         </is>
       </c>
       <c r="G318" s="5" t="inlineStr">
@@ -17389,7 +17389,7 @@
       </c>
       <c r="B319" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438212 - KIT4M058725047FZ</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437872 - KIT4M06490319DDN</t>
         </is>
       </c>
       <c r="C319" s="3" t="n">
@@ -17400,12 +17400,12 @@
       </c>
       <c r="E319" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725047FZ</t>
+          <t>KIT4M06490319DDN</t>
         </is>
       </c>
       <c r="F319" s="4" t="inlineStr">
         <is>
-          <t>816289</t>
+          <t>816220</t>
         </is>
       </c>
       <c r="G319" s="5" t="inlineStr">
@@ -17442,7 +17442,7 @@
       </c>
       <c r="B320" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437702 - KIT4M05872515PJT</t>
+          <t>SS - 05900510 - Los Angeles, CA - 021437852 - KIT4M0587257292W</t>
         </is>
       </c>
       <c r="C320" s="3" t="n">
@@ -17453,12 +17453,12 @@
       </c>
       <c r="E320" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872515PJT</t>
+          <t>KIT4M0587257292W</t>
         </is>
       </c>
       <c r="F320" s="4" t="inlineStr">
         <is>
-          <t>816218</t>
+          <t>816207</t>
         </is>
       </c>
       <c r="G320" s="5" t="inlineStr">
@@ -17495,7 +17495,7 @@
       </c>
       <c r="B321" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649772 - KIT4M04475152RGR</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437452 - KIT4M05872580C6X</t>
         </is>
       </c>
       <c r="C321" s="3" t="n">
@@ -17506,12 +17506,12 @@
       </c>
       <c r="E321" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475152RGR</t>
+          <t>KIT4M05872580C6X</t>
         </is>
       </c>
       <c r="F321" s="4" t="inlineStr">
         <is>
-          <t>809861</t>
+          <t>816097</t>
         </is>
       </c>
       <c r="G321" s="5" t="inlineStr">
@@ -17548,7 +17548,7 @@
       </c>
       <c r="B322" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438062 - KIT4M05799676NNK</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437892 - KIT4M06490321NJX</t>
         </is>
       </c>
       <c r="C322" s="3" t="n">
@@ -17559,12 +17559,12 @@
       </c>
       <c r="E322" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799676NNK</t>
+          <t>KIT4M06490321NJX</t>
         </is>
       </c>
       <c r="F322" s="4" t="inlineStr">
         <is>
-          <t>816283</t>
+          <t>816219</t>
         </is>
       </c>
       <c r="G322" s="5" t="inlineStr">
@@ -17601,7 +17601,7 @@
       </c>
       <c r="B323" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438142  - KIT4M05799685DG5</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649772 - KIT4M04475152RGR</t>
         </is>
       </c>
       <c r="C323" s="3" t="n">
@@ -17612,12 +17612,12 @@
       </c>
       <c r="E323" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799685DG5</t>
+          <t>KIT4M04475152RGR</t>
         </is>
       </c>
       <c r="F323" s="4" t="inlineStr">
         <is>
-          <t>816271</t>
+          <t>809861</t>
         </is>
       </c>
       <c r="G323" s="5" t="inlineStr">
@@ -17654,7 +17654,7 @@
       </c>
       <c r="B324" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437982 - KIT4M05799678R5P</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955042 - KIT4P00072391SZM</t>
         </is>
       </c>
       <c r="C324" s="3" t="n">
@@ -17665,17 +17665,17 @@
       </c>
       <c r="E324" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799678R5P</t>
+          <t>KIT4P00072391SZM</t>
         </is>
       </c>
       <c r="F324" s="4" t="inlineStr">
         <is>
-          <t>816281</t>
+          <t>814493</t>
         </is>
       </c>
       <c r="G324" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H324" s="5" t="inlineStr">
@@ -17707,7 +17707,7 @@
       </c>
       <c r="B325" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955042 - KIT4P00072391SZM</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437972 - KIT4M06490327GMP</t>
         </is>
       </c>
       <c r="C325" s="3" t="n">
@@ -17718,17 +17718,17 @@
       </c>
       <c r="E325" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00072391SZM</t>
+          <t>KIT4M06490327GMP</t>
         </is>
       </c>
       <c r="F325" s="4" t="inlineStr">
         <is>
-          <t>814493</t>
+          <t>816199</t>
         </is>
       </c>
       <c r="G325" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H325" s="5" t="inlineStr">
@@ -17760,7 +17760,7 @@
       </c>
       <c r="B326" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437872 - KIT4M06490319DDN</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064917936NF</t>
         </is>
       </c>
       <c r="C326" s="3" t="n">
@@ -17771,12 +17771,12 @@
       </c>
       <c r="E326" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06490319DDN</t>
+          <t>KIT4M064917936NF</t>
         </is>
       </c>
       <c r="F326" s="4" t="inlineStr">
         <is>
-          <t>816220</t>
+          <t>816404</t>
         </is>
       </c>
       <c r="G326" s="5" t="inlineStr">
@@ -17813,7 +17813,7 @@
       </c>
       <c r="B327" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437892 - KIT4M06490321NJX</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437262 - KIT4P0008460369B</t>
         </is>
       </c>
       <c r="C327" s="3" t="n">
@@ -17824,17 +17824,17 @@
       </c>
       <c r="E327" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06490321NJX</t>
+          <t>KIT4P0008460369B</t>
         </is>
       </c>
       <c r="F327" s="4" t="inlineStr">
         <is>
-          <t>816219</t>
+          <t>816224</t>
         </is>
       </c>
       <c r="G327" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H327" s="5" t="inlineStr">
@@ -17866,7 +17866,7 @@
       </c>
       <c r="B328" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437972 - KIT4M06490327GMP</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649392 - KIT4M05368206BZP</t>
         </is>
       </c>
       <c r="C328" s="3" t="n">
@@ -17877,12 +17877,12 @@
       </c>
       <c r="E328" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06490327GMP</t>
+          <t>KIT4M05368206BZP</t>
         </is>
       </c>
       <c r="F328" s="4" t="inlineStr">
         <is>
-          <t>816199</t>
+          <t>810645</t>
         </is>
       </c>
       <c r="G328" s="5" t="inlineStr">
@@ -17919,7 +17919,7 @@
       </c>
       <c r="B329" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 021437772 - KIT4M05872563FWB</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437982 - KIT4M05799678R5P</t>
         </is>
       </c>
       <c r="C329" s="3" t="n">
@@ -17930,12 +17930,12 @@
       </c>
       <c r="E329" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872563FWB</t>
+          <t>KIT4M05799678R5P</t>
         </is>
       </c>
       <c r="F329" s="4" t="inlineStr">
         <is>
-          <t>816208</t>
+          <t>816281</t>
         </is>
       </c>
       <c r="G329" s="5" t="inlineStr">
@@ -17972,7 +17972,7 @@
       </c>
       <c r="B330" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438272 - KIT4M05872517VS2</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955642 - KIT4M05563573WKC</t>
         </is>
       </c>
       <c r="C330" s="3" t="n">
@@ -17983,12 +17983,12 @@
       </c>
       <c r="E330" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872517VS2</t>
+          <t>KIT4M05563573WKC</t>
         </is>
       </c>
       <c r="F330" s="4" t="inlineStr">
         <is>
-          <t>816288</t>
+          <t>814488</t>
         </is>
       </c>
       <c r="G330" s="5" t="inlineStr">
@@ -18025,7 +18025,7 @@
       </c>
       <c r="B331" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955642 - KIT4M05563573WKC</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438212 - KIT4M058725047FZ</t>
         </is>
       </c>
       <c r="C331" s="3" t="n">
@@ -18036,12 +18036,12 @@
       </c>
       <c r="E331" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563573WKC</t>
+          <t>KIT4M058725047FZ</t>
         </is>
       </c>
       <c r="F331" s="4" t="inlineStr">
         <is>
-          <t>814488</t>
+          <t>816289</t>
         </is>
       </c>
       <c r="G331" s="5" t="inlineStr">
@@ -18131,7 +18131,7 @@
       </c>
       <c r="B333" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437652 - KIT4M05872551G9S</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438062 - KIT4M05799676NNK</t>
         </is>
       </c>
       <c r="C333" s="3" t="n">
@@ -18142,12 +18142,12 @@
       </c>
       <c r="E333" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872551G9S</t>
+          <t>KIT4M05799676NNK</t>
         </is>
       </c>
       <c r="F333" s="4" t="inlineStr">
         <is>
-          <t>816180</t>
+          <t>816283</t>
         </is>
       </c>
       <c r="G333" s="5" t="inlineStr">
@@ -18184,7 +18184,7 @@
       </c>
       <c r="B334" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437492 - KIT4M0587256196K</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438142  - KIT4M05799685DG5</t>
         </is>
       </c>
       <c r="C334" s="3" t="n">
@@ -18195,12 +18195,12 @@
       </c>
       <c r="E334" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0587256196K</t>
+          <t>KIT4M05799685DG5</t>
         </is>
       </c>
       <c r="F334" s="4" t="inlineStr">
         <is>
-          <t>816098</t>
+          <t>816271</t>
         </is>
       </c>
       <c r="G334" s="5" t="inlineStr">
@@ -18237,7 +18237,7 @@
       </c>
       <c r="B335" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437762 - KIT4M05872564MCF</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020650222 - KIT4M05413790XCD</t>
         </is>
       </c>
       <c r="C335" s="3" t="n">
@@ -18248,12 +18248,12 @@
       </c>
       <c r="E335" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872564MCF</t>
+          <t>KIT4M05413790XCD</t>
         </is>
       </c>
       <c r="F335" s="4" t="inlineStr">
         <is>
-          <t>816203</t>
+          <t>812822</t>
         </is>
       </c>
       <c r="G335" s="5" t="inlineStr">
@@ -18290,7 +18290,7 @@
       </c>
       <c r="B336" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 021437852 - KIT4M0587257292W</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437702 - KIT4M05872515PJT</t>
         </is>
       </c>
       <c r="C336" s="3" t="n">
@@ -18301,12 +18301,12 @@
       </c>
       <c r="E336" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0587257292W</t>
+          <t>KIT4M05872515PJT</t>
         </is>
       </c>
       <c r="F336" s="4" t="inlineStr">
         <is>
-          <t>816207</t>
+          <t>816218</t>
         </is>
       </c>
       <c r="G336" s="5" t="inlineStr">
@@ -18343,7 +18343,7 @@
       </c>
       <c r="B337" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064917936NF</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438052 - KIT4M05872522W7W</t>
         </is>
       </c>
       <c r="C337" s="3" t="n">
@@ -18354,12 +18354,12 @@
       </c>
       <c r="E337" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064917936NF</t>
+          <t>KIT4M05872522W7W</t>
         </is>
       </c>
       <c r="F337" s="4" t="inlineStr">
         <is>
-          <t>816404</t>
+          <t>816217</t>
         </is>
       </c>
       <c r="G337" s="5" t="inlineStr">
@@ -18396,7 +18396,7 @@
       </c>
       <c r="B338" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918068FF</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438272 - KIT4M05872517VS2</t>
         </is>
       </c>
       <c r="C338" s="3" t="n">
@@ -18407,12 +18407,12 @@
       </c>
       <c r="E338" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918068FF</t>
+          <t>KIT4M05872517VS2</t>
         </is>
       </c>
       <c r="F338" s="4" t="inlineStr">
         <is>
-          <t>816400</t>
+          <t>816288</t>
         </is>
       </c>
       <c r="G338" s="5" t="inlineStr">
@@ -18449,7 +18449,7 @@
       </c>
       <c r="B339" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020650222 - KIT4M05413790XCD</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649382 - KIT4M05368219KRH</t>
         </is>
       </c>
       <c r="C339" s="3" t="n">
@@ -18460,12 +18460,12 @@
       </c>
       <c r="E339" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413790XCD</t>
+          <t>KIT4M05368219KRH</t>
         </is>
       </c>
       <c r="F339" s="4" t="inlineStr">
         <is>
-          <t>812822</t>
+          <t>810646</t>
         </is>
       </c>
       <c r="G339" s="5" t="inlineStr">
@@ -18502,7 +18502,7 @@
       </c>
       <c r="B340" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649392 - KIT4M05368206BZP</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918068FF</t>
         </is>
       </c>
       <c r="C340" s="3" t="n">
@@ -18513,12 +18513,12 @@
       </c>
       <c r="E340" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368206BZP</t>
+          <t>KIT4M064918068FF</t>
         </is>
       </c>
       <c r="F340" s="4" t="inlineStr">
         <is>
-          <t>810645</t>
+          <t>816400</t>
         </is>
       </c>
       <c r="G340" s="5" t="inlineStr">
@@ -18661,7 +18661,7 @@
       </c>
       <c r="B343" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649232 - KIT4P0006563862J</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438102 - KIT4M05872513F7N</t>
         </is>
       </c>
       <c r="C343" s="3" t="n">
@@ -18672,17 +18672,17 @@
       </c>
       <c r="E343" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0006563862J</t>
+          <t>KIT4M05872513F7N</t>
         </is>
       </c>
       <c r="F343" s="4" t="inlineStr">
         <is>
-          <t>812927</t>
+          <t>816161</t>
         </is>
       </c>
       <c r="G343" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H343" s="5" t="inlineStr">
@@ -18714,7 +18714,7 @@
       </c>
       <c r="B344" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438102 - KIT4M05872513F7N</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649232 - KIT4P0006563862J</t>
         </is>
       </c>
       <c r="C344" s="3" t="n">
@@ -18725,17 +18725,17 @@
       </c>
       <c r="E344" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872513F7N</t>
+          <t>KIT4P0006563862J</t>
         </is>
       </c>
       <c r="F344" s="4" t="inlineStr">
         <is>
-          <t>816161</t>
+          <t>812927</t>
         </is>
       </c>
       <c r="G344" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H344" s="5" t="inlineStr">
@@ -18812,7 +18812,7 @@
       </c>
       <c r="B346" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955442 - KIT4M05563503XXP</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437922 - KIT4M05872496MW6</t>
         </is>
       </c>
       <c r="C346" s="3" t="n">
@@ -18823,12 +18823,12 @@
       </c>
       <c r="E346" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563503XXP</t>
+          <t>KIT4M05872496MW6</t>
         </is>
       </c>
       <c r="F346" s="4" t="inlineStr">
         <is>
-          <t>814430</t>
+          <t>816206</t>
         </is>
       </c>
       <c r="G346" s="5" t="inlineStr">
@@ -18918,7 +18918,7 @@
       </c>
       <c r="B348" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437922 - KIT4M05872496MW6</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649482 - KIT4M054137938P7</t>
         </is>
       </c>
       <c r="C348" s="3" t="n">
@@ -18929,12 +18929,12 @@
       </c>
       <c r="E348" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872496MW6</t>
+          <t>KIT4M054137938P7</t>
         </is>
       </c>
       <c r="F348" s="4" t="inlineStr">
         <is>
-          <t>816206</t>
+          <t>812848</t>
         </is>
       </c>
       <c r="G348" s="5" t="inlineStr">
@@ -18971,7 +18971,7 @@
       </c>
       <c r="B349" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955512 - KIT4M055635779MM</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955162 - KIT4M05563554WCW</t>
         </is>
       </c>
       <c r="C349" s="3" t="n">
@@ -18982,12 +18982,12 @@
       </c>
       <c r="E349" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635779MM</t>
+          <t>KIT4M05563554WCW</t>
         </is>
       </c>
       <c r="F349" s="4" t="inlineStr">
         <is>
-          <t>814487</t>
+          <t>814444</t>
         </is>
       </c>
       <c r="G349" s="5" t="inlineStr">
@@ -19024,7 +19024,7 @@
       </c>
       <c r="B350" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955162 - KIT4M05563554WCW</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827011116 - KIT4M02578775B9Q</t>
         </is>
       </c>
       <c r="C350" s="3" t="n">
@@ -19035,12 +19035,12 @@
       </c>
       <c r="E350" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563554WCW</t>
+          <t>KIT4M02578775B9Q</t>
         </is>
       </c>
       <c r="F350" s="4" t="inlineStr">
         <is>
-          <t>814444</t>
+          <t>809611</t>
         </is>
       </c>
       <c r="G350" s="5" t="inlineStr">
@@ -19077,7 +19077,7 @@
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 020955572 - KIT4M05563606ZRC</t>
+          <t>STS - 05900510 - Los Angeles CA - 020650092 - KIT4M05413830JN7</t>
         </is>
       </c>
       <c r="C351" s="3" t="n">
@@ -19088,12 +19088,12 @@
       </c>
       <c r="E351" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563606ZRC</t>
+          <t>KIT4M05413830JN7</t>
         </is>
       </c>
       <c r="F351" s="4" t="inlineStr">
         <is>
-          <t>814464</t>
+          <t>810105</t>
         </is>
       </c>
       <c r="G351" s="5" t="inlineStr">
@@ -19130,7 +19130,7 @@
       </c>
       <c r="B352" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955222 - KIT4M05563536BPJ</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649612 - KIT4M05413827DC4</t>
         </is>
       </c>
       <c r="C352" s="3" t="n">
@@ -19141,12 +19141,12 @@
       </c>
       <c r="E352" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563536BPJ</t>
+          <t>KIT4M05413827DC4</t>
         </is>
       </c>
       <c r="F352" s="4" t="inlineStr">
         <is>
-          <t>814466</t>
+          <t>812829</t>
         </is>
       </c>
       <c r="G352" s="5" t="inlineStr">
@@ -19183,7 +19183,7 @@
       </c>
       <c r="B353" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955562 - KIT4M05563505WPS</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955442 - KIT4M05563503XXP</t>
         </is>
       </c>
       <c r="C353" s="3" t="n">
@@ -19194,12 +19194,12 @@
       </c>
       <c r="E353" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563505WPS</t>
+          <t>KIT4M05563503XXP</t>
         </is>
       </c>
       <c r="F353" s="4" t="inlineStr">
         <is>
-          <t>814448</t>
+          <t>814430</t>
         </is>
       </c>
       <c r="G353" s="5" t="inlineStr">
@@ -19236,7 +19236,7 @@
       </c>
       <c r="B354" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 021437632 - KIT4M05872585HZZ</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955222 - KIT4M05563536BPJ</t>
         </is>
       </c>
       <c r="C354" s="3" t="n">
@@ -19247,12 +19247,12 @@
       </c>
       <c r="E354" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872585HZZ</t>
+          <t>KIT4M05563536BPJ</t>
         </is>
       </c>
       <c r="F354" s="4" t="inlineStr">
         <is>
-          <t>816211</t>
+          <t>814466</t>
         </is>
       </c>
       <c r="G354" s="5" t="inlineStr">
@@ -19289,7 +19289,7 @@
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649612 - KIT4M05413827DC4</t>
+          <t>USPS - 05900510 - Los Angeles CA - CW6892232 - KIT4P00084601T5F</t>
         </is>
       </c>
       <c r="C355" s="3" t="n">
@@ -19300,17 +19300,17 @@
       </c>
       <c r="E355" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413827DC4</t>
+          <t>KIT4P00084601T5F</t>
         </is>
       </c>
       <c r="F355" s="4" t="inlineStr">
         <is>
-          <t>812829</t>
+          <t>816335</t>
         </is>
       </c>
       <c r="G355" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H355" s="5" t="inlineStr">
@@ -19342,7 +19342,7 @@
       </c>
       <c r="B356" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020650092 - KIT4M05413830JN7</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955562 - KIT4M05563505WPS</t>
         </is>
       </c>
       <c r="C356" s="3" t="n">
@@ -19353,12 +19353,12 @@
       </c>
       <c r="E356" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413830JN7</t>
+          <t>KIT4M05563505WPS</t>
         </is>
       </c>
       <c r="F356" s="4" t="inlineStr">
         <is>
-          <t>810105</t>
+          <t>814448</t>
         </is>
       </c>
       <c r="G356" s="5" t="inlineStr">
@@ -19395,7 +19395,7 @@
       </c>
       <c r="B357" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649922 - KIT4M05413780XFH</t>
+          <t>SMA - 05900510 - Los Angeles CA - CW6892232 - KIT4P000832637V6</t>
         </is>
       </c>
       <c r="C357" s="3" t="n">
@@ -19406,17 +19406,17 @@
       </c>
       <c r="E357" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413780XFH</t>
+          <t>KIT4P000832637V6</t>
         </is>
       </c>
       <c r="F357" s="4" t="inlineStr">
         <is>
-          <t>812833</t>
+          <t>816334</t>
         </is>
       </c>
       <c r="G357" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H357" s="5" t="inlineStr">
@@ -19448,7 +19448,7 @@
       </c>
       <c r="B358" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020650032-KIT4M05413802FVN</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482701114 - KIT4M03476114VCM</t>
         </is>
       </c>
       <c r="C358" s="3" t="n">
@@ -19459,12 +19459,12 @@
       </c>
       <c r="E358" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413802FVN</t>
+          <t>KIT4M03476114VCM</t>
         </is>
       </c>
       <c r="F358" s="4" t="inlineStr">
         <is>
-          <t>812813</t>
+          <t>809613</t>
         </is>
       </c>
       <c r="G358" s="5" t="inlineStr">
@@ -19501,7 +19501,7 @@
       </c>
       <c r="B359" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649482 - KIT4M054137938P7</t>
+          <t>SMRT-05900510-Los Angeles CA-020650032-KIT4M05413802FVN</t>
         </is>
       </c>
       <c r="C359" s="3" t="n">
@@ -19512,12 +19512,12 @@
       </c>
       <c r="E359" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137938P7</t>
+          <t>KIT4M05413802FVN</t>
         </is>
       </c>
       <c r="F359" s="4" t="inlineStr">
         <is>
-          <t>812848</t>
+          <t>812813</t>
         </is>
       </c>
       <c r="G359" s="5" t="inlineStr">
@@ -19554,7 +19554,7 @@
       </c>
       <c r="B360" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649502 - KIT4M05413801QJB</t>
+          <t>SS - 05900510 -  Los Angeles CA - 020955572 - KIT4M05563606ZRC</t>
         </is>
       </c>
       <c r="C360" s="3" t="n">
@@ -19565,12 +19565,12 @@
       </c>
       <c r="E360" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413801QJB</t>
+          <t>KIT4M05563606ZRC</t>
         </is>
       </c>
       <c r="F360" s="4" t="inlineStr">
         <is>
-          <t>812824</t>
+          <t>814464</t>
         </is>
       </c>
       <c r="G360" s="5" t="inlineStr">
@@ -19607,7 +19607,7 @@
       </c>
       <c r="B361" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020649662 - KIT4M05413772977</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649952 - KIT4M05413782GHW</t>
         </is>
       </c>
       <c r="C361" s="3" t="n">
@@ -19618,12 +19618,12 @@
       </c>
       <c r="E361" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413772977</t>
+          <t>KIT4M05413782GHW</t>
         </is>
       </c>
       <c r="F361" s="4" t="inlineStr">
         <is>
-          <t>812841</t>
+          <t>812835</t>
         </is>
       </c>
       <c r="G361" s="5" t="inlineStr">
@@ -19660,7 +19660,7 @@
       </c>
       <c r="B362" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649802 - KIT4M04604734ZZX</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649922 - KIT4M05413780XFH</t>
         </is>
       </c>
       <c r="C362" s="3" t="n">
@@ -19671,12 +19671,12 @@
       </c>
       <c r="E362" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604734ZZX</t>
+          <t>KIT4M05413780XFH</t>
         </is>
       </c>
       <c r="F362" s="4" t="inlineStr">
         <is>
-          <t>809876</t>
+          <t>812833</t>
         </is>
       </c>
       <c r="G362" s="5" t="inlineStr">
@@ -19713,7 +19713,7 @@
       </c>
       <c r="B363" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649952 - KIT4M05413782GHW</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955512 - KIT4M055635779MM</t>
         </is>
       </c>
       <c r="C363" s="3" t="n">
@@ -19724,12 +19724,12 @@
       </c>
       <c r="E363" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413782GHW</t>
+          <t>KIT4M055635779MM</t>
         </is>
       </c>
       <c r="F363" s="4" t="inlineStr">
         <is>
-          <t>812835</t>
+          <t>814487</t>
         </is>
       </c>
       <c r="G363" s="5" t="inlineStr">
@@ -19766,7 +19766,7 @@
       </c>
       <c r="B364" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649332 - KIT4M05368340DMZ</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649502 - KIT4M05413801QJB</t>
         </is>
       </c>
       <c r="C364" s="3" t="n">
@@ -19777,12 +19777,12 @@
       </c>
       <c r="E364" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368340DMZ</t>
+          <t>KIT4M05413801QJB</t>
         </is>
       </c>
       <c r="F364" s="4" t="inlineStr">
         <is>
-          <t>810649</t>
+          <t>812824</t>
         </is>
       </c>
       <c r="G364" s="5" t="inlineStr">
@@ -19819,7 +19819,7 @@
       </c>
       <c r="B365" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020426432 - KIT4P00066070HN4</t>
+          <t>SS - 05900510 -  Los Angeles CA - 021437632 - KIT4M05872585HZZ</t>
         </is>
       </c>
       <c r="C365" s="3" t="n">
@@ -19830,17 +19830,17 @@
       </c>
       <c r="E365" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00066070HN4</t>
+          <t>KIT4M05872585HZZ</t>
         </is>
       </c>
       <c r="F365" s="4" t="inlineStr">
         <is>
-          <t>807636</t>
+          <t>816211</t>
         </is>
       </c>
       <c r="G365" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H365" s="5" t="inlineStr">
@@ -19872,7 +19872,7 @@
       </c>
       <c r="B366" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491835TD6</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020649662 - KIT4M05413772977</t>
         </is>
       </c>
       <c r="C366" s="3" t="n">
@@ -19883,12 +19883,12 @@
       </c>
       <c r="E366" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491835TD6</t>
+          <t>KIT4M05413772977</t>
         </is>
       </c>
       <c r="F366" s="4" t="inlineStr">
         <is>
-          <t>816401</t>
+          <t>812841</t>
         </is>
       </c>
       <c r="G366" s="5" t="inlineStr">
@@ -19925,7 +19925,7 @@
       </c>
       <c r="B367" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482701114 - KIT4M03476114VCM</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649332 - KIT4M05368340DMZ</t>
         </is>
       </c>
       <c r="C367" s="3" t="n">
@@ -19936,12 +19936,12 @@
       </c>
       <c r="E367" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03476114VCM</t>
+          <t>KIT4M05368340DMZ</t>
         </is>
       </c>
       <c r="F367" s="4" t="inlineStr">
         <is>
-          <t>809613</t>
+          <t>810649</t>
         </is>
       </c>
       <c r="G367" s="5" t="inlineStr">
@@ -19978,7 +19978,7 @@
       </c>
       <c r="B368" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827011116 - KIT4M02578775B9Q</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491835TD6</t>
         </is>
       </c>
       <c r="C368" s="3" t="n">
@@ -19989,12 +19989,12 @@
       </c>
       <c r="E368" s="2" t="inlineStr">
         <is>
-          <t>KIT4M02578775B9Q</t>
+          <t>KIT4M06491835TD6</t>
         </is>
       </c>
       <c r="F368" s="4" t="inlineStr">
         <is>
-          <t>809611</t>
+          <t>816401</t>
         </is>
       </c>
       <c r="G368" s="5" t="inlineStr">
@@ -20024,101 +20024,207 @@
       </c>
     </row>
     <row r="369">
-      <c r="A369" s="9" t="inlineStr">
+      <c r="A369" s="2" t="inlineStr">
+        <is>
+          <t>SmartSource</t>
+        </is>
+      </c>
+      <c r="B369" s="2" t="inlineStr">
+        <is>
+          <t>SS - 05900510 - Los Angeles CA - 020649802 - KIT4M04604734ZZX</t>
+        </is>
+      </c>
+      <c r="C369" s="3" t="n">
+        <v>5900464</v>
+      </c>
+      <c r="D369" s="3" t="n">
+        <v>5900510</v>
+      </c>
+      <c r="E369" s="2" t="inlineStr">
+        <is>
+          <t>KIT4M04604734ZZX</t>
+        </is>
+      </c>
+      <c r="F369" s="4" t="inlineStr">
+        <is>
+          <t>809876</t>
+        </is>
+      </c>
+      <c r="G369" s="5" t="inlineStr">
+        <is>
+          <t>Mini</t>
+        </is>
+      </c>
+      <c r="H369" s="5" t="inlineStr">
+        <is>
+          <t>Master Serial List</t>
+        </is>
+      </c>
+      <c r="I369" s="6" t="n">
+        <v>46235</v>
+      </c>
+      <c r="J369" s="6" t="n">
+        <v>46266</v>
+      </c>
+      <c r="K369" s="5" t="inlineStr">
+        <is>
+          <t>50 GB</t>
+        </is>
+      </c>
+      <c r="L369" s="5" t="n"/>
+      <c r="M369" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="2" t="inlineStr">
+        <is>
+          <t>SmartSource</t>
+        </is>
+      </c>
+      <c r="B370" s="2" t="inlineStr">
+        <is>
+          <t>SMA - 05900510 - Los Angeles CA - 020426432 - KIT4P00066070HN4</t>
+        </is>
+      </c>
+      <c r="C370" s="3" t="n">
+        <v>5900464</v>
+      </c>
+      <c r="D370" s="3" t="n">
+        <v>5900510</v>
+      </c>
+      <c r="E370" s="2" t="inlineStr">
+        <is>
+          <t>KIT4P00066070HN4</t>
+        </is>
+      </c>
+      <c r="F370" s="4" t="inlineStr">
+        <is>
+          <t>807636</t>
+        </is>
+      </c>
+      <c r="G370" s="5" t="inlineStr">
+        <is>
+          <t>G3 HPERF</t>
+        </is>
+      </c>
+      <c r="H370" s="5" t="inlineStr">
+        <is>
+          <t>Master Serial List</t>
+        </is>
+      </c>
+      <c r="I370" s="6" t="n">
+        <v>46235</v>
+      </c>
+      <c r="J370" s="6" t="n">
+        <v>46266</v>
+      </c>
+      <c r="K370" s="5" t="inlineStr">
+        <is>
+          <t>50 GB</t>
+        </is>
+      </c>
+      <c r="L370" s="5" t="n"/>
+      <c r="M370" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="9" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B369" s="9" t="n"/>
-      <c r="C369" s="9" t="n"/>
-      <c r="D369" s="9" t="n"/>
-      <c r="E369" s="9" t="n"/>
-      <c r="F369" s="10">
-        <f>COUNTA(F2:F368)&amp;" mapped"</f>
+      <c r="B371" s="9" t="n"/>
+      <c r="C371" s="9" t="n"/>
+      <c r="D371" s="9" t="n"/>
+      <c r="E371" s="9" t="n"/>
+      <c r="F371" s="10">
+        <f>COUNTA(F2:F370)&amp;" mapped"</f>
         <v/>
       </c>
-      <c r="G369" s="9" t="n"/>
-      <c r="H369" s="9" t="n"/>
-      <c r="I369" s="9" t="n"/>
-      <c r="J369" s="9" t="n"/>
-      <c r="K369" s="11">
-        <f>COUNTIF(K2:K368,"50 GB")*50</f>
+      <c r="G371" s="9" t="n"/>
+      <c r="H371" s="9" t="n"/>
+      <c r="I371" s="9" t="n"/>
+      <c r="J371" s="9" t="n"/>
+      <c r="K371" s="11">
+        <f>COUNTIF(K2:K370,"50 GB")*50</f>
         <v/>
       </c>
-      <c r="L369" s="12">
-        <f>COUNTA(E2:E368)&amp;" kits"</f>
+      <c r="L371" s="12">
+        <f>COUNTA(E2:E370)&amp;" kits"</f>
         <v/>
       </c>
-      <c r="M369" s="13">
-        <f>SUM(M2:M368)</f>
+      <c r="M371" s="13">
+        <f>SUM(M2:M370)</f>
         <v/>
       </c>
     </row>
-    <row r="371">
-      <c r="A371" s="14" t="inlineStr">
+    <row r="373">
+      <c r="A373" s="14" t="inlineStr">
         <is>
           <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="372">
-      <c r="A372" s="15" t="inlineStr">
-        <is>
-          <t>One row per kit, deduplicated to each kit's most recent billing period.</t>
-        </is>
-      </c>
-    </row>
-    <row r="373">
-      <c r="A373" s="15" t="inlineStr">
-        <is>
-          <t>Ecode resolved from the Master Serial Number list, and from the Main Tracker when present.</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="15" t="inlineStr">
         <is>
-          <t>Ecode Source names which file supplied each code. Shaded cells have no code in either.</t>
+          <t>One row per kit, deduplicated to each kit's most recent billing period.</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="15" t="inlineStr">
         <is>
-          <t>The master list spells one kit with an extra character; it is corrected on read.</t>
+          <t>Ecode resolved from the Master Serial Number list, and from the Main Tracker when present.</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" s="15" t="inlineStr">
         <is>
-          <t>Plan Amount is set to 50 GB for every kit - all kits pool at 50 GB regardless of the export.</t>
+          <t>Ecode Source names which file supplied each code. Shaded cells have no code in either.</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="15" t="inlineStr">
         <is>
-          <t>Model is derived from the kit serial prefix: KIT4M = Mini, KIT4P = G3 HPERF.</t>
+          <t>The master list spells one kit with an extra character; it is corrected on read.</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" s="15" t="inlineStr">
         <is>
-          <t>Totals are stored in GB and display in TB past 1,000 GB (decimal, 1 TB = 1,000 GB).</t>
+          <t>Plan Amount is set to 50 GB for every kit - all kits pool at 50 GB regardless of the export.</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="15" t="inlineStr">
         <is>
-          <t>Generated 2026-08-27 14:27 by build_starlink_usage.py</t>
+          <t>Model is derived from the kit serial prefix: KIT4M = Mini, KIT4P = G3 HPERF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="15" t="inlineStr">
+        <is>
+          <t>Totals are stored in GB and display in TB past 1,000 GB (decimal, 1 TB = 1,000 GB).</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="15" t="inlineStr">
+        <is>
+          <t>Generated 2026-08-28 10:37 by build_starlink_usage.py</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M368"/>
+  <autoFilter ref="A1:M370"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Starlink_Usage_Current_by_Kit.xlsx
+++ b/Starlink_Usage_Current_by_Kit.xlsx
@@ -20219,7 +20219,7 @@
     <row r="381">
       <c r="A381" s="15" t="inlineStr">
         <is>
-          <t>Generated 2026-08-28 10:37 by build_starlink_usage.py</t>
+          <t>Generated 2026-08-28 12:01 by build_starlink_usage.py</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_Current_by_Kit.xlsx
+++ b/Starlink_Usage_Current_by_Kit.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="L3" s="5" t="n"/>
       <c r="M3" s="7" t="n">
-        <v>2262.88</v>
+        <v>2263.71</v>
       </c>
     </row>
     <row r="4">
@@ -842,7 +842,7 @@
       </c>
       <c r="L6" s="5" t="n"/>
       <c r="M6" s="7" t="n">
-        <v>1082.84</v>
+        <v>1097.27</v>
       </c>
     </row>
     <row r="7">
@@ -906,7 +906,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 021437242 - KIT4P00083890S2G</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437292 - KIT4P000832806P4</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
@@ -917,12 +917,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00083890S2G</t>
+          <t>KIT4P000832806P4</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>816226</t>
+          <t>816228</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="L8" s="5" t="n"/>
       <c r="M8" s="7" t="n">
-        <v>817.62</v>
+        <v>840.1799999999999</v>
       </c>
     </row>
     <row r="9">
@@ -959,7 +959,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437292 - KIT4P000832806P4</t>
+          <t>SMRT-05900510-Los Angeles CA-021437282-KIT4P00084593R9F</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
@@ -970,12 +970,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>KIT4P000832806P4</t>
+          <t>KIT4P00084593R9F</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>816228</t>
+          <t>816227</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="L9" s="5" t="n"/>
       <c r="M9" s="7" t="n">
-        <v>798.09</v>
+        <v>831.15</v>
       </c>
     </row>
     <row r="10">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437282-KIT4P00084593R9F</t>
+          <t>SS - 05900510 - Los Angeles, CA - 021437242 - KIT4P00083890S2G</t>
         </is>
       </c>
       <c r="C10" s="3" t="n">
@@ -1023,12 +1023,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00084593R9F</t>
+          <t>KIT4P00083890S2G</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>816227</t>
+          <t>816226</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="L10" s="5" t="n"/>
       <c r="M10" s="7" t="n">
-        <v>795.22</v>
+        <v>817.62</v>
       </c>
     </row>
     <row r="11">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270111116 - KIT4P00065612DJF</t>
+          <t>SMAR-05900510-Los Angeles CA-020426442-KIT4P00065630DZT</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065612DJF</t>
+          <t>KIT4P00065630DZT</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>809605</t>
+          <t>807635</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="L13" s="5" t="n"/>
       <c r="M13" s="7" t="n">
-        <v>716.11</v>
+        <v>728</v>
       </c>
     </row>
     <row r="14">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>SMAR-05900510-Los Angeles CA-020426442-KIT4P00065630DZT</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270111116 - KIT4P00065612DJF</t>
         </is>
       </c>
       <c r="C14" s="3" t="n">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065630DZT</t>
+          <t>KIT4P00065612DJF</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>807635</t>
+          <t>809605</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L14" s="5" t="n"/>
       <c r="M14" s="7" t="n">
-        <v>708.66</v>
+        <v>723.16</v>
       </c>
     </row>
     <row r="15">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955192 - KIT4M05563510TWC</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955102 - KIT4P000739257CR</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
@@ -1288,17 +1288,17 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563510TWC</t>
+          <t>KIT4P000739257CR</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>814433</t>
+          <t>814609</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="L15" s="5" t="n"/>
       <c r="M15" s="7" t="n">
-        <v>650.1799999999999</v>
+        <v>660.9299999999999</v>
       </c>
     </row>
     <row r="16">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955102 - KIT4P000739257CR</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955192 - KIT4M05563510TWC</t>
         </is>
       </c>
       <c r="C16" s="3" t="n">
@@ -1341,17 +1341,17 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>KIT4P000739257CR</t>
+          <t>KIT4M05563510TWC</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>814609</t>
+          <t>814433</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="L16" s="5" t="n"/>
       <c r="M16" s="7" t="n">
-        <v>643.77</v>
+        <v>660.7</v>
       </c>
     </row>
     <row r="17">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020649622 - KIT4M05413794SSC</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955052 - KIT4P00073152MPN</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413794SSC</t>
+          <t>KIT4P00073152MPN</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>812847</t>
+          <t>814494</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="L18" s="5" t="n"/>
       <c r="M18" s="7" t="n">
-        <v>476.04</v>
+        <v>498.72</v>
       </c>
     </row>
     <row r="19">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955052 - KIT4P00073152MPN</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020649622 - KIT4M05413794SSC</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
@@ -1500,17 +1500,17 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073152MPN</t>
+          <t>KIT4M05413794SSC</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>814494</t>
+          <t>812847</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="L19" s="5" t="n"/>
       <c r="M19" s="7" t="n">
-        <v>463.21</v>
+        <v>476.04</v>
       </c>
     </row>
     <row r="20">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="L21" s="5" t="n"/>
       <c r="M21" s="7" t="n">
-        <v>413.14</v>
+        <v>419.85</v>
       </c>
     </row>
     <row r="22">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="L27" s="5" t="n"/>
       <c r="M27" s="7" t="n">
-        <v>271.13</v>
+        <v>272.4</v>
       </c>
     </row>
     <row r="28">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="L28" s="5" t="n"/>
       <c r="M28" s="7" t="n">
-        <v>253.57</v>
+        <v>254</v>
       </c>
     </row>
     <row r="29">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482701110 - KIT4M041546939GJ</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437422 - KIT4M05872536JFD</t>
         </is>
       </c>
       <c r="C30" s="3" t="n">
@@ -2083,12 +2083,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>KIT4M041546939GJ</t>
+          <t>KIT4M05872536JFD</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>809607</t>
+          <t>816070</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="L30" s="5" t="n"/>
       <c r="M30" s="7" t="n">
-        <v>246.3</v>
+        <v>248.24</v>
       </c>
     </row>
     <row r="31">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437422 - KIT4M05872536JFD</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482701110 - KIT4M041546939GJ</t>
         </is>
       </c>
       <c r="C31" s="3" t="n">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872536JFD</t>
+          <t>KIT4M041546939GJ</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>816070</t>
+          <t>809607</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="L31" s="5" t="n"/>
       <c r="M31" s="7" t="n">
-        <v>222.58</v>
+        <v>246.3</v>
       </c>
     </row>
     <row r="32">
@@ -2178,7 +2178,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020649462-KIT4M05413796V9K</t>
+          <t>SMRT-05900510-LOS ANGELES CA-020955062-KIT4P00073915XX6</t>
         </is>
       </c>
       <c r="C32" s="3" t="n">
@@ -2189,17 +2189,17 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413796V9K</t>
+          <t>KIT4P00073915XX6</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>812820</t>
+          <t>814643</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="L32" s="5" t="n"/>
       <c r="M32" s="7" t="n">
-        <v>220.94</v>
+        <v>223.01</v>
       </c>
     </row>
     <row r="33">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-LOS ANGELES CA-020955062-KIT4P00073915XX6</t>
+          <t>SMRT-05900510-Los Angeles CA-020649462-KIT4M05413796V9K</t>
         </is>
       </c>
       <c r="C33" s="3" t="n">
@@ -2242,17 +2242,17 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073915XX6</t>
+          <t>KIT4M05413796V9K</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>814643</t>
+          <t>812820</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="L33" s="5" t="n"/>
       <c r="M33" s="7" t="n">
-        <v>214.46</v>
+        <v>220.94</v>
       </c>
     </row>
     <row r="34">
@@ -2326,7 +2326,7 @@
       </c>
       <c r="L34" s="5" t="n"/>
       <c r="M34" s="7" t="n">
-        <v>205.17</v>
+        <v>211.17</v>
       </c>
     </row>
     <row r="35">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="L35" s="5" t="n"/>
       <c r="M35" s="7" t="n">
-        <v>157.27</v>
+        <v>163.04</v>
       </c>
     </row>
     <row r="36">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="L36" s="5" t="n"/>
       <c r="M36" s="7" t="n">
-        <v>150.01</v>
+        <v>157.15</v>
       </c>
     </row>
     <row r="37">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649352 - KIT4M05368220FG8</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482701116 - KIT4M03986275Q4M</t>
         </is>
       </c>
       <c r="C37" s="3" t="n">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368220FG8</t>
+          <t>KIT4M03986275Q4M</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>810648</t>
+          <t>809621</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="L37" s="5" t="n"/>
       <c r="M37" s="7" t="n">
-        <v>128.41</v>
+        <v>143.69</v>
       </c>
     </row>
     <row r="38">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955682 - KIT4M055635887MK</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955522 - KIT4M05563504MBB</t>
         </is>
       </c>
       <c r="C38" s="3" t="n">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635887MK</t>
+          <t>KIT4M05563504MBB</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>814446</t>
+          <t>814460</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="L38" s="5" t="n"/>
       <c r="M38" s="7" t="n">
-        <v>126.61</v>
+        <v>139.55</v>
       </c>
     </row>
     <row r="39">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 -  Los Angeles CA - 020649422 - KIT4M05368200MVF</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649352 - KIT4M05368220FG8</t>
         </is>
       </c>
       <c r="C39" s="3" t="n">
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368200MVF</t>
+          <t>KIT4M05368220FG8</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>810650</t>
+          <t>810648</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="L39" s="5" t="n"/>
       <c r="M39" s="7" t="n">
-        <v>126.59</v>
+        <v>137.86</v>
       </c>
     </row>
     <row r="40">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955672 - KIT4M055635979XD</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955682 - KIT4M055635887MK</t>
         </is>
       </c>
       <c r="C40" s="3" t="n">
@@ -2613,12 +2613,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635979XD</t>
+          <t>KIT4M055635887MK</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>814441</t>
+          <t>814446</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="L40" s="5" t="n"/>
       <c r="M40" s="7" t="n">
-        <v>126.18</v>
+        <v>132.23</v>
       </c>
     </row>
     <row r="41">
@@ -2655,7 +2655,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955522 - KIT4M05563504MBB</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955672 - KIT4M055635979XD</t>
         </is>
       </c>
       <c r="C41" s="3" t="n">
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563504MBB</t>
+          <t>KIT4M055635979XD</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>814460</t>
+          <t>814441</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="L41" s="5" t="n"/>
       <c r="M41" s="7" t="n">
-        <v>121.77</v>
+        <v>127.97</v>
       </c>
     </row>
     <row r="42">
@@ -2708,7 +2708,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649842 - KIT4M025787739XF</t>
+          <t>SMA - 05900510 -  Los Angeles CA - 020649422 - KIT4M05368200MVF</t>
         </is>
       </c>
       <c r="C42" s="3" t="n">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>KIT4M025787739XF</t>
+          <t>KIT4M05368200MVF</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>809864</t>
+          <t>810650</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="L42" s="5" t="n"/>
       <c r="M42" s="7" t="n">
-        <v>121.62</v>
+        <v>126.59</v>
       </c>
     </row>
     <row r="43">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437252 - KIT4P00083897XCW</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649842 - KIT4M025787739XF</t>
         </is>
       </c>
       <c r="C43" s="3" t="n">
@@ -2772,17 +2772,17 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00083897XCW</t>
+          <t>KIT4M025787739XF</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>816223</t>
+          <t>809864</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="L43" s="5" t="n"/>
       <c r="M43" s="7" t="n">
-        <v>120.74</v>
+        <v>124.46</v>
       </c>
     </row>
     <row r="44">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482701116 - KIT4M03986275Q4M</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955632 - KIT4M055635329VD</t>
         </is>
       </c>
       <c r="C44" s="3" t="n">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03986275Q4M</t>
+          <t>KIT4M055635329VD</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>809621</t>
+          <t>814479</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="L44" s="5" t="n"/>
       <c r="M44" s="7" t="n">
-        <v>119.88</v>
+        <v>124.25</v>
       </c>
     </row>
     <row r="45">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020955622 - KIT4M05563549RSR</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827014 - KIT4M04475149XG5</t>
         </is>
       </c>
       <c r="C45" s="3" t="n">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563549RSR</t>
+          <t>KIT4M04475149XG5</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>814483</t>
+          <t>809657</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="L45" s="5" t="n"/>
       <c r="M45" s="7" t="n">
-        <v>113.16</v>
+        <v>121.29</v>
       </c>
     </row>
     <row r="46">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955632 - KIT4M055635329VD</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437252 - KIT4P00083897XCW</t>
         </is>
       </c>
       <c r="C46" s="3" t="n">
@@ -2931,17 +2931,17 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635329VD</t>
+          <t>KIT4P00083897XCW</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>814479</t>
+          <t>816223</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H46" s="5" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="L46" s="5" t="n"/>
       <c r="M46" s="7" t="n">
-        <v>111.47</v>
+        <v>120.74</v>
       </c>
     </row>
     <row r="47">
@@ -2973,7 +2973,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649542 - KIT4M05413810Q4Z</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955182 - KIT4M05563562F45</t>
         </is>
       </c>
       <c r="C47" s="3" t="n">
@@ -2984,12 +2984,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413810Q4Z</t>
+          <t>KIT4M05563562F45</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>812815</t>
+          <t>814443</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="L47" s="5" t="n"/>
       <c r="M47" s="7" t="n">
-        <v>109.69</v>
+        <v>117.66</v>
       </c>
     </row>
     <row r="48">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles, CA-020955372-KIT4M05563537G4G</t>
+          <t>SS - 05900510 - Los Angeles CA - CW6578840- KIT4M04475128THH</t>
         </is>
       </c>
       <c r="C48" s="3" t="n">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563537G4G</t>
+          <t>KIT4M04475128THH</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>814456</t>
+          <t>809860</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="L48" s="5" t="n"/>
       <c r="M48" s="7" t="n">
-        <v>108.22</v>
+        <v>116.56</v>
       </c>
     </row>
     <row r="49">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020650172 - KIT4M05413811F4Q</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020955622 - KIT4M05563549RSR</t>
         </is>
       </c>
       <c r="C49" s="3" t="n">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413811F4Q</t>
+          <t>KIT4M05563549RSR</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>810104</t>
+          <t>814483</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="L49" s="5" t="n"/>
       <c r="M49" s="7" t="n">
-        <v>99.37</v>
+        <v>113.16</v>
       </c>
     </row>
     <row r="50">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270111110 - KIT4M03867737P9P</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649542 - KIT4M05413810Q4Z</t>
         </is>
       </c>
       <c r="C50" s="3" t="n">
@@ -3143,12 +3143,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03867737P9P</t>
+          <t>KIT4M05413810Q4Z</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>809622</t>
+          <t>812815</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="L50" s="5" t="n"/>
       <c r="M50" s="7" t="n">
-        <v>99.18000000000001</v>
+        <v>109.7</v>
       </c>
     </row>
     <row r="51">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827014 - KIT4M04475149XG5</t>
+          <t>SMRT-05900510-Los Angeles, CA-020955372-KIT4M05563537G4G</t>
         </is>
       </c>
       <c r="C51" s="3" t="n">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475149XG5</t>
+          <t>KIT4M05563537G4G</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>809657</t>
+          <t>814456</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="L51" s="5" t="n"/>
       <c r="M51" s="7" t="n">
-        <v>98.89</v>
+        <v>108.22</v>
       </c>
     </row>
     <row r="52">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - CW6578840- KIT4M04475128THH</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270111110 - KIT4M03867737P9P</t>
         </is>
       </c>
       <c r="C52" s="3" t="n">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475128THH</t>
+          <t>KIT4M03867737P9P</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>809860</t>
+          <t>809622</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="L52" s="5" t="n"/>
       <c r="M52" s="7" t="n">
-        <v>97.45999999999999</v>
+        <v>102.98</v>
       </c>
     </row>
     <row r="53">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020650212 - KIT4M05413779VSD</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020650172 - KIT4M05413811F4Q</t>
         </is>
       </c>
       <c r="C53" s="3" t="n">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413779VSD</t>
+          <t>KIT4M05413811F4Q</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>810103</t>
+          <t>810104</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="L53" s="5" t="n"/>
       <c r="M53" s="7" t="n">
-        <v>96.01000000000001</v>
+        <v>99.37</v>
       </c>
     </row>
     <row r="54">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438042 - KIT4M05799686CMX</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020650212 - KIT4M05413779VSD</t>
         </is>
       </c>
       <c r="C54" s="3" t="n">
@@ -3355,12 +3355,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799686CMX</t>
+          <t>KIT4M05413779VSD</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>816282</t>
+          <t>810103</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="L54" s="5" t="n"/>
       <c r="M54" s="7" t="n">
-        <v>94.92</v>
+        <v>97.69</v>
       </c>
     </row>
     <row r="55">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="L55" s="5" t="n"/>
       <c r="M55" s="7" t="n">
-        <v>93.91</v>
+        <v>96.63</v>
       </c>
     </row>
     <row r="56">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020650232 - KIT4M054138222CP</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438042 - KIT4M05799686CMX</t>
         </is>
       </c>
       <c r="C56" s="3" t="n">
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138222CP</t>
+          <t>KIT4M05799686CMX</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>812811</t>
+          <t>816282</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="L56" s="5" t="n"/>
       <c r="M56" s="7" t="n">
-        <v>93.27</v>
+        <v>94.92</v>
       </c>
     </row>
     <row r="57">
@@ -3503,7 +3503,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955662 - KIT4M05563574ZBN</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020650232 - KIT4M054138222CP</t>
         </is>
       </c>
       <c r="C57" s="3" t="n">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563574ZBN</t>
+          <t>KIT4M054138222CP</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>814453</t>
+          <t>812811</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="L57" s="5" t="n"/>
       <c r="M57" s="7" t="n">
-        <v>91.48999999999999</v>
+        <v>93.27</v>
       </c>
     </row>
     <row r="58">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955472 - KIT4M055635834N7</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955662 - KIT4M05563574ZBN</t>
         </is>
       </c>
       <c r="C58" s="3" t="n">
@@ -3567,12 +3567,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635834N7</t>
+          <t>KIT4M05563574ZBN</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>814462</t>
+          <t>814453</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="L58" s="5" t="n"/>
       <c r="M58" s="7" t="n">
-        <v>89.20999999999999</v>
+        <v>91.91</v>
       </c>
     </row>
     <row r="59">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955182 - KIT4M05563562F45</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955472 - KIT4M055635834N7</t>
         </is>
       </c>
       <c r="C59" s="3" t="n">
@@ -3620,12 +3620,12 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563562F45</t>
+          <t>KIT4M055635834N7</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>814443</t>
+          <t>814462</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
@@ -3651,7 +3651,7 @@
       </c>
       <c r="L59" s="5" t="n"/>
       <c r="M59" s="7" t="n">
-        <v>89.04000000000001</v>
+        <v>89.20999999999999</v>
       </c>
     </row>
     <row r="60">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955142 - KIT4M05563518ZJD</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649782 - KIT4M03986264P49</t>
         </is>
       </c>
       <c r="C60" s="3" t="n">
@@ -3673,12 +3673,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563518ZJD</t>
+          <t>KIT4M03986264P49</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>814451</t>
+          <t>809875</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="L60" s="5" t="n"/>
       <c r="M60" s="7" t="n">
-        <v>85.18000000000001</v>
+        <v>86.77</v>
       </c>
     </row>
     <row r="61">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649872 - KIT4M054138175VJ</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955142 - KIT4M05563518ZJD</t>
         </is>
       </c>
       <c r="C61" s="3" t="n">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138175VJ</t>
+          <t>KIT4M05563518ZJD</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>812823</t>
+          <t>814451</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
@@ -3757,7 +3757,7 @@
       </c>
       <c r="L61" s="5" t="n"/>
       <c r="M61" s="7" t="n">
-        <v>83.95</v>
+        <v>85.18000000000001</v>
       </c>
     </row>
     <row r="62">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649782 - KIT4M03986264P49</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649872 - KIT4M054138175VJ</t>
         </is>
       </c>
       <c r="C62" s="3" t="n">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03986264P49</t>
+          <t>KIT4M054138175VJ</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>809875</t>
+          <t>812823</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="L62" s="5" t="n"/>
       <c r="M62" s="7" t="n">
-        <v>81.95</v>
+        <v>83.95</v>
       </c>
     </row>
     <row r="63">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="L63" s="5" t="n"/>
       <c r="M63" s="7" t="n">
-        <v>81.76000000000001</v>
+        <v>81.84999999999999</v>
       </c>
     </row>
     <row r="64">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649562 - KIT4M054138125NW</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649712 - KIT4M046047397TM</t>
         </is>
       </c>
       <c r="C64" s="3" t="n">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138125NW</t>
+          <t>KIT4M046047397TM</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>812826</t>
+          <t>809863</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="L64" s="5" t="n"/>
       <c r="M64" s="7" t="n">
-        <v>75.87</v>
+        <v>80.01000000000001</v>
       </c>
     </row>
     <row r="65">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="L65" s="5" t="n"/>
       <c r="M65" s="7" t="n">
-        <v>74.87</v>
+        <v>78.69</v>
       </c>
     </row>
     <row r="66">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955492 - KIT4M05563520SH2</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955112 - KIT4P00073918HBX</t>
         </is>
       </c>
       <c r="C66" s="3" t="n">
@@ -3991,17 +3991,17 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563520SH2</t>
+          <t>KIT4P00073918HBX</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>814478</t>
+          <t>814645</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H66" s="5" t="inlineStr">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="L66" s="5" t="n"/>
       <c r="M66" s="7" t="n">
-        <v>74.56999999999999</v>
+        <v>77.8</v>
       </c>
     </row>
     <row r="67">
@@ -4033,7 +4033,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955092 - KIT4P00073957GV5</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649562 - KIT4M054138125NW</t>
         </is>
       </c>
       <c r="C67" s="3" t="n">
@@ -4044,17 +4044,17 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073957GV5</t>
+          <t>KIT4M054138125NW</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>814642</t>
+          <t>812826</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H67" s="5" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="L67" s="5" t="n"/>
       <c r="M67" s="7" t="n">
-        <v>72.83</v>
+        <v>77.14</v>
       </c>
     </row>
     <row r="68">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955112 - KIT4P00073918HBX</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020650012 - KIT4M05413814GPJ</t>
         </is>
       </c>
       <c r="C68" s="3" t="n">
@@ -4097,17 +4097,17 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073918HBX</t>
+          <t>KIT4M05413814GPJ</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>814645</t>
+          <t>812812</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H68" s="5" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="L68" s="5" t="n"/>
       <c r="M68" s="7" t="n">
-        <v>69.8</v>
+        <v>75.04000000000001</v>
       </c>
     </row>
     <row r="69">
@@ -4139,7 +4139,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020650012 - KIT4M05413814GPJ</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955492 - KIT4M05563520SH2</t>
         </is>
       </c>
       <c r="C69" s="3" t="n">
@@ -4150,12 +4150,12 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413814GPJ</t>
+          <t>KIT4M05563520SH2</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>812812</t>
+          <t>814478</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="L69" s="5" t="n"/>
       <c r="M69" s="7" t="n">
-        <v>69.54000000000001</v>
+        <v>74.56999999999999</v>
       </c>
     </row>
     <row r="70">
@@ -4192,7 +4192,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649272 - KIT4M05413784W4K</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955092 - KIT4P00073957GV5</t>
         </is>
       </c>
       <c r="C70" s="3" t="n">
@@ -4203,17 +4203,17 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413784W4K</t>
+          <t>KIT4P00073957GV5</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>812821</t>
+          <t>814642</t>
         </is>
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H70" s="5" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="L70" s="5" t="n"/>
       <c r="M70" s="7" t="n">
-        <v>69.13</v>
+        <v>72.83</v>
       </c>
     </row>
     <row r="71">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649712 - KIT4M046047397TM</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438092 - KIT4M05799694RW2</t>
         </is>
       </c>
       <c r="C71" s="3" t="n">
@@ -4256,12 +4256,12 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047397TM</t>
+          <t>KIT4M05799694RW2</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>809863</t>
+          <t>816277</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
@@ -4287,7 +4287,7 @@
       </c>
       <c r="L71" s="5" t="n"/>
       <c r="M71" s="7" t="n">
-        <v>66.16</v>
+        <v>71.98999999999999</v>
       </c>
     </row>
     <row r="72">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="L72" s="5" t="n"/>
       <c r="M72" s="7" t="n">
-        <v>65.58</v>
+        <v>70.05</v>
       </c>
     </row>
     <row r="73">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SS - 05900510 - Los Angeles, CA - 020649552 - KIT4M05413835RPF </t>
+          <t>SS - 05900510 - Los Angeles CA - 020955132 - KIT4M055635238J6</t>
         </is>
       </c>
       <c r="C73" s="3" t="n">
@@ -4362,12 +4362,12 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413835RPF</t>
+          <t>KIT4M055635238J6</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>812827</t>
+          <t>814449</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="L73" s="5" t="n"/>
       <c r="M73" s="7" t="n">
-        <v>64.22</v>
+        <v>69.94</v>
       </c>
     </row>
     <row r="74">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955132 - KIT4M055635238J6</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649272 - KIT4M05413784W4K</t>
         </is>
       </c>
       <c r="C74" s="3" t="n">
@@ -4415,12 +4415,12 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635238J6</t>
+          <t>KIT4M05413784W4K</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>814449</t>
+          <t>812821</t>
         </is>
       </c>
       <c r="G74" s="5" t="inlineStr">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="L74" s="5" t="n"/>
       <c r="M74" s="7" t="n">
-        <v>61.97</v>
+        <v>69.13</v>
       </c>
     </row>
     <row r="75">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020650252 - KIT4M05413820QXJ</t>
+          <t xml:space="preserve">SS - 05900510 - Los Angeles, CA - 020649552 - KIT4M05413835RPF </t>
         </is>
       </c>
       <c r="C75" s="3" t="n">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413820QXJ</t>
+          <t>KIT4M05413835RPF</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>810098</t>
+          <t>812827</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="L75" s="5" t="n"/>
       <c r="M75" s="7" t="n">
-        <v>61.69</v>
+        <v>65.87</v>
       </c>
     </row>
     <row r="76">
@@ -4552,7 +4552,7 @@
       </c>
       <c r="L76" s="5" t="n"/>
       <c r="M76" s="7" t="n">
-        <v>61.35</v>
+        <v>62.51</v>
       </c>
     </row>
     <row r="77">
@@ -4563,7 +4563,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438092 - KIT4M05799694RW2</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020650252 - KIT4M05413820QXJ</t>
         </is>
       </c>
       <c r="C77" s="3" t="n">
@@ -4574,12 +4574,12 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799694RW2</t>
+          <t>KIT4M05413820QXJ</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>816277</t>
+          <t>810098</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr">
@@ -4605,7 +4605,7 @@
       </c>
       <c r="L77" s="5" t="n"/>
       <c r="M77" s="7" t="n">
-        <v>61.15</v>
+        <v>61.69</v>
       </c>
     </row>
     <row r="78">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482702 - KIT4M04604743HSS</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955292 - KIT4M05563531XSB</t>
         </is>
       </c>
       <c r="C78" s="3" t="n">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604743HSS</t>
+          <t>KIT4M05563531XSB</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>809663</t>
+          <t>814469</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="L78" s="5" t="n"/>
       <c r="M78" s="7" t="n">
-        <v>59.03</v>
+        <v>59.97</v>
       </c>
     </row>
     <row r="79">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="L79" s="5" t="n"/>
       <c r="M79" s="7" t="n">
-        <v>58.35</v>
+        <v>59.45</v>
       </c>
     </row>
     <row r="80">
@@ -4722,7 +4722,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649932 - KIT4M054138324MW</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482702 - KIT4M04604743HSS</t>
         </is>
       </c>
       <c r="C80" s="3" t="n">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138324MW</t>
+          <t>KIT4M04604743HSS</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>812834</t>
+          <t>809663</t>
         </is>
       </c>
       <c r="G80" s="5" t="inlineStr">
@@ -4764,7 +4764,7 @@
       </c>
       <c r="L80" s="5" t="n"/>
       <c r="M80" s="7" t="n">
-        <v>57.51</v>
+        <v>59.03</v>
       </c>
     </row>
     <row r="81">
@@ -4775,7 +4775,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482704 - KIT4M04604745G8Z</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955262 - KIT4M05563521ZSX</t>
         </is>
       </c>
       <c r="C81" s="3" t="n">
@@ -4786,12 +4786,12 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604745G8Z</t>
+          <t>KIT4M05563521ZSX</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>809661</t>
+          <t>814476</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="L81" s="5" t="n"/>
       <c r="M81" s="7" t="n">
-        <v>57.14</v>
+        <v>58.47</v>
       </c>
     </row>
     <row r="82">
@@ -4828,7 +4828,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955292 - KIT4M05563531XSB</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649932 - KIT4M054138324MW</t>
         </is>
       </c>
       <c r="C82" s="3" t="n">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563531XSB</t>
+          <t>KIT4M054138324MW</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>814469</t>
+          <t>812834</t>
         </is>
       </c>
       <c r="G82" s="5" t="inlineStr">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="L82" s="5" t="n"/>
       <c r="M82" s="7" t="n">
-        <v>56.35</v>
+        <v>58.27</v>
       </c>
     </row>
     <row r="83">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955262 - KIT4M05563521ZSX</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482704 - KIT4M04604745G8Z</t>
         </is>
       </c>
       <c r="C83" s="3" t="n">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563521ZSX</t>
+          <t>KIT4M04604745G8Z</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>814476</t>
+          <t>809661</t>
         </is>
       </c>
       <c r="G83" s="5" t="inlineStr">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="L83" s="5" t="n"/>
       <c r="M83" s="7" t="n">
-        <v>53.82</v>
+        <v>57.14</v>
       </c>
     </row>
     <row r="84">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="L84" s="5" t="n"/>
       <c r="M84" s="7" t="n">
-        <v>53.22</v>
+        <v>54.27</v>
       </c>
     </row>
     <row r="85">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649762 - KIT4M0460475549Z</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827011118 - KIT4M03867766NGK</t>
         </is>
       </c>
       <c r="C85" s="3" t="n">
@@ -4998,12 +4998,12 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0460475549Z</t>
+          <t>KIT4M03867766NGK</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>809859</t>
+          <t>809615</t>
         </is>
       </c>
       <c r="G85" s="5" t="inlineStr">
@@ -5029,7 +5029,7 @@
       </c>
       <c r="L85" s="5" t="n"/>
       <c r="M85" s="7" t="n">
-        <v>53.03</v>
+        <v>54.21</v>
       </c>
     </row>
     <row r="86">
@@ -5040,7 +5040,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827011118 - KIT4M03867766NGK</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649762 - KIT4M0460475549Z</t>
         </is>
       </c>
       <c r="C86" s="3" t="n">
@@ -5051,12 +5051,12 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03867766NGK</t>
+          <t>KIT4M0460475549Z</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>809615</t>
+          <t>809859</t>
         </is>
       </c>
       <c r="G86" s="5" t="inlineStr">
@@ -5082,7 +5082,7 @@
       </c>
       <c r="L86" s="5" t="n"/>
       <c r="M86" s="7" t="n">
-        <v>52.85</v>
+        <v>53.03</v>
       </c>
     </row>
     <row r="87">
@@ -5093,7 +5093,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020650142 - KIT4M05413839D24</t>
+          <t>SMRT-05900510-Los Angeles, CA-020955582-KIT4M05563593DMC</t>
         </is>
       </c>
       <c r="C87" s="3" t="n">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413839D24</t>
+          <t>KIT4M05563593DMC</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>810096</t>
+          <t>814442</t>
         </is>
       </c>
       <c r="G87" s="5" t="inlineStr">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="L87" s="5" t="n"/>
       <c r="M87" s="7" t="n">
-        <v>50.33</v>
+        <v>51.97</v>
       </c>
     </row>
     <row r="88">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270111114 - KIT4P00065593VWC</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270112 - KIT4M044751638F5</t>
         </is>
       </c>
       <c r="C88" s="3" t="n">
@@ -5157,17 +5157,17 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065593VWC</t>
+          <t>KIT4M044751638F5</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>809606</t>
+          <t>809618</t>
         </is>
       </c>
       <c r="G88" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H88" s="5" t="inlineStr">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="L88" s="5" t="n"/>
       <c r="M88" s="7" t="n">
-        <v>49.23</v>
+        <v>50.81</v>
       </c>
     </row>
     <row r="89">
@@ -5199,7 +5199,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-LOS ANGELES CA-020955202-KIT4M05563534GZ7</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955692 - KIT4M05563603CP4</t>
         </is>
       </c>
       <c r="C89" s="3" t="n">
@@ -5210,12 +5210,12 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563534GZ7</t>
+          <t>KIT4M05563603CP4</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>814467</t>
+          <t>814447</t>
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr">
@@ -5241,7 +5241,7 @@
       </c>
       <c r="L89" s="5" t="n"/>
       <c r="M89" s="7" t="n">
-        <v>49.16</v>
+        <v>50.38</v>
       </c>
     </row>
     <row r="90">
@@ -5252,7 +5252,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955692 - KIT4M05563603CP4</t>
+          <t>SMRT-05900510-LOS ANGELES CA-020955202-KIT4M05563534GZ7</t>
         </is>
       </c>
       <c r="C90" s="3" t="n">
@@ -5263,12 +5263,12 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563603CP4</t>
+          <t>KIT4M05563534GZ7</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>814447</t>
+          <t>814467</t>
         </is>
       </c>
       <c r="G90" s="5" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="L90" s="5" t="n"/>
       <c r="M90" s="7" t="n">
-        <v>48.93</v>
+        <v>50.34</v>
       </c>
     </row>
     <row r="91">
@@ -5305,7 +5305,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270112 - KIT4M044751638F5</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020650142 - KIT4M05413839D24</t>
         </is>
       </c>
       <c r="C91" s="3" t="n">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>KIT4M044751638F5</t>
+          <t>KIT4M05413839D24</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>809618</t>
+          <t>810096</t>
         </is>
       </c>
       <c r="G91" s="5" t="inlineStr">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="L91" s="5" t="n"/>
       <c r="M91" s="7" t="n">
-        <v>48.76</v>
+        <v>50.33</v>
       </c>
     </row>
     <row r="92">
@@ -5358,7 +5358,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles, CA - 0204827011112 - KIT4M04158967K28</t>
+          <t>SMRT-05900510-Los Angeles, CA-020955352-KIT4M05563525VC6</t>
         </is>
       </c>
       <c r="C92" s="3" t="n">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158967K28</t>
+          <t>KIT4M05563525VC6</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>809620</t>
+          <t>814458</t>
         </is>
       </c>
       <c r="G92" s="5" t="inlineStr">
@@ -5400,7 +5400,7 @@
       </c>
       <c r="L92" s="5" t="n"/>
       <c r="M92" s="7" t="n">
-        <v>47.81</v>
+        <v>50.03</v>
       </c>
     </row>
     <row r="93">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles, CA-020955582-KIT4M05563593DMC</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649372 - KIT4M05368221HQ5</t>
         </is>
       </c>
       <c r="C93" s="3" t="n">
@@ -5422,12 +5422,12 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563593DMC</t>
+          <t>KIT4M05368221HQ5</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>814442</t>
+          <t>810834</t>
         </is>
       </c>
       <c r="G93" s="5" t="inlineStr">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="L93" s="5" t="n"/>
       <c r="M93" s="7" t="n">
-        <v>47.67</v>
+        <v>49.71</v>
       </c>
     </row>
     <row r="94">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles, CA-020955352-KIT4M05563525VC6</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270111114 - KIT4P00065593VWC</t>
         </is>
       </c>
       <c r="C94" s="3" t="n">
@@ -5475,17 +5475,17 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563525VC6</t>
+          <t>KIT4P00065593VWC</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>814458</t>
+          <t>809606</t>
         </is>
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H94" s="5" t="inlineStr">
@@ -5506,7 +5506,7 @@
       </c>
       <c r="L94" s="5" t="n"/>
       <c r="M94" s="7" t="n">
-        <v>47.21</v>
+        <v>49.23</v>
       </c>
     </row>
     <row r="95">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649672 - KIT4M04606113TPB</t>
+          <t>STS - 05900510 - Los Angeles, CA - 0204827011112 - KIT4M04158967K28</t>
         </is>
       </c>
       <c r="C95" s="3" t="n">
@@ -5528,12 +5528,12 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04606113TPB</t>
+          <t>KIT4M04158967K28</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>809862</t>
+          <t>809620</t>
         </is>
       </c>
       <c r="G95" s="5" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="L95" s="5" t="n"/>
       <c r="M95" s="7" t="n">
-        <v>46.74</v>
+        <v>48.06</v>
       </c>
     </row>
     <row r="96">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles, CA-020955452-KIT4M05563529K2D</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955692 - KIT4M05563579H9F</t>
         </is>
       </c>
       <c r="C96" s="3" t="n">
@@ -5581,12 +5581,12 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563529K2D</t>
+          <t>KIT4M05563579H9F</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>814473</t>
+          <t>814480</t>
         </is>
       </c>
       <c r="G96" s="5" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="L96" s="5" t="n"/>
       <c r="M96" s="7" t="n">
-        <v>46.2</v>
+        <v>47.42</v>
       </c>
     </row>
     <row r="97">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437392 - KIT4M05872555BJR</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649672 - KIT4M04606113TPB</t>
         </is>
       </c>
       <c r="C97" s="3" t="n">
@@ -5634,12 +5634,12 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872555BJR</t>
+          <t>KIT4M04606113TPB</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>816074</t>
+          <t>809862</t>
         </is>
       </c>
       <c r="G97" s="5" t="inlineStr">
@@ -5665,7 +5665,7 @@
       </c>
       <c r="L97" s="5" t="n"/>
       <c r="M97" s="7" t="n">
-        <v>45.06</v>
+        <v>46.74</v>
       </c>
     </row>
     <row r="98">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649372 - KIT4M05368221HQ5</t>
+          <t>SMRT-05900510-Los Angeles, CA-020955452-KIT4M05563529K2D</t>
         </is>
       </c>
       <c r="C98" s="3" t="n">
@@ -5687,12 +5687,12 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368221HQ5</t>
+          <t>KIT4M05563529K2D</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>810834</t>
+          <t>814473</t>
         </is>
       </c>
       <c r="G98" s="5" t="inlineStr">
@@ -5718,7 +5718,7 @@
       </c>
       <c r="L98" s="5" t="n"/>
       <c r="M98" s="7" t="n">
-        <v>44.83</v>
+        <v>46.61</v>
       </c>
     </row>
     <row r="99">
@@ -5729,7 +5729,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649812 - KIT4M04604742S6S</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437392 - KIT4M05872555BJR</t>
         </is>
       </c>
       <c r="C99" s="3" t="n">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604742S6S</t>
+          <t>KIT4M05872555BJR</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>809874</t>
+          <t>816074</t>
         </is>
       </c>
       <c r="G99" s="5" t="inlineStr">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="L99" s="5" t="n"/>
       <c r="M99" s="7" t="n">
-        <v>43.24</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="100">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955692 - KIT4M05563579H9F</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827016 - KIT4M041536494G6</t>
         </is>
       </c>
       <c r="C100" s="3" t="n">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563579H9F</t>
+          <t>KIT4M041536494G6</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>814480</t>
+          <t>809617</t>
         </is>
       </c>
       <c r="G100" s="5" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="L100" s="5" t="n"/>
       <c r="M100" s="7" t="n">
-        <v>43.15</v>
+        <v>43.4</v>
       </c>
     </row>
     <row r="101">
@@ -5835,7 +5835,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649432 - KIT4M05413778RBR</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649812 - KIT4M04604742S6S</t>
         </is>
       </c>
       <c r="C101" s="3" t="n">
@@ -5846,12 +5846,12 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413778RBR</t>
+          <t>KIT4M04604742S6S</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>812843</t>
+          <t>809874</t>
         </is>
       </c>
       <c r="G101" s="5" t="inlineStr">
@@ -5877,7 +5877,7 @@
       </c>
       <c r="L101" s="5" t="n"/>
       <c r="M101" s="7" t="n">
-        <v>42.82</v>
+        <v>43.24</v>
       </c>
     </row>
     <row r="102">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020650192 - KIT4M054138007JF</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020955462 - KIT4M05563513GTF</t>
         </is>
       </c>
       <c r="C102" s="3" t="n">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138007JF</t>
+          <t>KIT4M05563513GTF</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>810095</t>
+          <t>814432</t>
         </is>
       </c>
       <c r="G102" s="5" t="inlineStr">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="L102" s="5" t="n"/>
       <c r="M102" s="7" t="n">
-        <v>42.59</v>
+        <v>43.23</v>
       </c>
     </row>
     <row r="103">
@@ -5941,7 +5941,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020650052 - KIT4M05413781K6C</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955702 - KIT4M05563571G8W</t>
         </is>
       </c>
       <c r="C103" s="3" t="n">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413781K6C</t>
+          <t>KIT4M05563571G8W</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>812798</t>
+          <t>814481</t>
         </is>
       </c>
       <c r="G103" s="5" t="inlineStr">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="L103" s="5" t="n"/>
       <c r="M103" s="7" t="n">
-        <v>42.04</v>
+        <v>42.83</v>
       </c>
     </row>
     <row r="104">
@@ -5994,7 +5994,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955702 - KIT4M05563571G8W</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649432 - KIT4M05413778RBR</t>
         </is>
       </c>
       <c r="C104" s="3" t="n">
@@ -6005,12 +6005,12 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563571G8W</t>
+          <t>KIT4M05413778RBR</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>814481</t>
+          <t>812843</t>
         </is>
       </c>
       <c r="G104" s="5" t="inlineStr">
@@ -6036,7 +6036,7 @@
       </c>
       <c r="L104" s="5" t="n"/>
       <c r="M104" s="7" t="n">
-        <v>41.94</v>
+        <v>42.82</v>
       </c>
     </row>
     <row r="105">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270116 - KIT4M03476116F45</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020650192 - KIT4M054138007JF</t>
         </is>
       </c>
       <c r="C105" s="3" t="n">
@@ -6058,12 +6058,12 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03476116F45</t>
+          <t>KIT4M054138007JF</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>809608</t>
+          <t>810095</t>
         </is>
       </c>
       <c r="G105" s="5" t="inlineStr">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="L105" s="5" t="n"/>
       <c r="M105" s="7" t="n">
-        <v>40.11</v>
+        <v>42.59</v>
       </c>
     </row>
     <row r="106">
@@ -6100,7 +6100,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020955652 - KIT4M0556358988Z</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020650052 - KIT4M05413781K6C</t>
         </is>
       </c>
       <c r="C106" s="3" t="n">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0556358988Z</t>
+          <t>KIT4M05413781K6C</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>814484</t>
+          <t>812798</t>
         </is>
       </c>
       <c r="G106" s="5" t="inlineStr">
@@ -6142,7 +6142,7 @@
       </c>
       <c r="L106" s="5" t="n"/>
       <c r="M106" s="7" t="n">
-        <v>40.07</v>
+        <v>42.04</v>
       </c>
     </row>
     <row r="107">
@@ -6153,7 +6153,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020650202-KIT4M05413803FDK</t>
+          <t>SS - 05900510 - Los Angeles CA - 020650042 - KIT4M05413819JV5</t>
         </is>
       </c>
       <c r="C107" s="3" t="n">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413803FDK</t>
+          <t>KIT4M05413819JV5</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>812850</t>
+          <t>812796</t>
         </is>
       </c>
       <c r="G107" s="5" t="inlineStr">
@@ -6195,7 +6195,7 @@
       </c>
       <c r="L107" s="5" t="n"/>
       <c r="M107" s="7" t="n">
-        <v>39.74</v>
+        <v>41.96</v>
       </c>
     </row>
     <row r="108">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 020955382 - KIT4M05563509CHJ</t>
+          <t>SMRT-05900510-Los Angeles CA-020650202-KIT4M05413803FDK</t>
         </is>
       </c>
       <c r="C108" s="3" t="n">
@@ -6217,12 +6217,12 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563509CHJ</t>
+          <t>KIT4M05413803FDK</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>814431</t>
+          <t>812850</t>
         </is>
       </c>
       <c r="G108" s="5" t="inlineStr">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="L108" s="5" t="n"/>
       <c r="M108" s="7" t="n">
-        <v>38.57</v>
+        <v>41.35</v>
       </c>
     </row>
     <row r="109">
@@ -6259,7 +6259,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020650042 - KIT4M05413819JV5</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270116 - KIT4M03476116F45</t>
         </is>
       </c>
       <c r="C109" s="3" t="n">
@@ -6270,12 +6270,12 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413819JV5</t>
+          <t>KIT4M03476116F45</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>812796</t>
+          <t>809608</t>
         </is>
       </c>
       <c r="G109" s="5" t="inlineStr">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="L109" s="5" t="n"/>
       <c r="M109" s="7" t="n">
-        <v>38.18</v>
+        <v>40.47</v>
       </c>
     </row>
     <row r="110">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955602 - KIT4M05563560225</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020955652 - KIT4M0556358988Z</t>
         </is>
       </c>
       <c r="C110" s="3" t="n">
@@ -6323,12 +6323,12 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563560225</t>
+          <t>KIT4M0556358988Z</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>814454</t>
+          <t>814484</t>
         </is>
       </c>
       <c r="G110" s="5" t="inlineStr">
@@ -6354,7 +6354,7 @@
       </c>
       <c r="L110" s="5" t="n"/>
       <c r="M110" s="7" t="n">
-        <v>38.09</v>
+        <v>40.07</v>
       </c>
     </row>
     <row r="111">
@@ -6365,7 +6365,7 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020650082 - KIT4M05413792H8C</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649832 - KIT4M03866596RZG</t>
         </is>
       </c>
       <c r="C111" s="3" t="n">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413792H8C</t>
+          <t>KIT4M03866596RZG</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>812803</t>
+          <t>809869</t>
         </is>
       </c>
       <c r="G111" s="5" t="inlineStr">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="L111" s="5" t="n"/>
       <c r="M111" s="7" t="n">
-        <v>37.81</v>
+        <v>40</v>
       </c>
     </row>
     <row r="112">
@@ -6418,7 +6418,7 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955272 - KIT4M05563585TXM</t>
+          <t>SS - 05900510 -  Los Angeles CA - 020955382 - KIT4M05563509CHJ</t>
         </is>
       </c>
       <c r="C112" s="3" t="n">
@@ -6429,12 +6429,12 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563585TXM</t>
+          <t>KIT4M05563509CHJ</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>814475</t>
+          <t>814431</t>
         </is>
       </c>
       <c r="G112" s="5" t="inlineStr">
@@ -6460,7 +6460,7 @@
       </c>
       <c r="L112" s="5" t="n"/>
       <c r="M112" s="7" t="n">
-        <v>36.91</v>
+        <v>39.2</v>
       </c>
     </row>
     <row r="113">
@@ -6471,7 +6471,7 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827016 - KIT4M041536494G6</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955272 - KIT4M05563585TXM</t>
         </is>
       </c>
       <c r="C113" s="3" t="n">
@@ -6482,12 +6482,12 @@
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>KIT4M041536494G6</t>
+          <t>KIT4M05563585TXM</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>809617</t>
+          <t>814475</t>
         </is>
       </c>
       <c r="G113" s="5" t="inlineStr">
@@ -6513,7 +6513,7 @@
       </c>
       <c r="L113" s="5" t="n"/>
       <c r="M113" s="7" t="n">
-        <v>35.85</v>
+        <v>38.58</v>
       </c>
     </row>
     <row r="114">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649942 - KIT4M05413786BXC</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955602 - KIT4M05563560225</t>
         </is>
       </c>
       <c r="C114" s="3" t="n">
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413786BXC</t>
+          <t>KIT4M05563560225</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>812838</t>
+          <t>814454</t>
         </is>
       </c>
       <c r="G114" s="5" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="L114" s="5" t="n"/>
       <c r="M114" s="7" t="n">
-        <v>34.4</v>
+        <v>38.09</v>
       </c>
     </row>
     <row r="115">
@@ -6577,7 +6577,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020955462 - KIT4M05563513GTF</t>
+          <t>STS - 05900510 - Los Angeles CA - 020650082 - KIT4M05413792H8C</t>
         </is>
       </c>
       <c r="C115" s="3" t="n">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563513GTF</t>
+          <t>KIT4M05413792H8C</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>814432</t>
+          <t>812803</t>
         </is>
       </c>
       <c r="G115" s="5" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="L115" s="5" t="n"/>
       <c r="M115" s="7" t="n">
-        <v>34.21</v>
+        <v>37.81</v>
       </c>
     </row>
     <row r="116">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020650112 - KIT4M05413840D9J</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649212 - KIT4P00065633ZXC</t>
         </is>
       </c>
       <c r="C116" s="3" t="n">
@@ -6641,17 +6641,17 @@
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413840D9J</t>
+          <t>KIT4P00065633ZXC</t>
         </is>
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>810099</t>
+          <t>812922</t>
         </is>
       </c>
       <c r="G116" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H116" s="5" t="inlineStr">
@@ -6672,7 +6672,7 @@
       </c>
       <c r="L116" s="5" t="n"/>
       <c r="M116" s="7" t="n">
-        <v>33.91</v>
+        <v>36.03</v>
       </c>
     </row>
     <row r="117">
@@ -6683,7 +6683,7 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649412 - KIT4M05413769796</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649942 - KIT4M05413786BXC</t>
         </is>
       </c>
       <c r="C117" s="3" t="n">
@@ -6694,12 +6694,12 @@
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413769796</t>
+          <t>KIT4M05413786BXC</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>812839</t>
+          <t>812838</t>
         </is>
       </c>
       <c r="G117" s="5" t="inlineStr">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="L117" s="5" t="n"/>
       <c r="M117" s="7" t="n">
-        <v>32.57</v>
+        <v>34.4</v>
       </c>
     </row>
     <row r="118">
@@ -6736,7 +6736,7 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482706 - KIT4M04604744V6K</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020650112 - KIT4M05413840D9J</t>
         </is>
       </c>
       <c r="C118" s="3" t="n">
@@ -6747,12 +6747,12 @@
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604744V6K</t>
+          <t>KIT4M05413840D9J</t>
         </is>
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>809659</t>
+          <t>810099</t>
         </is>
       </c>
       <c r="G118" s="5" t="inlineStr">
@@ -6778,7 +6778,7 @@
       </c>
       <c r="L118" s="5" t="n"/>
       <c r="M118" s="7" t="n">
-        <v>31.38</v>
+        <v>34.35</v>
       </c>
     </row>
     <row r="119">
@@ -6789,7 +6789,7 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 6858375 - KIT4M05872512N5W</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649682 - KIT4M046047384RX</t>
         </is>
       </c>
       <c r="C119" s="3" t="n">
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872512N5W</t>
+          <t>KIT4M046047384RX</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>816077</t>
+          <t>809870</t>
         </is>
       </c>
       <c r="G119" s="5" t="inlineStr">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="L119" s="5" t="n"/>
       <c r="M119" s="7" t="n">
-        <v>29.42</v>
+        <v>32.62</v>
       </c>
     </row>
     <row r="120">
@@ -6842,7 +6842,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649682 - KIT4M046047384RX</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649412 - KIT4M05413769796</t>
         </is>
       </c>
       <c r="C120" s="3" t="n">
@@ -6853,12 +6853,12 @@
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047384RX</t>
+          <t>KIT4M05413769796</t>
         </is>
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t>809870</t>
+          <t>812839</t>
         </is>
       </c>
       <c r="G120" s="5" t="inlineStr">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="L120" s="5" t="n"/>
       <c r="M120" s="7" t="n">
-        <v>28.64</v>
+        <v>32.57</v>
       </c>
     </row>
     <row r="121">
@@ -6937,7 +6937,7 @@
       </c>
       <c r="L121" s="5" t="n"/>
       <c r="M121" s="7" t="n">
-        <v>28.34</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="122">
@@ -6948,7 +6948,7 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649212 - KIT4P00065633ZXC</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482706 - KIT4M04604744V6K</t>
         </is>
       </c>
       <c r="C122" s="3" t="n">
@@ -6959,17 +6959,17 @@
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065633ZXC</t>
+          <t>KIT4M04604744V6K</t>
         </is>
       </c>
       <c r="F122" s="4" t="inlineStr">
         <is>
-          <t>812922</t>
+          <t>809659</t>
         </is>
       </c>
       <c r="G122" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H122" s="5" t="inlineStr">
@@ -6990,7 +6990,7 @@
       </c>
       <c r="L122" s="5" t="n"/>
       <c r="M122" s="7" t="n">
-        <v>27.32</v>
+        <v>31.38</v>
       </c>
     </row>
     <row r="123">
@@ -7001,7 +7001,7 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649742 - KIT4M04350554X4Z</t>
+          <t>SS - 05900510 - Los Angeles CA - 6858375 - KIT4M05872512N5W</t>
         </is>
       </c>
       <c r="C123" s="3" t="n">
@@ -7012,12 +7012,12 @@
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04350554X4Z</t>
+          <t>KIT4M05872512N5W</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>809866</t>
+          <t>816077</t>
         </is>
       </c>
       <c r="G123" s="5" t="inlineStr">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="L123" s="5" t="n"/>
       <c r="M123" s="7" t="n">
-        <v>27.16</v>
+        <v>31.03</v>
       </c>
     </row>
     <row r="124">
@@ -7054,7 +7054,7 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649532 - KIT4M05413808FFZ</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437782 - KIT4M058724975J4</t>
         </is>
       </c>
       <c r="C124" s="3" t="n">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413808FFZ</t>
+          <t>KIT4M058724975J4</t>
         </is>
       </c>
       <c r="F124" s="4" t="inlineStr">
         <is>
-          <t>812828</t>
+          <t>816075</t>
         </is>
       </c>
       <c r="G124" s="5" t="inlineStr">
@@ -7096,7 +7096,7 @@
       </c>
       <c r="L124" s="5" t="n"/>
       <c r="M124" s="7" t="n">
-        <v>27.14</v>
+        <v>28.85</v>
       </c>
     </row>
     <row r="125">
@@ -7107,7 +7107,7 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955342 - KIT4M05563524MJ4</t>
+          <t>SS - 05900510 -  Los Angeles CA - 021437622 - KIT4M0587258755W</t>
         </is>
       </c>
       <c r="C125" s="3" t="n">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563524MJ4</t>
+          <t>KIT4M0587258755W</t>
         </is>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>814472</t>
+          <t>816187</t>
         </is>
       </c>
       <c r="G125" s="5" t="inlineStr">
@@ -7149,7 +7149,7 @@
       </c>
       <c r="L125" s="5" t="n"/>
       <c r="M125" s="7" t="n">
-        <v>26.26</v>
+        <v>28.71</v>
       </c>
     </row>
     <row r="126">
@@ -7160,7 +7160,7 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437782 - KIT4M058724975J4</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649742 - KIT4M04350554X4Z</t>
         </is>
       </c>
       <c r="C126" s="3" t="n">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058724975J4</t>
+          <t>KIT4M04350554X4Z</t>
         </is>
       </c>
       <c r="F126" s="4" t="inlineStr">
         <is>
-          <t>816075</t>
+          <t>809866</t>
         </is>
       </c>
       <c r="G126" s="5" t="inlineStr">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="L126" s="5" t="n"/>
       <c r="M126" s="7" t="n">
-        <v>26.05</v>
+        <v>27.16</v>
       </c>
     </row>
     <row r="127">
@@ -7213,7 +7213,7 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649362 - KIT4M05368336DBC</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649532 - KIT4M05413808FFZ</t>
         </is>
       </c>
       <c r="C127" s="3" t="n">
@@ -7224,12 +7224,12 @@
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368336DBC</t>
+          <t>KIT4M05413808FFZ</t>
         </is>
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>810831</t>
+          <t>812828</t>
         </is>
       </c>
       <c r="G127" s="5" t="inlineStr">
@@ -7255,7 +7255,7 @@
       </c>
       <c r="L127" s="5" t="n"/>
       <c r="M127" s="7" t="n">
-        <v>25.14</v>
+        <v>27.14</v>
       </c>
     </row>
     <row r="128">
@@ -7266,7 +7266,7 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 021437622 - KIT4M0587258755W</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437992 -  KIT4M05799663CPM</t>
         </is>
       </c>
       <c r="C128" s="3" t="n">
@@ -7277,12 +7277,12 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0587258755W</t>
+          <t>KIT4M05799663CPM</t>
         </is>
       </c>
       <c r="F128" s="4" t="inlineStr">
         <is>
-          <t>816187</t>
+          <t>816272</t>
         </is>
       </c>
       <c r="G128" s="5" t="inlineStr">
@@ -7308,7 +7308,7 @@
       </c>
       <c r="L128" s="5" t="n"/>
       <c r="M128" s="7" t="n">
-        <v>24.84</v>
+        <v>26.55</v>
       </c>
     </row>
     <row r="129">
@@ -7319,7 +7319,7 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955212 - KIT4M05563512GBQ</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955342 - KIT4M05563524MJ4</t>
         </is>
       </c>
       <c r="C129" s="3" t="n">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563512GBQ</t>
+          <t>KIT4M05563524MJ4</t>
         </is>
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>814435</t>
+          <t>814472</t>
         </is>
       </c>
       <c r="G129" s="5" t="inlineStr">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="L129" s="5" t="n"/>
       <c r="M129" s="7" t="n">
-        <v>24.55</v>
+        <v>26.26</v>
       </c>
     </row>
     <row r="130">
@@ -7414,7 +7414,7 @@
       </c>
       <c r="L130" s="5" t="n"/>
       <c r="M130" s="7" t="n">
-        <v>23.9</v>
+        <v>25.44</v>
       </c>
     </row>
     <row r="131">
@@ -7425,7 +7425,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649832 - KIT4M03866596RZG</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649362 - KIT4M05368336DBC</t>
         </is>
       </c>
       <c r="C131" s="3" t="n">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03866596RZG</t>
+          <t>KIT4M05368336DBC</t>
         </is>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>809869</t>
+          <t>810831</t>
         </is>
       </c>
       <c r="G131" s="5" t="inlineStr">
@@ -7467,7 +7467,7 @@
       </c>
       <c r="L131" s="5" t="n"/>
       <c r="M131" s="7" t="n">
-        <v>23.59</v>
+        <v>25.14</v>
       </c>
     </row>
     <row r="132">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="L132" s="5" t="n"/>
       <c r="M132" s="7" t="n">
-        <v>23.32</v>
+        <v>24.68</v>
       </c>
     </row>
     <row r="133">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020650162 - KIT4M05413837SMB</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955212 - KIT4M05563512GBQ</t>
         </is>
       </c>
       <c r="C133" s="3" t="n">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413837SMB</t>
+          <t>KIT4M05563512GBQ</t>
         </is>
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>810100</t>
+          <t>814435</t>
         </is>
       </c>
       <c r="G133" s="5" t="inlineStr">
@@ -7573,7 +7573,7 @@
       </c>
       <c r="L133" s="5" t="n"/>
       <c r="M133" s="7" t="n">
-        <v>23.32</v>
+        <v>24.55</v>
       </c>
     </row>
     <row r="134">
@@ -7626,7 +7626,7 @@
       </c>
       <c r="L134" s="5" t="n"/>
       <c r="M134" s="7" t="n">
-        <v>22.82</v>
+        <v>24.12</v>
       </c>
     </row>
     <row r="135">
@@ -7637,7 +7637,7 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020650242 - KIT4M05413804SKS</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020650162 - KIT4M05413837SMB</t>
         </is>
       </c>
       <c r="C135" s="3" t="n">
@@ -7648,12 +7648,12 @@
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413804SKS</t>
+          <t>KIT4M05413837SMB</t>
         </is>
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>810102</t>
+          <t>810100</t>
         </is>
       </c>
       <c r="G135" s="5" t="inlineStr">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="L135" s="5" t="n"/>
       <c r="M135" s="7" t="n">
-        <v>21.64</v>
+        <v>23.32</v>
       </c>
     </row>
     <row r="136">
@@ -7690,7 +7690,7 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020650132-KIT4M05413828PCT</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482701112 - KIT4M04158973M2C</t>
         </is>
       </c>
       <c r="C136" s="3" t="n">
@@ -7701,12 +7701,12 @@
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413828PCT</t>
+          <t>KIT4M04158973M2C</t>
         </is>
       </c>
       <c r="F136" s="4" t="inlineStr">
         <is>
-          <t>812799</t>
+          <t>809610</t>
         </is>
       </c>
       <c r="G136" s="5" t="inlineStr">
@@ -7732,7 +7732,7 @@
       </c>
       <c r="L136" s="5" t="n"/>
       <c r="M136" s="7" t="n">
-        <v>21.54</v>
+        <v>22.79</v>
       </c>
     </row>
     <row r="137">
@@ -7743,7 +7743,7 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482701112 - KIT4M04158973M2C</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438242 - KIT4M058725094XP</t>
         </is>
       </c>
       <c r="C137" s="3" t="n">
@@ -7754,12 +7754,12 @@
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158973M2C</t>
+          <t>KIT4M058725094XP</t>
         </is>
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>809610</t>
+          <t>816085</t>
         </is>
       </c>
       <c r="G137" s="5" t="inlineStr">
@@ -7785,7 +7785,7 @@
       </c>
       <c r="L137" s="5" t="n"/>
       <c r="M137" s="7" t="n">
-        <v>21.32</v>
+        <v>22.66</v>
       </c>
     </row>
     <row r="138">
@@ -7796,7 +7796,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-LOS ANGELES CA-020955172-KIT4M05563526WNC</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020650242 - KIT4M05413804SKS</t>
         </is>
       </c>
       <c r="C138" s="3" t="n">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563526WNC</t>
+          <t>KIT4M05413804SKS</t>
         </is>
       </c>
       <c r="F138" s="4" t="inlineStr">
         <is>
-          <t>814463</t>
+          <t>810102</t>
         </is>
       </c>
       <c r="G138" s="5" t="inlineStr">
@@ -7838,7 +7838,7 @@
       </c>
       <c r="L138" s="5" t="n"/>
       <c r="M138" s="7" t="n">
-        <v>21.16</v>
+        <v>21.81</v>
       </c>
     </row>
     <row r="139">
@@ -7849,7 +7849,7 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020650072-KIT4M054137987GJ</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955712 - KIT4M05563586ZTR</t>
         </is>
       </c>
       <c r="C139" s="3" t="n">
@@ -7860,12 +7860,12 @@
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137987GJ</t>
+          <t>KIT4M05563586ZTR</t>
         </is>
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>812795</t>
+          <t>814445</t>
         </is>
       </c>
       <c r="G139" s="5" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="L139" s="5" t="n"/>
       <c r="M139" s="7" t="n">
-        <v>20.74</v>
+        <v>21.78</v>
       </c>
     </row>
     <row r="140">
@@ -7902,7 +7902,7 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955712 - KIT4M05563586ZTR</t>
+          <t>SMRT-05900510-Los Angeles CA-020650132-KIT4M05413828PCT</t>
         </is>
       </c>
       <c r="C140" s="3" t="n">
@@ -7913,12 +7913,12 @@
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563586ZTR</t>
+          <t>KIT4M05413828PCT</t>
         </is>
       </c>
       <c r="F140" s="4" t="inlineStr">
         <is>
-          <t>814445</t>
+          <t>812799</t>
         </is>
       </c>
       <c r="G140" s="5" t="inlineStr">
@@ -7944,7 +7944,7 @@
       </c>
       <c r="L140" s="5" t="n"/>
       <c r="M140" s="7" t="n">
-        <v>20.15</v>
+        <v>21.54</v>
       </c>
     </row>
     <row r="141">
@@ -7955,7 +7955,7 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649222 - KIT4P00065640BFW</t>
+          <t>SMRT-05900510-LOS ANGELES CA-020955172-KIT4M05563526WNC</t>
         </is>
       </c>
       <c r="C141" s="3" t="n">
@@ -7966,17 +7966,17 @@
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065640BFW</t>
+          <t>KIT4M05563526WNC</t>
         </is>
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>812929</t>
+          <t>814463</t>
         </is>
       </c>
       <c r="G141" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H141" s="5" t="inlineStr">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="L141" s="5" t="n"/>
       <c r="M141" s="7" t="n">
-        <v>19.87</v>
+        <v>21.16</v>
       </c>
     </row>
     <row r="142">
@@ -8008,7 +8008,7 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955532 - KIT4M05563548P9Q</t>
+          <t>SMRT-05900510-Los Angeles CA-020650072-KIT4M054137987GJ</t>
         </is>
       </c>
       <c r="C142" s="3" t="n">
@@ -8019,12 +8019,12 @@
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563548P9Q</t>
+          <t>KIT4M054137987GJ</t>
         </is>
       </c>
       <c r="F142" s="4" t="inlineStr">
         <is>
-          <t>814468</t>
+          <t>812795</t>
         </is>
       </c>
       <c r="G142" s="5" t="inlineStr">
@@ -8050,7 +8050,7 @@
       </c>
       <c r="L142" s="5" t="n"/>
       <c r="M142" s="7" t="n">
-        <v>19.77</v>
+        <v>20.74</v>
       </c>
     </row>
     <row r="143">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649912 - KIT4M05413836KJC</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955532 - KIT4M05563548P9Q</t>
         </is>
       </c>
       <c r="C143" s="3" t="n">
@@ -8072,12 +8072,12 @@
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413836KJC</t>
+          <t>KIT4M05563548P9Q</t>
         </is>
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>810097</t>
+          <t>814468</t>
         </is>
       </c>
       <c r="G143" s="5" t="inlineStr">
@@ -8103,7 +8103,7 @@
       </c>
       <c r="L143" s="5" t="n"/>
       <c r="M143" s="7" t="n">
-        <v>19.73</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="144">
@@ -8114,7 +8114,7 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649302 - KIT4M05368226W57</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649452 - KIT4M05413785QCG</t>
         </is>
       </c>
       <c r="C144" s="3" t="n">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368226W57</t>
+          <t>KIT4M05413785QCG</t>
         </is>
       </c>
       <c r="F144" s="4" t="inlineStr">
         <is>
-          <t>810833</t>
+          <t>812806</t>
         </is>
       </c>
       <c r="G144" s="5" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="L144" s="5" t="n"/>
       <c r="M144" s="7" t="n">
-        <v>19.62</v>
+        <v>20.29</v>
       </c>
     </row>
     <row r="145">
@@ -8167,7 +8167,7 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437992 -  KIT4M05799663CPM</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649222 - KIT4P00065640BFW</t>
         </is>
       </c>
       <c r="C145" s="3" t="n">
@@ -8178,17 +8178,17 @@
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799663CPM</t>
+          <t>KIT4P00065640BFW</t>
         </is>
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>816272</t>
+          <t>812929</t>
         </is>
       </c>
       <c r="G145" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H145" s="5" t="inlineStr">
@@ -8209,7 +8209,7 @@
       </c>
       <c r="L145" s="5" t="n"/>
       <c r="M145" s="7" t="n">
-        <v>19.53</v>
+        <v>19.87</v>
       </c>
     </row>
     <row r="146">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649452 - KIT4M05413785QCG</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649912 - KIT4M05413836KJC</t>
         </is>
       </c>
       <c r="C146" s="3" t="n">
@@ -8231,12 +8231,12 @@
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413785QCG</t>
+          <t>KIT4M05413836KJC</t>
         </is>
       </c>
       <c r="F146" s="4" t="inlineStr">
         <is>
-          <t>812806</t>
+          <t>810097</t>
         </is>
       </c>
       <c r="G146" s="5" t="inlineStr">
@@ -8262,7 +8262,7 @@
       </c>
       <c r="L146" s="5" t="n"/>
       <c r="M146" s="7" t="n">
-        <v>19.27</v>
+        <v>19.73</v>
       </c>
     </row>
     <row r="147">
@@ -8273,7 +8273,7 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955282 - KIT4M055635227ZR</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649302 - KIT4M05368226W57</t>
         </is>
       </c>
       <c r="C147" s="3" t="n">
@@ -8284,12 +8284,12 @@
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635227ZR</t>
+          <t>KIT4M05368226W57</t>
         </is>
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>814482</t>
+          <t>810833</t>
         </is>
       </c>
       <c r="G147" s="5" t="inlineStr">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="L147" s="5" t="n"/>
       <c r="M147" s="7" t="n">
-        <v>19.17</v>
+        <v>19.62</v>
       </c>
     </row>
     <row r="148">
@@ -8368,7 +8368,7 @@
       </c>
       <c r="L148" s="5" t="n"/>
       <c r="M148" s="7" t="n">
-        <v>18.76</v>
+        <v>19.59</v>
       </c>
     </row>
     <row r="149">
@@ -8379,7 +8379,7 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA  - 020649722 - KIT4M04604747TPT</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955282 - KIT4M055635227ZR</t>
         </is>
       </c>
       <c r="C149" s="3" t="n">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604747TPT</t>
+          <t>KIT4M055635227ZR</t>
         </is>
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>809873</t>
+          <t>814482</t>
         </is>
       </c>
       <c r="G149" s="5" t="inlineStr">
@@ -8421,7 +8421,7 @@
       </c>
       <c r="L149" s="5" t="n"/>
       <c r="M149" s="7" t="n">
-        <v>18.44</v>
+        <v>19.17</v>
       </c>
     </row>
     <row r="150">
@@ -8432,7 +8432,7 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649632 - KIT4M054138064J9</t>
+          <t>SS - 05900510 - Los Angeles, CA  - 020649722 - KIT4M04604747TPT</t>
         </is>
       </c>
       <c r="C150" s="3" t="n">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138064J9</t>
+          <t>KIT4M04604747TPT</t>
         </is>
       </c>
       <c r="F150" s="4" t="inlineStr">
         <is>
-          <t>812844</t>
+          <t>809873</t>
         </is>
       </c>
       <c r="G150" s="5" t="inlineStr">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="L150" s="5" t="n"/>
       <c r="M150" s="7" t="n">
-        <v>17.18</v>
+        <v>18.44</v>
       </c>
     </row>
     <row r="151">
@@ -8485,7 +8485,7 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649592 - KIT4M05413787HHK</t>
+          <t>SS - 05900510 -  Los Angeles CA - 021438232 - KIT4M05872520QJM</t>
         </is>
       </c>
       <c r="C151" s="3" t="n">
@@ -8496,12 +8496,12 @@
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413787HHK</t>
+          <t>KIT4M05872520QJM</t>
         </is>
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>812809</t>
+          <t>816078</t>
         </is>
       </c>
       <c r="G151" s="5" t="inlineStr">
@@ -8527,7 +8527,7 @@
       </c>
       <c r="L151" s="5" t="n"/>
       <c r="M151" s="7" t="n">
-        <v>15.65</v>
+        <v>18.36</v>
       </c>
     </row>
     <row r="152">
@@ -8580,7 +8580,7 @@
       </c>
       <c r="L152" s="5" t="n"/>
       <c r="M152" s="7" t="n">
-        <v>15.63</v>
+        <v>18.21</v>
       </c>
     </row>
     <row r="153">
@@ -8591,7 +8591,7 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482708 - KIT4M04604736T7C</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438072 - KIT4M057996885ZV</t>
         </is>
       </c>
       <c r="C153" s="3" t="n">
@@ -8602,12 +8602,12 @@
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604736T7C</t>
+          <t>KIT4M057996885ZV</t>
         </is>
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>809662</t>
+          <t>816269</t>
         </is>
       </c>
       <c r="G153" s="5" t="inlineStr">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="L153" s="5" t="n"/>
       <c r="M153" s="7" t="n">
-        <v>15.63</v>
+        <v>17.3</v>
       </c>
     </row>
     <row r="154">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438072 - KIT4M057996885ZV</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649322 - KIT4M053683324KZ</t>
         </is>
       </c>
       <c r="C154" s="3" t="n">
@@ -8655,12 +8655,12 @@
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>KIT4M057996885ZV</t>
+          <t>KIT4M053683324KZ</t>
         </is>
       </c>
       <c r="F154" s="4" t="inlineStr">
         <is>
-          <t>816269</t>
+          <t>810832</t>
         </is>
       </c>
       <c r="G154" s="5" t="inlineStr">
@@ -8686,7 +8686,7 @@
       </c>
       <c r="L154" s="5" t="n"/>
       <c r="M154" s="7" t="n">
-        <v>15.2</v>
+        <v>17.29</v>
       </c>
     </row>
     <row r="155">
@@ -8697,7 +8697,7 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438222 - KIT4M058725299QP</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649632 - KIT4M054138064J9</t>
         </is>
       </c>
       <c r="C155" s="3" t="n">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725299QP</t>
+          <t>KIT4M054138064J9</t>
         </is>
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>816080</t>
+          <t>812844</t>
         </is>
       </c>
       <c r="G155" s="5" t="inlineStr">
@@ -8739,7 +8739,7 @@
       </c>
       <c r="L155" s="5" t="n"/>
       <c r="M155" s="7" t="n">
-        <v>14.88</v>
+        <v>17.18</v>
       </c>
     </row>
     <row r="156">
@@ -8750,7 +8750,7 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955362 - KIT4M05563528MKX</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649592 - KIT4M05413787HHK</t>
         </is>
       </c>
       <c r="C156" s="3" t="n">
@@ -8761,12 +8761,12 @@
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563528MKX</t>
+          <t>KIT4M05413787HHK</t>
         </is>
       </c>
       <c r="F156" s="4" t="inlineStr">
         <is>
-          <t>814471</t>
+          <t>812809</t>
         </is>
       </c>
       <c r="G156" s="5" t="inlineStr">
@@ -8792,7 +8792,7 @@
       </c>
       <c r="L156" s="5" t="n"/>
       <c r="M156" s="7" t="n">
-        <v>14.51</v>
+        <v>15.8</v>
       </c>
     </row>
     <row r="157">
@@ -8803,7 +8803,7 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - CW6642812 - KIT4M054138292ZP</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482708 - KIT4M04604736T7C</t>
         </is>
       </c>
       <c r="C157" s="3" t="n">
@@ -8814,12 +8814,12 @@
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138292ZP</t>
+          <t>KIT4M04604736T7C</t>
         </is>
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>812784</t>
+          <t>809662</t>
         </is>
       </c>
       <c r="G157" s="5" t="inlineStr">
@@ -8845,7 +8845,7 @@
       </c>
       <c r="L157" s="5" t="n"/>
       <c r="M157" s="7" t="n">
-        <v>14.46</v>
+        <v>15.7</v>
       </c>
     </row>
     <row r="158">
@@ -8856,7 +8856,7 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020649862 - KIT4M04475159PMD</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438222 - KIT4M058725299QP</t>
         </is>
       </c>
       <c r="C158" s="3" t="n">
@@ -8867,12 +8867,12 @@
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475159PMD</t>
+          <t>KIT4M058725299QP</t>
         </is>
       </c>
       <c r="F158" s="4" t="inlineStr">
         <is>
-          <t>809868</t>
+          <t>816080</t>
         </is>
       </c>
       <c r="G158" s="5" t="inlineStr">
@@ -8898,7 +8898,7 @@
       </c>
       <c r="L158" s="5" t="n"/>
       <c r="M158" s="7" t="n">
-        <v>14.45</v>
+        <v>15.01</v>
       </c>
     </row>
     <row r="159">
@@ -8909,7 +8909,7 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438242 - KIT4M058725094XP</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955362 - KIT4M05563528MKX</t>
         </is>
       </c>
       <c r="C159" s="3" t="n">
@@ -8920,12 +8920,12 @@
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725094XP</t>
+          <t>KIT4M05563528MKX</t>
         </is>
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>816085</t>
+          <t>814471</t>
         </is>
       </c>
       <c r="G159" s="5" t="inlineStr">
@@ -8951,7 +8951,7 @@
       </c>
       <c r="L159" s="5" t="n"/>
       <c r="M159" s="7" t="n">
-        <v>14.01</v>
+        <v>14.96</v>
       </c>
     </row>
     <row r="160">
@@ -8962,7 +8962,7 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955482 - KIT4M055635088NK</t>
+          <t>SMA - 05900510 - Los Angeles CA - CW6642812 - KIT4M054138292ZP</t>
         </is>
       </c>
       <c r="C160" s="3" t="n">
@@ -8973,12 +8973,12 @@
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635088NK</t>
+          <t>KIT4M054138292ZP</t>
         </is>
       </c>
       <c r="F160" s="4" t="inlineStr">
         <is>
-          <t>814434</t>
+          <t>812784</t>
         </is>
       </c>
       <c r="G160" s="5" t="inlineStr">
@@ -9004,7 +9004,7 @@
       </c>
       <c r="L160" s="5" t="n"/>
       <c r="M160" s="7" t="n">
-        <v>13.92</v>
+        <v>14.46</v>
       </c>
     </row>
     <row r="161">
@@ -9015,7 +9015,7 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649322 - KIT4M053683324KZ</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020649862 - KIT4M04475159PMD</t>
         </is>
       </c>
       <c r="C161" s="3" t="n">
@@ -9026,12 +9026,12 @@
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>KIT4M053683324KZ</t>
+          <t>KIT4M04475159PMD</t>
         </is>
       </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
-          <t>810832</t>
+          <t>809868</t>
         </is>
       </c>
       <c r="G161" s="5" t="inlineStr">
@@ -9057,7 +9057,7 @@
       </c>
       <c r="L161" s="5" t="n"/>
       <c r="M161" s="7" t="n">
-        <v>13.85</v>
+        <v>14.45</v>
       </c>
     </row>
     <row r="162">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649442 - KIT4M054137885SM</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955642 - KIT4M05563573WKC</t>
         </is>
       </c>
       <c r="C162" s="3" t="n">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137885SM</t>
+          <t>KIT4M05563573WKC</t>
         </is>
       </c>
       <c r="F162" s="4" t="inlineStr">
         <is>
-          <t>812846</t>
+          <t>814488</t>
         </is>
       </c>
       <c r="G162" s="5" t="inlineStr">
@@ -9110,7 +9110,7 @@
       </c>
       <c r="L162" s="5" t="n"/>
       <c r="M162" s="7" t="n">
-        <v>13.24</v>
+        <v>14.14</v>
       </c>
     </row>
     <row r="163">
@@ -9163,7 +9163,7 @@
       </c>
       <c r="L163" s="5" t="n"/>
       <c r="M163" s="7" t="n">
-        <v>12.25</v>
+        <v>14.14</v>
       </c>
     </row>
     <row r="164">
@@ -9174,7 +9174,7 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955152 - KIT4M05563514P8T</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955482 - KIT4M055635088NK</t>
         </is>
       </c>
       <c r="C164" s="3" t="n">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563514P8T</t>
+          <t>KIT4M055635088NK</t>
         </is>
       </c>
       <c r="F164" s="4" t="inlineStr">
         <is>
-          <t>814436</t>
+          <t>814434</t>
         </is>
       </c>
       <c r="G164" s="5" t="inlineStr">
@@ -9216,7 +9216,7 @@
       </c>
       <c r="L164" s="5" t="n"/>
       <c r="M164" s="7" t="n">
-        <v>12.14</v>
+        <v>14.03</v>
       </c>
     </row>
     <row r="165">
@@ -9227,7 +9227,7 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020650152 - KIT4M054138189C7</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827010 - KIT4M046047372KJ</t>
         </is>
       </c>
       <c r="C165" s="3" t="n">
@@ -9238,12 +9238,12 @@
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138189C7</t>
+          <t>KIT4M046047372KJ</t>
         </is>
       </c>
       <c r="F165" s="4" t="inlineStr">
         <is>
-          <t>812831</t>
+          <t>809658</t>
         </is>
       </c>
       <c r="G165" s="5" t="inlineStr">
@@ -9269,7 +9269,7 @@
       </c>
       <c r="L165" s="5" t="n"/>
       <c r="M165" s="7" t="n">
-        <v>11.19</v>
+        <v>13.64</v>
       </c>
     </row>
     <row r="166">
@@ -9280,7 +9280,7 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 020955242 - KIT4M05563511FF4</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649442 - KIT4M054137885SM</t>
         </is>
       </c>
       <c r="C166" s="3" t="n">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563511FF4</t>
+          <t>KIT4M054137885SM</t>
         </is>
       </c>
       <c r="F166" s="4" t="inlineStr">
         <is>
-          <t>814437</t>
+          <t>812846</t>
         </is>
       </c>
       <c r="G166" s="5" t="inlineStr">
@@ -9322,7 +9322,7 @@
       </c>
       <c r="L166" s="5" t="n"/>
       <c r="M166" s="7" t="n">
-        <v>10.96</v>
+        <v>13.24</v>
       </c>
     </row>
     <row r="167">
@@ -9375,7 +9375,7 @@
       </c>
       <c r="L167" s="5" t="n"/>
       <c r="M167" s="7" t="n">
-        <v>10.72</v>
+        <v>13.12</v>
       </c>
     </row>
     <row r="168">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955252 - KIT4M05563584FVC</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955152 - KIT4M05563514P8T</t>
         </is>
       </c>
       <c r="C168" s="3" t="n">
@@ -9397,12 +9397,12 @@
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563584FVC</t>
+          <t>KIT4M05563514P8T</t>
         </is>
       </c>
       <c r="F168" s="4" t="inlineStr">
         <is>
-          <t>814439</t>
+          <t>814436</t>
         </is>
       </c>
       <c r="G168" s="5" t="inlineStr">
@@ -9428,7 +9428,7 @@
       </c>
       <c r="L168" s="5" t="n"/>
       <c r="M168" s="7" t="n">
-        <v>10.63</v>
+        <v>12.96</v>
       </c>
     </row>
     <row r="169">
@@ -9439,7 +9439,7 @@
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649582 - KIT4M05413774JZX</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955252 - KIT4M05563584FVC</t>
         </is>
       </c>
       <c r="C169" s="3" t="n">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413774JZX</t>
+          <t>KIT4M05563584FVC</t>
         </is>
       </c>
       <c r="F169" s="4" t="inlineStr">
         <is>
-          <t>812836</t>
+          <t>814439</t>
         </is>
       </c>
       <c r="G169" s="5" t="inlineStr">
@@ -9481,7 +9481,7 @@
       </c>
       <c r="L169" s="5" t="n"/>
       <c r="M169" s="7" t="n">
-        <v>10.46</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="170">
@@ -9492,7 +9492,7 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020955432 - KIT4M05563533M9N</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955042 - KIT4P00072391SZM</t>
         </is>
       </c>
       <c r="C170" s="3" t="n">
@@ -9503,17 +9503,17 @@
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563533M9N</t>
+          <t>KIT4P00072391SZM</t>
         </is>
       </c>
       <c r="F170" s="4" t="inlineStr">
         <is>
-          <t>814485</t>
+          <t>814493</t>
         </is>
       </c>
       <c r="G170" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H170" s="5" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="L170" s="5" t="n"/>
       <c r="M170" s="7" t="n">
-        <v>10.32</v>
+        <v>12.53</v>
       </c>
     </row>
     <row r="171">
@@ -9545,7 +9545,7 @@
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020650122-KIT4M05413776H84</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020955432 - KIT4M05563533M9N</t>
         </is>
       </c>
       <c r="C171" s="3" t="n">
@@ -9556,12 +9556,12 @@
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413776H84</t>
+          <t>KIT4M05563533M9N</t>
         </is>
       </c>
       <c r="F171" s="4" t="inlineStr">
         <is>
-          <t>810101</t>
+          <t>814485</t>
         </is>
       </c>
       <c r="G171" s="5" t="inlineStr">
@@ -9587,7 +9587,7 @@
       </c>
       <c r="L171" s="5" t="n"/>
       <c r="M171" s="7" t="n">
-        <v>10.27</v>
+        <v>11.62</v>
       </c>
     </row>
     <row r="172">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 021438232 - KIT4M05872520QJM</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020650152 - KIT4M054138189C7</t>
         </is>
       </c>
       <c r="C172" s="3" t="n">
@@ -9609,12 +9609,12 @@
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872520QJM</t>
+          <t>KIT4M054138189C7</t>
         </is>
       </c>
       <c r="F172" s="4" t="inlineStr">
         <is>
-          <t>816078</t>
+          <t>812831</t>
         </is>
       </c>
       <c r="G172" s="5" t="inlineStr">
@@ -9640,7 +9640,7 @@
       </c>
       <c r="L172" s="5" t="n"/>
       <c r="M172" s="7" t="n">
-        <v>9.82</v>
+        <v>11.19</v>
       </c>
     </row>
     <row r="173">
@@ -9651,7 +9651,7 @@
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649282 - KIT4M05368213974</t>
+          <t>SS - 05900510 -  Los Angeles CA - 020955242 - KIT4M05563511FF4</t>
         </is>
       </c>
       <c r="C173" s="3" t="n">
@@ -9662,12 +9662,12 @@
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368213974</t>
+          <t>KIT4M05563511FF4</t>
         </is>
       </c>
       <c r="F173" s="4" t="inlineStr">
         <is>
-          <t>810647</t>
+          <t>814437</t>
         </is>
       </c>
       <c r="G173" s="5" t="inlineStr">
@@ -9693,7 +9693,7 @@
       </c>
       <c r="L173" s="5" t="n"/>
       <c r="M173" s="7" t="n">
-        <v>9.18</v>
+        <v>10.96</v>
       </c>
     </row>
     <row r="174">
@@ -9704,7 +9704,7 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955612 - KIT4M0556355588P</t>
+          <t>SMRT-05900510-Los Angeles CA-020650122-KIT4M05413776H84</t>
         </is>
       </c>
       <c r="C174" s="3" t="n">
@@ -9715,12 +9715,12 @@
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0556355588P</t>
+          <t>KIT4M05413776H84</t>
         </is>
       </c>
       <c r="F174" s="4" t="inlineStr">
         <is>
-          <t>814455</t>
+          <t>810101</t>
         </is>
       </c>
       <c r="G174" s="5" t="inlineStr">
@@ -9746,7 +9746,7 @@
       </c>
       <c r="L174" s="5" t="n"/>
       <c r="M174" s="7" t="n">
-        <v>9.140000000000001</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="175">
@@ -9757,7 +9757,7 @@
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955502 - KIT4M05563502GJS</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649582 - KIT4M05413774JZX</t>
         </is>
       </c>
       <c r="C175" s="3" t="n">
@@ -9768,12 +9768,12 @@
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563502GJS</t>
+          <t>KIT4M05413774JZX</t>
         </is>
       </c>
       <c r="F175" s="4" t="inlineStr">
         <is>
-          <t>814470</t>
+          <t>812836</t>
         </is>
       </c>
       <c r="G175" s="5" t="inlineStr">
@@ -9799,7 +9799,7 @@
       </c>
       <c r="L175" s="5" t="n"/>
       <c r="M175" s="7" t="n">
-        <v>8.869999999999999</v>
+        <v>10.46</v>
       </c>
     </row>
     <row r="176">
@@ -9810,7 +9810,7 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827010 - KIT4M046047372KJ</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955502 - KIT4M05563502GJS</t>
         </is>
       </c>
       <c r="C176" s="3" t="n">
@@ -9821,12 +9821,12 @@
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047372KJ</t>
+          <t>KIT4M05563502GJS</t>
         </is>
       </c>
       <c r="F176" s="4" t="inlineStr">
         <is>
-          <t>809658</t>
+          <t>814470</t>
         </is>
       </c>
       <c r="G176" s="5" t="inlineStr">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="L176" s="5" t="n"/>
       <c r="M176" s="7" t="n">
-        <v>8.130000000000001</v>
+        <v>9.81</v>
       </c>
     </row>
     <row r="177">
@@ -9863,7 +9863,7 @@
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020649252 - KIT4P00066848VQM</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649282 - KIT4M05368213974</t>
         </is>
       </c>
       <c r="C177" s="3" t="n">
@@ -9874,17 +9874,17 @@
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00066848VQM</t>
+          <t>KIT4M05368213974</t>
         </is>
       </c>
       <c r="F177" s="4" t="inlineStr">
         <is>
-          <t>812923</t>
+          <t>810647</t>
         </is>
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H177" s="5" t="inlineStr">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="L177" s="5" t="n"/>
       <c r="M177" s="7" t="n">
-        <v>7.27</v>
+        <v>9.65</v>
       </c>
     </row>
     <row r="178">
@@ -9916,7 +9916,7 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649792 - KIT4M04475151HTP</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955612 - KIT4M0556355588P</t>
         </is>
       </c>
       <c r="C178" s="3" t="n">
@@ -9927,12 +9927,12 @@
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475151HTP</t>
+          <t>KIT4M0556355588P</t>
         </is>
       </c>
       <c r="F178" s="4" t="inlineStr">
         <is>
-          <t>809867</t>
+          <t>814455</t>
         </is>
       </c>
       <c r="G178" s="5" t="inlineStr">
@@ -9958,7 +9958,7 @@
       </c>
       <c r="L178" s="5" t="n"/>
       <c r="M178" s="7" t="n">
-        <v>7.08</v>
+        <v>9.140000000000001</v>
       </c>
     </row>
     <row r="179">
@@ -9969,7 +9969,7 @@
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles, CA - 0204827011114 - KIT4M03986267RWH</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020649252 - KIT4P00066848VQM</t>
         </is>
       </c>
       <c r="C179" s="3" t="n">
@@ -9980,17 +9980,17 @@
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03986267RWH</t>
+          <t>KIT4P00066848VQM</t>
         </is>
       </c>
       <c r="F179" s="4" t="inlineStr">
         <is>
-          <t>809616</t>
+          <t>812923</t>
         </is>
       </c>
       <c r="G179" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H179" s="5" t="inlineStr">
@@ -10011,7 +10011,7 @@
       </c>
       <c r="L179" s="5" t="n"/>
       <c r="M179" s="7" t="n">
-        <v>6.36</v>
+        <v>7.27</v>
       </c>
     </row>
     <row r="180">
@@ -10022,7 +10022,7 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649642 - KIT4M05413826Z6Z</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649792 - KIT4M04475151HTP</t>
         </is>
       </c>
       <c r="C180" s="3" t="n">
@@ -10033,12 +10033,12 @@
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413826Z6Z</t>
+          <t>KIT4M04475151HTP</t>
         </is>
       </c>
       <c r="F180" s="4" t="inlineStr">
         <is>
-          <t>812804</t>
+          <t>809867</t>
         </is>
       </c>
       <c r="G180" s="5" t="inlineStr">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="L180" s="5" t="n"/>
       <c r="M180" s="7" t="n">
-        <v>5.9</v>
+        <v>7.08</v>
       </c>
     </row>
     <row r="181">
@@ -10075,7 +10075,7 @@
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827011110 - KIT4M03866627GHD</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270114 - KIT4M04476539RJ5</t>
         </is>
       </c>
       <c r="C181" s="3" t="n">
@@ -10086,12 +10086,12 @@
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03866627GHD</t>
+          <t>KIT4M04476539RJ5</t>
         </is>
       </c>
       <c r="F181" s="4" t="inlineStr">
         <is>
-          <t>809619</t>
+          <t>809612</t>
         </is>
       </c>
       <c r="G181" s="5" t="inlineStr">
@@ -10117,7 +10117,7 @@
       </c>
       <c r="L181" s="5" t="n"/>
       <c r="M181" s="7" t="n">
-        <v>5.78</v>
+        <v>6.74</v>
       </c>
     </row>
     <row r="182">
@@ -10128,7 +10128,7 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270110 - KIT4M038677586ZX</t>
+          <t>STS - 05900510 - Los Angeles, CA - 0204827011114 - KIT4M03986267RWH</t>
         </is>
       </c>
       <c r="C182" s="3" t="n">
@@ -10139,12 +10139,12 @@
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>KIT4M038677586ZX</t>
+          <t>KIT4M03986267RWH</t>
         </is>
       </c>
       <c r="F182" s="4" t="inlineStr">
         <is>
-          <t>809623</t>
+          <t>809616</t>
         </is>
       </c>
       <c r="G182" s="5" t="inlineStr">
@@ -10170,7 +10170,7 @@
       </c>
       <c r="L182" s="5" t="n"/>
       <c r="M182" s="7" t="n">
-        <v>5.55</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="183">
@@ -10181,7 +10181,7 @@
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020650182 - KIT4M05413821GGW</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649642 - KIT4M05413826Z6Z</t>
         </is>
       </c>
       <c r="C183" s="3" t="n">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413821GGW</t>
+          <t>KIT4M05413826Z6Z</t>
         </is>
       </c>
       <c r="F183" s="4" t="inlineStr">
         <is>
-          <t>812830</t>
+          <t>812804</t>
         </is>
       </c>
       <c r="G183" s="5" t="inlineStr">
@@ -10223,7 +10223,7 @@
       </c>
       <c r="L183" s="5" t="n"/>
       <c r="M183" s="7" t="n">
-        <v>5.51</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="184">
@@ -10234,7 +10234,7 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649962 - KIT4M05413783PFQ</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827011110 - KIT4M03866627GHD</t>
         </is>
       </c>
       <c r="C184" s="3" t="n">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413783PFQ</t>
+          <t>KIT4M03866627GHD</t>
         </is>
       </c>
       <c r="F184" s="4" t="inlineStr">
         <is>
-          <t>812845</t>
+          <t>809619</t>
         </is>
       </c>
       <c r="G184" s="5" t="inlineStr">
@@ -10276,7 +10276,7 @@
       </c>
       <c r="L184" s="5" t="n"/>
       <c r="M184" s="7" t="n">
-        <v>4.65</v>
+        <v>5.78</v>
       </c>
     </row>
     <row r="185">
@@ -10287,7 +10287,7 @@
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270114 - KIT4M04476539RJ5</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270110 - KIT4M038677586ZX</t>
         </is>
       </c>
       <c r="C185" s="3" t="n">
@@ -10298,12 +10298,12 @@
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04476539RJ5</t>
+          <t>KIT4M038677586ZX</t>
         </is>
       </c>
       <c r="F185" s="4" t="inlineStr">
         <is>
-          <t>809612</t>
+          <t>809623</t>
         </is>
       </c>
       <c r="G185" s="5" t="inlineStr">
@@ -10329,7 +10329,7 @@
       </c>
       <c r="L185" s="5" t="n"/>
       <c r="M185" s="7" t="n">
-        <v>4.35</v>
+        <v>5.55</v>
       </c>
     </row>
     <row r="186">
@@ -10340,7 +10340,7 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437582 - KIT4M05872573K7P</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020650182 - KIT4M05413821GGW</t>
         </is>
       </c>
       <c r="C186" s="3" t="n">
@@ -10351,12 +10351,12 @@
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872573K7P</t>
+          <t>KIT4M05413821GGW</t>
         </is>
       </c>
       <c r="F186" s="4" t="inlineStr">
         <is>
-          <t>816067</t>
+          <t>812830</t>
         </is>
       </c>
       <c r="G186" s="5" t="inlineStr">
@@ -10382,7 +10382,7 @@
       </c>
       <c r="L186" s="5" t="n"/>
       <c r="M186" s="7" t="n">
-        <v>4.28</v>
+        <v>5.51</v>
       </c>
     </row>
     <row r="187">
@@ -10393,7 +10393,7 @@
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649492 - KIT4M054138074NS</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437902 - KIT4M05799717WZV</t>
         </is>
       </c>
       <c r="C187" s="3" t="n">
@@ -10404,12 +10404,12 @@
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138074NS</t>
+          <t>KIT4M05799717WZV</t>
         </is>
       </c>
       <c r="F187" s="4" t="inlineStr">
         <is>
-          <t>812816</t>
+          <t>816280</t>
         </is>
       </c>
       <c r="G187" s="5" t="inlineStr">
@@ -10435,7 +10435,7 @@
       </c>
       <c r="L187" s="5" t="n"/>
       <c r="M187" s="7" t="n">
-        <v>3.8</v>
+        <v>5.14</v>
       </c>
     </row>
     <row r="188">
@@ -10446,7 +10446,7 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649732 - KIT4M046047467T4</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649962 - KIT4M05413783PFQ</t>
         </is>
       </c>
       <c r="C188" s="3" t="n">
@@ -10457,12 +10457,12 @@
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047467T4</t>
+          <t>KIT4M05413783PFQ</t>
         </is>
       </c>
       <c r="F188" s="4" t="inlineStr">
         <is>
-          <t>809865</t>
+          <t>812845</t>
         </is>
       </c>
       <c r="G188" s="5" t="inlineStr">
@@ -10488,7 +10488,7 @@
       </c>
       <c r="L188" s="5" t="n"/>
       <c r="M188" s="7" t="n">
-        <v>3.43</v>
+        <v>4.65</v>
       </c>
     </row>
     <row r="189">
@@ -10499,7 +10499,7 @@
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437902 - KIT4M05799717WZV</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437582 - KIT4M05872573K7P</t>
         </is>
       </c>
       <c r="C189" s="3" t="n">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799717WZV</t>
+          <t>KIT4M05872573K7P</t>
         </is>
       </c>
       <c r="F189" s="4" t="inlineStr">
         <is>
-          <t>816280</t>
+          <t>816067</t>
         </is>
       </c>
       <c r="G189" s="5" t="inlineStr">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="L189" s="5" t="n"/>
       <c r="M189" s="7" t="n">
-        <v>2.96</v>
+        <v>4.28</v>
       </c>
     </row>
     <row r="190">
@@ -10552,7 +10552,7 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649752 - KIT4M03867749CW5</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649732 - KIT4M046047467T4</t>
         </is>
       </c>
       <c r="C190" s="3" t="n">
@@ -10563,12 +10563,12 @@
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03867749CW5</t>
+          <t>KIT4M046047467T4</t>
         </is>
       </c>
       <c r="F190" s="4" t="inlineStr">
         <is>
-          <t>809877</t>
+          <t>809865</t>
         </is>
       </c>
       <c r="G190" s="5" t="inlineStr">
@@ -10594,7 +10594,7 @@
       </c>
       <c r="L190" s="5" t="n"/>
       <c r="M190" s="7" t="n">
-        <v>2.96</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="191">
@@ -10605,7 +10605,7 @@
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827012 - KIT4M04606110GTV</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649492 - KIT4M054138074NS</t>
         </is>
       </c>
       <c r="C191" s="3" t="n">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04606110GTV</t>
+          <t>KIT4M054138074NS</t>
         </is>
       </c>
       <c r="F191" s="4" t="inlineStr">
         <is>
-          <t>809660</t>
+          <t>812816</t>
         </is>
       </c>
       <c r="G191" s="5" t="inlineStr">
@@ -10647,7 +10647,7 @@
       </c>
       <c r="L191" s="5" t="n"/>
       <c r="M191" s="7" t="n">
-        <v>2.61</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="192">
@@ -10658,7 +10658,7 @@
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437932 - KIT4M05799732NQK</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437402 - KIT4M05872537SGZ</t>
         </is>
       </c>
       <c r="C192" s="3" t="n">
@@ -10669,12 +10669,12 @@
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799732NQK</t>
+          <t>KIT4M05872537SGZ</t>
         </is>
       </c>
       <c r="F192" s="4" t="inlineStr">
         <is>
-          <t>816275</t>
+          <t>816073</t>
         </is>
       </c>
       <c r="G192" s="5" t="inlineStr">
@@ -10700,7 +10700,7 @@
       </c>
       <c r="L192" s="5" t="n"/>
       <c r="M192" s="7" t="n">
-        <v>2.48</v>
+        <v>3.05</v>
       </c>
     </row>
     <row r="193">
@@ -10711,7 +10711,7 @@
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437612 - KIT4M058725265DP</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649752 - KIT4M03867749CW5</t>
         </is>
       </c>
       <c r="C193" s="3" t="n">
@@ -10722,12 +10722,12 @@
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725265DP</t>
+          <t>KIT4M03867749CW5</t>
         </is>
       </c>
       <c r="F193" s="4" t="inlineStr">
         <is>
-          <t>816192</t>
+          <t>809877</t>
         </is>
       </c>
       <c r="G193" s="5" t="inlineStr">
@@ -10753,7 +10753,7 @@
       </c>
       <c r="L193" s="5" t="n"/>
       <c r="M193" s="7" t="n">
-        <v>1.58</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="194">
@@ -10764,7 +10764,7 @@
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020650022 - KIT4M05413813HSJ</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827012 - KIT4M04606110GTV</t>
         </is>
       </c>
       <c r="C194" s="3" t="n">
@@ -10775,12 +10775,12 @@
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413813HSJ</t>
+          <t>KIT4M04606110GTV</t>
         </is>
       </c>
       <c r="F194" s="4" t="inlineStr">
         <is>
-          <t>812797</t>
+          <t>809660</t>
         </is>
       </c>
       <c r="G194" s="5" t="inlineStr">
@@ -10806,7 +10806,7 @@
       </c>
       <c r="L194" s="5" t="n"/>
       <c r="M194" s="7" t="n">
-        <v>1.2</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="195">
@@ -10817,7 +10817,7 @@
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649852 - KIT4M05413789Z8C</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437932 - KIT4M05799732NQK</t>
         </is>
       </c>
       <c r="C195" s="3" t="n">
@@ -10828,12 +10828,12 @@
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413789Z8C</t>
+          <t>KIT4M05799732NQK</t>
         </is>
       </c>
       <c r="F195" s="4" t="inlineStr">
         <is>
-          <t>812840</t>
+          <t>816275</t>
         </is>
       </c>
       <c r="G195" s="5" t="inlineStr">
@@ -10859,7 +10859,7 @@
       </c>
       <c r="L195" s="5" t="n"/>
       <c r="M195" s="7" t="n">
-        <v>1.14</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="196">
@@ -10870,7 +10870,7 @@
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020649652 - KIT4M0541381584X</t>
+          <t>SSC - 05900510 - Los Angeles CA - 021437792 - KIT4M05872507528</t>
         </is>
       </c>
       <c r="C196" s="3" t="n">
@@ -10881,12 +10881,12 @@
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0541381584X</t>
+          <t>KIT4M05872507528</t>
         </is>
       </c>
       <c r="F196" s="4" t="inlineStr">
         <is>
-          <t>812810</t>
+          <t>816083</t>
         </is>
       </c>
       <c r="G196" s="5" t="inlineStr">
@@ -10912,7 +10912,7 @@
       </c>
       <c r="L196" s="5" t="n"/>
       <c r="M196" s="7" t="n">
-        <v>1.01</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="197">
@@ -10923,7 +10923,7 @@
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438282 - KIT4M05872508VTN</t>
+          <t>SSC - 05900510 -  Los Angeles CA - 021437862 - KIT4M05872516CJM</t>
         </is>
       </c>
       <c r="C197" s="3" t="n">
@@ -10934,12 +10934,12 @@
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872508VTN</t>
+          <t>KIT4M05872516CJM</t>
         </is>
       </c>
       <c r="F197" s="4" t="inlineStr">
         <is>
-          <t>816076</t>
+          <t>816087</t>
         </is>
       </c>
       <c r="G197" s="5" t="inlineStr">
@@ -10965,7 +10965,7 @@
       </c>
       <c r="L197" s="5" t="n"/>
       <c r="M197" s="7" t="n">
-        <v>0.92</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="198">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491804TBC</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438262 - KIT4M05872530RPF</t>
         </is>
       </c>
       <c r="C198" s="3" t="n">
@@ -10987,12 +10987,12 @@
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491804TBC</t>
+          <t>KIT4M05872530RPF</t>
         </is>
       </c>
       <c r="F198" s="4" t="inlineStr">
         <is>
-          <t>816373</t>
+          <t>816079</t>
         </is>
       </c>
       <c r="G198" s="5" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="L198" s="5" t="n"/>
       <c r="M198" s="7" t="n">
-        <v>0.6</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="199">
@@ -11029,7 +11029,7 @@
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>SSC - 05900510 - Los Angeles CA - 021437792 - KIT4M05872507528</t>
+          <t>SS - 05900510 -  Los Angeles CA - 020955572 - KIT4M05563606ZRC</t>
         </is>
       </c>
       <c r="C199" s="3" t="n">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872507528</t>
+          <t>KIT4M05563606ZRC</t>
         </is>
       </c>
       <c r="F199" s="4" t="inlineStr">
         <is>
-          <t>816083</t>
+          <t>814464</t>
         </is>
       </c>
       <c r="G199" s="5" t="inlineStr">
@@ -11071,7 +11071,7 @@
       </c>
       <c r="L199" s="5" t="n"/>
       <c r="M199" s="7" t="n">
-        <v>0.38</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="200">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491800F52</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437612 - KIT4M058725265DP</t>
         </is>
       </c>
       <c r="C200" s="3" t="n">
@@ -11093,12 +11093,12 @@
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491800F52</t>
+          <t>KIT4M058725265DP</t>
         </is>
       </c>
       <c r="F200" s="4" t="inlineStr">
         <is>
-          <t>816406</t>
+          <t>816192</t>
         </is>
       </c>
       <c r="G200" s="5" t="inlineStr">
@@ -11124,7 +11124,7 @@
       </c>
       <c r="L200" s="5" t="n"/>
       <c r="M200" s="7" t="n">
-        <v>0.35</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="201">
@@ -11135,7 +11135,7 @@
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437812-KIT4M058724947VX</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437412 - KIT4M05872548P2H</t>
         </is>
       </c>
       <c r="C201" s="3" t="n">
@@ -11146,12 +11146,12 @@
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058724947VX</t>
+          <t>KIT4M05872548P2H</t>
         </is>
       </c>
       <c r="F201" s="4" t="inlineStr">
         <is>
-          <t>816086</t>
+          <t>816066</t>
         </is>
       </c>
       <c r="G201" s="5" t="inlineStr">
@@ -11177,7 +11177,7 @@
       </c>
       <c r="L201" s="5" t="n"/>
       <c r="M201" s="7" t="n">
-        <v>0.26</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="202">
@@ -11188,7 +11188,7 @@
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020650062 - KIT4M05413797HK5</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020650022 - KIT4M05413813HSJ</t>
         </is>
       </c>
       <c r="C202" s="3" t="n">
@@ -11199,12 +11199,12 @@
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413797HK5</t>
+          <t>KIT4M05413813HSJ</t>
         </is>
       </c>
       <c r="F202" s="4" t="inlineStr">
         <is>
-          <t>812808</t>
+          <t>812797</t>
         </is>
       </c>
       <c r="G202" s="5" t="inlineStr">
@@ -11230,7 +11230,7 @@
       </c>
       <c r="L202" s="5" t="n"/>
       <c r="M202" s="7" t="n">
-        <v>0.24</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="203">
@@ -11241,7 +11241,7 @@
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437592 - KIT4M05872582TC7</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649852 - KIT4M05413789Z8C</t>
         </is>
       </c>
       <c r="C203" s="3" t="n">
@@ -11252,12 +11252,12 @@
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872582TC7</t>
+          <t>KIT4M05413789Z8C</t>
         </is>
       </c>
       <c r="F203" s="4" t="inlineStr">
         <is>
-          <t>816107</t>
+          <t>812840</t>
         </is>
       </c>
       <c r="G203" s="5" t="inlineStr">
@@ -11283,7 +11283,7 @@
       </c>
       <c r="L203" s="5" t="n"/>
       <c r="M203" s="7" t="n">
-        <v>0.23</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="204">
@@ -11294,7 +11294,7 @@
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020649522-KIT4M05413834FTH</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020649652 - KIT4M0541381584X</t>
         </is>
       </c>
       <c r="C204" s="3" t="n">
@@ -11305,12 +11305,12 @@
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413834FTH</t>
+          <t>KIT4M0541381584X</t>
         </is>
       </c>
       <c r="F204" s="4" t="inlineStr">
         <is>
-          <t>812817</t>
+          <t>812810</t>
         </is>
       </c>
       <c r="G204" s="5" t="inlineStr">
@@ -11336,7 +11336,7 @@
       </c>
       <c r="L204" s="5" t="n"/>
       <c r="M204" s="7" t="n">
-        <v>0.2</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="205">
@@ -11347,7 +11347,7 @@
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 6862083  - KIT4M05799682BXX</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438282 - KIT4M05872508VTN</t>
         </is>
       </c>
       <c r="C205" s="3" t="n">
@@ -11358,12 +11358,12 @@
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799682BXX</t>
+          <t>KIT4M05872508VTN</t>
         </is>
       </c>
       <c r="F205" s="4" t="inlineStr">
         <is>
-          <t>816278</t>
+          <t>816076</t>
         </is>
       </c>
       <c r="G205" s="5" t="inlineStr">
@@ -11389,7 +11389,7 @@
       </c>
       <c r="L205" s="5" t="n"/>
       <c r="M205" s="7" t="n">
-        <v>0.19</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="206">
@@ -11400,7 +11400,7 @@
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437832 - KIT4M05872486FXZ</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649892 - KIT4M05413777DGG</t>
         </is>
       </c>
       <c r="C206" s="3" t="n">
@@ -11411,12 +11411,12 @@
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872486FXZ</t>
+          <t>KIT4M05413777DGG</t>
         </is>
       </c>
       <c r="F206" s="4" t="inlineStr">
         <is>
-          <t>816088</t>
+          <t>812802</t>
         </is>
       </c>
       <c r="G206" s="5" t="inlineStr">
@@ -11442,7 +11442,7 @@
       </c>
       <c r="L206" s="5" t="n"/>
       <c r="M206" s="7" t="n">
-        <v>0.17</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="207">
@@ -11453,7 +11453,7 @@
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955422 - KIT4M05563517BVR</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491804TBC</t>
         </is>
       </c>
       <c r="C207" s="3" t="n">
@@ -11464,12 +11464,12 @@
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563517BVR</t>
+          <t>KIT4M06491804TBC</t>
         </is>
       </c>
       <c r="F207" s="4" t="inlineStr">
         <is>
-          <t>814438</t>
+          <t>816373</t>
         </is>
       </c>
       <c r="G207" s="5" t="inlineStr">
@@ -11495,7 +11495,7 @@
       </c>
       <c r="L207" s="5" t="n"/>
       <c r="M207" s="7" t="n">
-        <v>0.16</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="208">
@@ -11506,7 +11506,7 @@
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491790945</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491800F52</t>
         </is>
       </c>
       <c r="C208" s="3" t="n">
@@ -11517,12 +11517,12 @@
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491790945</t>
+          <t>KIT4M06491800F52</t>
         </is>
       </c>
       <c r="F208" s="4" t="inlineStr">
         <is>
-          <t>816410</t>
+          <t>816406</t>
         </is>
       </c>
       <c r="G208" s="5" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="L208" s="5" t="n"/>
       <c r="M208" s="7" t="n">
-        <v>0.14</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="209">
@@ -11559,7 +11559,7 @@
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 6862083  - KIT4M057996395ZF</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437592 - KIT4M05872582TC7</t>
         </is>
       </c>
       <c r="C209" s="3" t="n">
@@ -11570,12 +11570,12 @@
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>KIT4M057996395ZF</t>
+          <t>KIT4M05872582TC7</t>
         </is>
       </c>
       <c r="F209" s="4" t="inlineStr">
         <is>
-          <t>816268</t>
+          <t>816107</t>
         </is>
       </c>
       <c r="G209" s="5" t="inlineStr">
@@ -11601,7 +11601,7 @@
       </c>
       <c r="L209" s="5" t="n"/>
       <c r="M209" s="7" t="n">
-        <v>0.14</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="210">
@@ -11612,7 +11612,7 @@
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438172 - KIT4M05872500684</t>
+          <t>SMRT-05900510-Los Angeles CA-021437812-KIT4M058724947VX</t>
         </is>
       </c>
       <c r="C210" s="3" t="n">
@@ -11623,12 +11623,12 @@
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872500684</t>
+          <t>KIT4M058724947VX</t>
         </is>
       </c>
       <c r="F210" s="4" t="inlineStr">
         <is>
-          <t>816081</t>
+          <t>816086</t>
         </is>
       </c>
       <c r="G210" s="5" t="inlineStr">
@@ -11654,7 +11654,7 @@
       </c>
       <c r="L210" s="5" t="n"/>
       <c r="M210" s="7" t="n">
-        <v>0.14</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="211">
@@ -11665,7 +11665,7 @@
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491836Z2D</t>
+          <t>SS - 05900510 - Los Angeles CA - 020650062 - KIT4M05413797HK5</t>
         </is>
       </c>
       <c r="C211" s="3" t="n">
@@ -11676,12 +11676,12 @@
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491836Z2D</t>
+          <t>KIT4M05413797HK5</t>
         </is>
       </c>
       <c r="F211" s="4" t="inlineStr">
         <is>
-          <t>816366</t>
+          <t>812808</t>
         </is>
       </c>
       <c r="G211" s="5" t="inlineStr">
@@ -11707,7 +11707,7 @@
       </c>
       <c r="L211" s="5" t="n"/>
       <c r="M211" s="7" t="n">
-        <v>0.14</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="212">
@@ -11718,7 +11718,7 @@
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437412 - KIT4M05872548P2H</t>
+          <t>SMRT-05900510-Los Angeles CA-020649522-KIT4M05413834FTH</t>
         </is>
       </c>
       <c r="C212" s="3" t="n">
@@ -11729,12 +11729,12 @@
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872548P2H</t>
+          <t>KIT4M05413834FTH</t>
         </is>
       </c>
       <c r="F212" s="4" t="inlineStr">
         <is>
-          <t>816066</t>
+          <t>812817</t>
         </is>
       </c>
       <c r="G212" s="5" t="inlineStr">
@@ -11760,7 +11760,7 @@
       </c>
       <c r="L212" s="5" t="n"/>
       <c r="M212" s="7" t="n">
-        <v>0.13</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="213">
@@ -11771,7 +11771,7 @@
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491814FV7</t>
+          <t>SS - 05900510 - Los Angeles CA - 6862083  - KIT4M05799682BXX</t>
         </is>
       </c>
       <c r="C213" s="3" t="n">
@@ -11782,12 +11782,12 @@
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491814FV7</t>
+          <t>KIT4M05799682BXX</t>
         </is>
       </c>
       <c r="F213" s="4" t="inlineStr">
         <is>
-          <t>816370</t>
+          <t>816278</t>
         </is>
       </c>
       <c r="G213" s="5" t="inlineStr">
@@ -11813,7 +11813,7 @@
       </c>
       <c r="L213" s="5" t="n"/>
       <c r="M213" s="7" t="n">
-        <v>0.12</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="214">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437302 - KIT4M05872571T4K</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437832 - KIT4M05872486FXZ</t>
         </is>
       </c>
       <c r="C214" s="3" t="n">
@@ -11835,12 +11835,12 @@
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872571T4K</t>
+          <t>KIT4M05872486FXZ</t>
         </is>
       </c>
       <c r="F214" s="4" t="inlineStr">
         <is>
-          <t>816106</t>
+          <t>816088</t>
         </is>
       </c>
       <c r="G214" s="5" t="inlineStr">
@@ -11866,7 +11866,7 @@
       </c>
       <c r="L214" s="5" t="n"/>
       <c r="M214" s="7" t="n">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="215">
@@ -11877,7 +11877,7 @@
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438022 - KIT4M05799705T6B</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955422 - KIT4M05563517BVR</t>
         </is>
       </c>
       <c r="C215" s="3" t="n">
@@ -11888,12 +11888,12 @@
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799705T6B</t>
+          <t>KIT4M05563517BVR</t>
         </is>
       </c>
       <c r="F215" s="4" t="inlineStr">
         <is>
-          <t>816285</t>
+          <t>814438</t>
         </is>
       </c>
       <c r="G215" s="5" t="inlineStr">
@@ -11919,7 +11919,7 @@
       </c>
       <c r="L215" s="5" t="n"/>
       <c r="M215" s="7" t="n">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="216">
@@ -11930,7 +11930,7 @@
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918277QF</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491836Z2D</t>
         </is>
       </c>
       <c r="C216" s="3" t="n">
@@ -11941,12 +11941,12 @@
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918277QF</t>
+          <t>KIT4M06491836Z2D</t>
         </is>
       </c>
       <c r="F216" s="4" t="inlineStr">
         <is>
-          <t>816403</t>
+          <t>816366</t>
         </is>
       </c>
       <c r="G216" s="5" t="inlineStr">
@@ -11972,7 +11972,7 @@
       </c>
       <c r="L216" s="5" t="n"/>
       <c r="M216" s="7" t="n">
-        <v>0.11</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="217">
@@ -11983,7 +11983,7 @@
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437732 - KIT4M05872588W8G</t>
+          <t>SS - 05900510 - Los Angeles CA - 6862083  - KIT4M057996395ZF</t>
         </is>
       </c>
       <c r="C217" s="3" t="n">
@@ -11994,12 +11994,12 @@
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872588W8G</t>
+          <t>KIT4M057996395ZF</t>
         </is>
       </c>
       <c r="F217" s="4" t="inlineStr">
         <is>
-          <t>816100</t>
+          <t>816268</t>
         </is>
       </c>
       <c r="G217" s="5" t="inlineStr">
@@ -12025,7 +12025,7 @@
       </c>
       <c r="L217" s="5" t="n"/>
       <c r="M217" s="7" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="218">
@@ -12036,7 +12036,7 @@
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437312 - KIT4M05872568PR6</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438172 - KIT4M05872500684</t>
         </is>
       </c>
       <c r="C218" s="3" t="n">
@@ -12047,12 +12047,12 @@
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872568PR6</t>
+          <t>KIT4M05872500684</t>
         </is>
       </c>
       <c r="F218" s="4" t="inlineStr">
         <is>
-          <t>816094</t>
+          <t>816081</t>
         </is>
       </c>
       <c r="G218" s="5" t="inlineStr">
@@ -12078,7 +12078,7 @@
       </c>
       <c r="L218" s="5" t="n"/>
       <c r="M218" s="7" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="219">
@@ -12089,7 +12089,7 @@
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 021438182 - KIT4M05872528P9D</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491790945</t>
         </is>
       </c>
       <c r="C219" s="3" t="n">
@@ -12100,12 +12100,12 @@
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872528P9D</t>
+          <t>KIT4M06491790945</t>
         </is>
       </c>
       <c r="F219" s="4" t="inlineStr">
         <is>
-          <t>816089</t>
+          <t>816410</t>
         </is>
       </c>
       <c r="G219" s="5" t="inlineStr">
@@ -12131,7 +12131,7 @@
       </c>
       <c r="L219" s="5" t="n"/>
       <c r="M219" s="7" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="220">
@@ -12142,7 +12142,7 @@
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491821G25</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438022 - KIT4M05799705T6B</t>
         </is>
       </c>
       <c r="C220" s="3" t="n">
@@ -12153,12 +12153,12 @@
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491821G25</t>
+          <t>KIT4M05799705T6B</t>
         </is>
       </c>
       <c r="F220" s="4" t="inlineStr">
         <is>
-          <t>816379</t>
+          <t>816285</t>
         </is>
       </c>
       <c r="G220" s="5" t="inlineStr">
@@ -12184,7 +12184,7 @@
       </c>
       <c r="L220" s="5" t="n"/>
       <c r="M220" s="7" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="221">
@@ -12195,7 +12195,7 @@
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437722 - KIT4M05872498PP4</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491814FV7</t>
         </is>
       </c>
       <c r="C221" s="3" t="n">
@@ -12206,12 +12206,12 @@
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872498PP4</t>
+          <t>KIT4M06491814FV7</t>
         </is>
       </c>
       <c r="F221" s="4" t="inlineStr">
         <is>
-          <t>816104</t>
+          <t>816370</t>
         </is>
       </c>
       <c r="G221" s="5" t="inlineStr">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="L221" s="5" t="n"/>
       <c r="M221" s="7" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="222">
@@ -12248,7 +12248,7 @@
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438252 - KIT4M05872519KTN</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437302 - KIT4M05872571T4K</t>
         </is>
       </c>
       <c r="C222" s="3" t="n">
@@ -12259,12 +12259,12 @@
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872519KTN</t>
+          <t>KIT4M05872571T4K</t>
         </is>
       </c>
       <c r="F222" s="4" t="inlineStr">
         <is>
-          <t>816084</t>
+          <t>816106</t>
         </is>
       </c>
       <c r="G222" s="5" t="inlineStr">
@@ -12290,7 +12290,7 @@
       </c>
       <c r="L222" s="5" t="n"/>
       <c r="M222" s="7" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="223">
@@ -12301,7 +12301,7 @@
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437502 - KIT4M058725695CN</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918277QF</t>
         </is>
       </c>
       <c r="C223" s="3" t="n">
@@ -12312,12 +12312,12 @@
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725695CN</t>
+          <t>KIT4M064918277QF</t>
         </is>
       </c>
       <c r="F223" s="4" t="inlineStr">
         <is>
-          <t>816101</t>
+          <t>816403</t>
         </is>
       </c>
       <c r="G223" s="5" t="inlineStr">
@@ -12343,7 +12343,7 @@
       </c>
       <c r="L223" s="5" t="n"/>
       <c r="M223" s="7" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="224">
@@ -12354,7 +12354,7 @@
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437332 - KIT4M05872554RHM</t>
+          <t>SS - 05900510 -  Los Angeles CA - 021438182 - KIT4M05872528P9D</t>
         </is>
       </c>
       <c r="C224" s="3" t="n">
@@ -12365,12 +12365,12 @@
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872554RHM</t>
+          <t>KIT4M05872528P9D</t>
         </is>
       </c>
       <c r="F224" s="4" t="inlineStr">
         <is>
-          <t>816071</t>
+          <t>816089</t>
         </is>
       </c>
       <c r="G224" s="5" t="inlineStr">
@@ -12396,7 +12396,7 @@
       </c>
       <c r="L224" s="5" t="n"/>
       <c r="M224" s="7" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="225">
@@ -12407,7 +12407,7 @@
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437822-KIT4M0587253378R</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491821G25</t>
         </is>
       </c>
       <c r="C225" s="3" t="n">
@@ -12418,12 +12418,12 @@
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0587253378R</t>
+          <t>KIT4M06491821G25</t>
         </is>
       </c>
       <c r="F225" s="4" t="inlineStr">
         <is>
-          <t>816210</t>
+          <t>816379</t>
         </is>
       </c>
       <c r="G225" s="5" t="inlineStr">
@@ -12449,7 +12449,7 @@
       </c>
       <c r="L225" s="5" t="n"/>
       <c r="M225" s="7" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="226">
@@ -12460,7 +12460,7 @@
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437342 - KIT4M05872557NFB</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437312 - KIT4M05872568PR6</t>
         </is>
       </c>
       <c r="C226" s="3" t="n">
@@ -12471,12 +12471,12 @@
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872557NFB</t>
+          <t>KIT4M05872568PR6</t>
         </is>
       </c>
       <c r="F226" s="4" t="inlineStr">
         <is>
-          <t>816095</t>
+          <t>816094</t>
         </is>
       </c>
       <c r="G226" s="5" t="inlineStr">
@@ -12502,7 +12502,7 @@
       </c>
       <c r="L226" s="5" t="n"/>
       <c r="M226" s="7" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="227">
@@ -12513,7 +12513,7 @@
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>SSC - 05900510 -  Los Angeles CA - 021437862 - KIT4M05872516CJM</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438252 - KIT4M05872519KTN</t>
         </is>
       </c>
       <c r="C227" s="3" t="n">
@@ -12524,12 +12524,12 @@
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872516CJM</t>
+          <t>KIT4M05872519KTN</t>
         </is>
       </c>
       <c r="F227" s="4" t="inlineStr">
         <is>
-          <t>816087</t>
+          <t>816084</t>
         </is>
       </c>
       <c r="G227" s="5" t="inlineStr">
@@ -12555,7 +12555,7 @@
       </c>
       <c r="L227" s="5" t="n"/>
       <c r="M227" s="7" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="228">
@@ -12566,7 +12566,7 @@
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437692 - KIT4M05872518P78</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437732 - KIT4M05872588W8G</t>
         </is>
       </c>
       <c r="C228" s="3" t="n">
@@ -12577,12 +12577,12 @@
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872518P78</t>
+          <t>KIT4M05872588W8G</t>
         </is>
       </c>
       <c r="F228" s="4" t="inlineStr">
         <is>
-          <t>816184</t>
+          <t>816100</t>
         </is>
       </c>
       <c r="G228" s="5" t="inlineStr">
@@ -12608,7 +12608,7 @@
       </c>
       <c r="L228" s="5" t="n"/>
       <c r="M228" s="7" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="229">
@@ -12619,7 +12619,7 @@
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437952 - KIT4M05872523VVB</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437722 - KIT4M05872498PP4</t>
         </is>
       </c>
       <c r="C229" s="3" t="n">
@@ -12630,12 +12630,12 @@
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872523VVB</t>
+          <t>KIT4M05872498PP4</t>
         </is>
       </c>
       <c r="F229" s="4" t="inlineStr">
         <is>
-          <t>816215</t>
+          <t>816104</t>
         </is>
       </c>
       <c r="G229" s="5" t="inlineStr">
@@ -12661,7 +12661,7 @@
       </c>
       <c r="L229" s="5" t="n"/>
       <c r="M229" s="7" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="230">
@@ -12672,7 +12672,7 @@
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438112 - KIT4M0579970825J</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437332 - KIT4M05872554RHM</t>
         </is>
       </c>
       <c r="C230" s="3" t="n">
@@ -12683,12 +12683,12 @@
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0579970825J</t>
+          <t>KIT4M05872554RHM</t>
         </is>
       </c>
       <c r="F230" s="4" t="inlineStr">
         <is>
-          <t>816290</t>
+          <t>816071</t>
         </is>
       </c>
       <c r="G230" s="5" t="inlineStr">
@@ -12725,7 +12725,7 @@
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491829CD2</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437952 - KIT4M05872523VVB</t>
         </is>
       </c>
       <c r="C231" s="3" t="n">
@@ -12736,12 +12736,12 @@
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491829CD2</t>
+          <t>KIT4M05872523VVB</t>
         </is>
       </c>
       <c r="F231" s="4" t="inlineStr">
         <is>
-          <t>816393</t>
+          <t>816215</t>
         </is>
       </c>
       <c r="G231" s="5" t="inlineStr">
@@ -12778,7 +12778,7 @@
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M0649183125S</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437692 - KIT4M05872518P78</t>
         </is>
       </c>
       <c r="C232" s="3" t="n">
@@ -12789,12 +12789,12 @@
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0649183125S</t>
+          <t>KIT4M05872518P78</t>
         </is>
       </c>
       <c r="F232" s="4" t="inlineStr">
         <is>
-          <t>816371</t>
+          <t>816184</t>
         </is>
       </c>
       <c r="G232" s="5" t="inlineStr">
@@ -12831,7 +12831,7 @@
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491825PF9</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438112 - KIT4M0579970825J</t>
         </is>
       </c>
       <c r="C233" s="3" t="n">
@@ -12842,12 +12842,12 @@
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491825PF9</t>
+          <t>KIT4M0579970825J</t>
         </is>
       </c>
       <c r="F233" s="4" t="inlineStr">
         <is>
-          <t>816367</t>
+          <t>816290</t>
         </is>
       </c>
       <c r="G233" s="5" t="inlineStr">
@@ -12937,7 +12937,7 @@
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918165MW</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918154FM</t>
         </is>
       </c>
       <c r="C235" s="3" t="n">
@@ -12948,12 +12948,12 @@
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918165MW</t>
+          <t>KIT4M064918154FM</t>
         </is>
       </c>
       <c r="F235" s="4" t="inlineStr">
         <is>
-          <t>816374</t>
+          <t>816368</t>
         </is>
       </c>
       <c r="G235" s="5" t="inlineStr">
@@ -12990,7 +12990,7 @@
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491817T79</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918165MW</t>
         </is>
       </c>
       <c r="C236" s="3" t="n">
@@ -13001,12 +13001,12 @@
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491817T79</t>
+          <t>KIT4M064918165MW</t>
         </is>
       </c>
       <c r="F236" s="4" t="inlineStr">
         <is>
-          <t>816415</t>
+          <t>816374</t>
         </is>
       </c>
       <c r="G236" s="5" t="inlineStr">
@@ -13043,7 +13043,7 @@
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918154FM</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491817T79</t>
         </is>
       </c>
       <c r="C237" s="3" t="n">
@@ -13054,12 +13054,12 @@
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918154FM</t>
+          <t>KIT4M06491817T79</t>
         </is>
       </c>
       <c r="F237" s="4" t="inlineStr">
         <is>
-          <t>816368</t>
+          <t>816415</t>
         </is>
       </c>
       <c r="G237" s="5" t="inlineStr">
@@ -13096,7 +13096,7 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491818QD2</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491798S8Q</t>
         </is>
       </c>
       <c r="C238" s="3" t="n">
@@ -13107,12 +13107,12 @@
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491818QD2</t>
+          <t>KIT4M06491798S8Q</t>
         </is>
       </c>
       <c r="F238" s="4" t="inlineStr">
         <is>
-          <t>816378</t>
+          <t>816395</t>
         </is>
       </c>
       <c r="G238" s="5" t="inlineStr">
@@ -13149,7 +13149,7 @@
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491820X58</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918197VX</t>
         </is>
       </c>
       <c r="C239" s="3" t="n">
@@ -13160,12 +13160,12 @@
       </c>
       <c r="E239" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491820X58</t>
+          <t>KIT4M064918197VX</t>
         </is>
       </c>
       <c r="F239" s="4" t="inlineStr">
         <is>
-          <t>816385</t>
+          <t>816397</t>
         </is>
       </c>
       <c r="G239" s="5" t="inlineStr">
@@ -13202,7 +13202,7 @@
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918197VX</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491818QD2</t>
         </is>
       </c>
       <c r="C240" s="3" t="n">
@@ -13213,12 +13213,12 @@
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918197VX</t>
+          <t>KIT4M06491818QD2</t>
         </is>
       </c>
       <c r="F240" s="4" t="inlineStr">
         <is>
-          <t>816397</t>
+          <t>816378</t>
         </is>
       </c>
       <c r="G240" s="5" t="inlineStr">
@@ -13255,7 +13255,7 @@
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437462 - KIT4M05872575BC8</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491820X58</t>
         </is>
       </c>
       <c r="C241" s="3" t="n">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872575BC8</t>
+          <t>KIT4M06491820X58</t>
         </is>
       </c>
       <c r="F241" s="4" t="inlineStr">
         <is>
-          <t>816103</t>
+          <t>816385</t>
         </is>
       </c>
       <c r="G241" s="5" t="inlineStr">
@@ -13308,7 +13308,7 @@
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437752 - KIT4M05872577TWT</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M0649183125S</t>
         </is>
       </c>
       <c r="C242" s="3" t="n">
@@ -13319,12 +13319,12 @@
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872577TWT</t>
+          <t>KIT4M0649183125S</t>
         </is>
       </c>
       <c r="F242" s="4" t="inlineStr">
         <is>
-          <t>816212</t>
+          <t>816371</t>
         </is>
       </c>
       <c r="G242" s="5" t="inlineStr">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437882-KIT4M05872527QK6</t>
+          <t>SMRT-05900510-Los Angeles CA-021437712-KIT4M05872570FCC</t>
         </is>
       </c>
       <c r="C243" s="3" t="n">
@@ -13372,12 +13372,12 @@
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872527QK6</t>
+          <t>KIT4M05872570FCC</t>
         </is>
       </c>
       <c r="F243" s="4" t="inlineStr">
         <is>
-          <t>816214</t>
+          <t>816105</t>
         </is>
       </c>
       <c r="G243" s="5" t="inlineStr">
@@ -13520,7 +13520,7 @@
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437802 - KIT4M05872589TM9</t>
+          <t>SMRT-05900510-Los Angeles CA-021437482-KIT4M05872578G7Q</t>
         </is>
       </c>
       <c r="C246" s="3" t="n">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872589TM9</t>
+          <t>KIT4M05872578G7Q</t>
         </is>
       </c>
       <c r="F246" s="4" t="inlineStr">
         <is>
-          <t>816195</t>
+          <t>816102</t>
         </is>
       </c>
       <c r="G246" s="5" t="inlineStr">
@@ -13573,7 +13573,7 @@
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064917925MB</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064917914G5</t>
         </is>
       </c>
       <c r="C247" s="3" t="n">
@@ -13584,12 +13584,12 @@
       </c>
       <c r="E247" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064917925MB</t>
+          <t>KIT4M064917914G5</t>
         </is>
       </c>
       <c r="F247" s="4" t="inlineStr">
         <is>
-          <t>816381</t>
+          <t>816392</t>
         </is>
       </c>
       <c r="G247" s="5" t="inlineStr">
@@ -13626,7 +13626,7 @@
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491798S8Q</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064917925MB</t>
         </is>
       </c>
       <c r="C248" s="3" t="n">
@@ -13637,12 +13637,12 @@
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491798S8Q</t>
+          <t>KIT4M064917925MB</t>
         </is>
       </c>
       <c r="F248" s="4" t="inlineStr">
         <is>
-          <t>816395</t>
+          <t>816381</t>
         </is>
       </c>
       <c r="G248" s="5" t="inlineStr">
@@ -13679,7 +13679,7 @@
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064917914G5</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491789PJ6</t>
         </is>
       </c>
       <c r="C249" s="3" t="n">
@@ -13690,12 +13690,12 @@
       </c>
       <c r="E249" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064917914G5</t>
+          <t>KIT4M06491789PJ6</t>
         </is>
       </c>
       <c r="F249" s="4" t="inlineStr">
         <is>
-          <t>816392</t>
+          <t>816407</t>
         </is>
       </c>
       <c r="G249" s="5" t="inlineStr">
@@ -13732,7 +13732,7 @@
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491789PJ6</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437802 - KIT4M05872589TM9</t>
         </is>
       </c>
       <c r="C250" s="3" t="n">
@@ -13743,12 +13743,12 @@
       </c>
       <c r="E250" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491789PJ6</t>
+          <t>KIT4M05872589TM9</t>
         </is>
       </c>
       <c r="F250" s="4" t="inlineStr">
         <is>
-          <t>816407</t>
+          <t>816195</t>
         </is>
       </c>
       <c r="G250" s="5" t="inlineStr">
@@ -13785,7 +13785,7 @@
       </c>
       <c r="B251" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437482-KIT4M05872578G7Q</t>
+          <t>SMRT-05900510-Los Angeles CA-021437352-KIT4M05872545Q8H</t>
         </is>
       </c>
       <c r="C251" s="3" t="n">
@@ -13796,12 +13796,12 @@
       </c>
       <c r="E251" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872578G7Q</t>
+          <t>KIT4M05872545Q8H</t>
         </is>
       </c>
       <c r="F251" s="4" t="inlineStr">
         <is>
-          <t>816102</t>
+          <t>816112</t>
         </is>
       </c>
       <c r="G251" s="5" t="inlineStr">
@@ -13838,7 +13838,7 @@
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437712-KIT4M05872570FCC</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491825PF9</t>
         </is>
       </c>
       <c r="C252" s="3" t="n">
@@ -13849,12 +13849,12 @@
       </c>
       <c r="E252" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872570FCC</t>
+          <t>KIT4M06491825PF9</t>
         </is>
       </c>
       <c r="F252" s="4" t="inlineStr">
         <is>
-          <t>816105</t>
+          <t>816367</t>
         </is>
       </c>
       <c r="G252" s="5" t="inlineStr">
@@ -13891,7 +13891,7 @@
       </c>
       <c r="B253" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437352-KIT4M05872545Q8H</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491829CD2</t>
         </is>
       </c>
       <c r="C253" s="3" t="n">
@@ -13902,12 +13902,12 @@
       </c>
       <c r="E253" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872545Q8H</t>
+          <t>KIT4M06491829CD2</t>
         </is>
       </c>
       <c r="F253" s="4" t="inlineStr">
         <is>
-          <t>816112</t>
+          <t>816393</t>
         </is>
       </c>
       <c r="G253" s="5" t="inlineStr">
@@ -13944,7 +13944,7 @@
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438262 - KIT4M05872530RPF</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491826SQM</t>
         </is>
       </c>
       <c r="C254" s="3" t="n">
@@ -13955,12 +13955,12 @@
       </c>
       <c r="E254" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872530RPF</t>
+          <t>KIT4M06491826SQM</t>
         </is>
       </c>
       <c r="F254" s="4" t="inlineStr">
         <is>
-          <t>816079</t>
+          <t>816380</t>
         </is>
       </c>
       <c r="G254" s="5" t="inlineStr">
@@ -14050,7 +14050,7 @@
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491826SQM</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437342 - KIT4M05872557NFB</t>
         </is>
       </c>
       <c r="C256" s="3" t="n">
@@ -14061,12 +14061,12 @@
       </c>
       <c r="E256" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491826SQM</t>
+          <t>KIT4M05872557NFB</t>
         </is>
       </c>
       <c r="F256" s="4" t="inlineStr">
         <is>
-          <t>816380</t>
+          <t>816095</t>
         </is>
       </c>
       <c r="G256" s="5" t="inlineStr">
@@ -14103,7 +14103,7 @@
       </c>
       <c r="B257" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438192 - KIT4M05872511F6P</t>
+          <t>SMRT-05900510-Los Angeles CA-021437822-KIT4M0587253378R</t>
         </is>
       </c>
       <c r="C257" s="3" t="n">
@@ -14114,12 +14114,12 @@
       </c>
       <c r="E257" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872511F6P</t>
+          <t>KIT4M0587253378R</t>
         </is>
       </c>
       <c r="F257" s="4" t="inlineStr">
         <is>
-          <t>816090</t>
+          <t>816210</t>
         </is>
       </c>
       <c r="G257" s="5" t="inlineStr">
@@ -14145,7 +14145,7 @@
       </c>
       <c r="L257" s="5" t="n"/>
       <c r="M257" s="7" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="258">
@@ -14156,7 +14156,7 @@
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955542 - KIT4M05563551N6Q</t>
+          <t>SMRT-05900510-Los Angeles CA-021437882-KIT4M05872527QK6</t>
         </is>
       </c>
       <c r="C258" s="3" t="n">
@@ -14167,12 +14167,12 @@
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563551N6Q</t>
+          <t>KIT4M05872527QK6</t>
         </is>
       </c>
       <c r="F258" s="4" t="inlineStr">
         <is>
-          <t>814450</t>
+          <t>816214</t>
         </is>
       </c>
       <c r="G258" s="5" t="inlineStr">
@@ -14198,7 +14198,7 @@
       </c>
       <c r="L258" s="5" t="n"/>
       <c r="M258" s="7" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="259">
@@ -14209,7 +14209,7 @@
       </c>
       <c r="B259" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918346DB</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437462 - KIT4M05872575BC8</t>
         </is>
       </c>
       <c r="C259" s="3" t="n">
@@ -14220,12 +14220,12 @@
       </c>
       <c r="E259" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918346DB</t>
+          <t>KIT4M05872575BC8</t>
         </is>
       </c>
       <c r="F259" s="4" t="inlineStr">
         <is>
-          <t>816369</t>
+          <t>816103</t>
         </is>
       </c>
       <c r="G259" s="5" t="inlineStr">
@@ -14251,7 +14251,7 @@
       </c>
       <c r="L259" s="5" t="n"/>
       <c r="M259" s="7" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="260">
@@ -14262,7 +14262,7 @@
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491833JGV</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437752 - KIT4M05872577TWT</t>
         </is>
       </c>
       <c r="C260" s="3" t="n">
@@ -14273,12 +14273,12 @@
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491833JGV</t>
+          <t>KIT4M05872577TWT</t>
         </is>
       </c>
       <c r="F260" s="4" t="inlineStr">
         <is>
-          <t>816384</t>
+          <t>816212</t>
         </is>
       </c>
       <c r="G260" s="5" t="inlineStr">
@@ -14304,7 +14304,7 @@
       </c>
       <c r="L260" s="5" t="n"/>
       <c r="M260" s="7" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="261">
@@ -14315,7 +14315,7 @@
       </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649892 - KIT4M05413777DGG</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437502 - KIT4M058725695CN</t>
         </is>
       </c>
       <c r="C261" s="3" t="n">
@@ -14326,12 +14326,12 @@
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413777DGG</t>
+          <t>KIT4M058725695CN</t>
         </is>
       </c>
       <c r="F261" s="4" t="inlineStr">
         <is>
-          <t>812802</t>
+          <t>816101</t>
         </is>
       </c>
       <c r="G261" s="5" t="inlineStr">
@@ -14357,7 +14357,7 @@
       </c>
       <c r="L261" s="5" t="n"/>
       <c r="M261" s="7" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="262">
@@ -14421,7 +14421,7 @@
       </c>
       <c r="B263" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491813KGS</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491795MWG</t>
         </is>
       </c>
       <c r="C263" s="3" t="n">
@@ -14432,12 +14432,12 @@
       </c>
       <c r="E263" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491813KGS</t>
+          <t>KIT4M06491795MWG</t>
         </is>
       </c>
       <c r="F263" s="4" t="inlineStr">
         <is>
-          <t>816377</t>
+          <t>816383</t>
         </is>
       </c>
       <c r="G263" s="5" t="inlineStr">
@@ -14527,7 +14527,7 @@
       </c>
       <c r="B265" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437662 - KIT4M05872534RXS</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955542 - KIT4M05563551N6Q</t>
         </is>
       </c>
       <c r="C265" s="3" t="n">
@@ -14538,12 +14538,12 @@
       </c>
       <c r="E265" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872534RXS</t>
+          <t>KIT4M05563551N6Q</t>
         </is>
       </c>
       <c r="F265" s="4" t="inlineStr">
         <is>
-          <t>816216</t>
+          <t>814450</t>
         </is>
       </c>
       <c r="G265" s="5" t="inlineStr">
@@ -14580,7 +14580,7 @@
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437402 - KIT4M05872537SGZ</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438082 - KIT4M05799668SS7</t>
         </is>
       </c>
       <c r="C266" s="3" t="n">
@@ -14591,12 +14591,12 @@
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872537SGZ</t>
+          <t>KIT4M05799668SS7</t>
         </is>
       </c>
       <c r="F266" s="4" t="inlineStr">
         <is>
-          <t>816073</t>
+          <t>816279</t>
         </is>
       </c>
       <c r="G266" s="5" t="inlineStr">
@@ -14633,7 +14633,7 @@
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437372 - KIT4M058725505J5</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438192 - KIT4M05872511F6P</t>
         </is>
       </c>
       <c r="C267" s="3" t="n">
@@ -14644,12 +14644,12 @@
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725505J5</t>
+          <t>KIT4M05872511F6P</t>
         </is>
       </c>
       <c r="F267" s="4" t="inlineStr">
         <is>
-          <t>816117</t>
+          <t>816090</t>
         </is>
       </c>
       <c r="G267" s="5" t="inlineStr">
@@ -14686,7 +14686,7 @@
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438082 - KIT4M05799668SS7</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918346DB</t>
         </is>
       </c>
       <c r="C268" s="3" t="n">
@@ -14697,12 +14697,12 @@
       </c>
       <c r="E268" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799668SS7</t>
+          <t>KIT4M064918346DB</t>
         </is>
       </c>
       <c r="F268" s="4" t="inlineStr">
         <is>
-          <t>816279</t>
+          <t>816369</t>
         </is>
       </c>
       <c r="G268" s="5" t="inlineStr">
@@ -14739,7 +14739,7 @@
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491795MWG</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491833JGV</t>
         </is>
       </c>
       <c r="C269" s="3" t="n">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E269" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491795MWG</t>
+          <t>KIT4M06491833JGV</t>
         </is>
       </c>
       <c r="F269" s="4" t="inlineStr">
         <is>
-          <t>816383</t>
+          <t>816384</t>
         </is>
       </c>
       <c r="G269" s="5" t="inlineStr">
@@ -14792,7 +14792,7 @@
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437572 - KIT4M05872579JPF</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491813KGS</t>
         </is>
       </c>
       <c r="C270" s="3" t="n">
@@ -14803,12 +14803,12 @@
       </c>
       <c r="E270" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872579JPF</t>
+          <t>KIT4M06491813KGS</t>
         </is>
       </c>
       <c r="F270" s="4" t="inlineStr">
         <is>
-          <t>816111</t>
+          <t>816377</t>
         </is>
       </c>
       <c r="G270" s="5" t="inlineStr">
@@ -14845,7 +14845,7 @@
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA  - 020649572 - KIT4M05413816N8K</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437572 - KIT4M05872579JPF</t>
         </is>
       </c>
       <c r="C271" s="3" t="n">
@@ -14856,12 +14856,12 @@
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413816N8K</t>
+          <t>KIT4M05872579JPF</t>
         </is>
       </c>
       <c r="F271" s="4" t="inlineStr">
         <is>
-          <t>812832</t>
+          <t>816111</t>
         </is>
       </c>
       <c r="G271" s="5" t="inlineStr">
@@ -14887,7 +14887,7 @@
       </c>
       <c r="L271" s="5" t="n"/>
       <c r="M271" s="7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="272">
@@ -14898,7 +14898,7 @@
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491797NCX</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437662 - KIT4M05872534RXS</t>
         </is>
       </c>
       <c r="C272" s="3" t="n">
@@ -14909,12 +14909,12 @@
       </c>
       <c r="E272" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491797NCX</t>
+          <t>KIT4M05872534RXS</t>
         </is>
       </c>
       <c r="F272" s="4" t="inlineStr">
         <is>
-          <t>816408</t>
+          <t>816216</t>
         </is>
       </c>
       <c r="G272" s="5" t="inlineStr">
@@ -14940,7 +14940,7 @@
       </c>
       <c r="L272" s="5" t="n"/>
       <c r="M272" s="7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="273">
@@ -14951,7 +14951,7 @@
       </c>
       <c r="B273" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 -  Los Angeles CA - 020649602 - KIT4M05413773R6G</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437372 - KIT4M058725505J5</t>
         </is>
       </c>
       <c r="C273" s="3" t="n">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E273" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413773R6G</t>
+          <t>KIT4M058725505J5</t>
         </is>
       </c>
       <c r="F273" s="4" t="inlineStr">
         <is>
-          <t>812807</t>
+          <t>816117</t>
         </is>
       </c>
       <c r="G273" s="5" t="inlineStr">
@@ -14993,7 +14993,7 @@
       </c>
       <c r="L273" s="5" t="n"/>
       <c r="M273" s="7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="274">
@@ -15110,7 +15110,7 @@
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491796QQN</t>
+          <t>SS - 05900510 - Los Angeles, CA  - 020649572 - KIT4M05413816N8K</t>
         </is>
       </c>
       <c r="C276" s="3" t="n">
@@ -15121,12 +15121,12 @@
       </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491796QQN</t>
+          <t>KIT4M05413816N8K</t>
         </is>
       </c>
       <c r="F276" s="4" t="inlineStr">
         <is>
-          <t>816405</t>
+          <t>812832</t>
         </is>
       </c>
       <c r="G276" s="5" t="inlineStr">
@@ -15152,7 +15152,7 @@
       </c>
       <c r="L276" s="5" t="n"/>
       <c r="M276" s="7" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="277">
@@ -15163,7 +15163,7 @@
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918239TM</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491797NCX</t>
         </is>
       </c>
       <c r="C277" s="3" t="n">
@@ -15174,12 +15174,12 @@
       </c>
       <c r="E277" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918239TM</t>
+          <t>KIT4M06491797NCX</t>
         </is>
       </c>
       <c r="F277" s="4" t="inlineStr">
         <is>
-          <t>816398</t>
+          <t>816408</t>
         </is>
       </c>
       <c r="G277" s="5" t="inlineStr">
@@ -15205,7 +15205,7 @@
       </c>
       <c r="L277" s="5" t="n"/>
       <c r="M277" s="7" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="278">
@@ -15216,7 +15216,7 @@
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491822SF6</t>
+          <t>SMA - 05900510 -  Los Angeles CA - 020649602 - KIT4M05413773R6G</t>
         </is>
       </c>
       <c r="C278" s="3" t="n">
@@ -15227,12 +15227,12 @@
       </c>
       <c r="E278" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491822SF6</t>
+          <t>KIT4M05413773R6G</t>
         </is>
       </c>
       <c r="F278" s="4" t="inlineStr">
         <is>
-          <t>816412</t>
+          <t>812807</t>
         </is>
       </c>
       <c r="G278" s="5" t="inlineStr">
@@ -15258,7 +15258,7 @@
       </c>
       <c r="L278" s="5" t="n"/>
       <c r="M278" s="7" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="279">
@@ -15269,7 +15269,7 @@
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438162 - KIT4M05799712SBX</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437382 - KIT4M058725438WP</t>
         </is>
       </c>
       <c r="C279" s="3" t="n">
@@ -15280,12 +15280,12 @@
       </c>
       <c r="E279" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799712SBX</t>
+          <t>KIT4M058725438WP</t>
         </is>
       </c>
       <c r="F279" s="4" t="inlineStr">
         <is>
-          <t>816276</t>
+          <t>816115</t>
         </is>
       </c>
       <c r="G279" s="5" t="inlineStr">
@@ -15322,7 +15322,7 @@
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437382 - KIT4M058725438WP</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491796QQN</t>
         </is>
       </c>
       <c r="C280" s="3" t="n">
@@ -15333,12 +15333,12 @@
       </c>
       <c r="E280" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725438WP</t>
+          <t>KIT4M06491796QQN</t>
         </is>
       </c>
       <c r="F280" s="4" t="inlineStr">
         <is>
-          <t>816115</t>
+          <t>816405</t>
         </is>
       </c>
       <c r="G280" s="5" t="inlineStr">
@@ -15375,7 +15375,7 @@
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437962 - KIT4M05799706Z6R</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491822SF6</t>
         </is>
       </c>
       <c r="C281" s="3" t="n">
@@ -15386,12 +15386,12 @@
       </c>
       <c r="E281" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799706Z6R</t>
+          <t>KIT4M06491822SF6</t>
         </is>
       </c>
       <c r="F281" s="4" t="inlineStr">
         <is>
-          <t>816273</t>
+          <t>816412</t>
         </is>
       </c>
       <c r="G281" s="5" t="inlineStr">
@@ -15417,7 +15417,7 @@
       </c>
       <c r="L281" s="5" t="n"/>
       <c r="M281" s="7" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="282">
@@ -15428,7 +15428,7 @@
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649982 - KIT4M05413823B5P</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438162 - KIT4M05799712SBX</t>
         </is>
       </c>
       <c r="C282" s="3" t="n">
@@ -15439,12 +15439,12 @@
       </c>
       <c r="E282" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413823B5P</t>
+          <t>KIT4M05799712SBX</t>
         </is>
       </c>
       <c r="F282" s="4" t="inlineStr">
         <is>
-          <t>812837</t>
+          <t>816276</t>
         </is>
       </c>
       <c r="G282" s="5" t="inlineStr">
@@ -15470,7 +15470,7 @@
       </c>
       <c r="L282" s="5" t="n"/>
       <c r="M282" s="7" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="283">
@@ -15481,7 +15481,7 @@
       </c>
       <c r="B283" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491824JCK</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918239TM</t>
         </is>
       </c>
       <c r="C283" s="3" t="n">
@@ -15492,12 +15492,12 @@
       </c>
       <c r="E283" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491824JCK</t>
+          <t>KIT4M064918239TM</t>
         </is>
       </c>
       <c r="F283" s="4" t="inlineStr">
         <is>
-          <t>816413</t>
+          <t>816398</t>
         </is>
       </c>
       <c r="G283" s="5" t="inlineStr">
@@ -15523,7 +15523,7 @@
       </c>
       <c r="L283" s="5" t="n"/>
       <c r="M283" s="7" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="284">
@@ -15534,7 +15534,7 @@
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649992 - KIT4M05413809J58</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649982 - KIT4M05413823B5P</t>
         </is>
       </c>
       <c r="C284" s="3" t="n">
@@ -15545,12 +15545,12 @@
       </c>
       <c r="E284" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413809J58</t>
+          <t>KIT4M05413823B5P</t>
         </is>
       </c>
       <c r="F284" s="4" t="inlineStr">
         <is>
-          <t>812805</t>
+          <t>812837</t>
         </is>
       </c>
       <c r="G284" s="5" t="inlineStr">
@@ -15587,7 +15587,7 @@
       </c>
       <c r="B285" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 021437602 - KIT4M05872524CFG</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437962 - KIT4M05799706Z6R</t>
         </is>
       </c>
       <c r="C285" s="3" t="n">
@@ -15598,12 +15598,12 @@
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872524CFG</t>
+          <t>KIT4M05799706Z6R</t>
         </is>
       </c>
       <c r="F285" s="4" t="inlineStr">
         <is>
-          <t>816205</t>
+          <t>816273</t>
         </is>
       </c>
       <c r="G285" s="5" t="inlineStr">
@@ -15693,7 +15693,7 @@
       </c>
       <c r="B287" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M0649181062D</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491805F7Z</t>
         </is>
       </c>
       <c r="C287" s="3" t="n">
@@ -15704,12 +15704,12 @@
       </c>
       <c r="E287" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0649181062D</t>
+          <t>KIT4M06491805F7Z</t>
         </is>
       </c>
       <c r="F287" s="4" t="inlineStr">
         <is>
-          <t>816388</t>
+          <t>816382</t>
         </is>
       </c>
       <c r="G287" s="5" t="inlineStr">
@@ -15746,7 +15746,7 @@
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491805F7Z</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491803672</t>
         </is>
       </c>
       <c r="C288" s="3" t="n">
@@ -15757,12 +15757,12 @@
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491805F7Z</t>
+          <t>KIT4M06491803672</t>
         </is>
       </c>
       <c r="F288" s="4" t="inlineStr">
         <is>
-          <t>816382</t>
+          <t>816391</t>
         </is>
       </c>
       <c r="G288" s="5" t="inlineStr">
@@ -15799,7 +15799,7 @@
       </c>
       <c r="B289" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491803672</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491809ZR6</t>
         </is>
       </c>
       <c r="C289" s="3" t="n">
@@ -15810,12 +15810,12 @@
       </c>
       <c r="E289" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491803672</t>
+          <t>KIT4M06491809ZR6</t>
         </is>
       </c>
       <c r="F289" s="4" t="inlineStr">
         <is>
-          <t>816391</t>
+          <t>816402</t>
         </is>
       </c>
       <c r="G289" s="5" t="inlineStr">
@@ -15852,7 +15852,7 @@
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649702 - KIT4M04604741P2X</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491802BZV</t>
         </is>
       </c>
       <c r="C290" s="3" t="n">
@@ -15863,12 +15863,12 @@
       </c>
       <c r="E290" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604741P2X</t>
+          <t>KIT4M06491802BZV</t>
         </is>
       </c>
       <c r="F290" s="4" t="inlineStr">
         <is>
-          <t>809871</t>
+          <t>816390</t>
         </is>
       </c>
       <c r="G290" s="5" t="inlineStr">
@@ -15905,7 +15905,7 @@
       </c>
       <c r="B291" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437472 - KIT4M05872565VJK</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437432 - KIT4M0587256692N</t>
         </is>
       </c>
       <c r="C291" s="3" t="n">
@@ -15916,12 +15916,12 @@
       </c>
       <c r="E291" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872565VJK</t>
+          <t>KIT4M0587256692N</t>
         </is>
       </c>
       <c r="F291" s="4" t="inlineStr">
         <is>
-          <t>816109</t>
+          <t>816072</t>
         </is>
       </c>
       <c r="G291" s="5" t="inlineStr">
@@ -15958,7 +15958,7 @@
       </c>
       <c r="B292" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437322 - KIT4M05872567V72</t>
+          <t>SMRT-05900510-Los Angeles CA-021437842-KIT4M05872547MK2</t>
         </is>
       </c>
       <c r="C292" s="3" t="n">
@@ -15969,12 +15969,12 @@
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872567V72</t>
+          <t>KIT4M05872547MK2</t>
         </is>
       </c>
       <c r="F292" s="4" t="inlineStr">
         <is>
-          <t>816099</t>
+          <t>816209</t>
         </is>
       </c>
       <c r="G292" s="5" t="inlineStr">
@@ -16011,7 +16011,7 @@
       </c>
       <c r="B293" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437912 - KIT4M05872525NP5</t>
+          <t>SS - 05900510 -  Los Angeles CA - 021437602 - KIT4M05872524CFG</t>
         </is>
       </c>
       <c r="C293" s="3" t="n">
@@ -16022,12 +16022,12 @@
       </c>
       <c r="E293" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872525NP5</t>
+          <t>KIT4M05872524CFG</t>
         </is>
       </c>
       <c r="F293" s="4" t="inlineStr">
         <is>
-          <t>816213</t>
+          <t>816205</t>
         </is>
       </c>
       <c r="G293" s="5" t="inlineStr">
@@ -16117,7 +16117,7 @@
       </c>
       <c r="B295" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437842-KIT4M05872547MK2</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437912 - KIT4M05872525NP5</t>
         </is>
       </c>
       <c r="C295" s="3" t="n">
@@ -16128,12 +16128,12 @@
       </c>
       <c r="E295" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872547MK2</t>
+          <t>KIT4M05872525NP5</t>
         </is>
       </c>
       <c r="F295" s="4" t="inlineStr">
         <is>
-          <t>816209</t>
+          <t>816213</t>
         </is>
       </c>
       <c r="G295" s="5" t="inlineStr">
@@ -16223,7 +16223,7 @@
       </c>
       <c r="B297" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437512 - KIT4M05872559VR9</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437532 - KIT4M05872556RC9</t>
         </is>
       </c>
       <c r="C297" s="3" t="n">
@@ -16234,12 +16234,12 @@
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872559VR9</t>
+          <t>KIT4M05872556RC9</t>
         </is>
       </c>
       <c r="F297" s="4" t="inlineStr">
         <is>
-          <t>816114</t>
+          <t>816118</t>
         </is>
       </c>
       <c r="G297" s="5" t="inlineStr">
@@ -16382,7 +16382,7 @@
       </c>
       <c r="B300" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437432 - KIT4M0587256692N</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437512 - KIT4M05872559VR9</t>
         </is>
       </c>
       <c r="C300" s="3" t="n">
@@ -16393,12 +16393,12 @@
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0587256692N</t>
+          <t>KIT4M05872559VR9</t>
         </is>
       </c>
       <c r="F300" s="4" t="inlineStr">
         <is>
-          <t>816072</t>
+          <t>816114</t>
         </is>
       </c>
       <c r="G300" s="5" t="inlineStr">
@@ -16435,7 +16435,7 @@
       </c>
       <c r="B301" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437532 - KIT4M05872556RC9</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437472 - KIT4M05872565VJK</t>
         </is>
       </c>
       <c r="C301" s="3" t="n">
@@ -16446,12 +16446,12 @@
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872556RC9</t>
+          <t>KIT4M05872565VJK</t>
         </is>
       </c>
       <c r="F301" s="4" t="inlineStr">
         <is>
-          <t>816118</t>
+          <t>816109</t>
         </is>
       </c>
       <c r="G301" s="5" t="inlineStr">
@@ -16488,7 +16488,7 @@
       </c>
       <c r="B302" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491802BZV</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437322 - KIT4M05872567V72</t>
         </is>
       </c>
       <c r="C302" s="3" t="n">
@@ -16499,12 +16499,12 @@
       </c>
       <c r="E302" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491802BZV</t>
+          <t>KIT4M05872567V72</t>
         </is>
       </c>
       <c r="F302" s="4" t="inlineStr">
         <is>
-          <t>816390</t>
+          <t>816099</t>
         </is>
       </c>
       <c r="G302" s="5" t="inlineStr">
@@ -16700,7 +16700,7 @@
       </c>
       <c r="B306" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 021437562 - KIT4M05872583P58</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649992 - KIT4M05413809J58</t>
         </is>
       </c>
       <c r="C306" s="3" t="n">
@@ -16711,12 +16711,12 @@
       </c>
       <c r="E306" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872583P58</t>
+          <t>KIT4M05413809J58</t>
         </is>
       </c>
       <c r="F306" s="4" t="inlineStr">
         <is>
-          <t>816069</t>
+          <t>812805</t>
         </is>
       </c>
       <c r="G306" s="5" t="inlineStr">
@@ -16753,7 +16753,7 @@
       </c>
       <c r="B307" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491812JDV</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649702 - KIT4M04604741P2X</t>
         </is>
       </c>
       <c r="C307" s="3" t="n">
@@ -16764,12 +16764,12 @@
       </c>
       <c r="E307" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491812JDV</t>
+          <t>KIT4M04604741P2X</t>
         </is>
       </c>
       <c r="F307" s="4" t="inlineStr">
         <is>
-          <t>816409</t>
+          <t>809871</t>
         </is>
       </c>
       <c r="G307" s="5" t="inlineStr">
@@ -16965,7 +16965,7 @@
       </c>
       <c r="B311" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491811JB5</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491824JCK</t>
         </is>
       </c>
       <c r="C311" s="3" t="n">
@@ -16976,12 +16976,12 @@
       </c>
       <c r="E311" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491811JB5</t>
+          <t>KIT4M06491824JCK</t>
         </is>
       </c>
       <c r="F311" s="4" t="inlineStr">
         <is>
-          <t>816411</t>
+          <t>816413</t>
         </is>
       </c>
       <c r="G311" s="5" t="inlineStr">
@@ -17018,7 +17018,7 @@
       </c>
       <c r="B312" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491809ZR6</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M0649181062D</t>
         </is>
       </c>
       <c r="C312" s="3" t="n">
@@ -17029,12 +17029,12 @@
       </c>
       <c r="E312" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491809ZR6</t>
+          <t>KIT4M0649181062D</t>
         </is>
       </c>
       <c r="F312" s="4" t="inlineStr">
         <is>
-          <t>816402</t>
+          <t>816388</t>
         </is>
       </c>
       <c r="G312" s="5" t="inlineStr">
@@ -17071,7 +17071,7 @@
       </c>
       <c r="B313" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491807TRH</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491812JDV</t>
         </is>
       </c>
       <c r="C313" s="3" t="n">
@@ -17082,12 +17082,12 @@
       </c>
       <c r="E313" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491807TRH</t>
+          <t>KIT4M06491812JDV</t>
         </is>
       </c>
       <c r="F313" s="4" t="inlineStr">
         <is>
-          <t>816386</t>
+          <t>816409</t>
         </is>
       </c>
       <c r="G313" s="5" t="inlineStr">
@@ -17124,7 +17124,7 @@
       </c>
       <c r="B314" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020955312 - KIT4M0556351956H</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491807TRH</t>
         </is>
       </c>
       <c r="C314" s="3" t="n">
@@ -17135,12 +17135,12 @@
       </c>
       <c r="E314" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0556351956H</t>
+          <t>KIT4M06491807TRH</t>
         </is>
       </c>
       <c r="F314" s="4" t="inlineStr">
         <is>
-          <t>814477</t>
+          <t>816386</t>
         </is>
       </c>
       <c r="G314" s="5" t="inlineStr">
@@ -17166,7 +17166,7 @@
       </c>
       <c r="L314" s="5" t="n"/>
       <c r="M314" s="7" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="315">
@@ -17177,7 +17177,7 @@
       </c>
       <c r="B315" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437492 - KIT4M0587256196K</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491811JB5</t>
         </is>
       </c>
       <c r="C315" s="3" t="n">
@@ -17188,12 +17188,12 @@
       </c>
       <c r="E315" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0587256196K</t>
+          <t>KIT4M06491811JB5</t>
         </is>
       </c>
       <c r="F315" s="4" t="inlineStr">
         <is>
-          <t>816098</t>
+          <t>816411</t>
         </is>
       </c>
       <c r="G315" s="5" t="inlineStr">
@@ -17219,7 +17219,7 @@
       </c>
       <c r="L315" s="5" t="n"/>
       <c r="M315" s="7" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="316">
@@ -17230,7 +17230,7 @@
       </c>
       <c r="B316" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437652 - KIT4M05872551G9S</t>
+          <t>SS - 05900510 - Los Angeles CA  - 021437562 - KIT4M05872583P58</t>
         </is>
       </c>
       <c r="C316" s="3" t="n">
@@ -17241,12 +17241,12 @@
       </c>
       <c r="E316" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872551G9S</t>
+          <t>KIT4M05872583P58</t>
         </is>
       </c>
       <c r="F316" s="4" t="inlineStr">
         <is>
-          <t>816180</t>
+          <t>816069</t>
         </is>
       </c>
       <c r="G316" s="5" t="inlineStr">
@@ -17272,7 +17272,7 @@
       </c>
       <c r="L316" s="5" t="n"/>
       <c r="M316" s="7" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="317">
@@ -17283,7 +17283,7 @@
       </c>
       <c r="B317" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 021437772 - KIT4M05872563FWB</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437492 - KIT4M0587256196K</t>
         </is>
       </c>
       <c r="C317" s="3" t="n">
@@ -17294,12 +17294,12 @@
       </c>
       <c r="E317" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872563FWB</t>
+          <t>KIT4M0587256196K</t>
         </is>
       </c>
       <c r="F317" s="4" t="inlineStr">
         <is>
-          <t>816208</t>
+          <t>816098</t>
         </is>
       </c>
       <c r="G317" s="5" t="inlineStr">
@@ -17389,7 +17389,7 @@
       </c>
       <c r="B319" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437872 - KIT4M06490319DDN</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437652 - KIT4M05872551G9S</t>
         </is>
       </c>
       <c r="C319" s="3" t="n">
@@ -17400,12 +17400,12 @@
       </c>
       <c r="E319" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06490319DDN</t>
+          <t>KIT4M05872551G9S</t>
         </is>
       </c>
       <c r="F319" s="4" t="inlineStr">
         <is>
-          <t>816220</t>
+          <t>816180</t>
         </is>
       </c>
       <c r="G319" s="5" t="inlineStr">
@@ -17548,7 +17548,7 @@
       </c>
       <c r="B322" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437892 - KIT4M06490321NJX</t>
+          <t>SS - 05900510 - Los Angeles, CA - 021437772 - KIT4M05872563FWB</t>
         </is>
       </c>
       <c r="C322" s="3" t="n">
@@ -17559,12 +17559,12 @@
       </c>
       <c r="E322" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06490321NJX</t>
+          <t>KIT4M05872563FWB</t>
         </is>
       </c>
       <c r="F322" s="4" t="inlineStr">
         <is>
-          <t>816219</t>
+          <t>816208</t>
         </is>
       </c>
       <c r="G322" s="5" t="inlineStr">
@@ -17654,7 +17654,7 @@
       </c>
       <c r="B324" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955042 - KIT4P00072391SZM</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649392 - KIT4M05368206BZP</t>
         </is>
       </c>
       <c r="C324" s="3" t="n">
@@ -17665,17 +17665,17 @@
       </c>
       <c r="E324" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00072391SZM</t>
+          <t>KIT4M05368206BZP</t>
         </is>
       </c>
       <c r="F324" s="4" t="inlineStr">
         <is>
-          <t>814493</t>
+          <t>810645</t>
         </is>
       </c>
       <c r="G324" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H324" s="5" t="inlineStr">
@@ -17707,7 +17707,7 @@
       </c>
       <c r="B325" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437972 - KIT4M06490327GMP</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437892 - KIT4M06490321NJX</t>
         </is>
       </c>
       <c r="C325" s="3" t="n">
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E325" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06490327GMP</t>
+          <t>KIT4M06490321NJX</t>
         </is>
       </c>
       <c r="F325" s="4" t="inlineStr">
         <is>
-          <t>816199</t>
+          <t>816219</t>
         </is>
       </c>
       <c r="G325" s="5" t="inlineStr">
@@ -17813,7 +17813,7 @@
       </c>
       <c r="B327" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437262 - KIT4P0008460369B</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437972 - KIT4M06490327GMP</t>
         </is>
       </c>
       <c r="C327" s="3" t="n">
@@ -17824,17 +17824,17 @@
       </c>
       <c r="E327" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0008460369B</t>
+          <t>KIT4M06490327GMP</t>
         </is>
       </c>
       <c r="F327" s="4" t="inlineStr">
         <is>
-          <t>816224</t>
+          <t>816199</t>
         </is>
       </c>
       <c r="G327" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H327" s="5" t="inlineStr">
@@ -17866,7 +17866,7 @@
       </c>
       <c r="B328" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649392 - KIT4M05368206BZP</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438062 - KIT4M05799676NNK</t>
         </is>
       </c>
       <c r="C328" s="3" t="n">
@@ -17877,12 +17877,12 @@
       </c>
       <c r="E328" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368206BZP</t>
+          <t>KIT4M05799676NNK</t>
         </is>
       </c>
       <c r="F328" s="4" t="inlineStr">
         <is>
-          <t>810645</t>
+          <t>816283</t>
         </is>
       </c>
       <c r="G328" s="5" t="inlineStr">
@@ -17919,7 +17919,7 @@
       </c>
       <c r="B329" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437982 - KIT4M05799678R5P</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438212 - KIT4M058725047FZ</t>
         </is>
       </c>
       <c r="C329" s="3" t="n">
@@ -17930,12 +17930,12 @@
       </c>
       <c r="E329" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799678R5P</t>
+          <t>KIT4M058725047FZ</t>
         </is>
       </c>
       <c r="F329" s="4" t="inlineStr">
         <is>
-          <t>816281</t>
+          <t>816289</t>
         </is>
       </c>
       <c r="G329" s="5" t="inlineStr">
@@ -17972,7 +17972,7 @@
       </c>
       <c r="B330" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955642 - KIT4M05563573WKC</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020955312 - KIT4M0556351956H</t>
         </is>
       </c>
       <c r="C330" s="3" t="n">
@@ -17983,12 +17983,12 @@
       </c>
       <c r="E330" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563573WKC</t>
+          <t>KIT4M0556351956H</t>
         </is>
       </c>
       <c r="F330" s="4" t="inlineStr">
         <is>
-          <t>814488</t>
+          <t>814477</t>
         </is>
       </c>
       <c r="G330" s="5" t="inlineStr">
@@ -18025,7 +18025,7 @@
       </c>
       <c r="B331" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438212 - KIT4M058725047FZ</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437982 - KIT4M05799678R5P</t>
         </is>
       </c>
       <c r="C331" s="3" t="n">
@@ -18036,12 +18036,12 @@
       </c>
       <c r="E331" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725047FZ</t>
+          <t>KIT4M05799678R5P</t>
         </is>
       </c>
       <c r="F331" s="4" t="inlineStr">
         <is>
-          <t>816289</t>
+          <t>816281</t>
         </is>
       </c>
       <c r="G331" s="5" t="inlineStr">
@@ -18078,7 +18078,7 @@
       </c>
       <c r="B332" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA -021437942 - KIT4M05799709G5Q</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438142  - KIT4M05799685DG5</t>
         </is>
       </c>
       <c r="C332" s="3" t="n">
@@ -18089,12 +18089,12 @@
       </c>
       <c r="E332" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799709G5Q</t>
+          <t>KIT4M05799685DG5</t>
         </is>
       </c>
       <c r="F332" s="4" t="inlineStr">
         <is>
-          <t>816274</t>
+          <t>816271</t>
         </is>
       </c>
       <c r="G332" s="5" t="inlineStr">
@@ -18131,7 +18131,7 @@
       </c>
       <c r="B333" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438062 - KIT4M05799676NNK</t>
+          <t>SMS - 05900510 - Los Angeles CA -021437942 - KIT4M05799709G5Q</t>
         </is>
       </c>
       <c r="C333" s="3" t="n">
@@ -18142,12 +18142,12 @@
       </c>
       <c r="E333" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799676NNK</t>
+          <t>KIT4M05799709G5Q</t>
         </is>
       </c>
       <c r="F333" s="4" t="inlineStr">
         <is>
-          <t>816283</t>
+          <t>816274</t>
         </is>
       </c>
       <c r="G333" s="5" t="inlineStr">
@@ -18184,7 +18184,7 @@
       </c>
       <c r="B334" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438142  - KIT4M05799685DG5</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438052 - KIT4M05872522W7W</t>
         </is>
       </c>
       <c r="C334" s="3" t="n">
@@ -18195,12 +18195,12 @@
       </c>
       <c r="E334" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799685DG5</t>
+          <t>KIT4M05872522W7W</t>
         </is>
       </c>
       <c r="F334" s="4" t="inlineStr">
         <is>
-          <t>816271</t>
+          <t>816217</t>
         </is>
       </c>
       <c r="G334" s="5" t="inlineStr">
@@ -18237,7 +18237,7 @@
       </c>
       <c r="B335" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020650222 - KIT4M05413790XCD</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437702 - KIT4M05872515PJT</t>
         </is>
       </c>
       <c r="C335" s="3" t="n">
@@ -18248,12 +18248,12 @@
       </c>
       <c r="E335" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413790XCD</t>
+          <t>KIT4M05872515PJT</t>
         </is>
       </c>
       <c r="F335" s="4" t="inlineStr">
         <is>
-          <t>812822</t>
+          <t>816218</t>
         </is>
       </c>
       <c r="G335" s="5" t="inlineStr">
@@ -18290,7 +18290,7 @@
       </c>
       <c r="B336" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437702 - KIT4M05872515PJT</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020650222 - KIT4M05413790XCD</t>
         </is>
       </c>
       <c r="C336" s="3" t="n">
@@ -18301,12 +18301,12 @@
       </c>
       <c r="E336" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872515PJT</t>
+          <t>KIT4M05413790XCD</t>
         </is>
       </c>
       <c r="F336" s="4" t="inlineStr">
         <is>
-          <t>816218</t>
+          <t>812822</t>
         </is>
       </c>
       <c r="G336" s="5" t="inlineStr">
@@ -18343,7 +18343,7 @@
       </c>
       <c r="B337" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438052 - KIT4M05872522W7W</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438272 - KIT4M05872517VS2</t>
         </is>
       </c>
       <c r="C337" s="3" t="n">
@@ -18354,12 +18354,12 @@
       </c>
       <c r="E337" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872522W7W</t>
+          <t>KIT4M05872517VS2</t>
         </is>
       </c>
       <c r="F337" s="4" t="inlineStr">
         <is>
-          <t>816217</t>
+          <t>816288</t>
         </is>
       </c>
       <c r="G337" s="5" t="inlineStr">
@@ -18396,7 +18396,7 @@
       </c>
       <c r="B338" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438272 - KIT4M05872517VS2</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437872 - KIT4M06490319DDN</t>
         </is>
       </c>
       <c r="C338" s="3" t="n">
@@ -18407,12 +18407,12 @@
       </c>
       <c r="E338" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872517VS2</t>
+          <t>KIT4M06490319DDN</t>
         </is>
       </c>
       <c r="F338" s="4" t="inlineStr">
         <is>
-          <t>816288</t>
+          <t>816220</t>
         </is>
       </c>
       <c r="G338" s="5" t="inlineStr">
@@ -18502,7 +18502,7 @@
       </c>
       <c r="B340" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918068FF</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437262 - KIT4P0008460369B</t>
         </is>
       </c>
       <c r="C340" s="3" t="n">
@@ -18513,17 +18513,17 @@
       </c>
       <c r="E340" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918068FF</t>
+          <t>KIT4P0008460369B</t>
         </is>
       </c>
       <c r="F340" s="4" t="inlineStr">
         <is>
-          <t>816400</t>
+          <t>816224</t>
         </is>
       </c>
       <c r="G340" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H340" s="5" t="inlineStr">
@@ -18555,7 +18555,7 @@
       </c>
       <c r="B341" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020649472-KIT4M05413795QHK</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918068FF</t>
         </is>
       </c>
       <c r="C341" s="3" t="n">
@@ -18566,12 +18566,12 @@
       </c>
       <c r="E341" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413795QHK</t>
+          <t>KIT4M064918068FF</t>
         </is>
       </c>
       <c r="F341" s="4" t="inlineStr">
         <is>
-          <t>812801</t>
+          <t>816400</t>
         </is>
       </c>
       <c r="G341" s="5" t="inlineStr">
@@ -18597,7 +18597,7 @@
       </c>
       <c r="L341" s="5" t="n"/>
       <c r="M341" s="7" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="342">
@@ -18608,7 +18608,7 @@
       </c>
       <c r="B342" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437642 - KIT4M05872590N8X</t>
+          <t>SMRT-05900510-Los Angeles CA-020649472-KIT4M05413795QHK</t>
         </is>
       </c>
       <c r="C342" s="3" t="n">
@@ -18619,12 +18619,12 @@
       </c>
       <c r="E342" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872590N8X</t>
+          <t>KIT4M05413795QHK</t>
         </is>
       </c>
       <c r="F342" s="4" t="inlineStr">
         <is>
-          <t>816204</t>
+          <t>812801</t>
         </is>
       </c>
       <c r="G342" s="5" t="inlineStr">
@@ -18650,7 +18650,7 @@
       </c>
       <c r="L342" s="5" t="n"/>
       <c r="M342" s="7" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="343">
@@ -18661,7 +18661,7 @@
       </c>
       <c r="B343" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438102 - KIT4M05872513F7N</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437642 - KIT4M05872590N8X</t>
         </is>
       </c>
       <c r="C343" s="3" t="n">
@@ -18672,12 +18672,12 @@
       </c>
       <c r="E343" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872513F7N</t>
+          <t>KIT4M05872590N8X</t>
         </is>
       </c>
       <c r="F343" s="4" t="inlineStr">
         <is>
-          <t>816161</t>
+          <t>816204</t>
         </is>
       </c>
       <c r="G343" s="5" t="inlineStr">
@@ -18703,7 +18703,7 @@
       </c>
       <c r="L343" s="5" t="n"/>
       <c r="M343" s="7" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="344">
@@ -18767,7 +18767,7 @@
       </c>
       <c r="B345" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438012 - KIT4M05799715GJ2</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438102 - KIT4M05872513F7N</t>
         </is>
       </c>
       <c r="C345" s="3" t="n">
@@ -18778,16 +18778,24 @@
       </c>
       <c r="E345" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799715GJ2</t>
-        </is>
-      </c>
-      <c r="F345" s="8" t="n"/>
+          <t>KIT4M05872513F7N</t>
+        </is>
+      </c>
+      <c r="F345" s="4" t="inlineStr">
+        <is>
+          <t>816161</t>
+        </is>
+      </c>
       <c r="G345" s="5" t="inlineStr">
         <is>
           <t>Mini</t>
         </is>
       </c>
-      <c r="H345" s="5" t="n"/>
+      <c r="H345" s="5" t="inlineStr">
+        <is>
+          <t>Master Serial List</t>
+        </is>
+      </c>
       <c r="I345" s="6" t="n">
         <v>46235</v>
       </c>
@@ -18801,7 +18809,7 @@
       </c>
       <c r="L345" s="5" t="n"/>
       <c r="M345" s="7" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="346">
@@ -18812,7 +18820,7 @@
       </c>
       <c r="B346" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437922 - KIT4M05872496MW6</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649922 - KIT4M05413780XFH</t>
         </is>
       </c>
       <c r="C346" s="3" t="n">
@@ -18823,12 +18831,12 @@
       </c>
       <c r="E346" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872496MW6</t>
+          <t>KIT4M05413780XFH</t>
         </is>
       </c>
       <c r="F346" s="4" t="inlineStr">
         <is>
-          <t>816206</t>
+          <t>812833</t>
         </is>
       </c>
       <c r="G346" s="5" t="inlineStr">
@@ -18918,7 +18926,7 @@
       </c>
       <c r="B348" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649482 - KIT4M054137938P7</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649952 - KIT4M05413782GHW</t>
         </is>
       </c>
       <c r="C348" s="3" t="n">
@@ -18929,12 +18937,12 @@
       </c>
       <c r="E348" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137938P7</t>
+          <t>KIT4M05413782GHW</t>
         </is>
       </c>
       <c r="F348" s="4" t="inlineStr">
         <is>
-          <t>812848</t>
+          <t>812835</t>
         </is>
       </c>
       <c r="G348" s="5" t="inlineStr">
@@ -18971,7 +18979,7 @@
       </c>
       <c r="B349" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955162 - KIT4M05563554WCW</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955442 - KIT4M05563503XXP</t>
         </is>
       </c>
       <c r="C349" s="3" t="n">
@@ -18982,12 +18990,12 @@
       </c>
       <c r="E349" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563554WCW</t>
+          <t>KIT4M05563503XXP</t>
         </is>
       </c>
       <c r="F349" s="4" t="inlineStr">
         <is>
-          <t>814444</t>
+          <t>814430</t>
         </is>
       </c>
       <c r="G349" s="5" t="inlineStr">
@@ -19024,7 +19032,7 @@
       </c>
       <c r="B350" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827011116 - KIT4M02578775B9Q</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955562 - KIT4M05563505WPS</t>
         </is>
       </c>
       <c r="C350" s="3" t="n">
@@ -19035,12 +19043,12 @@
       </c>
       <c r="E350" s="2" t="inlineStr">
         <is>
-          <t>KIT4M02578775B9Q</t>
+          <t>KIT4M05563505WPS</t>
         </is>
       </c>
       <c r="F350" s="4" t="inlineStr">
         <is>
-          <t>809611</t>
+          <t>814448</t>
         </is>
       </c>
       <c r="G350" s="5" t="inlineStr">
@@ -19077,7 +19085,7 @@
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020650092 - KIT4M05413830JN7</t>
+          <t>USPS - 05900510 - Los Angeles CA - CW6892232 - KIT4P00084601T5F</t>
         </is>
       </c>
       <c r="C351" s="3" t="n">
@@ -19088,17 +19096,17 @@
       </c>
       <c r="E351" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413830JN7</t>
+          <t>KIT4P00084601T5F</t>
         </is>
       </c>
       <c r="F351" s="4" t="inlineStr">
         <is>
-          <t>810105</t>
+          <t>816335</t>
         </is>
       </c>
       <c r="G351" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H351" s="5" t="inlineStr">
@@ -19130,7 +19138,7 @@
       </c>
       <c r="B352" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649612 - KIT4M05413827DC4</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955222 - KIT4M05563536BPJ</t>
         </is>
       </c>
       <c r="C352" s="3" t="n">
@@ -19141,12 +19149,12 @@
       </c>
       <c r="E352" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413827DC4</t>
+          <t>KIT4M05563536BPJ</t>
         </is>
       </c>
       <c r="F352" s="4" t="inlineStr">
         <is>
-          <t>812829</t>
+          <t>814466</t>
         </is>
       </c>
       <c r="G352" s="5" t="inlineStr">
@@ -19183,7 +19191,7 @@
       </c>
       <c r="B353" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955442 - KIT4M05563503XXP</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649612 - KIT4M05413827DC4</t>
         </is>
       </c>
       <c r="C353" s="3" t="n">
@@ -19194,12 +19202,12 @@
       </c>
       <c r="E353" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563503XXP</t>
+          <t>KIT4M05413827DC4</t>
         </is>
       </c>
       <c r="F353" s="4" t="inlineStr">
         <is>
-          <t>814430</t>
+          <t>812829</t>
         </is>
       </c>
       <c r="G353" s="5" t="inlineStr">
@@ -19236,7 +19244,7 @@
       </c>
       <c r="B354" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955222 - KIT4M05563536BPJ</t>
+          <t>STS - 05900510 - Los Angeles CA - 020650092 - KIT4M05413830JN7</t>
         </is>
       </c>
       <c r="C354" s="3" t="n">
@@ -19247,12 +19255,12 @@
       </c>
       <c r="E354" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563536BPJ</t>
+          <t>KIT4M05413830JN7</t>
         </is>
       </c>
       <c r="F354" s="4" t="inlineStr">
         <is>
-          <t>814466</t>
+          <t>810105</t>
         </is>
       </c>
       <c r="G354" s="5" t="inlineStr">
@@ -19289,7 +19297,7 @@
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>USPS - 05900510 - Los Angeles CA - CW6892232 - KIT4P00084601T5F</t>
+          <t>SMA - 05900510 - Los Angeles CA - CW6892232 - KIT4P000832637V6</t>
         </is>
       </c>
       <c r="C355" s="3" t="n">
@@ -19300,12 +19308,12 @@
       </c>
       <c r="E355" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00084601T5F</t>
+          <t>KIT4P000832637V6</t>
         </is>
       </c>
       <c r="F355" s="4" t="inlineStr">
         <is>
-          <t>816335</t>
+          <t>816334</t>
         </is>
       </c>
       <c r="G355" s="5" t="inlineStr">
@@ -19342,7 +19350,7 @@
       </c>
       <c r="B356" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955562 - KIT4M05563505WPS</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482701114 - KIT4M03476114VCM</t>
         </is>
       </c>
       <c r="C356" s="3" t="n">
@@ -19353,12 +19361,12 @@
       </c>
       <c r="E356" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563505WPS</t>
+          <t>KIT4M03476114VCM</t>
         </is>
       </c>
       <c r="F356" s="4" t="inlineStr">
         <is>
-          <t>814448</t>
+          <t>809613</t>
         </is>
       </c>
       <c r="G356" s="5" t="inlineStr">
@@ -19395,7 +19403,7 @@
       </c>
       <c r="B357" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - CW6892232 - KIT4P000832637V6</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827011116 - KIT4M02578775B9Q</t>
         </is>
       </c>
       <c r="C357" s="3" t="n">
@@ -19406,17 +19414,17 @@
       </c>
       <c r="E357" s="2" t="inlineStr">
         <is>
-          <t>KIT4P000832637V6</t>
+          <t>KIT4M02578775B9Q</t>
         </is>
       </c>
       <c r="F357" s="4" t="inlineStr">
         <is>
-          <t>816334</t>
+          <t>809611</t>
         </is>
       </c>
       <c r="G357" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H357" s="5" t="inlineStr">
@@ -19448,7 +19456,7 @@
       </c>
       <c r="B358" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482701114 - KIT4M03476114VCM</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438012 - KIT4M05799715GJ2</t>
         </is>
       </c>
       <c r="C358" s="3" t="n">
@@ -19459,24 +19467,16 @@
       </c>
       <c r="E358" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03476114VCM</t>
-        </is>
-      </c>
-      <c r="F358" s="4" t="inlineStr">
-        <is>
-          <t>809613</t>
-        </is>
-      </c>
+          <t>KIT4M05799715GJ2</t>
+        </is>
+      </c>
+      <c r="F358" s="8" t="n"/>
       <c r="G358" s="5" t="inlineStr">
         <is>
           <t>Mini</t>
         </is>
       </c>
-      <c r="H358" s="5" t="inlineStr">
-        <is>
-          <t>Master Serial List</t>
-        </is>
-      </c>
+      <c r="H358" s="5" t="n"/>
       <c r="I358" s="6" t="n">
         <v>46235</v>
       </c>
@@ -19501,7 +19501,7 @@
       </c>
       <c r="B359" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020650032-KIT4M05413802FVN</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437922 - KIT4M05872496MW6</t>
         </is>
       </c>
       <c r="C359" s="3" t="n">
@@ -19512,12 +19512,12 @@
       </c>
       <c r="E359" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413802FVN</t>
+          <t>KIT4M05872496MW6</t>
         </is>
       </c>
       <c r="F359" s="4" t="inlineStr">
         <is>
-          <t>812813</t>
+          <t>816206</t>
         </is>
       </c>
       <c r="G359" s="5" t="inlineStr">
@@ -19554,7 +19554,7 @@
       </c>
       <c r="B360" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 020955572 - KIT4M05563606ZRC</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649482 - KIT4M054137938P7</t>
         </is>
       </c>
       <c r="C360" s="3" t="n">
@@ -19565,12 +19565,12 @@
       </c>
       <c r="E360" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563606ZRC</t>
+          <t>KIT4M054137938P7</t>
         </is>
       </c>
       <c r="F360" s="4" t="inlineStr">
         <is>
-          <t>814464</t>
+          <t>812848</t>
         </is>
       </c>
       <c r="G360" s="5" t="inlineStr">
@@ -19607,7 +19607,7 @@
       </c>
       <c r="B361" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649952 - KIT4M05413782GHW</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649502 - KIT4M05413801QJB</t>
         </is>
       </c>
       <c r="C361" s="3" t="n">
@@ -19618,12 +19618,12 @@
       </c>
       <c r="E361" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413782GHW</t>
+          <t>KIT4M05413801QJB</t>
         </is>
       </c>
       <c r="F361" s="4" t="inlineStr">
         <is>
-          <t>812835</t>
+          <t>812824</t>
         </is>
       </c>
       <c r="G361" s="5" t="inlineStr">
@@ -19660,7 +19660,7 @@
       </c>
       <c r="B362" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649922 - KIT4M05413780XFH</t>
+          <t>SMRT-05900510-Los Angeles CA-020650032-KIT4M05413802FVN</t>
         </is>
       </c>
       <c r="C362" s="3" t="n">
@@ -19671,12 +19671,12 @@
       </c>
       <c r="E362" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413780XFH</t>
+          <t>KIT4M05413802FVN</t>
         </is>
       </c>
       <c r="F362" s="4" t="inlineStr">
         <is>
-          <t>812833</t>
+          <t>812813</t>
         </is>
       </c>
       <c r="G362" s="5" t="inlineStr">
@@ -19766,7 +19766,7 @@
       </c>
       <c r="B364" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649502 - KIT4M05413801QJB</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955162 - KIT4M05563554WCW</t>
         </is>
       </c>
       <c r="C364" s="3" t="n">
@@ -19777,12 +19777,12 @@
       </c>
       <c r="E364" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413801QJB</t>
+          <t>KIT4M05563554WCW</t>
         </is>
       </c>
       <c r="F364" s="4" t="inlineStr">
         <is>
-          <t>812824</t>
+          <t>814444</t>
         </is>
       </c>
       <c r="G364" s="5" t="inlineStr">
@@ -20219,7 +20219,7 @@
     <row r="381">
       <c r="A381" s="15" t="inlineStr">
         <is>
-          <t>Generated 2026-08-28 12:01 by build_starlink_usage.py</t>
+          <t>Generated 2026-08-28 21:09 by build_starlink_usage.py</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_Current_by_Kit.xlsx
+++ b/Starlink_Usage_Current_by_Kit.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="L3" s="5" t="n"/>
       <c r="M3" s="7" t="n">
-        <v>2263.71</v>
+        <v>2268.85</v>
       </c>
     </row>
     <row r="4">
@@ -842,7 +842,7 @@
       </c>
       <c r="L6" s="5" t="n"/>
       <c r="M6" s="7" t="n">
-        <v>1097.27</v>
+        <v>1105.12</v>
       </c>
     </row>
     <row r="7">
@@ -948,7 +948,7 @@
       </c>
       <c r="L8" s="5" t="n"/>
       <c r="M8" s="7" t="n">
-        <v>840.1799999999999</v>
+        <v>915.73</v>
       </c>
     </row>
     <row r="9">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="L13" s="5" t="n"/>
       <c r="M13" s="7" t="n">
-        <v>728</v>
+        <v>731.5</v>
       </c>
     </row>
     <row r="14">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L14" s="5" t="n"/>
       <c r="M14" s="7" t="n">
-        <v>723.16</v>
+        <v>723.95</v>
       </c>
     </row>
     <row r="15">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="L15" s="5" t="n"/>
       <c r="M15" s="7" t="n">
-        <v>660.9299999999999</v>
+        <v>673.29</v>
       </c>
     </row>
     <row r="16">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="L16" s="5" t="n"/>
       <c r="M16" s="7" t="n">
-        <v>660.7</v>
+        <v>665.78</v>
       </c>
     </row>
     <row r="17">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="L18" s="5" t="n"/>
       <c r="M18" s="7" t="n">
-        <v>498.72</v>
+        <v>502.06</v>
       </c>
     </row>
     <row r="19">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="L21" s="5" t="n"/>
       <c r="M21" s="7" t="n">
-        <v>419.85</v>
+        <v>422.65</v>
       </c>
     </row>
     <row r="22">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="L27" s="5" t="n"/>
       <c r="M27" s="7" t="n">
-        <v>272.4</v>
+        <v>273.22</v>
       </c>
     </row>
     <row r="28">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="L28" s="5" t="n"/>
       <c r="M28" s="7" t="n">
-        <v>254</v>
+        <v>254.72</v>
       </c>
     </row>
     <row r="29">
@@ -2019,7 +2019,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482701118 - KIT4M04158951RH6</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437422 - KIT4M05872536JFD</t>
         </is>
       </c>
       <c r="C29" s="3" t="n">
@@ -2030,12 +2030,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158951RH6</t>
+          <t>KIT4M05872536JFD</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>809614</t>
+          <t>816070</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="L29" s="5" t="n"/>
       <c r="M29" s="7" t="n">
-        <v>251.27</v>
+        <v>253.43</v>
       </c>
     </row>
     <row r="30">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437422 - KIT4M05872536JFD</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482701118 - KIT4M04158951RH6</t>
         </is>
       </c>
       <c r="C30" s="3" t="n">
@@ -2083,12 +2083,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872536JFD</t>
+          <t>KIT4M04158951RH6</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>816070</t>
+          <t>809614</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="L30" s="5" t="n"/>
       <c r="M30" s="7" t="n">
-        <v>248.24</v>
+        <v>251.27</v>
       </c>
     </row>
     <row r="31">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="L32" s="5" t="n"/>
       <c r="M32" s="7" t="n">
-        <v>223.01</v>
+        <v>237.4</v>
       </c>
     </row>
     <row r="33">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020649462-KIT4M05413796V9K</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438032 - KIT4M05799683GCK</t>
         </is>
       </c>
       <c r="C33" s="3" t="n">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413796V9K</t>
+          <t>KIT4M05799683GCK</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>812820</t>
+          <t>816270</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="L33" s="5" t="n"/>
       <c r="M33" s="7" t="n">
-        <v>220.94</v>
+        <v>222.99</v>
       </c>
     </row>
     <row r="34">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438032 - KIT4M05799683GCK</t>
+          <t>SMRT-05900510-Los Angeles CA-020649462-KIT4M05413796V9K</t>
         </is>
       </c>
       <c r="C34" s="3" t="n">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799683GCK</t>
+          <t>KIT4M05413796V9K</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>816270</t>
+          <t>812820</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
@@ -2326,7 +2326,7 @@
       </c>
       <c r="L34" s="5" t="n"/>
       <c r="M34" s="7" t="n">
-        <v>211.17</v>
+        <v>220.94</v>
       </c>
     </row>
     <row r="35">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="L35" s="5" t="n"/>
       <c r="M35" s="7" t="n">
-        <v>163.04</v>
+        <v>167.01</v>
       </c>
     </row>
     <row r="36">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827018 - KIT4M0415609166K</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955522 - KIT4M05563504MBB</t>
         </is>
       </c>
       <c r="C36" s="3" t="n">
@@ -2401,12 +2401,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0415609166K</t>
+          <t>KIT4M05563504MBB</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>809609</t>
+          <t>814460</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="L36" s="5" t="n"/>
       <c r="M36" s="7" t="n">
-        <v>157.15</v>
+        <v>159.14</v>
       </c>
     </row>
     <row r="37">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482701116 - KIT4M03986275Q4M</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827018 - KIT4M0415609166K</t>
         </is>
       </c>
       <c r="C37" s="3" t="n">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03986275Q4M</t>
+          <t>KIT4M0415609166K</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>809621</t>
+          <t>809609</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="L37" s="5" t="n"/>
       <c r="M37" s="7" t="n">
-        <v>143.69</v>
+        <v>158.76</v>
       </c>
     </row>
     <row r="38">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955522 - KIT4M05563504MBB</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482701116 - KIT4M03986275Q4M</t>
         </is>
       </c>
       <c r="C38" s="3" t="n">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563504MBB</t>
+          <t>KIT4M03986275Q4M</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>814460</t>
+          <t>809621</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="L38" s="5" t="n"/>
       <c r="M38" s="7" t="n">
-        <v>139.55</v>
+        <v>151.92</v>
       </c>
     </row>
     <row r="39">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="L39" s="5" t="n"/>
       <c r="M39" s="7" t="n">
-        <v>137.86</v>
+        <v>138.22</v>
       </c>
     </row>
     <row r="40">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="L40" s="5" t="n"/>
       <c r="M40" s="7" t="n">
-        <v>132.23</v>
+        <v>136.41</v>
       </c>
     </row>
     <row r="41">
@@ -2655,7 +2655,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955672 - KIT4M055635979XD</t>
+          <t>SS - 05900510 - Los Angeles CA - CW6578840- KIT4M04475128THH</t>
         </is>
       </c>
       <c r="C41" s="3" t="n">
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635979XD</t>
+          <t>KIT4M04475128THH</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>814441</t>
+          <t>809860</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="L41" s="5" t="n"/>
       <c r="M41" s="7" t="n">
-        <v>127.97</v>
+        <v>133.25</v>
       </c>
     </row>
     <row r="42">
@@ -2708,7 +2708,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 -  Los Angeles CA - 020649422 - KIT4M05368200MVF</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827014 - KIT4M04475149XG5</t>
         </is>
       </c>
       <c r="C42" s="3" t="n">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368200MVF</t>
+          <t>KIT4M04475149XG5</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>810650</t>
+          <t>809657</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="L42" s="5" t="n"/>
       <c r="M42" s="7" t="n">
-        <v>126.59</v>
+        <v>128.45</v>
       </c>
     </row>
     <row r="43">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649842 - KIT4M025787739XF</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955672 - KIT4M055635979XD</t>
         </is>
       </c>
       <c r="C43" s="3" t="n">
@@ -2772,12 +2772,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>KIT4M025787739XF</t>
+          <t>KIT4M055635979XD</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>809864</t>
+          <t>814441</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="L43" s="5" t="n"/>
       <c r="M43" s="7" t="n">
-        <v>124.46</v>
+        <v>128.24</v>
       </c>
     </row>
     <row r="44">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955632 - KIT4M055635329VD</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955182 - KIT4M05563562F45</t>
         </is>
       </c>
       <c r="C44" s="3" t="n">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635329VD</t>
+          <t>KIT4M05563562F45</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>814479</t>
+          <t>814443</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="L44" s="5" t="n"/>
       <c r="M44" s="7" t="n">
-        <v>124.25</v>
+        <v>126.95</v>
       </c>
     </row>
     <row r="45">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827014 - KIT4M04475149XG5</t>
+          <t>SMA - 05900510 -  Los Angeles CA - 020649422 - KIT4M05368200MVF</t>
         </is>
       </c>
       <c r="C45" s="3" t="n">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475149XG5</t>
+          <t>KIT4M05368200MVF</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>809657</t>
+          <t>810650</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="L45" s="5" t="n"/>
       <c r="M45" s="7" t="n">
-        <v>121.29</v>
+        <v>126.59</v>
       </c>
     </row>
     <row r="46">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437252 - KIT4P00083897XCW</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649842 - KIT4M025787739XF</t>
         </is>
       </c>
       <c r="C46" s="3" t="n">
@@ -2931,17 +2931,17 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00083897XCW</t>
+          <t>KIT4M025787739XF</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>816223</t>
+          <t>809864</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H46" s="5" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="L46" s="5" t="n"/>
       <c r="M46" s="7" t="n">
-        <v>120.74</v>
+        <v>125.77</v>
       </c>
     </row>
     <row r="47">
@@ -2973,7 +2973,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955182 - KIT4M05563562F45</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955632 - KIT4M055635329VD</t>
         </is>
       </c>
       <c r="C47" s="3" t="n">
@@ -2984,12 +2984,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563562F45</t>
+          <t>KIT4M055635329VD</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>814443</t>
+          <t>814479</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="L47" s="5" t="n"/>
       <c r="M47" s="7" t="n">
-        <v>117.66</v>
+        <v>124.26</v>
       </c>
     </row>
     <row r="48">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - CW6578840- KIT4M04475128THH</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437252 - KIT4P00083897XCW</t>
         </is>
       </c>
       <c r="C48" s="3" t="n">
@@ -3037,17 +3037,17 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475128THH</t>
+          <t>KIT4P00083897XCW</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>809860</t>
+          <t>816223</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H48" s="5" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="L48" s="5" t="n"/>
       <c r="M48" s="7" t="n">
-        <v>116.56</v>
+        <v>120.74</v>
       </c>
     </row>
     <row r="49">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="L52" s="5" t="n"/>
       <c r="M52" s="7" t="n">
-        <v>102.98</v>
+        <v>103.65</v>
       </c>
     </row>
     <row r="53">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="L54" s="5" t="n"/>
       <c r="M54" s="7" t="n">
-        <v>97.69</v>
+        <v>99.06</v>
       </c>
     </row>
     <row r="55">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="L55" s="5" t="n"/>
       <c r="M55" s="7" t="n">
-        <v>96.63</v>
+        <v>97.09</v>
       </c>
     </row>
     <row r="56">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438042 - KIT4M05799686CMX</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955662 - KIT4M05563574ZBN</t>
         </is>
       </c>
       <c r="C56" s="3" t="n">
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799686CMX</t>
+          <t>KIT4M05563574ZBN</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>816282</t>
+          <t>814453</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="L56" s="5" t="n"/>
       <c r="M56" s="7" t="n">
-        <v>94.92</v>
+        <v>95.76000000000001</v>
       </c>
     </row>
     <row r="57">
@@ -3503,7 +3503,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020650232 - KIT4M054138222CP</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438042 - KIT4M05799686CMX</t>
         </is>
       </c>
       <c r="C57" s="3" t="n">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138222CP</t>
+          <t>KIT4M05799686CMX</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>812811</t>
+          <t>816282</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="L57" s="5" t="n"/>
       <c r="M57" s="7" t="n">
-        <v>93.27</v>
+        <v>94.92</v>
       </c>
     </row>
     <row r="58">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955662 - KIT4M05563574ZBN</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649782 - KIT4M03986264P49</t>
         </is>
       </c>
       <c r="C58" s="3" t="n">
@@ -3567,12 +3567,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563574ZBN</t>
+          <t>KIT4M03986264P49</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>814453</t>
+          <t>809875</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="L58" s="5" t="n"/>
       <c r="M58" s="7" t="n">
-        <v>91.91</v>
+        <v>94.79000000000001</v>
       </c>
     </row>
     <row r="59">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955472 - KIT4M055635834N7</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020650232 - KIT4M054138222CP</t>
         </is>
       </c>
       <c r="C59" s="3" t="n">
@@ -3620,12 +3620,12 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635834N7</t>
+          <t>KIT4M054138222CP</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>814462</t>
+          <t>812811</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
@@ -3651,7 +3651,7 @@
       </c>
       <c r="L59" s="5" t="n"/>
       <c r="M59" s="7" t="n">
-        <v>89.20999999999999</v>
+        <v>93.27</v>
       </c>
     </row>
     <row r="60">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649782 - KIT4M03986264P49</t>
+          <t>SS - 05900510 - Los Angeles CA - 020650102 - KIT4M054138257Z7</t>
         </is>
       </c>
       <c r="C60" s="3" t="n">
@@ -3673,12 +3673,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03986264P49</t>
+          <t>KIT4M054138257Z7</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>809875</t>
+          <t>810106</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="L60" s="5" t="n"/>
       <c r="M60" s="7" t="n">
-        <v>86.77</v>
+        <v>91.68000000000001</v>
       </c>
     </row>
     <row r="61">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955142 - KIT4M05563518ZJD</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955472 - KIT4M055635834N7</t>
         </is>
       </c>
       <c r="C61" s="3" t="n">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563518ZJD</t>
+          <t>KIT4M055635834N7</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>814451</t>
+          <t>814462</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
@@ -3757,7 +3757,7 @@
       </c>
       <c r="L61" s="5" t="n"/>
       <c r="M61" s="7" t="n">
-        <v>85.18000000000001</v>
+        <v>89.45</v>
       </c>
     </row>
     <row r="62">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649872 - KIT4M054138175VJ</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955142 - KIT4M05563518ZJD</t>
         </is>
       </c>
       <c r="C62" s="3" t="n">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138175VJ</t>
+          <t>KIT4M05563518ZJD</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>812823</t>
+          <t>814451</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="L62" s="5" t="n"/>
       <c r="M62" s="7" t="n">
-        <v>83.95</v>
+        <v>85.18000000000001</v>
       </c>
     </row>
     <row r="63">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955332 - KIT4M05563590ZFQ</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649872 - KIT4M054138175VJ</t>
         </is>
       </c>
       <c r="C63" s="3" t="n">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563590ZFQ</t>
+          <t>KIT4M054138175VJ</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>814461</t>
+          <t>812823</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="L63" s="5" t="n"/>
       <c r="M63" s="7" t="n">
-        <v>81.84999999999999</v>
+        <v>83.95</v>
       </c>
     </row>
     <row r="64">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649712 - KIT4M046047397TM</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955332 - KIT4M05563590ZFQ</t>
         </is>
       </c>
       <c r="C64" s="3" t="n">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047397TM</t>
+          <t>KIT4M05563590ZFQ</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>809863</t>
+          <t>814461</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="L64" s="5" t="n"/>
       <c r="M64" s="7" t="n">
-        <v>80.01000000000001</v>
+        <v>83.88</v>
       </c>
     </row>
     <row r="65">
@@ -3927,7 +3927,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020649312-KIT4M05413771PVH</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649712 - KIT4M046047397TM</t>
         </is>
       </c>
       <c r="C65" s="3" t="n">
@@ -3938,12 +3938,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413771PVH</t>
+          <t>KIT4M046047397TM</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>812800</t>
+          <t>809863</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="L65" s="5" t="n"/>
       <c r="M65" s="7" t="n">
-        <v>78.69</v>
+        <v>83.59999999999999</v>
       </c>
     </row>
     <row r="66">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955112 - KIT4P00073918HBX</t>
+          <t>SMRT-05900510-Los Angeles CA-020649312-KIT4M05413771PVH</t>
         </is>
       </c>
       <c r="C66" s="3" t="n">
@@ -3991,17 +3991,17 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073918HBX</t>
+          <t>KIT4M05413771PVH</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>814645</t>
+          <t>812800</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H66" s="5" t="inlineStr">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="L66" s="5" t="n"/>
       <c r="M66" s="7" t="n">
-        <v>77.8</v>
+        <v>79.63</v>
       </c>
     </row>
     <row r="67">
@@ -4033,7 +4033,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649562 - KIT4M054138125NW</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955112 - KIT4P00073918HBX</t>
         </is>
       </c>
       <c r="C67" s="3" t="n">
@@ -4044,17 +4044,17 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138125NW</t>
+          <t>KIT4P00073918HBX</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>812826</t>
+          <t>814645</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H67" s="5" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="L67" s="5" t="n"/>
       <c r="M67" s="7" t="n">
-        <v>77.14</v>
+        <v>79.54000000000001</v>
       </c>
     </row>
     <row r="68">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020650012 - KIT4M05413814GPJ</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649562 - KIT4M054138125NW</t>
         </is>
       </c>
       <c r="C68" s="3" t="n">
@@ -4097,12 +4097,12 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413814GPJ</t>
+          <t>KIT4M054138125NW</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>812812</t>
+          <t>812826</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="L68" s="5" t="n"/>
       <c r="M68" s="7" t="n">
-        <v>75.04000000000001</v>
+        <v>77.14</v>
       </c>
     </row>
     <row r="69">
@@ -4139,7 +4139,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955492 - KIT4M05563520SH2</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020650012 - KIT4M05413814GPJ</t>
         </is>
       </c>
       <c r="C69" s="3" t="n">
@@ -4150,12 +4150,12 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563520SH2</t>
+          <t>KIT4M05413814GPJ</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>814478</t>
+          <t>812812</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="L69" s="5" t="n"/>
       <c r="M69" s="7" t="n">
-        <v>74.56999999999999</v>
+        <v>76.54000000000001</v>
       </c>
     </row>
     <row r="70">
@@ -4192,7 +4192,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955092 - KIT4P00073957GV5</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955492 - KIT4M05563520SH2</t>
         </is>
       </c>
       <c r="C70" s="3" t="n">
@@ -4203,17 +4203,17 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073957GV5</t>
+          <t>KIT4M05563520SH2</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>814642</t>
+          <t>814478</t>
         </is>
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H70" s="5" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="L70" s="5" t="n"/>
       <c r="M70" s="7" t="n">
-        <v>72.83</v>
+        <v>74.56999999999999</v>
       </c>
     </row>
     <row r="71">
@@ -4287,7 +4287,7 @@
       </c>
       <c r="L71" s="5" t="n"/>
       <c r="M71" s="7" t="n">
-        <v>71.98999999999999</v>
+        <v>74.44</v>
       </c>
     </row>
     <row r="72">
@@ -4298,7 +4298,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020650102 - KIT4M054138257Z7</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955092 - KIT4P00073957GV5</t>
         </is>
       </c>
       <c r="C72" s="3" t="n">
@@ -4309,17 +4309,17 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138257Z7</t>
+          <t>KIT4P00073957GV5</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>810106</t>
+          <t>814642</t>
         </is>
       </c>
       <c r="G72" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H72" s="5" t="inlineStr">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="L72" s="5" t="n"/>
       <c r="M72" s="7" t="n">
-        <v>70.05</v>
+        <v>72.83</v>
       </c>
     </row>
     <row r="73">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="L73" s="5" t="n"/>
       <c r="M73" s="7" t="n">
-        <v>69.94</v>
+        <v>71.47</v>
       </c>
     </row>
     <row r="74">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="L75" s="5" t="n"/>
       <c r="M75" s="7" t="n">
-        <v>65.87</v>
+        <v>67.38</v>
       </c>
     </row>
     <row r="76">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649342 - KIT4M05413775N9M</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649932 - KIT4M054138324MW</t>
         </is>
       </c>
       <c r="C76" s="3" t="n">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413775N9M</t>
+          <t>KIT4M054138324MW</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>812818</t>
+          <t>812834</t>
         </is>
       </c>
       <c r="G76" s="5" t="inlineStr">
@@ -4552,7 +4552,7 @@
       </c>
       <c r="L76" s="5" t="n"/>
       <c r="M76" s="7" t="n">
-        <v>62.51</v>
+        <v>65.69</v>
       </c>
     </row>
     <row r="77">
@@ -4563,7 +4563,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020650252 - KIT4M05413820QXJ</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649342 - KIT4M05413775N9M</t>
         </is>
       </c>
       <c r="C77" s="3" t="n">
@@ -4574,12 +4574,12 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413820QXJ</t>
+          <t>KIT4M05413775N9M</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>810098</t>
+          <t>812818</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr">
@@ -4605,7 +4605,7 @@
       </c>
       <c r="L77" s="5" t="n"/>
       <c r="M77" s="7" t="n">
-        <v>61.69</v>
+        <v>62.78</v>
       </c>
     </row>
     <row r="78">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="L78" s="5" t="n"/>
       <c r="M78" s="7" t="n">
-        <v>59.97</v>
+        <v>62.75</v>
       </c>
     </row>
     <row r="79">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649902 - KIT4M05413805MKQ</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020650252 - KIT4M05413820QXJ</t>
         </is>
       </c>
       <c r="C79" s="3" t="n">
@@ -4680,12 +4680,12 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413805MKQ</t>
+          <t>KIT4M05413820QXJ</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>812849</t>
+          <t>810098</t>
         </is>
       </c>
       <c r="G79" s="5" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="L79" s="5" t="n"/>
       <c r="M79" s="7" t="n">
-        <v>59.45</v>
+        <v>61.69</v>
       </c>
     </row>
     <row r="80">
@@ -4722,7 +4722,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482702 - KIT4M04604743HSS</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955262 - KIT4M05563521ZSX</t>
         </is>
       </c>
       <c r="C80" s="3" t="n">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604743HSS</t>
+          <t>KIT4M05563521ZSX</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>809663</t>
+          <t>814476</t>
         </is>
       </c>
       <c r="G80" s="5" t="inlineStr">
@@ -4764,7 +4764,7 @@
       </c>
       <c r="L80" s="5" t="n"/>
       <c r="M80" s="7" t="n">
-        <v>59.03</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="81">
@@ -4775,7 +4775,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955262 - KIT4M05563521ZSX</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649902 - KIT4M05413805MKQ</t>
         </is>
       </c>
       <c r="C81" s="3" t="n">
@@ -4786,12 +4786,12 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563521ZSX</t>
+          <t>KIT4M05413805MKQ</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>814476</t>
+          <t>812849</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="L81" s="5" t="n"/>
       <c r="M81" s="7" t="n">
-        <v>58.47</v>
+        <v>59.46</v>
       </c>
     </row>
     <row r="82">
@@ -4828,7 +4828,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649932 - KIT4M054138324MW</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482702 - KIT4M04604743HSS</t>
         </is>
       </c>
       <c r="C82" s="3" t="n">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138324MW</t>
+          <t>KIT4M04604743HSS</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>812834</t>
+          <t>809663</t>
         </is>
       </c>
       <c r="G82" s="5" t="inlineStr">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="L82" s="5" t="n"/>
       <c r="M82" s="7" t="n">
-        <v>58.27</v>
+        <v>59.03</v>
       </c>
     </row>
     <row r="83">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482704 - KIT4M04604745G8Z</t>
+          <t>SMRT-05900510-Los Angeles, CA-020955352-KIT4M05563525VC6</t>
         </is>
       </c>
       <c r="C83" s="3" t="n">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604745G8Z</t>
+          <t>KIT4M05563525VC6</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>809661</t>
+          <t>814458</t>
         </is>
       </c>
       <c r="G83" s="5" t="inlineStr">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="L83" s="5" t="n"/>
       <c r="M83" s="7" t="n">
-        <v>57.14</v>
+        <v>57.37</v>
       </c>
     </row>
     <row r="84">
@@ -4934,7 +4934,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955412 - KIT4M05563598Z74</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482704 - KIT4M04604745G8Z</t>
         </is>
       </c>
       <c r="C84" s="3" t="n">
@@ -4945,12 +4945,12 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563598Z74</t>
+          <t>KIT4M04604745G8Z</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>814474</t>
+          <t>809661</t>
         </is>
       </c>
       <c r="G84" s="5" t="inlineStr">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="L84" s="5" t="n"/>
       <c r="M84" s="7" t="n">
-        <v>54.27</v>
+        <v>57.14</v>
       </c>
     </row>
     <row r="85">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827011118 - KIT4M03867766NGK</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437392 - KIT4M05872555BJR</t>
         </is>
       </c>
       <c r="C85" s="3" t="n">
@@ -4998,12 +4998,12 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03867766NGK</t>
+          <t>KIT4M05872555BJR</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>809615</t>
+          <t>816074</t>
         </is>
       </c>
       <c r="G85" s="5" t="inlineStr">
@@ -5029,7 +5029,7 @@
       </c>
       <c r="L85" s="5" t="n"/>
       <c r="M85" s="7" t="n">
-        <v>54.21</v>
+        <v>54.97</v>
       </c>
     </row>
     <row r="86">
@@ -5040,7 +5040,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649762 - KIT4M0460475549Z</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827011118 - KIT4M03867766NGK</t>
         </is>
       </c>
       <c r="C86" s="3" t="n">
@@ -5051,12 +5051,12 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0460475549Z</t>
+          <t>KIT4M03867766NGK</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>809859</t>
+          <t>809615</t>
         </is>
       </c>
       <c r="G86" s="5" t="inlineStr">
@@ -5082,7 +5082,7 @@
       </c>
       <c r="L86" s="5" t="n"/>
       <c r="M86" s="7" t="n">
-        <v>53.03</v>
+        <v>54.54</v>
       </c>
     </row>
     <row r="87">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="L87" s="5" t="n"/>
       <c r="M87" s="7" t="n">
-        <v>51.97</v>
+        <v>54.34</v>
       </c>
     </row>
     <row r="88">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270112 - KIT4M044751638F5</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955412 - KIT4M05563598Z74</t>
         </is>
       </c>
       <c r="C88" s="3" t="n">
@@ -5157,12 +5157,12 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>KIT4M044751638F5</t>
+          <t>KIT4M05563598Z74</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>809618</t>
+          <t>814474</t>
         </is>
       </c>
       <c r="G88" s="5" t="inlineStr">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="L88" s="5" t="n"/>
       <c r="M88" s="7" t="n">
-        <v>50.81</v>
+        <v>54.34</v>
       </c>
     </row>
     <row r="89">
@@ -5199,7 +5199,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955692 - KIT4M05563603CP4</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649762 - KIT4M0460475549Z</t>
         </is>
       </c>
       <c r="C89" s="3" t="n">
@@ -5210,12 +5210,12 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563603CP4</t>
+          <t>KIT4M0460475549Z</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>814447</t>
+          <t>809859</t>
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr">
@@ -5241,7 +5241,7 @@
       </c>
       <c r="L89" s="5" t="n"/>
       <c r="M89" s="7" t="n">
-        <v>50.38</v>
+        <v>53.03</v>
       </c>
     </row>
     <row r="90">
@@ -5252,7 +5252,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-LOS ANGELES CA-020955202-KIT4M05563534GZ7</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649372 - KIT4M05368221HQ5</t>
         </is>
       </c>
       <c r="C90" s="3" t="n">
@@ -5263,12 +5263,12 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563534GZ7</t>
+          <t>KIT4M05368221HQ5</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>814467</t>
+          <t>810834</t>
         </is>
       </c>
       <c r="G90" s="5" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="L90" s="5" t="n"/>
       <c r="M90" s="7" t="n">
-        <v>50.34</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="91">
@@ -5305,7 +5305,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020650142 - KIT4M05413839D24</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270112 - KIT4M044751638F5</t>
         </is>
       </c>
       <c r="C91" s="3" t="n">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413839D24</t>
+          <t>KIT4M044751638F5</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>810096</t>
+          <t>809618</t>
         </is>
       </c>
       <c r="G91" s="5" t="inlineStr">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="L91" s="5" t="n"/>
       <c r="M91" s="7" t="n">
-        <v>50.33</v>
+        <v>51.54</v>
       </c>
     </row>
     <row r="92">
@@ -5358,7 +5358,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles, CA-020955352-KIT4M05563525VC6</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955692 - KIT4M05563603CP4</t>
         </is>
       </c>
       <c r="C92" s="3" t="n">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563525VC6</t>
+          <t>KIT4M05563603CP4</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>814458</t>
+          <t>814447</t>
         </is>
       </c>
       <c r="G92" s="5" t="inlineStr">
@@ -5400,7 +5400,7 @@
       </c>
       <c r="L92" s="5" t="n"/>
       <c r="M92" s="7" t="n">
-        <v>50.03</v>
+        <v>51.44</v>
       </c>
     </row>
     <row r="93">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649372 - KIT4M05368221HQ5</t>
+          <t>SMRT-05900510-LOS ANGELES CA-020955202-KIT4M05563534GZ7</t>
         </is>
       </c>
       <c r="C93" s="3" t="n">
@@ -5422,12 +5422,12 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368221HQ5</t>
+          <t>KIT4M05563534GZ7</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>810834</t>
+          <t>814467</t>
         </is>
       </c>
       <c r="G93" s="5" t="inlineStr">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="L93" s="5" t="n"/>
       <c r="M93" s="7" t="n">
-        <v>49.71</v>
+        <v>50.61</v>
       </c>
     </row>
     <row r="94">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270111114 - KIT4P00065593VWC</t>
+          <t>SS - 05900510 -  Los Angeles CA - 021437622 - KIT4M0587258755W</t>
         </is>
       </c>
       <c r="C94" s="3" t="n">
@@ -5475,17 +5475,17 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065593VWC</t>
+          <t>KIT4M0587258755W</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>809606</t>
+          <t>816187</t>
         </is>
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H94" s="5" t="inlineStr">
@@ -5506,7 +5506,7 @@
       </c>
       <c r="L94" s="5" t="n"/>
       <c r="M94" s="7" t="n">
-        <v>49.23</v>
+        <v>50.57</v>
       </c>
     </row>
     <row r="95">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles, CA - 0204827011112 - KIT4M04158967K28</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020650142 - KIT4M05413839D24</t>
         </is>
       </c>
       <c r="C95" s="3" t="n">
@@ -5528,12 +5528,12 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158967K28</t>
+          <t>KIT4M05413839D24</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>809620</t>
+          <t>810096</t>
         </is>
       </c>
       <c r="G95" s="5" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="L95" s="5" t="n"/>
       <c r="M95" s="7" t="n">
-        <v>48.06</v>
+        <v>50.33</v>
       </c>
     </row>
     <row r="96">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955692 - KIT4M05563579H9F</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955042 - KIT4P00072391SZM</t>
         </is>
       </c>
       <c r="C96" s="3" t="n">
@@ -5581,17 +5581,17 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563579H9F</t>
+          <t>KIT4P00072391SZM</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>814480</t>
+          <t>814493</t>
         </is>
       </c>
       <c r="G96" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H96" s="5" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="L96" s="5" t="n"/>
       <c r="M96" s="7" t="n">
-        <v>47.42</v>
+        <v>49.91</v>
       </c>
     </row>
     <row r="97">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649672 - KIT4M04606113TPB</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955692 - KIT4M05563579H9F</t>
         </is>
       </c>
       <c r="C97" s="3" t="n">
@@ -5634,12 +5634,12 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04606113TPB</t>
+          <t>KIT4M05563579H9F</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>809862</t>
+          <t>814480</t>
         </is>
       </c>
       <c r="G97" s="5" t="inlineStr">
@@ -5665,7 +5665,7 @@
       </c>
       <c r="L97" s="5" t="n"/>
       <c r="M97" s="7" t="n">
-        <v>46.74</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="98">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles, CA-020955452-KIT4M05563529K2D</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270111114 - KIT4P00065593VWC</t>
         </is>
       </c>
       <c r="C98" s="3" t="n">
@@ -5687,17 +5687,17 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563529K2D</t>
+          <t>KIT4P00065593VWC</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>814473</t>
+          <t>809606</t>
         </is>
       </c>
       <c r="G98" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H98" s="5" t="inlineStr">
@@ -5718,7 +5718,7 @@
       </c>
       <c r="L98" s="5" t="n"/>
       <c r="M98" s="7" t="n">
-        <v>46.61</v>
+        <v>49.23</v>
       </c>
     </row>
     <row r="99">
@@ -5729,7 +5729,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437392 - KIT4M05872555BJR</t>
+          <t>STS - 05900510 - Los Angeles, CA - 0204827011112 - KIT4M04158967K28</t>
         </is>
       </c>
       <c r="C99" s="3" t="n">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872555BJR</t>
+          <t>KIT4M04158967K28</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>816074</t>
+          <t>809620</t>
         </is>
       </c>
       <c r="G99" s="5" t="inlineStr">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="L99" s="5" t="n"/>
       <c r="M99" s="7" t="n">
-        <v>46.6</v>
+        <v>49.19</v>
       </c>
     </row>
     <row r="100">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827016 - KIT4M041536494G6</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955702 - KIT4M05563571G8W</t>
         </is>
       </c>
       <c r="C100" s="3" t="n">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>KIT4M041536494G6</t>
+          <t>KIT4M05563571G8W</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>809617</t>
+          <t>814481</t>
         </is>
       </c>
       <c r="G100" s="5" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="L100" s="5" t="n"/>
       <c r="M100" s="7" t="n">
-        <v>43.4</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="101">
@@ -5835,7 +5835,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649812 - KIT4M04604742S6S</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649672 - KIT4M04606113TPB</t>
         </is>
       </c>
       <c r="C101" s="3" t="n">
@@ -5846,12 +5846,12 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604742S6S</t>
+          <t>KIT4M04606113TPB</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>809874</t>
+          <t>809862</t>
         </is>
       </c>
       <c r="G101" s="5" t="inlineStr">
@@ -5877,7 +5877,7 @@
       </c>
       <c r="L101" s="5" t="n"/>
       <c r="M101" s="7" t="n">
-        <v>43.24</v>
+        <v>46.74</v>
       </c>
     </row>
     <row r="102">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020955462 - KIT4M05563513GTF</t>
+          <t>SMRT-05900510-Los Angeles, CA-020955452-KIT4M05563529K2D</t>
         </is>
       </c>
       <c r="C102" s="3" t="n">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563513GTF</t>
+          <t>KIT4M05563529K2D</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>814432</t>
+          <t>814473</t>
         </is>
       </c>
       <c r="G102" s="5" t="inlineStr">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="L102" s="5" t="n"/>
       <c r="M102" s="7" t="n">
-        <v>43.23</v>
+        <v>46.61</v>
       </c>
     </row>
     <row r="103">
@@ -5941,7 +5941,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955702 - KIT4M05563571G8W</t>
+          <t>SS - 05900510 - Los Angeles CA - 020650042 - KIT4M05413819JV5</t>
         </is>
       </c>
       <c r="C103" s="3" t="n">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563571G8W</t>
+          <t>KIT4M05413819JV5</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>814481</t>
+          <t>812796</t>
         </is>
       </c>
       <c r="G103" s="5" t="inlineStr">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="L103" s="5" t="n"/>
       <c r="M103" s="7" t="n">
-        <v>42.83</v>
+        <v>45.57</v>
       </c>
     </row>
     <row r="104">
@@ -5994,7 +5994,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649432 - KIT4M05413778RBR</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827016 - KIT4M041536494G6</t>
         </is>
       </c>
       <c r="C104" s="3" t="n">
@@ -6005,12 +6005,12 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413778RBR</t>
+          <t>KIT4M041536494G6</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>812843</t>
+          <t>809617</t>
         </is>
       </c>
       <c r="G104" s="5" t="inlineStr">
@@ -6036,7 +6036,7 @@
       </c>
       <c r="L104" s="5" t="n"/>
       <c r="M104" s="7" t="n">
-        <v>42.82</v>
+        <v>45.09</v>
       </c>
     </row>
     <row r="105">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020650192 - KIT4M054138007JF</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020955462 - KIT4M05563513GTF</t>
         </is>
       </c>
       <c r="C105" s="3" t="n">
@@ -6058,12 +6058,12 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138007JF</t>
+          <t>KIT4M05563513GTF</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>810095</t>
+          <t>814432</t>
         </is>
       </c>
       <c r="G105" s="5" t="inlineStr">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="L105" s="5" t="n"/>
       <c r="M105" s="7" t="n">
-        <v>42.59</v>
+        <v>44.45</v>
       </c>
     </row>
     <row r="106">
@@ -6100,7 +6100,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020650052 - KIT4M05413781K6C</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649812 - KIT4M04604742S6S</t>
         </is>
       </c>
       <c r="C106" s="3" t="n">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413781K6C</t>
+          <t>KIT4M04604742S6S</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>812798</t>
+          <t>809874</t>
         </is>
       </c>
       <c r="G106" s="5" t="inlineStr">
@@ -6142,7 +6142,7 @@
       </c>
       <c r="L106" s="5" t="n"/>
       <c r="M106" s="7" t="n">
-        <v>42.04</v>
+        <v>43.24</v>
       </c>
     </row>
     <row r="107">
@@ -6153,7 +6153,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020650042 - KIT4M05413819JV5</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649432 - KIT4M05413778RBR</t>
         </is>
       </c>
       <c r="C107" s="3" t="n">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413819JV5</t>
+          <t>KIT4M05413778RBR</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>812796</t>
+          <t>812843</t>
         </is>
       </c>
       <c r="G107" s="5" t="inlineStr">
@@ -6195,7 +6195,7 @@
       </c>
       <c r="L107" s="5" t="n"/>
       <c r="M107" s="7" t="n">
-        <v>41.96</v>
+        <v>42.82</v>
       </c>
     </row>
     <row r="108">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="L108" s="5" t="n"/>
       <c r="M108" s="7" t="n">
-        <v>41.35</v>
+        <v>42.66</v>
       </c>
     </row>
     <row r="109">
@@ -6259,7 +6259,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270116 - KIT4M03476116F45</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020650192 - KIT4M054138007JF</t>
         </is>
       </c>
       <c r="C109" s="3" t="n">
@@ -6270,12 +6270,12 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03476116F45</t>
+          <t>KIT4M054138007JF</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>809608</t>
+          <t>810095</t>
         </is>
       </c>
       <c r="G109" s="5" t="inlineStr">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="L109" s="5" t="n"/>
       <c r="M109" s="7" t="n">
-        <v>40.47</v>
+        <v>42.59</v>
       </c>
     </row>
     <row r="110">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020955652 - KIT4M0556358988Z</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020650052 - KIT4M05413781K6C</t>
         </is>
       </c>
       <c r="C110" s="3" t="n">
@@ -6323,12 +6323,12 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0556358988Z</t>
+          <t>KIT4M05413781K6C</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>814484</t>
+          <t>812798</t>
         </is>
       </c>
       <c r="G110" s="5" t="inlineStr">
@@ -6354,7 +6354,7 @@
       </c>
       <c r="L110" s="5" t="n"/>
       <c r="M110" s="7" t="n">
-        <v>40.07</v>
+        <v>42.04</v>
       </c>
     </row>
     <row r="111">
@@ -6365,7 +6365,7 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649832 - KIT4M03866596RZG</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020955652 - KIT4M0556358988Z</t>
         </is>
       </c>
       <c r="C111" s="3" t="n">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03866596RZG</t>
+          <t>KIT4M0556358988Z</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>809869</t>
+          <t>814484</t>
         </is>
       </c>
       <c r="G111" s="5" t="inlineStr">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="L111" s="5" t="n"/>
       <c r="M111" s="7" t="n">
-        <v>40</v>
+        <v>41.86</v>
       </c>
     </row>
     <row r="112">
@@ -6418,7 +6418,7 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 020955382 - KIT4M05563509CHJ</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270116 - KIT4M03476116F45</t>
         </is>
       </c>
       <c r="C112" s="3" t="n">
@@ -6429,12 +6429,12 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563509CHJ</t>
+          <t>KIT4M03476116F45</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>814431</t>
+          <t>809608</t>
         </is>
       </c>
       <c r="G112" s="5" t="inlineStr">
@@ -6460,7 +6460,7 @@
       </c>
       <c r="L112" s="5" t="n"/>
       <c r="M112" s="7" t="n">
-        <v>39.2</v>
+        <v>41.43</v>
       </c>
     </row>
     <row r="113">
@@ -6471,7 +6471,7 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955272 - KIT4M05563585TXM</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649832 - KIT4M03866596RZG</t>
         </is>
       </c>
       <c r="C113" s="3" t="n">
@@ -6482,12 +6482,12 @@
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563585TXM</t>
+          <t>KIT4M03866596RZG</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>814475</t>
+          <t>809869</t>
         </is>
       </c>
       <c r="G113" s="5" t="inlineStr">
@@ -6513,7 +6513,7 @@
       </c>
       <c r="L113" s="5" t="n"/>
       <c r="M113" s="7" t="n">
-        <v>38.58</v>
+        <v>40.17</v>
       </c>
     </row>
     <row r="114">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955602 - KIT4M05563560225</t>
+          <t>SS - 05900510 -  Los Angeles CA - 020955382 - KIT4M05563509CHJ</t>
         </is>
       </c>
       <c r="C114" s="3" t="n">
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563560225</t>
+          <t>KIT4M05563509CHJ</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>814454</t>
+          <t>814431</t>
         </is>
       </c>
       <c r="G114" s="5" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="L114" s="5" t="n"/>
       <c r="M114" s="7" t="n">
-        <v>38.09</v>
+        <v>39.39</v>
       </c>
     </row>
     <row r="115">
@@ -6577,7 +6577,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020650082 - KIT4M05413792H8C</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955272 - KIT4M05563585TXM</t>
         </is>
       </c>
       <c r="C115" s="3" t="n">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413792H8C</t>
+          <t>KIT4M05563585TXM</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>812803</t>
+          <t>814475</t>
         </is>
       </c>
       <c r="G115" s="5" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="L115" s="5" t="n"/>
       <c r="M115" s="7" t="n">
-        <v>37.81</v>
+        <v>38.86</v>
       </c>
     </row>
     <row r="116">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649212 - KIT4P00065633ZXC</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955602 - KIT4M05563560225</t>
         </is>
       </c>
       <c r="C116" s="3" t="n">
@@ -6641,17 +6641,17 @@
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065633ZXC</t>
+          <t>KIT4M05563560225</t>
         </is>
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>812922</t>
+          <t>814454</t>
         </is>
       </c>
       <c r="G116" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H116" s="5" t="inlineStr">
@@ -6672,7 +6672,7 @@
       </c>
       <c r="L116" s="5" t="n"/>
       <c r="M116" s="7" t="n">
-        <v>36.03</v>
+        <v>38.09</v>
       </c>
     </row>
     <row r="117">
@@ -6683,7 +6683,7 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649942 - KIT4M05413786BXC</t>
+          <t>STS - 05900510 - Los Angeles CA - 020650082 - KIT4M05413792H8C</t>
         </is>
       </c>
       <c r="C117" s="3" t="n">
@@ -6694,12 +6694,12 @@
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413786BXC</t>
+          <t>KIT4M05413792H8C</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>812838</t>
+          <t>812803</t>
         </is>
       </c>
       <c r="G117" s="5" t="inlineStr">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="L117" s="5" t="n"/>
       <c r="M117" s="7" t="n">
-        <v>34.4</v>
+        <v>37.81</v>
       </c>
     </row>
     <row r="118">
@@ -6736,7 +6736,7 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020650112 - KIT4M05413840D9J</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649212 - KIT4P00065633ZXC</t>
         </is>
       </c>
       <c r="C118" s="3" t="n">
@@ -6747,17 +6747,17 @@
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413840D9J</t>
+          <t>KIT4P00065633ZXC</t>
         </is>
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>810099</t>
+          <t>812922</t>
         </is>
       </c>
       <c r="G118" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H118" s="5" t="inlineStr">
@@ -6778,7 +6778,7 @@
       </c>
       <c r="L118" s="5" t="n"/>
       <c r="M118" s="7" t="n">
-        <v>34.35</v>
+        <v>37.56</v>
       </c>
     </row>
     <row r="119">
@@ -6789,7 +6789,7 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649682 - KIT4M046047384RX</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020650112 - KIT4M05413840D9J</t>
         </is>
       </c>
       <c r="C119" s="3" t="n">
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047384RX</t>
+          <t>KIT4M05413840D9J</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>809870</t>
+          <t>810099</t>
         </is>
       </c>
       <c r="G119" s="5" t="inlineStr">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="L119" s="5" t="n"/>
       <c r="M119" s="7" t="n">
-        <v>32.62</v>
+        <v>34.44</v>
       </c>
     </row>
     <row r="120">
@@ -6842,7 +6842,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649412 - KIT4M05413769796</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649942 - KIT4M05413786BXC</t>
         </is>
       </c>
       <c r="C120" s="3" t="n">
@@ -6853,12 +6853,12 @@
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413769796</t>
+          <t>KIT4M05413786BXC</t>
         </is>
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t>812839</t>
+          <t>812838</t>
         </is>
       </c>
       <c r="G120" s="5" t="inlineStr">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="L120" s="5" t="n"/>
       <c r="M120" s="7" t="n">
-        <v>32.57</v>
+        <v>34.4</v>
       </c>
     </row>
     <row r="121">
@@ -6937,7 +6937,7 @@
       </c>
       <c r="L121" s="5" t="n"/>
       <c r="M121" s="7" t="n">
-        <v>31.97</v>
+        <v>33.05</v>
       </c>
     </row>
     <row r="122">
@@ -6948,7 +6948,7 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482706 - KIT4M04604744V6K</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649682 - KIT4M046047384RX</t>
         </is>
       </c>
       <c r="C122" s="3" t="n">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604744V6K</t>
+          <t>KIT4M046047384RX</t>
         </is>
       </c>
       <c r="F122" s="4" t="inlineStr">
         <is>
-          <t>809659</t>
+          <t>809870</t>
         </is>
       </c>
       <c r="G122" s="5" t="inlineStr">
@@ -6990,7 +6990,7 @@
       </c>
       <c r="L122" s="5" t="n"/>
       <c r="M122" s="7" t="n">
-        <v>31.38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="123">
@@ -7001,7 +7001,7 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 6858375 - KIT4M05872512N5W</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649412 - KIT4M05413769796</t>
         </is>
       </c>
       <c r="C123" s="3" t="n">
@@ -7012,12 +7012,12 @@
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872512N5W</t>
+          <t>KIT4M05413769796</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>816077</t>
+          <t>812839</t>
         </is>
       </c>
       <c r="G123" s="5" t="inlineStr">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="L123" s="5" t="n"/>
       <c r="M123" s="7" t="n">
-        <v>31.03</v>
+        <v>32.57</v>
       </c>
     </row>
     <row r="124">
@@ -7054,7 +7054,7 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437782 - KIT4M058724975J4</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482706 - KIT4M04604744V6K</t>
         </is>
       </c>
       <c r="C124" s="3" t="n">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058724975J4</t>
+          <t>KIT4M04604744V6K</t>
         </is>
       </c>
       <c r="F124" s="4" t="inlineStr">
         <is>
-          <t>816075</t>
+          <t>809659</t>
         </is>
       </c>
       <c r="G124" s="5" t="inlineStr">
@@ -7096,7 +7096,7 @@
       </c>
       <c r="L124" s="5" t="n"/>
       <c r="M124" s="7" t="n">
-        <v>28.85</v>
+        <v>31.38</v>
       </c>
     </row>
     <row r="125">
@@ -7107,7 +7107,7 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 021437622 - KIT4M0587258755W</t>
+          <t>SS - 05900510 - Los Angeles CA - 6858375 - KIT4M05872512N5W</t>
         </is>
       </c>
       <c r="C125" s="3" t="n">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0587258755W</t>
+          <t>KIT4M05872512N5W</t>
         </is>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>816187</t>
+          <t>816077</t>
         </is>
       </c>
       <c r="G125" s="5" t="inlineStr">
@@ -7149,7 +7149,7 @@
       </c>
       <c r="L125" s="5" t="n"/>
       <c r="M125" s="7" t="n">
-        <v>28.71</v>
+        <v>31.07</v>
       </c>
     </row>
     <row r="126">
@@ -7160,7 +7160,7 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649742 - KIT4M04350554X4Z</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437782 - KIT4M058724975J4</t>
         </is>
       </c>
       <c r="C126" s="3" t="n">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04350554X4Z</t>
+          <t>KIT4M058724975J4</t>
         </is>
       </c>
       <c r="F126" s="4" t="inlineStr">
         <is>
-          <t>809866</t>
+          <t>816075</t>
         </is>
       </c>
       <c r="G126" s="5" t="inlineStr">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="L126" s="5" t="n"/>
       <c r="M126" s="7" t="n">
-        <v>27.16</v>
+        <v>29.93</v>
       </c>
     </row>
     <row r="127">
@@ -7213,7 +7213,7 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649532 - KIT4M05413808FFZ</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437272 - KIT4P0008459589D</t>
         </is>
       </c>
       <c r="C127" s="3" t="n">
@@ -7224,17 +7224,17 @@
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413808FFZ</t>
+          <t>KIT4P0008459589D</t>
         </is>
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>812828</t>
+          <t>816222</t>
         </is>
       </c>
       <c r="G127" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H127" s="5" t="inlineStr">
@@ -7255,7 +7255,7 @@
       </c>
       <c r="L127" s="5" t="n"/>
       <c r="M127" s="7" t="n">
-        <v>27.14</v>
+        <v>28.57</v>
       </c>
     </row>
     <row r="128">
@@ -7266,7 +7266,7 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437992 -  KIT4M05799663CPM</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438002 - KIT4M05799701SGS</t>
         </is>
       </c>
       <c r="C128" s="3" t="n">
@@ -7277,12 +7277,12 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799663CPM</t>
+          <t>KIT4M05799701SGS</t>
         </is>
       </c>
       <c r="F128" s="4" t="inlineStr">
         <is>
-          <t>816272</t>
+          <t>816284</t>
         </is>
       </c>
       <c r="G128" s="5" t="inlineStr">
@@ -7308,7 +7308,7 @@
       </c>
       <c r="L128" s="5" t="n"/>
       <c r="M128" s="7" t="n">
-        <v>26.55</v>
+        <v>28.22</v>
       </c>
     </row>
     <row r="129">
@@ -7319,7 +7319,7 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955342 - KIT4M05563524MJ4</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649742 - KIT4M04350554X4Z</t>
         </is>
       </c>
       <c r="C129" s="3" t="n">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563524MJ4</t>
+          <t>KIT4M04350554X4Z</t>
         </is>
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>814472</t>
+          <t>809866</t>
         </is>
       </c>
       <c r="G129" s="5" t="inlineStr">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="L129" s="5" t="n"/>
       <c r="M129" s="7" t="n">
-        <v>26.26</v>
+        <v>27.16</v>
       </c>
     </row>
     <row r="130">
@@ -7372,7 +7372,7 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649822 - KIT4M04604740BM6</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649532 - KIT4M05413808FFZ</t>
         </is>
       </c>
       <c r="C130" s="3" t="n">
@@ -7383,12 +7383,12 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604740BM6</t>
+          <t>KIT4M05413808FFZ</t>
         </is>
       </c>
       <c r="F130" s="4" t="inlineStr">
         <is>
-          <t>809872</t>
+          <t>812828</t>
         </is>
       </c>
       <c r="G130" s="5" t="inlineStr">
@@ -7414,7 +7414,7 @@
       </c>
       <c r="L130" s="5" t="n"/>
       <c r="M130" s="7" t="n">
-        <v>25.44</v>
+        <v>27.14</v>
       </c>
     </row>
     <row r="131">
@@ -7425,7 +7425,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649362 - KIT4M05368336DBC</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649822 - KIT4M04604740BM6</t>
         </is>
       </c>
       <c r="C131" s="3" t="n">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368336DBC</t>
+          <t>KIT4M04604740BM6</t>
         </is>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>810831</t>
+          <t>809872</t>
         </is>
       </c>
       <c r="G131" s="5" t="inlineStr">
@@ -7467,7 +7467,7 @@
       </c>
       <c r="L131" s="5" t="n"/>
       <c r="M131" s="7" t="n">
-        <v>25.14</v>
+        <v>26.94</v>
       </c>
     </row>
     <row r="132">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020649292-KIT4M05368201SNV</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437992 -  KIT4M05799663CPM</t>
         </is>
       </c>
       <c r="C132" s="3" t="n">
@@ -7489,12 +7489,12 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368201SNV</t>
+          <t>KIT4M05799663CPM</t>
         </is>
       </c>
       <c r="F132" s="4" t="inlineStr">
         <is>
-          <t>810651</t>
+          <t>816272</t>
         </is>
       </c>
       <c r="G132" s="5" t="inlineStr">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="L132" s="5" t="n"/>
       <c r="M132" s="7" t="n">
-        <v>24.68</v>
+        <v>26.82</v>
       </c>
     </row>
     <row r="133">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955212 - KIT4M05563512GBQ</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955342 - KIT4M05563524MJ4</t>
         </is>
       </c>
       <c r="C133" s="3" t="n">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563512GBQ</t>
+          <t>KIT4M05563524MJ4</t>
         </is>
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>814435</t>
+          <t>814472</t>
         </is>
       </c>
       <c r="G133" s="5" t="inlineStr">
@@ -7573,7 +7573,7 @@
       </c>
       <c r="L133" s="5" t="n"/>
       <c r="M133" s="7" t="n">
-        <v>24.55</v>
+        <v>26.26</v>
       </c>
     </row>
     <row r="134">
@@ -7584,7 +7584,7 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438002 - KIT4M05799701SGS</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649362 - KIT4M05368336DBC</t>
         </is>
       </c>
       <c r="C134" s="3" t="n">
@@ -7595,12 +7595,12 @@
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799701SGS</t>
+          <t>KIT4M05368336DBC</t>
         </is>
       </c>
       <c r="F134" s="4" t="inlineStr">
         <is>
-          <t>816284</t>
+          <t>810831</t>
         </is>
       </c>
       <c r="G134" s="5" t="inlineStr">
@@ -7626,7 +7626,7 @@
       </c>
       <c r="L134" s="5" t="n"/>
       <c r="M134" s="7" t="n">
-        <v>24.12</v>
+        <v>25.14</v>
       </c>
     </row>
     <row r="135">
@@ -7637,7 +7637,7 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020650162 - KIT4M05413837SMB</t>
+          <t>SMRT-05900510-Los Angeles CA-020649292-KIT4M05368201SNV</t>
         </is>
       </c>
       <c r="C135" s="3" t="n">
@@ -7648,12 +7648,12 @@
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413837SMB</t>
+          <t>KIT4M05368201SNV</t>
         </is>
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>810100</t>
+          <t>810651</t>
         </is>
       </c>
       <c r="G135" s="5" t="inlineStr">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="L135" s="5" t="n"/>
       <c r="M135" s="7" t="n">
-        <v>23.32</v>
+        <v>24.72</v>
       </c>
     </row>
     <row r="136">
@@ -7690,7 +7690,7 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482701112 - KIT4M04158973M2C</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955212 - KIT4M05563512GBQ</t>
         </is>
       </c>
       <c r="C136" s="3" t="n">
@@ -7701,12 +7701,12 @@
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158973M2C</t>
+          <t>KIT4M05563512GBQ</t>
         </is>
       </c>
       <c r="F136" s="4" t="inlineStr">
         <is>
-          <t>809610</t>
+          <t>814435</t>
         </is>
       </c>
       <c r="G136" s="5" t="inlineStr">
@@ -7732,7 +7732,7 @@
       </c>
       <c r="L136" s="5" t="n"/>
       <c r="M136" s="7" t="n">
-        <v>22.79</v>
+        <v>24.55</v>
       </c>
     </row>
     <row r="137">
@@ -7743,7 +7743,7 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438242 - KIT4M058725094XP</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482701112 - KIT4M04158973M2C</t>
         </is>
       </c>
       <c r="C137" s="3" t="n">
@@ -7754,12 +7754,12 @@
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725094XP</t>
+          <t>KIT4M04158973M2C</t>
         </is>
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>816085</t>
+          <t>809610</t>
         </is>
       </c>
       <c r="G137" s="5" t="inlineStr">
@@ -7785,7 +7785,7 @@
       </c>
       <c r="L137" s="5" t="n"/>
       <c r="M137" s="7" t="n">
-        <v>22.66</v>
+        <v>24.48</v>
       </c>
     </row>
     <row r="138">
@@ -7796,7 +7796,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020650242 - KIT4M05413804SKS</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649452 - KIT4M05413785QCG</t>
         </is>
       </c>
       <c r="C138" s="3" t="n">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413804SKS</t>
+          <t>KIT4M05413785QCG</t>
         </is>
       </c>
       <c r="F138" s="4" t="inlineStr">
         <is>
-          <t>810102</t>
+          <t>812806</t>
         </is>
       </c>
       <c r="G138" s="5" t="inlineStr">
@@ -7838,7 +7838,7 @@
       </c>
       <c r="L138" s="5" t="n"/>
       <c r="M138" s="7" t="n">
-        <v>21.81</v>
+        <v>23.53</v>
       </c>
     </row>
     <row r="139">
@@ -7849,7 +7849,7 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955712 - KIT4M05563586ZTR</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438242 - KIT4M058725094XP</t>
         </is>
       </c>
       <c r="C139" s="3" t="n">
@@ -7860,12 +7860,12 @@
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563586ZTR</t>
+          <t>KIT4M058725094XP</t>
         </is>
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>814445</t>
+          <t>816085</t>
         </is>
       </c>
       <c r="G139" s="5" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="L139" s="5" t="n"/>
       <c r="M139" s="7" t="n">
-        <v>21.78</v>
+        <v>23.38</v>
       </c>
     </row>
     <row r="140">
@@ -7902,7 +7902,7 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020650132-KIT4M05413828PCT</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020650162 - KIT4M05413837SMB</t>
         </is>
       </c>
       <c r="C140" s="3" t="n">
@@ -7913,12 +7913,12 @@
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413828PCT</t>
+          <t>KIT4M05413837SMB</t>
         </is>
       </c>
       <c r="F140" s="4" t="inlineStr">
         <is>
-          <t>812799</t>
+          <t>810100</t>
         </is>
       </c>
       <c r="G140" s="5" t="inlineStr">
@@ -7944,7 +7944,7 @@
       </c>
       <c r="L140" s="5" t="n"/>
       <c r="M140" s="7" t="n">
-        <v>21.54</v>
+        <v>23.32</v>
       </c>
     </row>
     <row r="141">
@@ -7955,7 +7955,7 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-LOS ANGELES CA-020955172-KIT4M05563526WNC</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955502 - KIT4M05563502GJS</t>
         </is>
       </c>
       <c r="C141" s="3" t="n">
@@ -7966,12 +7966,12 @@
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563526WNC</t>
+          <t>KIT4M05563502GJS</t>
         </is>
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>814463</t>
+          <t>814470</t>
         </is>
       </c>
       <c r="G141" s="5" t="inlineStr">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="L141" s="5" t="n"/>
       <c r="M141" s="7" t="n">
-        <v>21.16</v>
+        <v>23.23</v>
       </c>
     </row>
     <row r="142">
@@ -8008,7 +8008,7 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020650072-KIT4M054137987GJ</t>
+          <t>SMA - 05900510 -  Los Angeles CA - 020649512 - KIT4M054138318Q7</t>
         </is>
       </c>
       <c r="C142" s="3" t="n">
@@ -8019,12 +8019,12 @@
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137987GJ</t>
+          <t>KIT4M054138318Q7</t>
         </is>
       </c>
       <c r="F142" s="4" t="inlineStr">
         <is>
-          <t>812795</t>
+          <t>812814</t>
         </is>
       </c>
       <c r="G142" s="5" t="inlineStr">
@@ -8050,7 +8050,7 @@
       </c>
       <c r="L142" s="5" t="n"/>
       <c r="M142" s="7" t="n">
-        <v>20.74</v>
+        <v>22.97</v>
       </c>
     </row>
     <row r="143">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955532 - KIT4M05563548P9Q</t>
+          <t>SS - 05900510 -  Los Angeles CA - 021438232 - KIT4M05872520QJM</t>
         </is>
       </c>
       <c r="C143" s="3" t="n">
@@ -8072,12 +8072,12 @@
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563548P9Q</t>
+          <t>KIT4M05872520QJM</t>
         </is>
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>814468</t>
+          <t>816078</t>
         </is>
       </c>
       <c r="G143" s="5" t="inlineStr">
@@ -8103,7 +8103,7 @@
       </c>
       <c r="L143" s="5" t="n"/>
       <c r="M143" s="7" t="n">
-        <v>20.5</v>
+        <v>22.38</v>
       </c>
     </row>
     <row r="144">
@@ -8114,7 +8114,7 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649452 - KIT4M05413785QCG</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955712 - KIT4M05563586ZTR</t>
         </is>
       </c>
       <c r="C144" s="3" t="n">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413785QCG</t>
+          <t>KIT4M05563586ZTR</t>
         </is>
       </c>
       <c r="F144" s="4" t="inlineStr">
         <is>
-          <t>812806</t>
+          <t>814445</t>
         </is>
       </c>
       <c r="G144" s="5" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="L144" s="5" t="n"/>
       <c r="M144" s="7" t="n">
-        <v>20.29</v>
+        <v>21.92</v>
       </c>
     </row>
     <row r="145">
@@ -8167,7 +8167,7 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649222 - KIT4P00065640BFW</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020650242 - KIT4M05413804SKS</t>
         </is>
       </c>
       <c r="C145" s="3" t="n">
@@ -8178,17 +8178,17 @@
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065640BFW</t>
+          <t>KIT4M05413804SKS</t>
         </is>
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>812929</t>
+          <t>810102</t>
         </is>
       </c>
       <c r="G145" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H145" s="5" t="inlineStr">
@@ -8209,7 +8209,7 @@
       </c>
       <c r="L145" s="5" t="n"/>
       <c r="M145" s="7" t="n">
-        <v>19.87</v>
+        <v>21.85</v>
       </c>
     </row>
     <row r="146">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649912 - KIT4M05413836KJC</t>
+          <t>SMRT-05900510-Los Angeles CA-020650132-KIT4M05413828PCT</t>
         </is>
       </c>
       <c r="C146" s="3" t="n">
@@ -8231,12 +8231,12 @@
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413836KJC</t>
+          <t>KIT4M05413828PCT</t>
         </is>
       </c>
       <c r="F146" s="4" t="inlineStr">
         <is>
-          <t>810097</t>
+          <t>812799</t>
         </is>
       </c>
       <c r="G146" s="5" t="inlineStr">
@@ -8262,7 +8262,7 @@
       </c>
       <c r="L146" s="5" t="n"/>
       <c r="M146" s="7" t="n">
-        <v>19.73</v>
+        <v>21.54</v>
       </c>
     </row>
     <row r="147">
@@ -8273,7 +8273,7 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649302 - KIT4M05368226W57</t>
+          <t>SMRT-05900510-LOS ANGELES CA-020955172-KIT4M05563526WNC</t>
         </is>
       </c>
       <c r="C147" s="3" t="n">
@@ -8284,12 +8284,12 @@
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368226W57</t>
+          <t>KIT4M05563526WNC</t>
         </is>
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>810833</t>
+          <t>814463</t>
         </is>
       </c>
       <c r="G147" s="5" t="inlineStr">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="L147" s="5" t="n"/>
       <c r="M147" s="7" t="n">
-        <v>19.62</v>
+        <v>21.16</v>
       </c>
     </row>
     <row r="148">
@@ -8326,7 +8326,7 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955302 - KIT4M055635158PC</t>
+          <t>SMRT-05900510-Los Angeles CA-020650072-KIT4M054137987GJ</t>
         </is>
       </c>
       <c r="C148" s="3" t="n">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635158PC</t>
+          <t>KIT4M054137987GJ</t>
         </is>
       </c>
       <c r="F148" s="4" t="inlineStr">
         <is>
-          <t>814457</t>
+          <t>812795</t>
         </is>
       </c>
       <c r="G148" s="5" t="inlineStr">
@@ -8368,7 +8368,7 @@
       </c>
       <c r="L148" s="5" t="n"/>
       <c r="M148" s="7" t="n">
-        <v>19.59</v>
+        <v>20.74</v>
       </c>
     </row>
     <row r="149">
@@ -8379,7 +8379,7 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955282 - KIT4M055635227ZR</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955532 - KIT4M05563548P9Q</t>
         </is>
       </c>
       <c r="C149" s="3" t="n">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635227ZR</t>
+          <t>KIT4M05563548P9Q</t>
         </is>
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>814482</t>
+          <t>814468</t>
         </is>
       </c>
       <c r="G149" s="5" t="inlineStr">
@@ -8421,7 +8421,7 @@
       </c>
       <c r="L149" s="5" t="n"/>
       <c r="M149" s="7" t="n">
-        <v>19.17</v>
+        <v>20.73</v>
       </c>
     </row>
     <row r="150">
@@ -8432,7 +8432,7 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA  - 020649722 - KIT4M04604747TPT</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649222 - KIT4P00065640BFW</t>
         </is>
       </c>
       <c r="C150" s="3" t="n">
@@ -8443,17 +8443,17 @@
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604747TPT</t>
+          <t>KIT4P00065640BFW</t>
         </is>
       </c>
       <c r="F150" s="4" t="inlineStr">
         <is>
-          <t>809873</t>
+          <t>812929</t>
         </is>
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="L150" s="5" t="n"/>
       <c r="M150" s="7" t="n">
-        <v>18.44</v>
+        <v>19.87</v>
       </c>
     </row>
     <row r="151">
@@ -8485,7 +8485,7 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 021438232 - KIT4M05872520QJM</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649912 - KIT4M05413836KJC</t>
         </is>
       </c>
       <c r="C151" s="3" t="n">
@@ -8496,12 +8496,12 @@
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872520QJM</t>
+          <t>KIT4M05413836KJC</t>
         </is>
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>816078</t>
+          <t>810097</t>
         </is>
       </c>
       <c r="G151" s="5" t="inlineStr">
@@ -8527,7 +8527,7 @@
       </c>
       <c r="L151" s="5" t="n"/>
       <c r="M151" s="7" t="n">
-        <v>18.36</v>
+        <v>19.73</v>
       </c>
     </row>
     <row r="152">
@@ -8538,7 +8538,7 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 -  Los Angeles CA - 020649512 - KIT4M054138318Q7</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649302 - KIT4M05368226W57</t>
         </is>
       </c>
       <c r="C152" s="3" t="n">
@@ -8549,12 +8549,12 @@
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138318Q7</t>
+          <t>KIT4M05368226W57</t>
         </is>
       </c>
       <c r="F152" s="4" t="inlineStr">
         <is>
-          <t>812814</t>
+          <t>810833</t>
         </is>
       </c>
       <c r="G152" s="5" t="inlineStr">
@@ -8580,7 +8580,7 @@
       </c>
       <c r="L152" s="5" t="n"/>
       <c r="M152" s="7" t="n">
-        <v>18.21</v>
+        <v>19.62</v>
       </c>
     </row>
     <row r="153">
@@ -8591,7 +8591,7 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438072 - KIT4M057996885ZV</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955302 - KIT4M055635158PC</t>
         </is>
       </c>
       <c r="C153" s="3" t="n">
@@ -8602,12 +8602,12 @@
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>KIT4M057996885ZV</t>
+          <t>KIT4M055635158PC</t>
         </is>
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>816269</t>
+          <t>814457</t>
         </is>
       </c>
       <c r="G153" s="5" t="inlineStr">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="L153" s="5" t="n"/>
       <c r="M153" s="7" t="n">
-        <v>17.3</v>
+        <v>19.59</v>
       </c>
     </row>
     <row r="154">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649322 - KIT4M053683324KZ</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955282 - KIT4M055635227ZR</t>
         </is>
       </c>
       <c r="C154" s="3" t="n">
@@ -8655,12 +8655,12 @@
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>KIT4M053683324KZ</t>
+          <t>KIT4M055635227ZR</t>
         </is>
       </c>
       <c r="F154" s="4" t="inlineStr">
         <is>
-          <t>810832</t>
+          <t>814482</t>
         </is>
       </c>
       <c r="G154" s="5" t="inlineStr">
@@ -8686,7 +8686,7 @@
       </c>
       <c r="L154" s="5" t="n"/>
       <c r="M154" s="7" t="n">
-        <v>17.29</v>
+        <v>19.17</v>
       </c>
     </row>
     <row r="155">
@@ -8697,7 +8697,7 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649632 - KIT4M054138064J9</t>
+          <t>SS - 05900510 - Los Angeles, CA  - 020649722 - KIT4M04604747TPT</t>
         </is>
       </c>
       <c r="C155" s="3" t="n">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138064J9</t>
+          <t>KIT4M04604747TPT</t>
         </is>
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>812844</t>
+          <t>809873</t>
         </is>
       </c>
       <c r="G155" s="5" t="inlineStr">
@@ -8739,7 +8739,7 @@
       </c>
       <c r="L155" s="5" t="n"/>
       <c r="M155" s="7" t="n">
-        <v>17.18</v>
+        <v>18.44</v>
       </c>
     </row>
     <row r="156">
@@ -8750,7 +8750,7 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649592 - KIT4M05413787HHK</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438072 - KIT4M057996885ZV</t>
         </is>
       </c>
       <c r="C156" s="3" t="n">
@@ -8761,12 +8761,12 @@
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413787HHK</t>
+          <t>KIT4M057996885ZV</t>
         </is>
       </c>
       <c r="F156" s="4" t="inlineStr">
         <is>
-          <t>812809</t>
+          <t>816269</t>
         </is>
       </c>
       <c r="G156" s="5" t="inlineStr">
@@ -8792,7 +8792,7 @@
       </c>
       <c r="L156" s="5" t="n"/>
       <c r="M156" s="7" t="n">
-        <v>15.8</v>
+        <v>17.89</v>
       </c>
     </row>
     <row r="157">
@@ -8803,7 +8803,7 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482708 - KIT4M04604736T7C</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438222 - KIT4M058725299QP</t>
         </is>
       </c>
       <c r="C157" s="3" t="n">
@@ -8814,12 +8814,12 @@
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604736T7C</t>
+          <t>KIT4M058725299QP</t>
         </is>
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>809662</t>
+          <t>816080</t>
         </is>
       </c>
       <c r="G157" s="5" t="inlineStr">
@@ -8845,7 +8845,7 @@
       </c>
       <c r="L157" s="5" t="n"/>
       <c r="M157" s="7" t="n">
-        <v>15.7</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="158">
@@ -8856,7 +8856,7 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438222 - KIT4M058725299QP</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649322 - KIT4M053683324KZ</t>
         </is>
       </c>
       <c r="C158" s="3" t="n">
@@ -8867,12 +8867,12 @@
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725299QP</t>
+          <t>KIT4M053683324KZ</t>
         </is>
       </c>
       <c r="F158" s="4" t="inlineStr">
         <is>
-          <t>816080</t>
+          <t>810832</t>
         </is>
       </c>
       <c r="G158" s="5" t="inlineStr">
@@ -8898,7 +8898,7 @@
       </c>
       <c r="L158" s="5" t="n"/>
       <c r="M158" s="7" t="n">
-        <v>15.01</v>
+        <v>17.29</v>
       </c>
     </row>
     <row r="159">
@@ -8909,7 +8909,7 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955362 - KIT4M05563528MKX</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649632 - KIT4M054138064J9</t>
         </is>
       </c>
       <c r="C159" s="3" t="n">
@@ -8920,12 +8920,12 @@
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563528MKX</t>
+          <t>KIT4M054138064J9</t>
         </is>
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>814471</t>
+          <t>812844</t>
         </is>
       </c>
       <c r="G159" s="5" t="inlineStr">
@@ -8951,7 +8951,7 @@
       </c>
       <c r="L159" s="5" t="n"/>
       <c r="M159" s="7" t="n">
-        <v>14.96</v>
+        <v>17.18</v>
       </c>
     </row>
     <row r="160">
@@ -8962,7 +8962,7 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - CW6642812 - KIT4M054138292ZP</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955642 - KIT4M05563573WKC</t>
         </is>
       </c>
       <c r="C160" s="3" t="n">
@@ -8973,12 +8973,12 @@
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138292ZP</t>
+          <t>KIT4M05563573WKC</t>
         </is>
       </c>
       <c r="F160" s="4" t="inlineStr">
         <is>
-          <t>812784</t>
+          <t>814488</t>
         </is>
       </c>
       <c r="G160" s="5" t="inlineStr">
@@ -9004,7 +9004,7 @@
       </c>
       <c r="L160" s="5" t="n"/>
       <c r="M160" s="7" t="n">
-        <v>14.46</v>
+        <v>15.92</v>
       </c>
     </row>
     <row r="161">
@@ -9015,7 +9015,7 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020649862 - KIT4M04475159PMD</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649592 - KIT4M05413787HHK</t>
         </is>
       </c>
       <c r="C161" s="3" t="n">
@@ -9026,12 +9026,12 @@
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475159PMD</t>
+          <t>KIT4M05413787HHK</t>
         </is>
       </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
-          <t>809868</t>
+          <t>812809</t>
         </is>
       </c>
       <c r="G161" s="5" t="inlineStr">
@@ -9057,7 +9057,7 @@
       </c>
       <c r="L161" s="5" t="n"/>
       <c r="M161" s="7" t="n">
-        <v>14.45</v>
+        <v>15.86</v>
       </c>
     </row>
     <row r="162">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955642 - KIT4M05563573WKC</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482708 - KIT4M04604736T7C</t>
         </is>
       </c>
       <c r="C162" s="3" t="n">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563573WKC</t>
+          <t>KIT4M04604736T7C</t>
         </is>
       </c>
       <c r="F162" s="4" t="inlineStr">
         <is>
-          <t>814488</t>
+          <t>809662</t>
         </is>
       </c>
       <c r="G162" s="5" t="inlineStr">
@@ -9110,7 +9110,7 @@
       </c>
       <c r="L162" s="5" t="n"/>
       <c r="M162" s="7" t="n">
-        <v>14.14</v>
+        <v>15.7</v>
       </c>
     </row>
     <row r="163">
@@ -9121,7 +9121,7 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955402 - KIT4M05563610HM2</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955362 - KIT4M05563528MKX</t>
         </is>
       </c>
       <c r="C163" s="3" t="n">
@@ -9132,12 +9132,12 @@
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563610HM2</t>
+          <t>KIT4M05563528MKX</t>
         </is>
       </c>
       <c r="F163" s="4" t="inlineStr">
         <is>
-          <t>814486</t>
+          <t>814471</t>
         </is>
       </c>
       <c r="G163" s="5" t="inlineStr">
@@ -9163,7 +9163,7 @@
       </c>
       <c r="L163" s="5" t="n"/>
       <c r="M163" s="7" t="n">
-        <v>14.14</v>
+        <v>15.05</v>
       </c>
     </row>
     <row r="164">
@@ -9174,7 +9174,7 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955482 - KIT4M055635088NK</t>
+          <t>SMA - 05900510 - Los Angeles CA - CW6642812 - KIT4M054138292ZP</t>
         </is>
       </c>
       <c r="C164" s="3" t="n">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635088NK</t>
+          <t>KIT4M054138292ZP</t>
         </is>
       </c>
       <c r="F164" s="4" t="inlineStr">
         <is>
-          <t>814434</t>
+          <t>812784</t>
         </is>
       </c>
       <c r="G164" s="5" t="inlineStr">
@@ -9216,7 +9216,7 @@
       </c>
       <c r="L164" s="5" t="n"/>
       <c r="M164" s="7" t="n">
-        <v>14.03</v>
+        <v>14.46</v>
       </c>
     </row>
     <row r="165">
@@ -9227,7 +9227,7 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827010 - KIT4M046047372KJ</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020649862 - KIT4M04475159PMD</t>
         </is>
       </c>
       <c r="C165" s="3" t="n">
@@ -9238,12 +9238,12 @@
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047372KJ</t>
+          <t>KIT4M04475159PMD</t>
         </is>
       </c>
       <c r="F165" s="4" t="inlineStr">
         <is>
-          <t>809658</t>
+          <t>809868</t>
         </is>
       </c>
       <c r="G165" s="5" t="inlineStr">
@@ -9269,7 +9269,7 @@
       </c>
       <c r="L165" s="5" t="n"/>
       <c r="M165" s="7" t="n">
-        <v>13.64</v>
+        <v>14.45</v>
       </c>
     </row>
     <row r="166">
@@ -9280,7 +9280,7 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649442 - KIT4M054137885SM</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020650262 - KIT4M054138249M8</t>
         </is>
       </c>
       <c r="C166" s="3" t="n">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137885SM</t>
+          <t>KIT4M054138249M8</t>
         </is>
       </c>
       <c r="F166" s="4" t="inlineStr">
         <is>
-          <t>812846</t>
+          <t>812794</t>
         </is>
       </c>
       <c r="G166" s="5" t="inlineStr">
@@ -9322,7 +9322,7 @@
       </c>
       <c r="L166" s="5" t="n"/>
       <c r="M166" s="7" t="n">
-        <v>13.24</v>
+        <v>14.28</v>
       </c>
     </row>
     <row r="167">
@@ -9333,7 +9333,7 @@
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020650262 - KIT4M054138249M8</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955402 - KIT4M05563610HM2</t>
         </is>
       </c>
       <c r="C167" s="3" t="n">
@@ -9344,12 +9344,12 @@
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138249M8</t>
+          <t>KIT4M05563610HM2</t>
         </is>
       </c>
       <c r="F167" s="4" t="inlineStr">
         <is>
-          <t>812794</t>
+          <t>814486</t>
         </is>
       </c>
       <c r="G167" s="5" t="inlineStr">
@@ -9375,7 +9375,7 @@
       </c>
       <c r="L167" s="5" t="n"/>
       <c r="M167" s="7" t="n">
-        <v>13.12</v>
+        <v>14.14</v>
       </c>
     </row>
     <row r="168">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955152 - KIT4M05563514P8T</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955482 - KIT4M055635088NK</t>
         </is>
       </c>
       <c r="C168" s="3" t="n">
@@ -9397,12 +9397,12 @@
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563514P8T</t>
+          <t>KIT4M055635088NK</t>
         </is>
       </c>
       <c r="F168" s="4" t="inlineStr">
         <is>
-          <t>814436</t>
+          <t>814434</t>
         </is>
       </c>
       <c r="G168" s="5" t="inlineStr">
@@ -9428,7 +9428,7 @@
       </c>
       <c r="L168" s="5" t="n"/>
       <c r="M168" s="7" t="n">
-        <v>12.96</v>
+        <v>14.13</v>
       </c>
     </row>
     <row r="169">
@@ -9481,7 +9481,7 @@
       </c>
       <c r="L169" s="5" t="n"/>
       <c r="M169" s="7" t="n">
-        <v>12.8</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="170">
@@ -9492,7 +9492,7 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955042 - KIT4P00072391SZM</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649492 - KIT4M054138074NS</t>
         </is>
       </c>
       <c r="C170" s="3" t="n">
@@ -9503,17 +9503,17 @@
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00072391SZM</t>
+          <t>KIT4M054138074NS</t>
         </is>
       </c>
       <c r="F170" s="4" t="inlineStr">
         <is>
-          <t>814493</t>
+          <t>812816</t>
         </is>
       </c>
       <c r="G170" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H170" s="5" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="L170" s="5" t="n"/>
       <c r="M170" s="7" t="n">
-        <v>12.53</v>
+        <v>13.83</v>
       </c>
     </row>
     <row r="171">
@@ -9545,7 +9545,7 @@
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020955432 - KIT4M05563533M9N</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827010 - KIT4M046047372KJ</t>
         </is>
       </c>
       <c r="C171" s="3" t="n">
@@ -9556,12 +9556,12 @@
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563533M9N</t>
+          <t>KIT4M046047372KJ</t>
         </is>
       </c>
       <c r="F171" s="4" t="inlineStr">
         <is>
-          <t>814485</t>
+          <t>809658</t>
         </is>
       </c>
       <c r="G171" s="5" t="inlineStr">
@@ -9587,7 +9587,7 @@
       </c>
       <c r="L171" s="5" t="n"/>
       <c r="M171" s="7" t="n">
-        <v>11.62</v>
+        <v>13.65</v>
       </c>
     </row>
     <row r="172">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020650152 - KIT4M054138189C7</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649442 - KIT4M054137885SM</t>
         </is>
       </c>
       <c r="C172" s="3" t="n">
@@ -9609,12 +9609,12 @@
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138189C7</t>
+          <t>KIT4M054137885SM</t>
         </is>
       </c>
       <c r="F172" s="4" t="inlineStr">
         <is>
-          <t>812831</t>
+          <t>812846</t>
         </is>
       </c>
       <c r="G172" s="5" t="inlineStr">
@@ -9640,7 +9640,7 @@
       </c>
       <c r="L172" s="5" t="n"/>
       <c r="M172" s="7" t="n">
-        <v>11.19</v>
+        <v>13.24</v>
       </c>
     </row>
     <row r="173">
@@ -9651,7 +9651,7 @@
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 020955242 - KIT4M05563511FF4</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955152 - KIT4M05563514P8T</t>
         </is>
       </c>
       <c r="C173" s="3" t="n">
@@ -9662,12 +9662,12 @@
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563511FF4</t>
+          <t>KIT4M05563514P8T</t>
         </is>
       </c>
       <c r="F173" s="4" t="inlineStr">
         <is>
-          <t>814437</t>
+          <t>814436</t>
         </is>
       </c>
       <c r="G173" s="5" t="inlineStr">
@@ -9693,7 +9693,7 @@
       </c>
       <c r="L173" s="5" t="n"/>
       <c r="M173" s="7" t="n">
-        <v>10.96</v>
+        <v>13.22</v>
       </c>
     </row>
     <row r="174">
@@ -9704,7 +9704,7 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020650122-KIT4M05413776H84</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020955432 - KIT4M05563533M9N</t>
         </is>
       </c>
       <c r="C174" s="3" t="n">
@@ -9715,12 +9715,12 @@
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413776H84</t>
+          <t>KIT4M05563533M9N</t>
         </is>
       </c>
       <c r="F174" s="4" t="inlineStr">
         <is>
-          <t>810101</t>
+          <t>814485</t>
         </is>
       </c>
       <c r="G174" s="5" t="inlineStr">
@@ -9746,7 +9746,7 @@
       </c>
       <c r="L174" s="5" t="n"/>
       <c r="M174" s="7" t="n">
-        <v>10.9</v>
+        <v>11.92</v>
       </c>
     </row>
     <row r="175">
@@ -9757,7 +9757,7 @@
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649582 - KIT4M05413774JZX</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649282 - KIT4M05368213974</t>
         </is>
       </c>
       <c r="C175" s="3" t="n">
@@ -9768,12 +9768,12 @@
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413774JZX</t>
+          <t>KIT4M05368213974</t>
         </is>
       </c>
       <c r="F175" s="4" t="inlineStr">
         <is>
-          <t>812836</t>
+          <t>810647</t>
         </is>
       </c>
       <c r="G175" s="5" t="inlineStr">
@@ -9799,7 +9799,7 @@
       </c>
       <c r="L175" s="5" t="n"/>
       <c r="M175" s="7" t="n">
-        <v>10.46</v>
+        <v>11.47</v>
       </c>
     </row>
     <row r="176">
@@ -9810,7 +9810,7 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955502 - KIT4M05563502GJS</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020650152 - KIT4M054138189C7</t>
         </is>
       </c>
       <c r="C176" s="3" t="n">
@@ -9821,12 +9821,12 @@
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563502GJS</t>
+          <t>KIT4M054138189C7</t>
         </is>
       </c>
       <c r="F176" s="4" t="inlineStr">
         <is>
-          <t>814470</t>
+          <t>812831</t>
         </is>
       </c>
       <c r="G176" s="5" t="inlineStr">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="L176" s="5" t="n"/>
       <c r="M176" s="7" t="n">
-        <v>9.81</v>
+        <v>11.19</v>
       </c>
     </row>
     <row r="177">
@@ -9863,7 +9863,7 @@
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649282 - KIT4M05368213974</t>
+          <t>SS - 05900510 -  Los Angeles CA - 020955242 - KIT4M05563511FF4</t>
         </is>
       </c>
       <c r="C177" s="3" t="n">
@@ -9874,12 +9874,12 @@
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368213974</t>
+          <t>KIT4M05563511FF4</t>
         </is>
       </c>
       <c r="F177" s="4" t="inlineStr">
         <is>
-          <t>810647</t>
+          <t>814437</t>
         </is>
       </c>
       <c r="G177" s="5" t="inlineStr">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="L177" s="5" t="n"/>
       <c r="M177" s="7" t="n">
-        <v>9.65</v>
+        <v>10.96</v>
       </c>
     </row>
     <row r="178">
@@ -9916,7 +9916,7 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955612 - KIT4M0556355588P</t>
+          <t>SMRT-05900510-Los Angeles CA-020650122-KIT4M05413776H84</t>
         </is>
       </c>
       <c r="C178" s="3" t="n">
@@ -9927,12 +9927,12 @@
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0556355588P</t>
+          <t>KIT4M05413776H84</t>
         </is>
       </c>
       <c r="F178" s="4" t="inlineStr">
         <is>
-          <t>814455</t>
+          <t>810101</t>
         </is>
       </c>
       <c r="G178" s="5" t="inlineStr">
@@ -9958,7 +9958,7 @@
       </c>
       <c r="L178" s="5" t="n"/>
       <c r="M178" s="7" t="n">
-        <v>9.140000000000001</v>
+        <v>10.94</v>
       </c>
     </row>
     <row r="179">
@@ -9969,7 +9969,7 @@
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020649252 - KIT4P00066848VQM</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649582 - KIT4M05413774JZX</t>
         </is>
       </c>
       <c r="C179" s="3" t="n">
@@ -9980,17 +9980,17 @@
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00066848VQM</t>
+          <t>KIT4M05413774JZX</t>
         </is>
       </c>
       <c r="F179" s="4" t="inlineStr">
         <is>
-          <t>812923</t>
+          <t>812836</t>
         </is>
       </c>
       <c r="G179" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H179" s="5" t="inlineStr">
@@ -10011,7 +10011,7 @@
       </c>
       <c r="L179" s="5" t="n"/>
       <c r="M179" s="7" t="n">
-        <v>7.27</v>
+        <v>10.46</v>
       </c>
     </row>
     <row r="180">
@@ -10022,7 +10022,7 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649792 - KIT4M04475151HTP</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955612 - KIT4M0556355588P</t>
         </is>
       </c>
       <c r="C180" s="3" t="n">
@@ -10033,12 +10033,12 @@
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475151HTP</t>
+          <t>KIT4M0556355588P</t>
         </is>
       </c>
       <c r="F180" s="4" t="inlineStr">
         <is>
-          <t>809867</t>
+          <t>814455</t>
         </is>
       </c>
       <c r="G180" s="5" t="inlineStr">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="L180" s="5" t="n"/>
       <c r="M180" s="7" t="n">
-        <v>7.08</v>
+        <v>9.140000000000001</v>
       </c>
     </row>
     <row r="181">
@@ -10075,7 +10075,7 @@
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270114 - KIT4M04476539RJ5</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020649252 - KIT4P00066848VQM</t>
         </is>
       </c>
       <c r="C181" s="3" t="n">
@@ -10086,17 +10086,17 @@
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04476539RJ5</t>
+          <t>KIT4P00066848VQM</t>
         </is>
       </c>
       <c r="F181" s="4" t="inlineStr">
         <is>
-          <t>809612</t>
+          <t>812923</t>
         </is>
       </c>
       <c r="G181" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H181" s="5" t="inlineStr">
@@ -10117,7 +10117,7 @@
       </c>
       <c r="L181" s="5" t="n"/>
       <c r="M181" s="7" t="n">
-        <v>6.74</v>
+        <v>8.93</v>
       </c>
     </row>
     <row r="182">
@@ -10128,7 +10128,7 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles, CA - 0204827011114 - KIT4M03986267RWH</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270114 - KIT4M04476539RJ5</t>
         </is>
       </c>
       <c r="C182" s="3" t="n">
@@ -10139,12 +10139,12 @@
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03986267RWH</t>
+          <t>KIT4M04476539RJ5</t>
         </is>
       </c>
       <c r="F182" s="4" t="inlineStr">
         <is>
-          <t>809616</t>
+          <t>809612</t>
         </is>
       </c>
       <c r="G182" s="5" t="inlineStr">
@@ -10170,7 +10170,7 @@
       </c>
       <c r="L182" s="5" t="n"/>
       <c r="M182" s="7" t="n">
-        <v>6.66</v>
+        <v>7.65</v>
       </c>
     </row>
     <row r="183">
@@ -10181,7 +10181,7 @@
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649642 - KIT4M05413826Z6Z</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649962 - KIT4M05413783PFQ</t>
         </is>
       </c>
       <c r="C183" s="3" t="n">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413826Z6Z</t>
+          <t>KIT4M05413783PFQ</t>
         </is>
       </c>
       <c r="F183" s="4" t="inlineStr">
         <is>
-          <t>812804</t>
+          <t>812845</t>
         </is>
       </c>
       <c r="G183" s="5" t="inlineStr">
@@ -10223,7 +10223,7 @@
       </c>
       <c r="L183" s="5" t="n"/>
       <c r="M183" s="7" t="n">
-        <v>5.9</v>
+        <v>7.24</v>
       </c>
     </row>
     <row r="184">
@@ -10234,7 +10234,7 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827011110 - KIT4M03866627GHD</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649792 - KIT4M04475151HTP</t>
         </is>
       </c>
       <c r="C184" s="3" t="n">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03866627GHD</t>
+          <t>KIT4M04475151HTP</t>
         </is>
       </c>
       <c r="F184" s="4" t="inlineStr">
         <is>
-          <t>809619</t>
+          <t>809867</t>
         </is>
       </c>
       <c r="G184" s="5" t="inlineStr">
@@ -10276,7 +10276,7 @@
       </c>
       <c r="L184" s="5" t="n"/>
       <c r="M184" s="7" t="n">
-        <v>5.78</v>
+        <v>7.08</v>
       </c>
     </row>
     <row r="185">
@@ -10287,7 +10287,7 @@
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270110 - KIT4M038677586ZX</t>
+          <t>STS - 05900510 - Los Angeles, CA - 0204827011114 - KIT4M03986267RWH</t>
         </is>
       </c>
       <c r="C185" s="3" t="n">
@@ -10298,12 +10298,12 @@
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>KIT4M038677586ZX</t>
+          <t>KIT4M03986267RWH</t>
         </is>
       </c>
       <c r="F185" s="4" t="inlineStr">
         <is>
-          <t>809623</t>
+          <t>809616</t>
         </is>
       </c>
       <c r="G185" s="5" t="inlineStr">
@@ -10329,7 +10329,7 @@
       </c>
       <c r="L185" s="5" t="n"/>
       <c r="M185" s="7" t="n">
-        <v>5.55</v>
+        <v>6.68</v>
       </c>
     </row>
     <row r="186">
@@ -10340,7 +10340,7 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020650182 - KIT4M05413821GGW</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649642 - KIT4M05413826Z6Z</t>
         </is>
       </c>
       <c r="C186" s="3" t="n">
@@ -10351,12 +10351,12 @@
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413821GGW</t>
+          <t>KIT4M05413826Z6Z</t>
         </is>
       </c>
       <c r="F186" s="4" t="inlineStr">
         <is>
-          <t>812830</t>
+          <t>812804</t>
         </is>
       </c>
       <c r="G186" s="5" t="inlineStr">
@@ -10382,7 +10382,7 @@
       </c>
       <c r="L186" s="5" t="n"/>
       <c r="M186" s="7" t="n">
-        <v>5.51</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="187">
@@ -10393,7 +10393,7 @@
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437902 - KIT4M05799717WZV</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827011110 - KIT4M03866627GHD</t>
         </is>
       </c>
       <c r="C187" s="3" t="n">
@@ -10404,12 +10404,12 @@
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799717WZV</t>
+          <t>KIT4M03866627GHD</t>
         </is>
       </c>
       <c r="F187" s="4" t="inlineStr">
         <is>
-          <t>816280</t>
+          <t>809619</t>
         </is>
       </c>
       <c r="G187" s="5" t="inlineStr">
@@ -10435,7 +10435,7 @@
       </c>
       <c r="L187" s="5" t="n"/>
       <c r="M187" s="7" t="n">
-        <v>5.14</v>
+        <v>5.78</v>
       </c>
     </row>
     <row r="188">
@@ -10446,7 +10446,7 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649962 - KIT4M05413783PFQ</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649732 - KIT4M046047467T4</t>
         </is>
       </c>
       <c r="C188" s="3" t="n">
@@ -10457,12 +10457,12 @@
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413783PFQ</t>
+          <t>KIT4M046047467T4</t>
         </is>
       </c>
       <c r="F188" s="4" t="inlineStr">
         <is>
-          <t>812845</t>
+          <t>809865</t>
         </is>
       </c>
       <c r="G188" s="5" t="inlineStr">
@@ -10488,7 +10488,7 @@
       </c>
       <c r="L188" s="5" t="n"/>
       <c r="M188" s="7" t="n">
-        <v>4.65</v>
+        <v>5.64</v>
       </c>
     </row>
     <row r="189">
@@ -10499,7 +10499,7 @@
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437582 - KIT4M05872573K7P</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270110 - KIT4M038677586ZX</t>
         </is>
       </c>
       <c r="C189" s="3" t="n">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872573K7P</t>
+          <t>KIT4M038677586ZX</t>
         </is>
       </c>
       <c r="F189" s="4" t="inlineStr">
         <is>
-          <t>816067</t>
+          <t>809623</t>
         </is>
       </c>
       <c r="G189" s="5" t="inlineStr">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="L189" s="5" t="n"/>
       <c r="M189" s="7" t="n">
-        <v>4.28</v>
+        <v>5.59</v>
       </c>
     </row>
     <row r="190">
@@ -10552,7 +10552,7 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649732 - KIT4M046047467T4</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020650182 - KIT4M05413821GGW</t>
         </is>
       </c>
       <c r="C190" s="3" t="n">
@@ -10563,12 +10563,12 @@
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047467T4</t>
+          <t>KIT4M05413821GGW</t>
         </is>
       </c>
       <c r="F190" s="4" t="inlineStr">
         <is>
-          <t>809865</t>
+          <t>812830</t>
         </is>
       </c>
       <c r="G190" s="5" t="inlineStr">
@@ -10594,7 +10594,7 @@
       </c>
       <c r="L190" s="5" t="n"/>
       <c r="M190" s="7" t="n">
-        <v>4.13</v>
+        <v>5.51</v>
       </c>
     </row>
     <row r="191">
@@ -10605,7 +10605,7 @@
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649492 - KIT4M054138074NS</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437902 - KIT4M05799717WZV</t>
         </is>
       </c>
       <c r="C191" s="3" t="n">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138074NS</t>
+          <t>KIT4M05799717WZV</t>
         </is>
       </c>
       <c r="F191" s="4" t="inlineStr">
         <is>
-          <t>812816</t>
+          <t>816280</t>
         </is>
       </c>
       <c r="G191" s="5" t="inlineStr">
@@ -10647,7 +10647,7 @@
       </c>
       <c r="L191" s="5" t="n"/>
       <c r="M191" s="7" t="n">
-        <v>3.8</v>
+        <v>5.24</v>
       </c>
     </row>
     <row r="192">
@@ -10658,7 +10658,7 @@
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437402 - KIT4M05872537SGZ</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437582 - KIT4M05872573K7P</t>
         </is>
       </c>
       <c r="C192" s="3" t="n">
@@ -10669,12 +10669,12 @@
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872537SGZ</t>
+          <t>KIT4M05872573K7P</t>
         </is>
       </c>
       <c r="F192" s="4" t="inlineStr">
         <is>
-          <t>816073</t>
+          <t>816067</t>
         </is>
       </c>
       <c r="G192" s="5" t="inlineStr">
@@ -10700,7 +10700,7 @@
       </c>
       <c r="L192" s="5" t="n"/>
       <c r="M192" s="7" t="n">
-        <v>3.05</v>
+        <v>4.28</v>
       </c>
     </row>
     <row r="193">
@@ -10711,7 +10711,7 @@
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649752 - KIT4M03867749CW5</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437592 - KIT4M05872582TC7</t>
         </is>
       </c>
       <c r="C193" s="3" t="n">
@@ -10722,12 +10722,12 @@
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03867749CW5</t>
+          <t>KIT4M05872582TC7</t>
         </is>
       </c>
       <c r="F193" s="4" t="inlineStr">
         <is>
-          <t>809877</t>
+          <t>816107</t>
         </is>
       </c>
       <c r="G193" s="5" t="inlineStr">
@@ -10753,7 +10753,7 @@
       </c>
       <c r="L193" s="5" t="n"/>
       <c r="M193" s="7" t="n">
-        <v>2.96</v>
+        <v>3.27</v>
       </c>
     </row>
     <row r="194">
@@ -10764,7 +10764,7 @@
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827012 - KIT4M04606110GTV</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437402 - KIT4M05872537SGZ</t>
         </is>
       </c>
       <c r="C194" s="3" t="n">
@@ -10775,12 +10775,12 @@
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04606110GTV</t>
+          <t>KIT4M05872537SGZ</t>
         </is>
       </c>
       <c r="F194" s="4" t="inlineStr">
         <is>
-          <t>809660</t>
+          <t>816073</t>
         </is>
       </c>
       <c r="G194" s="5" t="inlineStr">
@@ -10806,7 +10806,7 @@
       </c>
       <c r="L194" s="5" t="n"/>
       <c r="M194" s="7" t="n">
-        <v>2.61</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="195">
@@ -10817,7 +10817,7 @@
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437932 - KIT4M05799732NQK</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649752 - KIT4M03867749CW5</t>
         </is>
       </c>
       <c r="C195" s="3" t="n">
@@ -10828,12 +10828,12 @@
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799732NQK</t>
+          <t>KIT4M03867749CW5</t>
         </is>
       </c>
       <c r="F195" s="4" t="inlineStr">
         <is>
-          <t>816275</t>
+          <t>809877</t>
         </is>
       </c>
       <c r="G195" s="5" t="inlineStr">
@@ -10859,7 +10859,7 @@
       </c>
       <c r="L195" s="5" t="n"/>
       <c r="M195" s="7" t="n">
-        <v>2.48</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="196">
@@ -10912,7 +10912,7 @@
       </c>
       <c r="L196" s="5" t="n"/>
       <c r="M196" s="7" t="n">
-        <v>2.17</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="197">
@@ -10923,7 +10923,7 @@
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>SSC - 05900510 -  Los Angeles CA - 021437862 - KIT4M05872516CJM</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827012 - KIT4M04606110GTV</t>
         </is>
       </c>
       <c r="C197" s="3" t="n">
@@ -10934,12 +10934,12 @@
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872516CJM</t>
+          <t>KIT4M04606110GTV</t>
         </is>
       </c>
       <c r="F197" s="4" t="inlineStr">
         <is>
-          <t>816087</t>
+          <t>809660</t>
         </is>
       </c>
       <c r="G197" s="5" t="inlineStr">
@@ -10965,7 +10965,7 @@
       </c>
       <c r="L197" s="5" t="n"/>
       <c r="M197" s="7" t="n">
-        <v>1.89</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="198">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438262 - KIT4M05872530RPF</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437932 - KIT4M05799732NQK</t>
         </is>
       </c>
       <c r="C198" s="3" t="n">
@@ -10987,12 +10987,12 @@
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872530RPF</t>
+          <t>KIT4M05799732NQK</t>
         </is>
       </c>
       <c r="F198" s="4" t="inlineStr">
         <is>
-          <t>816079</t>
+          <t>816275</t>
         </is>
       </c>
       <c r="G198" s="5" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="L198" s="5" t="n"/>
       <c r="M198" s="7" t="n">
-        <v>1.79</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="199">
@@ -11029,7 +11029,7 @@
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 020955572 - KIT4M05563606ZRC</t>
+          <t>SSC - 05900510 -  Los Angeles CA - 021437862 - KIT4M05872516CJM</t>
         </is>
       </c>
       <c r="C199" s="3" t="n">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563606ZRC</t>
+          <t>KIT4M05872516CJM</t>
         </is>
       </c>
       <c r="F199" s="4" t="inlineStr">
         <is>
-          <t>814464</t>
+          <t>816087</t>
         </is>
       </c>
       <c r="G199" s="5" t="inlineStr">
@@ -11071,7 +11071,7 @@
       </c>
       <c r="L199" s="5" t="n"/>
       <c r="M199" s="7" t="n">
-        <v>1.6</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="200">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437612 - KIT4M058725265DP</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437412 - KIT4M05872548P2H</t>
         </is>
       </c>
       <c r="C200" s="3" t="n">
@@ -11093,12 +11093,12 @@
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725265DP</t>
+          <t>KIT4M05872548P2H</t>
         </is>
       </c>
       <c r="F200" s="4" t="inlineStr">
         <is>
-          <t>816192</t>
+          <t>816066</t>
         </is>
       </c>
       <c r="G200" s="5" t="inlineStr">
@@ -11124,7 +11124,7 @@
       </c>
       <c r="L200" s="5" t="n"/>
       <c r="M200" s="7" t="n">
-        <v>1.58</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="201">
@@ -11135,7 +11135,7 @@
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437412 - KIT4M05872548P2H</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438262 - KIT4M05872530RPF</t>
         </is>
       </c>
       <c r="C201" s="3" t="n">
@@ -11146,12 +11146,12 @@
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872548P2H</t>
+          <t>KIT4M05872530RPF</t>
         </is>
       </c>
       <c r="F201" s="4" t="inlineStr">
         <is>
-          <t>816066</t>
+          <t>816079</t>
         </is>
       </c>
       <c r="G201" s="5" t="inlineStr">
@@ -11177,7 +11177,7 @@
       </c>
       <c r="L201" s="5" t="n"/>
       <c r="M201" s="7" t="n">
-        <v>1.3</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="202">
@@ -11188,7 +11188,7 @@
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020650022 - KIT4M05413813HSJ</t>
+          <t>SS - 05900510 -  Los Angeles CA - 020955572 - KIT4M05563606ZRC</t>
         </is>
       </c>
       <c r="C202" s="3" t="n">
@@ -11199,12 +11199,12 @@
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413813HSJ</t>
+          <t>KIT4M05563606ZRC</t>
         </is>
       </c>
       <c r="F202" s="4" t="inlineStr">
         <is>
-          <t>812797</t>
+          <t>814464</t>
         </is>
       </c>
       <c r="G202" s="5" t="inlineStr">
@@ -11230,7 +11230,7 @@
       </c>
       <c r="L202" s="5" t="n"/>
       <c r="M202" s="7" t="n">
-        <v>1.2</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="203">
@@ -11241,7 +11241,7 @@
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649852 - KIT4M05413789Z8C</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437612 - KIT4M058725265DP</t>
         </is>
       </c>
       <c r="C203" s="3" t="n">
@@ -11252,12 +11252,12 @@
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413789Z8C</t>
+          <t>KIT4M058725265DP</t>
         </is>
       </c>
       <c r="F203" s="4" t="inlineStr">
         <is>
-          <t>812840</t>
+          <t>816192</t>
         </is>
       </c>
       <c r="G203" s="5" t="inlineStr">
@@ -11283,7 +11283,7 @@
       </c>
       <c r="L203" s="5" t="n"/>
       <c r="M203" s="7" t="n">
-        <v>1.14</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="204">
@@ -11294,7 +11294,7 @@
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020649652 - KIT4M0541381584X</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020650022 - KIT4M05413813HSJ</t>
         </is>
       </c>
       <c r="C204" s="3" t="n">
@@ -11305,12 +11305,12 @@
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0541381584X</t>
+          <t>KIT4M05413813HSJ</t>
         </is>
       </c>
       <c r="F204" s="4" t="inlineStr">
         <is>
-          <t>812810</t>
+          <t>812797</t>
         </is>
       </c>
       <c r="G204" s="5" t="inlineStr">
@@ -11336,7 +11336,7 @@
       </c>
       <c r="L204" s="5" t="n"/>
       <c r="M204" s="7" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="205">
@@ -11347,7 +11347,7 @@
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438282 - KIT4M05872508VTN</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649852 - KIT4M05413789Z8C</t>
         </is>
       </c>
       <c r="C205" s="3" t="n">
@@ -11358,12 +11358,12 @@
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872508VTN</t>
+          <t>KIT4M05413789Z8C</t>
         </is>
       </c>
       <c r="F205" s="4" t="inlineStr">
         <is>
-          <t>816076</t>
+          <t>812840</t>
         </is>
       </c>
       <c r="G205" s="5" t="inlineStr">
@@ -11389,7 +11389,7 @@
       </c>
       <c r="L205" s="5" t="n"/>
       <c r="M205" s="7" t="n">
-        <v>0.92</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="206">
@@ -11400,7 +11400,7 @@
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649892 - KIT4M05413777DGG</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020649652 - KIT4M0541381584X</t>
         </is>
       </c>
       <c r="C206" s="3" t="n">
@@ -11411,12 +11411,12 @@
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413777DGG</t>
+          <t>KIT4M0541381584X</t>
         </is>
       </c>
       <c r="F206" s="4" t="inlineStr">
         <is>
-          <t>812802</t>
+          <t>812810</t>
         </is>
       </c>
       <c r="G206" s="5" t="inlineStr">
@@ -11442,7 +11442,7 @@
       </c>
       <c r="L206" s="5" t="n"/>
       <c r="M206" s="7" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="207">
@@ -11453,7 +11453,7 @@
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491804TBC</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649892 - KIT4M05413777DGG</t>
         </is>
       </c>
       <c r="C207" s="3" t="n">
@@ -11464,12 +11464,12 @@
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491804TBC</t>
+          <t>KIT4M05413777DGG</t>
         </is>
       </c>
       <c r="F207" s="4" t="inlineStr">
         <is>
-          <t>816373</t>
+          <t>812802</t>
         </is>
       </c>
       <c r="G207" s="5" t="inlineStr">
@@ -11495,7 +11495,7 @@
       </c>
       <c r="L207" s="5" t="n"/>
       <c r="M207" s="7" t="n">
-        <v>0.6</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="208">
@@ -11506,7 +11506,7 @@
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491800F52</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438282 - KIT4M05872508VTN</t>
         </is>
       </c>
       <c r="C208" s="3" t="n">
@@ -11517,12 +11517,12 @@
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491800F52</t>
+          <t>KIT4M05872508VTN</t>
         </is>
       </c>
       <c r="F208" s="4" t="inlineStr">
         <is>
-          <t>816406</t>
+          <t>816076</t>
         </is>
       </c>
       <c r="G208" s="5" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="L208" s="5" t="n"/>
       <c r="M208" s="7" t="n">
-        <v>0.35</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="209">
@@ -11559,7 +11559,7 @@
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437592 - KIT4M05872582TC7</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491804TBC</t>
         </is>
       </c>
       <c r="C209" s="3" t="n">
@@ -11570,12 +11570,12 @@
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872582TC7</t>
+          <t>KIT4M06491804TBC</t>
         </is>
       </c>
       <c r="F209" s="4" t="inlineStr">
         <is>
-          <t>816107</t>
+          <t>816373</t>
         </is>
       </c>
       <c r="G209" s="5" t="inlineStr">
@@ -11601,7 +11601,7 @@
       </c>
       <c r="L209" s="5" t="n"/>
       <c r="M209" s="7" t="n">
-        <v>0.28</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="210">
@@ -11612,7 +11612,7 @@
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437812-KIT4M058724947VX</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491800F52</t>
         </is>
       </c>
       <c r="C210" s="3" t="n">
@@ -11623,12 +11623,12 @@
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058724947VX</t>
+          <t>KIT4M06491800F52</t>
         </is>
       </c>
       <c r="F210" s="4" t="inlineStr">
         <is>
-          <t>816086</t>
+          <t>816406</t>
         </is>
       </c>
       <c r="G210" s="5" t="inlineStr">
@@ -11654,7 +11654,7 @@
       </c>
       <c r="L210" s="5" t="n"/>
       <c r="M210" s="7" t="n">
-        <v>0.26</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="211">
@@ -11665,7 +11665,7 @@
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020650062 - KIT4M05413797HK5</t>
+          <t>SMRT-05900510-Los Angeles CA-021437812-KIT4M058724947VX</t>
         </is>
       </c>
       <c r="C211" s="3" t="n">
@@ -11676,12 +11676,12 @@
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413797HK5</t>
+          <t>KIT4M058724947VX</t>
         </is>
       </c>
       <c r="F211" s="4" t="inlineStr">
         <is>
-          <t>812808</t>
+          <t>816086</t>
         </is>
       </c>
       <c r="G211" s="5" t="inlineStr">
@@ -11707,7 +11707,7 @@
       </c>
       <c r="L211" s="5" t="n"/>
       <c r="M211" s="7" t="n">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="212">
@@ -11718,7 +11718,7 @@
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020649522-KIT4M05413834FTH</t>
+          <t>SS - 05900510 - Los Angeles CA - 020650062 - KIT4M05413797HK5</t>
         </is>
       </c>
       <c r="C212" s="3" t="n">
@@ -11729,12 +11729,12 @@
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413834FTH</t>
+          <t>KIT4M05413797HK5</t>
         </is>
       </c>
       <c r="F212" s="4" t="inlineStr">
         <is>
-          <t>812817</t>
+          <t>812808</t>
         </is>
       </c>
       <c r="G212" s="5" t="inlineStr">
@@ -11760,7 +11760,7 @@
       </c>
       <c r="L212" s="5" t="n"/>
       <c r="M212" s="7" t="n">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="213">
@@ -11771,7 +11771,7 @@
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 6862083  - KIT4M05799682BXX</t>
+          <t>SMRT-05900510-Los Angeles CA-020649522-KIT4M05413834FTH</t>
         </is>
       </c>
       <c r="C213" s="3" t="n">
@@ -11782,12 +11782,12 @@
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799682BXX</t>
+          <t>KIT4M05413834FTH</t>
         </is>
       </c>
       <c r="F213" s="4" t="inlineStr">
         <is>
-          <t>816278</t>
+          <t>812817</t>
         </is>
       </c>
       <c r="G213" s="5" t="inlineStr">
@@ -11813,7 +11813,7 @@
       </c>
       <c r="L213" s="5" t="n"/>
       <c r="M213" s="7" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="214">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437832 - KIT4M05872486FXZ</t>
+          <t>SS - 05900510 - Los Angeles CA - 6862083  - KIT4M05799682BXX</t>
         </is>
       </c>
       <c r="C214" s="3" t="n">
@@ -11835,12 +11835,12 @@
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872486FXZ</t>
+          <t>KIT4M05799682BXX</t>
         </is>
       </c>
       <c r="F214" s="4" t="inlineStr">
         <is>
-          <t>816088</t>
+          <t>816278</t>
         </is>
       </c>
       <c r="G214" s="5" t="inlineStr">
@@ -11866,7 +11866,7 @@
       </c>
       <c r="L214" s="5" t="n"/>
       <c r="M214" s="7" t="n">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="215">
@@ -11877,7 +11877,7 @@
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955422 - KIT4M05563517BVR</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437832 - KIT4M05872486FXZ</t>
         </is>
       </c>
       <c r="C215" s="3" t="n">
@@ -11888,12 +11888,12 @@
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563517BVR</t>
+          <t>KIT4M05872486FXZ</t>
         </is>
       </c>
       <c r="F215" s="4" t="inlineStr">
         <is>
-          <t>814438</t>
+          <t>816088</t>
         </is>
       </c>
       <c r="G215" s="5" t="inlineStr">
@@ -11919,7 +11919,7 @@
       </c>
       <c r="L215" s="5" t="n"/>
       <c r="M215" s="7" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="216">
@@ -11930,7 +11930,7 @@
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491836Z2D</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955422 - KIT4M05563517BVR</t>
         </is>
       </c>
       <c r="C216" s="3" t="n">
@@ -11941,12 +11941,12 @@
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491836Z2D</t>
+          <t>KIT4M05563517BVR</t>
         </is>
       </c>
       <c r="F216" s="4" t="inlineStr">
         <is>
-          <t>816366</t>
+          <t>814438</t>
         </is>
       </c>
       <c r="G216" s="5" t="inlineStr">
@@ -11972,7 +11972,7 @@
       </c>
       <c r="L216" s="5" t="n"/>
       <c r="M216" s="7" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="217">
@@ -11983,7 +11983,7 @@
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 6862083  - KIT4M057996395ZF</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438172 - KIT4M05872500684</t>
         </is>
       </c>
       <c r="C217" s="3" t="n">
@@ -11994,12 +11994,12 @@
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>KIT4M057996395ZF</t>
+          <t>KIT4M05872500684</t>
         </is>
       </c>
       <c r="F217" s="4" t="inlineStr">
         <is>
-          <t>816268</t>
+          <t>816081</t>
         </is>
       </c>
       <c r="G217" s="5" t="inlineStr">
@@ -12036,7 +12036,7 @@
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438172 - KIT4M05872500684</t>
+          <t>SS - 05900510 - Los Angeles CA - 6862083  - KIT4M057996395ZF</t>
         </is>
       </c>
       <c r="C218" s="3" t="n">
@@ -12047,12 +12047,12 @@
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872500684</t>
+          <t>KIT4M057996395ZF</t>
         </is>
       </c>
       <c r="F218" s="4" t="inlineStr">
         <is>
-          <t>816081</t>
+          <t>816268</t>
         </is>
       </c>
       <c r="G218" s="5" t="inlineStr">
@@ -12089,7 +12089,7 @@
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491790945</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491836Z2D</t>
         </is>
       </c>
       <c r="C219" s="3" t="n">
@@ -12100,12 +12100,12 @@
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491790945</t>
+          <t>KIT4M06491836Z2D</t>
         </is>
       </c>
       <c r="F219" s="4" t="inlineStr">
         <is>
-          <t>816410</t>
+          <t>816366</t>
         </is>
       </c>
       <c r="G219" s="5" t="inlineStr">
@@ -12142,7 +12142,7 @@
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438022 - KIT4M05799705T6B</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491790945</t>
         </is>
       </c>
       <c r="C220" s="3" t="n">
@@ -12153,12 +12153,12 @@
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799705T6B</t>
+          <t>KIT4M06491790945</t>
         </is>
       </c>
       <c r="F220" s="4" t="inlineStr">
         <is>
-          <t>816285</t>
+          <t>816410</t>
         </is>
       </c>
       <c r="G220" s="5" t="inlineStr">
@@ -12184,7 +12184,7 @@
       </c>
       <c r="L220" s="5" t="n"/>
       <c r="M220" s="7" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="221">
@@ -12195,7 +12195,7 @@
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491814FV7</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437302 - KIT4M05872571T4K</t>
         </is>
       </c>
       <c r="C221" s="3" t="n">
@@ -12206,12 +12206,12 @@
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491814FV7</t>
+          <t>KIT4M05872571T4K</t>
         </is>
       </c>
       <c r="F221" s="4" t="inlineStr">
         <is>
-          <t>816370</t>
+          <t>816106</t>
         </is>
       </c>
       <c r="G221" s="5" t="inlineStr">
@@ -12248,7 +12248,7 @@
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437302 - KIT4M05872571T4K</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491814FV7</t>
         </is>
       </c>
       <c r="C222" s="3" t="n">
@@ -12259,12 +12259,12 @@
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872571T4K</t>
+          <t>KIT4M06491814FV7</t>
         </is>
       </c>
       <c r="F222" s="4" t="inlineStr">
         <is>
-          <t>816106</t>
+          <t>816370</t>
         </is>
       </c>
       <c r="G222" s="5" t="inlineStr">
@@ -12301,7 +12301,7 @@
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918277QF</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438022 - KIT4M05799705T6B</t>
         </is>
       </c>
       <c r="C223" s="3" t="n">
@@ -12312,12 +12312,12 @@
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918277QF</t>
+          <t>KIT4M05799705T6B</t>
         </is>
       </c>
       <c r="F223" s="4" t="inlineStr">
         <is>
-          <t>816403</t>
+          <t>816285</t>
         </is>
       </c>
       <c r="G223" s="5" t="inlineStr">
@@ -12343,7 +12343,7 @@
       </c>
       <c r="L223" s="5" t="n"/>
       <c r="M223" s="7" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="224">
@@ -12354,7 +12354,7 @@
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 021438182 - KIT4M05872528P9D</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918277QF</t>
         </is>
       </c>
       <c r="C224" s="3" t="n">
@@ -12365,12 +12365,12 @@
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872528P9D</t>
+          <t>KIT4M064918277QF</t>
         </is>
       </c>
       <c r="F224" s="4" t="inlineStr">
         <is>
-          <t>816089</t>
+          <t>816403</t>
         </is>
       </c>
       <c r="G224" s="5" t="inlineStr">
@@ -12396,7 +12396,7 @@
       </c>
       <c r="L224" s="5" t="n"/>
       <c r="M224" s="7" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="225">
@@ -12407,7 +12407,7 @@
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491821G25</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437312 - KIT4M05872568PR6</t>
         </is>
       </c>
       <c r="C225" s="3" t="n">
@@ -12418,12 +12418,12 @@
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491821G25</t>
+          <t>KIT4M05872568PR6</t>
         </is>
       </c>
       <c r="F225" s="4" t="inlineStr">
         <is>
-          <t>816379</t>
+          <t>816094</t>
         </is>
       </c>
       <c r="G225" s="5" t="inlineStr">
@@ -12460,7 +12460,7 @@
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437312 - KIT4M05872568PR6</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437732 - KIT4M05872588W8G</t>
         </is>
       </c>
       <c r="C226" s="3" t="n">
@@ -12471,12 +12471,12 @@
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872568PR6</t>
+          <t>KIT4M05872588W8G</t>
         </is>
       </c>
       <c r="F226" s="4" t="inlineStr">
         <is>
-          <t>816094</t>
+          <t>816100</t>
         </is>
       </c>
       <c r="G226" s="5" t="inlineStr">
@@ -12513,7 +12513,7 @@
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438252 - KIT4M05872519KTN</t>
+          <t>SS - 05900510 -  Los Angeles CA - 021438182 - KIT4M05872528P9D</t>
         </is>
       </c>
       <c r="C227" s="3" t="n">
@@ -12524,12 +12524,12 @@
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872519KTN</t>
+          <t>KIT4M05872528P9D</t>
         </is>
       </c>
       <c r="F227" s="4" t="inlineStr">
         <is>
-          <t>816084</t>
+          <t>816089</t>
         </is>
       </c>
       <c r="G227" s="5" t="inlineStr">
@@ -12566,7 +12566,7 @@
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437732 - KIT4M05872588W8G</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437722 - KIT4M05872498PP4</t>
         </is>
       </c>
       <c r="C228" s="3" t="n">
@@ -12577,12 +12577,12 @@
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872588W8G</t>
+          <t>KIT4M05872498PP4</t>
         </is>
       </c>
       <c r="F228" s="4" t="inlineStr">
         <is>
-          <t>816100</t>
+          <t>816104</t>
         </is>
       </c>
       <c r="G228" s="5" t="inlineStr">
@@ -12619,7 +12619,7 @@
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437722 - KIT4M05872498PP4</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438252 - KIT4M05872519KTN</t>
         </is>
       </c>
       <c r="C229" s="3" t="n">
@@ -12630,12 +12630,12 @@
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872498PP4</t>
+          <t>KIT4M05872519KTN</t>
         </is>
       </c>
       <c r="F229" s="4" t="inlineStr">
         <is>
-          <t>816104</t>
+          <t>816084</t>
         </is>
       </c>
       <c r="G229" s="5" t="inlineStr">
@@ -12672,7 +12672,7 @@
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437332 - KIT4M05872554RHM</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491821G25</t>
         </is>
       </c>
       <c r="C230" s="3" t="n">
@@ -12683,12 +12683,12 @@
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872554RHM</t>
+          <t>KIT4M06491821G25</t>
         </is>
       </c>
       <c r="F230" s="4" t="inlineStr">
         <is>
-          <t>816071</t>
+          <t>816379</t>
         </is>
       </c>
       <c r="G230" s="5" t="inlineStr">
@@ -12714,7 +12714,7 @@
       </c>
       <c r="L230" s="5" t="n"/>
       <c r="M230" s="7" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="231">
@@ -12725,7 +12725,7 @@
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437952 - KIT4M05872523VVB</t>
+          <t>SMRT-05900510-Los Angeles CA-021437822-KIT4M0587253378R</t>
         </is>
       </c>
       <c r="C231" s="3" t="n">
@@ -12736,12 +12736,12 @@
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872523VVB</t>
+          <t>KIT4M0587253378R</t>
         </is>
       </c>
       <c r="F231" s="4" t="inlineStr">
         <is>
-          <t>816215</t>
+          <t>816210</t>
         </is>
       </c>
       <c r="G231" s="5" t="inlineStr">
@@ -12778,7 +12778,7 @@
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437692 - KIT4M05872518P78</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437332 - KIT4M05872554RHM</t>
         </is>
       </c>
       <c r="C232" s="3" t="n">
@@ -12789,12 +12789,12 @@
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872518P78</t>
+          <t>KIT4M05872554RHM</t>
         </is>
       </c>
       <c r="F232" s="4" t="inlineStr">
         <is>
-          <t>816184</t>
+          <t>816071</t>
         </is>
       </c>
       <c r="G232" s="5" t="inlineStr">
@@ -12831,7 +12831,7 @@
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438112 - KIT4M0579970825J</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437342 - KIT4M05872557NFB</t>
         </is>
       </c>
       <c r="C233" s="3" t="n">
@@ -12842,12 +12842,12 @@
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0579970825J</t>
+          <t>KIT4M05872557NFB</t>
         </is>
       </c>
       <c r="F233" s="4" t="inlineStr">
         <is>
-          <t>816290</t>
+          <t>816095</t>
         </is>
       </c>
       <c r="G233" s="5" t="inlineStr">
@@ -12884,7 +12884,7 @@
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491799CRP</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438112 - KIT4M0579970825J</t>
         </is>
       </c>
       <c r="C234" s="3" t="n">
@@ -12895,12 +12895,12 @@
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491799CRP</t>
+          <t>KIT4M0579970825J</t>
         </is>
       </c>
       <c r="F234" s="4" t="inlineStr">
         <is>
-          <t>816394</t>
+          <t>816290</t>
         </is>
       </c>
       <c r="G234" s="5" t="inlineStr">
@@ -12937,7 +12937,7 @@
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918154FM</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437692 - KIT4M05872518P78</t>
         </is>
       </c>
       <c r="C235" s="3" t="n">
@@ -12948,12 +12948,12 @@
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918154FM</t>
+          <t>KIT4M05872518P78</t>
         </is>
       </c>
       <c r="F235" s="4" t="inlineStr">
         <is>
-          <t>816368</t>
+          <t>816184</t>
         </is>
       </c>
       <c r="G235" s="5" t="inlineStr">
@@ -13043,7 +13043,7 @@
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491817T79</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491818QD2</t>
         </is>
       </c>
       <c r="C237" s="3" t="n">
@@ -13054,12 +13054,12 @@
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491817T79</t>
+          <t>KIT4M06491818QD2</t>
         </is>
       </c>
       <c r="F237" s="4" t="inlineStr">
         <is>
-          <t>816415</t>
+          <t>816378</t>
         </is>
       </c>
       <c r="G237" s="5" t="inlineStr">
@@ -13096,7 +13096,7 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491798S8Q</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918197VX</t>
         </is>
       </c>
       <c r="C238" s="3" t="n">
@@ -13107,12 +13107,12 @@
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491798S8Q</t>
+          <t>KIT4M064918197VX</t>
         </is>
       </c>
       <c r="F238" s="4" t="inlineStr">
         <is>
-          <t>816395</t>
+          <t>816397</t>
         </is>
       </c>
       <c r="G238" s="5" t="inlineStr">
@@ -13149,7 +13149,7 @@
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918197VX</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491820X58</t>
         </is>
       </c>
       <c r="C239" s="3" t="n">
@@ -13160,12 +13160,12 @@
       </c>
       <c r="E239" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918197VX</t>
+          <t>KIT4M06491820X58</t>
         </is>
       </c>
       <c r="F239" s="4" t="inlineStr">
         <is>
-          <t>816397</t>
+          <t>816385</t>
         </is>
       </c>
       <c r="G239" s="5" t="inlineStr">
@@ -13202,7 +13202,7 @@
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491818QD2</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491826SQM</t>
         </is>
       </c>
       <c r="C240" s="3" t="n">
@@ -13213,12 +13213,12 @@
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491818QD2</t>
+          <t>KIT4M06491826SQM</t>
         </is>
       </c>
       <c r="F240" s="4" t="inlineStr">
         <is>
-          <t>816378</t>
+          <t>816380</t>
         </is>
       </c>
       <c r="G240" s="5" t="inlineStr">
@@ -13255,7 +13255,7 @@
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491820X58</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491825PF9</t>
         </is>
       </c>
       <c r="C241" s="3" t="n">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491820X58</t>
+          <t>KIT4M06491825PF9</t>
         </is>
       </c>
       <c r="F241" s="4" t="inlineStr">
         <is>
-          <t>816385</t>
+          <t>816367</t>
         </is>
       </c>
       <c r="G241" s="5" t="inlineStr">
@@ -13308,7 +13308,7 @@
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M0649183125S</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437502 - KIT4M058725695CN</t>
         </is>
       </c>
       <c r="C242" s="3" t="n">
@@ -13319,12 +13319,12 @@
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0649183125S</t>
+          <t>KIT4M058725695CN</t>
         </is>
       </c>
       <c r="F242" s="4" t="inlineStr">
         <is>
-          <t>816371</t>
+          <t>816101</t>
         </is>
       </c>
       <c r="G242" s="5" t="inlineStr">
@@ -13414,7 +13414,7 @@
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437362 - KIT4M05872574NKX</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437752 - KIT4M05872577TWT</t>
         </is>
       </c>
       <c r="C244" s="3" t="n">
@@ -13425,12 +13425,12 @@
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872574NKX</t>
+          <t>KIT4M05872577TWT</t>
         </is>
       </c>
       <c r="F244" s="4" t="inlineStr">
         <is>
-          <t>816113</t>
+          <t>816212</t>
         </is>
       </c>
       <c r="G244" s="5" t="inlineStr">
@@ -13520,7 +13520,7 @@
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437482-KIT4M05872578G7Q</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437802 - KIT4M05872589TM9</t>
         </is>
       </c>
       <c r="C246" s="3" t="n">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872578G7Q</t>
+          <t>KIT4M05872589TM9</t>
         </is>
       </c>
       <c r="F246" s="4" t="inlineStr">
         <is>
-          <t>816102</t>
+          <t>816195</t>
         </is>
       </c>
       <c r="G246" s="5" t="inlineStr">
@@ -13573,7 +13573,7 @@
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064917914G5</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064917925MB</t>
         </is>
       </c>
       <c r="C247" s="3" t="n">
@@ -13584,12 +13584,12 @@
       </c>
       <c r="E247" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064917914G5</t>
+          <t>KIT4M064917925MB</t>
         </is>
       </c>
       <c r="F247" s="4" t="inlineStr">
         <is>
-          <t>816392</t>
+          <t>816381</t>
         </is>
       </c>
       <c r="G247" s="5" t="inlineStr">
@@ -13626,7 +13626,7 @@
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064917925MB</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064917914G5</t>
         </is>
       </c>
       <c r="C248" s="3" t="n">
@@ -13637,12 +13637,12 @@
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064917925MB</t>
+          <t>KIT4M064917914G5</t>
         </is>
       </c>
       <c r="F248" s="4" t="inlineStr">
         <is>
-          <t>816381</t>
+          <t>816392</t>
         </is>
       </c>
       <c r="G248" s="5" t="inlineStr">
@@ -13732,7 +13732,7 @@
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437802 - KIT4M05872589TM9</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491817T79</t>
         </is>
       </c>
       <c r="C250" s="3" t="n">
@@ -13743,12 +13743,12 @@
       </c>
       <c r="E250" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872589TM9</t>
+          <t>KIT4M06491817T79</t>
         </is>
       </c>
       <c r="F250" s="4" t="inlineStr">
         <is>
-          <t>816195</t>
+          <t>816415</t>
         </is>
       </c>
       <c r="G250" s="5" t="inlineStr">
@@ -13785,7 +13785,7 @@
       </c>
       <c r="B251" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437352-KIT4M05872545Q8H</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491798S8Q</t>
         </is>
       </c>
       <c r="C251" s="3" t="n">
@@ -13796,12 +13796,12 @@
       </c>
       <c r="E251" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872545Q8H</t>
+          <t>KIT4M06491798S8Q</t>
         </is>
       </c>
       <c r="F251" s="4" t="inlineStr">
         <is>
-          <t>816112</t>
+          <t>816395</t>
         </is>
       </c>
       <c r="G251" s="5" t="inlineStr">
@@ -13838,7 +13838,7 @@
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491825PF9</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491799CRP</t>
         </is>
       </c>
       <c r="C252" s="3" t="n">
@@ -13849,12 +13849,12 @@
       </c>
       <c r="E252" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491825PF9</t>
+          <t>KIT4M06491799CRP</t>
         </is>
       </c>
       <c r="F252" s="4" t="inlineStr">
         <is>
-          <t>816367</t>
+          <t>816394</t>
         </is>
       </c>
       <c r="G252" s="5" t="inlineStr">
@@ -13891,7 +13891,7 @@
       </c>
       <c r="B253" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491829CD2</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918154FM</t>
         </is>
       </c>
       <c r="C253" s="3" t="n">
@@ -13902,12 +13902,12 @@
       </c>
       <c r="E253" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491829CD2</t>
+          <t>KIT4M064918154FM</t>
         </is>
       </c>
       <c r="F253" s="4" t="inlineStr">
         <is>
-          <t>816393</t>
+          <t>816368</t>
         </is>
       </c>
       <c r="G253" s="5" t="inlineStr">
@@ -13944,7 +13944,7 @@
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491826SQM</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491829CD2</t>
         </is>
       </c>
       <c r="C254" s="3" t="n">
@@ -13955,12 +13955,12 @@
       </c>
       <c r="E254" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491826SQM</t>
+          <t>KIT4M06491829CD2</t>
         </is>
       </c>
       <c r="F254" s="4" t="inlineStr">
         <is>
-          <t>816380</t>
+          <t>816393</t>
         </is>
       </c>
       <c r="G254" s="5" t="inlineStr">
@@ -14050,7 +14050,7 @@
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437342 - KIT4M05872557NFB</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M0649183125S</t>
         </is>
       </c>
       <c r="C256" s="3" t="n">
@@ -14061,12 +14061,12 @@
       </c>
       <c r="E256" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872557NFB</t>
+          <t>KIT4M0649183125S</t>
         </is>
       </c>
       <c r="F256" s="4" t="inlineStr">
         <is>
-          <t>816095</t>
+          <t>816371</t>
         </is>
       </c>
       <c r="G256" s="5" t="inlineStr">
@@ -14103,7 +14103,7 @@
       </c>
       <c r="B257" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437822-KIT4M0587253378R</t>
+          <t>SMRT-05900510-Los Angeles CA-021437882-KIT4M05872527QK6</t>
         </is>
       </c>
       <c r="C257" s="3" t="n">
@@ -14114,12 +14114,12 @@
       </c>
       <c r="E257" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0587253378R</t>
+          <t>KIT4M05872527QK6</t>
         </is>
       </c>
       <c r="F257" s="4" t="inlineStr">
         <is>
-          <t>816210</t>
+          <t>816214</t>
         </is>
       </c>
       <c r="G257" s="5" t="inlineStr">
@@ -14156,7 +14156,7 @@
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437882-KIT4M05872527QK6</t>
+          <t>SMRT-05900510-Los Angeles CA-021437352-KIT4M05872545Q8H</t>
         </is>
       </c>
       <c r="C258" s="3" t="n">
@@ -14167,12 +14167,12 @@
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872527QK6</t>
+          <t>KIT4M05872545Q8H</t>
         </is>
       </c>
       <c r="F258" s="4" t="inlineStr">
         <is>
-          <t>816214</t>
+          <t>816112</t>
         </is>
       </c>
       <c r="G258" s="5" t="inlineStr">
@@ -14209,7 +14209,7 @@
       </c>
       <c r="B259" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437462 - KIT4M05872575BC8</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437362 - KIT4M05872574NKX</t>
         </is>
       </c>
       <c r="C259" s="3" t="n">
@@ -14220,12 +14220,12 @@
       </c>
       <c r="E259" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872575BC8</t>
+          <t>KIT4M05872574NKX</t>
         </is>
       </c>
       <c r="F259" s="4" t="inlineStr">
         <is>
-          <t>816103</t>
+          <t>816113</t>
         </is>
       </c>
       <c r="G259" s="5" t="inlineStr">
@@ -14262,7 +14262,7 @@
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437752 - KIT4M05872577TWT</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437462 - KIT4M05872575BC8</t>
         </is>
       </c>
       <c r="C260" s="3" t="n">
@@ -14273,12 +14273,12 @@
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872577TWT</t>
+          <t>KIT4M05872575BC8</t>
         </is>
       </c>
       <c r="F260" s="4" t="inlineStr">
         <is>
-          <t>816212</t>
+          <t>816103</t>
         </is>
       </c>
       <c r="G260" s="5" t="inlineStr">
@@ -14315,7 +14315,7 @@
       </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437502 - KIT4M058725695CN</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437952 - KIT4M05872523VVB</t>
         </is>
       </c>
       <c r="C261" s="3" t="n">
@@ -14326,12 +14326,12 @@
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725695CN</t>
+          <t>KIT4M05872523VVB</t>
         </is>
       </c>
       <c r="F261" s="4" t="inlineStr">
         <is>
-          <t>816101</t>
+          <t>816215</t>
         </is>
       </c>
       <c r="G261" s="5" t="inlineStr">
@@ -14368,7 +14368,7 @@
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918015Z2</t>
+          <t>SMRT-05900510-Los Angeles CA-021437482-KIT4M05872578G7Q</t>
         </is>
       </c>
       <c r="C262" s="3" t="n">
@@ -14379,12 +14379,12 @@
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918015Z2</t>
+          <t>KIT4M05872578G7Q</t>
         </is>
       </c>
       <c r="F262" s="4" t="inlineStr">
         <is>
-          <t>816376</t>
+          <t>816102</t>
         </is>
       </c>
       <c r="G262" s="5" t="inlineStr">
@@ -14410,7 +14410,7 @@
       </c>
       <c r="L262" s="5" t="n"/>
       <c r="M262" s="7" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="263">
@@ -14421,7 +14421,7 @@
       </c>
       <c r="B263" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491795MWG</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955542 - KIT4M05563551N6Q</t>
         </is>
       </c>
       <c r="C263" s="3" t="n">
@@ -14432,12 +14432,12 @@
       </c>
       <c r="E263" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491795MWG</t>
+          <t>KIT4M05563551N6Q</t>
         </is>
       </c>
       <c r="F263" s="4" t="inlineStr">
         <is>
-          <t>816383</t>
+          <t>814450</t>
         </is>
       </c>
       <c r="G263" s="5" t="inlineStr">
@@ -14474,7 +14474,7 @@
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 021437682 - KIT4M05872544BXG</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438082 - KIT4M05799668SS7</t>
         </is>
       </c>
       <c r="C264" s="3" t="n">
@@ -14485,12 +14485,12 @@
       </c>
       <c r="E264" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872544BXG</t>
+          <t>KIT4M05799668SS7</t>
         </is>
       </c>
       <c r="F264" s="4" t="inlineStr">
         <is>
-          <t>816176</t>
+          <t>816279</t>
         </is>
       </c>
       <c r="G264" s="5" t="inlineStr">
@@ -14527,7 +14527,7 @@
       </c>
       <c r="B265" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955542 - KIT4M05563551N6Q</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438192 - KIT4M05872511F6P</t>
         </is>
       </c>
       <c r="C265" s="3" t="n">
@@ -14538,12 +14538,12 @@
       </c>
       <c r="E265" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563551N6Q</t>
+          <t>KIT4M05872511F6P</t>
         </is>
       </c>
       <c r="F265" s="4" t="inlineStr">
         <is>
-          <t>814450</t>
+          <t>816090</t>
         </is>
       </c>
       <c r="G265" s="5" t="inlineStr">
@@ -14580,7 +14580,7 @@
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438082 - KIT4M05799668SS7</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918015Z2</t>
         </is>
       </c>
       <c r="C266" s="3" t="n">
@@ -14591,12 +14591,12 @@
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799668SS7</t>
+          <t>KIT4M064918015Z2</t>
         </is>
       </c>
       <c r="F266" s="4" t="inlineStr">
         <is>
-          <t>816279</t>
+          <t>816376</t>
         </is>
       </c>
       <c r="G266" s="5" t="inlineStr">
@@ -14633,7 +14633,7 @@
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438192 - KIT4M05872511F6P</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918346DB</t>
         </is>
       </c>
       <c r="C267" s="3" t="n">
@@ -14644,12 +14644,12 @@
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872511F6P</t>
+          <t>KIT4M064918346DB</t>
         </is>
       </c>
       <c r="F267" s="4" t="inlineStr">
         <is>
-          <t>816090</t>
+          <t>816369</t>
         </is>
       </c>
       <c r="G267" s="5" t="inlineStr">
@@ -14686,7 +14686,7 @@
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918346DB</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491833JGV</t>
         </is>
       </c>
       <c r="C268" s="3" t="n">
@@ -14697,12 +14697,12 @@
       </c>
       <c r="E268" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918346DB</t>
+          <t>KIT4M06491833JGV</t>
         </is>
       </c>
       <c r="F268" s="4" t="inlineStr">
         <is>
-          <t>816369</t>
+          <t>816384</t>
         </is>
       </c>
       <c r="G268" s="5" t="inlineStr">
@@ -14739,7 +14739,7 @@
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491833JGV</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491813KGS</t>
         </is>
       </c>
       <c r="C269" s="3" t="n">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E269" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491833JGV</t>
+          <t>KIT4M06491813KGS</t>
         </is>
       </c>
       <c r="F269" s="4" t="inlineStr">
         <is>
-          <t>816384</t>
+          <t>816377</t>
         </is>
       </c>
       <c r="G269" s="5" t="inlineStr">
@@ -14792,7 +14792,7 @@
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491813KGS</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491795MWG</t>
         </is>
       </c>
       <c r="C270" s="3" t="n">
@@ -14803,12 +14803,12 @@
       </c>
       <c r="E270" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491813KGS</t>
+          <t>KIT4M06491795MWG</t>
         </is>
       </c>
       <c r="F270" s="4" t="inlineStr">
         <is>
-          <t>816377</t>
+          <t>816383</t>
         </is>
       </c>
       <c r="G270" s="5" t="inlineStr">
@@ -14845,7 +14845,7 @@
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437572 - KIT4M05872579JPF</t>
+          <t>SS - 05900510 -  Los Angeles CA - 021437682 - KIT4M05872544BXG</t>
         </is>
       </c>
       <c r="C271" s="3" t="n">
@@ -14856,12 +14856,12 @@
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872579JPF</t>
+          <t>KIT4M05872544BXG</t>
         </is>
       </c>
       <c r="F271" s="4" t="inlineStr">
         <is>
-          <t>816111</t>
+          <t>816176</t>
         </is>
       </c>
       <c r="G271" s="5" t="inlineStr">
@@ -15004,7 +15004,7 @@
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491808P4F</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437572 - KIT4M05872579JPF</t>
         </is>
       </c>
       <c r="C274" s="3" t="n">
@@ -15015,12 +15015,12 @@
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491808P4F</t>
+          <t>KIT4M05872579JPF</t>
         </is>
       </c>
       <c r="F274" s="4" t="inlineStr">
         <is>
-          <t>816399</t>
+          <t>816111</t>
         </is>
       </c>
       <c r="G274" s="5" t="inlineStr">
@@ -15046,7 +15046,7 @@
       </c>
       <c r="L274" s="5" t="n"/>
       <c r="M274" s="7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="275">
@@ -15057,7 +15057,7 @@
       </c>
       <c r="B275" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437272 - KIT4P0008459589D</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491797NCX</t>
         </is>
       </c>
       <c r="C275" s="3" t="n">
@@ -15068,17 +15068,17 @@
       </c>
       <c r="E275" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0008459589D</t>
+          <t>KIT4M06491797NCX</t>
         </is>
       </c>
       <c r="F275" s="4" t="inlineStr">
         <is>
-          <t>816222</t>
+          <t>816408</t>
         </is>
       </c>
       <c r="G275" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H275" s="5" t="inlineStr">
@@ -15110,7 +15110,7 @@
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA  - 020649572 - KIT4M05413816N8K</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491808P4F</t>
         </is>
       </c>
       <c r="C276" s="3" t="n">
@@ -15121,12 +15121,12 @@
       </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413816N8K</t>
+          <t>KIT4M06491808P4F</t>
         </is>
       </c>
       <c r="F276" s="4" t="inlineStr">
         <is>
-          <t>812832</t>
+          <t>816399</t>
         </is>
       </c>
       <c r="G276" s="5" t="inlineStr">
@@ -15163,7 +15163,7 @@
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491797NCX</t>
+          <t>SMA - 05900510 -  Los Angeles CA - 020649602 - KIT4M05413773R6G</t>
         </is>
       </c>
       <c r="C277" s="3" t="n">
@@ -15174,12 +15174,12 @@
       </c>
       <c r="E277" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491797NCX</t>
+          <t>KIT4M05413773R6G</t>
         </is>
       </c>
       <c r="F277" s="4" t="inlineStr">
         <is>
-          <t>816408</t>
+          <t>812807</t>
         </is>
       </c>
       <c r="G277" s="5" t="inlineStr">
@@ -15216,7 +15216,7 @@
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 -  Los Angeles CA - 020649602 - KIT4M05413773R6G</t>
+          <t>SS - 05900510 - Los Angeles, CA  - 020649572 - KIT4M05413816N8K</t>
         </is>
       </c>
       <c r="C278" s="3" t="n">
@@ -15227,12 +15227,12 @@
       </c>
       <c r="E278" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413773R6G</t>
+          <t>KIT4M05413816N8K</t>
         </is>
       </c>
       <c r="F278" s="4" t="inlineStr">
         <is>
-          <t>812807</t>
+          <t>812832</t>
         </is>
       </c>
       <c r="G278" s="5" t="inlineStr">
@@ -15375,7 +15375,7 @@
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491822SF6</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438162 - KIT4M05799712SBX</t>
         </is>
       </c>
       <c r="C281" s="3" t="n">
@@ -15386,12 +15386,12 @@
       </c>
       <c r="E281" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491822SF6</t>
+          <t>KIT4M05799712SBX</t>
         </is>
       </c>
       <c r="F281" s="4" t="inlineStr">
         <is>
-          <t>816412</t>
+          <t>816276</t>
         </is>
       </c>
       <c r="G281" s="5" t="inlineStr">
@@ -15428,7 +15428,7 @@
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438162 - KIT4M05799712SBX</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491822SF6</t>
         </is>
       </c>
       <c r="C282" s="3" t="n">
@@ -15439,12 +15439,12 @@
       </c>
       <c r="E282" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799712SBX</t>
+          <t>KIT4M06491822SF6</t>
         </is>
       </c>
       <c r="F282" s="4" t="inlineStr">
         <is>
-          <t>816276</t>
+          <t>816412</t>
         </is>
       </c>
       <c r="G282" s="5" t="inlineStr">
@@ -15534,7 +15534,7 @@
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649982 - KIT4M05413823B5P</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438292 - KIt4m058725108K2</t>
         </is>
       </c>
       <c r="C284" s="3" t="n">
@@ -15545,12 +15545,12 @@
       </c>
       <c r="E284" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413823B5P</t>
+          <t>KIT4M058725108K2</t>
         </is>
       </c>
       <c r="F284" s="4" t="inlineStr">
         <is>
-          <t>812837</t>
+          <t>816287</t>
         </is>
       </c>
       <c r="G284" s="5" t="inlineStr">
@@ -15640,7 +15640,7 @@
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438292 - KIt4m058725108K2</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491803672</t>
         </is>
       </c>
       <c r="C286" s="3" t="n">
@@ -15651,12 +15651,12 @@
       </c>
       <c r="E286" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725108K2</t>
+          <t>KIT4M06491803672</t>
         </is>
       </c>
       <c r="F286" s="4" t="inlineStr">
         <is>
-          <t>816287</t>
+          <t>816391</t>
         </is>
       </c>
       <c r="G286" s="5" t="inlineStr">
@@ -15693,7 +15693,7 @@
       </c>
       <c r="B287" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491805F7Z</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491811JB5</t>
         </is>
       </c>
       <c r="C287" s="3" t="n">
@@ -15704,12 +15704,12 @@
       </c>
       <c r="E287" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491805F7Z</t>
+          <t>KIT4M06491811JB5</t>
         </is>
       </c>
       <c r="F287" s="4" t="inlineStr">
         <is>
-          <t>816382</t>
+          <t>816411</t>
         </is>
       </c>
       <c r="G287" s="5" t="inlineStr">
@@ -15746,7 +15746,7 @@
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491803672</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491805F7Z</t>
         </is>
       </c>
       <c r="C288" s="3" t="n">
@@ -15757,12 +15757,12 @@
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491803672</t>
+          <t>KIT4M06491805F7Z</t>
         </is>
       </c>
       <c r="F288" s="4" t="inlineStr">
         <is>
-          <t>816391</t>
+          <t>816382</t>
         </is>
       </c>
       <c r="G288" s="5" t="inlineStr">
@@ -15799,7 +15799,7 @@
       </c>
       <c r="B289" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491809ZR6</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491802BZV</t>
         </is>
       </c>
       <c r="C289" s="3" t="n">
@@ -15810,12 +15810,12 @@
       </c>
       <c r="E289" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491809ZR6</t>
+          <t>KIT4M06491802BZV</t>
         </is>
       </c>
       <c r="F289" s="4" t="inlineStr">
         <is>
-          <t>816402</t>
+          <t>816390</t>
         </is>
       </c>
       <c r="G289" s="5" t="inlineStr">
@@ -15852,7 +15852,7 @@
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491802BZV</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491824JCK</t>
         </is>
       </c>
       <c r="C290" s="3" t="n">
@@ -15863,12 +15863,12 @@
       </c>
       <c r="E290" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491802BZV</t>
+          <t>KIT4M06491824JCK</t>
         </is>
       </c>
       <c r="F290" s="4" t="inlineStr">
         <is>
-          <t>816390</t>
+          <t>816413</t>
         </is>
       </c>
       <c r="G290" s="5" t="inlineStr">
@@ -15905,7 +15905,7 @@
       </c>
       <c r="B291" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437432 - KIT4M0587256692N</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437322 - KIT4M05872567V72</t>
         </is>
       </c>
       <c r="C291" s="3" t="n">
@@ -15916,12 +15916,12 @@
       </c>
       <c r="E291" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0587256692N</t>
+          <t>KIT4M05872567V72</t>
         </is>
       </c>
       <c r="F291" s="4" t="inlineStr">
         <is>
-          <t>816072</t>
+          <t>816099</t>
         </is>
       </c>
       <c r="G291" s="5" t="inlineStr">
@@ -15958,7 +15958,7 @@
       </c>
       <c r="B292" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437842-KIT4M05872547MK2</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437742 - KIT4M05872539ZMR</t>
         </is>
       </c>
       <c r="C292" s="3" t="n">
@@ -15969,12 +15969,12 @@
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872547MK2</t>
+          <t>KIT4M05872539ZMR</t>
         </is>
       </c>
       <c r="F292" s="4" t="inlineStr">
         <is>
-          <t>816209</t>
+          <t>816108</t>
         </is>
       </c>
       <c r="G292" s="5" t="inlineStr">
@@ -16011,7 +16011,7 @@
       </c>
       <c r="B293" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 021437602 - KIT4M05872524CFG</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437912 - KIT4M05872525NP5</t>
         </is>
       </c>
       <c r="C293" s="3" t="n">
@@ -16022,12 +16022,12 @@
       </c>
       <c r="E293" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872524CFG</t>
+          <t>KIT4M05872525NP5</t>
         </is>
       </c>
       <c r="F293" s="4" t="inlineStr">
         <is>
-          <t>816205</t>
+          <t>816213</t>
         </is>
       </c>
       <c r="G293" s="5" t="inlineStr">
@@ -16117,7 +16117,7 @@
       </c>
       <c r="B295" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437912 - KIT4M05872525NP5</t>
+          <t>SS - 05900510 -  Los Angeles CA - 021437602 - KIT4M05872524CFG</t>
         </is>
       </c>
       <c r="C295" s="3" t="n">
@@ -16128,12 +16128,12 @@
       </c>
       <c r="E295" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872525NP5</t>
+          <t>KIT4M05872524CFG</t>
         </is>
       </c>
       <c r="F295" s="4" t="inlineStr">
         <is>
-          <t>816213</t>
+          <t>816205</t>
         </is>
       </c>
       <c r="G295" s="5" t="inlineStr">
@@ -16170,7 +16170,7 @@
       </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437742 - KIT4M05872539ZMR</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437542 - KIT4M05872553WFR</t>
         </is>
       </c>
       <c r="C296" s="3" t="n">
@@ -16181,12 +16181,12 @@
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872539ZMR</t>
+          <t>KIT4M05872553WFR</t>
         </is>
       </c>
       <c r="F296" s="4" t="inlineStr">
         <is>
-          <t>816108</t>
+          <t>816116</t>
         </is>
       </c>
       <c r="G296" s="5" t="inlineStr">
@@ -16276,7 +16276,7 @@
       </c>
       <c r="B298" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437542 - KIT4M05872553WFR</t>
+          <t>SMRT-05900510-Los Angeles CA-021437842-KIT4M05872547MK2</t>
         </is>
       </c>
       <c r="C298" s="3" t="n">
@@ -16287,12 +16287,12 @@
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872553WFR</t>
+          <t>KIT4M05872547MK2</t>
         </is>
       </c>
       <c r="F298" s="4" t="inlineStr">
         <is>
-          <t>816116</t>
+          <t>816209</t>
         </is>
       </c>
       <c r="G298" s="5" t="inlineStr">
@@ -16329,7 +16329,7 @@
       </c>
       <c r="B299" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491794MTJ</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437472 - KIT4M05872565VJK</t>
         </is>
       </c>
       <c r="C299" s="3" t="n">
@@ -16340,12 +16340,12 @@
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491794MTJ</t>
+          <t>KIT4M05872565VJK</t>
         </is>
       </c>
       <c r="F299" s="4" t="inlineStr">
         <is>
-          <t>816375</t>
+          <t>816109</t>
         </is>
       </c>
       <c r="G299" s="5" t="inlineStr">
@@ -16435,7 +16435,7 @@
       </c>
       <c r="B301" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437472 - KIT4M05872565VJK</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437432 - KIT4M0587256692N</t>
         </is>
       </c>
       <c r="C301" s="3" t="n">
@@ -16446,12 +16446,12 @@
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872565VJK</t>
+          <t>KIT4M0587256692N</t>
         </is>
       </c>
       <c r="F301" s="4" t="inlineStr">
         <is>
-          <t>816109</t>
+          <t>816072</t>
         </is>
       </c>
       <c r="G301" s="5" t="inlineStr">
@@ -16488,7 +16488,7 @@
       </c>
       <c r="B302" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437322 - KIT4M05872567V72</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437522 - KIT4M05872576R4B</t>
         </is>
       </c>
       <c r="C302" s="3" t="n">
@@ -16499,12 +16499,12 @@
       </c>
       <c r="E302" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872567V72</t>
+          <t>KIT4M05872576R4B</t>
         </is>
       </c>
       <c r="F302" s="4" t="inlineStr">
         <is>
-          <t>816099</t>
+          <t>816110</t>
         </is>
       </c>
       <c r="G302" s="5" t="inlineStr">
@@ -16541,7 +16541,7 @@
       </c>
       <c r="B303" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437442 - KIT4M05872584M6H</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437552 - KIT4M05872586VCH</t>
         </is>
       </c>
       <c r="C303" s="3" t="n">
@@ -16552,12 +16552,12 @@
       </c>
       <c r="E303" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872584M6H</t>
+          <t>KIT4M05872586VCH</t>
         </is>
       </c>
       <c r="F303" s="4" t="inlineStr">
         <is>
-          <t>816096</t>
+          <t>816068</t>
         </is>
       </c>
       <c r="G303" s="5" t="inlineStr">
@@ -16594,7 +16594,7 @@
       </c>
       <c r="B304" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437522 - KIT4M05872576R4B</t>
+          <t>SS - 05900510 - Los Angeles CA  - 021437562 - KIT4M05872583P58</t>
         </is>
       </c>
       <c r="C304" s="3" t="n">
@@ -16605,12 +16605,12 @@
       </c>
       <c r="E304" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872576R4B</t>
+          <t>KIT4M05872583P58</t>
         </is>
       </c>
       <c r="F304" s="4" t="inlineStr">
         <is>
-          <t>816110</t>
+          <t>816069</t>
         </is>
       </c>
       <c r="G304" s="5" t="inlineStr">
@@ -16647,7 +16647,7 @@
       </c>
       <c r="B305" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437552 - KIT4M05872586VCH</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649982 - KIT4M05413823B5P</t>
         </is>
       </c>
       <c r="C305" s="3" t="n">
@@ -16658,12 +16658,12 @@
       </c>
       <c r="E305" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872586VCH</t>
+          <t>KIT4M05413823B5P</t>
         </is>
       </c>
       <c r="F305" s="4" t="inlineStr">
         <is>
-          <t>816068</t>
+          <t>812837</t>
         </is>
       </c>
       <c r="G305" s="5" t="inlineStr">
@@ -16753,7 +16753,7 @@
       </c>
       <c r="B307" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649702 - KIT4M04604741P2X</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918322GZ</t>
         </is>
       </c>
       <c r="C307" s="3" t="n">
@@ -16764,12 +16764,12 @@
       </c>
       <c r="E307" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604741P2X</t>
+          <t>KIT4M064918322GZ</t>
         </is>
       </c>
       <c r="F307" s="4" t="inlineStr">
         <is>
-          <t>809871</t>
+          <t>816414</t>
         </is>
       </c>
       <c r="G307" s="5" t="inlineStr">
@@ -16859,7 +16859,7 @@
       </c>
       <c r="B309" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491837DPX</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491807TRH</t>
         </is>
       </c>
       <c r="C309" s="3" t="n">
@@ -16870,12 +16870,12 @@
       </c>
       <c r="E309" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491837DPX</t>
+          <t>KIT4M06491807TRH</t>
         </is>
       </c>
       <c r="F309" s="4" t="inlineStr">
         <is>
-          <t>816389</t>
+          <t>816386</t>
         </is>
       </c>
       <c r="G309" s="5" t="inlineStr">
@@ -16912,7 +16912,7 @@
       </c>
       <c r="B310" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918322GZ</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649702 - KIT4M04604741P2X</t>
         </is>
       </c>
       <c r="C310" s="3" t="n">
@@ -16923,12 +16923,12 @@
       </c>
       <c r="E310" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918322GZ</t>
+          <t>KIT4M04604741P2X</t>
         </is>
       </c>
       <c r="F310" s="4" t="inlineStr">
         <is>
-          <t>816414</t>
+          <t>809871</t>
         </is>
       </c>
       <c r="G310" s="5" t="inlineStr">
@@ -16965,7 +16965,7 @@
       </c>
       <c r="B311" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491824JCK</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491837DPX</t>
         </is>
       </c>
       <c r="C311" s="3" t="n">
@@ -16976,12 +16976,12 @@
       </c>
       <c r="E311" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491824JCK</t>
+          <t>KIT4M06491837DPX</t>
         </is>
       </c>
       <c r="F311" s="4" t="inlineStr">
         <is>
-          <t>816413</t>
+          <t>816389</t>
         </is>
       </c>
       <c r="G311" s="5" t="inlineStr">
@@ -17124,7 +17124,7 @@
       </c>
       <c r="B314" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491807TRH</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491809ZR6</t>
         </is>
       </c>
       <c r="C314" s="3" t="n">
@@ -17135,12 +17135,12 @@
       </c>
       <c r="E314" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491807TRH</t>
+          <t>KIT4M06491809ZR6</t>
         </is>
       </c>
       <c r="F314" s="4" t="inlineStr">
         <is>
-          <t>816386</t>
+          <t>816402</t>
         </is>
       </c>
       <c r="G314" s="5" t="inlineStr">
@@ -17177,7 +17177,7 @@
       </c>
       <c r="B315" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491811JB5</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437442 - KIT4M05872584M6H</t>
         </is>
       </c>
       <c r="C315" s="3" t="n">
@@ -17188,12 +17188,12 @@
       </c>
       <c r="E315" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491811JB5</t>
+          <t>KIT4M05872584M6H</t>
         </is>
       </c>
       <c r="F315" s="4" t="inlineStr">
         <is>
-          <t>816411</t>
+          <t>816096</t>
         </is>
       </c>
       <c r="G315" s="5" t="inlineStr">
@@ -17230,7 +17230,7 @@
       </c>
       <c r="B316" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 021437562 - KIT4M05872583P58</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491794MTJ</t>
         </is>
       </c>
       <c r="C316" s="3" t="n">
@@ -17241,12 +17241,12 @@
       </c>
       <c r="E316" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872583P58</t>
+          <t>KIT4M06491794MTJ</t>
         </is>
       </c>
       <c r="F316" s="4" t="inlineStr">
         <is>
-          <t>816069</t>
+          <t>816375</t>
         </is>
       </c>
       <c r="G316" s="5" t="inlineStr">
@@ -17283,7 +17283,7 @@
       </c>
       <c r="B317" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437492 - KIT4M0587256196K</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437652 - KIT4M05872551G9S</t>
         </is>
       </c>
       <c r="C317" s="3" t="n">
@@ -17294,12 +17294,12 @@
       </c>
       <c r="E317" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0587256196K</t>
+          <t>KIT4M05872551G9S</t>
         </is>
       </c>
       <c r="F317" s="4" t="inlineStr">
         <is>
-          <t>816098</t>
+          <t>816180</t>
         </is>
       </c>
       <c r="G317" s="5" t="inlineStr">
@@ -17389,7 +17389,7 @@
       </c>
       <c r="B319" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437652 - KIT4M05872551G9S</t>
+          <t>SS - 05900510 - Los Angeles, CA - 021437772 - KIT4M05872563FWB</t>
         </is>
       </c>
       <c r="C319" s="3" t="n">
@@ -17400,12 +17400,12 @@
       </c>
       <c r="E319" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872551G9S</t>
+          <t>KIT4M05872563FWB</t>
         </is>
       </c>
       <c r="F319" s="4" t="inlineStr">
         <is>
-          <t>816180</t>
+          <t>816208</t>
         </is>
       </c>
       <c r="G319" s="5" t="inlineStr">
@@ -17495,7 +17495,7 @@
       </c>
       <c r="B321" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437452 - KIT4M05872580C6X</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437492 - KIT4M0587256196K</t>
         </is>
       </c>
       <c r="C321" s="3" t="n">
@@ -17506,12 +17506,12 @@
       </c>
       <c r="E321" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872580C6X</t>
+          <t>KIT4M0587256196K</t>
         </is>
       </c>
       <c r="F321" s="4" t="inlineStr">
         <is>
-          <t>816097</t>
+          <t>816098</t>
         </is>
       </c>
       <c r="G321" s="5" t="inlineStr">
@@ -17548,7 +17548,7 @@
       </c>
       <c r="B322" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 021437772 - KIT4M05872563FWB</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438052 - KIT4M05872522W7W</t>
         </is>
       </c>
       <c r="C322" s="3" t="n">
@@ -17559,12 +17559,12 @@
       </c>
       <c r="E322" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872563FWB</t>
+          <t>KIT4M05872522W7W</t>
         </is>
       </c>
       <c r="F322" s="4" t="inlineStr">
         <is>
-          <t>816208</t>
+          <t>816217</t>
         </is>
       </c>
       <c r="G322" s="5" t="inlineStr">
@@ -17601,7 +17601,7 @@
       </c>
       <c r="B323" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649772 - KIT4M04475152RGR</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437262 - KIT4P0008460369B</t>
         </is>
       </c>
       <c r="C323" s="3" t="n">
@@ -17612,17 +17612,17 @@
       </c>
       <c r="E323" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475152RGR</t>
+          <t>KIT4P0008460369B</t>
         </is>
       </c>
       <c r="F323" s="4" t="inlineStr">
         <is>
-          <t>809861</t>
+          <t>816224</t>
         </is>
       </c>
       <c r="G323" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H323" s="5" t="inlineStr">
@@ -17707,7 +17707,7 @@
       </c>
       <c r="B325" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437892 - KIT4M06490321NJX</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437972 - KIT4M06490327GMP</t>
         </is>
       </c>
       <c r="C325" s="3" t="n">
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E325" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06490321NJX</t>
+          <t>KIT4M06490327GMP</t>
         </is>
       </c>
       <c r="F325" s="4" t="inlineStr">
         <is>
-          <t>816219</t>
+          <t>816199</t>
         </is>
       </c>
       <c r="G325" s="5" t="inlineStr">
@@ -17813,7 +17813,7 @@
       </c>
       <c r="B327" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437972 - KIT4M06490327GMP</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437892 - KIT4M06490321NJX</t>
         </is>
       </c>
       <c r="C327" s="3" t="n">
@@ -17824,12 +17824,12 @@
       </c>
       <c r="E327" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06490327GMP</t>
+          <t>KIT4M06490321NJX</t>
         </is>
       </c>
       <c r="F327" s="4" t="inlineStr">
         <is>
-          <t>816199</t>
+          <t>816219</t>
         </is>
       </c>
       <c r="G327" s="5" t="inlineStr">
@@ -17866,7 +17866,7 @@
       </c>
       <c r="B328" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438062 - KIT4M05799676NNK</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438142  - KIT4M05799685DG5</t>
         </is>
       </c>
       <c r="C328" s="3" t="n">
@@ -17877,12 +17877,12 @@
       </c>
       <c r="E328" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799676NNK</t>
+          <t>KIT4M05799685DG5</t>
         </is>
       </c>
       <c r="F328" s="4" t="inlineStr">
         <is>
-          <t>816283</t>
+          <t>816271</t>
         </is>
       </c>
       <c r="G328" s="5" t="inlineStr">
@@ -17972,7 +17972,7 @@
       </c>
       <c r="B330" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020955312 - KIT4M0556351956H</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438272 - KIT4M05872517VS2</t>
         </is>
       </c>
       <c r="C330" s="3" t="n">
@@ -17983,12 +17983,12 @@
       </c>
       <c r="E330" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0556351956H</t>
+          <t>KIT4M05872517VS2</t>
         </is>
       </c>
       <c r="F330" s="4" t="inlineStr">
         <is>
-          <t>814477</t>
+          <t>816288</t>
         </is>
       </c>
       <c r="G330" s="5" t="inlineStr">
@@ -18025,7 +18025,7 @@
       </c>
       <c r="B331" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437982 - KIT4M05799678R5P</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020955312 - KIT4M0556351956H</t>
         </is>
       </c>
       <c r="C331" s="3" t="n">
@@ -18036,12 +18036,12 @@
       </c>
       <c r="E331" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799678R5P</t>
+          <t>KIT4M0556351956H</t>
         </is>
       </c>
       <c r="F331" s="4" t="inlineStr">
         <is>
-          <t>816281</t>
+          <t>814477</t>
         </is>
       </c>
       <c r="G331" s="5" t="inlineStr">
@@ -18078,7 +18078,7 @@
       </c>
       <c r="B332" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438142  - KIT4M05799685DG5</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020650222 - KIT4M05413790XCD</t>
         </is>
       </c>
       <c r="C332" s="3" t="n">
@@ -18089,12 +18089,12 @@
       </c>
       <c r="E332" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799685DG5</t>
+          <t>KIT4M05413790XCD</t>
         </is>
       </c>
       <c r="F332" s="4" t="inlineStr">
         <is>
-          <t>816271</t>
+          <t>812822</t>
         </is>
       </c>
       <c r="G332" s="5" t="inlineStr">
@@ -18131,7 +18131,7 @@
       </c>
       <c r="B333" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA -021437942 - KIT4M05799709G5Q</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437702 - KIT4M05872515PJT</t>
         </is>
       </c>
       <c r="C333" s="3" t="n">
@@ -18142,12 +18142,12 @@
       </c>
       <c r="E333" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799709G5Q</t>
+          <t>KIT4M05872515PJT</t>
         </is>
       </c>
       <c r="F333" s="4" t="inlineStr">
         <is>
-          <t>816274</t>
+          <t>816218</t>
         </is>
       </c>
       <c r="G333" s="5" t="inlineStr">
@@ -18184,7 +18184,7 @@
       </c>
       <c r="B334" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438052 - KIT4M05872522W7W</t>
+          <t>SMS - 05900510 - Los Angeles CA -021437942 - KIT4M05799709G5Q</t>
         </is>
       </c>
       <c r="C334" s="3" t="n">
@@ -18195,12 +18195,12 @@
       </c>
       <c r="E334" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872522W7W</t>
+          <t>KIT4M05799709G5Q</t>
         </is>
       </c>
       <c r="F334" s="4" t="inlineStr">
         <is>
-          <t>816217</t>
+          <t>816274</t>
         </is>
       </c>
       <c r="G334" s="5" t="inlineStr">
@@ -18237,7 +18237,7 @@
       </c>
       <c r="B335" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437702 - KIT4M05872515PJT</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437982 - KIT4M05799678R5P</t>
         </is>
       </c>
       <c r="C335" s="3" t="n">
@@ -18248,12 +18248,12 @@
       </c>
       <c r="E335" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872515PJT</t>
+          <t>KIT4M05799678R5P</t>
         </is>
       </c>
       <c r="F335" s="4" t="inlineStr">
         <is>
-          <t>816218</t>
+          <t>816281</t>
         </is>
       </c>
       <c r="G335" s="5" t="inlineStr">
@@ -18290,7 +18290,7 @@
       </c>
       <c r="B336" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020650222 - KIT4M05413790XCD</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438062 - KIT4M05799676NNK</t>
         </is>
       </c>
       <c r="C336" s="3" t="n">
@@ -18301,12 +18301,12 @@
       </c>
       <c r="E336" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413790XCD</t>
+          <t>KIT4M05799676NNK</t>
         </is>
       </c>
       <c r="F336" s="4" t="inlineStr">
         <is>
-          <t>812822</t>
+          <t>816283</t>
         </is>
       </c>
       <c r="G336" s="5" t="inlineStr">
@@ -18343,7 +18343,7 @@
       </c>
       <c r="B337" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438272 - KIT4M05872517VS2</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437452 - KIT4M05872580C6X</t>
         </is>
       </c>
       <c r="C337" s="3" t="n">
@@ -18354,12 +18354,12 @@
       </c>
       <c r="E337" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872517VS2</t>
+          <t>KIT4M05872580C6X</t>
         </is>
       </c>
       <c r="F337" s="4" t="inlineStr">
         <is>
-          <t>816288</t>
+          <t>816097</t>
         </is>
       </c>
       <c r="G337" s="5" t="inlineStr">
@@ -18449,7 +18449,7 @@
       </c>
       <c r="B339" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649382 - KIT4M05368219KRH</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649772 - KIT4M04475152RGR</t>
         </is>
       </c>
       <c r="C339" s="3" t="n">
@@ -18460,12 +18460,12 @@
       </c>
       <c r="E339" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368219KRH</t>
+          <t>KIT4M04475152RGR</t>
         </is>
       </c>
       <c r="F339" s="4" t="inlineStr">
         <is>
-          <t>810646</t>
+          <t>809861</t>
         </is>
       </c>
       <c r="G339" s="5" t="inlineStr">
@@ -18502,7 +18502,7 @@
       </c>
       <c r="B340" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437262 - KIT4P0008460369B</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918068FF</t>
         </is>
       </c>
       <c r="C340" s="3" t="n">
@@ -18513,17 +18513,17 @@
       </c>
       <c r="E340" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0008460369B</t>
+          <t>KIT4M064918068FF</t>
         </is>
       </c>
       <c r="F340" s="4" t="inlineStr">
         <is>
-          <t>816224</t>
+          <t>816400</t>
         </is>
       </c>
       <c r="G340" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H340" s="5" t="inlineStr">
@@ -18555,7 +18555,7 @@
       </c>
       <c r="B341" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918068FF</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649382 - KIT4M05368219KRH</t>
         </is>
       </c>
       <c r="C341" s="3" t="n">
@@ -18566,12 +18566,12 @@
       </c>
       <c r="E341" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918068FF</t>
+          <t>KIT4M05368219KRH</t>
         </is>
       </c>
       <c r="F341" s="4" t="inlineStr">
         <is>
-          <t>816400</t>
+          <t>810646</t>
         </is>
       </c>
       <c r="G341" s="5" t="inlineStr">
@@ -18820,7 +18820,7 @@
       </c>
       <c r="B346" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649922 - KIT4M05413780XFH</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437922 - KIT4M05872496MW6</t>
         </is>
       </c>
       <c r="C346" s="3" t="n">
@@ -18831,12 +18831,12 @@
       </c>
       <c r="E346" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413780XFH</t>
+          <t>KIT4M05872496MW6</t>
         </is>
       </c>
       <c r="F346" s="4" t="inlineStr">
         <is>
-          <t>812833</t>
+          <t>816206</t>
         </is>
       </c>
       <c r="G346" s="5" t="inlineStr">
@@ -18873,7 +18873,7 @@
       </c>
       <c r="B347" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438202 - KIT4M05872506TTB</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649482 - KIT4M054137938P7</t>
         </is>
       </c>
       <c r="C347" s="3" t="n">
@@ -18884,12 +18884,12 @@
       </c>
       <c r="E347" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872506TTB</t>
+          <t>KIT4M054137938P7</t>
         </is>
       </c>
       <c r="F347" s="4" t="inlineStr">
         <is>
-          <t>816082</t>
+          <t>812848</t>
         </is>
       </c>
       <c r="G347" s="5" t="inlineStr">
@@ -18926,7 +18926,7 @@
       </c>
       <c r="B348" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649952 - KIT4M05413782GHW</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438202 - KIT4M05872506TTB</t>
         </is>
       </c>
       <c r="C348" s="3" t="n">
@@ -18937,12 +18937,12 @@
       </c>
       <c r="E348" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413782GHW</t>
+          <t>KIT4M05872506TTB</t>
         </is>
       </c>
       <c r="F348" s="4" t="inlineStr">
         <is>
-          <t>812835</t>
+          <t>816082</t>
         </is>
       </c>
       <c r="G348" s="5" t="inlineStr">
@@ -19032,7 +19032,7 @@
       </c>
       <c r="B350" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955562 - KIT4M05563505WPS</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955162 - KIT4M05563554WCW</t>
         </is>
       </c>
       <c r="C350" s="3" t="n">
@@ -19043,12 +19043,12 @@
       </c>
       <c r="E350" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563505WPS</t>
+          <t>KIT4M05563554WCW</t>
         </is>
       </c>
       <c r="F350" s="4" t="inlineStr">
         <is>
-          <t>814448</t>
+          <t>814444</t>
         </is>
       </c>
       <c r="G350" s="5" t="inlineStr">
@@ -19138,7 +19138,7 @@
       </c>
       <c r="B352" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955222 - KIT4M05563536BPJ</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955562 - KIT4M05563505WPS</t>
         </is>
       </c>
       <c r="C352" s="3" t="n">
@@ -19149,12 +19149,12 @@
       </c>
       <c r="E352" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563536BPJ</t>
+          <t>KIT4M05563505WPS</t>
         </is>
       </c>
       <c r="F352" s="4" t="inlineStr">
         <is>
-          <t>814466</t>
+          <t>814448</t>
         </is>
       </c>
       <c r="G352" s="5" t="inlineStr">
@@ -19191,7 +19191,7 @@
       </c>
       <c r="B353" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649612 - KIT4M05413827DC4</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955222 - KIT4M05563536BPJ</t>
         </is>
       </c>
       <c r="C353" s="3" t="n">
@@ -19202,12 +19202,12 @@
       </c>
       <c r="E353" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413827DC4</t>
+          <t>KIT4M05563536BPJ</t>
         </is>
       </c>
       <c r="F353" s="4" t="inlineStr">
         <is>
-          <t>812829</t>
+          <t>814466</t>
         </is>
       </c>
       <c r="G353" s="5" t="inlineStr">
@@ -19244,7 +19244,7 @@
       </c>
       <c r="B354" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020650092 - KIT4M05413830JN7</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649612 - KIT4M05413827DC4</t>
         </is>
       </c>
       <c r="C354" s="3" t="n">
@@ -19255,12 +19255,12 @@
       </c>
       <c r="E354" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413830JN7</t>
+          <t>KIT4M05413827DC4</t>
         </is>
       </c>
       <c r="F354" s="4" t="inlineStr">
         <is>
-          <t>810105</t>
+          <t>812829</t>
         </is>
       </c>
       <c r="G354" s="5" t="inlineStr">
@@ -19297,7 +19297,7 @@
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - CW6892232 - KIT4P000832637V6</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482701114 - KIT4M03476114VCM</t>
         </is>
       </c>
       <c r="C355" s="3" t="n">
@@ -19308,17 +19308,17 @@
       </c>
       <c r="E355" s="2" t="inlineStr">
         <is>
-          <t>KIT4P000832637V6</t>
+          <t>KIT4M03476114VCM</t>
         </is>
       </c>
       <c r="F355" s="4" t="inlineStr">
         <is>
-          <t>816334</t>
+          <t>809613</t>
         </is>
       </c>
       <c r="G355" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H355" s="5" t="inlineStr">
@@ -19350,7 +19350,7 @@
       </c>
       <c r="B356" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482701114 - KIT4M03476114VCM</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827011116 - KIT4M02578775B9Q</t>
         </is>
       </c>
       <c r="C356" s="3" t="n">
@@ -19361,12 +19361,12 @@
       </c>
       <c r="E356" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03476114VCM</t>
+          <t>KIT4M02578775B9Q</t>
         </is>
       </c>
       <c r="F356" s="4" t="inlineStr">
         <is>
-          <t>809613</t>
+          <t>809611</t>
         </is>
       </c>
       <c r="G356" s="5" t="inlineStr">
@@ -19403,7 +19403,7 @@
       </c>
       <c r="B357" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827011116 - KIT4M02578775B9Q</t>
+          <t>SMA - 05900510 - Los Angeles CA - CW6892232 - KIT4P000832637V6</t>
         </is>
       </c>
       <c r="C357" s="3" t="n">
@@ -19414,17 +19414,17 @@
       </c>
       <c r="E357" s="2" t="inlineStr">
         <is>
-          <t>KIT4M02578775B9Q</t>
+          <t>KIT4P000832637V6</t>
         </is>
       </c>
       <c r="F357" s="4" t="inlineStr">
         <is>
-          <t>809611</t>
+          <t>816334</t>
         </is>
       </c>
       <c r="G357" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H357" s="5" t="inlineStr">
@@ -19456,7 +19456,7 @@
       </c>
       <c r="B358" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438012 - KIT4M05799715GJ2</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649922 - KIT4M05413780XFH</t>
         </is>
       </c>
       <c r="C358" s="3" t="n">
@@ -19467,16 +19467,24 @@
       </c>
       <c r="E358" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799715GJ2</t>
-        </is>
-      </c>
-      <c r="F358" s="8" t="n"/>
+          <t>KIT4M05413780XFH</t>
+        </is>
+      </c>
+      <c r="F358" s="4" t="inlineStr">
+        <is>
+          <t>812833</t>
+        </is>
+      </c>
       <c r="G358" s="5" t="inlineStr">
         <is>
           <t>Mini</t>
         </is>
       </c>
-      <c r="H358" s="5" t="n"/>
+      <c r="H358" s="5" t="inlineStr">
+        <is>
+          <t>Master Serial List</t>
+        </is>
+      </c>
       <c r="I358" s="6" t="n">
         <v>46235</v>
       </c>
@@ -19501,7 +19509,7 @@
       </c>
       <c r="B359" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437922 - KIT4M05872496MW6</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438012 - KIT4M05799715GJ2</t>
         </is>
       </c>
       <c r="C359" s="3" t="n">
@@ -19512,24 +19520,16 @@
       </c>
       <c r="E359" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872496MW6</t>
-        </is>
-      </c>
-      <c r="F359" s="4" t="inlineStr">
-        <is>
-          <t>816206</t>
-        </is>
-      </c>
+          <t>KIT4M05799715GJ2</t>
+        </is>
+      </c>
+      <c r="F359" s="8" t="n"/>
       <c r="G359" s="5" t="inlineStr">
         <is>
           <t>Mini</t>
         </is>
       </c>
-      <c r="H359" s="5" t="inlineStr">
-        <is>
-          <t>Master Serial List</t>
-        </is>
-      </c>
+      <c r="H359" s="5" t="n"/>
       <c r="I359" s="6" t="n">
         <v>46235</v>
       </c>
@@ -19554,7 +19554,7 @@
       </c>
       <c r="B360" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649482 - KIT4M054137938P7</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649952 - KIT4M05413782GHW</t>
         </is>
       </c>
       <c r="C360" s="3" t="n">
@@ -19565,12 +19565,12 @@
       </c>
       <c r="E360" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137938P7</t>
+          <t>KIT4M05413782GHW</t>
         </is>
       </c>
       <c r="F360" s="4" t="inlineStr">
         <is>
-          <t>812848</t>
+          <t>812835</t>
         </is>
       </c>
       <c r="G360" s="5" t="inlineStr">
@@ -19607,7 +19607,7 @@
       </c>
       <c r="B361" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649502 - KIT4M05413801QJB</t>
+          <t>SMRT-05900510-Los Angeles CA-020650032-KIT4M05413802FVN</t>
         </is>
       </c>
       <c r="C361" s="3" t="n">
@@ -19618,12 +19618,12 @@
       </c>
       <c r="E361" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413801QJB</t>
+          <t>KIT4M05413802FVN</t>
         </is>
       </c>
       <c r="F361" s="4" t="inlineStr">
         <is>
-          <t>812824</t>
+          <t>812813</t>
         </is>
       </c>
       <c r="G361" s="5" t="inlineStr">
@@ -19660,7 +19660,7 @@
       </c>
       <c r="B362" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020650032-KIT4M05413802FVN</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649502 - KIT4M05413801QJB</t>
         </is>
       </c>
       <c r="C362" s="3" t="n">
@@ -19671,12 +19671,12 @@
       </c>
       <c r="E362" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413802FVN</t>
+          <t>KIT4M05413801QJB</t>
         </is>
       </c>
       <c r="F362" s="4" t="inlineStr">
         <is>
-          <t>812813</t>
+          <t>812824</t>
         </is>
       </c>
       <c r="G362" s="5" t="inlineStr">
@@ -19766,7 +19766,7 @@
       </c>
       <c r="B364" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955162 - KIT4M05563554WCW</t>
+          <t>STS - 05900510 - Los Angeles CA - 020650092 - KIT4M05413830JN7</t>
         </is>
       </c>
       <c r="C364" s="3" t="n">
@@ -19777,12 +19777,12 @@
       </c>
       <c r="E364" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563554WCW</t>
+          <t>KIT4M05413830JN7</t>
         </is>
       </c>
       <c r="F364" s="4" t="inlineStr">
         <is>
-          <t>814444</t>
+          <t>810105</t>
         </is>
       </c>
       <c r="G364" s="5" t="inlineStr">
@@ -19872,7 +19872,7 @@
       </c>
       <c r="B366" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020649662 - KIT4M05413772977</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491835TD6</t>
         </is>
       </c>
       <c r="C366" s="3" t="n">
@@ -19883,12 +19883,12 @@
       </c>
       <c r="E366" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413772977</t>
+          <t>KIT4M06491835TD6</t>
         </is>
       </c>
       <c r="F366" s="4" t="inlineStr">
         <is>
-          <t>812841</t>
+          <t>816401</t>
         </is>
       </c>
       <c r="G366" s="5" t="inlineStr">
@@ -19978,7 +19978,7 @@
       </c>
       <c r="B368" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491835TD6</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020649662 - KIT4M05413772977</t>
         </is>
       </c>
       <c r="C368" s="3" t="n">
@@ -19989,12 +19989,12 @@
       </c>
       <c r="E368" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491835TD6</t>
+          <t>KIT4M05413772977</t>
         </is>
       </c>
       <c r="F368" s="4" t="inlineStr">
         <is>
-          <t>816401</t>
+          <t>812841</t>
         </is>
       </c>
       <c r="G368" s="5" t="inlineStr">
@@ -20219,7 +20219,7 @@
     <row r="381">
       <c r="A381" s="15" t="inlineStr">
         <is>
-          <t>Generated 2026-08-28 21:09 by build_starlink_usage.py</t>
+          <t>Generated 2026-08-29 09:42 by build_starlink_usage.py</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_Current_by_Kit.xlsx
+++ b/Starlink_Usage_Current_by_Kit.xlsx
@@ -20219,7 +20219,7 @@
     <row r="381">
       <c r="A381" s="15" t="inlineStr">
         <is>
-          <t>Generated 2026-08-29 09:42 by build_starlink_usage.py</t>
+          <t>Generated 2026-08-29 09:44 by build_starlink_usage.py</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_Current_by_Kit.xlsx
+++ b/Starlink_Usage_Current_by_Kit.xlsx
@@ -630,7 +630,7 @@
       </c>
       <c r="L2" s="5" t="n"/>
       <c r="M2" s="7" t="n">
-        <v>2491.33</v>
+        <v>2498.63</v>
       </c>
     </row>
     <row r="3">
@@ -683,7 +683,7 @@
       </c>
       <c r="L3" s="5" t="n"/>
       <c r="M3" s="7" t="n">
-        <v>2268.85</v>
+        <v>2290.97</v>
       </c>
     </row>
     <row r="4">
@@ -736,7 +736,7 @@
       </c>
       <c r="L4" s="5" t="n"/>
       <c r="M4" s="7" t="n">
-        <v>1634.8</v>
+        <v>1637.22</v>
       </c>
     </row>
     <row r="5">
@@ -842,7 +842,7 @@
       </c>
       <c r="L6" s="5" t="n"/>
       <c r="M6" s="7" t="n">
-        <v>1105.12</v>
+        <v>1125.65</v>
       </c>
     </row>
     <row r="7">
@@ -895,7 +895,7 @@
       </c>
       <c r="L7" s="5" t="n"/>
       <c r="M7" s="7" t="n">
-        <v>980.35</v>
+        <v>996.03</v>
       </c>
     </row>
     <row r="8">
@@ -948,7 +948,7 @@
       </c>
       <c r="L8" s="5" t="n"/>
       <c r="M8" s="7" t="n">
-        <v>915.73</v>
+        <v>941.38</v>
       </c>
     </row>
     <row r="9">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="L13" s="5" t="n"/>
       <c r="M13" s="7" t="n">
-        <v>731.5</v>
+        <v>743.11</v>
       </c>
     </row>
     <row r="14">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L14" s="5" t="n"/>
       <c r="M14" s="7" t="n">
-        <v>723.95</v>
+        <v>730.46</v>
       </c>
     </row>
     <row r="15">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="L15" s="5" t="n"/>
       <c r="M15" s="7" t="n">
-        <v>673.29</v>
+        <v>687.97</v>
       </c>
     </row>
     <row r="16">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="L16" s="5" t="n"/>
       <c r="M16" s="7" t="n">
-        <v>665.78</v>
+        <v>678.92</v>
       </c>
     </row>
     <row r="17">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="L17" s="5" t="n"/>
       <c r="M17" s="7" t="n">
-        <v>603.4</v>
+        <v>608.39</v>
       </c>
     </row>
     <row r="18">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="L18" s="5" t="n"/>
       <c r="M18" s="7" t="n">
-        <v>502.06</v>
+        <v>529.85</v>
       </c>
     </row>
     <row r="19">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="L21" s="5" t="n"/>
       <c r="M21" s="7" t="n">
-        <v>422.65</v>
+        <v>451.32</v>
       </c>
     </row>
     <row r="22">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270111112 - KIT4P000655962DJ</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955072 - KIT4P0007258645B</t>
         </is>
       </c>
       <c r="C23" s="3" t="n">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>KIT4P000655962DJ</t>
+          <t>KIT4P0007258645B</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>809604</t>
+          <t>814495</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="L23" s="5" t="n"/>
       <c r="M23" s="7" t="n">
-        <v>343.27</v>
+        <v>376.27</v>
       </c>
     </row>
     <row r="24">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955072 - KIT4P0007258645B</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270111112 - KIT4P000655962DJ</t>
         </is>
       </c>
       <c r="C24" s="3" t="n">
@@ -1765,12 +1765,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0007258645B</t>
+          <t>KIT4P000655962DJ</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>814495</t>
+          <t>809604</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="L24" s="5" t="n"/>
       <c r="M24" s="7" t="n">
-        <v>335.8</v>
+        <v>343.27</v>
       </c>
     </row>
     <row r="25">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="L27" s="5" t="n"/>
       <c r="M27" s="7" t="n">
-        <v>273.22</v>
+        <v>275.65</v>
       </c>
     </row>
     <row r="28">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955392 - KIT4M05563527J4C</t>
+          <t>SMRT-05900510-LOS ANGELES CA-020955062-KIT4P00073915XX6</t>
         </is>
       </c>
       <c r="C28" s="3" t="n">
@@ -1977,17 +1977,17 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563527J4C</t>
+          <t>KIT4P00073915XX6</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>814452</t>
+          <t>814643</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="L28" s="5" t="n"/>
       <c r="M28" s="7" t="n">
-        <v>254.72</v>
+        <v>272.4</v>
       </c>
     </row>
     <row r="29">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="L29" s="5" t="n"/>
       <c r="M29" s="7" t="n">
-        <v>253.43</v>
+        <v>268.13</v>
       </c>
     </row>
     <row r="30">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482701118 - KIT4M04158951RH6</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955392 - KIT4M05563527J4C</t>
         </is>
       </c>
       <c r="C30" s="3" t="n">
@@ -2083,12 +2083,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158951RH6</t>
+          <t>KIT4M05563527J4C</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>809614</t>
+          <t>814452</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="L30" s="5" t="n"/>
       <c r="M30" s="7" t="n">
-        <v>251.27</v>
+        <v>258.21</v>
       </c>
     </row>
     <row r="31">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482701110 - KIT4M041546939GJ</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482701118 - KIT4M04158951RH6</t>
         </is>
       </c>
       <c r="C31" s="3" t="n">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>KIT4M041546939GJ</t>
+          <t>KIT4M04158951RH6</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>809607</t>
+          <t>809614</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="L31" s="5" t="n"/>
       <c r="M31" s="7" t="n">
-        <v>246.3</v>
+        <v>251.27</v>
       </c>
     </row>
     <row r="32">
@@ -2178,7 +2178,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-LOS ANGELES CA-020955062-KIT4P00073915XX6</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482701110 - KIT4M041546939GJ</t>
         </is>
       </c>
       <c r="C32" s="3" t="n">
@@ -2189,17 +2189,17 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073915XX6</t>
+          <t>KIT4M041546939GJ</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>814643</t>
+          <t>809607</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="L32" s="5" t="n"/>
       <c r="M32" s="7" t="n">
-        <v>237.4</v>
+        <v>246.3</v>
       </c>
     </row>
     <row r="33">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="L33" s="5" t="n"/>
       <c r="M33" s="7" t="n">
-        <v>222.99</v>
+        <v>233.2</v>
       </c>
     </row>
     <row r="34">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955322 - KIT4M055635305RS</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955522 - KIT4M05563504MBB</t>
         </is>
       </c>
       <c r="C35" s="3" t="n">
@@ -2348,12 +2348,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635305RS</t>
+          <t>KIT4M05563504MBB</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>814440</t>
+          <t>814460</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="L35" s="5" t="n"/>
       <c r="M35" s="7" t="n">
-        <v>167.01</v>
+        <v>183.43</v>
       </c>
     </row>
     <row r="36">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955522 - KIT4M05563504MBB</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482701116 - KIT4M03986275Q4M</t>
         </is>
       </c>
       <c r="C36" s="3" t="n">
@@ -2401,12 +2401,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563504MBB</t>
+          <t>KIT4M03986275Q4M</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>814460</t>
+          <t>809621</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="L36" s="5" t="n"/>
       <c r="M36" s="7" t="n">
-        <v>159.14</v>
+        <v>174.86</v>
       </c>
     </row>
     <row r="37">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827018 - KIT4M0415609166K</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955322 - KIT4M055635305RS</t>
         </is>
       </c>
       <c r="C37" s="3" t="n">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0415609166K</t>
+          <t>KIT4M055635305RS</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>809609</t>
+          <t>814440</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="L37" s="5" t="n"/>
       <c r="M37" s="7" t="n">
-        <v>158.76</v>
+        <v>170.78</v>
       </c>
     </row>
     <row r="38">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482701116 - KIT4M03986275Q4M</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827018 - KIT4M0415609166K</t>
         </is>
       </c>
       <c r="C38" s="3" t="n">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03986275Q4M</t>
+          <t>KIT4M0415609166K</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>809621</t>
+          <t>809609</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="L38" s="5" t="n"/>
       <c r="M38" s="7" t="n">
-        <v>151.92</v>
+        <v>170.01</v>
       </c>
     </row>
     <row r="39">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649352 - KIT4M05368220FG8</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955042 - KIT4P00072391SZM</t>
         </is>
       </c>
       <c r="C39" s="3" t="n">
@@ -2560,17 +2560,17 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368220FG8</t>
+          <t>KIT4P00072391SZM</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>810648</t>
+          <t>814493</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="L39" s="5" t="n"/>
       <c r="M39" s="7" t="n">
-        <v>138.22</v>
+        <v>169.46</v>
       </c>
     </row>
     <row r="40">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955682 - KIT4M055635887MK</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955182 - KIT4M05563562F45</t>
         </is>
       </c>
       <c r="C40" s="3" t="n">
@@ -2613,12 +2613,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635887MK</t>
+          <t>KIT4M05563562F45</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>814446</t>
+          <t>814443</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="L40" s="5" t="n"/>
       <c r="M40" s="7" t="n">
-        <v>136.41</v>
+        <v>153.41</v>
       </c>
     </row>
     <row r="41">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="L41" s="5" t="n"/>
       <c r="M41" s="7" t="n">
-        <v>133.25</v>
+        <v>148.9</v>
       </c>
     </row>
     <row r="42">
@@ -2708,7 +2708,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827014 - KIT4M04475149XG5</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649352 - KIT4M05368220FG8</t>
         </is>
       </c>
       <c r="C42" s="3" t="n">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475149XG5</t>
+          <t>KIT4M05368220FG8</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>809657</t>
+          <t>810648</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="L42" s="5" t="n"/>
       <c r="M42" s="7" t="n">
-        <v>128.45</v>
+        <v>148.28</v>
       </c>
     </row>
     <row r="43">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955672 - KIT4M055635979XD</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827014 - KIT4M04475149XG5</t>
         </is>
       </c>
       <c r="C43" s="3" t="n">
@@ -2772,12 +2772,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635979XD</t>
+          <t>KIT4M04475149XG5</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>814441</t>
+          <t>809657</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="L43" s="5" t="n"/>
       <c r="M43" s="7" t="n">
-        <v>128.24</v>
+        <v>143.2</v>
       </c>
     </row>
     <row r="44">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955182 - KIT4M05563562F45</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955682 - KIT4M055635887MK</t>
         </is>
       </c>
       <c r="C44" s="3" t="n">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563562F45</t>
+          <t>KIT4M055635887MK</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>814443</t>
+          <t>814446</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="L44" s="5" t="n"/>
       <c r="M44" s="7" t="n">
-        <v>126.95</v>
+        <v>137.62</v>
       </c>
     </row>
     <row r="45">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 -  Los Angeles CA - 020649422 - KIT4M05368200MVF</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955672 - KIT4M055635979XD</t>
         </is>
       </c>
       <c r="C45" s="3" t="n">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368200MVF</t>
+          <t>KIT4M055635979XD</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>810650</t>
+          <t>814441</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="L45" s="5" t="n"/>
       <c r="M45" s="7" t="n">
-        <v>126.59</v>
+        <v>129.43</v>
       </c>
     </row>
     <row r="46">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="L46" s="5" t="n"/>
       <c r="M46" s="7" t="n">
-        <v>125.77</v>
+        <v>127.51</v>
       </c>
     </row>
     <row r="47">
@@ -2973,7 +2973,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955632 - KIT4M055635329VD</t>
+          <t>SMA - 05900510 -  Los Angeles CA - 020649422 - KIT4M05368200MVF</t>
         </is>
       </c>
       <c r="C47" s="3" t="n">
@@ -2984,12 +2984,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635329VD</t>
+          <t>KIT4M05368200MVF</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>814479</t>
+          <t>810650</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="L47" s="5" t="n"/>
       <c r="M47" s="7" t="n">
-        <v>124.26</v>
+        <v>126.59</v>
       </c>
     </row>
     <row r="48">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437252 - KIT4P00083897XCW</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955632 - KIT4M055635329VD</t>
         </is>
       </c>
       <c r="C48" s="3" t="n">
@@ -3037,17 +3037,17 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00083897XCW</t>
+          <t>KIT4M055635329VD</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>816223</t>
+          <t>814479</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H48" s="5" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="L48" s="5" t="n"/>
       <c r="M48" s="7" t="n">
-        <v>120.74</v>
+        <v>124.26</v>
       </c>
     </row>
     <row r="49">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020955622 - KIT4M05563549RSR</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437252 - KIT4P00083897XCW</t>
         </is>
       </c>
       <c r="C49" s="3" t="n">
@@ -3090,17 +3090,17 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563549RSR</t>
+          <t>KIT4P00083897XCW</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>814483</t>
+          <t>816223</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="L49" s="5" t="n"/>
       <c r="M49" s="7" t="n">
-        <v>113.16</v>
+        <v>120.74</v>
       </c>
     </row>
     <row r="50">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649542 - KIT4M05413810Q4Z</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020955622 - KIT4M05563549RSR</t>
         </is>
       </c>
       <c r="C50" s="3" t="n">
@@ -3143,12 +3143,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413810Q4Z</t>
+          <t>KIT4M05563549RSR</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>812815</t>
+          <t>814483</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="L50" s="5" t="n"/>
       <c r="M50" s="7" t="n">
-        <v>109.7</v>
+        <v>113.16</v>
       </c>
     </row>
     <row r="51">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles, CA-020955372-KIT4M05563537G4G</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649542 - KIT4M05413810Q4Z</t>
         </is>
       </c>
       <c r="C51" s="3" t="n">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563537G4G</t>
+          <t>KIT4M05413810Q4Z</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>814456</t>
+          <t>812815</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="L51" s="5" t="n"/>
       <c r="M51" s="7" t="n">
-        <v>108.22</v>
+        <v>109.7</v>
       </c>
     </row>
     <row r="52">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270111110 - KIT4M03867737P9P</t>
+          <t>SMRT-05900510-Los Angeles, CA-020955372-KIT4M05563537G4G</t>
         </is>
       </c>
       <c r="C52" s="3" t="n">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03867737P9P</t>
+          <t>KIT4M05563537G4G</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>809622</t>
+          <t>814456</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="L52" s="5" t="n"/>
       <c r="M52" s="7" t="n">
-        <v>103.65</v>
+        <v>108.22</v>
       </c>
     </row>
     <row r="53">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020650172 - KIT4M05413811F4Q</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270111110 - KIT4M03867737P9P</t>
         </is>
       </c>
       <c r="C53" s="3" t="n">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413811F4Q</t>
+          <t>KIT4M03867737P9P</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>810104</t>
+          <t>809622</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="L53" s="5" t="n"/>
       <c r="M53" s="7" t="n">
-        <v>99.37</v>
+        <v>108.08</v>
       </c>
     </row>
     <row r="54">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="L54" s="5" t="n"/>
       <c r="M54" s="7" t="n">
-        <v>99.06</v>
+        <v>108.04</v>
       </c>
     </row>
     <row r="55">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955552 - KIT4M055635475JB</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649782 - KIT4M03986264P49</t>
         </is>
       </c>
       <c r="C55" s="3" t="n">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635475JB</t>
+          <t>KIT4M03986264P49</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>814465</t>
+          <t>809875</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="L55" s="5" t="n"/>
       <c r="M55" s="7" t="n">
-        <v>97.09</v>
+        <v>101.96</v>
       </c>
     </row>
     <row r="56">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955662 - KIT4M05563574ZBN</t>
+          <t>SS - 05900510 - Los Angeles CA - 020650102 - KIT4M054138257Z7</t>
         </is>
       </c>
       <c r="C56" s="3" t="n">
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563574ZBN</t>
+          <t>KIT4M054138257Z7</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>814453</t>
+          <t>810106</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="L56" s="5" t="n"/>
       <c r="M56" s="7" t="n">
-        <v>95.76000000000001</v>
+        <v>100.22</v>
       </c>
     </row>
     <row r="57">
@@ -3503,7 +3503,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438042 - KIT4M05799686CMX</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020650172 - KIT4M05413811F4Q</t>
         </is>
       </c>
       <c r="C57" s="3" t="n">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799686CMX</t>
+          <t>KIT4M05413811F4Q</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>816282</t>
+          <t>810104</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="L57" s="5" t="n"/>
       <c r="M57" s="7" t="n">
-        <v>94.92</v>
+        <v>99.37</v>
       </c>
     </row>
     <row r="58">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649782 - KIT4M03986264P49</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955552 - KIT4M055635475JB</t>
         </is>
       </c>
       <c r="C58" s="3" t="n">
@@ -3567,12 +3567,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03986264P49</t>
+          <t>KIT4M055635475JB</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>809875</t>
+          <t>814465</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="L58" s="5" t="n"/>
       <c r="M58" s="7" t="n">
-        <v>94.79000000000001</v>
+        <v>99.23</v>
       </c>
     </row>
     <row r="59">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020650232 - KIT4M054138222CP</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955662 - KIT4M05563574ZBN</t>
         </is>
       </c>
       <c r="C59" s="3" t="n">
@@ -3620,12 +3620,12 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138222CP</t>
+          <t>KIT4M05563574ZBN</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>812811</t>
+          <t>814453</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
@@ -3651,7 +3651,7 @@
       </c>
       <c r="L59" s="5" t="n"/>
       <c r="M59" s="7" t="n">
-        <v>93.27</v>
+        <v>96.91</v>
       </c>
     </row>
     <row r="60">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020650102 - KIT4M054138257Z7</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438042 - KIT4M05799686CMX</t>
         </is>
       </c>
       <c r="C60" s="3" t="n">
@@ -3673,12 +3673,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138257Z7</t>
+          <t>KIT4M05799686CMX</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>810106</t>
+          <t>816282</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="L60" s="5" t="n"/>
       <c r="M60" s="7" t="n">
-        <v>91.68000000000001</v>
+        <v>94.92</v>
       </c>
     </row>
     <row r="61">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955472 - KIT4M055635834N7</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020650232 - KIT4M054138222CP</t>
         </is>
       </c>
       <c r="C61" s="3" t="n">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635834N7</t>
+          <t>KIT4M054138222CP</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>814462</t>
+          <t>812811</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
@@ -3757,7 +3757,7 @@
       </c>
       <c r="L61" s="5" t="n"/>
       <c r="M61" s="7" t="n">
-        <v>89.45</v>
+        <v>93.27</v>
       </c>
     </row>
     <row r="62">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955142 - KIT4M05563518ZJD</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649712 - KIT4M046047397TM</t>
         </is>
       </c>
       <c r="C62" s="3" t="n">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563518ZJD</t>
+          <t>KIT4M046047397TM</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>814451</t>
+          <t>809863</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="L62" s="5" t="n"/>
       <c r="M62" s="7" t="n">
-        <v>85.18000000000001</v>
+        <v>90.26000000000001</v>
       </c>
     </row>
     <row r="63">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649872 - KIT4M054138175VJ</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955472 - KIT4M055635834N7</t>
         </is>
       </c>
       <c r="C63" s="3" t="n">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138175VJ</t>
+          <t>KIT4M055635834N7</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>812823</t>
+          <t>814462</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="L63" s="5" t="n"/>
       <c r="M63" s="7" t="n">
-        <v>83.95</v>
+        <v>89.45</v>
       </c>
     </row>
     <row r="64">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955332 - KIT4M05563590ZFQ</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955112 - KIT4P00073918HBX</t>
         </is>
       </c>
       <c r="C64" s="3" t="n">
@@ -3885,17 +3885,17 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563590ZFQ</t>
+          <t>KIT4P00073918HBX</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>814461</t>
+          <t>814645</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H64" s="5" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="L64" s="5" t="n"/>
       <c r="M64" s="7" t="n">
-        <v>83.88</v>
+        <v>88.79000000000001</v>
       </c>
     </row>
     <row r="65">
@@ -3927,7 +3927,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649712 - KIT4M046047397TM</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438092 - KIT4M05799694RW2</t>
         </is>
       </c>
       <c r="C65" s="3" t="n">
@@ -3938,12 +3938,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047397TM</t>
+          <t>KIT4M05799694RW2</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>809863</t>
+          <t>816277</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="L65" s="5" t="n"/>
       <c r="M65" s="7" t="n">
-        <v>83.59999999999999</v>
+        <v>87.29000000000001</v>
       </c>
     </row>
     <row r="66">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020649312-KIT4M05413771PVH</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955142 - KIT4M05563518ZJD</t>
         </is>
       </c>
       <c r="C66" s="3" t="n">
@@ -3991,12 +3991,12 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413771PVH</t>
+          <t>KIT4M05563518ZJD</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>812800</t>
+          <t>814451</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="L66" s="5" t="n"/>
       <c r="M66" s="7" t="n">
-        <v>79.63</v>
+        <v>85.18000000000001</v>
       </c>
     </row>
     <row r="67">
@@ -4033,7 +4033,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955112 - KIT4P00073918HBX</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955332 - KIT4M05563590ZFQ</t>
         </is>
       </c>
       <c r="C67" s="3" t="n">
@@ -4044,17 +4044,17 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073918HBX</t>
+          <t>KIT4M05563590ZFQ</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>814645</t>
+          <t>814461</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H67" s="5" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="L67" s="5" t="n"/>
       <c r="M67" s="7" t="n">
-        <v>79.54000000000001</v>
+        <v>84.56999999999999</v>
       </c>
     </row>
     <row r="68">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649562 - KIT4M054138125NW</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649872 - KIT4M054138175VJ</t>
         </is>
       </c>
       <c r="C68" s="3" t="n">
@@ -4097,12 +4097,12 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138125NW</t>
+          <t>KIT4M054138175VJ</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>812826</t>
+          <t>812823</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="L68" s="5" t="n"/>
       <c r="M68" s="7" t="n">
-        <v>77.14</v>
+        <v>83.95</v>
       </c>
     </row>
     <row r="69">
@@ -4139,7 +4139,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020650012 - KIT4M05413814GPJ</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955132 - KIT4M055635238J6</t>
         </is>
       </c>
       <c r="C69" s="3" t="n">
@@ -4150,12 +4150,12 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413814GPJ</t>
+          <t>KIT4M055635238J6</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>812812</t>
+          <t>814449</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="L69" s="5" t="n"/>
       <c r="M69" s="7" t="n">
-        <v>76.54000000000001</v>
+        <v>82.15000000000001</v>
       </c>
     </row>
     <row r="70">
@@ -4192,7 +4192,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955492 - KIT4M05563520SH2</t>
+          <t>SMRT-05900510-Los Angeles CA-020649312-KIT4M05413771PVH</t>
         </is>
       </c>
       <c r="C70" s="3" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563520SH2</t>
+          <t>KIT4M05413771PVH</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>814478</t>
+          <t>812800</t>
         </is>
       </c>
       <c r="G70" s="5" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="L70" s="5" t="n"/>
       <c r="M70" s="7" t="n">
-        <v>74.56999999999999</v>
+        <v>80.44</v>
       </c>
     </row>
     <row r="71">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438092 - KIT4M05799694RW2</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020650012 - KIT4M05413814GPJ</t>
         </is>
       </c>
       <c r="C71" s="3" t="n">
@@ -4256,12 +4256,12 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799694RW2</t>
+          <t>KIT4M05413814GPJ</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>816277</t>
+          <t>812812</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
@@ -4287,7 +4287,7 @@
       </c>
       <c r="L71" s="5" t="n"/>
       <c r="M71" s="7" t="n">
-        <v>74.44</v>
+        <v>78.33</v>
       </c>
     </row>
     <row r="72">
@@ -4298,7 +4298,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955092 - KIT4P00073957GV5</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649562 - KIT4M054138125NW</t>
         </is>
       </c>
       <c r="C72" s="3" t="n">
@@ -4309,17 +4309,17 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073957GV5</t>
+          <t>KIT4M054138125NW</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>814642</t>
+          <t>812826</t>
         </is>
       </c>
       <c r="G72" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H72" s="5" t="inlineStr">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="L72" s="5" t="n"/>
       <c r="M72" s="7" t="n">
-        <v>72.83</v>
+        <v>77.14</v>
       </c>
     </row>
     <row r="73">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955132 - KIT4M055635238J6</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955492 - KIT4M05563520SH2</t>
         </is>
       </c>
       <c r="C73" s="3" t="n">
@@ -4362,12 +4362,12 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635238J6</t>
+          <t>KIT4M05563520SH2</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>814449</t>
+          <t>814478</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="L73" s="5" t="n"/>
       <c r="M73" s="7" t="n">
-        <v>71.47</v>
+        <v>74.56999999999999</v>
       </c>
     </row>
     <row r="74">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649272 - KIT4M05413784W4K</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955092 - KIT4P00073957GV5</t>
         </is>
       </c>
       <c r="C74" s="3" t="n">
@@ -4415,17 +4415,17 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413784W4K</t>
+          <t>KIT4P00073957GV5</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>812821</t>
+          <t>814642</t>
         </is>
       </c>
       <c r="G74" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H74" s="5" t="inlineStr">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="L74" s="5" t="n"/>
       <c r="M74" s="7" t="n">
-        <v>69.13</v>
+        <v>72.86</v>
       </c>
     </row>
     <row r="75">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SS - 05900510 - Los Angeles, CA - 020649552 - KIT4M05413835RPF </t>
+          <t>SMRT-05900510-Los Angeles, CA-020955352-KIT4M05563525VC6</t>
         </is>
       </c>
       <c r="C75" s="3" t="n">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413835RPF</t>
+          <t>KIT4M05563525VC6</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>812827</t>
+          <t>814458</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="L75" s="5" t="n"/>
       <c r="M75" s="7" t="n">
-        <v>67.38</v>
+        <v>71.73999999999999</v>
       </c>
     </row>
     <row r="76">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649932 - KIT4M054138324MW</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482702 - KIT4M04604743HSS</t>
         </is>
       </c>
       <c r="C76" s="3" t="n">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138324MW</t>
+          <t>KIT4M04604743HSS</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>812834</t>
+          <t>809663</t>
         </is>
       </c>
       <c r="G76" s="5" t="inlineStr">
@@ -4552,7 +4552,7 @@
       </c>
       <c r="L76" s="5" t="n"/>
       <c r="M76" s="7" t="n">
-        <v>65.69</v>
+        <v>70.17</v>
       </c>
     </row>
     <row r="77">
@@ -4563,7 +4563,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649342 - KIT4M05413775N9M</t>
+          <t xml:space="preserve">SS - 05900510 - Los Angeles, CA - 020649552 - KIT4M05413835RPF </t>
         </is>
       </c>
       <c r="C77" s="3" t="n">
@@ -4574,12 +4574,12 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413775N9M</t>
+          <t>KIT4M05413835RPF</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>812818</t>
+          <t>812827</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr">
@@ -4605,7 +4605,7 @@
       </c>
       <c r="L77" s="5" t="n"/>
       <c r="M77" s="7" t="n">
-        <v>62.78</v>
+        <v>69.54000000000001</v>
       </c>
     </row>
     <row r="78">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955292 - KIT4M05563531XSB</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649272 - KIT4M05413784W4K</t>
         </is>
       </c>
       <c r="C78" s="3" t="n">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563531XSB</t>
+          <t>KIT4M05413784W4K</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>814469</t>
+          <t>812821</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="L78" s="5" t="n"/>
       <c r="M78" s="7" t="n">
-        <v>62.75</v>
+        <v>69.13</v>
       </c>
     </row>
     <row r="79">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020650252 - KIT4M05413820QXJ</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955262 - KIT4M05563521ZSX</t>
         </is>
       </c>
       <c r="C79" s="3" t="n">
@@ -4680,12 +4680,12 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413820QXJ</t>
+          <t>KIT4M05563521ZSX</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>810098</t>
+          <t>814476</t>
         </is>
       </c>
       <c r="G79" s="5" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="L79" s="5" t="n"/>
       <c r="M79" s="7" t="n">
-        <v>61.69</v>
+        <v>68.75</v>
       </c>
     </row>
     <row r="80">
@@ -4722,7 +4722,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955262 - KIT4M05563521ZSX</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649932 - KIT4M054138324MW</t>
         </is>
       </c>
       <c r="C80" s="3" t="n">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563521ZSX</t>
+          <t>KIT4M054138324MW</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>814476</t>
+          <t>812834</t>
         </is>
       </c>
       <c r="G80" s="5" t="inlineStr">
@@ -4764,7 +4764,7 @@
       </c>
       <c r="L80" s="5" t="n"/>
       <c r="M80" s="7" t="n">
-        <v>61.1</v>
+        <v>68.59</v>
       </c>
     </row>
     <row r="81">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="L81" s="5" t="n"/>
       <c r="M81" s="7" t="n">
-        <v>59.46</v>
+        <v>66.28</v>
       </c>
     </row>
     <row r="82">
@@ -4828,7 +4828,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482702 - KIT4M04604743HSS</t>
+          <t>SMRT-05900510-LOS ANGELES CA-020955202-KIT4M05563534GZ7</t>
         </is>
       </c>
       <c r="C82" s="3" t="n">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604743HSS</t>
+          <t>KIT4M05563534GZ7</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>809663</t>
+          <t>814467</t>
         </is>
       </c>
       <c r="G82" s="5" t="inlineStr">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="L82" s="5" t="n"/>
       <c r="M82" s="7" t="n">
-        <v>59.03</v>
+        <v>66.12</v>
       </c>
     </row>
     <row r="83">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles, CA-020955352-KIT4M05563525VC6</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955292 - KIT4M05563531XSB</t>
         </is>
       </c>
       <c r="C83" s="3" t="n">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563525VC6</t>
+          <t>KIT4M05563531XSB</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>814458</t>
+          <t>814469</t>
         </is>
       </c>
       <c r="G83" s="5" t="inlineStr">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="L83" s="5" t="n"/>
       <c r="M83" s="7" t="n">
-        <v>57.37</v>
+        <v>65.68000000000001</v>
       </c>
     </row>
     <row r="84">
@@ -4934,7 +4934,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482704 - KIT4M04604745G8Z</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649342 - KIT4M05413775N9M</t>
         </is>
       </c>
       <c r="C84" s="3" t="n">
@@ -4945,12 +4945,12 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604745G8Z</t>
+          <t>KIT4M05413775N9M</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>809661</t>
+          <t>812818</t>
         </is>
       </c>
       <c r="G84" s="5" t="inlineStr">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="L84" s="5" t="n"/>
       <c r="M84" s="7" t="n">
-        <v>57.14</v>
+        <v>63.82</v>
       </c>
     </row>
     <row r="85">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437392 - KIT4M05872555BJR</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020650252 - KIT4M05413820QXJ</t>
         </is>
       </c>
       <c r="C85" s="3" t="n">
@@ -4998,12 +4998,12 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872555BJR</t>
+          <t>KIT4M05413820QXJ</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>816074</t>
+          <t>810098</t>
         </is>
       </c>
       <c r="G85" s="5" t="inlineStr">
@@ -5029,7 +5029,7 @@
       </c>
       <c r="L85" s="5" t="n"/>
       <c r="M85" s="7" t="n">
-        <v>54.97</v>
+        <v>61.69</v>
       </c>
     </row>
     <row r="86">
@@ -5040,7 +5040,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827011118 - KIT4M03867766NGK</t>
+          <t>SMRT-05900510-Los Angeles, CA-020955582-KIT4M05563593DMC</t>
         </is>
       </c>
       <c r="C86" s="3" t="n">
@@ -5051,12 +5051,12 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03867766NGK</t>
+          <t>KIT4M05563593DMC</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>809615</t>
+          <t>814442</t>
         </is>
       </c>
       <c r="G86" s="5" t="inlineStr">
@@ -5082,7 +5082,7 @@
       </c>
       <c r="L86" s="5" t="n"/>
       <c r="M86" s="7" t="n">
-        <v>54.54</v>
+        <v>61.16</v>
       </c>
     </row>
     <row r="87">
@@ -5093,7 +5093,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles, CA-020955582-KIT4M05563593DMC</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955692 - KIT4M05563579H9F</t>
         </is>
       </c>
       <c r="C87" s="3" t="n">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563593DMC</t>
+          <t>KIT4M05563579H9F</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>814442</t>
+          <t>814480</t>
         </is>
       </c>
       <c r="G87" s="5" t="inlineStr">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="L87" s="5" t="n"/>
       <c r="M87" s="7" t="n">
-        <v>54.34</v>
+        <v>57.85</v>
       </c>
     </row>
     <row r="88">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955412 - KIT4M05563598Z74</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020955462 - KIT4M05563513GTF</t>
         </is>
       </c>
       <c r="C88" s="3" t="n">
@@ -5157,12 +5157,12 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563598Z74</t>
+          <t>KIT4M05563513GTF</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>814474</t>
+          <t>814432</t>
         </is>
       </c>
       <c r="G88" s="5" t="inlineStr">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="L88" s="5" t="n"/>
       <c r="M88" s="7" t="n">
-        <v>54.34</v>
+        <v>57.75</v>
       </c>
     </row>
     <row r="89">
@@ -5241,7 +5241,7 @@
       </c>
       <c r="L89" s="5" t="n"/>
       <c r="M89" s="7" t="n">
-        <v>53.03</v>
+        <v>57.47</v>
       </c>
     </row>
     <row r="90">
@@ -5252,7 +5252,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649372 - KIT4M05368221HQ5</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482704 - KIT4M04604745G8Z</t>
         </is>
       </c>
       <c r="C90" s="3" t="n">
@@ -5263,12 +5263,12 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368221HQ5</t>
+          <t>KIT4M04604745G8Z</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>810834</t>
+          <t>809661</t>
         </is>
       </c>
       <c r="G90" s="5" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="L90" s="5" t="n"/>
       <c r="M90" s="7" t="n">
-        <v>52.3</v>
+        <v>57.14</v>
       </c>
     </row>
     <row r="91">
@@ -5305,7 +5305,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270112 - KIT4M044751638F5</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827011118 - KIT4M03867766NGK</t>
         </is>
       </c>
       <c r="C91" s="3" t="n">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>KIT4M044751638F5</t>
+          <t>KIT4M03867766NGK</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>809618</t>
+          <t>809615</t>
         </is>
       </c>
       <c r="G91" s="5" t="inlineStr">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="L91" s="5" t="n"/>
       <c r="M91" s="7" t="n">
-        <v>51.54</v>
+        <v>56.33</v>
       </c>
     </row>
     <row r="92">
@@ -5358,7 +5358,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955692 - KIT4M05563603CP4</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437392 - KIT4M05872555BJR</t>
         </is>
       </c>
       <c r="C92" s="3" t="n">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563603CP4</t>
+          <t>KIT4M05872555BJR</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>814447</t>
+          <t>816074</t>
         </is>
       </c>
       <c r="G92" s="5" t="inlineStr">
@@ -5400,7 +5400,7 @@
       </c>
       <c r="L92" s="5" t="n"/>
       <c r="M92" s="7" t="n">
-        <v>51.44</v>
+        <v>56.28</v>
       </c>
     </row>
     <row r="93">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-LOS ANGELES CA-020955202-KIT4M05563534GZ7</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955412 - KIT4M05563598Z74</t>
         </is>
       </c>
       <c r="C93" s="3" t="n">
@@ -5422,12 +5422,12 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563534GZ7</t>
+          <t>KIT4M05563598Z74</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>814467</t>
+          <t>814474</t>
         </is>
       </c>
       <c r="G93" s="5" t="inlineStr">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="L93" s="5" t="n"/>
       <c r="M93" s="7" t="n">
-        <v>50.61</v>
+        <v>55.56</v>
       </c>
     </row>
     <row r="94">
@@ -5506,7 +5506,7 @@
       </c>
       <c r="L94" s="5" t="n"/>
       <c r="M94" s="7" t="n">
-        <v>50.57</v>
+        <v>54.72</v>
       </c>
     </row>
     <row r="95">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020650142 - KIT4M05413839D24</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270112 - KIT4M044751638F5</t>
         </is>
       </c>
       <c r="C95" s="3" t="n">
@@ -5528,12 +5528,12 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413839D24</t>
+          <t>KIT4M044751638F5</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>810096</t>
+          <t>809618</t>
         </is>
       </c>
       <c r="G95" s="5" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="L95" s="5" t="n"/>
       <c r="M95" s="7" t="n">
-        <v>50.33</v>
+        <v>53.88</v>
       </c>
     </row>
     <row r="96">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955042 - KIT4P00072391SZM</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649372 - KIT4M05368221HQ5</t>
         </is>
       </c>
       <c r="C96" s="3" t="n">
@@ -5581,17 +5581,17 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00072391SZM</t>
+          <t>KIT4M05368221HQ5</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>814493</t>
+          <t>810834</t>
         </is>
       </c>
       <c r="G96" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H96" s="5" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="L96" s="5" t="n"/>
       <c r="M96" s="7" t="n">
-        <v>49.91</v>
+        <v>53.65</v>
       </c>
     </row>
     <row r="97">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955692 - KIT4M05563579H9F</t>
+          <t>SS - 05900510 - Los Angeles CA - 020650042 - KIT4M05413819JV5</t>
         </is>
       </c>
       <c r="C97" s="3" t="n">
@@ -5634,12 +5634,12 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563579H9F</t>
+          <t>KIT4M05413819JV5</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>814480</t>
+          <t>812796</t>
         </is>
       </c>
       <c r="G97" s="5" t="inlineStr">
@@ -5665,7 +5665,7 @@
       </c>
       <c r="L97" s="5" t="n"/>
       <c r="M97" s="7" t="n">
-        <v>49.3</v>
+        <v>53.04</v>
       </c>
     </row>
     <row r="98">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270111114 - KIT4P00065593VWC</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955692 - KIT4M05563603CP4</t>
         </is>
       </c>
       <c r="C98" s="3" t="n">
@@ -5687,17 +5687,17 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065593VWC</t>
+          <t>KIT4M05563603CP4</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>809606</t>
+          <t>814447</t>
         </is>
       </c>
       <c r="G98" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H98" s="5" t="inlineStr">
@@ -5718,7 +5718,7 @@
       </c>
       <c r="L98" s="5" t="n"/>
       <c r="M98" s="7" t="n">
-        <v>49.23</v>
+        <v>52.74</v>
       </c>
     </row>
     <row r="99">
@@ -5729,7 +5729,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles, CA - 0204827011112 - KIT4M04158967K28</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020650142 - KIT4M05413839D24</t>
         </is>
       </c>
       <c r="C99" s="3" t="n">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158967K28</t>
+          <t>KIT4M05413839D24</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>809620</t>
+          <t>810096</t>
         </is>
       </c>
       <c r="G99" s="5" t="inlineStr">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="L99" s="5" t="n"/>
       <c r="M99" s="7" t="n">
-        <v>49.19</v>
+        <v>50.33</v>
       </c>
     </row>
     <row r="100">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955702 - KIT4M05563571G8W</t>
+          <t>STS - 05900510 - Los Angeles, CA - 0204827011112 - KIT4M04158967K28</t>
         </is>
       </c>
       <c r="C100" s="3" t="n">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563571G8W</t>
+          <t>KIT4M04158967K28</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>814481</t>
+          <t>809620</t>
         </is>
       </c>
       <c r="G100" s="5" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="L100" s="5" t="n"/>
       <c r="M100" s="7" t="n">
-        <v>48.6</v>
+        <v>50.16</v>
       </c>
     </row>
     <row r="101">
@@ -5835,7 +5835,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649672 - KIT4M04606113TPB</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827016 - KIT4M041536494G6</t>
         </is>
       </c>
       <c r="C101" s="3" t="n">
@@ -5846,12 +5846,12 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04606113TPB</t>
+          <t>KIT4M041536494G6</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>809862</t>
+          <t>809617</t>
         </is>
       </c>
       <c r="G101" s="5" t="inlineStr">
@@ -5877,7 +5877,7 @@
       </c>
       <c r="L101" s="5" t="n"/>
       <c r="M101" s="7" t="n">
-        <v>46.74</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="102">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles, CA-020955452-KIT4M05563529K2D</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955702 - KIT4M05563571G8W</t>
         </is>
       </c>
       <c r="C102" s="3" t="n">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563529K2D</t>
+          <t>KIT4M05563571G8W</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>814473</t>
+          <t>814481</t>
         </is>
       </c>
       <c r="G102" s="5" t="inlineStr">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="L102" s="5" t="n"/>
       <c r="M102" s="7" t="n">
-        <v>46.61</v>
+        <v>49.53</v>
       </c>
     </row>
     <row r="103">
@@ -5941,7 +5941,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020650042 - KIT4M05413819JV5</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270111114 - KIT4P00065593VWC</t>
         </is>
       </c>
       <c r="C103" s="3" t="n">
@@ -5952,17 +5952,17 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413819JV5</t>
+          <t>KIT4P00065593VWC</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>812796</t>
+          <t>809606</t>
         </is>
       </c>
       <c r="G103" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H103" s="5" t="inlineStr">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="L103" s="5" t="n"/>
       <c r="M103" s="7" t="n">
-        <v>45.57</v>
+        <v>49.23</v>
       </c>
     </row>
     <row r="104">
@@ -5994,7 +5994,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827016 - KIT4M041536494G6</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437272 - KIT4P0008459589D</t>
         </is>
       </c>
       <c r="C104" s="3" t="n">
@@ -6005,17 +6005,17 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>KIT4M041536494G6</t>
+          <t>KIT4P0008459589D</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>809617</t>
+          <t>816222</t>
         </is>
       </c>
       <c r="G104" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H104" s="5" t="inlineStr">
@@ -6036,7 +6036,7 @@
       </c>
       <c r="L104" s="5" t="n"/>
       <c r="M104" s="7" t="n">
-        <v>45.09</v>
+        <v>48.21</v>
       </c>
     </row>
     <row r="105">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020955462 - KIT4M05563513GTF</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649672 - KIT4M04606113TPB</t>
         </is>
       </c>
       <c r="C105" s="3" t="n">
@@ -6058,12 +6058,12 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563513GTF</t>
+          <t>KIT4M04606113TPB</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>814432</t>
+          <t>809862</t>
         </is>
       </c>
       <c r="G105" s="5" t="inlineStr">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="L105" s="5" t="n"/>
       <c r="M105" s="7" t="n">
-        <v>44.45</v>
+        <v>46.74</v>
       </c>
     </row>
     <row r="106">
@@ -6100,7 +6100,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649812 - KIT4M04604742S6S</t>
+          <t>SMRT-05900510-Los Angeles, CA-020955452-KIT4M05563529K2D</t>
         </is>
       </c>
       <c r="C106" s="3" t="n">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604742S6S</t>
+          <t>KIT4M05563529K2D</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>809874</t>
+          <t>814473</t>
         </is>
       </c>
       <c r="G106" s="5" t="inlineStr">
@@ -6142,7 +6142,7 @@
       </c>
       <c r="L106" s="5" t="n"/>
       <c r="M106" s="7" t="n">
-        <v>43.24</v>
+        <v>46.61</v>
       </c>
     </row>
     <row r="107">
@@ -6153,7 +6153,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649432 - KIT4M05413778RBR</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649212 - KIT4P00065633ZXC</t>
         </is>
       </c>
       <c r="C107" s="3" t="n">
@@ -6164,17 +6164,17 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413778RBR</t>
+          <t>KIT4P00065633ZXC</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>812843</t>
+          <t>812922</t>
         </is>
       </c>
       <c r="G107" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H107" s="5" t="inlineStr">
@@ -6195,7 +6195,7 @@
       </c>
       <c r="L107" s="5" t="n"/>
       <c r="M107" s="7" t="n">
-        <v>42.82</v>
+        <v>46.56</v>
       </c>
     </row>
     <row r="108">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="L108" s="5" t="n"/>
       <c r="M108" s="7" t="n">
-        <v>42.66</v>
+        <v>46.28</v>
       </c>
     </row>
     <row r="109">
@@ -6259,7 +6259,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020650192 - KIT4M054138007JF</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649832 - KIT4M03866596RZG</t>
         </is>
       </c>
       <c r="C109" s="3" t="n">
@@ -6270,12 +6270,12 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138007JF</t>
+          <t>KIT4M03866596RZG</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>810095</t>
+          <t>809869</t>
         </is>
       </c>
       <c r="G109" s="5" t="inlineStr">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="L109" s="5" t="n"/>
       <c r="M109" s="7" t="n">
-        <v>42.59</v>
+        <v>44.76</v>
       </c>
     </row>
     <row r="110">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020650052 - KIT4M05413781K6C</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649812 - KIT4M04604742S6S</t>
         </is>
       </c>
       <c r="C110" s="3" t="n">
@@ -6323,12 +6323,12 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413781K6C</t>
+          <t>KIT4M04604742S6S</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>812798</t>
+          <t>809874</t>
         </is>
       </c>
       <c r="G110" s="5" t="inlineStr">
@@ -6354,7 +6354,7 @@
       </c>
       <c r="L110" s="5" t="n"/>
       <c r="M110" s="7" t="n">
-        <v>42.04</v>
+        <v>43.24</v>
       </c>
     </row>
     <row r="111">
@@ -6365,7 +6365,7 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020955652 - KIT4M0556358988Z</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649432 - KIT4M05413778RBR</t>
         </is>
       </c>
       <c r="C111" s="3" t="n">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0556358988Z</t>
+          <t>KIT4M05413778RBR</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>814484</t>
+          <t>812843</t>
         </is>
       </c>
       <c r="G111" s="5" t="inlineStr">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="L111" s="5" t="n"/>
       <c r="M111" s="7" t="n">
-        <v>41.86</v>
+        <v>42.82</v>
       </c>
     </row>
     <row r="112">
@@ -6418,7 +6418,7 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270116 - KIT4M03476116F45</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020650192 - KIT4M054138007JF</t>
         </is>
       </c>
       <c r="C112" s="3" t="n">
@@ -6429,12 +6429,12 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03476116F45</t>
+          <t>KIT4M054138007JF</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>809608</t>
+          <t>810095</t>
         </is>
       </c>
       <c r="G112" s="5" t="inlineStr">
@@ -6460,7 +6460,7 @@
       </c>
       <c r="L112" s="5" t="n"/>
       <c r="M112" s="7" t="n">
-        <v>41.43</v>
+        <v>42.59</v>
       </c>
     </row>
     <row r="113">
@@ -6471,7 +6471,7 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649832 - KIT4M03866596RZG</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020955652 - KIT4M0556358988Z</t>
         </is>
       </c>
       <c r="C113" s="3" t="n">
@@ -6482,12 +6482,12 @@
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03866596RZG</t>
+          <t>KIT4M0556358988Z</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>809869</t>
+          <t>814484</t>
         </is>
       </c>
       <c r="G113" s="5" t="inlineStr">
@@ -6513,7 +6513,7 @@
       </c>
       <c r="L113" s="5" t="n"/>
       <c r="M113" s="7" t="n">
-        <v>40.17</v>
+        <v>42.15</v>
       </c>
     </row>
     <row r="114">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 020955382 - KIT4M05563509CHJ</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020650052 - KIT4M05413781K6C</t>
         </is>
       </c>
       <c r="C114" s="3" t="n">
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563509CHJ</t>
+          <t>KIT4M05413781K6C</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>814431</t>
+          <t>812798</t>
         </is>
       </c>
       <c r="G114" s="5" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="L114" s="5" t="n"/>
       <c r="M114" s="7" t="n">
-        <v>39.39</v>
+        <v>42.04</v>
       </c>
     </row>
     <row r="115">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="L115" s="5" t="n"/>
       <c r="M115" s="7" t="n">
-        <v>38.86</v>
+        <v>41.82</v>
       </c>
     </row>
     <row r="116">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955602 - KIT4M05563560225</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270116 - KIT4M03476116F45</t>
         </is>
       </c>
       <c r="C116" s="3" t="n">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563560225</t>
+          <t>KIT4M03476116F45</t>
         </is>
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>814454</t>
+          <t>809608</t>
         </is>
       </c>
       <c r="G116" s="5" t="inlineStr">
@@ -6672,7 +6672,7 @@
       </c>
       <c r="L116" s="5" t="n"/>
       <c r="M116" s="7" t="n">
-        <v>38.09</v>
+        <v>41.44</v>
       </c>
     </row>
     <row r="117">
@@ -6683,7 +6683,7 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020650082 - KIT4M05413792H8C</t>
+          <t>SS - 05900510 -  Los Angeles CA - 020955382 - KIT4M05563509CHJ</t>
         </is>
       </c>
       <c r="C117" s="3" t="n">
@@ -6694,12 +6694,12 @@
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413792H8C</t>
+          <t>KIT4M05563509CHJ</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>812803</t>
+          <t>814431</t>
         </is>
       </c>
       <c r="G117" s="5" t="inlineStr">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="L117" s="5" t="n"/>
       <c r="M117" s="7" t="n">
-        <v>37.81</v>
+        <v>40.3</v>
       </c>
     </row>
     <row r="118">
@@ -6736,7 +6736,7 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649212 - KIT4P00065633ZXC</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649682 - KIT4M046047384RX</t>
         </is>
       </c>
       <c r="C118" s="3" t="n">
@@ -6747,17 +6747,17 @@
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065633ZXC</t>
+          <t>KIT4M046047384RX</t>
         </is>
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>812922</t>
+          <t>809870</t>
         </is>
       </c>
       <c r="G118" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H118" s="5" t="inlineStr">
@@ -6778,7 +6778,7 @@
       </c>
       <c r="L118" s="5" t="n"/>
       <c r="M118" s="7" t="n">
-        <v>37.56</v>
+        <v>38.51</v>
       </c>
     </row>
     <row r="119">
@@ -6789,7 +6789,7 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020650112 - KIT4M05413840D9J</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955602 - KIT4M05563560225</t>
         </is>
       </c>
       <c r="C119" s="3" t="n">
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413840D9J</t>
+          <t>KIT4M05563560225</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>810099</t>
+          <t>814454</t>
         </is>
       </c>
       <c r="G119" s="5" t="inlineStr">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="L119" s="5" t="n"/>
       <c r="M119" s="7" t="n">
-        <v>34.44</v>
+        <v>38.09</v>
       </c>
     </row>
     <row r="120">
@@ -6842,7 +6842,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649942 - KIT4M05413786BXC</t>
+          <t>STS - 05900510 - Los Angeles CA - 020650082 - KIT4M05413792H8C</t>
         </is>
       </c>
       <c r="C120" s="3" t="n">
@@ -6853,12 +6853,12 @@
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413786BXC</t>
+          <t>KIT4M05413792H8C</t>
         </is>
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t>812838</t>
+          <t>812803</t>
         </is>
       </c>
       <c r="G120" s="5" t="inlineStr">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="L120" s="5" t="n"/>
       <c r="M120" s="7" t="n">
-        <v>34.4</v>
+        <v>37.81</v>
       </c>
     </row>
     <row r="121">
@@ -6937,7 +6937,7 @@
       </c>
       <c r="L121" s="5" t="n"/>
       <c r="M121" s="7" t="n">
-        <v>33.05</v>
+        <v>36.87</v>
       </c>
     </row>
     <row r="122">
@@ -6948,7 +6948,7 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649682 - KIT4M046047384RX</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482701112 - KIT4M04158973M2C</t>
         </is>
       </c>
       <c r="C122" s="3" t="n">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047384RX</t>
+          <t>KIT4M04158973M2C</t>
         </is>
       </c>
       <c r="F122" s="4" t="inlineStr">
         <is>
-          <t>809870</t>
+          <t>809610</t>
         </is>
       </c>
       <c r="G122" s="5" t="inlineStr">
@@ -6990,7 +6990,7 @@
       </c>
       <c r="L122" s="5" t="n"/>
       <c r="M122" s="7" t="n">
-        <v>33</v>
+        <v>36.26</v>
       </c>
     </row>
     <row r="123">
@@ -7001,7 +7001,7 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649412 - KIT4M05413769796</t>
+          <t>SS - 05900510 -  Los Angeles CA - 021438232 - KIT4M05872520QJM</t>
         </is>
       </c>
       <c r="C123" s="3" t="n">
@@ -7012,12 +7012,12 @@
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413769796</t>
+          <t>KIT4M05872520QJM</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>812839</t>
+          <t>816078</t>
         </is>
       </c>
       <c r="G123" s="5" t="inlineStr">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="L123" s="5" t="n"/>
       <c r="M123" s="7" t="n">
-        <v>32.57</v>
+        <v>34.98</v>
       </c>
     </row>
     <row r="124">
@@ -7054,7 +7054,7 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482706 - KIT4M04604744V6K</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020650112 - KIT4M05413840D9J</t>
         </is>
       </c>
       <c r="C124" s="3" t="n">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604744V6K</t>
+          <t>KIT4M05413840D9J</t>
         </is>
       </c>
       <c r="F124" s="4" t="inlineStr">
         <is>
-          <t>809659</t>
+          <t>810099</t>
         </is>
       </c>
       <c r="G124" s="5" t="inlineStr">
@@ -7096,7 +7096,7 @@
       </c>
       <c r="L124" s="5" t="n"/>
       <c r="M124" s="7" t="n">
-        <v>31.38</v>
+        <v>34.86</v>
       </c>
     </row>
     <row r="125">
@@ -7107,7 +7107,7 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 6858375 - KIT4M05872512N5W</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649942 - KIT4M05413786BXC</t>
         </is>
       </c>
       <c r="C125" s="3" t="n">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872512N5W</t>
+          <t>KIT4M05413786BXC</t>
         </is>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>816077</t>
+          <t>812838</t>
         </is>
       </c>
       <c r="G125" s="5" t="inlineStr">
@@ -7149,7 +7149,7 @@
       </c>
       <c r="L125" s="5" t="n"/>
       <c r="M125" s="7" t="n">
-        <v>31.07</v>
+        <v>34.4</v>
       </c>
     </row>
     <row r="126">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="L126" s="5" t="n"/>
       <c r="M126" s="7" t="n">
-        <v>29.93</v>
+        <v>33.87</v>
       </c>
     </row>
     <row r="127">
@@ -7213,7 +7213,7 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437272 - KIT4P0008459589D</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649412 - KIT4M05413769796</t>
         </is>
       </c>
       <c r="C127" s="3" t="n">
@@ -7224,17 +7224,17 @@
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0008459589D</t>
+          <t>KIT4M05413769796</t>
         </is>
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>816222</t>
+          <t>812839</t>
         </is>
       </c>
       <c r="G127" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H127" s="5" t="inlineStr">
@@ -7255,7 +7255,7 @@
       </c>
       <c r="L127" s="5" t="n"/>
       <c r="M127" s="7" t="n">
-        <v>28.57</v>
+        <v>32.57</v>
       </c>
     </row>
     <row r="128">
@@ -7266,7 +7266,7 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438002 - KIT4M05799701SGS</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482706 - KIT4M04604744V6K</t>
         </is>
       </c>
       <c r="C128" s="3" t="n">
@@ -7277,12 +7277,12 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799701SGS</t>
+          <t>KIT4M04604744V6K</t>
         </is>
       </c>
       <c r="F128" s="4" t="inlineStr">
         <is>
-          <t>816284</t>
+          <t>809659</t>
         </is>
       </c>
       <c r="G128" s="5" t="inlineStr">
@@ -7308,7 +7308,7 @@
       </c>
       <c r="L128" s="5" t="n"/>
       <c r="M128" s="7" t="n">
-        <v>28.22</v>
+        <v>31.38</v>
       </c>
     </row>
     <row r="129">
@@ -7319,7 +7319,7 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649742 - KIT4M04350554X4Z</t>
+          <t>SS - 05900510 - Los Angeles CA - 6858375 - KIT4M05872512N5W</t>
         </is>
       </c>
       <c r="C129" s="3" t="n">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04350554X4Z</t>
+          <t>KIT4M05872512N5W</t>
         </is>
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>809866</t>
+          <t>816077</t>
         </is>
       </c>
       <c r="G129" s="5" t="inlineStr">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="L129" s="5" t="n"/>
       <c r="M129" s="7" t="n">
-        <v>27.16</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="130">
@@ -7372,7 +7372,7 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649532 - KIT4M05413808FFZ</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955712 - KIT4M05563586ZTR</t>
         </is>
       </c>
       <c r="C130" s="3" t="n">
@@ -7383,12 +7383,12 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413808FFZ</t>
+          <t>KIT4M05563586ZTR</t>
         </is>
       </c>
       <c r="F130" s="4" t="inlineStr">
         <is>
-          <t>812828</t>
+          <t>814445</t>
         </is>
       </c>
       <c r="G130" s="5" t="inlineStr">
@@ -7414,7 +7414,7 @@
       </c>
       <c r="L130" s="5" t="n"/>
       <c r="M130" s="7" t="n">
-        <v>27.14</v>
+        <v>30.87</v>
       </c>
     </row>
     <row r="131">
@@ -7425,7 +7425,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649822 - KIT4M04604740BM6</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438002 - KIT4M05799701SGS</t>
         </is>
       </c>
       <c r="C131" s="3" t="n">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604740BM6</t>
+          <t>KIT4M05799701SGS</t>
         </is>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>809872</t>
+          <t>816284</t>
         </is>
       </c>
       <c r="G131" s="5" t="inlineStr">
@@ -7467,7 +7467,7 @@
       </c>
       <c r="L131" s="5" t="n"/>
       <c r="M131" s="7" t="n">
-        <v>26.94</v>
+        <v>29.64</v>
       </c>
     </row>
     <row r="132">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="L132" s="5" t="n"/>
       <c r="M132" s="7" t="n">
-        <v>26.82</v>
+        <v>29.07</v>
       </c>
     </row>
     <row r="133">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955342 - KIT4M05563524MJ4</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649822 - KIT4M04604740BM6</t>
         </is>
       </c>
       <c r="C133" s="3" t="n">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563524MJ4</t>
+          <t>KIT4M04604740BM6</t>
         </is>
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>814472</t>
+          <t>809872</t>
         </is>
       </c>
       <c r="G133" s="5" t="inlineStr">
@@ -7573,7 +7573,7 @@
       </c>
       <c r="L133" s="5" t="n"/>
       <c r="M133" s="7" t="n">
-        <v>26.26</v>
+        <v>28.63</v>
       </c>
     </row>
     <row r="134">
@@ -7584,7 +7584,7 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649362 - KIT4M05368336DBC</t>
+          <t>SMRT-05900510-Los Angeles CA-020649292-KIT4M05368201SNV</t>
         </is>
       </c>
       <c r="C134" s="3" t="n">
@@ -7595,12 +7595,12 @@
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368336DBC</t>
+          <t>KIT4M05368201SNV</t>
         </is>
       </c>
       <c r="F134" s="4" t="inlineStr">
         <is>
-          <t>810831</t>
+          <t>810651</t>
         </is>
       </c>
       <c r="G134" s="5" t="inlineStr">
@@ -7626,7 +7626,7 @@
       </c>
       <c r="L134" s="5" t="n"/>
       <c r="M134" s="7" t="n">
-        <v>25.14</v>
+        <v>28.01</v>
       </c>
     </row>
     <row r="135">
@@ -7637,7 +7637,7 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020649292-KIT4M05368201SNV</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649742 - KIT4M04350554X4Z</t>
         </is>
       </c>
       <c r="C135" s="3" t="n">
@@ -7648,12 +7648,12 @@
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368201SNV</t>
+          <t>KIT4M04350554X4Z</t>
         </is>
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>810651</t>
+          <t>809866</t>
         </is>
       </c>
       <c r="G135" s="5" t="inlineStr">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="L135" s="5" t="n"/>
       <c r="M135" s="7" t="n">
-        <v>24.72</v>
+        <v>27.16</v>
       </c>
     </row>
     <row r="136">
@@ -7690,7 +7690,7 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955212 - KIT4M05563512GBQ</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649532 - KIT4M05413808FFZ</t>
         </is>
       </c>
       <c r="C136" s="3" t="n">
@@ -7701,12 +7701,12 @@
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563512GBQ</t>
+          <t>KIT4M05413808FFZ</t>
         </is>
       </c>
       <c r="F136" s="4" t="inlineStr">
         <is>
-          <t>814435</t>
+          <t>812828</t>
         </is>
       </c>
       <c r="G136" s="5" t="inlineStr">
@@ -7732,7 +7732,7 @@
       </c>
       <c r="L136" s="5" t="n"/>
       <c r="M136" s="7" t="n">
-        <v>24.55</v>
+        <v>27.14</v>
       </c>
     </row>
     <row r="137">
@@ -7743,7 +7743,7 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482701112 - KIT4M04158973M2C</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649452 - KIT4M05413785QCG</t>
         </is>
       </c>
       <c r="C137" s="3" t="n">
@@ -7754,12 +7754,12 @@
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158973M2C</t>
+          <t>KIT4M05413785QCG</t>
         </is>
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>809610</t>
+          <t>812806</t>
         </is>
       </c>
       <c r="G137" s="5" t="inlineStr">
@@ -7785,7 +7785,7 @@
       </c>
       <c r="L137" s="5" t="n"/>
       <c r="M137" s="7" t="n">
-        <v>24.48</v>
+        <v>26.31</v>
       </c>
     </row>
     <row r="138">
@@ -7796,7 +7796,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649452 - KIT4M05413785QCG</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955342 - KIT4M05563524MJ4</t>
         </is>
       </c>
       <c r="C138" s="3" t="n">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413785QCG</t>
+          <t>KIT4M05563524MJ4</t>
         </is>
       </c>
       <c r="F138" s="4" t="inlineStr">
         <is>
-          <t>812806</t>
+          <t>814472</t>
         </is>
       </c>
       <c r="G138" s="5" t="inlineStr">
@@ -7838,7 +7838,7 @@
       </c>
       <c r="L138" s="5" t="n"/>
       <c r="M138" s="7" t="n">
-        <v>23.53</v>
+        <v>26.26</v>
       </c>
     </row>
     <row r="139">
@@ -7849,7 +7849,7 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438242 - KIT4M058725094XP</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955502 - KIT4M05563502GJS</t>
         </is>
       </c>
       <c r="C139" s="3" t="n">
@@ -7860,12 +7860,12 @@
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725094XP</t>
+          <t>KIT4M05563502GJS</t>
         </is>
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>816085</t>
+          <t>814470</t>
         </is>
       </c>
       <c r="G139" s="5" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="L139" s="5" t="n"/>
       <c r="M139" s="7" t="n">
-        <v>23.38</v>
+        <v>26.21</v>
       </c>
     </row>
     <row r="140">
@@ -7902,7 +7902,7 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020650162 - KIT4M05413837SMB</t>
+          <t>SMA - 05900510 -  Los Angeles CA - 020649512 - KIT4M054138318Q7</t>
         </is>
       </c>
       <c r="C140" s="3" t="n">
@@ -7913,12 +7913,12 @@
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413837SMB</t>
+          <t>KIT4M054138318Q7</t>
         </is>
       </c>
       <c r="F140" s="4" t="inlineStr">
         <is>
-          <t>810100</t>
+          <t>812814</t>
         </is>
       </c>
       <c r="G140" s="5" t="inlineStr">
@@ -7944,7 +7944,7 @@
       </c>
       <c r="L140" s="5" t="n"/>
       <c r="M140" s="7" t="n">
-        <v>23.32</v>
+        <v>26.18</v>
       </c>
     </row>
     <row r="141">
@@ -7955,7 +7955,7 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955502 - KIT4M05563502GJS</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020650162 - KIT4M05413837SMB</t>
         </is>
       </c>
       <c r="C141" s="3" t="n">
@@ -7966,12 +7966,12 @@
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563502GJS</t>
+          <t>KIT4M05413837SMB</t>
         </is>
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>814470</t>
+          <t>810100</t>
         </is>
       </c>
       <c r="G141" s="5" t="inlineStr">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="L141" s="5" t="n"/>
       <c r="M141" s="7" t="n">
-        <v>23.23</v>
+        <v>25.34</v>
       </c>
     </row>
     <row r="142">
@@ -8008,7 +8008,7 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 -  Los Angeles CA - 020649512 - KIT4M054138318Q7</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649362 - KIT4M05368336DBC</t>
         </is>
       </c>
       <c r="C142" s="3" t="n">
@@ -8019,12 +8019,12 @@
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138318Q7</t>
+          <t>KIT4M05368336DBC</t>
         </is>
       </c>
       <c r="F142" s="4" t="inlineStr">
         <is>
-          <t>812814</t>
+          <t>810831</t>
         </is>
       </c>
       <c r="G142" s="5" t="inlineStr">
@@ -8050,7 +8050,7 @@
       </c>
       <c r="L142" s="5" t="n"/>
       <c r="M142" s="7" t="n">
-        <v>22.97</v>
+        <v>25.14</v>
       </c>
     </row>
     <row r="143">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 021438232 - KIT4M05872520QJM</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955212 - KIT4M05563512GBQ</t>
         </is>
       </c>
       <c r="C143" s="3" t="n">
@@ -8072,12 +8072,12 @@
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872520QJM</t>
+          <t>KIT4M05563512GBQ</t>
         </is>
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>816078</t>
+          <t>814435</t>
         </is>
       </c>
       <c r="G143" s="5" t="inlineStr">
@@ -8103,7 +8103,7 @@
       </c>
       <c r="L143" s="5" t="n"/>
       <c r="M143" s="7" t="n">
-        <v>22.38</v>
+        <v>24.55</v>
       </c>
     </row>
     <row r="144">
@@ -8114,7 +8114,7 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955712 - KIT4M05563586ZTR</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438242 - KIT4M058725094XP</t>
         </is>
       </c>
       <c r="C144" s="3" t="n">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563586ZTR</t>
+          <t>KIT4M058725094XP</t>
         </is>
       </c>
       <c r="F144" s="4" t="inlineStr">
         <is>
-          <t>814445</t>
+          <t>816085</t>
         </is>
       </c>
       <c r="G144" s="5" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="L144" s="5" t="n"/>
       <c r="M144" s="7" t="n">
-        <v>21.92</v>
+        <v>24.02</v>
       </c>
     </row>
     <row r="145">
@@ -8167,7 +8167,7 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020650242 - KIT4M05413804SKS</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955532 - KIT4M05563548P9Q</t>
         </is>
       </c>
       <c r="C145" s="3" t="n">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413804SKS</t>
+          <t>KIT4M05563548P9Q</t>
         </is>
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>810102</t>
+          <t>814468</t>
         </is>
       </c>
       <c r="G145" s="5" t="inlineStr">
@@ -8209,7 +8209,7 @@
       </c>
       <c r="L145" s="5" t="n"/>
       <c r="M145" s="7" t="n">
-        <v>21.85</v>
+        <v>22.94</v>
       </c>
     </row>
     <row r="146">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020650132-KIT4M05413828PCT</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438222 - KIT4M058725299QP</t>
         </is>
       </c>
       <c r="C146" s="3" t="n">
@@ -8231,12 +8231,12 @@
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413828PCT</t>
+          <t>KIT4M058725299QP</t>
         </is>
       </c>
       <c r="F146" s="4" t="inlineStr">
         <is>
-          <t>812799</t>
+          <t>816080</t>
         </is>
       </c>
       <c r="G146" s="5" t="inlineStr">
@@ -8262,7 +8262,7 @@
       </c>
       <c r="L146" s="5" t="n"/>
       <c r="M146" s="7" t="n">
-        <v>21.54</v>
+        <v>22.94</v>
       </c>
     </row>
     <row r="147">
@@ -8273,7 +8273,7 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-LOS ANGELES CA-020955172-KIT4M05563526WNC</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020650242 - KIT4M05413804SKS</t>
         </is>
       </c>
       <c r="C147" s="3" t="n">
@@ -8284,12 +8284,12 @@
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563526WNC</t>
+          <t>KIT4M05413804SKS</t>
         </is>
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>814463</t>
+          <t>810102</t>
         </is>
       </c>
       <c r="G147" s="5" t="inlineStr">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="L147" s="5" t="n"/>
       <c r="M147" s="7" t="n">
-        <v>21.16</v>
+        <v>22.63</v>
       </c>
     </row>
     <row r="148">
@@ -8326,7 +8326,7 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020650072-KIT4M054137987GJ</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649592 - KIT4M05413787HHK</t>
         </is>
       </c>
       <c r="C148" s="3" t="n">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137987GJ</t>
+          <t>KIT4M05413787HHK</t>
         </is>
       </c>
       <c r="F148" s="4" t="inlineStr">
         <is>
-          <t>812795</t>
+          <t>812809</t>
         </is>
       </c>
       <c r="G148" s="5" t="inlineStr">
@@ -8368,7 +8368,7 @@
       </c>
       <c r="L148" s="5" t="n"/>
       <c r="M148" s="7" t="n">
-        <v>20.74</v>
+        <v>21.73</v>
       </c>
     </row>
     <row r="149">
@@ -8379,7 +8379,7 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955532 - KIT4M05563548P9Q</t>
+          <t>SMRT-05900510-Los Angeles CA-020650132-KIT4M05413828PCT</t>
         </is>
       </c>
       <c r="C149" s="3" t="n">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563548P9Q</t>
+          <t>KIT4M05413828PCT</t>
         </is>
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>814468</t>
+          <t>812799</t>
         </is>
       </c>
       <c r="G149" s="5" t="inlineStr">
@@ -8421,7 +8421,7 @@
       </c>
       <c r="L149" s="5" t="n"/>
       <c r="M149" s="7" t="n">
-        <v>20.73</v>
+        <v>21.54</v>
       </c>
     </row>
     <row r="150">
@@ -8432,7 +8432,7 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649222 - KIT4P00065640BFW</t>
+          <t>SMRT-05900510-LOS ANGELES CA-020955172-KIT4M05563526WNC</t>
         </is>
       </c>
       <c r="C150" s="3" t="n">
@@ -8443,17 +8443,17 @@
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065640BFW</t>
+          <t>KIT4M05563526WNC</t>
         </is>
       </c>
       <c r="F150" s="4" t="inlineStr">
         <is>
-          <t>812929</t>
+          <t>814463</t>
         </is>
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="L150" s="5" t="n"/>
       <c r="M150" s="7" t="n">
-        <v>19.87</v>
+        <v>21.16</v>
       </c>
     </row>
     <row r="151">
@@ -8485,7 +8485,7 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649912 - KIT4M05413836KJC</t>
+          <t>SMRT-05900510-Los Angeles CA-020650072-KIT4M054137987GJ</t>
         </is>
       </c>
       <c r="C151" s="3" t="n">
@@ -8496,12 +8496,12 @@
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413836KJC</t>
+          <t>KIT4M054137987GJ</t>
         </is>
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>810097</t>
+          <t>812795</t>
         </is>
       </c>
       <c r="G151" s="5" t="inlineStr">
@@ -8527,7 +8527,7 @@
       </c>
       <c r="L151" s="5" t="n"/>
       <c r="M151" s="7" t="n">
-        <v>19.73</v>
+        <v>20.74</v>
       </c>
     </row>
     <row r="152">
@@ -8538,7 +8538,7 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649302 - KIT4M05368226W57</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438072 - KIT4M057996885ZV</t>
         </is>
       </c>
       <c r="C152" s="3" t="n">
@@ -8549,12 +8549,12 @@
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368226W57</t>
+          <t>KIT4M057996885ZV</t>
         </is>
       </c>
       <c r="F152" s="4" t="inlineStr">
         <is>
-          <t>810833</t>
+          <t>816269</t>
         </is>
       </c>
       <c r="G152" s="5" t="inlineStr">
@@ -8580,7 +8580,7 @@
       </c>
       <c r="L152" s="5" t="n"/>
       <c r="M152" s="7" t="n">
-        <v>19.62</v>
+        <v>20.55</v>
       </c>
     </row>
     <row r="153">
@@ -8591,7 +8591,7 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955302 - KIT4M055635158PC</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649222 - KIT4P00065640BFW</t>
         </is>
       </c>
       <c r="C153" s="3" t="n">
@@ -8602,17 +8602,17 @@
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635158PC</t>
+          <t>KIT4P00065640BFW</t>
         </is>
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>814457</t>
+          <t>812929</t>
         </is>
       </c>
       <c r="G153" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H153" s="5" t="inlineStr">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="L153" s="5" t="n"/>
       <c r="M153" s="7" t="n">
-        <v>19.59</v>
+        <v>19.87</v>
       </c>
     </row>
     <row r="154">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955282 - KIT4M055635227ZR</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649912 - KIT4M05413836KJC</t>
         </is>
       </c>
       <c r="C154" s="3" t="n">
@@ -8655,12 +8655,12 @@
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635227ZR</t>
+          <t>KIT4M05413836KJC</t>
         </is>
       </c>
       <c r="F154" s="4" t="inlineStr">
         <is>
-          <t>814482</t>
+          <t>810097</t>
         </is>
       </c>
       <c r="G154" s="5" t="inlineStr">
@@ -8686,7 +8686,7 @@
       </c>
       <c r="L154" s="5" t="n"/>
       <c r="M154" s="7" t="n">
-        <v>19.17</v>
+        <v>19.73</v>
       </c>
     </row>
     <row r="155">
@@ -8697,7 +8697,7 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA  - 020649722 - KIT4M04604747TPT</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649302 - KIT4M05368226W57</t>
         </is>
       </c>
       <c r="C155" s="3" t="n">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604747TPT</t>
+          <t>KIT4M05368226W57</t>
         </is>
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>809873</t>
+          <t>810833</t>
         </is>
       </c>
       <c r="G155" s="5" t="inlineStr">
@@ -8739,7 +8739,7 @@
       </c>
       <c r="L155" s="5" t="n"/>
       <c r="M155" s="7" t="n">
-        <v>18.44</v>
+        <v>19.62</v>
       </c>
     </row>
     <row r="156">
@@ -8750,7 +8750,7 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438072 - KIT4M057996885ZV</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955302 - KIT4M055635158PC</t>
         </is>
       </c>
       <c r="C156" s="3" t="n">
@@ -8761,12 +8761,12 @@
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>KIT4M057996885ZV</t>
+          <t>KIT4M055635158PC</t>
         </is>
       </c>
       <c r="F156" s="4" t="inlineStr">
         <is>
-          <t>816269</t>
+          <t>814457</t>
         </is>
       </c>
       <c r="G156" s="5" t="inlineStr">
@@ -8792,7 +8792,7 @@
       </c>
       <c r="L156" s="5" t="n"/>
       <c r="M156" s="7" t="n">
-        <v>17.89</v>
+        <v>19.59</v>
       </c>
     </row>
     <row r="157">
@@ -8803,7 +8803,7 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438222 - KIT4M058725299QP</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955282 - KIT4M055635227ZR</t>
         </is>
       </c>
       <c r="C157" s="3" t="n">
@@ -8814,12 +8814,12 @@
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725299QP</t>
+          <t>KIT4M055635227ZR</t>
         </is>
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>816080</t>
+          <t>814482</t>
         </is>
       </c>
       <c r="G157" s="5" t="inlineStr">
@@ -8845,7 +8845,7 @@
       </c>
       <c r="L157" s="5" t="n"/>
       <c r="M157" s="7" t="n">
-        <v>17.5</v>
+        <v>19.17</v>
       </c>
     </row>
     <row r="158">
@@ -8898,7 +8898,7 @@
       </c>
       <c r="L158" s="5" t="n"/>
       <c r="M158" s="7" t="n">
-        <v>17.29</v>
+        <v>18.54</v>
       </c>
     </row>
     <row r="159">
@@ -8909,7 +8909,7 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649632 - KIT4M054138064J9</t>
+          <t>SS - 05900510 - Los Angeles, CA  - 020649722 - KIT4M04604747TPT</t>
         </is>
       </c>
       <c r="C159" s="3" t="n">
@@ -8920,12 +8920,12 @@
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138064J9</t>
+          <t>KIT4M04604747TPT</t>
         </is>
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>812844</t>
+          <t>809873</t>
         </is>
       </c>
       <c r="G159" s="5" t="inlineStr">
@@ -8951,7 +8951,7 @@
       </c>
       <c r="L159" s="5" t="n"/>
       <c r="M159" s="7" t="n">
-        <v>17.18</v>
+        <v>18.44</v>
       </c>
     </row>
     <row r="160">
@@ -8962,7 +8962,7 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955642 - KIT4M05563573WKC</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020650262 - KIT4M054138249M8</t>
         </is>
       </c>
       <c r="C160" s="3" t="n">
@@ -8973,12 +8973,12 @@
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563573WKC</t>
+          <t>KIT4M054138249M8</t>
         </is>
       </c>
       <c r="F160" s="4" t="inlineStr">
         <is>
-          <t>814488</t>
+          <t>812794</t>
         </is>
       </c>
       <c r="G160" s="5" t="inlineStr">
@@ -9004,7 +9004,7 @@
       </c>
       <c r="L160" s="5" t="n"/>
       <c r="M160" s="7" t="n">
-        <v>15.92</v>
+        <v>17.75</v>
       </c>
     </row>
     <row r="161">
@@ -9015,7 +9015,7 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649592 - KIT4M05413787HHK</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649492 - KIT4M054138074NS</t>
         </is>
       </c>
       <c r="C161" s="3" t="n">
@@ -9026,12 +9026,12 @@
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413787HHK</t>
+          <t>KIT4M054138074NS</t>
         </is>
       </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
-          <t>812809</t>
+          <t>812816</t>
         </is>
       </c>
       <c r="G161" s="5" t="inlineStr">
@@ -9057,7 +9057,7 @@
       </c>
       <c r="L161" s="5" t="n"/>
       <c r="M161" s="7" t="n">
-        <v>15.86</v>
+        <v>17.3</v>
       </c>
     </row>
     <row r="162">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482708 - KIT4M04604736T7C</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827010 - KIT4M046047372KJ</t>
         </is>
       </c>
       <c r="C162" s="3" t="n">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604736T7C</t>
+          <t>KIT4M046047372KJ</t>
         </is>
       </c>
       <c r="F162" s="4" t="inlineStr">
         <is>
-          <t>809662</t>
+          <t>809658</t>
         </is>
       </c>
       <c r="G162" s="5" t="inlineStr">
@@ -9110,7 +9110,7 @@
       </c>
       <c r="L162" s="5" t="n"/>
       <c r="M162" s="7" t="n">
-        <v>15.7</v>
+        <v>17.27</v>
       </c>
     </row>
     <row r="163">
@@ -9121,7 +9121,7 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955362 - KIT4M05563528MKX</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649632 - KIT4M054138064J9</t>
         </is>
       </c>
       <c r="C163" s="3" t="n">
@@ -9132,12 +9132,12 @@
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563528MKX</t>
+          <t>KIT4M054138064J9</t>
         </is>
       </c>
       <c r="F163" s="4" t="inlineStr">
         <is>
-          <t>814471</t>
+          <t>812844</t>
         </is>
       </c>
       <c r="G163" s="5" t="inlineStr">
@@ -9163,7 +9163,7 @@
       </c>
       <c r="L163" s="5" t="n"/>
       <c r="M163" s="7" t="n">
-        <v>15.05</v>
+        <v>17.18</v>
       </c>
     </row>
     <row r="164">
@@ -9174,7 +9174,7 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - CW6642812 - KIT4M054138292ZP</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482708 - KIT4M04604736T7C</t>
         </is>
       </c>
       <c r="C164" s="3" t="n">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138292ZP</t>
+          <t>KIT4M04604736T7C</t>
         </is>
       </c>
       <c r="F164" s="4" t="inlineStr">
         <is>
-          <t>812784</t>
+          <t>809662</t>
         </is>
       </c>
       <c r="G164" s="5" t="inlineStr">
@@ -9216,7 +9216,7 @@
       </c>
       <c r="L164" s="5" t="n"/>
       <c r="M164" s="7" t="n">
-        <v>14.46</v>
+        <v>16.93</v>
       </c>
     </row>
     <row r="165">
@@ -9227,7 +9227,7 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020649862 - KIT4M04475159PMD</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955642 - KIT4M05563573WKC</t>
         </is>
       </c>
       <c r="C165" s="3" t="n">
@@ -9238,12 +9238,12 @@
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475159PMD</t>
+          <t>KIT4M05563573WKC</t>
         </is>
       </c>
       <c r="F165" s="4" t="inlineStr">
         <is>
-          <t>809868</t>
+          <t>814488</t>
         </is>
       </c>
       <c r="G165" s="5" t="inlineStr">
@@ -9269,7 +9269,7 @@
       </c>
       <c r="L165" s="5" t="n"/>
       <c r="M165" s="7" t="n">
-        <v>14.45</v>
+        <v>16.33</v>
       </c>
     </row>
     <row r="166">
@@ -9280,7 +9280,7 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020650262 - KIT4M054138249M8</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955362 - KIT4M05563528MKX</t>
         </is>
       </c>
       <c r="C166" s="3" t="n">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138249M8</t>
+          <t>KIT4M05563528MKX</t>
         </is>
       </c>
       <c r="F166" s="4" t="inlineStr">
         <is>
-          <t>812794</t>
+          <t>814471</t>
         </is>
       </c>
       <c r="G166" s="5" t="inlineStr">
@@ -9322,7 +9322,7 @@
       </c>
       <c r="L166" s="5" t="n"/>
       <c r="M166" s="7" t="n">
-        <v>14.28</v>
+        <v>16.23</v>
       </c>
     </row>
     <row r="167">
@@ -9333,7 +9333,7 @@
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955402 - KIT4M05563610HM2</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955252 - KIT4M05563584FVC</t>
         </is>
       </c>
       <c r="C167" s="3" t="n">
@@ -9344,12 +9344,12 @@
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563610HM2</t>
+          <t>KIT4M05563584FVC</t>
         </is>
       </c>
       <c r="F167" s="4" t="inlineStr">
         <is>
-          <t>814486</t>
+          <t>814439</t>
         </is>
       </c>
       <c r="G167" s="5" t="inlineStr">
@@ -9375,7 +9375,7 @@
       </c>
       <c r="L167" s="5" t="n"/>
       <c r="M167" s="7" t="n">
-        <v>14.14</v>
+        <v>15.44</v>
       </c>
     </row>
     <row r="168">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955482 - KIT4M055635088NK</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020649252 - KIT4P00066848VQM</t>
         </is>
       </c>
       <c r="C168" s="3" t="n">
@@ -9397,17 +9397,17 @@
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635088NK</t>
+          <t>KIT4P00066848VQM</t>
         </is>
       </c>
       <c r="F168" s="4" t="inlineStr">
         <is>
-          <t>814434</t>
+          <t>812923</t>
         </is>
       </c>
       <c r="G168" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H168" s="5" t="inlineStr">
@@ -9428,7 +9428,7 @@
       </c>
       <c r="L168" s="5" t="n"/>
       <c r="M168" s="7" t="n">
-        <v>14.13</v>
+        <v>14.84</v>
       </c>
     </row>
     <row r="169">
@@ -9439,7 +9439,7 @@
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955252 - KIT4M05563584FVC</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955482 - KIT4M055635088NK</t>
         </is>
       </c>
       <c r="C169" s="3" t="n">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563584FVC</t>
+          <t>KIT4M055635088NK</t>
         </is>
       </c>
       <c r="F169" s="4" t="inlineStr">
         <is>
-          <t>814439</t>
+          <t>814434</t>
         </is>
       </c>
       <c r="G169" s="5" t="inlineStr">
@@ -9481,7 +9481,7 @@
       </c>
       <c r="L169" s="5" t="n"/>
       <c r="M169" s="7" t="n">
-        <v>13.9</v>
+        <v>14.62</v>
       </c>
     </row>
     <row r="170">
@@ -9492,7 +9492,7 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649492 - KIT4M054138074NS</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955152 - KIT4M05563514P8T</t>
         </is>
       </c>
       <c r="C170" s="3" t="n">
@@ -9503,12 +9503,12 @@
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138074NS</t>
+          <t>KIT4M05563514P8T</t>
         </is>
       </c>
       <c r="F170" s="4" t="inlineStr">
         <is>
-          <t>812816</t>
+          <t>814436</t>
         </is>
       </c>
       <c r="G170" s="5" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="L170" s="5" t="n"/>
       <c r="M170" s="7" t="n">
-        <v>13.83</v>
+        <v>14.62</v>
       </c>
     </row>
     <row r="171">
@@ -9545,7 +9545,7 @@
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827010 - KIT4M046047372KJ</t>
+          <t>SMA - 05900510 - Los Angeles CA - CW6642812 - KIT4M054138292ZP</t>
         </is>
       </c>
       <c r="C171" s="3" t="n">
@@ -9556,12 +9556,12 @@
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047372KJ</t>
+          <t>KIT4M054138292ZP</t>
         </is>
       </c>
       <c r="F171" s="4" t="inlineStr">
         <is>
-          <t>809658</t>
+          <t>812784</t>
         </is>
       </c>
       <c r="G171" s="5" t="inlineStr">
@@ -9587,7 +9587,7 @@
       </c>
       <c r="L171" s="5" t="n"/>
       <c r="M171" s="7" t="n">
-        <v>13.65</v>
+        <v>14.46</v>
       </c>
     </row>
     <row r="172">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649442 - KIT4M054137885SM</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020649862 - KIT4M04475159PMD</t>
         </is>
       </c>
       <c r="C172" s="3" t="n">
@@ -9609,12 +9609,12 @@
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137885SM</t>
+          <t>KIT4M04475159PMD</t>
         </is>
       </c>
       <c r="F172" s="4" t="inlineStr">
         <is>
-          <t>812846</t>
+          <t>809868</t>
         </is>
       </c>
       <c r="G172" s="5" t="inlineStr">
@@ -9640,7 +9640,7 @@
       </c>
       <c r="L172" s="5" t="n"/>
       <c r="M172" s="7" t="n">
-        <v>13.24</v>
+        <v>14.45</v>
       </c>
     </row>
     <row r="173">
@@ -9651,7 +9651,7 @@
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955152 - KIT4M05563514P8T</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020650152 - KIT4M054138189C7</t>
         </is>
       </c>
       <c r="C173" s="3" t="n">
@@ -9662,12 +9662,12 @@
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563514P8T</t>
+          <t>KIT4M054138189C7</t>
         </is>
       </c>
       <c r="F173" s="4" t="inlineStr">
         <is>
-          <t>814436</t>
+          <t>812831</t>
         </is>
       </c>
       <c r="G173" s="5" t="inlineStr">
@@ -9693,7 +9693,7 @@
       </c>
       <c r="L173" s="5" t="n"/>
       <c r="M173" s="7" t="n">
-        <v>13.22</v>
+        <v>14.32</v>
       </c>
     </row>
     <row r="174">
@@ -9704,7 +9704,7 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020955432 - KIT4M05563533M9N</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955402 - KIT4M05563610HM2</t>
         </is>
       </c>
       <c r="C174" s="3" t="n">
@@ -9715,12 +9715,12 @@
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563533M9N</t>
+          <t>KIT4M05563610HM2</t>
         </is>
       </c>
       <c r="F174" s="4" t="inlineStr">
         <is>
-          <t>814485</t>
+          <t>814486</t>
         </is>
       </c>
       <c r="G174" s="5" t="inlineStr">
@@ -9746,7 +9746,7 @@
       </c>
       <c r="L174" s="5" t="n"/>
       <c r="M174" s="7" t="n">
-        <v>11.92</v>
+        <v>14.14</v>
       </c>
     </row>
     <row r="175">
@@ -9757,7 +9757,7 @@
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649282 - KIT4M05368213974</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270110 - KIT4M038677586ZX</t>
         </is>
       </c>
       <c r="C175" s="3" t="n">
@@ -9768,12 +9768,12 @@
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368213974</t>
+          <t>KIT4M038677586ZX</t>
         </is>
       </c>
       <c r="F175" s="4" t="inlineStr">
         <is>
-          <t>810647</t>
+          <t>809623</t>
         </is>
       </c>
       <c r="G175" s="5" t="inlineStr">
@@ -9799,7 +9799,7 @@
       </c>
       <c r="L175" s="5" t="n"/>
       <c r="M175" s="7" t="n">
-        <v>11.47</v>
+        <v>13.86</v>
       </c>
     </row>
     <row r="176">
@@ -9810,7 +9810,7 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020650152 - KIT4M054138189C7</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649442 - KIT4M054137885SM</t>
         </is>
       </c>
       <c r="C176" s="3" t="n">
@@ -9821,12 +9821,12 @@
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138189C7</t>
+          <t>KIT4M054137885SM</t>
         </is>
       </c>
       <c r="F176" s="4" t="inlineStr">
         <is>
-          <t>812831</t>
+          <t>812846</t>
         </is>
       </c>
       <c r="G176" s="5" t="inlineStr">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="L176" s="5" t="n"/>
       <c r="M176" s="7" t="n">
-        <v>11.19</v>
+        <v>13.24</v>
       </c>
     </row>
     <row r="177">
@@ -9863,7 +9863,7 @@
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 020955242 - KIT4M05563511FF4</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020955432 - KIT4M05563533M9N</t>
         </is>
       </c>
       <c r="C177" s="3" t="n">
@@ -9874,12 +9874,12 @@
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563511FF4</t>
+          <t>KIT4M05563533M9N</t>
         </is>
       </c>
       <c r="F177" s="4" t="inlineStr">
         <is>
-          <t>814437</t>
+          <t>814485</t>
         </is>
       </c>
       <c r="G177" s="5" t="inlineStr">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="L177" s="5" t="n"/>
       <c r="M177" s="7" t="n">
-        <v>10.96</v>
+        <v>12.94</v>
       </c>
     </row>
     <row r="178">
@@ -9916,7 +9916,7 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020650122-KIT4M05413776H84</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649282 - KIT4M05368213974</t>
         </is>
       </c>
       <c r="C178" s="3" t="n">
@@ -9927,12 +9927,12 @@
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413776H84</t>
+          <t>KIT4M05368213974</t>
         </is>
       </c>
       <c r="F178" s="4" t="inlineStr">
         <is>
-          <t>810101</t>
+          <t>810647</t>
         </is>
       </c>
       <c r="G178" s="5" t="inlineStr">
@@ -9958,7 +9958,7 @@
       </c>
       <c r="L178" s="5" t="n"/>
       <c r="M178" s="7" t="n">
-        <v>10.94</v>
+        <v>12.89</v>
       </c>
     </row>
     <row r="179">
@@ -9969,7 +9969,7 @@
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649582 - KIT4M05413774JZX</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270114 - KIT4M04476539RJ5</t>
         </is>
       </c>
       <c r="C179" s="3" t="n">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413774JZX</t>
+          <t>KIT4M04476539RJ5</t>
         </is>
       </c>
       <c r="F179" s="4" t="inlineStr">
         <is>
-          <t>812836</t>
+          <t>809612</t>
         </is>
       </c>
       <c r="G179" s="5" t="inlineStr">
@@ -10011,7 +10011,7 @@
       </c>
       <c r="L179" s="5" t="n"/>
       <c r="M179" s="7" t="n">
-        <v>10.46</v>
+        <v>11.32</v>
       </c>
     </row>
     <row r="180">
@@ -10022,7 +10022,7 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955612 - KIT4M0556355588P</t>
+          <t>SMRT-05900510-Los Angeles CA-020650122-KIT4M05413776H84</t>
         </is>
       </c>
       <c r="C180" s="3" t="n">
@@ -10033,12 +10033,12 @@
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0556355588P</t>
+          <t>KIT4M05413776H84</t>
         </is>
       </c>
       <c r="F180" s="4" t="inlineStr">
         <is>
-          <t>814455</t>
+          <t>810101</t>
         </is>
       </c>
       <c r="G180" s="5" t="inlineStr">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="L180" s="5" t="n"/>
       <c r="M180" s="7" t="n">
-        <v>9.140000000000001</v>
+        <v>11.05</v>
       </c>
     </row>
     <row r="181">
@@ -10075,7 +10075,7 @@
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020649252 - KIT4P00066848VQM</t>
+          <t>SS - 05900510 -  Los Angeles CA - 020955242 - KIT4M05563511FF4</t>
         </is>
       </c>
       <c r="C181" s="3" t="n">
@@ -10086,17 +10086,17 @@
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00066848VQM</t>
+          <t>KIT4M05563511FF4</t>
         </is>
       </c>
       <c r="F181" s="4" t="inlineStr">
         <is>
-          <t>812923</t>
+          <t>814437</t>
         </is>
       </c>
       <c r="G181" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H181" s="5" t="inlineStr">
@@ -10117,7 +10117,7 @@
       </c>
       <c r="L181" s="5" t="n"/>
       <c r="M181" s="7" t="n">
-        <v>8.93</v>
+        <v>10.96</v>
       </c>
     </row>
     <row r="182">
@@ -10128,7 +10128,7 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270114 - KIT4M04476539RJ5</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437552 - KIT4M05872586VCH</t>
         </is>
       </c>
       <c r="C182" s="3" t="n">
@@ -10139,12 +10139,12 @@
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04476539RJ5</t>
+          <t>KIT4M05872586VCH</t>
         </is>
       </c>
       <c r="F182" s="4" t="inlineStr">
         <is>
-          <t>809612</t>
+          <t>816068</t>
         </is>
       </c>
       <c r="G182" s="5" t="inlineStr">
@@ -10170,7 +10170,7 @@
       </c>
       <c r="L182" s="5" t="n"/>
       <c r="M182" s="7" t="n">
-        <v>7.65</v>
+        <v>10.46</v>
       </c>
     </row>
     <row r="183">
@@ -10181,7 +10181,7 @@
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649962 - KIT4M05413783PFQ</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649582 - KIT4M05413774JZX</t>
         </is>
       </c>
       <c r="C183" s="3" t="n">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413783PFQ</t>
+          <t>KIT4M05413774JZX</t>
         </is>
       </c>
       <c r="F183" s="4" t="inlineStr">
         <is>
-          <t>812845</t>
+          <t>812836</t>
         </is>
       </c>
       <c r="G183" s="5" t="inlineStr">
@@ -10223,7 +10223,7 @@
       </c>
       <c r="L183" s="5" t="n"/>
       <c r="M183" s="7" t="n">
-        <v>7.24</v>
+        <v>10.46</v>
       </c>
     </row>
     <row r="184">
@@ -10234,7 +10234,7 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649792 - KIT4M04475151HTP</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437932 - KIT4M05799732NQK</t>
         </is>
       </c>
       <c r="C184" s="3" t="n">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475151HTP</t>
+          <t>KIT4M05799732NQK</t>
         </is>
       </c>
       <c r="F184" s="4" t="inlineStr">
         <is>
-          <t>809867</t>
+          <t>816275</t>
         </is>
       </c>
       <c r="G184" s="5" t="inlineStr">
@@ -10276,7 +10276,7 @@
       </c>
       <c r="L184" s="5" t="n"/>
       <c r="M184" s="7" t="n">
-        <v>7.08</v>
+        <v>10.29</v>
       </c>
     </row>
     <row r="185">
@@ -10287,7 +10287,7 @@
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles, CA - 0204827011114 - KIT4M03986267RWH</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955612 - KIT4M0556355588P</t>
         </is>
       </c>
       <c r="C185" s="3" t="n">
@@ -10298,12 +10298,12 @@
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03986267RWH</t>
+          <t>KIT4M0556355588P</t>
         </is>
       </c>
       <c r="F185" s="4" t="inlineStr">
         <is>
-          <t>809616</t>
+          <t>814455</t>
         </is>
       </c>
       <c r="G185" s="5" t="inlineStr">
@@ -10329,7 +10329,7 @@
       </c>
       <c r="L185" s="5" t="n"/>
       <c r="M185" s="7" t="n">
-        <v>6.68</v>
+        <v>9.140000000000001</v>
       </c>
     </row>
     <row r="186">
@@ -10340,7 +10340,7 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649642 - KIT4M05413826Z6Z</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649962 - KIT4M05413783PFQ</t>
         </is>
       </c>
       <c r="C186" s="3" t="n">
@@ -10351,12 +10351,12 @@
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413826Z6Z</t>
+          <t>KIT4M05413783PFQ</t>
         </is>
       </c>
       <c r="F186" s="4" t="inlineStr">
         <is>
-          <t>812804</t>
+          <t>812845</t>
         </is>
       </c>
       <c r="G186" s="5" t="inlineStr">
@@ -10382,7 +10382,7 @@
       </c>
       <c r="L186" s="5" t="n"/>
       <c r="M186" s="7" t="n">
-        <v>5.9</v>
+        <v>7.46</v>
       </c>
     </row>
     <row r="187">
@@ -10393,7 +10393,7 @@
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827011110 - KIT4M03866627GHD</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437402 - KIT4M05872537SGZ</t>
         </is>
       </c>
       <c r="C187" s="3" t="n">
@@ -10404,12 +10404,12 @@
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03866627GHD</t>
+          <t>KIT4M05872537SGZ</t>
         </is>
       </c>
       <c r="F187" s="4" t="inlineStr">
         <is>
-          <t>809619</t>
+          <t>816073</t>
         </is>
       </c>
       <c r="G187" s="5" t="inlineStr">
@@ -10435,7 +10435,7 @@
       </c>
       <c r="L187" s="5" t="n"/>
       <c r="M187" s="7" t="n">
-        <v>5.78</v>
+        <v>7.42</v>
       </c>
     </row>
     <row r="188">
@@ -10446,7 +10446,7 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649732 - KIT4M046047467T4</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649792 - KIT4M04475151HTP</t>
         </is>
       </c>
       <c r="C188" s="3" t="n">
@@ -10457,12 +10457,12 @@
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047467T4</t>
+          <t>KIT4M04475151HTP</t>
         </is>
       </c>
       <c r="F188" s="4" t="inlineStr">
         <is>
-          <t>809865</t>
+          <t>809867</t>
         </is>
       </c>
       <c r="G188" s="5" t="inlineStr">
@@ -10488,7 +10488,7 @@
       </c>
       <c r="L188" s="5" t="n"/>
       <c r="M188" s="7" t="n">
-        <v>5.64</v>
+        <v>7.08</v>
       </c>
     </row>
     <row r="189">
@@ -10499,7 +10499,7 @@
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270110 - KIT4M038677586ZX</t>
+          <t>STS - 05900510 - Los Angeles, CA - 0204827011114 - KIT4M03986267RWH</t>
         </is>
       </c>
       <c r="C189" s="3" t="n">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>KIT4M038677586ZX</t>
+          <t>KIT4M03986267RWH</t>
         </is>
       </c>
       <c r="F189" s="4" t="inlineStr">
         <is>
-          <t>809623</t>
+          <t>809616</t>
         </is>
       </c>
       <c r="G189" s="5" t="inlineStr">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="L189" s="5" t="n"/>
       <c r="M189" s="7" t="n">
-        <v>5.59</v>
+        <v>6.86</v>
       </c>
     </row>
     <row r="190">
@@ -10552,7 +10552,7 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020650182 - KIT4M05413821GGW</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437592 - KIT4M05872582TC7</t>
         </is>
       </c>
       <c r="C190" s="3" t="n">
@@ -10563,12 +10563,12 @@
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413821GGW</t>
+          <t>KIT4M05872582TC7</t>
         </is>
       </c>
       <c r="F190" s="4" t="inlineStr">
         <is>
-          <t>812830</t>
+          <t>816107</t>
         </is>
       </c>
       <c r="G190" s="5" t="inlineStr">
@@ -10594,7 +10594,7 @@
       </c>
       <c r="L190" s="5" t="n"/>
       <c r="M190" s="7" t="n">
-        <v>5.51</v>
+        <v>6.51</v>
       </c>
     </row>
     <row r="191">
@@ -10647,7 +10647,7 @@
       </c>
       <c r="L191" s="5" t="n"/>
       <c r="M191" s="7" t="n">
-        <v>5.24</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="192">
@@ -10658,7 +10658,7 @@
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437582 - KIT4M05872573K7P</t>
+          <t>SSC - 05900510 -  Los Angeles CA - 021437862 - KIT4M05872516CJM</t>
         </is>
       </c>
       <c r="C192" s="3" t="n">
@@ -10669,12 +10669,12 @@
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872573K7P</t>
+          <t>KIT4M05872516CJM</t>
         </is>
       </c>
       <c r="F192" s="4" t="inlineStr">
         <is>
-          <t>816067</t>
+          <t>816087</t>
         </is>
       </c>
       <c r="G192" s="5" t="inlineStr">
@@ -10700,7 +10700,7 @@
       </c>
       <c r="L192" s="5" t="n"/>
       <c r="M192" s="7" t="n">
-        <v>4.28</v>
+        <v>6.14</v>
       </c>
     </row>
     <row r="193">
@@ -10711,7 +10711,7 @@
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437592 - KIT4M05872582TC7</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438262 - KIT4M05872530RPF</t>
         </is>
       </c>
       <c r="C193" s="3" t="n">
@@ -10722,12 +10722,12 @@
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872582TC7</t>
+          <t>KIT4M05872530RPF</t>
         </is>
       </c>
       <c r="F193" s="4" t="inlineStr">
         <is>
-          <t>816107</t>
+          <t>816079</t>
         </is>
       </c>
       <c r="G193" s="5" t="inlineStr">
@@ -10753,7 +10753,7 @@
       </c>
       <c r="L193" s="5" t="n"/>
       <c r="M193" s="7" t="n">
-        <v>3.27</v>
+        <v>6.07</v>
       </c>
     </row>
     <row r="194">
@@ -10764,7 +10764,7 @@
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437402 - KIT4M05872537SGZ</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649732 - KIT4M046047467T4</t>
         </is>
       </c>
       <c r="C194" s="3" t="n">
@@ -10775,12 +10775,12 @@
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872537SGZ</t>
+          <t>KIT4M046047467T4</t>
         </is>
       </c>
       <c r="F194" s="4" t="inlineStr">
         <is>
-          <t>816073</t>
+          <t>809865</t>
         </is>
       </c>
       <c r="G194" s="5" t="inlineStr">
@@ -10806,7 +10806,7 @@
       </c>
       <c r="L194" s="5" t="n"/>
       <c r="M194" s="7" t="n">
-        <v>3.2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="195">
@@ -10817,7 +10817,7 @@
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649752 - KIT4M03867749CW5</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649642 - KIT4M05413826Z6Z</t>
         </is>
       </c>
       <c r="C195" s="3" t="n">
@@ -10828,12 +10828,12 @@
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03867749CW5</t>
+          <t>KIT4M05413826Z6Z</t>
         </is>
       </c>
       <c r="F195" s="4" t="inlineStr">
         <is>
-          <t>809877</t>
+          <t>812804</t>
         </is>
       </c>
       <c r="G195" s="5" t="inlineStr">
@@ -10859,7 +10859,7 @@
       </c>
       <c r="L195" s="5" t="n"/>
       <c r="M195" s="7" t="n">
-        <v>2.96</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="196">
@@ -10912,7 +10912,7 @@
       </c>
       <c r="L196" s="5" t="n"/>
       <c r="M196" s="7" t="n">
-        <v>2.76</v>
+        <v>5.85</v>
       </c>
     </row>
     <row r="197">
@@ -10923,7 +10923,7 @@
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827012 - KIT4M04606110GTV</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827011110 - KIT4M03866627GHD</t>
         </is>
       </c>
       <c r="C197" s="3" t="n">
@@ -10934,12 +10934,12 @@
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04606110GTV</t>
+          <t>KIT4M03866627GHD</t>
         </is>
       </c>
       <c r="F197" s="4" t="inlineStr">
         <is>
-          <t>809660</t>
+          <t>809619</t>
         </is>
       </c>
       <c r="G197" s="5" t="inlineStr">
@@ -10965,7 +10965,7 @@
       </c>
       <c r="L197" s="5" t="n"/>
       <c r="M197" s="7" t="n">
-        <v>2.61</v>
+        <v>5.78</v>
       </c>
     </row>
     <row r="198">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437932 - KIT4M05799732NQK</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020650182 - KIT4M05413821GGW</t>
         </is>
       </c>
       <c r="C198" s="3" t="n">
@@ -10987,12 +10987,12 @@
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799732NQK</t>
+          <t>KIT4M05413821GGW</t>
         </is>
       </c>
       <c r="F198" s="4" t="inlineStr">
         <is>
-          <t>816275</t>
+          <t>812830</t>
         </is>
       </c>
       <c r="G198" s="5" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="L198" s="5" t="n"/>
       <c r="M198" s="7" t="n">
-        <v>2.48</v>
+        <v>5.51</v>
       </c>
     </row>
     <row r="199">
@@ -11029,7 +11029,7 @@
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>SSC - 05900510 -  Los Angeles CA - 021437862 - KIT4M05872516CJM</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827011116 - KIT4M02578775B9Q</t>
         </is>
       </c>
       <c r="C199" s="3" t="n">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872516CJM</t>
+          <t>KIT4M02578775B9Q</t>
         </is>
       </c>
       <c r="F199" s="4" t="inlineStr">
         <is>
-          <t>816087</t>
+          <t>809611</t>
         </is>
       </c>
       <c r="G199" s="5" t="inlineStr">
@@ -11071,7 +11071,7 @@
       </c>
       <c r="L199" s="5" t="n"/>
       <c r="M199" s="7" t="n">
-        <v>1.98</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="200">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437412 - KIT4M05872548P2H</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437582 - KIT4M05872573K7P</t>
         </is>
       </c>
       <c r="C200" s="3" t="n">
@@ -11093,12 +11093,12 @@
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872548P2H</t>
+          <t>KIT4M05872573K7P</t>
         </is>
       </c>
       <c r="F200" s="4" t="inlineStr">
         <is>
-          <t>816066</t>
+          <t>816067</t>
         </is>
       </c>
       <c r="G200" s="5" t="inlineStr">
@@ -11124,7 +11124,7 @@
       </c>
       <c r="L200" s="5" t="n"/>
       <c r="M200" s="7" t="n">
-        <v>1.91</v>
+        <v>4.28</v>
       </c>
     </row>
     <row r="201">
@@ -11135,7 +11135,7 @@
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438262 - KIT4M05872530RPF</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437412 - KIT4M05872548P2H</t>
         </is>
       </c>
       <c r="C201" s="3" t="n">
@@ -11146,12 +11146,12 @@
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872530RPF</t>
+          <t>KIT4M05872548P2H</t>
         </is>
       </c>
       <c r="F201" s="4" t="inlineStr">
         <is>
-          <t>816079</t>
+          <t>816066</t>
         </is>
       </c>
       <c r="G201" s="5" t="inlineStr">
@@ -11177,7 +11177,7 @@
       </c>
       <c r="L201" s="5" t="n"/>
       <c r="M201" s="7" t="n">
-        <v>1.91</v>
+        <v>3.95</v>
       </c>
     </row>
     <row r="202">
@@ -11188,7 +11188,7 @@
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 020955572 - KIT4M05563606ZRC</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438252 - KIT4M05872519KTN</t>
         </is>
       </c>
       <c r="C202" s="3" t="n">
@@ -11199,12 +11199,12 @@
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563606ZRC</t>
+          <t>KIT4M05872519KTN</t>
         </is>
       </c>
       <c r="F202" s="4" t="inlineStr">
         <is>
-          <t>814464</t>
+          <t>816084</t>
         </is>
       </c>
       <c r="G202" s="5" t="inlineStr">
@@ -11230,7 +11230,7 @@
       </c>
       <c r="L202" s="5" t="n"/>
       <c r="M202" s="7" t="n">
-        <v>1.82</v>
+        <v>3.21</v>
       </c>
     </row>
     <row r="203">
@@ -11241,7 +11241,7 @@
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437612 - KIT4M058725265DP</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649752 - KIT4M03867749CW5</t>
         </is>
       </c>
       <c r="C203" s="3" t="n">
@@ -11252,12 +11252,12 @@
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725265DP</t>
+          <t>KIT4M03867749CW5</t>
         </is>
       </c>
       <c r="F203" s="4" t="inlineStr">
         <is>
-          <t>816192</t>
+          <t>809877</t>
         </is>
       </c>
       <c r="G203" s="5" t="inlineStr">
@@ -11283,7 +11283,7 @@
       </c>
       <c r="L203" s="5" t="n"/>
       <c r="M203" s="7" t="n">
-        <v>1.58</v>
+        <v>3</v>
       </c>
     </row>
     <row r="204">
@@ -11294,7 +11294,7 @@
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020650022 - KIT4M05413813HSJ</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649392 - KIT4M05368206BZP</t>
         </is>
       </c>
       <c r="C204" s="3" t="n">
@@ -11305,12 +11305,12 @@
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413813HSJ</t>
+          <t>KIT4M05368206BZP</t>
         </is>
       </c>
       <c r="F204" s="4" t="inlineStr">
         <is>
-          <t>812797</t>
+          <t>810645</t>
         </is>
       </c>
       <c r="G204" s="5" t="inlineStr">
@@ -11336,7 +11336,7 @@
       </c>
       <c r="L204" s="5" t="n"/>
       <c r="M204" s="7" t="n">
-        <v>1.2</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="205">
@@ -11347,7 +11347,7 @@
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649852 - KIT4M05413789Z8C</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827012 - KIT4M04606110GTV</t>
         </is>
       </c>
       <c r="C205" s="3" t="n">
@@ -11358,12 +11358,12 @@
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413789Z8C</t>
+          <t>KIT4M04606110GTV</t>
         </is>
       </c>
       <c r="F205" s="4" t="inlineStr">
         <is>
-          <t>812840</t>
+          <t>809660</t>
         </is>
       </c>
       <c r="G205" s="5" t="inlineStr">
@@ -11389,7 +11389,7 @@
       </c>
       <c r="L205" s="5" t="n"/>
       <c r="M205" s="7" t="n">
-        <v>1.14</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="206">
@@ -11400,7 +11400,7 @@
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020649652 - KIT4M0541381584X</t>
+          <t>SS - 05900510 -  Los Angeles CA - 020955572 - KIT4M05563606ZRC</t>
         </is>
       </c>
       <c r="C206" s="3" t="n">
@@ -11411,12 +11411,12 @@
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0541381584X</t>
+          <t>KIT4M05563606ZRC</t>
         </is>
       </c>
       <c r="F206" s="4" t="inlineStr">
         <is>
-          <t>812810</t>
+          <t>814464</t>
         </is>
       </c>
       <c r="G206" s="5" t="inlineStr">
@@ -11442,7 +11442,7 @@
       </c>
       <c r="L206" s="5" t="n"/>
       <c r="M206" s="7" t="n">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="207">
@@ -11495,7 +11495,7 @@
       </c>
       <c r="L207" s="5" t="n"/>
       <c r="M207" s="7" t="n">
-        <v>0.96</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="208">
@@ -11506,7 +11506,7 @@
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438282 - KIT4M05872508VTN</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437612 - KIT4M058725265DP</t>
         </is>
       </c>
       <c r="C208" s="3" t="n">
@@ -11517,12 +11517,12 @@
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872508VTN</t>
+          <t>KIT4M058725265DP</t>
         </is>
       </c>
       <c r="F208" s="4" t="inlineStr">
         <is>
-          <t>816076</t>
+          <t>816192</t>
         </is>
       </c>
       <c r="G208" s="5" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="L208" s="5" t="n"/>
       <c r="M208" s="7" t="n">
-        <v>0.92</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="209">
@@ -11559,7 +11559,7 @@
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491804TBC</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020650022 - KIT4M05413813HSJ</t>
         </is>
       </c>
       <c r="C209" s="3" t="n">
@@ -11570,12 +11570,12 @@
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491804TBC</t>
+          <t>KIT4M05413813HSJ</t>
         </is>
       </c>
       <c r="F209" s="4" t="inlineStr">
         <is>
-          <t>816373</t>
+          <t>812797</t>
         </is>
       </c>
       <c r="G209" s="5" t="inlineStr">
@@ -11601,7 +11601,7 @@
       </c>
       <c r="L209" s="5" t="n"/>
       <c r="M209" s="7" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="210">
@@ -11612,7 +11612,7 @@
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491800F52</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649852 - KIT4M05413789Z8C</t>
         </is>
       </c>
       <c r="C210" s="3" t="n">
@@ -11623,12 +11623,12 @@
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491800F52</t>
+          <t>KIT4M05413789Z8C</t>
         </is>
       </c>
       <c r="F210" s="4" t="inlineStr">
         <is>
-          <t>816406</t>
+          <t>812840</t>
         </is>
       </c>
       <c r="G210" s="5" t="inlineStr">
@@ -11654,7 +11654,7 @@
       </c>
       <c r="L210" s="5" t="n"/>
       <c r="M210" s="7" t="n">
-        <v>0.35</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="211">
@@ -11665,7 +11665,7 @@
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437812-KIT4M058724947VX</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020649652 - KIT4M0541381584X</t>
         </is>
       </c>
       <c r="C211" s="3" t="n">
@@ -11676,12 +11676,12 @@
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058724947VX</t>
+          <t>KIT4M0541381584X</t>
         </is>
       </c>
       <c r="F211" s="4" t="inlineStr">
         <is>
-          <t>816086</t>
+          <t>812810</t>
         </is>
       </c>
       <c r="G211" s="5" t="inlineStr">
@@ -11707,7 +11707,7 @@
       </c>
       <c r="L211" s="5" t="n"/>
       <c r="M211" s="7" t="n">
-        <v>0.26</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="212">
@@ -11718,7 +11718,7 @@
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020650062 - KIT4M05413797HK5</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438282 - KIT4M05872508VTN</t>
         </is>
       </c>
       <c r="C212" s="3" t="n">
@@ -11729,12 +11729,12 @@
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413797HK5</t>
+          <t>KIT4M05872508VTN</t>
         </is>
       </c>
       <c r="F212" s="4" t="inlineStr">
         <is>
-          <t>812808</t>
+          <t>816076</t>
         </is>
       </c>
       <c r="G212" s="5" t="inlineStr">
@@ -11760,7 +11760,7 @@
       </c>
       <c r="L212" s="5" t="n"/>
       <c r="M212" s="7" t="n">
-        <v>0.24</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="213">
@@ -11771,7 +11771,7 @@
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020649522-KIT4M05413834FTH</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491804TBC</t>
         </is>
       </c>
       <c r="C213" s="3" t="n">
@@ -11782,12 +11782,12 @@
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413834FTH</t>
+          <t>KIT4M06491804TBC</t>
         </is>
       </c>
       <c r="F213" s="4" t="inlineStr">
         <is>
-          <t>812817</t>
+          <t>816373</t>
         </is>
       </c>
       <c r="G213" s="5" t="inlineStr">
@@ -11813,7 +11813,7 @@
       </c>
       <c r="L213" s="5" t="n"/>
       <c r="M213" s="7" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="214">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 6862083  - KIT4M05799682BXX</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491800F52</t>
         </is>
       </c>
       <c r="C214" s="3" t="n">
@@ -11835,12 +11835,12 @@
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799682BXX</t>
+          <t>KIT4M06491800F52</t>
         </is>
       </c>
       <c r="F214" s="4" t="inlineStr">
         <is>
-          <t>816278</t>
+          <t>816406</t>
         </is>
       </c>
       <c r="G214" s="5" t="inlineStr">
@@ -11866,7 +11866,7 @@
       </c>
       <c r="L214" s="5" t="n"/>
       <c r="M214" s="7" t="n">
-        <v>0.19</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="215">
@@ -11877,7 +11877,7 @@
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437832 - KIT4M05872486FXZ</t>
+          <t>SMRT-05900510-Los Angeles CA-021437812-KIT4M058724947VX</t>
         </is>
       </c>
       <c r="C215" s="3" t="n">
@@ -11888,12 +11888,12 @@
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872486FXZ</t>
+          <t>KIT4M058724947VX</t>
         </is>
       </c>
       <c r="F215" s="4" t="inlineStr">
         <is>
-          <t>816088</t>
+          <t>816086</t>
         </is>
       </c>
       <c r="G215" s="5" t="inlineStr">
@@ -11919,7 +11919,7 @@
       </c>
       <c r="L215" s="5" t="n"/>
       <c r="M215" s="7" t="n">
-        <v>0.17</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="216">
@@ -11930,7 +11930,7 @@
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955422 - KIT4M05563517BVR</t>
+          <t>SS - 05900510 - Los Angeles CA - 020650062 - KIT4M05413797HK5</t>
         </is>
       </c>
       <c r="C216" s="3" t="n">
@@ -11941,12 +11941,12 @@
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563517BVR</t>
+          <t>KIT4M05413797HK5</t>
         </is>
       </c>
       <c r="F216" s="4" t="inlineStr">
         <is>
-          <t>814438</t>
+          <t>812808</t>
         </is>
       </c>
       <c r="G216" s="5" t="inlineStr">
@@ -11972,7 +11972,7 @@
       </c>
       <c r="L216" s="5" t="n"/>
       <c r="M216" s="7" t="n">
-        <v>0.16</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="217">
@@ -11983,7 +11983,7 @@
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438172 - KIT4M05872500684</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649702 - KIT4M04604741P2X</t>
         </is>
       </c>
       <c r="C217" s="3" t="n">
@@ -11994,12 +11994,12 @@
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872500684</t>
+          <t>KIT4M04604741P2X</t>
         </is>
       </c>
       <c r="F217" s="4" t="inlineStr">
         <is>
-          <t>816081</t>
+          <t>809871</t>
         </is>
       </c>
       <c r="G217" s="5" t="inlineStr">
@@ -12025,7 +12025,7 @@
       </c>
       <c r="L217" s="5" t="n"/>
       <c r="M217" s="7" t="n">
-        <v>0.14</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="218">
@@ -12036,7 +12036,7 @@
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 6862083  - KIT4M057996395ZF</t>
+          <t>SMRT-05900510-Los Angeles CA-020649522-KIT4M05413834FTH</t>
         </is>
       </c>
       <c r="C218" s="3" t="n">
@@ -12047,12 +12047,12 @@
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>KIT4M057996395ZF</t>
+          <t>KIT4M05413834FTH</t>
         </is>
       </c>
       <c r="F218" s="4" t="inlineStr">
         <is>
-          <t>816268</t>
+          <t>812817</t>
         </is>
       </c>
       <c r="G218" s="5" t="inlineStr">
@@ -12078,7 +12078,7 @@
       </c>
       <c r="L218" s="5" t="n"/>
       <c r="M218" s="7" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="219">
@@ -12089,7 +12089,7 @@
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491836Z2D</t>
+          <t>SS - 05900510 - Los Angeles CA - 6862083  - KIT4M05799682BXX</t>
         </is>
       </c>
       <c r="C219" s="3" t="n">
@@ -12100,12 +12100,12 @@
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491836Z2D</t>
+          <t>KIT4M05799682BXX</t>
         </is>
       </c>
       <c r="F219" s="4" t="inlineStr">
         <is>
-          <t>816366</t>
+          <t>816278</t>
         </is>
       </c>
       <c r="G219" s="5" t="inlineStr">
@@ -12131,7 +12131,7 @@
       </c>
       <c r="L219" s="5" t="n"/>
       <c r="M219" s="7" t="n">
-        <v>0.14</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="220">
@@ -12142,7 +12142,7 @@
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491790945</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437832 - KIT4M05872486FXZ</t>
         </is>
       </c>
       <c r="C220" s="3" t="n">
@@ -12153,12 +12153,12 @@
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491790945</t>
+          <t>KIT4M05872486FXZ</t>
         </is>
       </c>
       <c r="F220" s="4" t="inlineStr">
         <is>
-          <t>816410</t>
+          <t>816088</t>
         </is>
       </c>
       <c r="G220" s="5" t="inlineStr">
@@ -12184,7 +12184,7 @@
       </c>
       <c r="L220" s="5" t="n"/>
       <c r="M220" s="7" t="n">
-        <v>0.14</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="221">
@@ -12195,7 +12195,7 @@
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437302 - KIT4M05872571T4K</t>
+          <t>SMRT-05900510-Los Angeles CA-020649472-KIT4M05413795QHK</t>
         </is>
       </c>
       <c r="C221" s="3" t="n">
@@ -12206,12 +12206,12 @@
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872571T4K</t>
+          <t>KIT4M05413795QHK</t>
         </is>
       </c>
       <c r="F221" s="4" t="inlineStr">
         <is>
-          <t>816106</t>
+          <t>812801</t>
         </is>
       </c>
       <c r="G221" s="5" t="inlineStr">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="L221" s="5" t="n"/>
       <c r="M221" s="7" t="n">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="222">
@@ -12248,7 +12248,7 @@
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491814FV7</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955422 - KIT4M05563517BVR</t>
         </is>
       </c>
       <c r="C222" s="3" t="n">
@@ -12259,12 +12259,12 @@
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491814FV7</t>
+          <t>KIT4M05563517BVR</t>
         </is>
       </c>
       <c r="F222" s="4" t="inlineStr">
         <is>
-          <t>816370</t>
+          <t>814438</t>
         </is>
       </c>
       <c r="G222" s="5" t="inlineStr">
@@ -12290,7 +12290,7 @@
       </c>
       <c r="L222" s="5" t="n"/>
       <c r="M222" s="7" t="n">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="223">
@@ -12301,7 +12301,7 @@
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438022 - KIT4M05799705T6B</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491836Z2D</t>
         </is>
       </c>
       <c r="C223" s="3" t="n">
@@ -12312,12 +12312,12 @@
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799705T6B</t>
+          <t>KIT4M06491836Z2D</t>
         </is>
       </c>
       <c r="F223" s="4" t="inlineStr">
         <is>
-          <t>816285</t>
+          <t>816366</t>
         </is>
       </c>
       <c r="G223" s="5" t="inlineStr">
@@ -12343,7 +12343,7 @@
       </c>
       <c r="L223" s="5" t="n"/>
       <c r="M223" s="7" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="224">
@@ -12354,7 +12354,7 @@
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918277QF</t>
+          <t>SS - 05900510 - Los Angeles CA - 6862083  - KIT4M057996395ZF</t>
         </is>
       </c>
       <c r="C224" s="3" t="n">
@@ -12365,12 +12365,12 @@
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918277QF</t>
+          <t>KIT4M057996395ZF</t>
         </is>
       </c>
       <c r="F224" s="4" t="inlineStr">
         <is>
-          <t>816403</t>
+          <t>816268</t>
         </is>
       </c>
       <c r="G224" s="5" t="inlineStr">
@@ -12396,7 +12396,7 @@
       </c>
       <c r="L224" s="5" t="n"/>
       <c r="M224" s="7" t="n">
-        <v>0.11</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="225">
@@ -12407,7 +12407,7 @@
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437312 - KIT4M05872568PR6</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438172 - KIT4M05872500684</t>
         </is>
       </c>
       <c r="C225" s="3" t="n">
@@ -12418,12 +12418,12 @@
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872568PR6</t>
+          <t>KIT4M05872500684</t>
         </is>
       </c>
       <c r="F225" s="4" t="inlineStr">
         <is>
-          <t>816094</t>
+          <t>816081</t>
         </is>
       </c>
       <c r="G225" s="5" t="inlineStr">
@@ -12449,7 +12449,7 @@
       </c>
       <c r="L225" s="5" t="n"/>
       <c r="M225" s="7" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="226">
@@ -12460,7 +12460,7 @@
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437732 - KIT4M05872588W8G</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491790945</t>
         </is>
       </c>
       <c r="C226" s="3" t="n">
@@ -12471,12 +12471,12 @@
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872588W8G</t>
+          <t>KIT4M06491790945</t>
         </is>
       </c>
       <c r="F226" s="4" t="inlineStr">
         <is>
-          <t>816100</t>
+          <t>816410</t>
         </is>
       </c>
       <c r="G226" s="5" t="inlineStr">
@@ -12502,7 +12502,7 @@
       </c>
       <c r="L226" s="5" t="n"/>
       <c r="M226" s="7" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="227">
@@ -12513,7 +12513,7 @@
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 021438182 - KIT4M05872528P9D</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437302 - KIT4M05872571T4K</t>
         </is>
       </c>
       <c r="C227" s="3" t="n">
@@ -12524,12 +12524,12 @@
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872528P9D</t>
+          <t>KIT4M05872571T4K</t>
         </is>
       </c>
       <c r="F227" s="4" t="inlineStr">
         <is>
-          <t>816089</t>
+          <t>816106</t>
         </is>
       </c>
       <c r="G227" s="5" t="inlineStr">
@@ -12555,7 +12555,7 @@
       </c>
       <c r="L227" s="5" t="n"/>
       <c r="M227" s="7" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="228">
@@ -12566,7 +12566,7 @@
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437722 - KIT4M05872498PP4</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491814FV7</t>
         </is>
       </c>
       <c r="C228" s="3" t="n">
@@ -12577,12 +12577,12 @@
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872498PP4</t>
+          <t>KIT4M06491814FV7</t>
         </is>
       </c>
       <c r="F228" s="4" t="inlineStr">
         <is>
-          <t>816104</t>
+          <t>816370</t>
         </is>
       </c>
       <c r="G228" s="5" t="inlineStr">
@@ -12608,7 +12608,7 @@
       </c>
       <c r="L228" s="5" t="n"/>
       <c r="M228" s="7" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="229">
@@ -12619,7 +12619,7 @@
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438252 - KIT4M05872519KTN</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438022 - KIT4M05799705T6B</t>
         </is>
       </c>
       <c r="C229" s="3" t="n">
@@ -12630,12 +12630,12 @@
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872519KTN</t>
+          <t>KIT4M05799705T6B</t>
         </is>
       </c>
       <c r="F229" s="4" t="inlineStr">
         <is>
-          <t>816084</t>
+          <t>816285</t>
         </is>
       </c>
       <c r="G229" s="5" t="inlineStr">
@@ -12661,7 +12661,7 @@
       </c>
       <c r="L229" s="5" t="n"/>
       <c r="M229" s="7" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="230">
@@ -12672,7 +12672,7 @@
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491821G25</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918277QF</t>
         </is>
       </c>
       <c r="C230" s="3" t="n">
@@ -12683,12 +12683,12 @@
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491821G25</t>
+          <t>KIT4M064918277QF</t>
         </is>
       </c>
       <c r="F230" s="4" t="inlineStr">
         <is>
-          <t>816379</t>
+          <t>816403</t>
         </is>
       </c>
       <c r="G230" s="5" t="inlineStr">
@@ -12714,7 +12714,7 @@
       </c>
       <c r="L230" s="5" t="n"/>
       <c r="M230" s="7" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="231">
@@ -12725,7 +12725,7 @@
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437822-KIT4M0587253378R</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437312 - KIT4M05872568PR6</t>
         </is>
       </c>
       <c r="C231" s="3" t="n">
@@ -12736,12 +12736,12 @@
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0587253378R</t>
+          <t>KIT4M05872568PR6</t>
         </is>
       </c>
       <c r="F231" s="4" t="inlineStr">
         <is>
-          <t>816210</t>
+          <t>816094</t>
         </is>
       </c>
       <c r="G231" s="5" t="inlineStr">
@@ -12767,7 +12767,7 @@
       </c>
       <c r="L231" s="5" t="n"/>
       <c r="M231" s="7" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="232">
@@ -12778,7 +12778,7 @@
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437332 - KIT4M05872554RHM</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437732 - KIT4M05872588W8G</t>
         </is>
       </c>
       <c r="C232" s="3" t="n">
@@ -12789,12 +12789,12 @@
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872554RHM</t>
+          <t>KIT4M05872588W8G</t>
         </is>
       </c>
       <c r="F232" s="4" t="inlineStr">
         <is>
-          <t>816071</t>
+          <t>816100</t>
         </is>
       </c>
       <c r="G232" s="5" t="inlineStr">
@@ -12820,7 +12820,7 @@
       </c>
       <c r="L232" s="5" t="n"/>
       <c r="M232" s="7" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="233">
@@ -12831,7 +12831,7 @@
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437342 - KIT4M05872557NFB</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491821G25</t>
         </is>
       </c>
       <c r="C233" s="3" t="n">
@@ -12842,12 +12842,12 @@
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872557NFB</t>
+          <t>KIT4M06491821G25</t>
         </is>
       </c>
       <c r="F233" s="4" t="inlineStr">
         <is>
-          <t>816095</t>
+          <t>816379</t>
         </is>
       </c>
       <c r="G233" s="5" t="inlineStr">
@@ -12873,7 +12873,7 @@
       </c>
       <c r="L233" s="5" t="n"/>
       <c r="M233" s="7" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="234">
@@ -12884,7 +12884,7 @@
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438112 - KIT4M0579970825J</t>
+          <t>SS - 05900510 -  Los Angeles CA - 021438182 - KIT4M05872528P9D</t>
         </is>
       </c>
       <c r="C234" s="3" t="n">
@@ -12895,12 +12895,12 @@
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0579970825J</t>
+          <t>KIT4M05872528P9D</t>
         </is>
       </c>
       <c r="F234" s="4" t="inlineStr">
         <is>
-          <t>816290</t>
+          <t>816089</t>
         </is>
       </c>
       <c r="G234" s="5" t="inlineStr">
@@ -12926,7 +12926,7 @@
       </c>
       <c r="L234" s="5" t="n"/>
       <c r="M234" s="7" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="235">
@@ -12937,7 +12937,7 @@
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437692 - KIT4M05872518P78</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437722 - KIT4M05872498PP4</t>
         </is>
       </c>
       <c r="C235" s="3" t="n">
@@ -12948,12 +12948,12 @@
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872518P78</t>
+          <t>KIT4M05872498PP4</t>
         </is>
       </c>
       <c r="F235" s="4" t="inlineStr">
         <is>
-          <t>816184</t>
+          <t>816104</t>
         </is>
       </c>
       <c r="G235" s="5" t="inlineStr">
@@ -12979,7 +12979,7 @@
       </c>
       <c r="L235" s="5" t="n"/>
       <c r="M235" s="7" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="236">
@@ -12990,7 +12990,7 @@
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918165MW</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437692 - KIT4M05872518P78</t>
         </is>
       </c>
       <c r="C236" s="3" t="n">
@@ -13001,12 +13001,12 @@
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918165MW</t>
+          <t>KIT4M05872518P78</t>
         </is>
       </c>
       <c r="F236" s="4" t="inlineStr">
         <is>
-          <t>816374</t>
+          <t>816184</t>
         </is>
       </c>
       <c r="G236" s="5" t="inlineStr">
@@ -13043,7 +13043,7 @@
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491818QD2</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438112 - KIT4M0579970825J</t>
         </is>
       </c>
       <c r="C237" s="3" t="n">
@@ -13054,12 +13054,12 @@
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491818QD2</t>
+          <t>KIT4M0579970825J</t>
         </is>
       </c>
       <c r="F237" s="4" t="inlineStr">
         <is>
-          <t>816378</t>
+          <t>816290</t>
         </is>
       </c>
       <c r="G237" s="5" t="inlineStr">
@@ -13096,7 +13096,7 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918197VX</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491818QD2</t>
         </is>
       </c>
       <c r="C238" s="3" t="n">
@@ -13107,12 +13107,12 @@
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918197VX</t>
+          <t>KIT4M06491818QD2</t>
         </is>
       </c>
       <c r="F238" s="4" t="inlineStr">
         <is>
-          <t>816397</t>
+          <t>816378</t>
         </is>
       </c>
       <c r="G238" s="5" t="inlineStr">
@@ -13202,7 +13202,7 @@
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491826SQM</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491825PF9</t>
         </is>
       </c>
       <c r="C240" s="3" t="n">
@@ -13213,12 +13213,12 @@
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491826SQM</t>
+          <t>KIT4M06491825PF9</t>
         </is>
       </c>
       <c r="F240" s="4" t="inlineStr">
         <is>
-          <t>816380</t>
+          <t>816367</t>
         </is>
       </c>
       <c r="G240" s="5" t="inlineStr">
@@ -13255,7 +13255,7 @@
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491825PF9</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491826SQM</t>
         </is>
       </c>
       <c r="C241" s="3" t="n">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491825PF9</t>
+          <t>KIT4M06491826SQM</t>
         </is>
       </c>
       <c r="F241" s="4" t="inlineStr">
         <is>
-          <t>816367</t>
+          <t>816380</t>
         </is>
       </c>
       <c r="G241" s="5" t="inlineStr">
@@ -13308,7 +13308,7 @@
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437502 - KIT4M058725695CN</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491830G2J</t>
         </is>
       </c>
       <c r="C242" s="3" t="n">
@@ -13319,12 +13319,12 @@
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725695CN</t>
+          <t>KIT4M06491830G2J</t>
         </is>
       </c>
       <c r="F242" s="4" t="inlineStr">
         <is>
-          <t>816101</t>
+          <t>816372</t>
         </is>
       </c>
       <c r="G242" s="5" t="inlineStr">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437712-KIT4M05872570FCC</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437502 - KIT4M058725695CN</t>
         </is>
       </c>
       <c r="C243" s="3" t="n">
@@ -13372,12 +13372,12 @@
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872570FCC</t>
+          <t>KIT4M058725695CN</t>
         </is>
       </c>
       <c r="F243" s="4" t="inlineStr">
         <is>
-          <t>816105</t>
+          <t>816101</t>
         </is>
       </c>
       <c r="G243" s="5" t="inlineStr">
@@ -13414,7 +13414,7 @@
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437752 - KIT4M05872577TWT</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437462 - KIT4M05872575BC8</t>
         </is>
       </c>
       <c r="C244" s="3" t="n">
@@ -13425,12 +13425,12 @@
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872577TWT</t>
+          <t>KIT4M05872575BC8</t>
         </is>
       </c>
       <c r="F244" s="4" t="inlineStr">
         <is>
-          <t>816212</t>
+          <t>816103</t>
         </is>
       </c>
       <c r="G244" s="5" t="inlineStr">
@@ -13467,7 +13467,7 @@
       </c>
       <c r="B245" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491786BS9</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437362 - KIT4M05872574NKX</t>
         </is>
       </c>
       <c r="C245" s="3" t="n">
@@ -13478,12 +13478,12 @@
       </c>
       <c r="E245" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491786BS9</t>
+          <t>KIT4M05872574NKX</t>
         </is>
       </c>
       <c r="F245" s="4" t="inlineStr">
         <is>
-          <t>816396</t>
+          <t>816113</t>
         </is>
       </c>
       <c r="G245" s="5" t="inlineStr">
@@ -13573,7 +13573,7 @@
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064917925MB</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064917914G5</t>
         </is>
       </c>
       <c r="C247" s="3" t="n">
@@ -13584,12 +13584,12 @@
       </c>
       <c r="E247" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064917925MB</t>
+          <t>KIT4M064917914G5</t>
         </is>
       </c>
       <c r="F247" s="4" t="inlineStr">
         <is>
-          <t>816381</t>
+          <t>816392</t>
         </is>
       </c>
       <c r="G247" s="5" t="inlineStr">
@@ -13626,7 +13626,7 @@
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064917914G5</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918197VX</t>
         </is>
       </c>
       <c r="C248" s="3" t="n">
@@ -13637,12 +13637,12 @@
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064917914G5</t>
+          <t>KIT4M064918197VX</t>
         </is>
       </c>
       <c r="F248" s="4" t="inlineStr">
         <is>
-          <t>816392</t>
+          <t>816397</t>
         </is>
       </c>
       <c r="G248" s="5" t="inlineStr">
@@ -13679,7 +13679,7 @@
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491789PJ6</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491817T79</t>
         </is>
       </c>
       <c r="C249" s="3" t="n">
@@ -13690,12 +13690,12 @@
       </c>
       <c r="E249" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491789PJ6</t>
+          <t>KIT4M06491817T79</t>
         </is>
       </c>
       <c r="F249" s="4" t="inlineStr">
         <is>
-          <t>816407</t>
+          <t>816415</t>
         </is>
       </c>
       <c r="G249" s="5" t="inlineStr">
@@ -13732,7 +13732,7 @@
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491817T79</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918165MW</t>
         </is>
       </c>
       <c r="C250" s="3" t="n">
@@ -13743,12 +13743,12 @@
       </c>
       <c r="E250" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491817T79</t>
+          <t>KIT4M064918165MW</t>
         </is>
       </c>
       <c r="F250" s="4" t="inlineStr">
         <is>
-          <t>816415</t>
+          <t>816374</t>
         </is>
       </c>
       <c r="G250" s="5" t="inlineStr">
@@ -13785,7 +13785,7 @@
       </c>
       <c r="B251" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491798S8Q</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491799CRP</t>
         </is>
       </c>
       <c r="C251" s="3" t="n">
@@ -13796,12 +13796,12 @@
       </c>
       <c r="E251" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491798S8Q</t>
+          <t>KIT4M06491799CRP</t>
         </is>
       </c>
       <c r="F251" s="4" t="inlineStr">
         <is>
-          <t>816395</t>
+          <t>816394</t>
         </is>
       </c>
       <c r="G251" s="5" t="inlineStr">
@@ -13838,7 +13838,7 @@
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491799CRP</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491798S8Q</t>
         </is>
       </c>
       <c r="C252" s="3" t="n">
@@ -13849,12 +13849,12 @@
       </c>
       <c r="E252" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491799CRP</t>
+          <t>KIT4M06491798S8Q</t>
         </is>
       </c>
       <c r="F252" s="4" t="inlineStr">
         <is>
-          <t>816394</t>
+          <t>816395</t>
         </is>
       </c>
       <c r="G252" s="5" t="inlineStr">
@@ -13997,7 +13997,7 @@
       </c>
       <c r="B255" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491830G2J</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M0649183125S</t>
         </is>
       </c>
       <c r="C255" s="3" t="n">
@@ -14008,12 +14008,12 @@
       </c>
       <c r="E255" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491830G2J</t>
+          <t>KIT4M0649183125S</t>
         </is>
       </c>
       <c r="F255" s="4" t="inlineStr">
         <is>
-          <t>816372</t>
+          <t>816371</t>
         </is>
       </c>
       <c r="G255" s="5" t="inlineStr">
@@ -14050,7 +14050,7 @@
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M0649183125S</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437342 - KIT4M05872557NFB</t>
         </is>
       </c>
       <c r="C256" s="3" t="n">
@@ -14061,12 +14061,12 @@
       </c>
       <c r="E256" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0649183125S</t>
+          <t>KIT4M05872557NFB</t>
         </is>
       </c>
       <c r="F256" s="4" t="inlineStr">
         <is>
-          <t>816371</t>
+          <t>816095</t>
         </is>
       </c>
       <c r="G256" s="5" t="inlineStr">
@@ -14156,7 +14156,7 @@
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437352-KIT4M05872545Q8H</t>
+          <t>SMRT-05900510-Los Angeles CA-021437822-KIT4M0587253378R</t>
         </is>
       </c>
       <c r="C258" s="3" t="n">
@@ -14167,12 +14167,12 @@
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872545Q8H</t>
+          <t>KIT4M0587253378R</t>
         </is>
       </c>
       <c r="F258" s="4" t="inlineStr">
         <is>
-          <t>816112</t>
+          <t>816210</t>
         </is>
       </c>
       <c r="G258" s="5" t="inlineStr">
@@ -14209,7 +14209,7 @@
       </c>
       <c r="B259" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437362 - KIT4M05872574NKX</t>
+          <t>SMRT-05900510-Los Angeles CA-021437712-KIT4M05872570FCC</t>
         </is>
       </c>
       <c r="C259" s="3" t="n">
@@ -14220,12 +14220,12 @@
       </c>
       <c r="E259" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872574NKX</t>
+          <t>KIT4M05872570FCC</t>
         </is>
       </c>
       <c r="F259" s="4" t="inlineStr">
         <is>
-          <t>816113</t>
+          <t>816105</t>
         </is>
       </c>
       <c r="G259" s="5" t="inlineStr">
@@ -14262,7 +14262,7 @@
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437462 - KIT4M05872575BC8</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437332 - KIT4M05872554RHM</t>
         </is>
       </c>
       <c r="C260" s="3" t="n">
@@ -14273,12 +14273,12 @@
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872575BC8</t>
+          <t>KIT4M05872554RHM</t>
         </is>
       </c>
       <c r="F260" s="4" t="inlineStr">
         <is>
-          <t>816103</t>
+          <t>816071</t>
         </is>
       </c>
       <c r="G260" s="5" t="inlineStr">
@@ -14315,7 +14315,7 @@
       </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437952 - KIT4M05872523VVB</t>
+          <t>SMRT-05900510-Los Angeles CA-021437352-KIT4M05872545Q8H</t>
         </is>
       </c>
       <c r="C261" s="3" t="n">
@@ -14326,12 +14326,12 @@
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872523VVB</t>
+          <t>KIT4M05872545Q8H</t>
         </is>
       </c>
       <c r="F261" s="4" t="inlineStr">
         <is>
-          <t>816215</t>
+          <t>816112</t>
         </is>
       </c>
       <c r="G261" s="5" t="inlineStr">
@@ -14368,7 +14368,7 @@
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437482-KIT4M05872578G7Q</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437952 - KIT4M05872523VVB</t>
         </is>
       </c>
       <c r="C262" s="3" t="n">
@@ -14379,12 +14379,12 @@
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872578G7Q</t>
+          <t>KIT4M05872523VVB</t>
         </is>
       </c>
       <c r="F262" s="4" t="inlineStr">
         <is>
-          <t>816102</t>
+          <t>816215</t>
         </is>
       </c>
       <c r="G262" s="5" t="inlineStr">
@@ -14421,7 +14421,7 @@
       </c>
       <c r="B263" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955542 - KIT4M05563551N6Q</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064917925MB</t>
         </is>
       </c>
       <c r="C263" s="3" t="n">
@@ -14432,12 +14432,12 @@
       </c>
       <c r="E263" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563551N6Q</t>
+          <t>KIT4M064917925MB</t>
         </is>
       </c>
       <c r="F263" s="4" t="inlineStr">
         <is>
-          <t>814450</t>
+          <t>816381</t>
         </is>
       </c>
       <c r="G263" s="5" t="inlineStr">
@@ -14463,7 +14463,7 @@
       </c>
       <c r="L263" s="5" t="n"/>
       <c r="M263" s="7" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="264">
@@ -14474,7 +14474,7 @@
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438082 - KIT4M05799668SS7</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491789PJ6</t>
         </is>
       </c>
       <c r="C264" s="3" t="n">
@@ -14485,12 +14485,12 @@
       </c>
       <c r="E264" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799668SS7</t>
+          <t>KIT4M06491789PJ6</t>
         </is>
       </c>
       <c r="F264" s="4" t="inlineStr">
         <is>
-          <t>816279</t>
+          <t>816407</t>
         </is>
       </c>
       <c r="G264" s="5" t="inlineStr">
@@ -14516,7 +14516,7 @@
       </c>
       <c r="L264" s="5" t="n"/>
       <c r="M264" s="7" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="265">
@@ -14527,7 +14527,7 @@
       </c>
       <c r="B265" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438192 - KIT4M05872511F6P</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437752 - KIT4M05872577TWT</t>
         </is>
       </c>
       <c r="C265" s="3" t="n">
@@ -14538,12 +14538,12 @@
       </c>
       <c r="E265" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872511F6P</t>
+          <t>KIT4M05872577TWT</t>
         </is>
       </c>
       <c r="F265" s="4" t="inlineStr">
         <is>
-          <t>816090</t>
+          <t>816212</t>
         </is>
       </c>
       <c r="G265" s="5" t="inlineStr">
@@ -14569,7 +14569,7 @@
       </c>
       <c r="L265" s="5" t="n"/>
       <c r="M265" s="7" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="266">
@@ -14580,7 +14580,7 @@
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918015Z2</t>
+          <t>SMRT-05900510-Los Angeles CA-021437482-KIT4M05872578G7Q</t>
         </is>
       </c>
       <c r="C266" s="3" t="n">
@@ -14591,12 +14591,12 @@
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918015Z2</t>
+          <t>KIT4M05872578G7Q</t>
         </is>
       </c>
       <c r="F266" s="4" t="inlineStr">
         <is>
-          <t>816376</t>
+          <t>816102</t>
         </is>
       </c>
       <c r="G266" s="5" t="inlineStr">
@@ -14622,7 +14622,7 @@
       </c>
       <c r="L266" s="5" t="n"/>
       <c r="M266" s="7" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="267">
@@ -14633,7 +14633,7 @@
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918346DB</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491786BS9</t>
         </is>
       </c>
       <c r="C267" s="3" t="n">
@@ -14644,12 +14644,12 @@
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918346DB</t>
+          <t>KIT4M06491786BS9</t>
         </is>
       </c>
       <c r="F267" s="4" t="inlineStr">
         <is>
-          <t>816369</t>
+          <t>816396</t>
         </is>
       </c>
       <c r="G267" s="5" t="inlineStr">
@@ -14675,7 +14675,7 @@
       </c>
       <c r="L267" s="5" t="n"/>
       <c r="M267" s="7" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="268">
@@ -14686,7 +14686,7 @@
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491833JGV</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918015Z2</t>
         </is>
       </c>
       <c r="C268" s="3" t="n">
@@ -14697,12 +14697,12 @@
       </c>
       <c r="E268" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491833JGV</t>
+          <t>KIT4M064918015Z2</t>
         </is>
       </c>
       <c r="F268" s="4" t="inlineStr">
         <is>
-          <t>816384</t>
+          <t>816376</t>
         </is>
       </c>
       <c r="G268" s="5" t="inlineStr">
@@ -14739,7 +14739,7 @@
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491813KGS</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491833JGV</t>
         </is>
       </c>
       <c r="C269" s="3" t="n">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E269" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491813KGS</t>
+          <t>KIT4M06491833JGV</t>
         </is>
       </c>
       <c r="F269" s="4" t="inlineStr">
         <is>
-          <t>816377</t>
+          <t>816384</t>
         </is>
       </c>
       <c r="G269" s="5" t="inlineStr">
@@ -14792,7 +14792,7 @@
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491795MWG</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491813KGS</t>
         </is>
       </c>
       <c r="C270" s="3" t="n">
@@ -14803,12 +14803,12 @@
       </c>
       <c r="E270" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491795MWG</t>
+          <t>KIT4M06491813KGS</t>
         </is>
       </c>
       <c r="F270" s="4" t="inlineStr">
         <is>
-          <t>816383</t>
+          <t>816377</t>
         </is>
       </c>
       <c r="G270" s="5" t="inlineStr">
@@ -14845,7 +14845,7 @@
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 021437682 - KIT4M05872544BXG</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437372 - KIT4M058725505J5</t>
         </is>
       </c>
       <c r="C271" s="3" t="n">
@@ -14856,12 +14856,12 @@
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872544BXG</t>
+          <t>KIT4M058725505J5</t>
         </is>
       </c>
       <c r="F271" s="4" t="inlineStr">
         <is>
-          <t>816176</t>
+          <t>816117</t>
         </is>
       </c>
       <c r="G271" s="5" t="inlineStr">
@@ -14898,7 +14898,7 @@
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437662 - KIT4M05872534RXS</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918346DB</t>
         </is>
       </c>
       <c r="C272" s="3" t="n">
@@ -14909,12 +14909,12 @@
       </c>
       <c r="E272" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872534RXS</t>
+          <t>KIT4M064918346DB</t>
         </is>
       </c>
       <c r="F272" s="4" t="inlineStr">
         <is>
-          <t>816216</t>
+          <t>816369</t>
         </is>
       </c>
       <c r="G272" s="5" t="inlineStr">
@@ -14951,7 +14951,7 @@
       </c>
       <c r="B273" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437372 - KIT4M058725505J5</t>
+          <t>SS - 05900510 -  Los Angeles CA - 021437682 - KIT4M05872544BXG</t>
         </is>
       </c>
       <c r="C273" s="3" t="n">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E273" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725505J5</t>
+          <t>KIT4M05872544BXG</t>
         </is>
       </c>
       <c r="F273" s="4" t="inlineStr">
         <is>
-          <t>816117</t>
+          <t>816176</t>
         </is>
       </c>
       <c r="G273" s="5" t="inlineStr">
@@ -15004,7 +15004,7 @@
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437572 - KIT4M05872579JPF</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437662 - KIT4M05872534RXS</t>
         </is>
       </c>
       <c r="C274" s="3" t="n">
@@ -15015,12 +15015,12 @@
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872579JPF</t>
+          <t>KIT4M05872534RXS</t>
         </is>
       </c>
       <c r="F274" s="4" t="inlineStr">
         <is>
-          <t>816111</t>
+          <t>816216</t>
         </is>
       </c>
       <c r="G274" s="5" t="inlineStr">
@@ -15057,7 +15057,7 @@
       </c>
       <c r="B275" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491797NCX</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438082 - KIT4M05799668SS7</t>
         </is>
       </c>
       <c r="C275" s="3" t="n">
@@ -15068,12 +15068,12 @@
       </c>
       <c r="E275" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491797NCX</t>
+          <t>KIT4M05799668SS7</t>
         </is>
       </c>
       <c r="F275" s="4" t="inlineStr">
         <is>
-          <t>816408</t>
+          <t>816279</t>
         </is>
       </c>
       <c r="G275" s="5" t="inlineStr">
@@ -15099,7 +15099,7 @@
       </c>
       <c r="L275" s="5" t="n"/>
       <c r="M275" s="7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="276">
@@ -15110,7 +15110,7 @@
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491808P4F</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437572 - KIT4M05872579JPF</t>
         </is>
       </c>
       <c r="C276" s="3" t="n">
@@ -15121,12 +15121,12 @@
       </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491808P4F</t>
+          <t>KIT4M05872579JPF</t>
         </is>
       </c>
       <c r="F276" s="4" t="inlineStr">
         <is>
-          <t>816399</t>
+          <t>816111</t>
         </is>
       </c>
       <c r="G276" s="5" t="inlineStr">
@@ -15152,7 +15152,7 @@
       </c>
       <c r="L276" s="5" t="n"/>
       <c r="M276" s="7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="277">
@@ -15163,7 +15163,7 @@
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 -  Los Angeles CA - 020649602 - KIT4M05413773R6G</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955542 - KIT4M05563551N6Q</t>
         </is>
       </c>
       <c r="C277" s="3" t="n">
@@ -15174,12 +15174,12 @@
       </c>
       <c r="E277" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413773R6G</t>
+          <t>KIT4M05563551N6Q</t>
         </is>
       </c>
       <c r="F277" s="4" t="inlineStr">
         <is>
-          <t>812807</t>
+          <t>814450</t>
         </is>
       </c>
       <c r="G277" s="5" t="inlineStr">
@@ -15205,7 +15205,7 @@
       </c>
       <c r="L277" s="5" t="n"/>
       <c r="M277" s="7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="278">
@@ -15216,7 +15216,7 @@
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA  - 020649572 - KIT4M05413816N8K</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438192 - KIT4M05872511F6P</t>
         </is>
       </c>
       <c r="C278" s="3" t="n">
@@ -15227,12 +15227,12 @@
       </c>
       <c r="E278" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413816N8K</t>
+          <t>KIT4M05872511F6P</t>
         </is>
       </c>
       <c r="F278" s="4" t="inlineStr">
         <is>
-          <t>812832</t>
+          <t>816090</t>
         </is>
       </c>
       <c r="G278" s="5" t="inlineStr">
@@ -15258,7 +15258,7 @@
       </c>
       <c r="L278" s="5" t="n"/>
       <c r="M278" s="7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="279">
@@ -15269,7 +15269,7 @@
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437382 - KIT4M058725438WP</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491795MWG</t>
         </is>
       </c>
       <c r="C279" s="3" t="n">
@@ -15280,12 +15280,12 @@
       </c>
       <c r="E279" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725438WP</t>
+          <t>KIT4M06491795MWG</t>
         </is>
       </c>
       <c r="F279" s="4" t="inlineStr">
         <is>
-          <t>816115</t>
+          <t>816383</t>
         </is>
       </c>
       <c r="G279" s="5" t="inlineStr">
@@ -15311,7 +15311,7 @@
       </c>
       <c r="L279" s="5" t="n"/>
       <c r="M279" s="7" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="280">
@@ -15322,7 +15322,7 @@
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491796QQN</t>
+          <t>SS - 05900510 - Los Angeles, CA  - 020649572 - KIT4M05413816N8K</t>
         </is>
       </c>
       <c r="C280" s="3" t="n">
@@ -15333,12 +15333,12 @@
       </c>
       <c r="E280" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491796QQN</t>
+          <t>KIT4M05413816N8K</t>
         </is>
       </c>
       <c r="F280" s="4" t="inlineStr">
         <is>
-          <t>816405</t>
+          <t>812832</t>
         </is>
       </c>
       <c r="G280" s="5" t="inlineStr">
@@ -15364,7 +15364,7 @@
       </c>
       <c r="L280" s="5" t="n"/>
       <c r="M280" s="7" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="281">
@@ -15375,7 +15375,7 @@
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438162 - KIT4M05799712SBX</t>
+          <t>SMA - 05900510 -  Los Angeles CA - 020649602 - KIT4M05413773R6G</t>
         </is>
       </c>
       <c r="C281" s="3" t="n">
@@ -15386,12 +15386,12 @@
       </c>
       <c r="E281" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799712SBX</t>
+          <t>KIT4M05413773R6G</t>
         </is>
       </c>
       <c r="F281" s="4" t="inlineStr">
         <is>
-          <t>816276</t>
+          <t>812807</t>
         </is>
       </c>
       <c r="G281" s="5" t="inlineStr">
@@ -15417,7 +15417,7 @@
       </c>
       <c r="L281" s="5" t="n"/>
       <c r="M281" s="7" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="282">
@@ -15428,7 +15428,7 @@
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491822SF6</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491797NCX</t>
         </is>
       </c>
       <c r="C282" s="3" t="n">
@@ -15439,12 +15439,12 @@
       </c>
       <c r="E282" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491822SF6</t>
+          <t>KIT4M06491797NCX</t>
         </is>
       </c>
       <c r="F282" s="4" t="inlineStr">
         <is>
-          <t>816412</t>
+          <t>816408</t>
         </is>
       </c>
       <c r="G282" s="5" t="inlineStr">
@@ -15470,7 +15470,7 @@
       </c>
       <c r="L282" s="5" t="n"/>
       <c r="M282" s="7" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="283">
@@ -15481,7 +15481,7 @@
       </c>
       <c r="B283" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918239TM</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491808P4F</t>
         </is>
       </c>
       <c r="C283" s="3" t="n">
@@ -15492,12 +15492,12 @@
       </c>
       <c r="E283" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918239TM</t>
+          <t>KIT4M06491808P4F</t>
         </is>
       </c>
       <c r="F283" s="4" t="inlineStr">
         <is>
-          <t>816398</t>
+          <t>816399</t>
         </is>
       </c>
       <c r="G283" s="5" t="inlineStr">
@@ -15523,7 +15523,7 @@
       </c>
       <c r="L283" s="5" t="n"/>
       <c r="M283" s="7" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="284">
@@ -15534,7 +15534,7 @@
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438292 - KIt4m058725108K2</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438162 - KIT4M05799712SBX</t>
         </is>
       </c>
       <c r="C284" s="3" t="n">
@@ -15545,12 +15545,12 @@
       </c>
       <c r="E284" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725108K2</t>
+          <t>KIT4M05799712SBX</t>
         </is>
       </c>
       <c r="F284" s="4" t="inlineStr">
         <is>
-          <t>816287</t>
+          <t>816276</t>
         </is>
       </c>
       <c r="G284" s="5" t="inlineStr">
@@ -15576,7 +15576,7 @@
       </c>
       <c r="L284" s="5" t="n"/>
       <c r="M284" s="7" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="285">
@@ -15587,7 +15587,7 @@
       </c>
       <c r="B285" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437962 - KIT4M05799706Z6R</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491822SF6</t>
         </is>
       </c>
       <c r="C285" s="3" t="n">
@@ -15598,12 +15598,12 @@
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799706Z6R</t>
+          <t>KIT4M06491822SF6</t>
         </is>
       </c>
       <c r="F285" s="4" t="inlineStr">
         <is>
-          <t>816273</t>
+          <t>816412</t>
         </is>
       </c>
       <c r="G285" s="5" t="inlineStr">
@@ -15629,7 +15629,7 @@
       </c>
       <c r="L285" s="5" t="n"/>
       <c r="M285" s="7" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="286">
@@ -15640,7 +15640,7 @@
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491803672</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491796QQN</t>
         </is>
       </c>
       <c r="C286" s="3" t="n">
@@ -15651,12 +15651,12 @@
       </c>
       <c r="E286" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491803672</t>
+          <t>KIT4M06491796QQN</t>
         </is>
       </c>
       <c r="F286" s="4" t="inlineStr">
         <is>
-          <t>816391</t>
+          <t>816405</t>
         </is>
       </c>
       <c r="G286" s="5" t="inlineStr">
@@ -15682,7 +15682,7 @@
       </c>
       <c r="L286" s="5" t="n"/>
       <c r="M286" s="7" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="287">
@@ -15693,7 +15693,7 @@
       </c>
       <c r="B287" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491811JB5</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437382 - KIT4M058725438WP</t>
         </is>
       </c>
       <c r="C287" s="3" t="n">
@@ -15704,12 +15704,12 @@
       </c>
       <c r="E287" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491811JB5</t>
+          <t>KIT4M058725438WP</t>
         </is>
       </c>
       <c r="F287" s="4" t="inlineStr">
         <is>
-          <t>816411</t>
+          <t>816115</t>
         </is>
       </c>
       <c r="G287" s="5" t="inlineStr">
@@ -15735,7 +15735,7 @@
       </c>
       <c r="L287" s="5" t="n"/>
       <c r="M287" s="7" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="288">
@@ -15746,7 +15746,7 @@
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491805F7Z</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918239TM</t>
         </is>
       </c>
       <c r="C288" s="3" t="n">
@@ -15757,12 +15757,12 @@
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491805F7Z</t>
+          <t>KIT4M064918239TM</t>
         </is>
       </c>
       <c r="F288" s="4" t="inlineStr">
         <is>
-          <t>816382</t>
+          <t>816398</t>
         </is>
       </c>
       <c r="G288" s="5" t="inlineStr">
@@ -15788,7 +15788,7 @@
       </c>
       <c r="L288" s="5" t="n"/>
       <c r="M288" s="7" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="289">
@@ -15799,7 +15799,7 @@
       </c>
       <c r="B289" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491802BZV</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491803672</t>
         </is>
       </c>
       <c r="C289" s="3" t="n">
@@ -15810,12 +15810,12 @@
       </c>
       <c r="E289" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491802BZV</t>
+          <t>KIT4M06491803672</t>
         </is>
       </c>
       <c r="F289" s="4" t="inlineStr">
         <is>
-          <t>816390</t>
+          <t>816391</t>
         </is>
       </c>
       <c r="G289" s="5" t="inlineStr">
@@ -15852,7 +15852,7 @@
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491824JCK</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491802BZV</t>
         </is>
       </c>
       <c r="C290" s="3" t="n">
@@ -15863,12 +15863,12 @@
       </c>
       <c r="E290" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491824JCK</t>
+          <t>KIT4M06491802BZV</t>
         </is>
       </c>
       <c r="F290" s="4" t="inlineStr">
         <is>
-          <t>816413</t>
+          <t>816390</t>
         </is>
       </c>
       <c r="G290" s="5" t="inlineStr">
@@ -16170,7 +16170,7 @@
       </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437542 - KIT4M05872553WFR</t>
+          <t>SMRT-05900510-Los Angeles CA-021437842-KIT4M05872547MK2</t>
         </is>
       </c>
       <c r="C296" s="3" t="n">
@@ -16181,12 +16181,12 @@
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872553WFR</t>
+          <t>KIT4M05872547MK2</t>
         </is>
       </c>
       <c r="F296" s="4" t="inlineStr">
         <is>
-          <t>816116</t>
+          <t>816209</t>
         </is>
       </c>
       <c r="G296" s="5" t="inlineStr">
@@ -16276,7 +16276,7 @@
       </c>
       <c r="B298" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437842-KIT4M05872547MK2</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437542 - KIT4M05872553WFR</t>
         </is>
       </c>
       <c r="C298" s="3" t="n">
@@ -16287,12 +16287,12 @@
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872547MK2</t>
+          <t>KIT4M05872553WFR</t>
         </is>
       </c>
       <c r="F298" s="4" t="inlineStr">
         <is>
-          <t>816209</t>
+          <t>816116</t>
         </is>
       </c>
       <c r="G298" s="5" t="inlineStr">
@@ -16329,7 +16329,7 @@
       </c>
       <c r="B299" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437472 - KIT4M05872565VJK</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437432 - KIT4M0587256692N</t>
         </is>
       </c>
       <c r="C299" s="3" t="n">
@@ -16340,12 +16340,12 @@
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872565VJK</t>
+          <t>KIT4M0587256692N</t>
         </is>
       </c>
       <c r="F299" s="4" t="inlineStr">
         <is>
-          <t>816109</t>
+          <t>816072</t>
         </is>
       </c>
       <c r="G299" s="5" t="inlineStr">
@@ -16435,7 +16435,7 @@
       </c>
       <c r="B301" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437432 - KIT4M0587256692N</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437472 - KIT4M05872565VJK</t>
         </is>
       </c>
       <c r="C301" s="3" t="n">
@@ -16446,12 +16446,12 @@
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0587256692N</t>
+          <t>KIT4M05872565VJK</t>
         </is>
       </c>
       <c r="F301" s="4" t="inlineStr">
         <is>
-          <t>816072</t>
+          <t>816109</t>
         </is>
       </c>
       <c r="G301" s="5" t="inlineStr">
@@ -16541,7 +16541,7 @@
       </c>
       <c r="B303" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437552 - KIT4M05872586VCH</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649992 - KIT4M05413809J58</t>
         </is>
       </c>
       <c r="C303" s="3" t="n">
@@ -16552,12 +16552,12 @@
       </c>
       <c r="E303" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872586VCH</t>
+          <t>KIT4M05413809J58</t>
         </is>
       </c>
       <c r="F303" s="4" t="inlineStr">
         <is>
-          <t>816068</t>
+          <t>812805</t>
         </is>
       </c>
       <c r="G303" s="5" t="inlineStr">
@@ -16594,7 +16594,7 @@
       </c>
       <c r="B304" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 021437562 - KIT4M05872583P58</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437962 - KIT4M05799706Z6R</t>
         </is>
       </c>
       <c r="C304" s="3" t="n">
@@ -16605,12 +16605,12 @@
       </c>
       <c r="E304" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872583P58</t>
+          <t>KIT4M05799706Z6R</t>
         </is>
       </c>
       <c r="F304" s="4" t="inlineStr">
         <is>
-          <t>816069</t>
+          <t>816273</t>
         </is>
       </c>
       <c r="G304" s="5" t="inlineStr">
@@ -16647,7 +16647,7 @@
       </c>
       <c r="B305" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649982 - KIT4M05413823B5P</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438292 - KIt4m058725108K2</t>
         </is>
       </c>
       <c r="C305" s="3" t="n">
@@ -16658,12 +16658,12 @@
       </c>
       <c r="E305" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413823B5P</t>
+          <t>KIT4M058725108K2</t>
         </is>
       </c>
       <c r="F305" s="4" t="inlineStr">
         <is>
-          <t>812837</t>
+          <t>816287</t>
         </is>
       </c>
       <c r="G305" s="5" t="inlineStr">
@@ -16700,7 +16700,7 @@
       </c>
       <c r="B306" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649992 - KIT4M05413809J58</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649982 - KIT4M05413823B5P</t>
         </is>
       </c>
       <c r="C306" s="3" t="n">
@@ -16711,12 +16711,12 @@
       </c>
       <c r="E306" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413809J58</t>
+          <t>KIT4M05413823B5P</t>
         </is>
       </c>
       <c r="F306" s="4" t="inlineStr">
         <is>
-          <t>812805</t>
+          <t>812837</t>
         </is>
       </c>
       <c r="G306" s="5" t="inlineStr">
@@ -16806,7 +16806,7 @@
       </c>
       <c r="B308" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491828XWF</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491824JCK</t>
         </is>
       </c>
       <c r="C308" s="3" t="n">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E308" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491828XWF</t>
+          <t>KIT4M06491824JCK</t>
         </is>
       </c>
       <c r="F308" s="4" t="inlineStr">
         <is>
-          <t>816387</t>
+          <t>816413</t>
         </is>
       </c>
       <c r="G308" s="5" t="inlineStr">
@@ -16912,7 +16912,7 @@
       </c>
       <c r="B310" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649702 - KIT4M04604741P2X</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491812JDV</t>
         </is>
       </c>
       <c r="C310" s="3" t="n">
@@ -16923,12 +16923,12 @@
       </c>
       <c r="E310" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604741P2X</t>
+          <t>KIT4M06491812JDV</t>
         </is>
       </c>
       <c r="F310" s="4" t="inlineStr">
         <is>
-          <t>809871</t>
+          <t>816409</t>
         </is>
       </c>
       <c r="G310" s="5" t="inlineStr">
@@ -17018,7 +17018,7 @@
       </c>
       <c r="B312" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M0649181062D</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491828XWF</t>
         </is>
       </c>
       <c r="C312" s="3" t="n">
@@ -17029,12 +17029,12 @@
       </c>
       <c r="E312" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0649181062D</t>
+          <t>KIT4M06491828XWF</t>
         </is>
       </c>
       <c r="F312" s="4" t="inlineStr">
         <is>
-          <t>816388</t>
+          <t>816387</t>
         </is>
       </c>
       <c r="G312" s="5" t="inlineStr">
@@ -17071,7 +17071,7 @@
       </c>
       <c r="B313" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491812JDV</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491811JB5</t>
         </is>
       </c>
       <c r="C313" s="3" t="n">
@@ -17082,12 +17082,12 @@
       </c>
       <c r="E313" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491812JDV</t>
+          <t>KIT4M06491811JB5</t>
         </is>
       </c>
       <c r="F313" s="4" t="inlineStr">
         <is>
-          <t>816409</t>
+          <t>816411</t>
         </is>
       </c>
       <c r="G313" s="5" t="inlineStr">
@@ -17124,7 +17124,7 @@
       </c>
       <c r="B314" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491809ZR6</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491805F7Z</t>
         </is>
       </c>
       <c r="C314" s="3" t="n">
@@ -17135,12 +17135,12 @@
       </c>
       <c r="E314" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491809ZR6</t>
+          <t>KIT4M06491805F7Z</t>
         </is>
       </c>
       <c r="F314" s="4" t="inlineStr">
         <is>
-          <t>816402</t>
+          <t>816382</t>
         </is>
       </c>
       <c r="G314" s="5" t="inlineStr">
@@ -17177,7 +17177,7 @@
       </c>
       <c r="B315" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437442 - KIT4M05872584M6H</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491809ZR6</t>
         </is>
       </c>
       <c r="C315" s="3" t="n">
@@ -17188,12 +17188,12 @@
       </c>
       <c r="E315" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872584M6H</t>
+          <t>KIT4M06491809ZR6</t>
         </is>
       </c>
       <c r="F315" s="4" t="inlineStr">
         <is>
-          <t>816096</t>
+          <t>816402</t>
         </is>
       </c>
       <c r="G315" s="5" t="inlineStr">
@@ -17230,7 +17230,7 @@
       </c>
       <c r="B316" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491794MTJ</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437442 - KIT4M05872584M6H</t>
         </is>
       </c>
       <c r="C316" s="3" t="n">
@@ -17241,12 +17241,12 @@
       </c>
       <c r="E316" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491794MTJ</t>
+          <t>KIT4M05872584M6H</t>
         </is>
       </c>
       <c r="F316" s="4" t="inlineStr">
         <is>
-          <t>816375</t>
+          <t>816096</t>
         </is>
       </c>
       <c r="G316" s="5" t="inlineStr">
@@ -17283,7 +17283,7 @@
       </c>
       <c r="B317" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437652 - KIT4M05872551G9S</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491794MTJ</t>
         </is>
       </c>
       <c r="C317" s="3" t="n">
@@ -17294,12 +17294,12 @@
       </c>
       <c r="E317" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872551G9S</t>
+          <t>KIT4M06491794MTJ</t>
         </is>
       </c>
       <c r="F317" s="4" t="inlineStr">
         <is>
-          <t>816180</t>
+          <t>816375</t>
         </is>
       </c>
       <c r="G317" s="5" t="inlineStr">
@@ -17325,7 +17325,7 @@
       </c>
       <c r="L317" s="5" t="n"/>
       <c r="M317" s="7" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="318">
@@ -17336,7 +17336,7 @@
       </c>
       <c r="B318" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437762 - KIT4M05872564MCF</t>
+          <t>SS - 05900510 - Los Angeles CA  - 021437562 - KIT4M05872583P58</t>
         </is>
       </c>
       <c r="C318" s="3" t="n">
@@ -17347,12 +17347,12 @@
       </c>
       <c r="E318" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872564MCF</t>
+          <t>KIT4M05872583P58</t>
         </is>
       </c>
       <c r="F318" s="4" t="inlineStr">
         <is>
-          <t>816203</t>
+          <t>816069</t>
         </is>
       </c>
       <c r="G318" s="5" t="inlineStr">
@@ -17378,7 +17378,7 @@
       </c>
       <c r="L318" s="5" t="n"/>
       <c r="M318" s="7" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="319">
@@ -17389,7 +17389,7 @@
       </c>
       <c r="B319" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 021437772 - KIT4M05872563FWB</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M0649181062D</t>
         </is>
       </c>
       <c r="C319" s="3" t="n">
@@ -17400,12 +17400,12 @@
       </c>
       <c r="E319" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872563FWB</t>
+          <t>KIT4M0649181062D</t>
         </is>
       </c>
       <c r="F319" s="4" t="inlineStr">
         <is>
-          <t>816208</t>
+          <t>816388</t>
         </is>
       </c>
       <c r="G319" s="5" t="inlineStr">
@@ -17431,7 +17431,7 @@
       </c>
       <c r="L319" s="5" t="n"/>
       <c r="M319" s="7" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="320">
@@ -17442,7 +17442,7 @@
       </c>
       <c r="B320" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 021437852 - KIT4M0587257292W</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437652 - KIT4M05872551G9S</t>
         </is>
       </c>
       <c r="C320" s="3" t="n">
@@ -17453,12 +17453,12 @@
       </c>
       <c r="E320" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0587257292W</t>
+          <t>KIT4M05872551G9S</t>
         </is>
       </c>
       <c r="F320" s="4" t="inlineStr">
         <is>
-          <t>816207</t>
+          <t>816180</t>
         </is>
       </c>
       <c r="G320" s="5" t="inlineStr">
@@ -17495,7 +17495,7 @@
       </c>
       <c r="B321" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437492 - KIT4M0587256196K</t>
+          <t>SS - 05900510 - Los Angeles, CA - 021437772 - KIT4M05872563FWB</t>
         </is>
       </c>
       <c r="C321" s="3" t="n">
@@ -17506,12 +17506,12 @@
       </c>
       <c r="E321" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0587256196K</t>
+          <t>KIT4M05872563FWB</t>
         </is>
       </c>
       <c r="F321" s="4" t="inlineStr">
         <is>
-          <t>816098</t>
+          <t>816208</t>
         </is>
       </c>
       <c r="G321" s="5" t="inlineStr">
@@ -17654,7 +17654,7 @@
       </c>
       <c r="B324" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649392 - KIT4M05368206BZP</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649772 - KIT4M04475152RGR</t>
         </is>
       </c>
       <c r="C324" s="3" t="n">
@@ -17665,12 +17665,12 @@
       </c>
       <c r="E324" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368206BZP</t>
+          <t>KIT4M04475152RGR</t>
         </is>
       </c>
       <c r="F324" s="4" t="inlineStr">
         <is>
-          <t>810645</t>
+          <t>809861</t>
         </is>
       </c>
       <c r="G324" s="5" t="inlineStr">
@@ -17707,7 +17707,7 @@
       </c>
       <c r="B325" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437972 - KIT4M06490327GMP</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064917936NF</t>
         </is>
       </c>
       <c r="C325" s="3" t="n">
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E325" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06490327GMP</t>
+          <t>KIT4M064917936NF</t>
         </is>
       </c>
       <c r="F325" s="4" t="inlineStr">
         <is>
-          <t>816199</t>
+          <t>816404</t>
         </is>
       </c>
       <c r="G325" s="5" t="inlineStr">
@@ -17760,7 +17760,7 @@
       </c>
       <c r="B326" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064917936NF</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020650222 - KIT4M05413790XCD</t>
         </is>
       </c>
       <c r="C326" s="3" t="n">
@@ -17771,12 +17771,12 @@
       </c>
       <c r="E326" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064917936NF</t>
+          <t>KIT4M05413790XCD</t>
         </is>
       </c>
       <c r="F326" s="4" t="inlineStr">
         <is>
-          <t>816404</t>
+          <t>812822</t>
         </is>
       </c>
       <c r="G326" s="5" t="inlineStr">
@@ -17813,7 +17813,7 @@
       </c>
       <c r="B327" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437892 - KIT4M06490321NJX</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437982 - KIT4M05799678R5P</t>
         </is>
       </c>
       <c r="C327" s="3" t="n">
@@ -17824,12 +17824,12 @@
       </c>
       <c r="E327" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06490321NJX</t>
+          <t>KIT4M05799678R5P</t>
         </is>
       </c>
       <c r="F327" s="4" t="inlineStr">
         <is>
-          <t>816219</t>
+          <t>816281</t>
         </is>
       </c>
       <c r="G327" s="5" t="inlineStr">
@@ -17866,7 +17866,7 @@
       </c>
       <c r="B328" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438142  - KIT4M05799685DG5</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437702 - KIT4M05872515PJT</t>
         </is>
       </c>
       <c r="C328" s="3" t="n">
@@ -17877,12 +17877,12 @@
       </c>
       <c r="E328" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799685DG5</t>
+          <t>KIT4M05872515PJT</t>
         </is>
       </c>
       <c r="F328" s="4" t="inlineStr">
         <is>
-          <t>816271</t>
+          <t>816218</t>
         </is>
       </c>
       <c r="G328" s="5" t="inlineStr">
@@ -17919,7 +17919,7 @@
       </c>
       <c r="B329" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438212 - KIT4M058725047FZ</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438062 - KIT4M05799676NNK</t>
         </is>
       </c>
       <c r="C329" s="3" t="n">
@@ -17930,12 +17930,12 @@
       </c>
       <c r="E329" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725047FZ</t>
+          <t>KIT4M05799676NNK</t>
         </is>
       </c>
       <c r="F329" s="4" t="inlineStr">
         <is>
-          <t>816289</t>
+          <t>816283</t>
         </is>
       </c>
       <c r="G329" s="5" t="inlineStr">
@@ -18025,7 +18025,7 @@
       </c>
       <c r="B331" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020955312 - KIT4M0556351956H</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438142  - KIT4M05799685DG5</t>
         </is>
       </c>
       <c r="C331" s="3" t="n">
@@ -18036,12 +18036,12 @@
       </c>
       <c r="E331" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0556351956H</t>
+          <t>KIT4M05799685DG5</t>
         </is>
       </c>
       <c r="F331" s="4" t="inlineStr">
         <is>
-          <t>814477</t>
+          <t>816271</t>
         </is>
       </c>
       <c r="G331" s="5" t="inlineStr">
@@ -18078,7 +18078,7 @@
       </c>
       <c r="B332" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020650222 - KIT4M05413790XCD</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020955312 - KIT4M0556351956H</t>
         </is>
       </c>
       <c r="C332" s="3" t="n">
@@ -18089,12 +18089,12 @@
       </c>
       <c r="E332" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413790XCD</t>
+          <t>KIT4M0556351956H</t>
         </is>
       </c>
       <c r="F332" s="4" t="inlineStr">
         <is>
-          <t>812822</t>
+          <t>814477</t>
         </is>
       </c>
       <c r="G332" s="5" t="inlineStr">
@@ -18131,7 +18131,7 @@
       </c>
       <c r="B333" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437702 - KIT4M05872515PJT</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438212 - KIT4M058725047FZ</t>
         </is>
       </c>
       <c r="C333" s="3" t="n">
@@ -18142,12 +18142,12 @@
       </c>
       <c r="E333" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872515PJT</t>
+          <t>KIT4M058725047FZ</t>
         </is>
       </c>
       <c r="F333" s="4" t="inlineStr">
         <is>
-          <t>816218</t>
+          <t>816289</t>
         </is>
       </c>
       <c r="G333" s="5" t="inlineStr">
@@ -18237,7 +18237,7 @@
       </c>
       <c r="B335" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437982 - KIT4M05799678R5P</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437762 - KIT4M05872564MCF</t>
         </is>
       </c>
       <c r="C335" s="3" t="n">
@@ -18248,12 +18248,12 @@
       </c>
       <c r="E335" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799678R5P</t>
+          <t>KIT4M05872564MCF</t>
         </is>
       </c>
       <c r="F335" s="4" t="inlineStr">
         <is>
-          <t>816281</t>
+          <t>816203</t>
         </is>
       </c>
       <c r="G335" s="5" t="inlineStr">
@@ -18290,7 +18290,7 @@
       </c>
       <c r="B336" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438062 - KIT4M05799676NNK</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437492 - KIT4M0587256196K</t>
         </is>
       </c>
       <c r="C336" s="3" t="n">
@@ -18301,12 +18301,12 @@
       </c>
       <c r="E336" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799676NNK</t>
+          <t>KIT4M0587256196K</t>
         </is>
       </c>
       <c r="F336" s="4" t="inlineStr">
         <is>
-          <t>816283</t>
+          <t>816098</t>
         </is>
       </c>
       <c r="G336" s="5" t="inlineStr">
@@ -18343,7 +18343,7 @@
       </c>
       <c r="B337" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437452 - KIT4M05872580C6X</t>
+          <t>SS - 05900510 - Los Angeles, CA - 021437852 - KIT4M0587257292W</t>
         </is>
       </c>
       <c r="C337" s="3" t="n">
@@ -18354,12 +18354,12 @@
       </c>
       <c r="E337" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872580C6X</t>
+          <t>KIT4M0587257292W</t>
         </is>
       </c>
       <c r="F337" s="4" t="inlineStr">
         <is>
-          <t>816097</t>
+          <t>816207</t>
         </is>
       </c>
       <c r="G337" s="5" t="inlineStr">
@@ -18396,7 +18396,7 @@
       </c>
       <c r="B338" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437872 - KIT4M06490319DDN</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437452 - KIT4M05872580C6X</t>
         </is>
       </c>
       <c r="C338" s="3" t="n">
@@ -18407,12 +18407,12 @@
       </c>
       <c r="E338" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06490319DDN</t>
+          <t>KIT4M05872580C6X</t>
         </is>
       </c>
       <c r="F338" s="4" t="inlineStr">
         <is>
-          <t>816220</t>
+          <t>816097</t>
         </is>
       </c>
       <c r="G338" s="5" t="inlineStr">
@@ -18449,7 +18449,7 @@
       </c>
       <c r="B339" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649772 - KIT4M04475152RGR</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437972 - KIT4M06490327GMP</t>
         </is>
       </c>
       <c r="C339" s="3" t="n">
@@ -18460,12 +18460,12 @@
       </c>
       <c r="E339" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475152RGR</t>
+          <t>KIT4M06490327GMP</t>
         </is>
       </c>
       <c r="F339" s="4" t="inlineStr">
         <is>
-          <t>809861</t>
+          <t>816199</t>
         </is>
       </c>
       <c r="G339" s="5" t="inlineStr">
@@ -18502,7 +18502,7 @@
       </c>
       <c r="B340" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918068FF</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437872 - KIT4M06490319DDN</t>
         </is>
       </c>
       <c r="C340" s="3" t="n">
@@ -18513,12 +18513,12 @@
       </c>
       <c r="E340" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918068FF</t>
+          <t>KIT4M06490319DDN</t>
         </is>
       </c>
       <c r="F340" s="4" t="inlineStr">
         <is>
-          <t>816400</t>
+          <t>816220</t>
         </is>
       </c>
       <c r="G340" s="5" t="inlineStr">
@@ -18555,7 +18555,7 @@
       </c>
       <c r="B341" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649382 - KIT4M05368219KRH</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918068FF</t>
         </is>
       </c>
       <c r="C341" s="3" t="n">
@@ -18566,12 +18566,12 @@
       </c>
       <c r="E341" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368219KRH</t>
+          <t>KIT4M064918068FF</t>
         </is>
       </c>
       <c r="F341" s="4" t="inlineStr">
         <is>
-          <t>810646</t>
+          <t>816400</t>
         </is>
       </c>
       <c r="G341" s="5" t="inlineStr">
@@ -18608,7 +18608,7 @@
       </c>
       <c r="B342" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020649472-KIT4M05413795QHK</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437892 - KIT4M06490321NJX</t>
         </is>
       </c>
       <c r="C342" s="3" t="n">
@@ -18619,12 +18619,12 @@
       </c>
       <c r="E342" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413795QHK</t>
+          <t>KIT4M06490321NJX</t>
         </is>
       </c>
       <c r="F342" s="4" t="inlineStr">
         <is>
-          <t>812801</t>
+          <t>816219</t>
         </is>
       </c>
       <c r="G342" s="5" t="inlineStr">
@@ -18650,7 +18650,7 @@
       </c>
       <c r="L342" s="5" t="n"/>
       <c r="M342" s="7" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="343">
@@ -18661,7 +18661,7 @@
       </c>
       <c r="B343" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437642 - KIT4M05872590N8X</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649382 - KIT4M05368219KRH</t>
         </is>
       </c>
       <c r="C343" s="3" t="n">
@@ -18672,12 +18672,12 @@
       </c>
       <c r="E343" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872590N8X</t>
+          <t>KIT4M05368219KRH</t>
         </is>
       </c>
       <c r="F343" s="4" t="inlineStr">
         <is>
-          <t>816204</t>
+          <t>810646</t>
         </is>
       </c>
       <c r="G343" s="5" t="inlineStr">
@@ -18703,7 +18703,7 @@
       </c>
       <c r="L343" s="5" t="n"/>
       <c r="M343" s="7" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="344">
@@ -18714,7 +18714,7 @@
       </c>
       <c r="B344" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649232 - KIT4P0006563862J</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437642 - KIT4M05872590N8X</t>
         </is>
       </c>
       <c r="C344" s="3" t="n">
@@ -18725,17 +18725,17 @@
       </c>
       <c r="E344" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0006563862J</t>
+          <t>KIT4M05872590N8X</t>
         </is>
       </c>
       <c r="F344" s="4" t="inlineStr">
         <is>
-          <t>812927</t>
+          <t>816204</t>
         </is>
       </c>
       <c r="G344" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H344" s="5" t="inlineStr">
@@ -18756,7 +18756,7 @@
       </c>
       <c r="L344" s="5" t="n"/>
       <c r="M344" s="7" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="345">
@@ -18820,7 +18820,7 @@
       </c>
       <c r="B346" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437922 - KIT4M05872496MW6</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649232 - KIT4P0006563862J</t>
         </is>
       </c>
       <c r="C346" s="3" t="n">
@@ -18831,17 +18831,17 @@
       </c>
       <c r="E346" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872496MW6</t>
+          <t>KIT4P0006563862J</t>
         </is>
       </c>
       <c r="F346" s="4" t="inlineStr">
         <is>
-          <t>816206</t>
+          <t>812927</t>
         </is>
       </c>
       <c r="G346" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H346" s="5" t="inlineStr">
@@ -18862,7 +18862,7 @@
       </c>
       <c r="L346" s="5" t="n"/>
       <c r="M346" s="7" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="347">
@@ -18926,7 +18926,7 @@
       </c>
       <c r="B348" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438202 - KIT4M05872506TTB</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649952 - KIT4M05413782GHW</t>
         </is>
       </c>
       <c r="C348" s="3" t="n">
@@ -18937,12 +18937,12 @@
       </c>
       <c r="E348" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872506TTB</t>
+          <t>KIT4M05413782GHW</t>
         </is>
       </c>
       <c r="F348" s="4" t="inlineStr">
         <is>
-          <t>816082</t>
+          <t>812835</t>
         </is>
       </c>
       <c r="G348" s="5" t="inlineStr">
@@ -18979,7 +18979,7 @@
       </c>
       <c r="B349" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955442 - KIT4M05563503XXP</t>
+          <t>STS - 05900510 - Los Angeles CA - 020650092 - KIT4M05413830JN7</t>
         </is>
       </c>
       <c r="C349" s="3" t="n">
@@ -18990,12 +18990,12 @@
       </c>
       <c r="E349" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563503XXP</t>
+          <t>KIT4M05413830JN7</t>
         </is>
       </c>
       <c r="F349" s="4" t="inlineStr">
         <is>
-          <t>814430</t>
+          <t>810105</t>
         </is>
       </c>
       <c r="G349" s="5" t="inlineStr">
@@ -19032,7 +19032,7 @@
       </c>
       <c r="B350" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955162 - KIT4M05563554WCW</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955442 - KIT4M05563503XXP</t>
         </is>
       </c>
       <c r="C350" s="3" t="n">
@@ -19043,12 +19043,12 @@
       </c>
       <c r="E350" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563554WCW</t>
+          <t>KIT4M05563503XXP</t>
         </is>
       </c>
       <c r="F350" s="4" t="inlineStr">
         <is>
-          <t>814444</t>
+          <t>814430</t>
         </is>
       </c>
       <c r="G350" s="5" t="inlineStr">
@@ -19085,7 +19085,7 @@
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>USPS - 05900510 - Los Angeles CA - CW6892232 - KIT4P00084601T5F</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955162 - KIT4M05563554WCW</t>
         </is>
       </c>
       <c r="C351" s="3" t="n">
@@ -19096,17 +19096,17 @@
       </c>
       <c r="E351" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00084601T5F</t>
+          <t>KIT4M05563554WCW</t>
         </is>
       </c>
       <c r="F351" s="4" t="inlineStr">
         <is>
-          <t>816335</t>
+          <t>814444</t>
         </is>
       </c>
       <c r="G351" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H351" s="5" t="inlineStr">
@@ -19138,7 +19138,7 @@
       </c>
       <c r="B352" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955562 - KIT4M05563505WPS</t>
+          <t>USPS - 05900510 - Los Angeles CA - CW6892232 - KIT4P00084601T5F</t>
         </is>
       </c>
       <c r="C352" s="3" t="n">
@@ -19149,17 +19149,17 @@
       </c>
       <c r="E352" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563505WPS</t>
+          <t>KIT4P00084601T5F</t>
         </is>
       </c>
       <c r="F352" s="4" t="inlineStr">
         <is>
-          <t>814448</t>
+          <t>816335</t>
         </is>
       </c>
       <c r="G352" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H352" s="5" t="inlineStr">
@@ -19244,7 +19244,7 @@
       </c>
       <c r="B354" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649612 - KIT4M05413827DC4</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955562 - KIT4M05563505WPS</t>
         </is>
       </c>
       <c r="C354" s="3" t="n">
@@ -19255,12 +19255,12 @@
       </c>
       <c r="E354" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413827DC4</t>
+          <t>KIT4M05563505WPS</t>
         </is>
       </c>
       <c r="F354" s="4" t="inlineStr">
         <is>
-          <t>812829</t>
+          <t>814448</t>
         </is>
       </c>
       <c r="G354" s="5" t="inlineStr">
@@ -19297,7 +19297,7 @@
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482701114 - KIT4M03476114VCM</t>
+          <t>SMA - 05900510 - Los Angeles CA - CW6892232 - KIT4P000832637V6</t>
         </is>
       </c>
       <c r="C355" s="3" t="n">
@@ -19308,17 +19308,17 @@
       </c>
       <c r="E355" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03476114VCM</t>
+          <t>KIT4P000832637V6</t>
         </is>
       </c>
       <c r="F355" s="4" t="inlineStr">
         <is>
-          <t>809613</t>
+          <t>816334</t>
         </is>
       </c>
       <c r="G355" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H355" s="5" t="inlineStr">
@@ -19350,7 +19350,7 @@
       </c>
       <c r="B356" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827011116 - KIT4M02578775B9Q</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482701114 - KIT4M03476114VCM</t>
         </is>
       </c>
       <c r="C356" s="3" t="n">
@@ -19361,12 +19361,12 @@
       </c>
       <c r="E356" s="2" t="inlineStr">
         <is>
-          <t>KIT4M02578775B9Q</t>
+          <t>KIT4M03476114VCM</t>
         </is>
       </c>
       <c r="F356" s="4" t="inlineStr">
         <is>
-          <t>809611</t>
+          <t>809613</t>
         </is>
       </c>
       <c r="G356" s="5" t="inlineStr">
@@ -19403,7 +19403,7 @@
       </c>
       <c r="B357" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - CW6892232 - KIT4P000832637V6</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649922 - KIT4M05413780XFH</t>
         </is>
       </c>
       <c r="C357" s="3" t="n">
@@ -19414,17 +19414,17 @@
       </c>
       <c r="E357" s="2" t="inlineStr">
         <is>
-          <t>KIT4P000832637V6</t>
+          <t>KIT4M05413780XFH</t>
         </is>
       </c>
       <c r="F357" s="4" t="inlineStr">
         <is>
-          <t>816334</t>
+          <t>812833</t>
         </is>
       </c>
       <c r="G357" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H357" s="5" t="inlineStr">
@@ -19456,7 +19456,7 @@
       </c>
       <c r="B358" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649922 - KIT4M05413780XFH</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438202 - KIT4M05872506TTB</t>
         </is>
       </c>
       <c r="C358" s="3" t="n">
@@ -19467,12 +19467,12 @@
       </c>
       <c r="E358" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413780XFH</t>
+          <t>KIT4M05872506TTB</t>
         </is>
       </c>
       <c r="F358" s="4" t="inlineStr">
         <is>
-          <t>812833</t>
+          <t>816082</t>
         </is>
       </c>
       <c r="G358" s="5" t="inlineStr">
@@ -19509,7 +19509,7 @@
       </c>
       <c r="B359" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438012 - KIT4M05799715GJ2</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437922 - KIT4M05872496MW6</t>
         </is>
       </c>
       <c r="C359" s="3" t="n">
@@ -19520,16 +19520,24 @@
       </c>
       <c r="E359" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799715GJ2</t>
-        </is>
-      </c>
-      <c r="F359" s="8" t="n"/>
+          <t>KIT4M05872496MW6</t>
+        </is>
+      </c>
+      <c r="F359" s="4" t="inlineStr">
+        <is>
+          <t>816206</t>
+        </is>
+      </c>
       <c r="G359" s="5" t="inlineStr">
         <is>
           <t>Mini</t>
         </is>
       </c>
-      <c r="H359" s="5" t="n"/>
+      <c r="H359" s="5" t="inlineStr">
+        <is>
+          <t>Master Serial List</t>
+        </is>
+      </c>
       <c r="I359" s="6" t="n">
         <v>46235</v>
       </c>
@@ -19554,7 +19562,7 @@
       </c>
       <c r="B360" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649952 - KIT4M05413782GHW</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438012 - KIT4M05799715GJ2</t>
         </is>
       </c>
       <c r="C360" s="3" t="n">
@@ -19565,24 +19573,16 @@
       </c>
       <c r="E360" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413782GHW</t>
-        </is>
-      </c>
-      <c r="F360" s="4" t="inlineStr">
-        <is>
-          <t>812835</t>
-        </is>
-      </c>
+          <t>KIT4M05799715GJ2</t>
+        </is>
+      </c>
+      <c r="F360" s="8" t="n"/>
       <c r="G360" s="5" t="inlineStr">
         <is>
           <t>Mini</t>
         </is>
       </c>
-      <c r="H360" s="5" t="inlineStr">
-        <is>
-          <t>Master Serial List</t>
-        </is>
-      </c>
+      <c r="H360" s="5" t="n"/>
       <c r="I360" s="6" t="n">
         <v>46235</v>
       </c>
@@ -19607,7 +19607,7 @@
       </c>
       <c r="B361" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020650032-KIT4M05413802FVN</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649502 - KIT4M05413801QJB</t>
         </is>
       </c>
       <c r="C361" s="3" t="n">
@@ -19618,12 +19618,12 @@
       </c>
       <c r="E361" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413802FVN</t>
+          <t>KIT4M05413801QJB</t>
         </is>
       </c>
       <c r="F361" s="4" t="inlineStr">
         <is>
-          <t>812813</t>
+          <t>812824</t>
         </is>
       </c>
       <c r="G361" s="5" t="inlineStr">
@@ -19660,7 +19660,7 @@
       </c>
       <c r="B362" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649502 - KIT4M05413801QJB</t>
+          <t>SMRT-05900510-Los Angeles CA-020650032-KIT4M05413802FVN</t>
         </is>
       </c>
       <c r="C362" s="3" t="n">
@@ -19671,12 +19671,12 @@
       </c>
       <c r="E362" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413801QJB</t>
+          <t>KIT4M05413802FVN</t>
         </is>
       </c>
       <c r="F362" s="4" t="inlineStr">
         <is>
-          <t>812824</t>
+          <t>812813</t>
         </is>
       </c>
       <c r="G362" s="5" t="inlineStr">
@@ -19713,7 +19713,7 @@
       </c>
       <c r="B363" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955512 - KIT4M055635779MM</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649612 - KIT4M05413827DC4</t>
         </is>
       </c>
       <c r="C363" s="3" t="n">
@@ -19724,12 +19724,12 @@
       </c>
       <c r="E363" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635779MM</t>
+          <t>KIT4M05413827DC4</t>
         </is>
       </c>
       <c r="F363" s="4" t="inlineStr">
         <is>
-          <t>814487</t>
+          <t>812829</t>
         </is>
       </c>
       <c r="G363" s="5" t="inlineStr">
@@ -19766,7 +19766,7 @@
       </c>
       <c r="B364" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020650092 - KIT4M05413830JN7</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955512 - KIT4M055635779MM</t>
         </is>
       </c>
       <c r="C364" s="3" t="n">
@@ -19777,12 +19777,12 @@
       </c>
       <c r="E364" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413830JN7</t>
+          <t>KIT4M055635779MM</t>
         </is>
       </c>
       <c r="F364" s="4" t="inlineStr">
         <is>
-          <t>810105</t>
+          <t>814487</t>
         </is>
       </c>
       <c r="G364" s="5" t="inlineStr">
@@ -19925,7 +19925,7 @@
       </c>
       <c r="B367" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649332 - KIT4M05368340DMZ</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020649662 - KIT4M05413772977</t>
         </is>
       </c>
       <c r="C367" s="3" t="n">
@@ -19936,12 +19936,12 @@
       </c>
       <c r="E367" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368340DMZ</t>
+          <t>KIT4M05413772977</t>
         </is>
       </c>
       <c r="F367" s="4" t="inlineStr">
         <is>
-          <t>810649</t>
+          <t>812841</t>
         </is>
       </c>
       <c r="G367" s="5" t="inlineStr">
@@ -19978,7 +19978,7 @@
       </c>
       <c r="B368" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020649662 - KIT4M05413772977</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649332 - KIT4M05368340DMZ</t>
         </is>
       </c>
       <c r="C368" s="3" t="n">
@@ -19989,12 +19989,12 @@
       </c>
       <c r="E368" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413772977</t>
+          <t>KIT4M05368340DMZ</t>
         </is>
       </c>
       <c r="F368" s="4" t="inlineStr">
         <is>
-          <t>812841</t>
+          <t>810649</t>
         </is>
       </c>
       <c r="G368" s="5" t="inlineStr">
@@ -20219,7 +20219,7 @@
     <row r="381">
       <c r="A381" s="15" t="inlineStr">
         <is>
-          <t>Generated 2026-08-29 09:44 by build_starlink_usage.py</t>
+          <t>Generated 2026-08-29 21:09 by build_starlink_usage.py</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_Current_by_Kit.xlsx
+++ b/Starlink_Usage_Current_by_Kit.xlsx
@@ -630,7 +630,7 @@
       </c>
       <c r="L2" s="5" t="n"/>
       <c r="M2" s="7" t="n">
-        <v>2498.63</v>
+        <v>2530.49</v>
       </c>
     </row>
     <row r="3">
@@ -683,7 +683,7 @@
       </c>
       <c r="L3" s="5" t="n"/>
       <c r="M3" s="7" t="n">
-        <v>2290.97</v>
+        <v>2298.41</v>
       </c>
     </row>
     <row r="4">
@@ -736,7 +736,7 @@
       </c>
       <c r="L4" s="5" t="n"/>
       <c r="M4" s="7" t="n">
-        <v>1637.22</v>
+        <v>1643.3</v>
       </c>
     </row>
     <row r="5">
@@ -842,7 +842,7 @@
       </c>
       <c r="L6" s="5" t="n"/>
       <c r="M6" s="7" t="n">
-        <v>1125.65</v>
+        <v>1133.29</v>
       </c>
     </row>
     <row r="7">
@@ -853,7 +853,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955032 - KIT4P00073954DZ8</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437292 - KIT4P000832806P4</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
@@ -864,12 +864,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073954DZ8</t>
+          <t>KIT4P000832806P4</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>814644</t>
+          <t>816228</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="L7" s="5" t="n"/>
       <c r="M7" s="7" t="n">
-        <v>996.03</v>
+        <v>1018.27</v>
       </c>
     </row>
     <row r="8">
@@ -906,7 +906,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437292 - KIT4P000832806P4</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955032 - KIT4P00073954DZ8</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
@@ -917,12 +917,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>KIT4P000832806P4</t>
+          <t>KIT4P00073954DZ8</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>816228</t>
+          <t>814644</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="L8" s="5" t="n"/>
       <c r="M8" s="7" t="n">
-        <v>941.38</v>
+        <v>1005.66</v>
       </c>
     </row>
     <row r="9">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="L13" s="5" t="n"/>
       <c r="M13" s="7" t="n">
-        <v>743.11</v>
+        <v>747.83</v>
       </c>
     </row>
     <row r="14">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L14" s="5" t="n"/>
       <c r="M14" s="7" t="n">
-        <v>730.46</v>
+        <v>730.71</v>
       </c>
     </row>
     <row r="15">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="L15" s="5" t="n"/>
       <c r="M15" s="7" t="n">
-        <v>687.97</v>
+        <v>694.25</v>
       </c>
     </row>
     <row r="16">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="L16" s="5" t="n"/>
       <c r="M16" s="7" t="n">
-        <v>678.92</v>
+        <v>689.3</v>
       </c>
     </row>
     <row r="17">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="L17" s="5" t="n"/>
       <c r="M17" s="7" t="n">
-        <v>608.39</v>
+        <v>613.42</v>
       </c>
     </row>
     <row r="18">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="L18" s="5" t="n"/>
       <c r="M18" s="7" t="n">
-        <v>529.85</v>
+        <v>532.45</v>
       </c>
     </row>
     <row r="19">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020650002 - KIT4M05413770WCC</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955082 - KIT4P000739124KF</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
@@ -1553,17 +1553,17 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413770WCC</t>
+          <t>KIT4P000739124KF</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>812819</t>
+          <t>814640</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="L20" s="5" t="n"/>
       <c r="M20" s="7" t="n">
-        <v>462.9</v>
+        <v>463.25</v>
       </c>
     </row>
     <row r="21">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955082 - KIT4P000739124KF</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020650002 - KIT4M05413770WCC</t>
         </is>
       </c>
       <c r="C21" s="3" t="n">
@@ -1606,17 +1606,17 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>KIT4P000739124KF</t>
+          <t>KIT4M05413770WCC</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>814640</t>
+          <t>812819</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="L21" s="5" t="n"/>
       <c r="M21" s="7" t="n">
-        <v>451.32</v>
+        <v>462.9</v>
       </c>
     </row>
     <row r="22">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649972 - KIT4M05413791FK5</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955072 - KIT4P0007258645B</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
@@ -1659,17 +1659,17 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413791FK5</t>
+          <t>KIT4P0007258645B</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>812842</t>
+          <t>814495</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="L22" s="5" t="n"/>
       <c r="M22" s="7" t="n">
-        <v>380.11</v>
+        <v>401.08</v>
       </c>
     </row>
     <row r="23">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955072 - KIT4P0007258645B</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649972 - KIT4M05413791FK5</t>
         </is>
       </c>
       <c r="C23" s="3" t="n">
@@ -1712,17 +1712,17 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0007258645B</t>
+          <t>KIT4M05413791FK5</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>814495</t>
+          <t>812842</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="L23" s="5" t="n"/>
       <c r="M23" s="7" t="n">
-        <v>376.27</v>
+        <v>380.11</v>
       </c>
     </row>
     <row r="24">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649402 - KIT4M05368194X6V</t>
+          <t>SMRT-05900510-LOS ANGELES CA-020955062-KIT4P00073915XX6</t>
         </is>
       </c>
       <c r="C26" s="3" t="n">
@@ -1871,17 +1871,17 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368194X6V</t>
+          <t>KIT4P00073915XX6</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>810644</t>
+          <t>814643</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="L26" s="5" t="n"/>
       <c r="M26" s="7" t="n">
-        <v>296.73</v>
+        <v>306.11</v>
       </c>
     </row>
     <row r="27">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649882 - KIT4M054137997HR</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649402 - KIT4M05368194X6V</t>
         </is>
       </c>
       <c r="C27" s="3" t="n">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137997HR</t>
+          <t>KIT4M05368194X6V</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>812825</t>
+          <t>810644</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="L27" s="5" t="n"/>
       <c r="M27" s="7" t="n">
-        <v>275.65</v>
+        <v>296.73</v>
       </c>
     </row>
     <row r="28">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-LOS ANGELES CA-020955062-KIT4P00073915XX6</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649882 - KIT4M054137997HR</t>
         </is>
       </c>
       <c r="C28" s="3" t="n">
@@ -1977,17 +1977,17 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073915XX6</t>
+          <t>KIT4M054137997HR</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>814643</t>
+          <t>812825</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="L28" s="5" t="n"/>
       <c r="M28" s="7" t="n">
-        <v>272.4</v>
+        <v>275.65</v>
       </c>
     </row>
     <row r="29">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="L29" s="5" t="n"/>
       <c r="M29" s="7" t="n">
-        <v>268.13</v>
+        <v>269.87</v>
       </c>
     </row>
     <row r="30">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="L30" s="5" t="n"/>
       <c r="M30" s="7" t="n">
-        <v>258.21</v>
+        <v>259.24</v>
       </c>
     </row>
     <row r="31">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="L33" s="5" t="n"/>
       <c r="M33" s="7" t="n">
-        <v>233.2</v>
+        <v>238.45</v>
       </c>
     </row>
     <row r="34">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955522 - KIT4M05563504MBB</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955042 - KIT4P00072391SZM</t>
         </is>
       </c>
       <c r="C35" s="3" t="n">
@@ -2348,17 +2348,17 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563504MBB</t>
+          <t>KIT4P00072391SZM</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>814460</t>
+          <t>814493</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="L35" s="5" t="n"/>
       <c r="M35" s="7" t="n">
-        <v>183.43</v>
+        <v>204.14</v>
       </c>
     </row>
     <row r="36">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482701116 - KIT4M03986275Q4M</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955522 - KIT4M05563504MBB</t>
         </is>
       </c>
       <c r="C36" s="3" t="n">
@@ -2401,12 +2401,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03986275Q4M</t>
+          <t>KIT4M05563504MBB</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>809621</t>
+          <t>814460</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="L36" s="5" t="n"/>
       <c r="M36" s="7" t="n">
-        <v>174.86</v>
+        <v>198.62</v>
       </c>
     </row>
     <row r="37">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955322 - KIT4M055635305RS</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482701116 - KIT4M03986275Q4M</t>
         </is>
       </c>
       <c r="C37" s="3" t="n">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635305RS</t>
+          <t>KIT4M03986275Q4M</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>814440</t>
+          <t>809621</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="L37" s="5" t="n"/>
       <c r="M37" s="7" t="n">
-        <v>170.78</v>
+        <v>186.16</v>
       </c>
     </row>
     <row r="38">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="L38" s="5" t="n"/>
       <c r="M38" s="7" t="n">
-        <v>170.01</v>
+        <v>172.99</v>
       </c>
     </row>
     <row r="39">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955042 - KIT4P00072391SZM</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955322 - KIT4M055635305RS</t>
         </is>
       </c>
       <c r="C39" s="3" t="n">
@@ -2560,17 +2560,17 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00072391SZM</t>
+          <t>KIT4M055635305RS</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>814493</t>
+          <t>814440</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="L39" s="5" t="n"/>
       <c r="M39" s="7" t="n">
-        <v>169.46</v>
+        <v>171.56</v>
       </c>
     </row>
     <row r="40">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="L40" s="5" t="n"/>
       <c r="M40" s="7" t="n">
-        <v>153.41</v>
+        <v>167.19</v>
       </c>
     </row>
     <row r="41">
@@ -2655,7 +2655,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - CW6578840- KIT4M04475128THH</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649352 - KIT4M05368220FG8</t>
         </is>
       </c>
       <c r="C41" s="3" t="n">
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475128THH</t>
+          <t>KIT4M05368220FG8</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>809860</t>
+          <t>810648</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="L41" s="5" t="n"/>
       <c r="M41" s="7" t="n">
-        <v>148.9</v>
+        <v>149.34</v>
       </c>
     </row>
     <row r="42">
@@ -2708,7 +2708,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649352 - KIT4M05368220FG8</t>
+          <t>SS - 05900510 - Los Angeles CA - CW6578840- KIT4M04475128THH</t>
         </is>
       </c>
       <c r="C42" s="3" t="n">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368220FG8</t>
+          <t>KIT4M04475128THH</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>810648</t>
+          <t>809860</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="L42" s="5" t="n"/>
       <c r="M42" s="7" t="n">
-        <v>148.28</v>
+        <v>148.9</v>
       </c>
     </row>
     <row r="43">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="L43" s="5" t="n"/>
       <c r="M43" s="7" t="n">
-        <v>143.2</v>
+        <v>143.46</v>
       </c>
     </row>
     <row r="44">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="L45" s="5" t="n"/>
       <c r="M45" s="7" t="n">
-        <v>129.43</v>
+        <v>129.97</v>
       </c>
     </row>
     <row r="46">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437252 - KIT4P00083897XCW</t>
+          <t>SS - 05900510 - Los Angeles CA - 020650102 - KIT4M054138257Z7</t>
         </is>
       </c>
       <c r="C49" s="3" t="n">
@@ -3090,17 +3090,17 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00083897XCW</t>
+          <t>KIT4M054138257Z7</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>816223</t>
+          <t>810106</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="L49" s="5" t="n"/>
       <c r="M49" s="7" t="n">
-        <v>120.74</v>
+        <v>122.65</v>
       </c>
     </row>
     <row r="50">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020955622 - KIT4M05563549RSR</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437252 - KIT4P00083897XCW</t>
         </is>
       </c>
       <c r="C50" s="3" t="n">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563549RSR</t>
+          <t>KIT4P00083897XCW</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>814483</t>
+          <t>816223</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H50" s="5" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="L50" s="5" t="n"/>
       <c r="M50" s="7" t="n">
-        <v>113.16</v>
+        <v>120.74</v>
       </c>
     </row>
     <row r="51">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649542 - KIT4M05413810Q4Z</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020955622 - KIT4M05563549RSR</t>
         </is>
       </c>
       <c r="C51" s="3" t="n">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413810Q4Z</t>
+          <t>KIT4M05563549RSR</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>812815</t>
+          <t>814483</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="L51" s="5" t="n"/>
       <c r="M51" s="7" t="n">
-        <v>109.7</v>
+        <v>113.16</v>
       </c>
     </row>
     <row r="52">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles, CA-020955372-KIT4M05563537G4G</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020650212 - KIT4M05413779VSD</t>
         </is>
       </c>
       <c r="C52" s="3" t="n">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563537G4G</t>
+          <t>KIT4M05413779VSD</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>814456</t>
+          <t>810103</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="L52" s="5" t="n"/>
       <c r="M52" s="7" t="n">
-        <v>108.22</v>
+        <v>113.12</v>
       </c>
     </row>
     <row r="53">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270111110 - KIT4M03867737P9P</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649542 - KIT4M05413810Q4Z</t>
         </is>
       </c>
       <c r="C53" s="3" t="n">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03867737P9P</t>
+          <t>KIT4M05413810Q4Z</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>809622</t>
+          <t>812815</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="L53" s="5" t="n"/>
       <c r="M53" s="7" t="n">
-        <v>108.08</v>
+        <v>109.7</v>
       </c>
     </row>
     <row r="54">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020650212 - KIT4M05413779VSD</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270111110 - KIT4M03867737P9P</t>
         </is>
       </c>
       <c r="C54" s="3" t="n">
@@ -3355,12 +3355,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413779VSD</t>
+          <t>KIT4M03867737P9P</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>810103</t>
+          <t>809622</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="L54" s="5" t="n"/>
       <c r="M54" s="7" t="n">
-        <v>108.04</v>
+        <v>108.88</v>
       </c>
     </row>
     <row r="55">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649782 - KIT4M03986264P49</t>
+          <t>SMRT-05900510-Los Angeles, CA-020955372-KIT4M05563537G4G</t>
         </is>
       </c>
       <c r="C55" s="3" t="n">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03986264P49</t>
+          <t>KIT4M05563537G4G</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>809875</t>
+          <t>814456</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="L55" s="5" t="n"/>
       <c r="M55" s="7" t="n">
-        <v>101.96</v>
+        <v>108.22</v>
       </c>
     </row>
     <row r="56">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020650102 - KIT4M054138257Z7</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649782 - KIT4M03986264P49</t>
         </is>
       </c>
       <c r="C56" s="3" t="n">
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138257Z7</t>
+          <t>KIT4M03986264P49</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>810106</t>
+          <t>809875</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="L56" s="5" t="n"/>
       <c r="M56" s="7" t="n">
-        <v>100.22</v>
+        <v>105.49</v>
       </c>
     </row>
     <row r="57">
@@ -3503,7 +3503,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020650172 - KIT4M05413811F4Q</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955662 - KIT4M05563574ZBN</t>
         </is>
       </c>
       <c r="C57" s="3" t="n">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413811F4Q</t>
+          <t>KIT4M05563574ZBN</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>810104</t>
+          <t>814453</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="L57" s="5" t="n"/>
       <c r="M57" s="7" t="n">
-        <v>99.37</v>
+        <v>103.74</v>
       </c>
     </row>
     <row r="58">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="L58" s="5" t="n"/>
       <c r="M58" s="7" t="n">
-        <v>99.23</v>
+        <v>99.62</v>
       </c>
     </row>
     <row r="59">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955662 - KIT4M05563574ZBN</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020650172 - KIT4M05413811F4Q</t>
         </is>
       </c>
       <c r="C59" s="3" t="n">
@@ -3620,12 +3620,12 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563574ZBN</t>
+          <t>KIT4M05413811F4Q</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>814453</t>
+          <t>810104</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
@@ -3651,7 +3651,7 @@
       </c>
       <c r="L59" s="5" t="n"/>
       <c r="M59" s="7" t="n">
-        <v>96.91</v>
+        <v>99.37</v>
       </c>
     </row>
     <row r="60">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438042 - KIT4M05799686CMX</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955332 - KIT4M05563590ZFQ</t>
         </is>
       </c>
       <c r="C60" s="3" t="n">
@@ -3673,12 +3673,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799686CMX</t>
+          <t>KIT4M05563590ZFQ</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>816282</t>
+          <t>814461</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="L60" s="5" t="n"/>
       <c r="M60" s="7" t="n">
-        <v>94.92</v>
+        <v>95.19</v>
       </c>
     </row>
     <row r="61">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020650232 - KIT4M054138222CP</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438042 - KIT4M05799686CMX</t>
         </is>
       </c>
       <c r="C61" s="3" t="n">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138222CP</t>
+          <t>KIT4M05799686CMX</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>812811</t>
+          <t>816282</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
@@ -3757,7 +3757,7 @@
       </c>
       <c r="L61" s="5" t="n"/>
       <c r="M61" s="7" t="n">
-        <v>93.27</v>
+        <v>94.92</v>
       </c>
     </row>
     <row r="62">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649712 - KIT4M046047397TM</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020650232 - KIT4M054138222CP</t>
         </is>
       </c>
       <c r="C62" s="3" t="n">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047397TM</t>
+          <t>KIT4M054138222CP</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>809863</t>
+          <t>812811</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="L62" s="5" t="n"/>
       <c r="M62" s="7" t="n">
-        <v>90.26000000000001</v>
+        <v>93.27</v>
       </c>
     </row>
     <row r="63">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955472 - KIT4M055635834N7</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649712 - KIT4M046047397TM</t>
         </is>
       </c>
       <c r="C63" s="3" t="n">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635834N7</t>
+          <t>KIT4M046047397TM</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>814462</t>
+          <t>809863</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="L63" s="5" t="n"/>
       <c r="M63" s="7" t="n">
-        <v>89.45</v>
+        <v>92.65000000000001</v>
       </c>
     </row>
     <row r="64">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="L64" s="5" t="n"/>
       <c r="M64" s="7" t="n">
-        <v>88.79000000000001</v>
+        <v>90.26000000000001</v>
       </c>
     </row>
     <row r="65">
@@ -3927,7 +3927,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438092 - KIT4M05799694RW2</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955472 - KIT4M055635834N7</t>
         </is>
       </c>
       <c r="C65" s="3" t="n">
@@ -3938,12 +3938,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799694RW2</t>
+          <t>KIT4M055635834N7</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>816277</t>
+          <t>814462</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="L65" s="5" t="n"/>
       <c r="M65" s="7" t="n">
-        <v>87.29000000000001</v>
+        <v>89.45</v>
       </c>
     </row>
     <row r="66">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955142 - KIT4M05563518ZJD</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438092 - KIT4M05799694RW2</t>
         </is>
       </c>
       <c r="C66" s="3" t="n">
@@ -3991,12 +3991,12 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563518ZJD</t>
+          <t>KIT4M05799694RW2</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>814451</t>
+          <t>816277</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="L66" s="5" t="n"/>
       <c r="M66" s="7" t="n">
-        <v>85.18000000000001</v>
+        <v>89.01000000000001</v>
       </c>
     </row>
     <row r="67">
@@ -4033,7 +4033,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955332 - KIT4M05563590ZFQ</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955142 - KIT4M05563518ZJD</t>
         </is>
       </c>
       <c r="C67" s="3" t="n">
@@ -4044,12 +4044,12 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563590ZFQ</t>
+          <t>KIT4M05563518ZJD</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>814461</t>
+          <t>814451</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="L67" s="5" t="n"/>
       <c r="M67" s="7" t="n">
-        <v>84.56999999999999</v>
+        <v>85.18000000000001</v>
       </c>
     </row>
     <row r="68">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649872 - KIT4M054138175VJ</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955132 - KIT4M055635238J6</t>
         </is>
       </c>
       <c r="C68" s="3" t="n">
@@ -4097,12 +4097,12 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138175VJ</t>
+          <t>KIT4M055635238J6</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>812823</t>
+          <t>814449</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="L68" s="5" t="n"/>
       <c r="M68" s="7" t="n">
-        <v>83.95</v>
+        <v>84.23</v>
       </c>
     </row>
     <row r="69">
@@ -4139,7 +4139,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955132 - KIT4M055635238J6</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649872 - KIT4M054138175VJ</t>
         </is>
       </c>
       <c r="C69" s="3" t="n">
@@ -4150,12 +4150,12 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635238J6</t>
+          <t>KIT4M054138175VJ</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>814449</t>
+          <t>812823</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="L69" s="5" t="n"/>
       <c r="M69" s="7" t="n">
-        <v>82.15000000000001</v>
+        <v>83.95</v>
       </c>
     </row>
     <row r="70">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="L70" s="5" t="n"/>
       <c r="M70" s="7" t="n">
-        <v>80.44</v>
+        <v>81.16</v>
       </c>
     </row>
     <row r="71">
@@ -4287,7 +4287,7 @@
       </c>
       <c r="L71" s="5" t="n"/>
       <c r="M71" s="7" t="n">
-        <v>78.33</v>
+        <v>79.23</v>
       </c>
     </row>
     <row r="72">
@@ -4298,7 +4298,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649562 - KIT4M054138125NW</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437272 - KIT4P0008459589D</t>
         </is>
       </c>
       <c r="C72" s="3" t="n">
@@ -4309,17 +4309,17 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138125NW</t>
+          <t>KIT4P0008459589D</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>812826</t>
+          <t>816222</t>
         </is>
       </c>
       <c r="G72" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H72" s="5" t="inlineStr">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="L72" s="5" t="n"/>
       <c r="M72" s="7" t="n">
-        <v>77.14</v>
+        <v>77.8</v>
       </c>
     </row>
     <row r="73">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955492 - KIT4M05563520SH2</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649562 - KIT4M054138125NW</t>
         </is>
       </c>
       <c r="C73" s="3" t="n">
@@ -4362,12 +4362,12 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563520SH2</t>
+          <t>KIT4M054138125NW</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>814478</t>
+          <t>812826</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="L73" s="5" t="n"/>
       <c r="M73" s="7" t="n">
-        <v>74.56999999999999</v>
+        <v>77.14</v>
       </c>
     </row>
     <row r="74">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955092 - KIT4P00073957GV5</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955492 - KIT4M05563520SH2</t>
         </is>
       </c>
       <c r="C74" s="3" t="n">
@@ -4415,17 +4415,17 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073957GV5</t>
+          <t>KIT4M05563520SH2</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>814642</t>
+          <t>814478</t>
         </is>
       </c>
       <c r="G74" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H74" s="5" t="inlineStr">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="L74" s="5" t="n"/>
       <c r="M74" s="7" t="n">
-        <v>72.86</v>
+        <v>74.56999999999999</v>
       </c>
     </row>
     <row r="75">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles, CA-020955352-KIT4M05563525VC6</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955092 - KIT4P00073957GV5</t>
         </is>
       </c>
       <c r="C75" s="3" t="n">
@@ -4468,17 +4468,17 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563525VC6</t>
+          <t>KIT4P00073957GV5</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>814458</t>
+          <t>814642</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H75" s="5" t="inlineStr">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="L75" s="5" t="n"/>
       <c r="M75" s="7" t="n">
-        <v>71.73999999999999</v>
+        <v>72.91</v>
       </c>
     </row>
     <row r="76">
@@ -4552,7 +4552,7 @@
       </c>
       <c r="L76" s="5" t="n"/>
       <c r="M76" s="7" t="n">
-        <v>70.17</v>
+        <v>72.59999999999999</v>
       </c>
     </row>
     <row r="77">
@@ -4563,7 +4563,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SS - 05900510 - Los Angeles, CA - 020649552 - KIT4M05413835RPF </t>
+          <t>SMRT-05900510-Los Angeles, CA-020955352-KIT4M05563525VC6</t>
         </is>
       </c>
       <c r="C77" s="3" t="n">
@@ -4574,12 +4574,12 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413835RPF</t>
+          <t>KIT4M05563525VC6</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>812827</t>
+          <t>814458</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr">
@@ -4605,7 +4605,7 @@
       </c>
       <c r="L77" s="5" t="n"/>
       <c r="M77" s="7" t="n">
-        <v>69.54000000000001</v>
+        <v>72.45</v>
       </c>
     </row>
     <row r="78">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649272 - KIT4M05413784W4K</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649932 - KIT4M054138324MW</t>
         </is>
       </c>
       <c r="C78" s="3" t="n">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413784W4K</t>
+          <t>KIT4M054138324MW</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>812821</t>
+          <t>812834</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="L78" s="5" t="n"/>
       <c r="M78" s="7" t="n">
-        <v>69.13</v>
+        <v>71.52</v>
       </c>
     </row>
     <row r="79">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955262 - KIT4M05563521ZSX</t>
+          <t xml:space="preserve">SS - 05900510 - Los Angeles, CA - 020649552 - KIT4M05413835RPF </t>
         </is>
       </c>
       <c r="C79" s="3" t="n">
@@ -4680,12 +4680,12 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563521ZSX</t>
+          <t>KIT4M05413835RPF</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>814476</t>
+          <t>812827</t>
         </is>
       </c>
       <c r="G79" s="5" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="L79" s="5" t="n"/>
       <c r="M79" s="7" t="n">
-        <v>68.75</v>
+        <v>70.56</v>
       </c>
     </row>
     <row r="80">
@@ -4722,7 +4722,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649932 - KIT4M054138324MW</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955292 - KIT4M05563531XSB</t>
         </is>
       </c>
       <c r="C80" s="3" t="n">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138324MW</t>
+          <t>KIT4M05563531XSB</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>812834</t>
+          <t>814469</t>
         </is>
       </c>
       <c r="G80" s="5" t="inlineStr">
@@ -4764,7 +4764,7 @@
       </c>
       <c r="L80" s="5" t="n"/>
       <c r="M80" s="7" t="n">
-        <v>68.59</v>
+        <v>69.23</v>
       </c>
     </row>
     <row r="81">
@@ -4775,7 +4775,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649902 - KIT4M05413805MKQ</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649272 - KIT4M05413784W4K</t>
         </is>
       </c>
       <c r="C81" s="3" t="n">
@@ -4786,12 +4786,12 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413805MKQ</t>
+          <t>KIT4M05413784W4K</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>812849</t>
+          <t>812821</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="L81" s="5" t="n"/>
       <c r="M81" s="7" t="n">
-        <v>66.28</v>
+        <v>69.13</v>
       </c>
     </row>
     <row r="82">
@@ -4828,7 +4828,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-LOS ANGELES CA-020955202-KIT4M05563534GZ7</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955262 - KIT4M05563521ZSX</t>
         </is>
       </c>
       <c r="C82" s="3" t="n">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563534GZ7</t>
+          <t>KIT4M05563521ZSX</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>814467</t>
+          <t>814476</t>
         </is>
       </c>
       <c r="G82" s="5" t="inlineStr">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="L82" s="5" t="n"/>
       <c r="M82" s="7" t="n">
-        <v>66.12</v>
+        <v>68.75</v>
       </c>
     </row>
     <row r="83">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955292 - KIT4M05563531XSB</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649902 - KIT4M05413805MKQ</t>
         </is>
       </c>
       <c r="C83" s="3" t="n">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563531XSB</t>
+          <t>KIT4M05413805MKQ</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>814469</t>
+          <t>812849</t>
         </is>
       </c>
       <c r="G83" s="5" t="inlineStr">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="L83" s="5" t="n"/>
       <c r="M83" s="7" t="n">
-        <v>65.68000000000001</v>
+        <v>66.45</v>
       </c>
     </row>
     <row r="84">
@@ -4934,7 +4934,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649342 - KIT4M05413775N9M</t>
+          <t>SMRT-05900510-LOS ANGELES CA-020955202-KIT4M05563534GZ7</t>
         </is>
       </c>
       <c r="C84" s="3" t="n">
@@ -4945,12 +4945,12 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413775N9M</t>
+          <t>KIT4M05563534GZ7</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>812818</t>
+          <t>814467</t>
         </is>
       </c>
       <c r="G84" s="5" t="inlineStr">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="L84" s="5" t="n"/>
       <c r="M84" s="7" t="n">
-        <v>63.82</v>
+        <v>66.15000000000001</v>
       </c>
     </row>
     <row r="85">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020650252 - KIT4M05413820QXJ</t>
+          <t>SS - 05900510 -  Los Angeles CA - 021437622 - KIT4M0587258755W</t>
         </is>
       </c>
       <c r="C85" s="3" t="n">
@@ -4998,12 +4998,12 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413820QXJ</t>
+          <t>KIT4M0587258755W</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>810098</t>
+          <t>816187</t>
         </is>
       </c>
       <c r="G85" s="5" t="inlineStr">
@@ -5029,7 +5029,7 @@
       </c>
       <c r="L85" s="5" t="n"/>
       <c r="M85" s="7" t="n">
-        <v>61.69</v>
+        <v>65.16</v>
       </c>
     </row>
     <row r="86">
@@ -5040,7 +5040,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles, CA-020955582-KIT4M05563593DMC</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649342 - KIT4M05413775N9M</t>
         </is>
       </c>
       <c r="C86" s="3" t="n">
@@ -5051,12 +5051,12 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563593DMC</t>
+          <t>KIT4M05413775N9M</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>814442</t>
+          <t>812818</t>
         </is>
       </c>
       <c r="G86" s="5" t="inlineStr">
@@ -5082,7 +5082,7 @@
       </c>
       <c r="L86" s="5" t="n"/>
       <c r="M86" s="7" t="n">
-        <v>61.16</v>
+        <v>64.45</v>
       </c>
     </row>
     <row r="87">
@@ -5093,7 +5093,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955692 - KIT4M05563579H9F</t>
+          <t>SMRT-05900510-Los Angeles, CA-020955582-KIT4M05563593DMC</t>
         </is>
       </c>
       <c r="C87" s="3" t="n">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563579H9F</t>
+          <t>KIT4M05563593DMC</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>814480</t>
+          <t>814442</t>
         </is>
       </c>
       <c r="G87" s="5" t="inlineStr">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="L87" s="5" t="n"/>
       <c r="M87" s="7" t="n">
-        <v>57.85</v>
+        <v>64.27</v>
       </c>
     </row>
     <row r="88">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020955462 - KIT4M05563513GTF</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437392 - KIT4M05872555BJR</t>
         </is>
       </c>
       <c r="C88" s="3" t="n">
@@ -5157,12 +5157,12 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563513GTF</t>
+          <t>KIT4M05872555BJR</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>814432</t>
+          <t>816074</t>
         </is>
       </c>
       <c r="G88" s="5" t="inlineStr">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="L88" s="5" t="n"/>
       <c r="M88" s="7" t="n">
-        <v>57.75</v>
+        <v>62.09</v>
       </c>
     </row>
     <row r="89">
@@ -5199,7 +5199,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649762 - KIT4M0460475549Z</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020650252 - KIT4M05413820QXJ</t>
         </is>
       </c>
       <c r="C89" s="3" t="n">
@@ -5210,12 +5210,12 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0460475549Z</t>
+          <t>KIT4M05413820QXJ</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>809859</t>
+          <t>810098</t>
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr">
@@ -5241,7 +5241,7 @@
       </c>
       <c r="L89" s="5" t="n"/>
       <c r="M89" s="7" t="n">
-        <v>57.47</v>
+        <v>61.69</v>
       </c>
     </row>
     <row r="90">
@@ -5252,7 +5252,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482704 - KIT4M04604745G8Z</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955692 - KIT4M05563579H9F</t>
         </is>
       </c>
       <c r="C90" s="3" t="n">
@@ -5263,12 +5263,12 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604745G8Z</t>
+          <t>KIT4M05563579H9F</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>809661</t>
+          <t>814480</t>
         </is>
       </c>
       <c r="G90" s="5" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="L90" s="5" t="n"/>
       <c r="M90" s="7" t="n">
-        <v>57.14</v>
+        <v>59.68</v>
       </c>
     </row>
     <row r="91">
@@ -5305,7 +5305,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827011118 - KIT4M03867766NGK</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020955462 - KIT4M05563513GTF</t>
         </is>
       </c>
       <c r="C91" s="3" t="n">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03867766NGK</t>
+          <t>KIT4M05563513GTF</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>809615</t>
+          <t>814432</t>
         </is>
       </c>
       <c r="G91" s="5" t="inlineStr">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="L91" s="5" t="n"/>
       <c r="M91" s="7" t="n">
-        <v>56.33</v>
+        <v>59.65</v>
       </c>
     </row>
     <row r="92">
@@ -5358,7 +5358,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437392 - KIT4M05872555BJR</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649762 - KIT4M0460475549Z</t>
         </is>
       </c>
       <c r="C92" s="3" t="n">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872555BJR</t>
+          <t>KIT4M0460475549Z</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>816074</t>
+          <t>809859</t>
         </is>
       </c>
       <c r="G92" s="5" t="inlineStr">
@@ -5400,7 +5400,7 @@
       </c>
       <c r="L92" s="5" t="n"/>
       <c r="M92" s="7" t="n">
-        <v>56.28</v>
+        <v>58.39</v>
       </c>
     </row>
     <row r="93">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955412 - KIT4M05563598Z74</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482704 - KIT4M04604745G8Z</t>
         </is>
       </c>
       <c r="C93" s="3" t="n">
@@ -5422,12 +5422,12 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563598Z74</t>
+          <t>KIT4M04604745G8Z</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>814474</t>
+          <t>809661</t>
         </is>
       </c>
       <c r="G93" s="5" t="inlineStr">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="L93" s="5" t="n"/>
       <c r="M93" s="7" t="n">
-        <v>55.56</v>
+        <v>57.14</v>
       </c>
     </row>
     <row r="94">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 021437622 - KIT4M0587258755W</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827011118 - KIT4M03867766NGK</t>
         </is>
       </c>
       <c r="C94" s="3" t="n">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0587258755W</t>
+          <t>KIT4M03867766NGK</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>816187</t>
+          <t>809615</t>
         </is>
       </c>
       <c r="G94" s="5" t="inlineStr">
@@ -5506,7 +5506,7 @@
       </c>
       <c r="L94" s="5" t="n"/>
       <c r="M94" s="7" t="n">
-        <v>54.72</v>
+        <v>56.55</v>
       </c>
     </row>
     <row r="95">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270112 - KIT4M044751638F5</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955412 - KIT4M05563598Z74</t>
         </is>
       </c>
       <c r="C95" s="3" t="n">
@@ -5528,12 +5528,12 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>KIT4M044751638F5</t>
+          <t>KIT4M05563598Z74</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>809618</t>
+          <t>814474</t>
         </is>
       </c>
       <c r="G95" s="5" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="L95" s="5" t="n"/>
       <c r="M95" s="7" t="n">
-        <v>53.88</v>
+        <v>55.57</v>
       </c>
     </row>
     <row r="96">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649372 - KIT4M05368221HQ5</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270112 - KIT4M044751638F5</t>
         </is>
       </c>
       <c r="C96" s="3" t="n">
@@ -5581,12 +5581,12 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368221HQ5</t>
+          <t>KIT4M044751638F5</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>810834</t>
+          <t>809618</t>
         </is>
       </c>
       <c r="G96" s="5" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="L96" s="5" t="n"/>
       <c r="M96" s="7" t="n">
-        <v>53.65</v>
+        <v>54.28</v>
       </c>
     </row>
     <row r="97">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020650042 - KIT4M05413819JV5</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955692 - KIT4M05563603CP4</t>
         </is>
       </c>
       <c r="C97" s="3" t="n">
@@ -5634,12 +5634,12 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413819JV5</t>
+          <t>KIT4M05563603CP4</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>812796</t>
+          <t>814447</t>
         </is>
       </c>
       <c r="G97" s="5" t="inlineStr">
@@ -5665,7 +5665,7 @@
       </c>
       <c r="L97" s="5" t="n"/>
       <c r="M97" s="7" t="n">
-        <v>53.04</v>
+        <v>54.23</v>
       </c>
     </row>
     <row r="98">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955692 - KIT4M05563603CP4</t>
+          <t>SS - 05900510 - Los Angeles CA - 020650042 - KIT4M05413819JV5</t>
         </is>
       </c>
       <c r="C98" s="3" t="n">
@@ -5687,12 +5687,12 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563603CP4</t>
+          <t>KIT4M05413819JV5</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>814447</t>
+          <t>812796</t>
         </is>
       </c>
       <c r="G98" s="5" t="inlineStr">
@@ -5718,7 +5718,7 @@
       </c>
       <c r="L98" s="5" t="n"/>
       <c r="M98" s="7" t="n">
-        <v>52.74</v>
+        <v>53.68</v>
       </c>
     </row>
     <row r="99">
@@ -5729,7 +5729,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020650142 - KIT4M05413839D24</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649372 - KIT4M05368221HQ5</t>
         </is>
       </c>
       <c r="C99" s="3" t="n">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413839D24</t>
+          <t>KIT4M05368221HQ5</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>810096</t>
+          <t>810834</t>
         </is>
       </c>
       <c r="G99" s="5" t="inlineStr">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="L99" s="5" t="n"/>
       <c r="M99" s="7" t="n">
-        <v>50.33</v>
+        <v>53.65</v>
       </c>
     </row>
     <row r="100">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="L100" s="5" t="n"/>
       <c r="M100" s="7" t="n">
-        <v>50.16</v>
+        <v>51.87</v>
       </c>
     </row>
     <row r="101">
@@ -5835,7 +5835,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827016 - KIT4M041536494G6</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955702 - KIT4M05563571G8W</t>
         </is>
       </c>
       <c r="C101" s="3" t="n">
@@ -5846,12 +5846,12 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>KIT4M041536494G6</t>
+          <t>KIT4M05563571G8W</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>809617</t>
+          <t>814481</t>
         </is>
       </c>
       <c r="G101" s="5" t="inlineStr">
@@ -5877,7 +5877,7 @@
       </c>
       <c r="L101" s="5" t="n"/>
       <c r="M101" s="7" t="n">
-        <v>50.1</v>
+        <v>51.58</v>
       </c>
     </row>
     <row r="102">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955702 - KIT4M05563571G8W</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827016 - KIT4M041536494G6</t>
         </is>
       </c>
       <c r="C102" s="3" t="n">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563571G8W</t>
+          <t>KIT4M041536494G6</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>814481</t>
+          <t>809617</t>
         </is>
       </c>
       <c r="G102" s="5" t="inlineStr">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="L102" s="5" t="n"/>
       <c r="M102" s="7" t="n">
-        <v>49.53</v>
+        <v>51.33</v>
       </c>
     </row>
     <row r="103">
@@ -5941,7 +5941,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270111114 - KIT4P00065593VWC</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020650142 - KIT4M05413839D24</t>
         </is>
       </c>
       <c r="C103" s="3" t="n">
@@ -5952,17 +5952,17 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065593VWC</t>
+          <t>KIT4M05413839D24</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>809606</t>
+          <t>810096</t>
         </is>
       </c>
       <c r="G103" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H103" s="5" t="inlineStr">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="L103" s="5" t="n"/>
       <c r="M103" s="7" t="n">
-        <v>49.23</v>
+        <v>50.33</v>
       </c>
     </row>
     <row r="104">
@@ -5994,7 +5994,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437272 - KIT4P0008459589D</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270111114 - KIT4P00065593VWC</t>
         </is>
       </c>
       <c r="C104" s="3" t="n">
@@ -6005,12 +6005,12 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0008459589D</t>
+          <t>KIT4P00065593VWC</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>816222</t>
+          <t>809606</t>
         </is>
       </c>
       <c r="G104" s="5" t="inlineStr">
@@ -6036,7 +6036,7 @@
       </c>
       <c r="L104" s="5" t="n"/>
       <c r="M104" s="7" t="n">
-        <v>48.21</v>
+        <v>49.23</v>
       </c>
     </row>
     <row r="105">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649672 - KIT4M04606113TPB</t>
+          <t>SMRT-05900510-Los Angeles CA-020650202-KIT4M05413803FDK</t>
         </is>
       </c>
       <c r="C105" s="3" t="n">
@@ -6058,12 +6058,12 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04606113TPB</t>
+          <t>KIT4M05413803FDK</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>809862</t>
+          <t>812850</t>
         </is>
       </c>
       <c r="G105" s="5" t="inlineStr">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="L105" s="5" t="n"/>
       <c r="M105" s="7" t="n">
-        <v>46.74</v>
+        <v>47.53</v>
       </c>
     </row>
     <row r="106">
@@ -6100,7 +6100,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles, CA-020955452-KIT4M05563529K2D</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649212 - KIT4P00065633ZXC</t>
         </is>
       </c>
       <c r="C106" s="3" t="n">
@@ -6111,17 +6111,17 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563529K2D</t>
+          <t>KIT4P00065633ZXC</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>814473</t>
+          <t>812922</t>
         </is>
       </c>
       <c r="G106" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H106" s="5" t="inlineStr">
@@ -6142,7 +6142,7 @@
       </c>
       <c r="L106" s="5" t="n"/>
       <c r="M106" s="7" t="n">
-        <v>46.61</v>
+        <v>46.95</v>
       </c>
     </row>
     <row r="107">
@@ -6153,7 +6153,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649212 - KIT4P00065633ZXC</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649832 - KIT4M03866596RZG</t>
         </is>
       </c>
       <c r="C107" s="3" t="n">
@@ -6164,17 +6164,17 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065633ZXC</t>
+          <t>KIT4M03866596RZG</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>812922</t>
+          <t>809869</t>
         </is>
       </c>
       <c r="G107" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H107" s="5" t="inlineStr">
@@ -6195,7 +6195,7 @@
       </c>
       <c r="L107" s="5" t="n"/>
       <c r="M107" s="7" t="n">
-        <v>46.56</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="108">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020650202-KIT4M05413803FDK</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649672 - KIT4M04606113TPB</t>
         </is>
       </c>
       <c r="C108" s="3" t="n">
@@ -6217,12 +6217,12 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413803FDK</t>
+          <t>KIT4M04606113TPB</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>812850</t>
+          <t>809862</t>
         </is>
       </c>
       <c r="G108" s="5" t="inlineStr">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="L108" s="5" t="n"/>
       <c r="M108" s="7" t="n">
-        <v>46.28</v>
+        <v>46.74</v>
       </c>
     </row>
     <row r="109">
@@ -6259,7 +6259,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649832 - KIT4M03866596RZG</t>
+          <t>SMRT-05900510-Los Angeles, CA-020955452-KIT4M05563529K2D</t>
         </is>
       </c>
       <c r="C109" s="3" t="n">
@@ -6270,12 +6270,12 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03866596RZG</t>
+          <t>KIT4M05563529K2D</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>809869</t>
+          <t>814473</t>
         </is>
       </c>
       <c r="G109" s="5" t="inlineStr">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="L109" s="5" t="n"/>
       <c r="M109" s="7" t="n">
-        <v>44.76</v>
+        <v>46.61</v>
       </c>
     </row>
     <row r="110">
@@ -6418,7 +6418,7 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020650192 - KIT4M054138007JF</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020955652 - KIT4M0556358988Z</t>
         </is>
       </c>
       <c r="C112" s="3" t="n">
@@ -6429,12 +6429,12 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138007JF</t>
+          <t>KIT4M0556358988Z</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>810095</t>
+          <t>814484</t>
         </is>
       </c>
       <c r="G112" s="5" t="inlineStr">
@@ -6460,7 +6460,7 @@
       </c>
       <c r="L112" s="5" t="n"/>
       <c r="M112" s="7" t="n">
-        <v>42.59</v>
+        <v>42.76</v>
       </c>
     </row>
     <row r="113">
@@ -6471,7 +6471,7 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020955652 - KIT4M0556358988Z</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955272 - KIT4M05563585TXM</t>
         </is>
       </c>
       <c r="C113" s="3" t="n">
@@ -6482,12 +6482,12 @@
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0556358988Z</t>
+          <t>KIT4M05563585TXM</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>814484</t>
+          <t>814475</t>
         </is>
       </c>
       <c r="G113" s="5" t="inlineStr">
@@ -6513,7 +6513,7 @@
       </c>
       <c r="L113" s="5" t="n"/>
       <c r="M113" s="7" t="n">
-        <v>42.15</v>
+        <v>42.74</v>
       </c>
     </row>
     <row r="114">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020650052 - KIT4M05413781K6C</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020650192 - KIT4M054138007JF</t>
         </is>
       </c>
       <c r="C114" s="3" t="n">
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413781K6C</t>
+          <t>KIT4M054138007JF</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>812798</t>
+          <t>810095</t>
         </is>
       </c>
       <c r="G114" s="5" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="L114" s="5" t="n"/>
       <c r="M114" s="7" t="n">
-        <v>42.04</v>
+        <v>42.59</v>
       </c>
     </row>
     <row r="115">
@@ -6577,7 +6577,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955272 - KIT4M05563585TXM</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020650052 - KIT4M05413781K6C</t>
         </is>
       </c>
       <c r="C115" s="3" t="n">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563585TXM</t>
+          <t>KIT4M05413781K6C</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>814475</t>
+          <t>812798</t>
         </is>
       </c>
       <c r="G115" s="5" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="L115" s="5" t="n"/>
       <c r="M115" s="7" t="n">
-        <v>41.82</v>
+        <v>42.04</v>
       </c>
     </row>
     <row r="116">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="L117" s="5" t="n"/>
       <c r="M117" s="7" t="n">
-        <v>40.3</v>
+        <v>40.86</v>
       </c>
     </row>
     <row r="118">
@@ -6736,7 +6736,7 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649682 - KIT4M046047384RX</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438152 - KIT4M05799733FPK</t>
         </is>
       </c>
       <c r="C118" s="3" t="n">
@@ -6747,12 +6747,12 @@
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047384RX</t>
+          <t>KIT4M05799733FPK</t>
         </is>
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>809870</t>
+          <t>816286</t>
         </is>
       </c>
       <c r="G118" s="5" t="inlineStr">
@@ -6778,7 +6778,7 @@
       </c>
       <c r="L118" s="5" t="n"/>
       <c r="M118" s="7" t="n">
-        <v>38.51</v>
+        <v>40.63</v>
       </c>
     </row>
     <row r="119">
@@ -6789,7 +6789,7 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955602 - KIT4M05563560225</t>
+          <t>SS - 05900510 -  Los Angeles CA - 021438232 - KIT4M05872520QJM</t>
         </is>
       </c>
       <c r="C119" s="3" t="n">
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563560225</t>
+          <t>KIT4M05872520QJM</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>814454</t>
+          <t>816078</t>
         </is>
       </c>
       <c r="G119" s="5" t="inlineStr">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="L119" s="5" t="n"/>
       <c r="M119" s="7" t="n">
-        <v>38.09</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="120">
@@ -6842,7 +6842,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020650082 - KIT4M05413792H8C</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649682 - KIT4M046047384RX</t>
         </is>
       </c>
       <c r="C120" s="3" t="n">
@@ -6853,12 +6853,12 @@
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413792H8C</t>
+          <t>KIT4M046047384RX</t>
         </is>
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t>812803</t>
+          <t>809870</t>
         </is>
       </c>
       <c r="G120" s="5" t="inlineStr">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="L120" s="5" t="n"/>
       <c r="M120" s="7" t="n">
-        <v>37.81</v>
+        <v>39.38</v>
       </c>
     </row>
     <row r="121">
@@ -6895,7 +6895,7 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438152 - KIT4M05799733FPK</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955602 - KIT4M05563560225</t>
         </is>
       </c>
       <c r="C121" s="3" t="n">
@@ -6906,12 +6906,12 @@
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799733FPK</t>
+          <t>KIT4M05563560225</t>
         </is>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>816286</t>
+          <t>814454</t>
         </is>
       </c>
       <c r="G121" s="5" t="inlineStr">
@@ -6937,7 +6937,7 @@
       </c>
       <c r="L121" s="5" t="n"/>
       <c r="M121" s="7" t="n">
-        <v>36.87</v>
+        <v>38.09</v>
       </c>
     </row>
     <row r="122">
@@ -6948,7 +6948,7 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482701112 - KIT4M04158973M2C</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437782 - KIT4M058724975J4</t>
         </is>
       </c>
       <c r="C122" s="3" t="n">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158973M2C</t>
+          <t>KIT4M058724975J4</t>
         </is>
       </c>
       <c r="F122" s="4" t="inlineStr">
         <is>
-          <t>809610</t>
+          <t>816075</t>
         </is>
       </c>
       <c r="G122" s="5" t="inlineStr">
@@ -6990,7 +6990,7 @@
       </c>
       <c r="L122" s="5" t="n"/>
       <c r="M122" s="7" t="n">
-        <v>36.26</v>
+        <v>37.82</v>
       </c>
     </row>
     <row r="123">
@@ -7001,7 +7001,7 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 021438232 - KIT4M05872520QJM</t>
+          <t>STS - 05900510 - Los Angeles CA - 020650082 - KIT4M05413792H8C</t>
         </is>
       </c>
       <c r="C123" s="3" t="n">
@@ -7012,12 +7012,12 @@
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872520QJM</t>
+          <t>KIT4M05413792H8C</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>816078</t>
+          <t>812803</t>
         </is>
       </c>
       <c r="G123" s="5" t="inlineStr">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="L123" s="5" t="n"/>
       <c r="M123" s="7" t="n">
-        <v>34.98</v>
+        <v>37.81</v>
       </c>
     </row>
     <row r="124">
@@ -7054,7 +7054,7 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020650112 - KIT4M05413840D9J</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482701112 - KIT4M04158973M2C</t>
         </is>
       </c>
       <c r="C124" s="3" t="n">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413840D9J</t>
+          <t>KIT4M04158973M2C</t>
         </is>
       </c>
       <c r="F124" s="4" t="inlineStr">
         <is>
-          <t>810099</t>
+          <t>809610</t>
         </is>
       </c>
       <c r="G124" s="5" t="inlineStr">
@@ -7096,7 +7096,7 @@
       </c>
       <c r="L124" s="5" t="n"/>
       <c r="M124" s="7" t="n">
-        <v>34.86</v>
+        <v>36.43</v>
       </c>
     </row>
     <row r="125">
@@ -7107,7 +7107,7 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649942 - KIT4M05413786BXC</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020650112 - KIT4M05413840D9J</t>
         </is>
       </c>
       <c r="C125" s="3" t="n">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413786BXC</t>
+          <t>KIT4M05413840D9J</t>
         </is>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>812838</t>
+          <t>810099</t>
         </is>
       </c>
       <c r="G125" s="5" t="inlineStr">
@@ -7149,7 +7149,7 @@
       </c>
       <c r="L125" s="5" t="n"/>
       <c r="M125" s="7" t="n">
-        <v>34.4</v>
+        <v>35.17</v>
       </c>
     </row>
     <row r="126">
@@ -7160,7 +7160,7 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437782 - KIT4M058724975J4</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955502 - KIT4M05563502GJS</t>
         </is>
       </c>
       <c r="C126" s="3" t="n">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058724975J4</t>
+          <t>KIT4M05563502GJS</t>
         </is>
       </c>
       <c r="F126" s="4" t="inlineStr">
         <is>
-          <t>816075</t>
+          <t>814470</t>
         </is>
       </c>
       <c r="G126" s="5" t="inlineStr">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="L126" s="5" t="n"/>
       <c r="M126" s="7" t="n">
-        <v>33.87</v>
+        <v>35.08</v>
       </c>
     </row>
     <row r="127">
@@ -7213,7 +7213,7 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649412 - KIT4M05413769796</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649942 - KIT4M05413786BXC</t>
         </is>
       </c>
       <c r="C127" s="3" t="n">
@@ -7224,12 +7224,12 @@
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413769796</t>
+          <t>KIT4M05413786BXC</t>
         </is>
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>812839</t>
+          <t>812838</t>
         </is>
       </c>
       <c r="G127" s="5" t="inlineStr">
@@ -7255,7 +7255,7 @@
       </c>
       <c r="L127" s="5" t="n"/>
       <c r="M127" s="7" t="n">
-        <v>32.57</v>
+        <v>34.4</v>
       </c>
     </row>
     <row r="128">
@@ -7266,7 +7266,7 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482706 - KIT4M04604744V6K</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649442 - KIT4M054137885SM</t>
         </is>
       </c>
       <c r="C128" s="3" t="n">
@@ -7277,12 +7277,12 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604744V6K</t>
+          <t>KIT4M054137885SM</t>
         </is>
       </c>
       <c r="F128" s="4" t="inlineStr">
         <is>
-          <t>809659</t>
+          <t>812846</t>
         </is>
       </c>
       <c r="G128" s="5" t="inlineStr">
@@ -7308,7 +7308,7 @@
       </c>
       <c r="L128" s="5" t="n"/>
       <c r="M128" s="7" t="n">
-        <v>31.38</v>
+        <v>32.77</v>
       </c>
     </row>
     <row r="129">
@@ -7319,7 +7319,7 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 6858375 - KIT4M05872512N5W</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649412 - KIT4M05413769796</t>
         </is>
       </c>
       <c r="C129" s="3" t="n">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872512N5W</t>
+          <t>KIT4M05413769796</t>
         </is>
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>816077</t>
+          <t>812839</t>
         </is>
       </c>
       <c r="G129" s="5" t="inlineStr">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="L129" s="5" t="n"/>
       <c r="M129" s="7" t="n">
-        <v>31.1</v>
+        <v>32.57</v>
       </c>
     </row>
     <row r="130">
@@ -7372,7 +7372,7 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955712 - KIT4M05563586ZTR</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482706 - KIT4M04604744V6K</t>
         </is>
       </c>
       <c r="C130" s="3" t="n">
@@ -7383,12 +7383,12 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563586ZTR</t>
+          <t>KIT4M04604744V6K</t>
         </is>
       </c>
       <c r="F130" s="4" t="inlineStr">
         <is>
-          <t>814445</t>
+          <t>809659</t>
         </is>
       </c>
       <c r="G130" s="5" t="inlineStr">
@@ -7414,7 +7414,7 @@
       </c>
       <c r="L130" s="5" t="n"/>
       <c r="M130" s="7" t="n">
-        <v>30.87</v>
+        <v>31.38</v>
       </c>
     </row>
     <row r="131">
@@ -7425,7 +7425,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438002 - KIT4M05799701SGS</t>
+          <t>SS - 05900510 - Los Angeles CA - 6858375 - KIT4M05872512N5W</t>
         </is>
       </c>
       <c r="C131" s="3" t="n">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799701SGS</t>
+          <t>KIT4M05872512N5W</t>
         </is>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>816284</t>
+          <t>816077</t>
         </is>
       </c>
       <c r="G131" s="5" t="inlineStr">
@@ -7467,7 +7467,7 @@
       </c>
       <c r="L131" s="5" t="n"/>
       <c r="M131" s="7" t="n">
-        <v>29.64</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="132">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437992 -  KIT4M05799663CPM</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955712 - KIT4M05563586ZTR</t>
         </is>
       </c>
       <c r="C132" s="3" t="n">
@@ -7489,12 +7489,12 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799663CPM</t>
+          <t>KIT4M05563586ZTR</t>
         </is>
       </c>
       <c r="F132" s="4" t="inlineStr">
         <is>
-          <t>816272</t>
+          <t>814445</t>
         </is>
       </c>
       <c r="G132" s="5" t="inlineStr">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="L132" s="5" t="n"/>
       <c r="M132" s="7" t="n">
-        <v>29.07</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="133">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649822 - KIT4M04604740BM6</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438002 - KIT4M05799701SGS</t>
         </is>
       </c>
       <c r="C133" s="3" t="n">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604740BM6</t>
+          <t>KIT4M05799701SGS</t>
         </is>
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>809872</t>
+          <t>816284</t>
         </is>
       </c>
       <c r="G133" s="5" t="inlineStr">
@@ -7573,7 +7573,7 @@
       </c>
       <c r="L133" s="5" t="n"/>
       <c r="M133" s="7" t="n">
-        <v>28.63</v>
+        <v>30.71</v>
       </c>
     </row>
     <row r="134">
@@ -7584,7 +7584,7 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020649292-KIT4M05368201SNV</t>
+          <t>SMA - 05900510 -  Los Angeles CA - 020649512 - KIT4M054138318Q7</t>
         </is>
       </c>
       <c r="C134" s="3" t="n">
@@ -7595,12 +7595,12 @@
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368201SNV</t>
+          <t>KIT4M054138318Q7</t>
         </is>
       </c>
       <c r="F134" s="4" t="inlineStr">
         <is>
-          <t>810651</t>
+          <t>812814</t>
         </is>
       </c>
       <c r="G134" s="5" t="inlineStr">
@@ -7626,7 +7626,7 @@
       </c>
       <c r="L134" s="5" t="n"/>
       <c r="M134" s="7" t="n">
-        <v>28.01</v>
+        <v>30.7</v>
       </c>
     </row>
     <row r="135">
@@ -7637,7 +7637,7 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649742 - KIT4M04350554X4Z</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649822 - KIT4M04604740BM6</t>
         </is>
       </c>
       <c r="C135" s="3" t="n">
@@ -7648,12 +7648,12 @@
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04350554X4Z</t>
+          <t>KIT4M04604740BM6</t>
         </is>
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>809866</t>
+          <t>809872</t>
         </is>
       </c>
       <c r="G135" s="5" t="inlineStr">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="L135" s="5" t="n"/>
       <c r="M135" s="7" t="n">
-        <v>27.16</v>
+        <v>29.72</v>
       </c>
     </row>
     <row r="136">
@@ -7690,7 +7690,7 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649532 - KIT4M05413808FFZ</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437992 -  KIT4M05799663CPM</t>
         </is>
       </c>
       <c r="C136" s="3" t="n">
@@ -7701,12 +7701,12 @@
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413808FFZ</t>
+          <t>KIT4M05799663CPM</t>
         </is>
       </c>
       <c r="F136" s="4" t="inlineStr">
         <is>
-          <t>812828</t>
+          <t>816272</t>
         </is>
       </c>
       <c r="G136" s="5" t="inlineStr">
@@ -7732,7 +7732,7 @@
       </c>
       <c r="L136" s="5" t="n"/>
       <c r="M136" s="7" t="n">
-        <v>27.14</v>
+        <v>29.7</v>
       </c>
     </row>
     <row r="137">
@@ -7743,7 +7743,7 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649452 - KIT4M05413785QCG</t>
+          <t>SMRT-05900510-Los Angeles CA-020649292-KIT4M05368201SNV</t>
         </is>
       </c>
       <c r="C137" s="3" t="n">
@@ -7754,12 +7754,12 @@
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413785QCG</t>
+          <t>KIT4M05368201SNV</t>
         </is>
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>812806</t>
+          <t>810651</t>
         </is>
       </c>
       <c r="G137" s="5" t="inlineStr">
@@ -7785,7 +7785,7 @@
       </c>
       <c r="L137" s="5" t="n"/>
       <c r="M137" s="7" t="n">
-        <v>26.31</v>
+        <v>28.18</v>
       </c>
     </row>
     <row r="138">
@@ -7796,7 +7796,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955342 - KIT4M05563524MJ4</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649592 - KIT4M05413787HHK</t>
         </is>
       </c>
       <c r="C138" s="3" t="n">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563524MJ4</t>
+          <t>KIT4M05413787HHK</t>
         </is>
       </c>
       <c r="F138" s="4" t="inlineStr">
         <is>
-          <t>814472</t>
+          <t>812809</t>
         </is>
       </c>
       <c r="G138" s="5" t="inlineStr">
@@ -7838,7 +7838,7 @@
       </c>
       <c r="L138" s="5" t="n"/>
       <c r="M138" s="7" t="n">
-        <v>26.26</v>
+        <v>28.08</v>
       </c>
     </row>
     <row r="139">
@@ -7849,7 +7849,7 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955502 - KIT4M05563502GJS</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649452 - KIT4M05413785QCG</t>
         </is>
       </c>
       <c r="C139" s="3" t="n">
@@ -7860,12 +7860,12 @@
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563502GJS</t>
+          <t>KIT4M05413785QCG</t>
         </is>
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>814470</t>
+          <t>812806</t>
         </is>
       </c>
       <c r="G139" s="5" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="L139" s="5" t="n"/>
       <c r="M139" s="7" t="n">
-        <v>26.21</v>
+        <v>27.96</v>
       </c>
     </row>
     <row r="140">
@@ -7902,7 +7902,7 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 -  Los Angeles CA - 020649512 - KIT4M054138318Q7</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649742 - KIT4M04350554X4Z</t>
         </is>
       </c>
       <c r="C140" s="3" t="n">
@@ -7913,12 +7913,12 @@
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138318Q7</t>
+          <t>KIT4M04350554X4Z</t>
         </is>
       </c>
       <c r="F140" s="4" t="inlineStr">
         <is>
-          <t>812814</t>
+          <t>809866</t>
         </is>
       </c>
       <c r="G140" s="5" t="inlineStr">
@@ -7944,7 +7944,7 @@
       </c>
       <c r="L140" s="5" t="n"/>
       <c r="M140" s="7" t="n">
-        <v>26.18</v>
+        <v>27.16</v>
       </c>
     </row>
     <row r="141">
@@ -7955,7 +7955,7 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020650162 - KIT4M05413837SMB</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649532 - KIT4M05413808FFZ</t>
         </is>
       </c>
       <c r="C141" s="3" t="n">
@@ -7966,12 +7966,12 @@
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413837SMB</t>
+          <t>KIT4M05413808FFZ</t>
         </is>
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>810100</t>
+          <t>812828</t>
         </is>
       </c>
       <c r="G141" s="5" t="inlineStr">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="L141" s="5" t="n"/>
       <c r="M141" s="7" t="n">
-        <v>25.34</v>
+        <v>27.14</v>
       </c>
     </row>
     <row r="142">
@@ -8008,7 +8008,7 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649362 - KIT4M05368336DBC</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955342 - KIT4M05563524MJ4</t>
         </is>
       </c>
       <c r="C142" s="3" t="n">
@@ -8019,12 +8019,12 @@
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368336DBC</t>
+          <t>KIT4M05563524MJ4</t>
         </is>
       </c>
       <c r="F142" s="4" t="inlineStr">
         <is>
-          <t>810831</t>
+          <t>814472</t>
         </is>
       </c>
       <c r="G142" s="5" t="inlineStr">
@@ -8050,7 +8050,7 @@
       </c>
       <c r="L142" s="5" t="n"/>
       <c r="M142" s="7" t="n">
-        <v>25.14</v>
+        <v>26.26</v>
       </c>
     </row>
     <row r="143">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955212 - KIT4M05563512GBQ</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020650162 - KIT4M05413837SMB</t>
         </is>
       </c>
       <c r="C143" s="3" t="n">
@@ -8072,12 +8072,12 @@
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563512GBQ</t>
+          <t>KIT4M05413837SMB</t>
         </is>
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>814435</t>
+          <t>810100</t>
         </is>
       </c>
       <c r="G143" s="5" t="inlineStr">
@@ -8103,7 +8103,7 @@
       </c>
       <c r="L143" s="5" t="n"/>
       <c r="M143" s="7" t="n">
-        <v>24.55</v>
+        <v>25.59</v>
       </c>
     </row>
     <row r="144">
@@ -8114,7 +8114,7 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438242 - KIT4M058725094XP</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649362 - KIT4M05368336DBC</t>
         </is>
       </c>
       <c r="C144" s="3" t="n">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725094XP</t>
+          <t>KIT4M05368336DBC</t>
         </is>
       </c>
       <c r="F144" s="4" t="inlineStr">
         <is>
-          <t>816085</t>
+          <t>810831</t>
         </is>
       </c>
       <c r="G144" s="5" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="L144" s="5" t="n"/>
       <c r="M144" s="7" t="n">
-        <v>24.02</v>
+        <v>25.14</v>
       </c>
     </row>
     <row r="145">
@@ -8167,7 +8167,7 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955532 - KIT4M05563548P9Q</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955212 - KIT4M05563512GBQ</t>
         </is>
       </c>
       <c r="C145" s="3" t="n">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563548P9Q</t>
+          <t>KIT4M05563512GBQ</t>
         </is>
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>814468</t>
+          <t>814435</t>
         </is>
       </c>
       <c r="G145" s="5" t="inlineStr">
@@ -8209,7 +8209,7 @@
       </c>
       <c r="L145" s="5" t="n"/>
       <c r="M145" s="7" t="n">
-        <v>22.94</v>
+        <v>24.55</v>
       </c>
     </row>
     <row r="146">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438222 - KIT4M058725299QP</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438242 - KIT4M058725094XP</t>
         </is>
       </c>
       <c r="C146" s="3" t="n">
@@ -8231,12 +8231,12 @@
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725299QP</t>
+          <t>KIT4M058725094XP</t>
         </is>
       </c>
       <c r="F146" s="4" t="inlineStr">
         <is>
-          <t>816080</t>
+          <t>816085</t>
         </is>
       </c>
       <c r="G146" s="5" t="inlineStr">
@@ -8262,7 +8262,7 @@
       </c>
       <c r="L146" s="5" t="n"/>
       <c r="M146" s="7" t="n">
-        <v>22.94</v>
+        <v>24.37</v>
       </c>
     </row>
     <row r="147">
@@ -8273,7 +8273,7 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020650242 - KIT4M05413804SKS</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955532 - KIT4M05563548P9Q</t>
         </is>
       </c>
       <c r="C147" s="3" t="n">
@@ -8284,12 +8284,12 @@
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413804SKS</t>
+          <t>KIT4M05563548P9Q</t>
         </is>
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>810102</t>
+          <t>814468</t>
         </is>
       </c>
       <c r="G147" s="5" t="inlineStr">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="L147" s="5" t="n"/>
       <c r="M147" s="7" t="n">
-        <v>22.63</v>
+        <v>23.04</v>
       </c>
     </row>
     <row r="148">
@@ -8326,7 +8326,7 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649592 - KIT4M05413787HHK</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438222 - KIT4M058725299QP</t>
         </is>
       </c>
       <c r="C148" s="3" t="n">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413787HHK</t>
+          <t>KIT4M058725299QP</t>
         </is>
       </c>
       <c r="F148" s="4" t="inlineStr">
         <is>
-          <t>812809</t>
+          <t>816080</t>
         </is>
       </c>
       <c r="G148" s="5" t="inlineStr">
@@ -8368,7 +8368,7 @@
       </c>
       <c r="L148" s="5" t="n"/>
       <c r="M148" s="7" t="n">
-        <v>21.73</v>
+        <v>22.96</v>
       </c>
     </row>
     <row r="149">
@@ -8379,7 +8379,7 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020650132-KIT4M05413828PCT</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020650242 - KIT4M05413804SKS</t>
         </is>
       </c>
       <c r="C149" s="3" t="n">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413828PCT</t>
+          <t>KIT4M05413804SKS</t>
         </is>
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>812799</t>
+          <t>810102</t>
         </is>
       </c>
       <c r="G149" s="5" t="inlineStr">
@@ -8421,7 +8421,7 @@
       </c>
       <c r="L149" s="5" t="n"/>
       <c r="M149" s="7" t="n">
-        <v>21.54</v>
+        <v>22.64</v>
       </c>
     </row>
     <row r="150">
@@ -8432,7 +8432,7 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-LOS ANGELES CA-020955172-KIT4M05563526WNC</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649492 - KIT4M054138074NS</t>
         </is>
       </c>
       <c r="C150" s="3" t="n">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563526WNC</t>
+          <t>KIT4M054138074NS</t>
         </is>
       </c>
       <c r="F150" s="4" t="inlineStr">
         <is>
-          <t>814463</t>
+          <t>812816</t>
         </is>
       </c>
       <c r="G150" s="5" t="inlineStr">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="L150" s="5" t="n"/>
       <c r="M150" s="7" t="n">
-        <v>21.16</v>
+        <v>21.81</v>
       </c>
     </row>
     <row r="151">
@@ -8485,7 +8485,7 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020650072-KIT4M054137987GJ</t>
+          <t>SMRT-05900510-Los Angeles CA-020650132-KIT4M05413828PCT</t>
         </is>
       </c>
       <c r="C151" s="3" t="n">
@@ -8496,12 +8496,12 @@
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137987GJ</t>
+          <t>KIT4M05413828PCT</t>
         </is>
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>812795</t>
+          <t>812799</t>
         </is>
       </c>
       <c r="G151" s="5" t="inlineStr">
@@ -8527,7 +8527,7 @@
       </c>
       <c r="L151" s="5" t="n"/>
       <c r="M151" s="7" t="n">
-        <v>20.74</v>
+        <v>21.54</v>
       </c>
     </row>
     <row r="152">
@@ -8580,7 +8580,7 @@
       </c>
       <c r="L152" s="5" t="n"/>
       <c r="M152" s="7" t="n">
-        <v>20.55</v>
+        <v>21.52</v>
       </c>
     </row>
     <row r="153">
@@ -8591,7 +8591,7 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649222 - KIT4P00065640BFW</t>
+          <t>SMRT-05900510-LOS ANGELES CA-020955172-KIT4M05563526WNC</t>
         </is>
       </c>
       <c r="C153" s="3" t="n">
@@ -8602,17 +8602,17 @@
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065640BFW</t>
+          <t>KIT4M05563526WNC</t>
         </is>
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>812929</t>
+          <t>814463</t>
         </is>
       </c>
       <c r="G153" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H153" s="5" t="inlineStr">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="L153" s="5" t="n"/>
       <c r="M153" s="7" t="n">
-        <v>19.87</v>
+        <v>21.16</v>
       </c>
     </row>
     <row r="154">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649912 - KIT4M05413836KJC</t>
+          <t>SMRT-05900510-Los Angeles CA-020650072-KIT4M054137987GJ</t>
         </is>
       </c>
       <c r="C154" s="3" t="n">
@@ -8655,12 +8655,12 @@
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413836KJC</t>
+          <t>KIT4M054137987GJ</t>
         </is>
       </c>
       <c r="F154" s="4" t="inlineStr">
         <is>
-          <t>810097</t>
+          <t>812795</t>
         </is>
       </c>
       <c r="G154" s="5" t="inlineStr">
@@ -8686,7 +8686,7 @@
       </c>
       <c r="L154" s="5" t="n"/>
       <c r="M154" s="7" t="n">
-        <v>19.73</v>
+        <v>20.74</v>
       </c>
     </row>
     <row r="155">
@@ -8697,7 +8697,7 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649302 - KIT4M05368226W57</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649222 - KIT4P00065640BFW</t>
         </is>
       </c>
       <c r="C155" s="3" t="n">
@@ -8708,17 +8708,17 @@
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368226W57</t>
+          <t>KIT4P00065640BFW</t>
         </is>
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>810833</t>
+          <t>812929</t>
         </is>
       </c>
       <c r="G155" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H155" s="5" t="inlineStr">
@@ -8739,7 +8739,7 @@
       </c>
       <c r="L155" s="5" t="n"/>
       <c r="M155" s="7" t="n">
-        <v>19.62</v>
+        <v>19.87</v>
       </c>
     </row>
     <row r="156">
@@ -8750,7 +8750,7 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955302 - KIT4M055635158PC</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649912 - KIT4M05413836KJC</t>
         </is>
       </c>
       <c r="C156" s="3" t="n">
@@ -8761,12 +8761,12 @@
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635158PC</t>
+          <t>KIT4M05413836KJC</t>
         </is>
       </c>
       <c r="F156" s="4" t="inlineStr">
         <is>
-          <t>814457</t>
+          <t>810097</t>
         </is>
       </c>
       <c r="G156" s="5" t="inlineStr">
@@ -8792,7 +8792,7 @@
       </c>
       <c r="L156" s="5" t="n"/>
       <c r="M156" s="7" t="n">
-        <v>19.59</v>
+        <v>19.73</v>
       </c>
     </row>
     <row r="157">
@@ -8803,7 +8803,7 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955282 - KIT4M055635227ZR</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649302 - KIT4M05368226W57</t>
         </is>
       </c>
       <c r="C157" s="3" t="n">
@@ -8814,12 +8814,12 @@
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635227ZR</t>
+          <t>KIT4M05368226W57</t>
         </is>
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>814482</t>
+          <t>810833</t>
         </is>
       </c>
       <c r="G157" s="5" t="inlineStr">
@@ -8845,7 +8845,7 @@
       </c>
       <c r="L157" s="5" t="n"/>
       <c r="M157" s="7" t="n">
-        <v>19.17</v>
+        <v>19.62</v>
       </c>
     </row>
     <row r="158">
@@ -8856,7 +8856,7 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649322 - KIT4M053683324KZ</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955302 - KIT4M055635158PC</t>
         </is>
       </c>
       <c r="C158" s="3" t="n">
@@ -8867,12 +8867,12 @@
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>KIT4M053683324KZ</t>
+          <t>KIT4M055635158PC</t>
         </is>
       </c>
       <c r="F158" s="4" t="inlineStr">
         <is>
-          <t>810832</t>
+          <t>814457</t>
         </is>
       </c>
       <c r="G158" s="5" t="inlineStr">
@@ -8898,7 +8898,7 @@
       </c>
       <c r="L158" s="5" t="n"/>
       <c r="M158" s="7" t="n">
-        <v>18.54</v>
+        <v>19.59</v>
       </c>
     </row>
     <row r="159">
@@ -8909,7 +8909,7 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA  - 020649722 - KIT4M04604747TPT</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955282 - KIT4M055635227ZR</t>
         </is>
       </c>
       <c r="C159" s="3" t="n">
@@ -8920,12 +8920,12 @@
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604747TPT</t>
+          <t>KIT4M055635227ZR</t>
         </is>
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>809873</t>
+          <t>814482</t>
         </is>
       </c>
       <c r="G159" s="5" t="inlineStr">
@@ -8951,7 +8951,7 @@
       </c>
       <c r="L159" s="5" t="n"/>
       <c r="M159" s="7" t="n">
-        <v>18.44</v>
+        <v>19.17</v>
       </c>
     </row>
     <row r="160">
@@ -8962,7 +8962,7 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020650262 - KIT4M054138249M8</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649322 - KIT4M053683324KZ</t>
         </is>
       </c>
       <c r="C160" s="3" t="n">
@@ -8973,12 +8973,12 @@
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138249M8</t>
+          <t>KIT4M053683324KZ</t>
         </is>
       </c>
       <c r="F160" s="4" t="inlineStr">
         <is>
-          <t>812794</t>
+          <t>810832</t>
         </is>
       </c>
       <c r="G160" s="5" t="inlineStr">
@@ -9004,7 +9004,7 @@
       </c>
       <c r="L160" s="5" t="n"/>
       <c r="M160" s="7" t="n">
-        <v>17.75</v>
+        <v>18.89</v>
       </c>
     </row>
     <row r="161">
@@ -9015,7 +9015,7 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649492 - KIT4M054138074NS</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020650262 - KIT4M054138249M8</t>
         </is>
       </c>
       <c r="C161" s="3" t="n">
@@ -9026,12 +9026,12 @@
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138074NS</t>
+          <t>KIT4M054138249M8</t>
         </is>
       </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
-          <t>812816</t>
+          <t>812794</t>
         </is>
       </c>
       <c r="G161" s="5" t="inlineStr">
@@ -9057,7 +9057,7 @@
       </c>
       <c r="L161" s="5" t="n"/>
       <c r="M161" s="7" t="n">
-        <v>17.3</v>
+        <v>18.49</v>
       </c>
     </row>
     <row r="162">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827010 - KIT4M046047372KJ</t>
+          <t>SS - 05900510 - Los Angeles, CA  - 020649722 - KIT4M04604747TPT</t>
         </is>
       </c>
       <c r="C162" s="3" t="n">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047372KJ</t>
+          <t>KIT4M04604747TPT</t>
         </is>
       </c>
       <c r="F162" s="4" t="inlineStr">
         <is>
-          <t>809658</t>
+          <t>809873</t>
         </is>
       </c>
       <c r="G162" s="5" t="inlineStr">
@@ -9110,7 +9110,7 @@
       </c>
       <c r="L162" s="5" t="n"/>
       <c r="M162" s="7" t="n">
-        <v>17.27</v>
+        <v>18.44</v>
       </c>
     </row>
     <row r="163">
@@ -9121,7 +9121,7 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649632 - KIT4M054138064J9</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827010 - KIT4M046047372KJ</t>
         </is>
       </c>
       <c r="C163" s="3" t="n">
@@ -9132,12 +9132,12 @@
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138064J9</t>
+          <t>KIT4M046047372KJ</t>
         </is>
       </c>
       <c r="F163" s="4" t="inlineStr">
         <is>
-          <t>812844</t>
+          <t>809658</t>
         </is>
       </c>
       <c r="G163" s="5" t="inlineStr">
@@ -9163,7 +9163,7 @@
       </c>
       <c r="L163" s="5" t="n"/>
       <c r="M163" s="7" t="n">
-        <v>17.18</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="164">
@@ -9174,7 +9174,7 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482708 - KIT4M04604736T7C</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649632 - KIT4M054138064J9</t>
         </is>
       </c>
       <c r="C164" s="3" t="n">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604736T7C</t>
+          <t>KIT4M054138064J9</t>
         </is>
       </c>
       <c r="F164" s="4" t="inlineStr">
         <is>
-          <t>809662</t>
+          <t>812844</t>
         </is>
       </c>
       <c r="G164" s="5" t="inlineStr">
@@ -9216,7 +9216,7 @@
       </c>
       <c r="L164" s="5" t="n"/>
       <c r="M164" s="7" t="n">
-        <v>16.93</v>
+        <v>17.18</v>
       </c>
     </row>
     <row r="165">
@@ -9227,7 +9227,7 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955642 - KIT4M05563573WKC</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482708 - KIT4M04604736T7C</t>
         </is>
       </c>
       <c r="C165" s="3" t="n">
@@ -9238,12 +9238,12 @@
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563573WKC</t>
+          <t>KIT4M04604736T7C</t>
         </is>
       </c>
       <c r="F165" s="4" t="inlineStr">
         <is>
-          <t>814488</t>
+          <t>809662</t>
         </is>
       </c>
       <c r="G165" s="5" t="inlineStr">
@@ -9269,7 +9269,7 @@
       </c>
       <c r="L165" s="5" t="n"/>
       <c r="M165" s="7" t="n">
-        <v>16.33</v>
+        <v>16.93</v>
       </c>
     </row>
     <row r="166">
@@ -9322,7 +9322,7 @@
       </c>
       <c r="L166" s="5" t="n"/>
       <c r="M166" s="7" t="n">
-        <v>16.23</v>
+        <v>16.43</v>
       </c>
     </row>
     <row r="167">
@@ -9333,7 +9333,7 @@
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955252 - KIT4M05563584FVC</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955642 - KIT4M05563573WKC</t>
         </is>
       </c>
       <c r="C167" s="3" t="n">
@@ -9344,12 +9344,12 @@
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563584FVC</t>
+          <t>KIT4M05563573WKC</t>
         </is>
       </c>
       <c r="F167" s="4" t="inlineStr">
         <is>
-          <t>814439</t>
+          <t>814488</t>
         </is>
       </c>
       <c r="G167" s="5" t="inlineStr">
@@ -9375,7 +9375,7 @@
       </c>
       <c r="L167" s="5" t="n"/>
       <c r="M167" s="7" t="n">
-        <v>15.44</v>
+        <v>16.34</v>
       </c>
     </row>
     <row r="168">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020649252 - KIT4P00066848VQM</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955252 - KIT4M05563584FVC</t>
         </is>
       </c>
       <c r="C168" s="3" t="n">
@@ -9397,17 +9397,17 @@
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00066848VQM</t>
+          <t>KIT4M05563584FVC</t>
         </is>
       </c>
       <c r="F168" s="4" t="inlineStr">
         <is>
-          <t>812923</t>
+          <t>814439</t>
         </is>
       </c>
       <c r="G168" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H168" s="5" t="inlineStr">
@@ -9428,7 +9428,7 @@
       </c>
       <c r="L168" s="5" t="n"/>
       <c r="M168" s="7" t="n">
-        <v>14.84</v>
+        <v>16.19</v>
       </c>
     </row>
     <row r="169">
@@ -9439,7 +9439,7 @@
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955482 - KIT4M055635088NK</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020649252 - KIT4P00066848VQM</t>
         </is>
       </c>
       <c r="C169" s="3" t="n">
@@ -9450,17 +9450,17 @@
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635088NK</t>
+          <t>KIT4P00066848VQM</t>
         </is>
       </c>
       <c r="F169" s="4" t="inlineStr">
         <is>
-          <t>814434</t>
+          <t>812923</t>
         </is>
       </c>
       <c r="G169" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H169" s="5" t="inlineStr">
@@ -9481,7 +9481,7 @@
       </c>
       <c r="L169" s="5" t="n"/>
       <c r="M169" s="7" t="n">
-        <v>14.62</v>
+        <v>16.08</v>
       </c>
     </row>
     <row r="170">
@@ -9492,7 +9492,7 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955152 - KIT4M05563514P8T</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955482 - KIT4M055635088NK</t>
         </is>
       </c>
       <c r="C170" s="3" t="n">
@@ -9503,12 +9503,12 @@
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563514P8T</t>
+          <t>KIT4M055635088NK</t>
         </is>
       </c>
       <c r="F170" s="4" t="inlineStr">
         <is>
-          <t>814436</t>
+          <t>814434</t>
         </is>
       </c>
       <c r="G170" s="5" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="L170" s="5" t="n"/>
       <c r="M170" s="7" t="n">
-        <v>14.62</v>
+        <v>15.45</v>
       </c>
     </row>
     <row r="171">
@@ -9545,7 +9545,7 @@
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - CW6642812 - KIT4M054138292ZP</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955152 - KIT4M05563514P8T</t>
         </is>
       </c>
       <c r="C171" s="3" t="n">
@@ -9556,12 +9556,12 @@
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138292ZP</t>
+          <t>KIT4M05563514P8T</t>
         </is>
       </c>
       <c r="F171" s="4" t="inlineStr">
         <is>
-          <t>812784</t>
+          <t>814436</t>
         </is>
       </c>
       <c r="G171" s="5" t="inlineStr">
@@ -9587,7 +9587,7 @@
       </c>
       <c r="L171" s="5" t="n"/>
       <c r="M171" s="7" t="n">
-        <v>14.46</v>
+        <v>14.75</v>
       </c>
     </row>
     <row r="172">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020649862 - KIT4M04475159PMD</t>
+          <t>SMA - 05900510 - Los Angeles CA - CW6642812 - KIT4M054138292ZP</t>
         </is>
       </c>
       <c r="C172" s="3" t="n">
@@ -9609,12 +9609,12 @@
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475159PMD</t>
+          <t>KIT4M054138292ZP</t>
         </is>
       </c>
       <c r="F172" s="4" t="inlineStr">
         <is>
-          <t>809868</t>
+          <t>812784</t>
         </is>
       </c>
       <c r="G172" s="5" t="inlineStr">
@@ -9640,7 +9640,7 @@
       </c>
       <c r="L172" s="5" t="n"/>
       <c r="M172" s="7" t="n">
-        <v>14.45</v>
+        <v>14.46</v>
       </c>
     </row>
     <row r="173">
@@ -9651,7 +9651,7 @@
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020650152 - KIT4M054138189C7</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020649862 - KIT4M04475159PMD</t>
         </is>
       </c>
       <c r="C173" s="3" t="n">
@@ -9662,12 +9662,12 @@
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138189C7</t>
+          <t>KIT4M04475159PMD</t>
         </is>
       </c>
       <c r="F173" s="4" t="inlineStr">
         <is>
-          <t>812831</t>
+          <t>809868</t>
         </is>
       </c>
       <c r="G173" s="5" t="inlineStr">
@@ -9693,7 +9693,7 @@
       </c>
       <c r="L173" s="5" t="n"/>
       <c r="M173" s="7" t="n">
-        <v>14.32</v>
+        <v>14.45</v>
       </c>
     </row>
     <row r="174">
@@ -9704,7 +9704,7 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955402 - KIT4M05563610HM2</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020650152 - KIT4M054138189C7</t>
         </is>
       </c>
       <c r="C174" s="3" t="n">
@@ -9715,12 +9715,12 @@
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563610HM2</t>
+          <t>KIT4M054138189C7</t>
         </is>
       </c>
       <c r="F174" s="4" t="inlineStr">
         <is>
-          <t>814486</t>
+          <t>812831</t>
         </is>
       </c>
       <c r="G174" s="5" t="inlineStr">
@@ -9746,7 +9746,7 @@
       </c>
       <c r="L174" s="5" t="n"/>
       <c r="M174" s="7" t="n">
-        <v>14.14</v>
+        <v>14.38</v>
       </c>
     </row>
     <row r="175">
@@ -9757,7 +9757,7 @@
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270110 - KIT4M038677586ZX</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955402 - KIT4M05563610HM2</t>
         </is>
       </c>
       <c r="C175" s="3" t="n">
@@ -9768,12 +9768,12 @@
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>KIT4M038677586ZX</t>
+          <t>KIT4M05563610HM2</t>
         </is>
       </c>
       <c r="F175" s="4" t="inlineStr">
         <is>
-          <t>809623</t>
+          <t>814486</t>
         </is>
       </c>
       <c r="G175" s="5" t="inlineStr">
@@ -9799,7 +9799,7 @@
       </c>
       <c r="L175" s="5" t="n"/>
       <c r="M175" s="7" t="n">
-        <v>13.86</v>
+        <v>14.14</v>
       </c>
     </row>
     <row r="176">
@@ -9810,7 +9810,7 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649442 - KIT4M054137885SM</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020955432 - KIT4M05563533M9N</t>
         </is>
       </c>
       <c r="C176" s="3" t="n">
@@ -9821,12 +9821,12 @@
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137885SM</t>
+          <t>KIT4M05563533M9N</t>
         </is>
       </c>
       <c r="F176" s="4" t="inlineStr">
         <is>
-          <t>812846</t>
+          <t>814485</t>
         </is>
       </c>
       <c r="G176" s="5" t="inlineStr">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="L176" s="5" t="n"/>
       <c r="M176" s="7" t="n">
-        <v>13.24</v>
+        <v>13.91</v>
       </c>
     </row>
     <row r="177">
@@ -9863,7 +9863,7 @@
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020955432 - KIT4M05563533M9N</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270110 - KIT4M038677586ZX</t>
         </is>
       </c>
       <c r="C177" s="3" t="n">
@@ -9874,12 +9874,12 @@
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563533M9N</t>
+          <t>KIT4M038677586ZX</t>
         </is>
       </c>
       <c r="F177" s="4" t="inlineStr">
         <is>
-          <t>814485</t>
+          <t>809623</t>
         </is>
       </c>
       <c r="G177" s="5" t="inlineStr">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="L177" s="5" t="n"/>
       <c r="M177" s="7" t="n">
-        <v>12.94</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="178">
@@ -9916,7 +9916,7 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649282 - KIT4M05368213974</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437932 - KIT4M05799732NQK</t>
         </is>
       </c>
       <c r="C178" s="3" t="n">
@@ -9927,12 +9927,12 @@
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368213974</t>
+          <t>KIT4M05799732NQK</t>
         </is>
       </c>
       <c r="F178" s="4" t="inlineStr">
         <is>
-          <t>810647</t>
+          <t>816275</t>
         </is>
       </c>
       <c r="G178" s="5" t="inlineStr">
@@ -9958,7 +9958,7 @@
       </c>
       <c r="L178" s="5" t="n"/>
       <c r="M178" s="7" t="n">
-        <v>12.89</v>
+        <v>13.88</v>
       </c>
     </row>
     <row r="179">
@@ -9969,7 +9969,7 @@
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270114 - KIT4M04476539RJ5</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827011116 - KIT4M02578775B9Q</t>
         </is>
       </c>
       <c r="C179" s="3" t="n">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04476539RJ5</t>
+          <t>KIT4M02578775B9Q</t>
         </is>
       </c>
       <c r="F179" s="4" t="inlineStr">
         <is>
-          <t>809612</t>
+          <t>809611</t>
         </is>
       </c>
       <c r="G179" s="5" t="inlineStr">
@@ -10011,7 +10011,7 @@
       </c>
       <c r="L179" s="5" t="n"/>
       <c r="M179" s="7" t="n">
-        <v>11.32</v>
+        <v>13.67</v>
       </c>
     </row>
     <row r="180">
@@ -10022,7 +10022,7 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020650122-KIT4M05413776H84</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649282 - KIT4M05368213974</t>
         </is>
       </c>
       <c r="C180" s="3" t="n">
@@ -10033,12 +10033,12 @@
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413776H84</t>
+          <t>KIT4M05368213974</t>
         </is>
       </c>
       <c r="F180" s="4" t="inlineStr">
         <is>
-          <t>810101</t>
+          <t>810647</t>
         </is>
       </c>
       <c r="G180" s="5" t="inlineStr">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="L180" s="5" t="n"/>
       <c r="M180" s="7" t="n">
-        <v>11.05</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="181">
@@ -10075,7 +10075,7 @@
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 020955242 - KIT4M05563511FF4</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437612 - KIT4M058725265DP</t>
         </is>
       </c>
       <c r="C181" s="3" t="n">
@@ -10086,12 +10086,12 @@
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563511FF4</t>
+          <t>KIT4M058725265DP</t>
         </is>
       </c>
       <c r="F181" s="4" t="inlineStr">
         <is>
-          <t>814437</t>
+          <t>816192</t>
         </is>
       </c>
       <c r="G181" s="5" t="inlineStr">
@@ -10117,7 +10117,7 @@
       </c>
       <c r="L181" s="5" t="n"/>
       <c r="M181" s="7" t="n">
-        <v>10.96</v>
+        <v>12.21</v>
       </c>
     </row>
     <row r="182">
@@ -10128,7 +10128,7 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437552 - KIT4M05872586VCH</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270114 - KIT4M04476539RJ5</t>
         </is>
       </c>
       <c r="C182" s="3" t="n">
@@ -10139,12 +10139,12 @@
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872586VCH</t>
+          <t>KIT4M04476539RJ5</t>
         </is>
       </c>
       <c r="F182" s="4" t="inlineStr">
         <is>
-          <t>816068</t>
+          <t>809612</t>
         </is>
       </c>
       <c r="G182" s="5" t="inlineStr">
@@ -10170,7 +10170,7 @@
       </c>
       <c r="L182" s="5" t="n"/>
       <c r="M182" s="7" t="n">
-        <v>10.46</v>
+        <v>11.84</v>
       </c>
     </row>
     <row r="183">
@@ -10181,7 +10181,7 @@
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649582 - KIT4M05413774JZX</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437552 - KIT4M05872586VCH</t>
         </is>
       </c>
       <c r="C183" s="3" t="n">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413774JZX</t>
+          <t>KIT4M05872586VCH</t>
         </is>
       </c>
       <c r="F183" s="4" t="inlineStr">
         <is>
-          <t>812836</t>
+          <t>816068</t>
         </is>
       </c>
       <c r="G183" s="5" t="inlineStr">
@@ -10223,7 +10223,7 @@
       </c>
       <c r="L183" s="5" t="n"/>
       <c r="M183" s="7" t="n">
-        <v>10.46</v>
+        <v>11.58</v>
       </c>
     </row>
     <row r="184">
@@ -10234,7 +10234,7 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437932 - KIT4M05799732NQK</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438252 - KIT4M05872519KTN</t>
         </is>
       </c>
       <c r="C184" s="3" t="n">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799732NQK</t>
+          <t>KIT4M05872519KTN</t>
         </is>
       </c>
       <c r="F184" s="4" t="inlineStr">
         <is>
-          <t>816275</t>
+          <t>816084</t>
         </is>
       </c>
       <c r="G184" s="5" t="inlineStr">
@@ -10276,7 +10276,7 @@
       </c>
       <c r="L184" s="5" t="n"/>
       <c r="M184" s="7" t="n">
-        <v>10.29</v>
+        <v>11.13</v>
       </c>
     </row>
     <row r="185">
@@ -10287,7 +10287,7 @@
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955612 - KIT4M0556355588P</t>
+          <t>SMRT-05900510-Los Angeles CA-020650122-KIT4M05413776H84</t>
         </is>
       </c>
       <c r="C185" s="3" t="n">
@@ -10298,12 +10298,12 @@
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0556355588P</t>
+          <t>KIT4M05413776H84</t>
         </is>
       </c>
       <c r="F185" s="4" t="inlineStr">
         <is>
-          <t>814455</t>
+          <t>810101</t>
         </is>
       </c>
       <c r="G185" s="5" t="inlineStr">
@@ -10329,7 +10329,7 @@
       </c>
       <c r="L185" s="5" t="n"/>
       <c r="M185" s="7" t="n">
-        <v>9.140000000000001</v>
+        <v>11.05</v>
       </c>
     </row>
     <row r="186">
@@ -10340,7 +10340,7 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649962 - KIT4M05413783PFQ</t>
+          <t>SS - 05900510 -  Los Angeles CA - 020955242 - KIT4M05563511FF4</t>
         </is>
       </c>
       <c r="C186" s="3" t="n">
@@ -10351,12 +10351,12 @@
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413783PFQ</t>
+          <t>KIT4M05563511FF4</t>
         </is>
       </c>
       <c r="F186" s="4" t="inlineStr">
         <is>
-          <t>812845</t>
+          <t>814437</t>
         </is>
       </c>
       <c r="G186" s="5" t="inlineStr">
@@ -10382,7 +10382,7 @@
       </c>
       <c r="L186" s="5" t="n"/>
       <c r="M186" s="7" t="n">
-        <v>7.46</v>
+        <v>10.96</v>
       </c>
     </row>
     <row r="187">
@@ -10393,7 +10393,7 @@
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437402 - KIT4M05872537SGZ</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649582 - KIT4M05413774JZX</t>
         </is>
       </c>
       <c r="C187" s="3" t="n">
@@ -10404,12 +10404,12 @@
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872537SGZ</t>
+          <t>KIT4M05413774JZX</t>
         </is>
       </c>
       <c r="F187" s="4" t="inlineStr">
         <is>
-          <t>816073</t>
+          <t>812836</t>
         </is>
       </c>
       <c r="G187" s="5" t="inlineStr">
@@ -10435,7 +10435,7 @@
       </c>
       <c r="L187" s="5" t="n"/>
       <c r="M187" s="7" t="n">
-        <v>7.42</v>
+        <v>10.46</v>
       </c>
     </row>
     <row r="188">
@@ -10446,7 +10446,7 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649792 - KIT4M04475151HTP</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955612 - KIT4M0556355588P</t>
         </is>
       </c>
       <c r="C188" s="3" t="n">
@@ -10457,12 +10457,12 @@
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475151HTP</t>
+          <t>KIT4M0556355588P</t>
         </is>
       </c>
       <c r="F188" s="4" t="inlineStr">
         <is>
-          <t>809867</t>
+          <t>814455</t>
         </is>
       </c>
       <c r="G188" s="5" t="inlineStr">
@@ -10488,7 +10488,7 @@
       </c>
       <c r="L188" s="5" t="n"/>
       <c r="M188" s="7" t="n">
-        <v>7.08</v>
+        <v>9.140000000000001</v>
       </c>
     </row>
     <row r="189">
@@ -10499,7 +10499,7 @@
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles, CA - 0204827011114 - KIT4M03986267RWH</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649962 - KIT4M05413783PFQ</t>
         </is>
       </c>
       <c r="C189" s="3" t="n">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03986267RWH</t>
+          <t>KIT4M05413783PFQ</t>
         </is>
       </c>
       <c r="F189" s="4" t="inlineStr">
         <is>
-          <t>809616</t>
+          <t>812845</t>
         </is>
       </c>
       <c r="G189" s="5" t="inlineStr">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="L189" s="5" t="n"/>
       <c r="M189" s="7" t="n">
-        <v>6.86</v>
+        <v>8.359999999999999</v>
       </c>
     </row>
     <row r="190">
@@ -10594,7 +10594,7 @@
       </c>
       <c r="L190" s="5" t="n"/>
       <c r="M190" s="7" t="n">
-        <v>6.51</v>
+        <v>7.96</v>
       </c>
     </row>
     <row r="191">
@@ -10605,7 +10605,7 @@
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437902 - KIT4M05799717WZV</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437402 - KIT4M05872537SGZ</t>
         </is>
       </c>
       <c r="C191" s="3" t="n">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799717WZV</t>
+          <t>KIT4M05872537SGZ</t>
         </is>
       </c>
       <c r="F191" s="4" t="inlineStr">
         <is>
-          <t>816280</t>
+          <t>816073</t>
         </is>
       </c>
       <c r="G191" s="5" t="inlineStr">
@@ -10647,7 +10647,7 @@
       </c>
       <c r="L191" s="5" t="n"/>
       <c r="M191" s="7" t="n">
-        <v>6.42</v>
+        <v>7.61</v>
       </c>
     </row>
     <row r="192">
@@ -10658,7 +10658,7 @@
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>SSC - 05900510 -  Los Angeles CA - 021437862 - KIT4M05872516CJM</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649732 - KIT4M046047467T4</t>
         </is>
       </c>
       <c r="C192" s="3" t="n">
@@ -10669,12 +10669,12 @@
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872516CJM</t>
+          <t>KIT4M046047467T4</t>
         </is>
       </c>
       <c r="F192" s="4" t="inlineStr">
         <is>
-          <t>816087</t>
+          <t>809865</t>
         </is>
       </c>
       <c r="G192" s="5" t="inlineStr">
@@ -10700,7 +10700,7 @@
       </c>
       <c r="L192" s="5" t="n"/>
       <c r="M192" s="7" t="n">
-        <v>6.14</v>
+        <v>7.15</v>
       </c>
     </row>
     <row r="193">
@@ -10711,7 +10711,7 @@
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438262 - KIT4M05872530RPF</t>
+          <t>SSC - 05900510 -  Los Angeles CA - 021437862 - KIT4M05872516CJM</t>
         </is>
       </c>
       <c r="C193" s="3" t="n">
@@ -10722,12 +10722,12 @@
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872530RPF</t>
+          <t>KIT4M05872516CJM</t>
         </is>
       </c>
       <c r="F193" s="4" t="inlineStr">
         <is>
-          <t>816079</t>
+          <t>816087</t>
         </is>
       </c>
       <c r="G193" s="5" t="inlineStr">
@@ -10753,7 +10753,7 @@
       </c>
       <c r="L193" s="5" t="n"/>
       <c r="M193" s="7" t="n">
-        <v>6.07</v>
+        <v>7.09</v>
       </c>
     </row>
     <row r="194">
@@ -10764,7 +10764,7 @@
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649732 - KIT4M046047467T4</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649792 - KIT4M04475151HTP</t>
         </is>
       </c>
       <c r="C194" s="3" t="n">
@@ -10775,12 +10775,12 @@
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047467T4</t>
+          <t>KIT4M04475151HTP</t>
         </is>
       </c>
       <c r="F194" s="4" t="inlineStr">
         <is>
-          <t>809865</t>
+          <t>809867</t>
         </is>
       </c>
       <c r="G194" s="5" t="inlineStr">
@@ -10806,7 +10806,7 @@
       </c>
       <c r="L194" s="5" t="n"/>
       <c r="M194" s="7" t="n">
-        <v>6</v>
+        <v>7.08</v>
       </c>
     </row>
     <row r="195">
@@ -10817,7 +10817,7 @@
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649642 - KIT4M05413826Z6Z</t>
+          <t>STS - 05900510 - Los Angeles, CA - 0204827011114 - KIT4M03986267RWH</t>
         </is>
       </c>
       <c r="C195" s="3" t="n">
@@ -10828,12 +10828,12 @@
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413826Z6Z</t>
+          <t>KIT4M03986267RWH</t>
         </is>
       </c>
       <c r="F195" s="4" t="inlineStr">
         <is>
-          <t>812804</t>
+          <t>809616</t>
         </is>
       </c>
       <c r="G195" s="5" t="inlineStr">
@@ -10859,7 +10859,7 @@
       </c>
       <c r="L195" s="5" t="n"/>
       <c r="M195" s="7" t="n">
-        <v>5.9</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="196">
@@ -10870,7 +10870,7 @@
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>SSC - 05900510 - Los Angeles CA - 021437792 - KIT4M05872507528</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437902 - KIT4M05799717WZV</t>
         </is>
       </c>
       <c r="C196" s="3" t="n">
@@ -10881,12 +10881,12 @@
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872507528</t>
+          <t>KIT4M05799717WZV</t>
         </is>
       </c>
       <c r="F196" s="4" t="inlineStr">
         <is>
-          <t>816083</t>
+          <t>816280</t>
         </is>
       </c>
       <c r="G196" s="5" t="inlineStr">
@@ -10912,7 +10912,7 @@
       </c>
       <c r="L196" s="5" t="n"/>
       <c r="M196" s="7" t="n">
-        <v>5.85</v>
+        <v>6.77</v>
       </c>
     </row>
     <row r="197">
@@ -10923,7 +10923,7 @@
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827011110 - KIT4M03866627GHD</t>
+          <t>SSC - 05900510 - Los Angeles CA - 021437792 - KIT4M05872507528</t>
         </is>
       </c>
       <c r="C197" s="3" t="n">
@@ -10934,12 +10934,12 @@
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03866627GHD</t>
+          <t>KIT4M05872507528</t>
         </is>
       </c>
       <c r="F197" s="4" t="inlineStr">
         <is>
-          <t>809619</t>
+          <t>816083</t>
         </is>
       </c>
       <c r="G197" s="5" t="inlineStr">
@@ -10965,7 +10965,7 @@
       </c>
       <c r="L197" s="5" t="n"/>
       <c r="M197" s="7" t="n">
-        <v>5.78</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="198">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020650182 - KIT4M05413821GGW</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438262 - KIT4M05872530RPF</t>
         </is>
       </c>
       <c r="C198" s="3" t="n">
@@ -10987,12 +10987,12 @@
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413821GGW</t>
+          <t>KIT4M05872530RPF</t>
         </is>
       </c>
       <c r="F198" s="4" t="inlineStr">
         <is>
-          <t>812830</t>
+          <t>816079</t>
         </is>
       </c>
       <c r="G198" s="5" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="L198" s="5" t="n"/>
       <c r="M198" s="7" t="n">
-        <v>5.51</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="199">
@@ -11029,7 +11029,7 @@
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827011116 - KIT4M02578775B9Q</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649642 - KIT4M05413826Z6Z</t>
         </is>
       </c>
       <c r="C199" s="3" t="n">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>KIT4M02578775B9Q</t>
+          <t>KIT4M05413826Z6Z</t>
         </is>
       </c>
       <c r="F199" s="4" t="inlineStr">
         <is>
-          <t>809611</t>
+          <t>812804</t>
         </is>
       </c>
       <c r="G199" s="5" t="inlineStr">
@@ -11071,7 +11071,7 @@
       </c>
       <c r="L199" s="5" t="n"/>
       <c r="M199" s="7" t="n">
-        <v>4.95</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="200">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437582 - KIT4M05872573K7P</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827011110 - KIT4M03866627GHD</t>
         </is>
       </c>
       <c r="C200" s="3" t="n">
@@ -11093,12 +11093,12 @@
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872573K7P</t>
+          <t>KIT4M03866627GHD</t>
         </is>
       </c>
       <c r="F200" s="4" t="inlineStr">
         <is>
-          <t>816067</t>
+          <t>809619</t>
         </is>
       </c>
       <c r="G200" s="5" t="inlineStr">
@@ -11124,7 +11124,7 @@
       </c>
       <c r="L200" s="5" t="n"/>
       <c r="M200" s="7" t="n">
-        <v>4.28</v>
+        <v>5.78</v>
       </c>
     </row>
     <row r="201">
@@ -11135,7 +11135,7 @@
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437412 - KIT4M05872548P2H</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020650182 - KIT4M05413821GGW</t>
         </is>
       </c>
       <c r="C201" s="3" t="n">
@@ -11146,12 +11146,12 @@
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872548P2H</t>
+          <t>KIT4M05413821GGW</t>
         </is>
       </c>
       <c r="F201" s="4" t="inlineStr">
         <is>
-          <t>816066</t>
+          <t>812830</t>
         </is>
       </c>
       <c r="G201" s="5" t="inlineStr">
@@ -11177,7 +11177,7 @@
       </c>
       <c r="L201" s="5" t="n"/>
       <c r="M201" s="7" t="n">
-        <v>3.95</v>
+        <v>5.51</v>
       </c>
     </row>
     <row r="202">
@@ -11188,7 +11188,7 @@
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438252 - KIT4M05872519KTN</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437412 - KIT4M05872548P2H</t>
         </is>
       </c>
       <c r="C202" s="3" t="n">
@@ -11199,12 +11199,12 @@
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872519KTN</t>
+          <t>KIT4M05872548P2H</t>
         </is>
       </c>
       <c r="F202" s="4" t="inlineStr">
         <is>
-          <t>816084</t>
+          <t>816066</t>
         </is>
       </c>
       <c r="G202" s="5" t="inlineStr">
@@ -11230,7 +11230,7 @@
       </c>
       <c r="L202" s="5" t="n"/>
       <c r="M202" s="7" t="n">
-        <v>3.21</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="203">
@@ -11241,7 +11241,7 @@
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649752 - KIT4M03867749CW5</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437582 - KIT4M05872573K7P</t>
         </is>
       </c>
       <c r="C203" s="3" t="n">
@@ -11252,12 +11252,12 @@
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03867749CW5</t>
+          <t>KIT4M05872573K7P</t>
         </is>
       </c>
       <c r="F203" s="4" t="inlineStr">
         <is>
-          <t>809877</t>
+          <t>816067</t>
         </is>
       </c>
       <c r="G203" s="5" t="inlineStr">
@@ -11283,7 +11283,7 @@
       </c>
       <c r="L203" s="5" t="n"/>
       <c r="M203" s="7" t="n">
-        <v>3</v>
+        <v>4.28</v>
       </c>
     </row>
     <row r="204">
@@ -11336,7 +11336,7 @@
       </c>
       <c r="L204" s="5" t="n"/>
       <c r="M204" s="7" t="n">
-        <v>2.95</v>
+        <v>3.22</v>
       </c>
     </row>
     <row r="205">
@@ -11347,7 +11347,7 @@
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827012 - KIT4M04606110GTV</t>
+          <t>SS - 05900510 -  Los Angeles CA - 020955572 - KIT4M05563606ZRC</t>
         </is>
       </c>
       <c r="C205" s="3" t="n">
@@ -11358,12 +11358,12 @@
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04606110GTV</t>
+          <t>KIT4M05563606ZRC</t>
         </is>
       </c>
       <c r="F205" s="4" t="inlineStr">
         <is>
-          <t>809660</t>
+          <t>814464</t>
         </is>
       </c>
       <c r="G205" s="5" t="inlineStr">
@@ -11389,7 +11389,7 @@
       </c>
       <c r="L205" s="5" t="n"/>
       <c r="M205" s="7" t="n">
-        <v>2.61</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="206">
@@ -11400,7 +11400,7 @@
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 020955572 - KIT4M05563606ZRC</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649752 - KIT4M03867749CW5</t>
         </is>
       </c>
       <c r="C206" s="3" t="n">
@@ -11411,12 +11411,12 @@
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563606ZRC</t>
+          <t>KIT4M03867749CW5</t>
         </is>
       </c>
       <c r="F206" s="4" t="inlineStr">
         <is>
-          <t>814464</t>
+          <t>809877</t>
         </is>
       </c>
       <c r="G206" s="5" t="inlineStr">
@@ -11442,7 +11442,7 @@
       </c>
       <c r="L206" s="5" t="n"/>
       <c r="M206" s="7" t="n">
-        <v>2.48</v>
+        <v>3.05</v>
       </c>
     </row>
     <row r="207">
@@ -11453,7 +11453,7 @@
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649892 - KIT4M05413777DGG</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827012 - KIT4M04606110GTV</t>
         </is>
       </c>
       <c r="C207" s="3" t="n">
@@ -11464,12 +11464,12 @@
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413777DGG</t>
+          <t>KIT4M04606110GTV</t>
         </is>
       </c>
       <c r="F207" s="4" t="inlineStr">
         <is>
-          <t>812802</t>
+          <t>809660</t>
         </is>
       </c>
       <c r="G207" s="5" t="inlineStr">
@@ -11495,7 +11495,7 @@
       </c>
       <c r="L207" s="5" t="n"/>
       <c r="M207" s="7" t="n">
-        <v>1.65</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="208">
@@ -11506,7 +11506,7 @@
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437612 - KIT4M058725265DP</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649892 - KIT4M05413777DGG</t>
         </is>
       </c>
       <c r="C208" s="3" t="n">
@@ -11517,12 +11517,12 @@
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725265DP</t>
+          <t>KIT4M05413777DGG</t>
         </is>
       </c>
       <c r="F208" s="4" t="inlineStr">
         <is>
-          <t>816192</t>
+          <t>812802</t>
         </is>
       </c>
       <c r="G208" s="5" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="L208" s="5" t="n"/>
       <c r="M208" s="7" t="n">
-        <v>1.58</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="209">
@@ -11771,7 +11771,7 @@
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491804TBC</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955542 - KIT4M05563551N6Q</t>
         </is>
       </c>
       <c r="C213" s="3" t="n">
@@ -11782,12 +11782,12 @@
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491804TBC</t>
+          <t>KIT4M05563551N6Q</t>
         </is>
       </c>
       <c r="F213" s="4" t="inlineStr">
         <is>
-          <t>816373</t>
+          <t>814450</t>
         </is>
       </c>
       <c r="G213" s="5" t="inlineStr">
@@ -11813,7 +11813,7 @@
       </c>
       <c r="L213" s="5" t="n"/>
       <c r="M213" s="7" t="n">
-        <v>0.6</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="214">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491800F52</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491804TBC</t>
         </is>
       </c>
       <c r="C214" s="3" t="n">
@@ -11835,12 +11835,12 @@
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491800F52</t>
+          <t>KIT4M06491804TBC</t>
         </is>
       </c>
       <c r="F214" s="4" t="inlineStr">
         <is>
-          <t>816406</t>
+          <t>816373</t>
         </is>
       </c>
       <c r="G214" s="5" t="inlineStr">
@@ -11866,7 +11866,7 @@
       </c>
       <c r="L214" s="5" t="n"/>
       <c r="M214" s="7" t="n">
-        <v>0.35</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="215">
@@ -11877,7 +11877,7 @@
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437812-KIT4M058724947VX</t>
+          <t>SMRT-05900510-Los Angeles CA-020649472-KIT4M05413795QHK</t>
         </is>
       </c>
       <c r="C215" s="3" t="n">
@@ -11888,12 +11888,12 @@
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058724947VX</t>
+          <t>KIT4M05413795QHK</t>
         </is>
       </c>
       <c r="F215" s="4" t="inlineStr">
         <is>
-          <t>816086</t>
+          <t>812801</t>
         </is>
       </c>
       <c r="G215" s="5" t="inlineStr">
@@ -11919,7 +11919,7 @@
       </c>
       <c r="L215" s="5" t="n"/>
       <c r="M215" s="7" t="n">
-        <v>0.26</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="216">
@@ -11930,7 +11930,7 @@
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020650062 - KIT4M05413797HK5</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491800F52</t>
         </is>
       </c>
       <c r="C216" s="3" t="n">
@@ -11941,12 +11941,12 @@
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413797HK5</t>
+          <t>KIT4M06491800F52</t>
         </is>
       </c>
       <c r="F216" s="4" t="inlineStr">
         <is>
-          <t>812808</t>
+          <t>816406</t>
         </is>
       </c>
       <c r="G216" s="5" t="inlineStr">
@@ -11972,7 +11972,7 @@
       </c>
       <c r="L216" s="5" t="n"/>
       <c r="M216" s="7" t="n">
-        <v>0.24</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="217">
@@ -11983,7 +11983,7 @@
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649702 - KIT4M04604741P2X</t>
+          <t>SMRT-05900510-Los Angeles CA-021437812-KIT4M058724947VX</t>
         </is>
       </c>
       <c r="C217" s="3" t="n">
@@ -11994,12 +11994,12 @@
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604741P2X</t>
+          <t>KIT4M058724947VX</t>
         </is>
       </c>
       <c r="F217" s="4" t="inlineStr">
         <is>
-          <t>809871</t>
+          <t>816086</t>
         </is>
       </c>
       <c r="G217" s="5" t="inlineStr">
@@ -12025,7 +12025,7 @@
       </c>
       <c r="L217" s="5" t="n"/>
       <c r="M217" s="7" t="n">
-        <v>0.23</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="218">
@@ -12036,7 +12036,7 @@
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020649522-KIT4M05413834FTH</t>
+          <t>SS - 05900510 - Los Angeles CA - 020650062 - KIT4M05413797HK5</t>
         </is>
       </c>
       <c r="C218" s="3" t="n">
@@ -12047,12 +12047,12 @@
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413834FTH</t>
+          <t>KIT4M05413797HK5</t>
         </is>
       </c>
       <c r="F218" s="4" t="inlineStr">
         <is>
-          <t>812817</t>
+          <t>812808</t>
         </is>
       </c>
       <c r="G218" s="5" t="inlineStr">
@@ -12078,7 +12078,7 @@
       </c>
       <c r="L218" s="5" t="n"/>
       <c r="M218" s="7" t="n">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="219">
@@ -12089,7 +12089,7 @@
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 6862083  - KIT4M05799682BXX</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649702 - KIT4M04604741P2X</t>
         </is>
       </c>
       <c r="C219" s="3" t="n">
@@ -12100,12 +12100,12 @@
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799682BXX</t>
+          <t>KIT4M04604741P2X</t>
         </is>
       </c>
       <c r="F219" s="4" t="inlineStr">
         <is>
-          <t>816278</t>
+          <t>809871</t>
         </is>
       </c>
       <c r="G219" s="5" t="inlineStr">
@@ -12131,7 +12131,7 @@
       </c>
       <c r="L219" s="5" t="n"/>
       <c r="M219" s="7" t="n">
-        <v>0.19</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="220">
@@ -12142,7 +12142,7 @@
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437832 - KIT4M05872486FXZ</t>
+          <t>SMRT-05900510-Los Angeles CA-020649522-KIT4M05413834FTH</t>
         </is>
       </c>
       <c r="C220" s="3" t="n">
@@ -12153,12 +12153,12 @@
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872486FXZ</t>
+          <t>KIT4M05413834FTH</t>
         </is>
       </c>
       <c r="F220" s="4" t="inlineStr">
         <is>
-          <t>816088</t>
+          <t>812817</t>
         </is>
       </c>
       <c r="G220" s="5" t="inlineStr">
@@ -12184,7 +12184,7 @@
       </c>
       <c r="L220" s="5" t="n"/>
       <c r="M220" s="7" t="n">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="221">
@@ -12195,7 +12195,7 @@
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020649472-KIT4M05413795QHK</t>
+          <t>SS - 05900510 - Los Angeles CA - 6862083  - KIT4M05799682BXX</t>
         </is>
       </c>
       <c r="C221" s="3" t="n">
@@ -12206,12 +12206,12 @@
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413795QHK</t>
+          <t>KIT4M05799682BXX</t>
         </is>
       </c>
       <c r="F221" s="4" t="inlineStr">
         <is>
-          <t>812801</t>
+          <t>816278</t>
         </is>
       </c>
       <c r="G221" s="5" t="inlineStr">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="L221" s="5" t="n"/>
       <c r="M221" s="7" t="n">
-        <v>0.16</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="222">
@@ -12248,7 +12248,7 @@
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955422 - KIT4M05563517BVR</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437832 - KIT4M05872486FXZ</t>
         </is>
       </c>
       <c r="C222" s="3" t="n">
@@ -12259,12 +12259,12 @@
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563517BVR</t>
+          <t>KIT4M05872486FXZ</t>
         </is>
       </c>
       <c r="F222" s="4" t="inlineStr">
         <is>
-          <t>814438</t>
+          <t>816088</t>
         </is>
       </c>
       <c r="G222" s="5" t="inlineStr">
@@ -12290,7 +12290,7 @@
       </c>
       <c r="L222" s="5" t="n"/>
       <c r="M222" s="7" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="223">
@@ -12301,7 +12301,7 @@
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491836Z2D</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955422 - KIT4M05563517BVR</t>
         </is>
       </c>
       <c r="C223" s="3" t="n">
@@ -12312,12 +12312,12 @@
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491836Z2D</t>
+          <t>KIT4M05563517BVR</t>
         </is>
       </c>
       <c r="F223" s="4" t="inlineStr">
         <is>
-          <t>816366</t>
+          <t>814438</t>
         </is>
       </c>
       <c r="G223" s="5" t="inlineStr">
@@ -12343,7 +12343,7 @@
       </c>
       <c r="L223" s="5" t="n"/>
       <c r="M223" s="7" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="224">
@@ -12354,7 +12354,7 @@
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 6862083  - KIT4M057996395ZF</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491836Z2D</t>
         </is>
       </c>
       <c r="C224" s="3" t="n">
@@ -12365,12 +12365,12 @@
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>KIT4M057996395ZF</t>
+          <t>KIT4M06491836Z2D</t>
         </is>
       </c>
       <c r="F224" s="4" t="inlineStr">
         <is>
-          <t>816268</t>
+          <t>816366</t>
         </is>
       </c>
       <c r="G224" s="5" t="inlineStr">
@@ -12513,7 +12513,7 @@
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437302 - KIT4M05872571T4K</t>
+          <t>SS - 05900510 - Los Angeles CA - 6862083  - KIT4M057996395ZF</t>
         </is>
       </c>
       <c r="C227" s="3" t="n">
@@ -12524,12 +12524,12 @@
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872571T4K</t>
+          <t>KIT4M057996395ZF</t>
         </is>
       </c>
       <c r="F227" s="4" t="inlineStr">
         <is>
-          <t>816106</t>
+          <t>816268</t>
         </is>
       </c>
       <c r="G227" s="5" t="inlineStr">
@@ -12555,7 +12555,7 @@
       </c>
       <c r="L227" s="5" t="n"/>
       <c r="M227" s="7" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="228">
@@ -12566,7 +12566,7 @@
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491814FV7</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438022 - KIT4M05799705T6B</t>
         </is>
       </c>
       <c r="C228" s="3" t="n">
@@ -12577,12 +12577,12 @@
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491814FV7</t>
+          <t>KIT4M05799705T6B</t>
         </is>
       </c>
       <c r="F228" s="4" t="inlineStr">
         <is>
-          <t>816370</t>
+          <t>816285</t>
         </is>
       </c>
       <c r="G228" s="5" t="inlineStr">
@@ -12619,7 +12619,7 @@
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438022 - KIT4M05799705T6B</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437302 - KIT4M05872571T4K</t>
         </is>
       </c>
       <c r="C229" s="3" t="n">
@@ -12630,12 +12630,12 @@
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799705T6B</t>
+          <t>KIT4M05872571T4K</t>
         </is>
       </c>
       <c r="F229" s="4" t="inlineStr">
         <is>
-          <t>816285</t>
+          <t>816106</t>
         </is>
       </c>
       <c r="G229" s="5" t="inlineStr">
@@ -12672,7 +12672,7 @@
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918277QF</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491814FV7</t>
         </is>
       </c>
       <c r="C230" s="3" t="n">
@@ -12683,12 +12683,12 @@
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918277QF</t>
+          <t>KIT4M06491814FV7</t>
         </is>
       </c>
       <c r="F230" s="4" t="inlineStr">
         <is>
-          <t>816403</t>
+          <t>816370</t>
         </is>
       </c>
       <c r="G230" s="5" t="inlineStr">
@@ -12714,7 +12714,7 @@
       </c>
       <c r="L230" s="5" t="n"/>
       <c r="M230" s="7" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="231">
@@ -12725,7 +12725,7 @@
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437312 - KIT4M05872568PR6</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918277QF</t>
         </is>
       </c>
       <c r="C231" s="3" t="n">
@@ -12736,12 +12736,12 @@
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872568PR6</t>
+          <t>KIT4M064918277QF</t>
         </is>
       </c>
       <c r="F231" s="4" t="inlineStr">
         <is>
-          <t>816094</t>
+          <t>816403</t>
         </is>
       </c>
       <c r="G231" s="5" t="inlineStr">
@@ -12767,7 +12767,7 @@
       </c>
       <c r="L231" s="5" t="n"/>
       <c r="M231" s="7" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="232">
@@ -12937,7 +12937,7 @@
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437722 - KIT4M05872498PP4</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437312 - KIT4M05872568PR6</t>
         </is>
       </c>
       <c r="C235" s="3" t="n">
@@ -12948,12 +12948,12 @@
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872498PP4</t>
+          <t>KIT4M05872568PR6</t>
         </is>
       </c>
       <c r="F235" s="4" t="inlineStr">
         <is>
-          <t>816104</t>
+          <t>816094</t>
         </is>
       </c>
       <c r="G235" s="5" t="inlineStr">
@@ -12990,7 +12990,7 @@
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437692 - KIT4M05872518P78</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437722 - KIT4M05872498PP4</t>
         </is>
       </c>
       <c r="C236" s="3" t="n">
@@ -13001,12 +13001,12 @@
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872518P78</t>
+          <t>KIT4M05872498PP4</t>
         </is>
       </c>
       <c r="F236" s="4" t="inlineStr">
         <is>
-          <t>816184</t>
+          <t>816104</t>
         </is>
       </c>
       <c r="G236" s="5" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="L236" s="5" t="n"/>
       <c r="M236" s="7" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="237">
@@ -13096,7 +13096,7 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491818QD2</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437692 - KIT4M05872518P78</t>
         </is>
       </c>
       <c r="C238" s="3" t="n">
@@ -13107,12 +13107,12 @@
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491818QD2</t>
+          <t>KIT4M05872518P78</t>
         </is>
       </c>
       <c r="F238" s="4" t="inlineStr">
         <is>
-          <t>816378</t>
+          <t>816184</t>
         </is>
       </c>
       <c r="G238" s="5" t="inlineStr">
@@ -13573,7 +13573,7 @@
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064917914G5</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491818QD2</t>
         </is>
       </c>
       <c r="C247" s="3" t="n">
@@ -13584,12 +13584,12 @@
       </c>
       <c r="E247" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064917914G5</t>
+          <t>KIT4M06491818QD2</t>
         </is>
       </c>
       <c r="F247" s="4" t="inlineStr">
         <is>
-          <t>816392</t>
+          <t>816378</t>
         </is>
       </c>
       <c r="G247" s="5" t="inlineStr">
@@ -14421,7 +14421,7 @@
       </c>
       <c r="B263" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064917925MB</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064917914G5</t>
         </is>
       </c>
       <c r="C263" s="3" t="n">
@@ -14432,12 +14432,12 @@
       </c>
       <c r="E263" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064917925MB</t>
+          <t>KIT4M064917914G5</t>
         </is>
       </c>
       <c r="F263" s="4" t="inlineStr">
         <is>
-          <t>816381</t>
+          <t>816392</t>
         </is>
       </c>
       <c r="G263" s="5" t="inlineStr">
@@ -14633,7 +14633,7 @@
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491786BS9</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064917925MB</t>
         </is>
       </c>
       <c r="C267" s="3" t="n">
@@ -14644,12 +14644,12 @@
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491786BS9</t>
+          <t>KIT4M064917925MB</t>
         </is>
       </c>
       <c r="F267" s="4" t="inlineStr">
         <is>
-          <t>816396</t>
+          <t>816381</t>
         </is>
       </c>
       <c r="G267" s="5" t="inlineStr">
@@ -14686,7 +14686,7 @@
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918015Z2</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491786BS9</t>
         </is>
       </c>
       <c r="C268" s="3" t="n">
@@ -14697,12 +14697,12 @@
       </c>
       <c r="E268" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918015Z2</t>
+          <t>KIT4M06491786BS9</t>
         </is>
       </c>
       <c r="F268" s="4" t="inlineStr">
         <is>
-          <t>816376</t>
+          <t>816396</t>
         </is>
       </c>
       <c r="G268" s="5" t="inlineStr">
@@ -14728,7 +14728,7 @@
       </c>
       <c r="L268" s="5" t="n"/>
       <c r="M268" s="7" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="269">
@@ -14845,7 +14845,7 @@
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437372 - KIT4M058725505J5</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918015Z2</t>
         </is>
       </c>
       <c r="C271" s="3" t="n">
@@ -14856,12 +14856,12 @@
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725505J5</t>
+          <t>KIT4M064918015Z2</t>
         </is>
       </c>
       <c r="F271" s="4" t="inlineStr">
         <is>
-          <t>816117</t>
+          <t>816376</t>
         </is>
       </c>
       <c r="G271" s="5" t="inlineStr">
@@ -15057,7 +15057,7 @@
       </c>
       <c r="B275" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438082 - KIT4M05799668SS7</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437372 - KIT4M058725505J5</t>
         </is>
       </c>
       <c r="C275" s="3" t="n">
@@ -15068,12 +15068,12 @@
       </c>
       <c r="E275" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799668SS7</t>
+          <t>KIT4M058725505J5</t>
         </is>
       </c>
       <c r="F275" s="4" t="inlineStr">
         <is>
-          <t>816279</t>
+          <t>816117</t>
         </is>
       </c>
       <c r="G275" s="5" t="inlineStr">
@@ -15163,7 +15163,7 @@
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955542 - KIT4M05563551N6Q</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438082 - KIT4M05799668SS7</t>
         </is>
       </c>
       <c r="C277" s="3" t="n">
@@ -15174,12 +15174,12 @@
       </c>
       <c r="E277" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563551N6Q</t>
+          <t>KIT4M05799668SS7</t>
         </is>
       </c>
       <c r="F277" s="4" t="inlineStr">
         <is>
-          <t>814450</t>
+          <t>816279</t>
         </is>
       </c>
       <c r="G277" s="5" t="inlineStr">
@@ -16541,7 +16541,7 @@
       </c>
       <c r="B303" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649992 - KIT4M05413809J58</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437962 - KIT4M05799706Z6R</t>
         </is>
       </c>
       <c r="C303" s="3" t="n">
@@ -16552,12 +16552,12 @@
       </c>
       <c r="E303" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413809J58</t>
+          <t>KIT4M05799706Z6R</t>
         </is>
       </c>
       <c r="F303" s="4" t="inlineStr">
         <is>
-          <t>812805</t>
+          <t>816273</t>
         </is>
       </c>
       <c r="G303" s="5" t="inlineStr">
@@ -16594,7 +16594,7 @@
       </c>
       <c r="B304" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437962 - KIT4M05799706Z6R</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438292 - KIt4m058725108K2</t>
         </is>
       </c>
       <c r="C304" s="3" t="n">
@@ -16605,12 +16605,12 @@
       </c>
       <c r="E304" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799706Z6R</t>
+          <t>KIT4M058725108K2</t>
         </is>
       </c>
       <c r="F304" s="4" t="inlineStr">
         <is>
-          <t>816273</t>
+          <t>816287</t>
         </is>
       </c>
       <c r="G304" s="5" t="inlineStr">
@@ -16647,7 +16647,7 @@
       </c>
       <c r="B305" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438292 - KIt4m058725108K2</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649992 - KIT4M05413809J58</t>
         </is>
       </c>
       <c r="C305" s="3" t="n">
@@ -16658,12 +16658,12 @@
       </c>
       <c r="E305" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725108K2</t>
+          <t>KIT4M05413809J58</t>
         </is>
       </c>
       <c r="F305" s="4" t="inlineStr">
         <is>
-          <t>816287</t>
+          <t>812805</t>
         </is>
       </c>
       <c r="G305" s="5" t="inlineStr">
@@ -17760,7 +17760,7 @@
       </c>
       <c r="B326" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020650222 - KIT4M05413790XCD</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438272 - KIT4M05872517VS2</t>
         </is>
       </c>
       <c r="C326" s="3" t="n">
@@ -17771,12 +17771,12 @@
       </c>
       <c r="E326" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413790XCD</t>
+          <t>KIT4M05872517VS2</t>
         </is>
       </c>
       <c r="F326" s="4" t="inlineStr">
         <is>
-          <t>812822</t>
+          <t>816288</t>
         </is>
       </c>
       <c r="G326" s="5" t="inlineStr">
@@ -17813,7 +17813,7 @@
       </c>
       <c r="B327" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437982 - KIT4M05799678R5P</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438142  - KIT4M05799685DG5</t>
         </is>
       </c>
       <c r="C327" s="3" t="n">
@@ -17824,12 +17824,12 @@
       </c>
       <c r="E327" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799678R5P</t>
+          <t>KIT4M05799685DG5</t>
         </is>
       </c>
       <c r="F327" s="4" t="inlineStr">
         <is>
-          <t>816281</t>
+          <t>816271</t>
         </is>
       </c>
       <c r="G327" s="5" t="inlineStr">
@@ -17866,7 +17866,7 @@
       </c>
       <c r="B328" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437702 - KIT4M05872515PJT</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438062 - KIT4M05799676NNK</t>
         </is>
       </c>
       <c r="C328" s="3" t="n">
@@ -17877,12 +17877,12 @@
       </c>
       <c r="E328" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872515PJT</t>
+          <t>KIT4M05799676NNK</t>
         </is>
       </c>
       <c r="F328" s="4" t="inlineStr">
         <is>
-          <t>816218</t>
+          <t>816283</t>
         </is>
       </c>
       <c r="G328" s="5" t="inlineStr">
@@ -17919,7 +17919,7 @@
       </c>
       <c r="B329" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438062 - KIT4M05799676NNK</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437982 - KIT4M05799678R5P</t>
         </is>
       </c>
       <c r="C329" s="3" t="n">
@@ -17930,12 +17930,12 @@
       </c>
       <c r="E329" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799676NNK</t>
+          <t>KIT4M05799678R5P</t>
         </is>
       </c>
       <c r="F329" s="4" t="inlineStr">
         <is>
-          <t>816283</t>
+          <t>816281</t>
         </is>
       </c>
       <c r="G329" s="5" t="inlineStr">
@@ -17972,7 +17972,7 @@
       </c>
       <c r="B330" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438272 - KIT4M05872517VS2</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437702 - KIT4M05872515PJT</t>
         </is>
       </c>
       <c r="C330" s="3" t="n">
@@ -17983,12 +17983,12 @@
       </c>
       <c r="E330" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872517VS2</t>
+          <t>KIT4M05872515PJT</t>
         </is>
       </c>
       <c r="F330" s="4" t="inlineStr">
         <is>
-          <t>816288</t>
+          <t>816218</t>
         </is>
       </c>
       <c r="G330" s="5" t="inlineStr">
@@ -18025,7 +18025,7 @@
       </c>
       <c r="B331" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438142  - KIT4M05799685DG5</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020650222 - KIT4M05413790XCD</t>
         </is>
       </c>
       <c r="C331" s="3" t="n">
@@ -18036,12 +18036,12 @@
       </c>
       <c r="E331" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799685DG5</t>
+          <t>KIT4M05413790XCD</t>
         </is>
       </c>
       <c r="F331" s="4" t="inlineStr">
         <is>
-          <t>816271</t>
+          <t>812822</t>
         </is>
       </c>
       <c r="G331" s="5" t="inlineStr">
@@ -18979,7 +18979,7 @@
       </c>
       <c r="B349" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020650092 - KIT4M05413830JN7</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955512 - KIT4M055635779MM</t>
         </is>
       </c>
       <c r="C349" s="3" t="n">
@@ -18990,12 +18990,12 @@
       </c>
       <c r="E349" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413830JN7</t>
+          <t>KIT4M055635779MM</t>
         </is>
       </c>
       <c r="F349" s="4" t="inlineStr">
         <is>
-          <t>810105</t>
+          <t>814487</t>
         </is>
       </c>
       <c r="G349" s="5" t="inlineStr">
@@ -19032,7 +19032,7 @@
       </c>
       <c r="B350" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955442 - KIT4M05563503XXP</t>
+          <t>STS - 05900510 - Los Angeles CA - 020650092 - KIT4M05413830JN7</t>
         </is>
       </c>
       <c r="C350" s="3" t="n">
@@ -19043,12 +19043,12 @@
       </c>
       <c r="E350" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563503XXP</t>
+          <t>KIT4M05413830JN7</t>
         </is>
       </c>
       <c r="F350" s="4" t="inlineStr">
         <is>
-          <t>814430</t>
+          <t>810105</t>
         </is>
       </c>
       <c r="G350" s="5" t="inlineStr">
@@ -19085,7 +19085,7 @@
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955162 - KIT4M05563554WCW</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955442 - KIT4M05563503XXP</t>
         </is>
       </c>
       <c r="C351" s="3" t="n">
@@ -19096,12 +19096,12 @@
       </c>
       <c r="E351" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563554WCW</t>
+          <t>KIT4M05563503XXP</t>
         </is>
       </c>
       <c r="F351" s="4" t="inlineStr">
         <is>
-          <t>814444</t>
+          <t>814430</t>
         </is>
       </c>
       <c r="G351" s="5" t="inlineStr">
@@ -19191,7 +19191,7 @@
       </c>
       <c r="B353" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955222 - KIT4M05563536BPJ</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955562 - KIT4M05563505WPS</t>
         </is>
       </c>
       <c r="C353" s="3" t="n">
@@ -19202,12 +19202,12 @@
       </c>
       <c r="E353" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563536BPJ</t>
+          <t>KIT4M05563505WPS</t>
         </is>
       </c>
       <c r="F353" s="4" t="inlineStr">
         <is>
-          <t>814466</t>
+          <t>814448</t>
         </is>
       </c>
       <c r="G353" s="5" t="inlineStr">
@@ -19244,7 +19244,7 @@
       </c>
       <c r="B354" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955562 - KIT4M05563505WPS</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955222 - KIT4M05563536BPJ</t>
         </is>
       </c>
       <c r="C354" s="3" t="n">
@@ -19255,12 +19255,12 @@
       </c>
       <c r="E354" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563505WPS</t>
+          <t>KIT4M05563536BPJ</t>
         </is>
       </c>
       <c r="F354" s="4" t="inlineStr">
         <is>
-          <t>814448</t>
+          <t>814466</t>
         </is>
       </c>
       <c r="G354" s="5" t="inlineStr">
@@ -19509,7 +19509,7 @@
       </c>
       <c r="B359" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437922 - KIT4M05872496MW6</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438012 - KIT4M05799715GJ2</t>
         </is>
       </c>
       <c r="C359" s="3" t="n">
@@ -19520,24 +19520,16 @@
       </c>
       <c r="E359" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872496MW6</t>
-        </is>
-      </c>
-      <c r="F359" s="4" t="inlineStr">
-        <is>
-          <t>816206</t>
-        </is>
-      </c>
+          <t>KIT4M05799715GJ2</t>
+        </is>
+      </c>
+      <c r="F359" s="8" t="n"/>
       <c r="G359" s="5" t="inlineStr">
         <is>
           <t>Mini</t>
         </is>
       </c>
-      <c r="H359" s="5" t="inlineStr">
-        <is>
-          <t>Master Serial List</t>
-        </is>
-      </c>
+      <c r="H359" s="5" t="n"/>
       <c r="I359" s="6" t="n">
         <v>46235</v>
       </c>
@@ -19562,7 +19554,7 @@
       </c>
       <c r="B360" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438012 - KIT4M05799715GJ2</t>
+          <t>SMRT-05900510-Los Angeles CA-020650032-KIT4M05413802FVN</t>
         </is>
       </c>
       <c r="C360" s="3" t="n">
@@ -19573,16 +19565,24 @@
       </c>
       <c r="E360" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799715GJ2</t>
-        </is>
-      </c>
-      <c r="F360" s="8" t="n"/>
+          <t>KIT4M05413802FVN</t>
+        </is>
+      </c>
+      <c r="F360" s="4" t="inlineStr">
+        <is>
+          <t>812813</t>
+        </is>
+      </c>
       <c r="G360" s="5" t="inlineStr">
         <is>
           <t>Mini</t>
         </is>
       </c>
-      <c r="H360" s="5" t="n"/>
+      <c r="H360" s="5" t="inlineStr">
+        <is>
+          <t>Master Serial List</t>
+        </is>
+      </c>
       <c r="I360" s="6" t="n">
         <v>46235</v>
       </c>
@@ -19607,7 +19607,7 @@
       </c>
       <c r="B361" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649502 - KIT4M05413801QJB</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437922 - KIT4M05872496MW6</t>
         </is>
       </c>
       <c r="C361" s="3" t="n">
@@ -19618,12 +19618,12 @@
       </c>
       <c r="E361" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413801QJB</t>
+          <t>KIT4M05872496MW6</t>
         </is>
       </c>
       <c r="F361" s="4" t="inlineStr">
         <is>
-          <t>812824</t>
+          <t>816206</t>
         </is>
       </c>
       <c r="G361" s="5" t="inlineStr">
@@ -19660,7 +19660,7 @@
       </c>
       <c r="B362" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020650032-KIT4M05413802FVN</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649502 - KIT4M05413801QJB</t>
         </is>
       </c>
       <c r="C362" s="3" t="n">
@@ -19671,12 +19671,12 @@
       </c>
       <c r="E362" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413802FVN</t>
+          <t>KIT4M05413801QJB</t>
         </is>
       </c>
       <c r="F362" s="4" t="inlineStr">
         <is>
-          <t>812813</t>
+          <t>812824</t>
         </is>
       </c>
       <c r="G362" s="5" t="inlineStr">
@@ -19766,7 +19766,7 @@
       </c>
       <c r="B364" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955512 - KIT4M055635779MM</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955162 - KIT4M05563554WCW</t>
         </is>
       </c>
       <c r="C364" s="3" t="n">
@@ -19777,12 +19777,12 @@
       </c>
       <c r="E364" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635779MM</t>
+          <t>KIT4M05563554WCW</t>
         </is>
       </c>
       <c r="F364" s="4" t="inlineStr">
         <is>
-          <t>814487</t>
+          <t>814444</t>
         </is>
       </c>
       <c r="G364" s="5" t="inlineStr">
@@ -20219,7 +20219,7 @@
     <row r="381">
       <c r="A381" s="15" t="inlineStr">
         <is>
-          <t>Generated 2026-08-29 21:09 by build_starlink_usage.py</t>
+          <t>Generated 2026-08-30 09:35 by build_starlink_usage.py</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_Current_by_Kit.xlsx
+++ b/Starlink_Usage_Current_by_Kit.xlsx
@@ -630,7 +630,7 @@
       </c>
       <c r="L2" s="5" t="n"/>
       <c r="M2" s="7" t="n">
-        <v>2530.49</v>
+        <v>2545.68</v>
       </c>
     </row>
     <row r="3">
@@ -683,7 +683,7 @@
       </c>
       <c r="L3" s="5" t="n"/>
       <c r="M3" s="7" t="n">
-        <v>2298.41</v>
+        <v>2303.66</v>
       </c>
     </row>
     <row r="4">
@@ -736,7 +736,7 @@
       </c>
       <c r="L4" s="5" t="n"/>
       <c r="M4" s="7" t="n">
-        <v>1643.3</v>
+        <v>1645.47</v>
       </c>
     </row>
     <row r="5">
@@ -842,7 +842,7 @@
       </c>
       <c r="L6" s="5" t="n"/>
       <c r="M6" s="7" t="n">
-        <v>1133.29</v>
+        <v>1138.34</v>
       </c>
     </row>
     <row r="7">
@@ -895,7 +895,7 @@
       </c>
       <c r="L7" s="5" t="n"/>
       <c r="M7" s="7" t="n">
-        <v>1018.27</v>
+        <v>1034.93</v>
       </c>
     </row>
     <row r="8">
@@ -948,7 +948,7 @@
       </c>
       <c r="L8" s="5" t="n"/>
       <c r="M8" s="7" t="n">
-        <v>1005.66</v>
+        <v>1017.13</v>
       </c>
     </row>
     <row r="9">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="L13" s="5" t="n"/>
       <c r="M13" s="7" t="n">
-        <v>747.83</v>
+        <v>749.75</v>
       </c>
     </row>
     <row r="14">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L14" s="5" t="n"/>
       <c r="M14" s="7" t="n">
-        <v>730.71</v>
+        <v>734.04</v>
       </c>
     </row>
     <row r="15">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="L15" s="5" t="n"/>
       <c r="M15" s="7" t="n">
-        <v>694.25</v>
+        <v>696.64</v>
       </c>
     </row>
     <row r="16">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="L16" s="5" t="n"/>
       <c r="M16" s="7" t="n">
-        <v>689.3</v>
+        <v>691.78</v>
       </c>
     </row>
     <row r="17">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="L17" s="5" t="n"/>
       <c r="M17" s="7" t="n">
-        <v>613.42</v>
+        <v>614.96</v>
       </c>
     </row>
     <row r="18">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="L18" s="5" t="n"/>
       <c r="M18" s="7" t="n">
-        <v>532.45</v>
+        <v>547.35</v>
       </c>
     </row>
     <row r="19">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="L20" s="5" t="n"/>
       <c r="M20" s="7" t="n">
-        <v>463.25</v>
+        <v>471.14</v>
       </c>
     </row>
     <row r="21">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="L22" s="5" t="n"/>
       <c r="M22" s="7" t="n">
-        <v>401.08</v>
+        <v>401.2</v>
       </c>
     </row>
     <row r="23">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649242 - KIT4P00065644SB2</t>
+          <t>SMRT-05900510-LOS ANGELES CA-020955062-KIT4P00073915XX6</t>
         </is>
       </c>
       <c r="C25" s="3" t="n">
@@ -1818,12 +1818,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065644SB2</t>
+          <t>KIT4P00073915XX6</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>812928</t>
+          <t>814643</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="L25" s="5" t="n"/>
       <c r="M25" s="7" t="n">
-        <v>307.21</v>
+        <v>333.67</v>
       </c>
     </row>
     <row r="26">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-LOS ANGELES CA-020955062-KIT4P00073915XX6</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649242 - KIT4P00065644SB2</t>
         </is>
       </c>
       <c r="C26" s="3" t="n">
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073915XX6</t>
+          <t>KIT4P00065644SB2</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>814643</t>
+          <t>812928</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="L26" s="5" t="n"/>
       <c r="M26" s="7" t="n">
-        <v>306.11</v>
+        <v>307.21</v>
       </c>
     </row>
     <row r="27">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="L28" s="5" t="n"/>
       <c r="M28" s="7" t="n">
-        <v>275.65</v>
+        <v>275.96</v>
       </c>
     </row>
     <row r="29">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="L29" s="5" t="n"/>
       <c r="M29" s="7" t="n">
-        <v>269.87</v>
+        <v>274.1</v>
       </c>
     </row>
     <row r="30">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="L30" s="5" t="n"/>
       <c r="M30" s="7" t="n">
-        <v>259.24</v>
+        <v>259.29</v>
       </c>
     </row>
     <row r="31">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="L33" s="5" t="n"/>
       <c r="M33" s="7" t="n">
-        <v>238.45</v>
+        <v>243.29</v>
       </c>
     </row>
     <row r="34">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020649462-KIT4M05413796V9K</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955042 - KIT4P00072391SZM</t>
         </is>
       </c>
       <c r="C34" s="3" t="n">
@@ -2295,17 +2295,17 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413796V9K</t>
+          <t>KIT4P00072391SZM</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>812820</t>
+          <t>814493</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H34" s="5" t="inlineStr">
@@ -2326,7 +2326,7 @@
       </c>
       <c r="L34" s="5" t="n"/>
       <c r="M34" s="7" t="n">
-        <v>220.94</v>
+        <v>225.68</v>
       </c>
     </row>
     <row r="35">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955042 - KIT4P00072391SZM</t>
+          <t>SMRT-05900510-Los Angeles CA-020649462-KIT4M05413796V9K</t>
         </is>
       </c>
       <c r="C35" s="3" t="n">
@@ -2348,17 +2348,17 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00072391SZM</t>
+          <t>KIT4M05413796V9K</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>814493</t>
+          <t>812820</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="L35" s="5" t="n"/>
       <c r="M35" s="7" t="n">
-        <v>204.14</v>
+        <v>220.94</v>
       </c>
     </row>
     <row r="36">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955522 - KIT4M05563504MBB</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482701116 - KIT4M03986275Q4M</t>
         </is>
       </c>
       <c r="C36" s="3" t="n">
@@ -2401,12 +2401,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563504MBB</t>
+          <t>KIT4M03986275Q4M</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>814460</t>
+          <t>809621</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="L36" s="5" t="n"/>
       <c r="M36" s="7" t="n">
-        <v>198.62</v>
+        <v>204.16</v>
       </c>
     </row>
     <row r="37">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482701116 - KIT4M03986275Q4M</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955522 - KIT4M05563504MBB</t>
         </is>
       </c>
       <c r="C37" s="3" t="n">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03986275Q4M</t>
+          <t>KIT4M05563504MBB</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>809621</t>
+          <t>814460</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="L37" s="5" t="n"/>
       <c r="M37" s="7" t="n">
-        <v>186.16</v>
+        <v>203.67</v>
       </c>
     </row>
     <row r="38">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="L38" s="5" t="n"/>
       <c r="M38" s="7" t="n">
-        <v>172.99</v>
+        <v>177.87</v>
       </c>
     </row>
     <row r="39">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955322 - KIT4M055635305RS</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955182 - KIT4M05563562F45</t>
         </is>
       </c>
       <c r="C39" s="3" t="n">
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635305RS</t>
+          <t>KIT4M05563562F45</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>814440</t>
+          <t>814443</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="L39" s="5" t="n"/>
       <c r="M39" s="7" t="n">
-        <v>171.56</v>
+        <v>173.95</v>
       </c>
     </row>
     <row r="40">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955182 - KIT4M05563562F45</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955322 - KIT4M055635305RS</t>
         </is>
       </c>
       <c r="C40" s="3" t="n">
@@ -2613,12 +2613,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563562F45</t>
+          <t>KIT4M055635305RS</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>814443</t>
+          <t>814440</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="L40" s="5" t="n"/>
       <c r="M40" s="7" t="n">
-        <v>167.19</v>
+        <v>171.56</v>
       </c>
     </row>
     <row r="41">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="L41" s="5" t="n"/>
       <c r="M41" s="7" t="n">
-        <v>149.34</v>
+        <v>151.32</v>
       </c>
     </row>
     <row r="42">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="L44" s="5" t="n"/>
       <c r="M44" s="7" t="n">
-        <v>137.62</v>
+        <v>138.21</v>
       </c>
     </row>
     <row r="45">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="L45" s="5" t="n"/>
       <c r="M45" s="7" t="n">
-        <v>129.97</v>
+        <v>129.99</v>
       </c>
     </row>
     <row r="46">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955632 - KIT4M055635329VD</t>
+          <t>SS - 05900510 - Los Angeles CA - 020650102 - KIT4M054138257Z7</t>
         </is>
       </c>
       <c r="C48" s="3" t="n">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635329VD</t>
+          <t>KIT4M054138257Z7</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>814479</t>
+          <t>810106</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="L48" s="5" t="n"/>
       <c r="M48" s="7" t="n">
-        <v>124.26</v>
+        <v>125.77</v>
       </c>
     </row>
     <row r="49">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020650102 - KIT4M054138257Z7</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955632 - KIT4M055635329VD</t>
         </is>
       </c>
       <c r="C49" s="3" t="n">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138257Z7</t>
+          <t>KIT4M055635329VD</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>810106</t>
+          <t>814479</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="L49" s="5" t="n"/>
       <c r="M49" s="7" t="n">
-        <v>122.65</v>
+        <v>124.35</v>
       </c>
     </row>
     <row r="50">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020955622 - KIT4M05563549RSR</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020650212 - KIT4M05413779VSD</t>
         </is>
       </c>
       <c r="C51" s="3" t="n">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563549RSR</t>
+          <t>KIT4M05413779VSD</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>814483</t>
+          <t>810103</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="L51" s="5" t="n"/>
       <c r="M51" s="7" t="n">
-        <v>113.16</v>
+        <v>113.23</v>
       </c>
     </row>
     <row r="52">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020650212 - KIT4M05413779VSD</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020955622 - KIT4M05563549RSR</t>
         </is>
       </c>
       <c r="C52" s="3" t="n">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413779VSD</t>
+          <t>KIT4M05563549RSR</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>810103</t>
+          <t>814483</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="L52" s="5" t="n"/>
       <c r="M52" s="7" t="n">
-        <v>113.12</v>
+        <v>113.16</v>
       </c>
     </row>
     <row r="53">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649542 - KIT4M05413810Q4Z</t>
+          <t>SMRT-05900510-Los Angeles, CA-020955372-KIT4M05563537G4G</t>
         </is>
       </c>
       <c r="C53" s="3" t="n">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413810Q4Z</t>
+          <t>KIT4M05563537G4G</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>812815</t>
+          <t>814456</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="L53" s="5" t="n"/>
       <c r="M53" s="7" t="n">
-        <v>109.7</v>
+        <v>112.54</v>
       </c>
     </row>
     <row r="54">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270111110 - KIT4M03867737P9P</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649542 - KIT4M05413810Q4Z</t>
         </is>
       </c>
       <c r="C54" s="3" t="n">
@@ -3355,12 +3355,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03867737P9P</t>
+          <t>KIT4M05413810Q4Z</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>809622</t>
+          <t>812815</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="L54" s="5" t="n"/>
       <c r="M54" s="7" t="n">
-        <v>108.88</v>
+        <v>109.7</v>
       </c>
     </row>
     <row r="55">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles, CA-020955372-KIT4M05563537G4G</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270111110 - KIT4M03867737P9P</t>
         </is>
       </c>
       <c r="C55" s="3" t="n">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563537G4G</t>
+          <t>KIT4M03867737P9P</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>814456</t>
+          <t>809622</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="L55" s="5" t="n"/>
       <c r="M55" s="7" t="n">
-        <v>108.22</v>
+        <v>109.44</v>
       </c>
     </row>
     <row r="56">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="L56" s="5" t="n"/>
       <c r="M56" s="7" t="n">
-        <v>105.49</v>
+        <v>107.23</v>
       </c>
     </row>
     <row r="57">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="L57" s="5" t="n"/>
       <c r="M57" s="7" t="n">
-        <v>103.74</v>
+        <v>106.06</v>
       </c>
     </row>
     <row r="58">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="L58" s="5" t="n"/>
       <c r="M58" s="7" t="n">
-        <v>99.62</v>
+        <v>100.22</v>
       </c>
     </row>
     <row r="59">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955332 - KIT4M05563590ZFQ</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649712 - KIT4M046047397TM</t>
         </is>
       </c>
       <c r="C60" s="3" t="n">
@@ -3673,12 +3673,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563590ZFQ</t>
+          <t>KIT4M046047397TM</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>814461</t>
+          <t>809863</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="L60" s="5" t="n"/>
       <c r="M60" s="7" t="n">
-        <v>95.19</v>
+        <v>98.28</v>
       </c>
     </row>
     <row r="61">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438042 - KIT4M05799686CMX</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955332 - KIT4M05563590ZFQ</t>
         </is>
       </c>
       <c r="C61" s="3" t="n">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799686CMX</t>
+          <t>KIT4M05563590ZFQ</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>816282</t>
+          <t>814461</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
@@ -3757,7 +3757,7 @@
       </c>
       <c r="L61" s="5" t="n"/>
       <c r="M61" s="7" t="n">
-        <v>94.92</v>
+        <v>95.59999999999999</v>
       </c>
     </row>
     <row r="62">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020650232 - KIT4M054138222CP</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438042 - KIT4M05799686CMX</t>
         </is>
       </c>
       <c r="C62" s="3" t="n">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138222CP</t>
+          <t>KIT4M05799686CMX</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>812811</t>
+          <t>816282</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="L62" s="5" t="n"/>
       <c r="M62" s="7" t="n">
-        <v>93.27</v>
+        <v>94.92</v>
       </c>
     </row>
     <row r="63">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649712 - KIT4M046047397TM</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955112 - KIT4P00073918HBX</t>
         </is>
       </c>
       <c r="C63" s="3" t="n">
@@ -3832,17 +3832,17 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047397TM</t>
+          <t>KIT4P00073918HBX</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>809863</t>
+          <t>814645</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H63" s="5" t="inlineStr">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="L63" s="5" t="n"/>
       <c r="M63" s="7" t="n">
-        <v>92.65000000000001</v>
+        <v>93.39</v>
       </c>
     </row>
     <row r="64">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955112 - KIT4P00073918HBX</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020650232 - KIT4M054138222CP</t>
         </is>
       </c>
       <c r="C64" s="3" t="n">
@@ -3885,17 +3885,17 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073918HBX</t>
+          <t>KIT4M054138222CP</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>814645</t>
+          <t>812811</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H64" s="5" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="L64" s="5" t="n"/>
       <c r="M64" s="7" t="n">
-        <v>90.26000000000001</v>
+        <v>93.27</v>
       </c>
     </row>
     <row r="65">
@@ -3927,7 +3927,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955472 - KIT4M055635834N7</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438092 - KIT4M05799694RW2</t>
         </is>
       </c>
       <c r="C65" s="3" t="n">
@@ -3938,12 +3938,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635834N7</t>
+          <t>KIT4M05799694RW2</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>814462</t>
+          <t>816277</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="L65" s="5" t="n"/>
       <c r="M65" s="7" t="n">
-        <v>89.45</v>
+        <v>91.25</v>
       </c>
     </row>
     <row r="66">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438092 - KIT4M05799694RW2</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955472 - KIT4M055635834N7</t>
         </is>
       </c>
       <c r="C66" s="3" t="n">
@@ -3991,12 +3991,12 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799694RW2</t>
+          <t>KIT4M055635834N7</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>816277</t>
+          <t>814462</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="L66" s="5" t="n"/>
       <c r="M66" s="7" t="n">
-        <v>89.01000000000001</v>
+        <v>89.45999999999999</v>
       </c>
     </row>
     <row r="67">
@@ -4033,7 +4033,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955142 - KIT4M05563518ZJD</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955132 - KIT4M055635238J6</t>
         </is>
       </c>
       <c r="C67" s="3" t="n">
@@ -4044,12 +4044,12 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563518ZJD</t>
+          <t>KIT4M055635238J6</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>814451</t>
+          <t>814449</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="L67" s="5" t="n"/>
       <c r="M67" s="7" t="n">
-        <v>85.18000000000001</v>
+        <v>86.86</v>
       </c>
     </row>
     <row r="68">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955132 - KIT4M055635238J6</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955142 - KIT4M05563518ZJD</t>
         </is>
       </c>
       <c r="C68" s="3" t="n">
@@ -4097,12 +4097,12 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635238J6</t>
+          <t>KIT4M05563518ZJD</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>814449</t>
+          <t>814451</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="L68" s="5" t="n"/>
       <c r="M68" s="7" t="n">
-        <v>84.23</v>
+        <v>85.18000000000001</v>
       </c>
     </row>
     <row r="69">
@@ -4139,7 +4139,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649872 - KIT4M054138175VJ</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437272 - KIT4P0008459589D</t>
         </is>
       </c>
       <c r="C69" s="3" t="n">
@@ -4150,17 +4150,17 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138175VJ</t>
+          <t>KIT4P0008459589D</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>812823</t>
+          <t>816222</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H69" s="5" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="L69" s="5" t="n"/>
       <c r="M69" s="7" t="n">
-        <v>83.95</v>
+        <v>84.73</v>
       </c>
     </row>
     <row r="70">
@@ -4192,7 +4192,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020649312-KIT4M05413771PVH</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649872 - KIT4M054138175VJ</t>
         </is>
       </c>
       <c r="C70" s="3" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413771PVH</t>
+          <t>KIT4M054138175VJ</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>812800</t>
+          <t>812823</t>
         </is>
       </c>
       <c r="G70" s="5" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="L70" s="5" t="n"/>
       <c r="M70" s="7" t="n">
-        <v>81.16</v>
+        <v>83.95</v>
       </c>
     </row>
     <row r="71">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020650012 - KIT4M05413814GPJ</t>
+          <t>SMRT-05900510-Los Angeles CA-020649312-KIT4M05413771PVH</t>
         </is>
       </c>
       <c r="C71" s="3" t="n">
@@ -4256,12 +4256,12 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413814GPJ</t>
+          <t>KIT4M05413771PVH</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>812812</t>
+          <t>812800</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
@@ -4287,7 +4287,7 @@
       </c>
       <c r="L71" s="5" t="n"/>
       <c r="M71" s="7" t="n">
-        <v>79.23</v>
+        <v>81.34999999999999</v>
       </c>
     </row>
     <row r="72">
@@ -4298,7 +4298,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437272 - KIT4P0008459589D</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020650012 - KIT4M05413814GPJ</t>
         </is>
       </c>
       <c r="C72" s="3" t="n">
@@ -4309,17 +4309,17 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0008459589D</t>
+          <t>KIT4M05413814GPJ</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>816222</t>
+          <t>812812</t>
         </is>
       </c>
       <c r="G72" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H72" s="5" t="inlineStr">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="L72" s="5" t="n"/>
       <c r="M72" s="7" t="n">
-        <v>77.8</v>
+        <v>81.06</v>
       </c>
     </row>
     <row r="73">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955492 - KIT4M05563520SH2</t>
+          <t>SMRT-05900510-Los Angeles, CA-020955352-KIT4M05563525VC6</t>
         </is>
       </c>
       <c r="C74" s="3" t="n">
@@ -4415,12 +4415,12 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563520SH2</t>
+          <t>KIT4M05563525VC6</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>814478</t>
+          <t>814458</t>
         </is>
       </c>
       <c r="G74" s="5" t="inlineStr">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="L74" s="5" t="n"/>
       <c r="M74" s="7" t="n">
-        <v>74.56999999999999</v>
+        <v>75.01000000000001</v>
       </c>
     </row>
     <row r="75">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955092 - KIT4P00073957GV5</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955492 - KIT4M05563520SH2</t>
         </is>
       </c>
       <c r="C75" s="3" t="n">
@@ -4468,17 +4468,17 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073957GV5</t>
+          <t>KIT4M05563520SH2</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>814642</t>
+          <t>814478</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H75" s="5" t="inlineStr">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="L75" s="5" t="n"/>
       <c r="M75" s="7" t="n">
-        <v>72.91</v>
+        <v>74.56999999999999</v>
       </c>
     </row>
     <row r="76">
@@ -4552,7 +4552,7 @@
       </c>
       <c r="L76" s="5" t="n"/>
       <c r="M76" s="7" t="n">
-        <v>72.59999999999999</v>
+        <v>73.87</v>
       </c>
     </row>
     <row r="77">
@@ -4563,7 +4563,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles, CA-020955352-KIT4M05563525VC6</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955092 - KIT4P00073957GV5</t>
         </is>
       </c>
       <c r="C77" s="3" t="n">
@@ -4574,17 +4574,17 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563525VC6</t>
+          <t>KIT4P00073957GV5</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>814458</t>
+          <t>814642</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H77" s="5" t="inlineStr">
@@ -4605,7 +4605,7 @@
       </c>
       <c r="L77" s="5" t="n"/>
       <c r="M77" s="7" t="n">
-        <v>72.45</v>
+        <v>72.95</v>
       </c>
     </row>
     <row r="78">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="L78" s="5" t="n"/>
       <c r="M78" s="7" t="n">
-        <v>71.52</v>
+        <v>72.64</v>
       </c>
     </row>
     <row r="79">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="L79" s="5" t="n"/>
       <c r="M79" s="7" t="n">
-        <v>70.56</v>
+        <v>70.63</v>
       </c>
     </row>
     <row r="80">
@@ -4764,7 +4764,7 @@
       </c>
       <c r="L80" s="5" t="n"/>
       <c r="M80" s="7" t="n">
-        <v>69.23</v>
+        <v>70.61</v>
       </c>
     </row>
     <row r="81">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649902 - KIT4M05413805MKQ</t>
+          <t>SS - 05900510 -  Los Angeles CA - 021437622 - KIT4M0587258755W</t>
         </is>
       </c>
       <c r="C83" s="3" t="n">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413805MKQ</t>
+          <t>KIT4M0587258755W</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>812849</t>
+          <t>816187</t>
         </is>
       </c>
       <c r="G83" s="5" t="inlineStr">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="L83" s="5" t="n"/>
       <c r="M83" s="7" t="n">
-        <v>66.45</v>
+        <v>68</v>
       </c>
     </row>
     <row r="84">
@@ -4934,7 +4934,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-LOS ANGELES CA-020955202-KIT4M05563534GZ7</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649902 - KIT4M05413805MKQ</t>
         </is>
       </c>
       <c r="C84" s="3" t="n">
@@ -4945,12 +4945,12 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563534GZ7</t>
+          <t>KIT4M05413805MKQ</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>814467</t>
+          <t>812849</t>
         </is>
       </c>
       <c r="G84" s="5" t="inlineStr">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="L84" s="5" t="n"/>
       <c r="M84" s="7" t="n">
-        <v>66.15000000000001</v>
+        <v>66.45</v>
       </c>
     </row>
     <row r="85">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 021437622 - KIT4M0587258755W</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649212 - KIT4P00065633ZXC</t>
         </is>
       </c>
       <c r="C85" s="3" t="n">
@@ -4998,17 +4998,17 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0587258755W</t>
+          <t>KIT4P00065633ZXC</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>816187</t>
+          <t>812922</t>
         </is>
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H85" s="5" t="inlineStr">
@@ -5029,7 +5029,7 @@
       </c>
       <c r="L85" s="5" t="n"/>
       <c r="M85" s="7" t="n">
-        <v>65.16</v>
+        <v>66.38</v>
       </c>
     </row>
     <row r="86">
@@ -5040,7 +5040,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649342 - KIT4M05413775N9M</t>
+          <t>SMRT-05900510-LOS ANGELES CA-020955202-KIT4M05563534GZ7</t>
         </is>
       </c>
       <c r="C86" s="3" t="n">
@@ -5051,12 +5051,12 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413775N9M</t>
+          <t>KIT4M05563534GZ7</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>812818</t>
+          <t>814467</t>
         </is>
       </c>
       <c r="G86" s="5" t="inlineStr">
@@ -5082,7 +5082,7 @@
       </c>
       <c r="L86" s="5" t="n"/>
       <c r="M86" s="7" t="n">
-        <v>64.45</v>
+        <v>66.22</v>
       </c>
     </row>
     <row r="87">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="L87" s="5" t="n"/>
       <c r="M87" s="7" t="n">
-        <v>64.27</v>
+        <v>64.81999999999999</v>
       </c>
     </row>
     <row r="88">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437392 - KIT4M05872555BJR</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649342 - KIT4M05413775N9M</t>
         </is>
       </c>
       <c r="C88" s="3" t="n">
@@ -5157,12 +5157,12 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872555BJR</t>
+          <t>KIT4M05413775N9M</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>816074</t>
+          <t>812818</t>
         </is>
       </c>
       <c r="G88" s="5" t="inlineStr">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="L88" s="5" t="n"/>
       <c r="M88" s="7" t="n">
-        <v>62.09</v>
+        <v>64.48999999999999</v>
       </c>
     </row>
     <row r="89">
@@ -5199,7 +5199,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020650252 - KIT4M05413820QXJ</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437392 - KIT4M05872555BJR</t>
         </is>
       </c>
       <c r="C89" s="3" t="n">
@@ -5210,12 +5210,12 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413820QXJ</t>
+          <t>KIT4M05872555BJR</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>810098</t>
+          <t>816074</t>
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr">
@@ -5241,7 +5241,7 @@
       </c>
       <c r="L89" s="5" t="n"/>
       <c r="M89" s="7" t="n">
-        <v>61.69</v>
+        <v>63.26</v>
       </c>
     </row>
     <row r="90">
@@ -5252,7 +5252,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955692 - KIT4M05563579H9F</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020650252 - KIT4M05413820QXJ</t>
         </is>
       </c>
       <c r="C90" s="3" t="n">
@@ -5263,12 +5263,12 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563579H9F</t>
+          <t>KIT4M05413820QXJ</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>814480</t>
+          <t>810098</t>
         </is>
       </c>
       <c r="G90" s="5" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="L90" s="5" t="n"/>
       <c r="M90" s="7" t="n">
-        <v>59.68</v>
+        <v>61.69</v>
       </c>
     </row>
     <row r="91">
@@ -5305,7 +5305,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020955462 - KIT4M05563513GTF</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955692 - KIT4M05563579H9F</t>
         </is>
       </c>
       <c r="C91" s="3" t="n">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563513GTF</t>
+          <t>KIT4M05563579H9F</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>814432</t>
+          <t>814480</t>
         </is>
       </c>
       <c r="G91" s="5" t="inlineStr">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="L91" s="5" t="n"/>
       <c r="M91" s="7" t="n">
-        <v>59.65</v>
+        <v>61.03</v>
       </c>
     </row>
     <row r="92">
@@ -5358,7 +5358,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649762 - KIT4M0460475549Z</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020955462 - KIT4M05563513GTF</t>
         </is>
       </c>
       <c r="C92" s="3" t="n">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0460475549Z</t>
+          <t>KIT4M05563513GTF</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>809859</t>
+          <t>814432</t>
         </is>
       </c>
       <c r="G92" s="5" t="inlineStr">
@@ -5400,7 +5400,7 @@
       </c>
       <c r="L92" s="5" t="n"/>
       <c r="M92" s="7" t="n">
-        <v>58.39</v>
+        <v>60.61</v>
       </c>
     </row>
     <row r="93">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482704 - KIT4M04604745G8Z</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649762 - KIT4M0460475549Z</t>
         </is>
       </c>
       <c r="C93" s="3" t="n">
@@ -5422,12 +5422,12 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604745G8Z</t>
+          <t>KIT4M0460475549Z</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>809661</t>
+          <t>809859</t>
         </is>
       </c>
       <c r="G93" s="5" t="inlineStr">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="L93" s="5" t="n"/>
       <c r="M93" s="7" t="n">
-        <v>57.14</v>
+        <v>60.32</v>
       </c>
     </row>
     <row r="94">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827011118 - KIT4M03867766NGK</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482704 - KIT4M04604745G8Z</t>
         </is>
       </c>
       <c r="C94" s="3" t="n">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03867766NGK</t>
+          <t>KIT4M04604745G8Z</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>809615</t>
+          <t>809661</t>
         </is>
       </c>
       <c r="G94" s="5" t="inlineStr">
@@ -5506,7 +5506,7 @@
       </c>
       <c r="L94" s="5" t="n"/>
       <c r="M94" s="7" t="n">
-        <v>56.55</v>
+        <v>57.53</v>
       </c>
     </row>
     <row r="95">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955412 - KIT4M05563598Z74</t>
+          <t>SS - 05900510 - Los Angeles CA - 020650042 - KIT4M05413819JV5</t>
         </is>
       </c>
       <c r="C95" s="3" t="n">
@@ -5528,12 +5528,12 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563598Z74</t>
+          <t>KIT4M05413819JV5</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>814474</t>
+          <t>812796</t>
         </is>
       </c>
       <c r="G95" s="5" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="L95" s="5" t="n"/>
       <c r="M95" s="7" t="n">
-        <v>55.57</v>
+        <v>57.31</v>
       </c>
     </row>
     <row r="96">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270112 - KIT4M044751638F5</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827011118 - KIT4M03867766NGK</t>
         </is>
       </c>
       <c r="C96" s="3" t="n">
@@ -5581,12 +5581,12 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>KIT4M044751638F5</t>
+          <t>KIT4M03867766NGK</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>809618</t>
+          <t>809615</t>
         </is>
       </c>
       <c r="G96" s="5" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="L96" s="5" t="n"/>
       <c r="M96" s="7" t="n">
-        <v>54.28</v>
+        <v>57.05</v>
       </c>
     </row>
     <row r="97">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955692 - KIT4M05563603CP4</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955412 - KIT4M05563598Z74</t>
         </is>
       </c>
       <c r="C97" s="3" t="n">
@@ -5634,12 +5634,12 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563603CP4</t>
+          <t>KIT4M05563598Z74</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>814447</t>
+          <t>814474</t>
         </is>
       </c>
       <c r="G97" s="5" t="inlineStr">
@@ -5665,7 +5665,7 @@
       </c>
       <c r="L97" s="5" t="n"/>
       <c r="M97" s="7" t="n">
-        <v>54.23</v>
+        <v>55.57</v>
       </c>
     </row>
     <row r="98">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020650042 - KIT4M05413819JV5</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955692 - KIT4M05563603CP4</t>
         </is>
       </c>
       <c r="C98" s="3" t="n">
@@ -5687,12 +5687,12 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413819JV5</t>
+          <t>KIT4M05563603CP4</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>812796</t>
+          <t>814447</t>
         </is>
       </c>
       <c r="G98" s="5" t="inlineStr">
@@ -5718,7 +5718,7 @@
       </c>
       <c r="L98" s="5" t="n"/>
       <c r="M98" s="7" t="n">
-        <v>53.68</v>
+        <v>54.88</v>
       </c>
     </row>
     <row r="99">
@@ -5729,7 +5729,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649372 - KIT4M05368221HQ5</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270112 - KIT4M044751638F5</t>
         </is>
       </c>
       <c r="C99" s="3" t="n">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368221HQ5</t>
+          <t>KIT4M044751638F5</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>810834</t>
+          <t>809618</t>
         </is>
       </c>
       <c r="G99" s="5" t="inlineStr">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="L99" s="5" t="n"/>
       <c r="M99" s="7" t="n">
-        <v>53.65</v>
+        <v>54.6</v>
       </c>
     </row>
     <row r="100">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles, CA - 0204827011112 - KIT4M04158967K28</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649372 - KIT4M05368221HQ5</t>
         </is>
       </c>
       <c r="C100" s="3" t="n">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158967K28</t>
+          <t>KIT4M05368221HQ5</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>809620</t>
+          <t>810834</t>
         </is>
       </c>
       <c r="G100" s="5" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="L100" s="5" t="n"/>
       <c r="M100" s="7" t="n">
-        <v>51.87</v>
+        <v>53.65</v>
       </c>
     </row>
     <row r="101">
@@ -5835,7 +5835,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955702 - KIT4M05563571G8W</t>
+          <t>STS - 05900510 - Los Angeles, CA - 0204827011112 - KIT4M04158967K28</t>
         </is>
       </c>
       <c r="C101" s="3" t="n">
@@ -5846,12 +5846,12 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563571G8W</t>
+          <t>KIT4M04158967K28</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>814481</t>
+          <t>809620</t>
         </is>
       </c>
       <c r="G101" s="5" t="inlineStr">
@@ -5877,7 +5877,7 @@
       </c>
       <c r="L101" s="5" t="n"/>
       <c r="M101" s="7" t="n">
-        <v>51.58</v>
+        <v>52.05</v>
       </c>
     </row>
     <row r="102">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827016 - KIT4M041536494G6</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955702 - KIT4M05563571G8W</t>
         </is>
       </c>
       <c r="C102" s="3" t="n">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>KIT4M041536494G6</t>
+          <t>KIT4M05563571G8W</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>809617</t>
+          <t>814481</t>
         </is>
       </c>
       <c r="G102" s="5" t="inlineStr">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="L102" s="5" t="n"/>
       <c r="M102" s="7" t="n">
-        <v>51.33</v>
+        <v>51.85</v>
       </c>
     </row>
     <row r="103">
@@ -5941,7 +5941,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020650142 - KIT4M05413839D24</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827016 - KIT4M041536494G6</t>
         </is>
       </c>
       <c r="C103" s="3" t="n">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413839D24</t>
+          <t>KIT4M041536494G6</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>810096</t>
+          <t>809617</t>
         </is>
       </c>
       <c r="G103" s="5" t="inlineStr">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="L103" s="5" t="n"/>
       <c r="M103" s="7" t="n">
-        <v>50.33</v>
+        <v>51.67</v>
       </c>
     </row>
     <row r="104">
@@ -5994,7 +5994,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270111114 - KIT4P00065593VWC</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020650142 - KIT4M05413839D24</t>
         </is>
       </c>
       <c r="C104" s="3" t="n">
@@ -6005,17 +6005,17 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065593VWC</t>
+          <t>KIT4M05413839D24</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>809606</t>
+          <t>810096</t>
         </is>
       </c>
       <c r="G104" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H104" s="5" t="inlineStr">
@@ -6036,7 +6036,7 @@
       </c>
       <c r="L104" s="5" t="n"/>
       <c r="M104" s="7" t="n">
-        <v>49.23</v>
+        <v>50.33</v>
       </c>
     </row>
     <row r="105">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020650202-KIT4M05413803FDK</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649442 - KIT4M054137885SM</t>
         </is>
       </c>
       <c r="C105" s="3" t="n">
@@ -6058,12 +6058,12 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413803FDK</t>
+          <t>KIT4M054137885SM</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>812850</t>
+          <t>812846</t>
         </is>
       </c>
       <c r="G105" s="5" t="inlineStr">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="L105" s="5" t="n"/>
       <c r="M105" s="7" t="n">
-        <v>47.53</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="106">
@@ -6100,7 +6100,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649212 - KIT4P00065633ZXC</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270111114 - KIT4P00065593VWC</t>
         </is>
       </c>
       <c r="C106" s="3" t="n">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065633ZXC</t>
+          <t>KIT4P00065593VWC</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>812922</t>
+          <t>809606</t>
         </is>
       </c>
       <c r="G106" s="5" t="inlineStr">
@@ -6142,7 +6142,7 @@
       </c>
       <c r="L106" s="5" t="n"/>
       <c r="M106" s="7" t="n">
-        <v>46.95</v>
+        <v>49.23</v>
       </c>
     </row>
     <row r="107">
@@ -6153,7 +6153,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649832 - KIT4M03866596RZG</t>
+          <t>SMRT-05900510-Los Angeles CA-020650202-KIT4M05413803FDK</t>
         </is>
       </c>
       <c r="C107" s="3" t="n">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03866596RZG</t>
+          <t>KIT4M05413803FDK</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>809869</t>
+          <t>812850</t>
         </is>
       </c>
       <c r="G107" s="5" t="inlineStr">
@@ -6195,7 +6195,7 @@
       </c>
       <c r="L107" s="5" t="n"/>
       <c r="M107" s="7" t="n">
-        <v>46.83</v>
+        <v>48.51</v>
       </c>
     </row>
     <row r="108">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649672 - KIT4M04606113TPB</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649832 - KIT4M03866596RZG</t>
         </is>
       </c>
       <c r="C108" s="3" t="n">
@@ -6217,12 +6217,12 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04606113TPB</t>
+          <t>KIT4M03866596RZG</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>809862</t>
+          <t>809869</t>
         </is>
       </c>
       <c r="G108" s="5" t="inlineStr">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="L108" s="5" t="n"/>
       <c r="M108" s="7" t="n">
-        <v>46.74</v>
+        <v>48.12</v>
       </c>
     </row>
     <row r="109">
@@ -6259,7 +6259,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles, CA-020955452-KIT4M05563529K2D</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649672 - KIT4M04606113TPB</t>
         </is>
       </c>
       <c r="C109" s="3" t="n">
@@ -6270,12 +6270,12 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563529K2D</t>
+          <t>KIT4M04606113TPB</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>814473</t>
+          <t>809862</t>
         </is>
       </c>
       <c r="G109" s="5" t="inlineStr">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="L109" s="5" t="n"/>
       <c r="M109" s="7" t="n">
-        <v>46.61</v>
+        <v>46.74</v>
       </c>
     </row>
     <row r="110">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649812 - KIT4M04604742S6S</t>
+          <t>SMRT-05900510-Los Angeles, CA-020955452-KIT4M05563529K2D</t>
         </is>
       </c>
       <c r="C110" s="3" t="n">
@@ -6323,12 +6323,12 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604742S6S</t>
+          <t>KIT4M05563529K2D</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>809874</t>
+          <t>814473</t>
         </is>
       </c>
       <c r="G110" s="5" t="inlineStr">
@@ -6354,7 +6354,7 @@
       </c>
       <c r="L110" s="5" t="n"/>
       <c r="M110" s="7" t="n">
-        <v>43.24</v>
+        <v>46.61</v>
       </c>
     </row>
     <row r="111">
@@ -6365,7 +6365,7 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649432 - KIT4M05413778RBR</t>
+          <t>SS - 05900510 -  Los Angeles CA - 021438232 - KIT4M05872520QJM</t>
         </is>
       </c>
       <c r="C111" s="3" t="n">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413778RBR</t>
+          <t>KIT4M05872520QJM</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>812843</t>
+          <t>816078</t>
         </is>
       </c>
       <c r="G111" s="5" t="inlineStr">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="L111" s="5" t="n"/>
       <c r="M111" s="7" t="n">
-        <v>42.82</v>
+        <v>44.93</v>
       </c>
     </row>
     <row r="112">
@@ -6418,7 +6418,7 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020955652 - KIT4M0556358988Z</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955272 - KIT4M05563585TXM</t>
         </is>
       </c>
       <c r="C112" s="3" t="n">
@@ -6429,12 +6429,12 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0556358988Z</t>
+          <t>KIT4M05563585TXM</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>814484</t>
+          <t>814475</t>
         </is>
       </c>
       <c r="G112" s="5" t="inlineStr">
@@ -6460,7 +6460,7 @@
       </c>
       <c r="L112" s="5" t="n"/>
       <c r="M112" s="7" t="n">
-        <v>42.76</v>
+        <v>44.12</v>
       </c>
     </row>
     <row r="113">
@@ -6471,7 +6471,7 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955272 - KIT4M05563585TXM</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649812 - KIT4M04604742S6S</t>
         </is>
       </c>
       <c r="C113" s="3" t="n">
@@ -6482,12 +6482,12 @@
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563585TXM</t>
+          <t>KIT4M04604742S6S</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>814475</t>
+          <t>809874</t>
         </is>
       </c>
       <c r="G113" s="5" t="inlineStr">
@@ -6513,7 +6513,7 @@
       </c>
       <c r="L113" s="5" t="n"/>
       <c r="M113" s="7" t="n">
-        <v>42.74</v>
+        <v>43.24</v>
       </c>
     </row>
     <row r="114">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020650192 - KIT4M054138007JF</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020955652 - KIT4M0556358988Z</t>
         </is>
       </c>
       <c r="C114" s="3" t="n">
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138007JF</t>
+          <t>KIT4M0556358988Z</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>810095</t>
+          <t>814484</t>
         </is>
       </c>
       <c r="G114" s="5" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="L114" s="5" t="n"/>
       <c r="M114" s="7" t="n">
-        <v>42.59</v>
+        <v>42.98</v>
       </c>
     </row>
     <row r="115">
@@ -6577,7 +6577,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020650052 - KIT4M05413781K6C</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649432 - KIT4M05413778RBR</t>
         </is>
       </c>
       <c r="C115" s="3" t="n">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413781K6C</t>
+          <t>KIT4M05413778RBR</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>812798</t>
+          <t>812843</t>
         </is>
       </c>
       <c r="G115" s="5" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="L115" s="5" t="n"/>
       <c r="M115" s="7" t="n">
-        <v>42.04</v>
+        <v>42.82</v>
       </c>
     </row>
     <row r="116">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270116 - KIT4M03476116F45</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020650192 - KIT4M054138007JF</t>
         </is>
       </c>
       <c r="C116" s="3" t="n">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03476116F45</t>
+          <t>KIT4M054138007JF</t>
         </is>
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>809608</t>
+          <t>810095</t>
         </is>
       </c>
       <c r="G116" s="5" t="inlineStr">
@@ -6672,7 +6672,7 @@
       </c>
       <c r="L116" s="5" t="n"/>
       <c r="M116" s="7" t="n">
-        <v>41.44</v>
+        <v>42.59</v>
       </c>
     </row>
     <row r="117">
@@ -6683,7 +6683,7 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 020955382 - KIT4M05563509CHJ</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020650052 - KIT4M05413781K6C</t>
         </is>
       </c>
       <c r="C117" s="3" t="n">
@@ -6694,12 +6694,12 @@
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563509CHJ</t>
+          <t>KIT4M05413781K6C</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>814431</t>
+          <t>812798</t>
         </is>
       </c>
       <c r="G117" s="5" t="inlineStr">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="L117" s="5" t="n"/>
       <c r="M117" s="7" t="n">
-        <v>40.86</v>
+        <v>42.04</v>
       </c>
     </row>
     <row r="118">
@@ -6778,7 +6778,7 @@
       </c>
       <c r="L118" s="5" t="n"/>
       <c r="M118" s="7" t="n">
-        <v>40.63</v>
+        <v>41.61</v>
       </c>
     </row>
     <row r="119">
@@ -6789,7 +6789,7 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 021438232 - KIT4M05872520QJM</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270116 - KIT4M03476116F45</t>
         </is>
       </c>
       <c r="C119" s="3" t="n">
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872520QJM</t>
+          <t>KIT4M03476116F45</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>816078</t>
+          <t>809608</t>
         </is>
       </c>
       <c r="G119" s="5" t="inlineStr">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="L119" s="5" t="n"/>
       <c r="M119" s="7" t="n">
-        <v>39.83</v>
+        <v>41.44</v>
       </c>
     </row>
     <row r="120">
@@ -6842,7 +6842,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649682 - KIT4M046047384RX</t>
+          <t>SS - 05900510 -  Los Angeles CA - 020955382 - KIT4M05563509CHJ</t>
         </is>
       </c>
       <c r="C120" s="3" t="n">
@@ -6853,12 +6853,12 @@
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047384RX</t>
+          <t>KIT4M05563509CHJ</t>
         </is>
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t>809870</t>
+          <t>814431</t>
         </is>
       </c>
       <c r="G120" s="5" t="inlineStr">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="L120" s="5" t="n"/>
       <c r="M120" s="7" t="n">
-        <v>39.38</v>
+        <v>40.96</v>
       </c>
     </row>
     <row r="121">
@@ -6895,7 +6895,7 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955602 - KIT4M05563560225</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649682 - KIT4M046047384RX</t>
         </is>
       </c>
       <c r="C121" s="3" t="n">
@@ -6906,12 +6906,12 @@
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563560225</t>
+          <t>KIT4M046047384RX</t>
         </is>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>814454</t>
+          <t>809870</t>
         </is>
       </c>
       <c r="G121" s="5" t="inlineStr">
@@ -6937,7 +6937,7 @@
       </c>
       <c r="L121" s="5" t="n"/>
       <c r="M121" s="7" t="n">
-        <v>38.09</v>
+        <v>39.73</v>
       </c>
     </row>
     <row r="122">
@@ -6990,7 +6990,7 @@
       </c>
       <c r="L122" s="5" t="n"/>
       <c r="M122" s="7" t="n">
-        <v>37.82</v>
+        <v>39.52</v>
       </c>
     </row>
     <row r="123">
@@ -7001,7 +7001,7 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020650082 - KIT4M05413792H8C</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482701112 - KIT4M04158973M2C</t>
         </is>
       </c>
       <c r="C123" s="3" t="n">
@@ -7012,12 +7012,12 @@
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413792H8C</t>
+          <t>KIT4M04158973M2C</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>812803</t>
+          <t>809610</t>
         </is>
       </c>
       <c r="G123" s="5" t="inlineStr">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="L123" s="5" t="n"/>
       <c r="M123" s="7" t="n">
-        <v>37.81</v>
+        <v>38.34</v>
       </c>
     </row>
     <row r="124">
@@ -7054,7 +7054,7 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482701112 - KIT4M04158973M2C</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955602 - KIT4M05563560225</t>
         </is>
       </c>
       <c r="C124" s="3" t="n">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158973M2C</t>
+          <t>KIT4M05563560225</t>
         </is>
       </c>
       <c r="F124" s="4" t="inlineStr">
         <is>
-          <t>809610</t>
+          <t>814454</t>
         </is>
       </c>
       <c r="G124" s="5" t="inlineStr">
@@ -7096,7 +7096,7 @@
       </c>
       <c r="L124" s="5" t="n"/>
       <c r="M124" s="7" t="n">
-        <v>36.43</v>
+        <v>38.09</v>
       </c>
     </row>
     <row r="125">
@@ -7107,7 +7107,7 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020650112 - KIT4M05413840D9J</t>
+          <t>STS - 05900510 - Los Angeles CA - 020650082 - KIT4M05413792H8C</t>
         </is>
       </c>
       <c r="C125" s="3" t="n">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413840D9J</t>
+          <t>KIT4M05413792H8C</t>
         </is>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>810099</t>
+          <t>812803</t>
         </is>
       </c>
       <c r="G125" s="5" t="inlineStr">
@@ -7149,7 +7149,7 @@
       </c>
       <c r="L125" s="5" t="n"/>
       <c r="M125" s="7" t="n">
-        <v>35.17</v>
+        <v>37.81</v>
       </c>
     </row>
     <row r="126">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="L126" s="5" t="n"/>
       <c r="M126" s="7" t="n">
-        <v>35.08</v>
+        <v>37.55</v>
       </c>
     </row>
     <row r="127">
@@ -7213,7 +7213,7 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649942 - KIT4M05413786BXC</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020650112 - KIT4M05413840D9J</t>
         </is>
       </c>
       <c r="C127" s="3" t="n">
@@ -7224,12 +7224,12 @@
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413786BXC</t>
+          <t>KIT4M05413840D9J</t>
         </is>
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>812838</t>
+          <t>810099</t>
         </is>
       </c>
       <c r="G127" s="5" t="inlineStr">
@@ -7255,7 +7255,7 @@
       </c>
       <c r="L127" s="5" t="n"/>
       <c r="M127" s="7" t="n">
-        <v>34.4</v>
+        <v>35.21</v>
       </c>
     </row>
     <row r="128">
@@ -7266,7 +7266,7 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649442 - KIT4M054137885SM</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649592 - KIT4M05413787HHK</t>
         </is>
       </c>
       <c r="C128" s="3" t="n">
@@ -7277,12 +7277,12 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137885SM</t>
+          <t>KIT4M05413787HHK</t>
         </is>
       </c>
       <c r="F128" s="4" t="inlineStr">
         <is>
-          <t>812846</t>
+          <t>812809</t>
         </is>
       </c>
       <c r="G128" s="5" t="inlineStr">
@@ -7308,7 +7308,7 @@
       </c>
       <c r="L128" s="5" t="n"/>
       <c r="M128" s="7" t="n">
-        <v>32.77</v>
+        <v>34.61</v>
       </c>
     </row>
     <row r="129">
@@ -7319,7 +7319,7 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649412 - KIT4M05413769796</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649942 - KIT4M05413786BXC</t>
         </is>
       </c>
       <c r="C129" s="3" t="n">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413769796</t>
+          <t>KIT4M05413786BXC</t>
         </is>
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>812839</t>
+          <t>812838</t>
         </is>
       </c>
       <c r="G129" s="5" t="inlineStr">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="L129" s="5" t="n"/>
       <c r="M129" s="7" t="n">
-        <v>32.57</v>
+        <v>34.4</v>
       </c>
     </row>
     <row r="130">
@@ -7372,7 +7372,7 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482706 - KIT4M04604744V6K</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649412 - KIT4M05413769796</t>
         </is>
       </c>
       <c r="C130" s="3" t="n">
@@ -7383,12 +7383,12 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604744V6K</t>
+          <t>KIT4M05413769796</t>
         </is>
       </c>
       <c r="F130" s="4" t="inlineStr">
         <is>
-          <t>809659</t>
+          <t>812839</t>
         </is>
       </c>
       <c r="G130" s="5" t="inlineStr">
@@ -7414,7 +7414,7 @@
       </c>
       <c r="L130" s="5" t="n"/>
       <c r="M130" s="7" t="n">
-        <v>31.38</v>
+        <v>32.57</v>
       </c>
     </row>
     <row r="131">
@@ -7425,7 +7425,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 6858375 - KIT4M05872512N5W</t>
+          <t>SMA - 05900510 -  Los Angeles CA - 020649512 - KIT4M054138318Q7</t>
         </is>
       </c>
       <c r="C131" s="3" t="n">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872512N5W</t>
+          <t>KIT4M054138318Q7</t>
         </is>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>816077</t>
+          <t>812814</t>
         </is>
       </c>
       <c r="G131" s="5" t="inlineStr">
@@ -7467,7 +7467,7 @@
       </c>
       <c r="L131" s="5" t="n"/>
       <c r="M131" s="7" t="n">
-        <v>31.1</v>
+        <v>32.07</v>
       </c>
     </row>
     <row r="132">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="L132" s="5" t="n"/>
       <c r="M132" s="7" t="n">
-        <v>31.1</v>
+        <v>31.69</v>
       </c>
     </row>
     <row r="133">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438002 - KIT4M05799701SGS</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482706 - KIT4M04604744V6K</t>
         </is>
       </c>
       <c r="C133" s="3" t="n">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799701SGS</t>
+          <t>KIT4M04604744V6K</t>
         </is>
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>816284</t>
+          <t>809659</t>
         </is>
       </c>
       <c r="G133" s="5" t="inlineStr">
@@ -7573,7 +7573,7 @@
       </c>
       <c r="L133" s="5" t="n"/>
       <c r="M133" s="7" t="n">
-        <v>30.71</v>
+        <v>31.38</v>
       </c>
     </row>
     <row r="134">
@@ -7584,7 +7584,7 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 -  Los Angeles CA - 020649512 - KIT4M054138318Q7</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438002 - KIT4M05799701SGS</t>
         </is>
       </c>
       <c r="C134" s="3" t="n">
@@ -7595,12 +7595,12 @@
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138318Q7</t>
+          <t>KIT4M05799701SGS</t>
         </is>
       </c>
       <c r="F134" s="4" t="inlineStr">
         <is>
-          <t>812814</t>
+          <t>816284</t>
         </is>
       </c>
       <c r="G134" s="5" t="inlineStr">
@@ -7626,7 +7626,7 @@
       </c>
       <c r="L134" s="5" t="n"/>
       <c r="M134" s="7" t="n">
-        <v>30.7</v>
+        <v>31.24</v>
       </c>
     </row>
     <row r="135">
@@ -7637,7 +7637,7 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649822 - KIT4M04604740BM6</t>
+          <t>SS - 05900510 - Los Angeles CA - 6858375 - KIT4M05872512N5W</t>
         </is>
       </c>
       <c r="C135" s="3" t="n">
@@ -7648,12 +7648,12 @@
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604740BM6</t>
+          <t>KIT4M05872512N5W</t>
         </is>
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>809872</t>
+          <t>816077</t>
         </is>
       </c>
       <c r="G135" s="5" t="inlineStr">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="L135" s="5" t="n"/>
       <c r="M135" s="7" t="n">
-        <v>29.72</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="136">
@@ -7690,7 +7690,7 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437992 -  KIT4M05799663CPM</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649452 - KIT4M05413785QCG</t>
         </is>
       </c>
       <c r="C136" s="3" t="n">
@@ -7701,12 +7701,12 @@
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799663CPM</t>
+          <t>KIT4M05413785QCG</t>
         </is>
       </c>
       <c r="F136" s="4" t="inlineStr">
         <is>
-          <t>816272</t>
+          <t>812806</t>
         </is>
       </c>
       <c r="G136" s="5" t="inlineStr">
@@ -7732,7 +7732,7 @@
       </c>
       <c r="L136" s="5" t="n"/>
       <c r="M136" s="7" t="n">
-        <v>29.7</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="137">
@@ -7743,7 +7743,7 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020649292-KIT4M05368201SNV</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649822 - KIT4M04604740BM6</t>
         </is>
       </c>
       <c r="C137" s="3" t="n">
@@ -7754,12 +7754,12 @@
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368201SNV</t>
+          <t>KIT4M04604740BM6</t>
         </is>
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>810651</t>
+          <t>809872</t>
         </is>
       </c>
       <c r="G137" s="5" t="inlineStr">
@@ -7785,7 +7785,7 @@
       </c>
       <c r="L137" s="5" t="n"/>
       <c r="M137" s="7" t="n">
-        <v>28.18</v>
+        <v>30.04</v>
       </c>
     </row>
     <row r="138">
@@ -7796,7 +7796,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649592 - KIT4M05413787HHK</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437992 -  KIT4M05799663CPM</t>
         </is>
       </c>
       <c r="C138" s="3" t="n">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413787HHK</t>
+          <t>KIT4M05799663CPM</t>
         </is>
       </c>
       <c r="F138" s="4" t="inlineStr">
         <is>
-          <t>812809</t>
+          <t>816272</t>
         </is>
       </c>
       <c r="G138" s="5" t="inlineStr">
@@ -7838,7 +7838,7 @@
       </c>
       <c r="L138" s="5" t="n"/>
       <c r="M138" s="7" t="n">
-        <v>28.08</v>
+        <v>30.03</v>
       </c>
     </row>
     <row r="139">
@@ -7849,7 +7849,7 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649452 - KIT4M05413785QCG</t>
+          <t>SMRT-05900510-Los Angeles CA-020649292-KIT4M05368201SNV</t>
         </is>
       </c>
       <c r="C139" s="3" t="n">
@@ -7860,12 +7860,12 @@
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413785QCG</t>
+          <t>KIT4M05368201SNV</t>
         </is>
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>812806</t>
+          <t>810651</t>
         </is>
       </c>
       <c r="G139" s="5" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="L139" s="5" t="n"/>
       <c r="M139" s="7" t="n">
-        <v>27.96</v>
+        <v>29.33</v>
       </c>
     </row>
     <row r="140">
@@ -8008,7 +8008,7 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955342 - KIT4M05563524MJ4</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020650162 - KIT4M05413837SMB</t>
         </is>
       </c>
       <c r="C142" s="3" t="n">
@@ -8019,12 +8019,12 @@
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563524MJ4</t>
+          <t>KIT4M05413837SMB</t>
         </is>
       </c>
       <c r="F142" s="4" t="inlineStr">
         <is>
-          <t>814472</t>
+          <t>810100</t>
         </is>
       </c>
       <c r="G142" s="5" t="inlineStr">
@@ -8050,7 +8050,7 @@
       </c>
       <c r="L142" s="5" t="n"/>
       <c r="M142" s="7" t="n">
-        <v>26.26</v>
+        <v>26.75</v>
       </c>
     </row>
     <row r="143">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020650162 - KIT4M05413837SMB</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955342 - KIT4M05563524MJ4</t>
         </is>
       </c>
       <c r="C143" s="3" t="n">
@@ -8072,12 +8072,12 @@
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413837SMB</t>
+          <t>KIT4M05563524MJ4</t>
         </is>
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>810100</t>
+          <t>814472</t>
         </is>
       </c>
       <c r="G143" s="5" t="inlineStr">
@@ -8103,7 +8103,7 @@
       </c>
       <c r="L143" s="5" t="n"/>
       <c r="M143" s="7" t="n">
-        <v>25.59</v>
+        <v>26.26</v>
       </c>
     </row>
     <row r="144">
@@ -8114,7 +8114,7 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649362 - KIT4M05368336DBC</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438242 - KIT4M058725094XP</t>
         </is>
       </c>
       <c r="C144" s="3" t="n">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368336DBC</t>
+          <t>KIT4M058725094XP</t>
         </is>
       </c>
       <c r="F144" s="4" t="inlineStr">
         <is>
-          <t>810831</t>
+          <t>816085</t>
         </is>
       </c>
       <c r="G144" s="5" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="L144" s="5" t="n"/>
       <c r="M144" s="7" t="n">
-        <v>25.14</v>
+        <v>25.33</v>
       </c>
     </row>
     <row r="145">
@@ -8167,7 +8167,7 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955212 - KIT4M05563512GBQ</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649492 - KIT4M054138074NS</t>
         </is>
       </c>
       <c r="C145" s="3" t="n">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563512GBQ</t>
+          <t>KIT4M054138074NS</t>
         </is>
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>814435</t>
+          <t>812816</t>
         </is>
       </c>
       <c r="G145" s="5" t="inlineStr">
@@ -8209,7 +8209,7 @@
       </c>
       <c r="L145" s="5" t="n"/>
       <c r="M145" s="7" t="n">
-        <v>24.55</v>
+        <v>25.31</v>
       </c>
     </row>
     <row r="146">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438242 - KIT4M058725094XP</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649362 - KIT4M05368336DBC</t>
         </is>
       </c>
       <c r="C146" s="3" t="n">
@@ -8231,12 +8231,12 @@
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725094XP</t>
+          <t>KIT4M05368336DBC</t>
         </is>
       </c>
       <c r="F146" s="4" t="inlineStr">
         <is>
-          <t>816085</t>
+          <t>810831</t>
         </is>
       </c>
       <c r="G146" s="5" t="inlineStr">
@@ -8262,7 +8262,7 @@
       </c>
       <c r="L146" s="5" t="n"/>
       <c r="M146" s="7" t="n">
-        <v>24.37</v>
+        <v>25.14</v>
       </c>
     </row>
     <row r="147">
@@ -8273,7 +8273,7 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955532 - KIT4M05563548P9Q</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955212 - KIT4M05563512GBQ</t>
         </is>
       </c>
       <c r="C147" s="3" t="n">
@@ -8284,12 +8284,12 @@
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563548P9Q</t>
+          <t>KIT4M05563512GBQ</t>
         </is>
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>814468</t>
+          <t>814435</t>
         </is>
       </c>
       <c r="G147" s="5" t="inlineStr">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="L147" s="5" t="n"/>
       <c r="M147" s="7" t="n">
-        <v>23.04</v>
+        <v>24.55</v>
       </c>
     </row>
     <row r="148">
@@ -8326,7 +8326,7 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438222 - KIT4M058725299QP</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955532 - KIT4M05563548P9Q</t>
         </is>
       </c>
       <c r="C148" s="3" t="n">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725299QP</t>
+          <t>KIT4M05563548P9Q</t>
         </is>
       </c>
       <c r="F148" s="4" t="inlineStr">
         <is>
-          <t>816080</t>
+          <t>814468</t>
         </is>
       </c>
       <c r="G148" s="5" t="inlineStr">
@@ -8368,7 +8368,7 @@
       </c>
       <c r="L148" s="5" t="n"/>
       <c r="M148" s="7" t="n">
-        <v>22.96</v>
+        <v>23.1</v>
       </c>
     </row>
     <row r="149">
@@ -8379,7 +8379,7 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020650242 - KIT4M05413804SKS</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438222 - KIT4M058725299QP</t>
         </is>
       </c>
       <c r="C149" s="3" t="n">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413804SKS</t>
+          <t>KIT4M058725299QP</t>
         </is>
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>810102</t>
+          <t>816080</t>
         </is>
       </c>
       <c r="G149" s="5" t="inlineStr">
@@ -8421,7 +8421,7 @@
       </c>
       <c r="L149" s="5" t="n"/>
       <c r="M149" s="7" t="n">
-        <v>22.64</v>
+        <v>22.96</v>
       </c>
     </row>
     <row r="150">
@@ -8432,7 +8432,7 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649492 - KIT4M054138074NS</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020650242 - KIT4M05413804SKS</t>
         </is>
       </c>
       <c r="C150" s="3" t="n">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138074NS</t>
+          <t>KIT4M05413804SKS</t>
         </is>
       </c>
       <c r="F150" s="4" t="inlineStr">
         <is>
-          <t>812816</t>
+          <t>810102</t>
         </is>
       </c>
       <c r="G150" s="5" t="inlineStr">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="L150" s="5" t="n"/>
       <c r="M150" s="7" t="n">
-        <v>21.81</v>
+        <v>22.68</v>
       </c>
     </row>
     <row r="151">
@@ -8485,7 +8485,7 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020650132-KIT4M05413828PCT</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438072 - KIT4M057996885ZV</t>
         </is>
       </c>
       <c r="C151" s="3" t="n">
@@ -8496,12 +8496,12 @@
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413828PCT</t>
+          <t>KIT4M057996885ZV</t>
         </is>
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>812799</t>
+          <t>816269</t>
         </is>
       </c>
       <c r="G151" s="5" t="inlineStr">
@@ -8527,7 +8527,7 @@
       </c>
       <c r="L151" s="5" t="n"/>
       <c r="M151" s="7" t="n">
-        <v>21.54</v>
+        <v>21.96</v>
       </c>
     </row>
     <row r="152">
@@ -8538,7 +8538,7 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438072 - KIT4M057996885ZV</t>
+          <t>SMRT-05900510-Los Angeles CA-020650132-KIT4M05413828PCT</t>
         </is>
       </c>
       <c r="C152" s="3" t="n">
@@ -8549,12 +8549,12 @@
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>KIT4M057996885ZV</t>
+          <t>KIT4M05413828PCT</t>
         </is>
       </c>
       <c r="F152" s="4" t="inlineStr">
         <is>
-          <t>816269</t>
+          <t>812799</t>
         </is>
       </c>
       <c r="G152" s="5" t="inlineStr">
@@ -8580,7 +8580,7 @@
       </c>
       <c r="L152" s="5" t="n"/>
       <c r="M152" s="7" t="n">
-        <v>21.52</v>
+        <v>21.54</v>
       </c>
     </row>
     <row r="153">
@@ -8591,7 +8591,7 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-LOS ANGELES CA-020955172-KIT4M05563526WNC</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827011116 - KIT4M02578775B9Q</t>
         </is>
       </c>
       <c r="C153" s="3" t="n">
@@ -8602,12 +8602,12 @@
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563526WNC</t>
+          <t>KIT4M02578775B9Q</t>
         </is>
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>814463</t>
+          <t>809611</t>
         </is>
       </c>
       <c r="G153" s="5" t="inlineStr">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="L153" s="5" t="n"/>
       <c r="M153" s="7" t="n">
-        <v>21.16</v>
+        <v>21.52</v>
       </c>
     </row>
     <row r="154">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020650072-KIT4M054137987GJ</t>
+          <t>SMRT-05900510-LOS ANGELES CA-020955172-KIT4M05563526WNC</t>
         </is>
       </c>
       <c r="C154" s="3" t="n">
@@ -8655,12 +8655,12 @@
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137987GJ</t>
+          <t>KIT4M05563526WNC</t>
         </is>
       </c>
       <c r="F154" s="4" t="inlineStr">
         <is>
-          <t>812795</t>
+          <t>814463</t>
         </is>
       </c>
       <c r="G154" s="5" t="inlineStr">
@@ -8686,7 +8686,7 @@
       </c>
       <c r="L154" s="5" t="n"/>
       <c r="M154" s="7" t="n">
-        <v>20.74</v>
+        <v>21.16</v>
       </c>
     </row>
     <row r="155">
@@ -8697,7 +8697,7 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649222 - KIT4P00065640BFW</t>
+          <t>SMRT-05900510-Los Angeles CA-020650072-KIT4M054137987GJ</t>
         </is>
       </c>
       <c r="C155" s="3" t="n">
@@ -8708,17 +8708,17 @@
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065640BFW</t>
+          <t>KIT4M054137987GJ</t>
         </is>
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>812929</t>
+          <t>812795</t>
         </is>
       </c>
       <c r="G155" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H155" s="5" t="inlineStr">
@@ -8739,7 +8739,7 @@
       </c>
       <c r="L155" s="5" t="n"/>
       <c r="M155" s="7" t="n">
-        <v>19.87</v>
+        <v>20.86</v>
       </c>
     </row>
     <row r="156">
@@ -8750,7 +8750,7 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649912 - KIT4M05413836KJC</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649222 - KIT4P00065640BFW</t>
         </is>
       </c>
       <c r="C156" s="3" t="n">
@@ -8761,17 +8761,17 @@
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413836KJC</t>
+          <t>KIT4P00065640BFW</t>
         </is>
       </c>
       <c r="F156" s="4" t="inlineStr">
         <is>
-          <t>810097</t>
+          <t>812929</t>
         </is>
       </c>
       <c r="G156" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H156" s="5" t="inlineStr">
@@ -8792,7 +8792,7 @@
       </c>
       <c r="L156" s="5" t="n"/>
       <c r="M156" s="7" t="n">
-        <v>19.73</v>
+        <v>19.87</v>
       </c>
     </row>
     <row r="157">
@@ -8803,7 +8803,7 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649302 - KIT4M05368226W57</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649912 - KIT4M05413836KJC</t>
         </is>
       </c>
       <c r="C157" s="3" t="n">
@@ -8814,12 +8814,12 @@
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368226W57</t>
+          <t>KIT4M05413836KJC</t>
         </is>
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>810833</t>
+          <t>810097</t>
         </is>
       </c>
       <c r="G157" s="5" t="inlineStr">
@@ -8845,7 +8845,7 @@
       </c>
       <c r="L157" s="5" t="n"/>
       <c r="M157" s="7" t="n">
-        <v>19.62</v>
+        <v>19.73</v>
       </c>
     </row>
     <row r="158">
@@ -8856,7 +8856,7 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955302 - KIT4M055635158PC</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649302 - KIT4M05368226W57</t>
         </is>
       </c>
       <c r="C158" s="3" t="n">
@@ -8867,12 +8867,12 @@
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635158PC</t>
+          <t>KIT4M05368226W57</t>
         </is>
       </c>
       <c r="F158" s="4" t="inlineStr">
         <is>
-          <t>814457</t>
+          <t>810833</t>
         </is>
       </c>
       <c r="G158" s="5" t="inlineStr">
@@ -8898,7 +8898,7 @@
       </c>
       <c r="L158" s="5" t="n"/>
       <c r="M158" s="7" t="n">
-        <v>19.59</v>
+        <v>19.62</v>
       </c>
     </row>
     <row r="159">
@@ -8909,7 +8909,7 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955282 - KIT4M055635227ZR</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955302 - KIT4M055635158PC</t>
         </is>
       </c>
       <c r="C159" s="3" t="n">
@@ -8920,12 +8920,12 @@
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635227ZR</t>
+          <t>KIT4M055635158PC</t>
         </is>
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>814482</t>
+          <t>814457</t>
         </is>
       </c>
       <c r="G159" s="5" t="inlineStr">
@@ -8951,7 +8951,7 @@
       </c>
       <c r="L159" s="5" t="n"/>
       <c r="M159" s="7" t="n">
-        <v>19.17</v>
+        <v>19.59</v>
       </c>
     </row>
     <row r="160">
@@ -8962,7 +8962,7 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649322 - KIT4M053683324KZ</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020650262 - KIT4M054138249M8</t>
         </is>
       </c>
       <c r="C160" s="3" t="n">
@@ -8973,12 +8973,12 @@
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>KIT4M053683324KZ</t>
+          <t>KIT4M054138249M8</t>
         </is>
       </c>
       <c r="F160" s="4" t="inlineStr">
         <is>
-          <t>810832</t>
+          <t>812794</t>
         </is>
       </c>
       <c r="G160" s="5" t="inlineStr">
@@ -9004,7 +9004,7 @@
       </c>
       <c r="L160" s="5" t="n"/>
       <c r="M160" s="7" t="n">
-        <v>18.89</v>
+        <v>19.38</v>
       </c>
     </row>
     <row r="161">
@@ -9015,7 +9015,7 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020650262 - KIT4M054138249M8</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955282 - KIT4M055635227ZR</t>
         </is>
       </c>
       <c r="C161" s="3" t="n">
@@ -9026,12 +9026,12 @@
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138249M8</t>
+          <t>KIT4M055635227ZR</t>
         </is>
       </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
-          <t>812794</t>
+          <t>814482</t>
         </is>
       </c>
       <c r="G161" s="5" t="inlineStr">
@@ -9057,7 +9057,7 @@
       </c>
       <c r="L161" s="5" t="n"/>
       <c r="M161" s="7" t="n">
-        <v>18.49</v>
+        <v>19.17</v>
       </c>
     </row>
     <row r="162">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA  - 020649722 - KIT4M04604747TPT</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649322 - KIT4M053683324KZ</t>
         </is>
       </c>
       <c r="C162" s="3" t="n">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604747TPT</t>
+          <t>KIT4M053683324KZ</t>
         </is>
       </c>
       <c r="F162" s="4" t="inlineStr">
         <is>
-          <t>809873</t>
+          <t>810832</t>
         </is>
       </c>
       <c r="G162" s="5" t="inlineStr">
@@ -9110,7 +9110,7 @@
       </c>
       <c r="L162" s="5" t="n"/>
       <c r="M162" s="7" t="n">
-        <v>18.44</v>
+        <v>18.89</v>
       </c>
     </row>
     <row r="163">
@@ -9121,7 +9121,7 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827010 - KIT4M046047372KJ</t>
+          <t>SS - 05900510 - Los Angeles, CA  - 020649722 - KIT4M04604747TPT</t>
         </is>
       </c>
       <c r="C163" s="3" t="n">
@@ -9132,12 +9132,12 @@
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047372KJ</t>
+          <t>KIT4M04604747TPT</t>
         </is>
       </c>
       <c r="F163" s="4" t="inlineStr">
         <is>
-          <t>809658</t>
+          <t>809873</t>
         </is>
       </c>
       <c r="G163" s="5" t="inlineStr">
@@ -9163,7 +9163,7 @@
       </c>
       <c r="L163" s="5" t="n"/>
       <c r="M163" s="7" t="n">
-        <v>17.99</v>
+        <v>18.44</v>
       </c>
     </row>
     <row r="164">
@@ -9174,7 +9174,7 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649632 - KIT4M054138064J9</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827010 - KIT4M046047372KJ</t>
         </is>
       </c>
       <c r="C164" s="3" t="n">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138064J9</t>
+          <t>KIT4M046047372KJ</t>
         </is>
       </c>
       <c r="F164" s="4" t="inlineStr">
         <is>
-          <t>812844</t>
+          <t>809658</t>
         </is>
       </c>
       <c r="G164" s="5" t="inlineStr">
@@ -9216,7 +9216,7 @@
       </c>
       <c r="L164" s="5" t="n"/>
       <c r="M164" s="7" t="n">
-        <v>17.18</v>
+        <v>18.15</v>
       </c>
     </row>
     <row r="165">
@@ -9227,7 +9227,7 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482708 - KIT4M04604736T7C</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020649252 - KIT4P00066848VQM</t>
         </is>
       </c>
       <c r="C165" s="3" t="n">
@@ -9238,17 +9238,17 @@
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604736T7C</t>
+          <t>KIT4P00066848VQM</t>
         </is>
       </c>
       <c r="F165" s="4" t="inlineStr">
         <is>
-          <t>809662</t>
+          <t>812923</t>
         </is>
       </c>
       <c r="G165" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H165" s="5" t="inlineStr">
@@ -9269,7 +9269,7 @@
       </c>
       <c r="L165" s="5" t="n"/>
       <c r="M165" s="7" t="n">
-        <v>16.93</v>
+        <v>17.63</v>
       </c>
     </row>
     <row r="166">
@@ -9280,7 +9280,7 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955362 - KIT4M05563528MKX</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482708 - KIT4M04604736T7C</t>
         </is>
 